--- a/engineering/drainage-design/retention_volume/Volume_Retention_Ponceau_900.xlsx
+++ b/engineering/drainage-design/retention_volume/Volume_Retention_Ponceau_900.xlsx
@@ -147,7 +147,6 @@
     <xf numFmtId="1" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -167,6 +166,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1338,7 +1338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1656,25 +1656,30 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Résultats (formules — feuille Calcul_A)</t>
+          <t>Résultats Méthode A — Qout constant (feuille Calcul_A)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Vmax (m³)</t>
+          <t>Vmax_A (m³)</t>
         </is>
       </c>
       <c r="B27" s="18">
         <f>Calcul_A!B3</f>
         <v/>
       </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Volume max stocké avec Qout fixe (Parametres B22)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>V_dimensionnement = Vmax × facteur (m³)</t>
+          <t>V_dimensionnement_A = Vmax_A × facteur (m³)</t>
         </is>
       </c>
       <c r="B28" s="18">
@@ -1685,7 +1690,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hmax approx (m) = Vmax / Aire</t>
+          <t>Hmax approx_A (m) = Vmax_A / Aire</t>
         </is>
       </c>
       <c r="B29" s="19">
@@ -1694,14 +1699,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Estimation grossière si l'aire de bassin est constante</t>
+          <t>Estimation grossière si l'aire de bassin est constante (pas le levé)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>WSEmax depuis levé (m) — feuille Stage_Storage</t>
+          <t>WSEmax_A depuis levé (m) — feuille Stage_Storage</t>
         </is>
       </c>
       <c r="B30" s="20">
@@ -1710,14 +1715,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Niveau d'eau max lu sur courbe volume–cote du levé (recommandé)</t>
+          <t>Cote d'eau max pour le Vmax_A: on lit sur Stage_Storage quelle WSE donne ce volume (courbe volume–cote du levé)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HW max = WSEmax − radier Ø900 (m)</t>
+          <t>HW max_A = WSEmax_A − radier Ø900 (m)</t>
         </is>
       </c>
       <c r="B31" s="20">
@@ -1733,165 +1738,246 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Inlet control vs outlet control — qu'est-ce que ça veut dire?</t>
+          <t>Résultats Méthode B — Qout = f(H) FHWA (feuille Calcul_B)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>• Inlet control (contrôle à l'entrée): le débit est limité par l'entrée du ponceau (forme d'entrée, HW/D).</t>
+          <t>Vmax_B (m³)</t>
+        </is>
+      </c>
+      <c r="B34" s="18">
+        <f>Calcul_B!B7</f>
+        <v/>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Volume max stocké avec Q lu sur Courbe_QH_900 (dépend de Aire B24)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Le tuyau aval « n'aspire » pas assez pour influencer — Q dépend surtout de la charge amont H, pas de L ni de n.</t>
-        </is>
+          <t>V_dimensionnement_B = Vmax_B × facteur (m³)</t>
+        </is>
+      </c>
+      <c r="B35" s="18">
+        <f>B34*B23</f>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>• Outlet control (contrôle à la sortie / frottement): le débit dépend de la longueur, de n, de la pente et de la charge</t>
+          <t>WSEmax_B depuis levé (m) — feuille Stage_Storage</t>
+        </is>
+      </c>
+      <c r="B36" s="20">
+        <f>IF(B34&lt;=Stage_Storage!E11,Stage_Storage!A11,IF(B34&gt;=Stage_Storage!E18,"Hors table (&gt;=39.5 m — étendre levé)",INDEX(Stage_Storage!$A$11:$A$18,MATCH(B34,Stage_Storage!$E$11:$E$18,1))+(B34-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B34,Stage_Storage!$E$11:$E$18,1)))/(INDEX(Stage_Storage!$E$11:$E$18,MATCH(B34,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B34,Stage_Storage!$E$11:$E$18,1)))*(INDEX(Stage_Storage!$A$11:$A$18,MATCH(B34,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(B34,Stage_Storage!$E$11:$E$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Même lecture volume→cote que B30, mais avec Vmax_B au lieu de Vmax_A</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (énergie amont → aval). Manning pleine section est une hypothèse de type outlet/frottement à section pleine.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>• Ici L/D = 56 (tuyau assez long) → le contrôle par frottement (outlet) est souvent plausible,</t>
+          <t>HW max_B = WSEmax_B − radier Ø900 (m)</t>
+        </is>
+      </c>
+      <c r="B37" s="20">
+        <f>IF(ISNUMBER(B36),B36-34.88,"")</f>
+        <v/>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Comparer à 2.40 m (limite patron)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  mais sans analyse FHWA/HY-8 on ne peut pas l'affirmer. Pour dimensionner la rétention, Q_plein constant est</t>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Comment lire WSEmax (A ou B)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">  en général prudent (si la charge monte, le débit réel peut être un peu plus élevé → Vmax un peu plus bas).</t>
+          <t>1) Calcul_A (ou B) donne un volume max stocké Vmax pendant l'orage.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>• On n'a pas besoin de trancher IC/OC pour utiliser ce classeur: garder Qout = Q_plein (ou 1.77) suffit pour une 1re estimation.</t>
+          <t>2) La feuille Stage_Storage convertit vos surfaces de levé en courbe: volume cumulé ↔ cote d'eau (WSE).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>3) WSEmax = la cote sur cette courbe qui correspond à ce Vmax (interpolation).</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Notes</t>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Exemple: si Vmax_A ≈ volume entre 37.28 m et 39.5 m sur le levé → WSEmax_A ≈ 38.75 m.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>• Méthode A: Qout fixe = Q_plein Manning Ø900 (n=0,013). Pas un jugement IC/OC complet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>• Le stockage commence quand Qin dépasse Qout; Vmax = max du volume stocké (pas (Qp−Qout)×durée).</t>
+          <t>4) Ce n'est PAS une cote saisie à la main: c'est Vmax lu sur le levé. Hmax≈V/Aire (B29) est plus grossier.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>• Méthode B: Qout = f(H) depuis feuille Courbe_QH_900 (FHWA inlet+outlet).</t>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Inlet control vs outlet control — qu'est-ce que ça veut dire?</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>• Voir feuille Fichiers_lies pour les anciens Excel HY-8 / ponceau+fossé.</t>
+          <t>• Inlet control (contrôle à l'entrée): le débit est limité par l'entrée du ponceau (forme d'entrée, HW/D).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>• Vérifier que le radier amont Ø900 (34.88) est bien le fond de la zone de rétention étudiée.</t>
+          <t xml:space="preserve">  Le tuyau aval « n'aspire » pas assez pour influencer — Q dépend surtout de la charge amont H, pas de L ni de n.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>• Niveau max (WSEmax): feuille Stage_Storage + case Parametres!B30 (Vmax → cote du levé).</t>
+          <t>• Outlet control (contrôle à la sortie / frottement): le débit dépend de la longueur, de n, de la pente et de la charge</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Vmax_B courbe FHWA (m³)</t>
-        </is>
-      </c>
-      <c r="B50" s="18">
-        <f>Calcul_B!B7</f>
-        <v/>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Routage avec Q=f(H) — dépend de Aire_bassin (B24)</t>
+          <t xml:space="preserve">  (énergie amont → aval). Manning pleine section est une hypothèse de type outlet/frottement à section pleine.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>WSEmax (rappel)</t>
-        </is>
-      </c>
-      <c r="B51" s="21">
-        <f>B30</f>
-        <v/>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Même valeur que B30 — niveau max depuis levé Stage_Storage</t>
+          <t>• Ici L/D = 56 (tuyau assez long) → le contrôle par frottement (outlet) est souvent plausible,</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  mais sans analyse FHWA/HY-8 on ne peut pas l'affirmer. Pour dimensionner la rétention, Q_plein constant est</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  en général prudent (si la charge monte, le débit réel peut être un peu plus élevé → Vmax un peu plus bas).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>• On n'a pas besoin de trancher IC/OC pour utiliser ce classeur: garder Qout = Q_plein (ou 1.77) suffit pour une 1re estimation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>• Méthode A: Qout fixe = Q_plein Manning Ø900 (n=0,013). Pas un jugement IC/OC complet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>• Le stockage commence quand Qin dépasse Qout; Vmax = max du volume stocké (pas (Qp−Qout)×durée).</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>• Méthode B: Qout = f(H) depuis feuille Courbe_QH_900 (FHWA inlet+outlet) — résultats en B34–B37.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>• Voir feuille Fichiers_lies pour les anciens Excel HY-8 / ponceau+fossé.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>• Vérifier que le radier amont Ø900 (34.88) est bien le fond de la zone de rétention étudiée.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>• WSEmax_A = B30 (depuis Vmax_A); WSEmax_B = B36 (depuis Vmax_B); les deux lisent Stage_Storage.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="21">
     <mergeCell ref="A48:H48"/>
+    <mergeCell ref="A59:H59"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A61:H61"/>
+    <mergeCell ref="A54:H54"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A50:H50"/>
     <mergeCell ref="A9:H10"/>
-    <mergeCell ref="A39:H39"/>
-    <mergeCell ref="A46:H46"/>
-    <mergeCell ref="A35:H35"/>
-    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A57:H57"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A62:H62"/>
+    <mergeCell ref="A53:H53"/>
+    <mergeCell ref="A43:H43"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A52:H52"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="A58:H58"/>
     <mergeCell ref="A40:H40"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="A36:H36"/>
-    <mergeCell ref="A49:H49"/>
-    <mergeCell ref="A44:H44"/>
-    <mergeCell ref="A47:H47"/>
-    <mergeCell ref="A45:H45"/>
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="A34:H34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1913,7 +1999,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>Hydrogramme d'entrée (point Ø1500 / entrée rétention) — FORMULES LIVE</t>
         </is>
@@ -1948,7 +2034,7 @@
           <t>t pointe (min)</t>
         </is>
       </c>
-      <c r="B5" s="23" t="n">
+      <c r="B5" s="22" t="n">
         <v>22.5</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -1980,10 +2066,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="n">
+      <c r="A8" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="B8" s="25" t="n">
+      <c r="B8" s="24" t="n">
         <v>0.081042</v>
       </c>
       <c r="C8" s="5">
@@ -1997,10 +2083,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="n">
+      <c r="A9" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="25" t="n">
+      <c r="B9" s="24" t="n">
         <v>0.121875</v>
       </c>
       <c r="C9" s="5">
@@ -2010,10 +2096,10 @@
       <c r="D9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="n">
+      <c r="A10" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="B10" s="25" t="n">
+      <c r="B10" s="24" t="n">
         <v>0.193438</v>
       </c>
       <c r="C10" s="5">
@@ -2023,10 +2109,10 @@
       <c r="D10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="n">
+      <c r="A11" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="B11" s="25" t="n">
+      <c r="B11" s="24" t="n">
         <v>0.333542</v>
       </c>
       <c r="C11" s="5">
@@ -2036,10 +2122,10 @@
       <c r="D11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="n">
+      <c r="A12" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="B12" s="25" t="n">
+      <c r="B12" s="24" t="n">
         <v>0.657188</v>
       </c>
       <c r="C12" s="5">
@@ -2049,10 +2135,10 @@
       <c r="D12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="n">
+      <c r="A13" s="23" t="n">
         <v>22.5</v>
       </c>
-      <c r="B13" s="25" t="n">
+      <c r="B13" s="24" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="8">
@@ -2066,10 +2152,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="n">
+      <c r="A14" s="23" t="n">
         <v>27.5</v>
       </c>
-      <c r="B14" s="25" t="n">
+      <c r="B14" s="24" t="n">
         <v>0.608958</v>
       </c>
       <c r="C14" s="5">
@@ -2079,10 +2165,10 @@
       <c r="D14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="n">
+      <c r="A15" s="23" t="n">
         <v>32.5</v>
       </c>
-      <c r="B15" s="25" t="n">
+      <c r="B15" s="24" t="n">
         <v>0.401771</v>
       </c>
       <c r="C15" s="5">
@@ -2092,10 +2178,10 @@
       <c r="D15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="n">
+      <c r="A16" s="23" t="n">
         <v>37.5</v>
       </c>
-      <c r="B16" s="25" t="n">
+      <c r="B16" s="24" t="n">
         <v>0.280104</v>
       </c>
       <c r="C16" s="5">
@@ -2105,10 +2191,10 @@
       <c r="D16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="n">
+      <c r="A17" s="23" t="n">
         <v>42.5</v>
       </c>
-      <c r="B17" s="25" t="n">
+      <c r="B17" s="24" t="n">
         <v>0.203438</v>
       </c>
       <c r="C17" s="5">
@@ -2118,10 +2204,10 @@
       <c r="D17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="n">
+      <c r="A18" s="23" t="n">
         <v>47.5</v>
       </c>
-      <c r="B18" s="25" t="n">
+      <c r="B18" s="24" t="n">
         <v>0.152292</v>
       </c>
       <c r="C18" s="5">
@@ -2131,10 +2217,10 @@
       <c r="D18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="24" t="n">
+      <c r="A19" s="23" t="n">
         <v>52.5</v>
       </c>
-      <c r="B19" s="25" t="n">
+      <c r="B19" s="24" t="n">
         <v>0.116771</v>
       </c>
       <c r="C19" s="5">
@@ -2144,10 +2230,10 @@
       <c r="D19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="24" t="n">
+      <c r="A20" s="23" t="n">
         <v>57.5</v>
       </c>
-      <c r="B20" s="25" t="n">
+      <c r="B20" s="24" t="n">
         <v>0.091146</v>
       </c>
       <c r="C20" s="5">
@@ -2162,7 +2248,7 @@
           <t>Qin max (contrôle)</t>
         </is>
       </c>
-      <c r="B22" s="26">
+      <c r="B22" s="25">
         <f>MAX(C8:C20)</f>
         <v/>
       </c>
@@ -2213,7 +2299,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>Méthode A — Qout constant = capacité Ø900</t>
         </is>
@@ -2225,7 +2311,7 @@
           <t>Qout (m³/s)</t>
         </is>
       </c>
-      <c r="B2" s="27">
+      <c r="B2" s="26">
         <f>Parametres!B22</f>
         <v/>
       </c>
@@ -2236,7 +2322,7 @@
           <t>Vmax (m³)</t>
         </is>
       </c>
-      <c r="B3" s="28">
+      <c r="B3" s="27">
         <f>MAX(H8:H20)</f>
         <v/>
       </c>
@@ -2318,7 +2404,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24">
+      <c r="A8" s="23">
         <f>Hydrogramme!A8</f>
         <v/>
       </c>
@@ -2326,7 +2412,7 @@
         <f>Hydrogramme!C8</f>
         <v/>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="28">
         <f>$B$2</f>
         <v/>
       </c>
@@ -2343,7 +2429,7 @@
       <c r="G8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="30" t="n">
+      <c r="H8" s="29" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="4">
@@ -2352,7 +2438,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24">
+      <c r="A9" s="23">
         <f>Hydrogramme!A9</f>
         <v/>
       </c>
@@ -2360,7 +2446,7 @@
         <f>Hydrogramme!C9</f>
         <v/>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="28">
         <f>$B$2</f>
         <v/>
       </c>
@@ -2368,19 +2454,19 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="23">
         <f>(A9-A8)*60</f>
         <v/>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="23">
         <f>0.5*(B8+B9)*E9</f>
         <v/>
       </c>
-      <c r="G9" s="24">
+      <c r="G9" s="23">
         <f>F9-(H9-H8)</f>
         <v/>
       </c>
-      <c r="H9" s="31">
+      <c r="H9" s="30">
         <f>MAX(0,H8+0.5*(D8+D9)*E9)</f>
         <v/>
       </c>
@@ -2390,7 +2476,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24">
+      <c r="A10" s="23">
         <f>Hydrogramme!A10</f>
         <v/>
       </c>
@@ -2398,7 +2484,7 @@
         <f>Hydrogramme!C10</f>
         <v/>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="28">
         <f>$B$2</f>
         <v/>
       </c>
@@ -2406,19 +2492,19 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="23">
         <f>(A10-A9)*60</f>
         <v/>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="23">
         <f>0.5*(B9+B10)*E10</f>
         <v/>
       </c>
-      <c r="G10" s="24">
+      <c r="G10" s="23">
         <f>F10-(H10-H9)</f>
         <v/>
       </c>
-      <c r="H10" s="31">
+      <c r="H10" s="30">
         <f>MAX(0,H9+0.5*(D9+D10)*E10)</f>
         <v/>
       </c>
@@ -2428,7 +2514,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24">
+      <c r="A11" s="23">
         <f>Hydrogramme!A11</f>
         <v/>
       </c>
@@ -2436,7 +2522,7 @@
         <f>Hydrogramme!C11</f>
         <v/>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="28">
         <f>$B$2</f>
         <v/>
       </c>
@@ -2444,19 +2530,19 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="23">
         <f>(A11-A10)*60</f>
         <v/>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="23">
         <f>0.5*(B10+B11)*E11</f>
         <v/>
       </c>
-      <c r="G11" s="24">
+      <c r="G11" s="23">
         <f>F11-(H11-H10)</f>
         <v/>
       </c>
-      <c r="H11" s="31">
+      <c r="H11" s="30">
         <f>MAX(0,H10+0.5*(D10+D11)*E11)</f>
         <v/>
       </c>
@@ -2466,7 +2552,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="24">
+      <c r="A12" s="23">
         <f>Hydrogramme!A12</f>
         <v/>
       </c>
@@ -2474,7 +2560,7 @@
         <f>Hydrogramme!C12</f>
         <v/>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="28">
         <f>$B$2</f>
         <v/>
       </c>
@@ -2482,19 +2568,19 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="23">
         <f>(A12-A11)*60</f>
         <v/>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="23">
         <f>0.5*(B11+B12)*E12</f>
         <v/>
       </c>
-      <c r="G12" s="24">
+      <c r="G12" s="23">
         <f>F12-(H12-H11)</f>
         <v/>
       </c>
-      <c r="H12" s="31">
+      <c r="H12" s="30">
         <f>MAX(0,H11+0.5*(D11+D12)*E12)</f>
         <v/>
       </c>
@@ -2504,7 +2590,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24">
+      <c r="A13" s="23">
         <f>Hydrogramme!A13</f>
         <v/>
       </c>
@@ -2512,7 +2598,7 @@
         <f>Hydrogramme!C13</f>
         <v/>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="28">
         <f>$B$2</f>
         <v/>
       </c>
@@ -2520,19 +2606,19 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="23">
         <f>(A13-A12)*60</f>
         <v/>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="23">
         <f>0.5*(B12+B13)*E13</f>
         <v/>
       </c>
-      <c r="G13" s="24">
+      <c r="G13" s="23">
         <f>F13-(H13-H12)</f>
         <v/>
       </c>
-      <c r="H13" s="31">
+      <c r="H13" s="30">
         <f>MAX(0,H12+0.5*(D12+D13)*E13)</f>
         <v/>
       </c>
@@ -2542,7 +2628,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="24">
+      <c r="A14" s="23">
         <f>Hydrogramme!A14</f>
         <v/>
       </c>
@@ -2550,7 +2636,7 @@
         <f>Hydrogramme!C14</f>
         <v/>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="28">
         <f>$B$2</f>
         <v/>
       </c>
@@ -2558,19 +2644,19 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="23">
         <f>(A14-A13)*60</f>
         <v/>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="23">
         <f>0.5*(B13+B14)*E14</f>
         <v/>
       </c>
-      <c r="G14" s="24">
+      <c r="G14" s="23">
         <f>F14-(H14-H13)</f>
         <v/>
       </c>
-      <c r="H14" s="31">
+      <c r="H14" s="30">
         <f>MAX(0,H13+0.5*(D13+D14)*E14)</f>
         <v/>
       </c>
@@ -2580,7 +2666,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="24">
+      <c r="A15" s="23">
         <f>Hydrogramme!A15</f>
         <v/>
       </c>
@@ -2588,7 +2674,7 @@
         <f>Hydrogramme!C15</f>
         <v/>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="28">
         <f>$B$2</f>
         <v/>
       </c>
@@ -2596,19 +2682,19 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="23">
         <f>(A15-A14)*60</f>
         <v/>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="23">
         <f>0.5*(B14+B15)*E15</f>
         <v/>
       </c>
-      <c r="G15" s="24">
+      <c r="G15" s="23">
         <f>F15-(H15-H14)</f>
         <v/>
       </c>
-      <c r="H15" s="31">
+      <c r="H15" s="30">
         <f>MAX(0,H14+0.5*(D14+D15)*E15)</f>
         <v/>
       </c>
@@ -2618,7 +2704,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="24">
+      <c r="A16" s="23">
         <f>Hydrogramme!A16</f>
         <v/>
       </c>
@@ -2626,7 +2712,7 @@
         <f>Hydrogramme!C16</f>
         <v/>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="28">
         <f>$B$2</f>
         <v/>
       </c>
@@ -2634,19 +2720,19 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="23">
         <f>(A16-A15)*60</f>
         <v/>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="23">
         <f>0.5*(B15+B16)*E16</f>
         <v/>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="23">
         <f>F16-(H16-H15)</f>
         <v/>
       </c>
-      <c r="H16" s="31">
+      <c r="H16" s="30">
         <f>MAX(0,H15+0.5*(D15+D16)*E16)</f>
         <v/>
       </c>
@@ -2656,7 +2742,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24">
+      <c r="A17" s="23">
         <f>Hydrogramme!A17</f>
         <v/>
       </c>
@@ -2664,7 +2750,7 @@
         <f>Hydrogramme!C17</f>
         <v/>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="28">
         <f>$B$2</f>
         <v/>
       </c>
@@ -2672,19 +2758,19 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="23">
         <f>(A17-A16)*60</f>
         <v/>
       </c>
-      <c r="F17" s="24">
+      <c r="F17" s="23">
         <f>0.5*(B16+B17)*E17</f>
         <v/>
       </c>
-      <c r="G17" s="24">
+      <c r="G17" s="23">
         <f>F17-(H17-H16)</f>
         <v/>
       </c>
-      <c r="H17" s="31">
+      <c r="H17" s="30">
         <f>MAX(0,H16+0.5*(D16+D17)*E17)</f>
         <v/>
       </c>
@@ -2694,7 +2780,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="24">
+      <c r="A18" s="23">
         <f>Hydrogramme!A18</f>
         <v/>
       </c>
@@ -2702,7 +2788,7 @@
         <f>Hydrogramme!C18</f>
         <v/>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="28">
         <f>$B$2</f>
         <v/>
       </c>
@@ -2710,19 +2796,19 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="23">
         <f>(A18-A17)*60</f>
         <v/>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="23">
         <f>0.5*(B17+B18)*E18</f>
         <v/>
       </c>
-      <c r="G18" s="24">
+      <c r="G18" s="23">
         <f>F18-(H18-H17)</f>
         <v/>
       </c>
-      <c r="H18" s="31">
+      <c r="H18" s="30">
         <f>MAX(0,H17+0.5*(D17+D18)*E18)</f>
         <v/>
       </c>
@@ -2732,7 +2818,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="24">
+      <c r="A19" s="23">
         <f>Hydrogramme!A19</f>
         <v/>
       </c>
@@ -2740,7 +2826,7 @@
         <f>Hydrogramme!C19</f>
         <v/>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="28">
         <f>$B$2</f>
         <v/>
       </c>
@@ -2748,19 +2834,19 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="23">
         <f>(A19-A18)*60</f>
         <v/>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="23">
         <f>0.5*(B18+B19)*E19</f>
         <v/>
       </c>
-      <c r="G19" s="24">
+      <c r="G19" s="23">
         <f>F19-(H19-H18)</f>
         <v/>
       </c>
-      <c r="H19" s="31">
+      <c r="H19" s="30">
         <f>MAX(0,H18+0.5*(D18+D19)*E19)</f>
         <v/>
       </c>
@@ -2770,7 +2856,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="24">
+      <c r="A20" s="23">
         <f>Hydrogramme!A20</f>
         <v/>
       </c>
@@ -2778,7 +2864,7 @@
         <f>Hydrogramme!C20</f>
         <v/>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="28">
         <f>$B$2</f>
         <v/>
       </c>
@@ -2786,19 +2872,19 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="24">
+      <c r="E20" s="23">
         <f>(A20-A19)*60</f>
         <v/>
       </c>
-      <c r="F20" s="24">
+      <c r="F20" s="23">
         <f>0.5*(B19+B20)*E20</f>
         <v/>
       </c>
-      <c r="G20" s="24">
+      <c r="G20" s="23">
         <f>F20-(H20-H19)</f>
         <v/>
       </c>
-      <c r="H20" s="31">
+      <c r="H20" s="30">
         <f>MAX(0,H19+0.5*(D19+D20)*E20)</f>
         <v/>
       </c>
@@ -2832,7 +2918,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>Courbe de capacité Ø900 — Q = f(H) (FHWA HDS-5 inlet + outlet) — FORMULES LIVE</t>
         </is>
@@ -2872,32 +2958,32 @@
           <t>béton typ. 0.012–0.015</t>
         </is>
       </c>
-      <c r="E6" s="32" t="inlineStr">
+      <c r="E6" s="31" t="inlineStr">
         <is>
           <t>entrée</t>
         </is>
       </c>
-      <c r="F6" s="32" t="inlineStr">
+      <c r="F6" s="31" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="G6" s="32" t="inlineStr">
+      <c r="G6" s="31" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H6" s="32" t="inlineStr">
+      <c r="H6" s="31" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="I6" s="32" t="inlineStr">
+      <c r="I6" s="31" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J6" s="32" t="inlineStr">
+      <c r="J6" s="31" t="inlineStr">
         <is>
           <t>Ke</t>
         </is>
@@ -3013,7 +3099,7 @@
           <t>S0 = (Zin-Zout)/L</t>
         </is>
       </c>
-      <c r="B11" s="33">
+      <c r="B11" s="32">
         <f>(B9-B10)/B8</f>
         <v/>
       </c>
@@ -3044,7 +3130,7 @@
           <t>Entrée (texte exact)</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="33" t="inlineStr">
         <is>
           <t>square_edge</t>
         </is>
@@ -3061,7 +3147,7 @@
           <t>Q_plein Manning (réf.)</t>
         </is>
       </c>
-      <c r="B15" s="26">
+      <c r="B15" s="25">
         <f>(1/B6)*(PI()*B7^2/4)*((B7/4)^(2/3))*SQRT(B11)</f>
         <v/>
       </c>
@@ -3077,7 +3163,7 @@
           <t>K (lu)</t>
         </is>
       </c>
-      <c r="B17" s="35">
+      <c r="B17" s="34">
         <f>IFERROR(VLOOKUP(B13,$E$7:$J$9,2,FALSE),0.0098)</f>
         <v/>
       </c>
@@ -3088,7 +3174,7 @@
           <t>M (lu)</t>
         </is>
       </c>
-      <c r="B18" s="35">
+      <c r="B18" s="34">
         <f>IFERROR(VLOOKUP(B13,$E$7:$J$9,3,FALSE),2)</f>
         <v/>
       </c>
@@ -3099,7 +3185,7 @@
           <t>c (lu)</t>
         </is>
       </c>
-      <c r="B19" s="35">
+      <c r="B19" s="34">
         <f>IFERROR(VLOOKUP(B13,$E$7:$J$9,4,FALSE),0.0398)</f>
         <v/>
       </c>
@@ -3110,7 +3196,7 @@
           <t>Y (lu)</t>
         </is>
       </c>
-      <c r="B20" s="35">
+      <c r="B20" s="34">
         <f>IFERROR(VLOOKUP(B13,$E$7:$J$9,5,FALSE),0.67)</f>
         <v/>
       </c>
@@ -3121,7 +3207,7 @@
           <t>Ke (lu)</t>
         </is>
       </c>
-      <c r="B21" s="35">
+      <c r="B21" s="34">
         <f>IFERROR(VLOOKUP(B13,$E$7:$J$9,6,FALSE),0.5)</f>
         <v/>
       </c>
@@ -3159,10 +3245,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="29" t="n">
+      <c r="A24" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="B24" s="29">
+      <c r="B24" s="28">
         <f>$B$9+A24</f>
         <v/>
       </c>
@@ -3184,10 +3270,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="29" t="n">
+      <c r="A25" s="28" t="n">
         <v>0.05</v>
       </c>
-      <c r="B25" s="29">
+      <c r="B25" s="28">
         <f>$B$9+A25</f>
         <v/>
       </c>
@@ -3209,10 +3295,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="29" t="n">
+      <c r="A26" s="28" t="n">
         <v>0.1</v>
       </c>
-      <c r="B26" s="29">
+      <c r="B26" s="28">
         <f>$B$9+A26</f>
         <v/>
       </c>
@@ -3234,10 +3320,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="29" t="n">
+      <c r="A27" s="28" t="n">
         <v>0.15</v>
       </c>
-      <c r="B27" s="29">
+      <c r="B27" s="28">
         <f>$B$9+A27</f>
         <v/>
       </c>
@@ -3259,10 +3345,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="29" t="n">
+      <c r="A28" s="28" t="n">
         <v>0.2</v>
       </c>
-      <c r="B28" s="29">
+      <c r="B28" s="28">
         <f>$B$9+A28</f>
         <v/>
       </c>
@@ -3284,10 +3370,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="29" t="n">
+      <c r="A29" s="28" t="n">
         <v>0.25</v>
       </c>
-      <c r="B29" s="29">
+      <c r="B29" s="28">
         <f>$B$9+A29</f>
         <v/>
       </c>
@@ -3309,10 +3395,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="29" t="n">
+      <c r="A30" s="28" t="n">
         <v>0.3</v>
       </c>
-      <c r="B30" s="29">
+      <c r="B30" s="28">
         <f>$B$9+A30</f>
         <v/>
       </c>
@@ -3334,10 +3420,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="29" t="n">
+      <c r="A31" s="28" t="n">
         <v>0.35</v>
       </c>
-      <c r="B31" s="29">
+      <c r="B31" s="28">
         <f>$B$9+A31</f>
         <v/>
       </c>
@@ -3359,10 +3445,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="29" t="n">
+      <c r="A32" s="28" t="n">
         <v>0.4</v>
       </c>
-      <c r="B32" s="29">
+      <c r="B32" s="28">
         <f>$B$9+A32</f>
         <v/>
       </c>
@@ -3384,10 +3470,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="29" t="n">
+      <c r="A33" s="28" t="n">
         <v>0.45</v>
       </c>
-      <c r="B33" s="29">
+      <c r="B33" s="28">
         <f>$B$9+A33</f>
         <v/>
       </c>
@@ -3409,10 +3495,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="29" t="n">
+      <c r="A34" s="28" t="n">
         <v>0.5</v>
       </c>
-      <c r="B34" s="29">
+      <c r="B34" s="28">
         <f>$B$9+A34</f>
         <v/>
       </c>
@@ -3434,10 +3520,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="29" t="n">
+      <c r="A35" s="28" t="n">
         <v>0.55</v>
       </c>
-      <c r="B35" s="29">
+      <c r="B35" s="28">
         <f>$B$9+A35</f>
         <v/>
       </c>
@@ -3459,10 +3545,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="29" t="n">
+      <c r="A36" s="28" t="n">
         <v>0.6</v>
       </c>
-      <c r="B36" s="29">
+      <c r="B36" s="28">
         <f>$B$9+A36</f>
         <v/>
       </c>
@@ -3484,10 +3570,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="29" t="n">
+      <c r="A37" s="28" t="n">
         <v>0.65</v>
       </c>
-      <c r="B37" s="29">
+      <c r="B37" s="28">
         <f>$B$9+A37</f>
         <v/>
       </c>
@@ -3509,10 +3595,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="29" t="n">
+      <c r="A38" s="28" t="n">
         <v>0.7</v>
       </c>
-      <c r="B38" s="29">
+      <c r="B38" s="28">
         <f>$B$9+A38</f>
         <v/>
       </c>
@@ -3534,10 +3620,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="29" t="n">
+      <c r="A39" s="28" t="n">
         <v>0.75</v>
       </c>
-      <c r="B39" s="29">
+      <c r="B39" s="28">
         <f>$B$9+A39</f>
         <v/>
       </c>
@@ -3559,10 +3645,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="29" t="n">
+      <c r="A40" s="28" t="n">
         <v>0.8</v>
       </c>
-      <c r="B40" s="29">
+      <c r="B40" s="28">
         <f>$B$9+A40</f>
         <v/>
       </c>
@@ -3584,10 +3670,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="29" t="n">
+      <c r="A41" s="28" t="n">
         <v>0.85</v>
       </c>
-      <c r="B41" s="29">
+      <c r="B41" s="28">
         <f>$B$9+A41</f>
         <v/>
       </c>
@@ -3609,10 +3695,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="29" t="n">
+      <c r="A42" s="28" t="n">
         <v>0.9</v>
       </c>
-      <c r="B42" s="29">
+      <c r="B42" s="28">
         <f>$B$9+A42</f>
         <v/>
       </c>
@@ -3634,10 +3720,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="29" t="n">
+      <c r="A43" s="28" t="n">
         <v>0.95</v>
       </c>
-      <c r="B43" s="29">
+      <c r="B43" s="28">
         <f>$B$9+A43</f>
         <v/>
       </c>
@@ -3659,10 +3745,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="29" t="n">
+      <c r="A44" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="B44" s="29">
+      <c r="B44" s="28">
         <f>$B$9+A44</f>
         <v/>
       </c>
@@ -3684,10 +3770,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="29" t="n">
+      <c r="A45" s="28" t="n">
         <v>1.05</v>
       </c>
-      <c r="B45" s="29">
+      <c r="B45" s="28">
         <f>$B$9+A45</f>
         <v/>
       </c>
@@ -3709,10 +3795,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="29" t="n">
+      <c r="A46" s="28" t="n">
         <v>1.1</v>
       </c>
-      <c r="B46" s="29">
+      <c r="B46" s="28">
         <f>$B$9+A46</f>
         <v/>
       </c>
@@ -3734,10 +3820,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="29" t="n">
+      <c r="A47" s="28" t="n">
         <v>1.15</v>
       </c>
-      <c r="B47" s="29">
+      <c r="B47" s="28">
         <f>$B$9+A47</f>
         <v/>
       </c>
@@ -3759,10 +3845,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="29" t="n">
+      <c r="A48" s="28" t="n">
         <v>1.2</v>
       </c>
-      <c r="B48" s="29">
+      <c r="B48" s="28">
         <f>$B$9+A48</f>
         <v/>
       </c>
@@ -3784,10 +3870,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="29" t="n">
+      <c r="A49" s="28" t="n">
         <v>1.25</v>
       </c>
-      <c r="B49" s="29">
+      <c r="B49" s="28">
         <f>$B$9+A49</f>
         <v/>
       </c>
@@ -3809,10 +3895,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="29" t="n">
+      <c r="A50" s="28" t="n">
         <v>1.3</v>
       </c>
-      <c r="B50" s="29">
+      <c r="B50" s="28">
         <f>$B$9+A50</f>
         <v/>
       </c>
@@ -3834,10 +3920,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="29" t="n">
+      <c r="A51" s="28" t="n">
         <v>1.35</v>
       </c>
-      <c r="B51" s="29">
+      <c r="B51" s="28">
         <f>$B$9+A51</f>
         <v/>
       </c>
@@ -3859,10 +3945,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="29" t="n">
+      <c r="A52" s="28" t="n">
         <v>1.4</v>
       </c>
-      <c r="B52" s="29">
+      <c r="B52" s="28">
         <f>$B$9+A52</f>
         <v/>
       </c>
@@ -3884,10 +3970,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="29" t="n">
+      <c r="A53" s="28" t="n">
         <v>1.45</v>
       </c>
-      <c r="B53" s="29">
+      <c r="B53" s="28">
         <f>$B$9+A53</f>
         <v/>
       </c>
@@ -3909,10 +3995,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="29" t="n">
+      <c r="A54" s="28" t="n">
         <v>1.5</v>
       </c>
-      <c r="B54" s="29">
+      <c r="B54" s="28">
         <f>$B$9+A54</f>
         <v/>
       </c>
@@ -3934,10 +4020,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="29" t="n">
+      <c r="A55" s="28" t="n">
         <v>1.55</v>
       </c>
-      <c r="B55" s="29">
+      <c r="B55" s="28">
         <f>$B$9+A55</f>
         <v/>
       </c>
@@ -3959,10 +4045,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="29" t="n">
+      <c r="A56" s="28" t="n">
         <v>1.6</v>
       </c>
-      <c r="B56" s="29">
+      <c r="B56" s="28">
         <f>$B$9+A56</f>
         <v/>
       </c>
@@ -3984,10 +4070,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="29" t="n">
+      <c r="A57" s="28" t="n">
         <v>1.65</v>
       </c>
-      <c r="B57" s="29">
+      <c r="B57" s="28">
         <f>$B$9+A57</f>
         <v/>
       </c>
@@ -4009,10 +4095,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="29" t="n">
+      <c r="A58" s="28" t="n">
         <v>1.7</v>
       </c>
-      <c r="B58" s="29">
+      <c r="B58" s="28">
         <f>$B$9+A58</f>
         <v/>
       </c>
@@ -4034,10 +4120,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="29" t="n">
+      <c r="A59" s="28" t="n">
         <v>1.75</v>
       </c>
-      <c r="B59" s="29">
+      <c r="B59" s="28">
         <f>$B$9+A59</f>
         <v/>
       </c>
@@ -4059,10 +4145,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="29" t="n">
+      <c r="A60" s="28" t="n">
         <v>1.8</v>
       </c>
-      <c r="B60" s="29">
+      <c r="B60" s="28">
         <f>$B$9+A60</f>
         <v/>
       </c>
@@ -4084,10 +4170,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="29" t="n">
+      <c r="A61" s="28" t="n">
         <v>1.85</v>
       </c>
-      <c r="B61" s="29">
+      <c r="B61" s="28">
         <f>$B$9+A61</f>
         <v/>
       </c>
@@ -4109,10 +4195,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="29" t="n">
+      <c r="A62" s="28" t="n">
         <v>1.9</v>
       </c>
-      <c r="B62" s="29">
+      <c r="B62" s="28">
         <f>$B$9+A62</f>
         <v/>
       </c>
@@ -4134,10 +4220,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="29" t="n">
+      <c r="A63" s="28" t="n">
         <v>1.95</v>
       </c>
-      <c r="B63" s="29">
+      <c r="B63" s="28">
         <f>$B$9+A63</f>
         <v/>
       </c>
@@ -4159,10 +4245,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="29" t="n">
+      <c r="A64" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="B64" s="29">
+      <c r="B64" s="28">
         <f>$B$9+A64</f>
         <v/>
       </c>
@@ -4184,10 +4270,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="29" t="n">
+      <c r="A65" s="28" t="n">
         <v>2.05</v>
       </c>
-      <c r="B65" s="29">
+      <c r="B65" s="28">
         <f>$B$9+A65</f>
         <v/>
       </c>
@@ -4209,10 +4295,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="29" t="n">
+      <c r="A66" s="28" t="n">
         <v>2.1</v>
       </c>
-      <c r="B66" s="29">
+      <c r="B66" s="28">
         <f>$B$9+A66</f>
         <v/>
       </c>
@@ -4234,10 +4320,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="29" t="n">
+      <c r="A67" s="28" t="n">
         <v>2.15</v>
       </c>
-      <c r="B67" s="29">
+      <c r="B67" s="28">
         <f>$B$9+A67</f>
         <v/>
       </c>
@@ -4259,10 +4345,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="29" t="n">
+      <c r="A68" s="28" t="n">
         <v>2.2</v>
       </c>
-      <c r="B68" s="29">
+      <c r="B68" s="28">
         <f>$B$9+A68</f>
         <v/>
       </c>
@@ -4284,10 +4370,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="29" t="n">
+      <c r="A69" s="28" t="n">
         <v>2.25</v>
       </c>
-      <c r="B69" s="29">
+      <c r="B69" s="28">
         <f>$B$9+A69</f>
         <v/>
       </c>
@@ -4309,10 +4395,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="29" t="n">
+      <c r="A70" s="28" t="n">
         <v>2.3</v>
       </c>
-      <c r="B70" s="29">
+      <c r="B70" s="28">
         <f>$B$9+A70</f>
         <v/>
       </c>
@@ -4334,10 +4420,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="29" t="n">
+      <c r="A71" s="28" t="n">
         <v>2.35</v>
       </c>
-      <c r="B71" s="29">
+      <c r="B71" s="28">
         <f>$B$9+A71</f>
         <v/>
       </c>
@@ -4359,10 +4445,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="36" t="n">
+      <c r="A72" s="35" t="n">
         <v>2.4</v>
       </c>
-      <c r="B72" s="36">
+      <c r="B72" s="35">
         <f>$B$9+A72</f>
         <v/>
       </c>
@@ -4384,10 +4470,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="29" t="n">
+      <c r="A73" s="28" t="n">
         <v>2.45</v>
       </c>
-      <c r="B73" s="29">
+      <c r="B73" s="28">
         <f>$B$9+A73</f>
         <v/>
       </c>
@@ -4409,10 +4495,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="29" t="n">
+      <c r="A74" s="28" t="n">
         <v>2.5</v>
       </c>
-      <c r="B74" s="29">
+      <c r="B74" s="28">
         <f>$B$9+A74</f>
         <v/>
       </c>
@@ -4434,10 +4520,10 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="29" t="n">
+      <c r="A75" s="28" t="n">
         <v>2.55</v>
       </c>
-      <c r="B75" s="29">
+      <c r="B75" s="28">
         <f>$B$9+A75</f>
         <v/>
       </c>
@@ -4459,10 +4545,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="29" t="n">
+      <c r="A76" s="28" t="n">
         <v>2.6</v>
       </c>
-      <c r="B76" s="29">
+      <c r="B76" s="28">
         <f>$B$9+A76</f>
         <v/>
       </c>
@@ -4484,10 +4570,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="29" t="n">
+      <c r="A77" s="28" t="n">
         <v>2.65</v>
       </c>
-      <c r="B77" s="29">
+      <c r="B77" s="28">
         <f>$B$9+A77</f>
         <v/>
       </c>
@@ -4509,10 +4595,10 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="29" t="n">
+      <c r="A78" s="28" t="n">
         <v>2.7</v>
       </c>
-      <c r="B78" s="29">
+      <c r="B78" s="28">
         <f>$B$9+A78</f>
         <v/>
       </c>
@@ -4534,10 +4620,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="29" t="n">
+      <c r="A79" s="28" t="n">
         <v>2.75</v>
       </c>
-      <c r="B79" s="29">
+      <c r="B79" s="28">
         <f>$B$9+A79</f>
         <v/>
       </c>
@@ -4559,10 +4645,10 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="29" t="n">
+      <c r="A80" s="28" t="n">
         <v>2.8</v>
       </c>
-      <c r="B80" s="29">
+      <c r="B80" s="28">
         <f>$B$9+A80</f>
         <v/>
       </c>
@@ -4584,10 +4670,10 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="29" t="n">
+      <c r="A81" s="28" t="n">
         <v>2.85</v>
       </c>
-      <c r="B81" s="29">
+      <c r="B81" s="28">
         <f>$B$9+A81</f>
         <v/>
       </c>
@@ -4609,10 +4695,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="29" t="n">
+      <c r="A82" s="28" t="n">
         <v>2.9</v>
       </c>
-      <c r="B82" s="29">
+      <c r="B82" s="28">
         <f>$B$9+A82</f>
         <v/>
       </c>
@@ -4634,10 +4720,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="29" t="n">
+      <c r="A83" s="28" t="n">
         <v>2.95</v>
       </c>
-      <c r="B83" s="29">
+      <c r="B83" s="28">
         <f>$B$9+A83</f>
         <v/>
       </c>
@@ -4659,10 +4745,10 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="29" t="n">
+      <c r="A84" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="B84" s="29">
+      <c r="B84" s="28">
         <f>$B$9+A84</f>
         <v/>
       </c>
@@ -4711,14 +4797,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>Méthode B — routage avec Qout = f(H) depuis Courbe_QH_900 (FHWA)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="37" t="inlineStr">
+      <c r="A2" s="36" t="inlineStr">
         <is>
           <t>H = V / Aire_bassin. Qout interpolé sur Courbe_QH_900!E (Q gouvernant). Si V≈0, Qout = MIN(Qin, Q_plein). ΔV = (Qin_moy - Qout)*Δt. La courbe Courbe_QH_900 est en formules live (changer n/L/entrée/TW).</t>
         </is>
@@ -4731,7 +4817,7 @@
           <t>Aire (m²)</t>
         </is>
       </c>
-      <c r="B5" s="38">
+      <c r="B5" s="37">
         <f>Parametres!B24</f>
         <v/>
       </c>
@@ -4742,7 +4828,7 @@
           <t>Q_plein réf. (m³/s)</t>
         </is>
       </c>
-      <c r="B6" s="38">
+      <c r="B6" s="37">
         <f>Parametres!B22</f>
         <v/>
       </c>
@@ -4753,7 +4839,7 @@
           <t>Vmax_B (m³)</t>
         </is>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="27">
         <f>MAX(G12:G24)</f>
         <v/>
       </c>
@@ -4825,10 +4911,10 @@
         <f>MIN(B12,$B$6)</f>
         <v/>
       </c>
-      <c r="F12" s="24" t="n">
+      <c r="F12" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="31" t="n">
+      <c r="G12" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4853,11 +4939,11 @@
         <f>IF(G12&lt;=0.01,MIN(0.5*(B12+B13),$B$6),D13)</f>
         <v/>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="23">
         <f>(A13-A12)*60</f>
         <v/>
       </c>
-      <c r="G13" s="31">
+      <c r="G13" s="30">
         <f>MAX(0,G12+(0.5*(B12+B13)-E13)*F13)</f>
         <v/>
       </c>
@@ -4883,11 +4969,11 @@
         <f>IF(G13&lt;=0.01,MIN(0.5*(B13+B14),$B$6),D14)</f>
         <v/>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="23">
         <f>(A14-A13)*60</f>
         <v/>
       </c>
-      <c r="G14" s="31">
+      <c r="G14" s="30">
         <f>MAX(0,G13+(0.5*(B13+B14)-E14)*F14)</f>
         <v/>
       </c>
@@ -4913,11 +4999,11 @@
         <f>IF(G14&lt;=0.01,MIN(0.5*(B14+B15),$B$6),D15)</f>
         <v/>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="23">
         <f>(A15-A14)*60</f>
         <v/>
       </c>
-      <c r="G15" s="31">
+      <c r="G15" s="30">
         <f>MAX(0,G14+(0.5*(B14+B15)-E15)*F15)</f>
         <v/>
       </c>
@@ -4943,11 +5029,11 @@
         <f>IF(G15&lt;=0.01,MIN(0.5*(B15+B16),$B$6),D16)</f>
         <v/>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="23">
         <f>(A16-A15)*60</f>
         <v/>
       </c>
-      <c r="G16" s="31">
+      <c r="G16" s="30">
         <f>MAX(0,G15+(0.5*(B15+B16)-E16)*F16)</f>
         <v/>
       </c>
@@ -4973,11 +5059,11 @@
         <f>IF(G16&lt;=0.01,MIN(0.5*(B16+B17),$B$6),D17)</f>
         <v/>
       </c>
-      <c r="F17" s="24">
+      <c r="F17" s="23">
         <f>(A17-A16)*60</f>
         <v/>
       </c>
-      <c r="G17" s="31">
+      <c r="G17" s="30">
         <f>MAX(0,G16+(0.5*(B16+B17)-E17)*F17)</f>
         <v/>
       </c>
@@ -5003,11 +5089,11 @@
         <f>IF(G17&lt;=0.01,MIN(0.5*(B17+B18),$B$6),D18)</f>
         <v/>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="23">
         <f>(A18-A17)*60</f>
         <v/>
       </c>
-      <c r="G18" s="31">
+      <c r="G18" s="30">
         <f>MAX(0,G17+(0.5*(B17+B18)-E18)*F18)</f>
         <v/>
       </c>
@@ -5033,11 +5119,11 @@
         <f>IF(G18&lt;=0.01,MIN(0.5*(B18+B19),$B$6),D19)</f>
         <v/>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="23">
         <f>(A19-A18)*60</f>
         <v/>
       </c>
-      <c r="G19" s="31">
+      <c r="G19" s="30">
         <f>MAX(0,G18+(0.5*(B18+B19)-E19)*F19)</f>
         <v/>
       </c>
@@ -5063,11 +5149,11 @@
         <f>IF(G19&lt;=0.01,MIN(0.5*(B19+B20),$B$6),D20)</f>
         <v/>
       </c>
-      <c r="F20" s="24">
+      <c r="F20" s="23">
         <f>(A20-A19)*60</f>
         <v/>
       </c>
-      <c r="G20" s="31">
+      <c r="G20" s="30">
         <f>MAX(0,G19+(0.5*(B19+B20)-E20)*F20)</f>
         <v/>
       </c>
@@ -5093,11 +5179,11 @@
         <f>IF(G20&lt;=0.01,MIN(0.5*(B20+B21),$B$6),D21)</f>
         <v/>
       </c>
-      <c r="F21" s="24">
+      <c r="F21" s="23">
         <f>(A21-A20)*60</f>
         <v/>
       </c>
-      <c r="G21" s="31">
+      <c r="G21" s="30">
         <f>MAX(0,G20+(0.5*(B20+B21)-E21)*F21)</f>
         <v/>
       </c>
@@ -5123,11 +5209,11 @@
         <f>IF(G21&lt;=0.01,MIN(0.5*(B21+B22),$B$6),D22)</f>
         <v/>
       </c>
-      <c r="F22" s="24">
+      <c r="F22" s="23">
         <f>(A22-A21)*60</f>
         <v/>
       </c>
-      <c r="G22" s="31">
+      <c r="G22" s="30">
         <f>MAX(0,G21+(0.5*(B21+B22)-E22)*F22)</f>
         <v/>
       </c>
@@ -5153,11 +5239,11 @@
         <f>IF(G22&lt;=0.01,MIN(0.5*(B22+B23),$B$6),D23)</f>
         <v/>
       </c>
-      <c r="F23" s="24">
+      <c r="F23" s="23">
         <f>(A23-A22)*60</f>
         <v/>
       </c>
-      <c r="G23" s="31">
+      <c r="G23" s="30">
         <f>MAX(0,G22+(0.5*(B22+B23)-E23)*F23)</f>
         <v/>
       </c>
@@ -5183,11 +5269,11 @@
         <f>IF(G23&lt;=0.01,MIN(0.5*(B23+B24),$B$6),D24)</f>
         <v/>
       </c>
-      <c r="F24" s="24">
+      <c r="F24" s="23">
         <f>(A24-A23)*60</f>
         <v/>
       </c>
-      <c r="G24" s="31">
+      <c r="G24" s="30">
         <f>MAX(0,G23+(0.5*(B23+B24)-E24)*F24)</f>
         <v/>
       </c>
@@ -5206,7 +5292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5218,7 +5304,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>Stage–storage du levé — V = f(WSE) → lire le niveau max</t>
         </is>
@@ -5227,7 +5313,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>PROCÉDURE (dans CE fichier): 1) Routage → Vmax sur Parametres (Calcul_A ou B). 2) Cette feuille calcule V cumulé vs NSE/WSE à partir des surfaces du levé (jaune). 3) Parametres!B30 interpolates Vmax → WSEmax. Remplacez les surfaces jaunes par vos polygones; 543 m² @ 37.28 et 1932 m² @ 39.5 sont vos mesures.</t>
+          <t>PROCÉDURE (dans CE fichier): 1) Routage → Vmax_A / Vmax_B sur Parametres (Calcul_A et Calcul_B). 2) Cette feuille calcule V cumulé vs NSE/WSE à partir des surfaces du levé (jaune). 3) Parametres!B30 = WSEmax_A (depuis Vmax_A); B36 = WSEmax_B (depuis Vmax_B). Remplacez les surfaces jaunes par vos polygones; 543 m² @ 37.28 et 1932 m² @ 39.5 sont vos mesures.</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5327,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="38" t="inlineStr">
         <is>
           <t>V_pas (m³) = (A_basse + A_haute) / 2 × (WSE_haute − WSE_basse)</t>
         </is>
@@ -5287,7 +5373,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="n">
+      <c r="A11" s="28" t="n">
         <v>34.88</v>
       </c>
       <c r="B11" s="17" t="n">
@@ -5309,21 +5395,21 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="29" t="n">
+      <c r="A12" s="28" t="n">
         <v>35.5</v>
       </c>
       <c r="B12" s="17" t="n">
         <v>80</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="28">
         <f>A12-A11</f>
         <v/>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="23">
         <f>0.5*(B11+B12)*C12</f>
         <v/>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="30">
         <f>E11+D12</f>
         <v/>
       </c>
@@ -5334,21 +5420,21 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="n">
+      <c r="A13" s="28" t="n">
         <v>36</v>
       </c>
       <c r="B13" s="17" t="n">
         <v>180</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="28">
         <f>A13-A12</f>
         <v/>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="23">
         <f>0.5*(B12+B13)*C13</f>
         <v/>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="30">
         <f>E12+D13</f>
         <v/>
       </c>
@@ -5359,21 +5445,21 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="29" t="n">
+      <c r="A14" s="28" t="n">
         <v>36.5</v>
       </c>
       <c r="B14" s="17" t="n">
         <v>320</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="28">
         <f>A14-A13</f>
         <v/>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="23">
         <f>0.5*(B13+B14)*C14</f>
         <v/>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="30">
         <f>E13+D14</f>
         <v/>
       </c>
@@ -5384,21 +5470,21 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="29" t="n">
+      <c r="A15" s="28" t="n">
         <v>37</v>
       </c>
       <c r="B15" s="17" t="n">
         <v>480</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="28">
         <f>A15-A14</f>
         <v/>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="23">
         <f>0.5*(B14+B15)*C15</f>
         <v/>
       </c>
-      <c r="E15" s="31">
+      <c r="E15" s="30">
         <f>E14+D15</f>
         <v/>
       </c>
@@ -5409,13 +5495,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="36" t="n">
+      <c r="A16" s="35" t="n">
         <v>37.28</v>
       </c>
       <c r="B16" s="17" t="n">
         <v>543</v>
       </c>
-      <c r="C16" s="36">
+      <c r="C16" s="35">
         <f>A16-A15</f>
         <v/>
       </c>
@@ -5434,21 +5520,21 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="29" t="n">
+      <c r="A17" s="28" t="n">
         <v>37.5</v>
       </c>
       <c r="B17" s="17" t="n">
         <v>700</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="28">
         <f>A17-A16</f>
         <v/>
       </c>
-      <c r="D17" s="24">
+      <c r="D17" s="23">
         <f>0.5*(B16+B17)*C17</f>
         <v/>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="30">
         <f>E16+D17</f>
         <v/>
       </c>
@@ -5459,21 +5545,21 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="29" t="n">
+      <c r="A18" s="28" t="n">
         <v>39.5</v>
       </c>
       <c r="B18" s="17" t="n">
         <v>1932</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="28">
         <f>A18-A17</f>
         <v/>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="23">
         <f>0.5*(B17+B18)*C18</f>
         <v/>
       </c>
-      <c r="E18" s="31">
+      <c r="E18" s="30">
         <f>E17+D18</f>
         <v/>
       </c>
@@ -5486,7 +5572,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Vmax (depuis Calcul_A)</t>
+          <t>Vmax_A (Calcul_A)</t>
         </is>
       </c>
       <c r="B21" s="18">
@@ -5497,10 +5583,10 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>WSEmax correspondant (m)</t>
-        </is>
-      </c>
-      <c r="B22" s="21">
+          <t>WSEmax_A (m)</t>
+        </is>
+      </c>
+      <c r="B22" s="38">
         <f>Parametres!B30</f>
         <v/>
       </c>
@@ -5508,41 +5594,63 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Vmax_B (Calcul_B)</t>
+        </is>
+      </c>
+      <c r="B23" s="18">
+        <f>Parametres!B34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>WSEmax_B (m)</t>
+        </is>
+      </c>
+      <c r="B24" s="38">
+        <f>Parametres!B36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>V disponible à 37.28 m (m³)</t>
         </is>
       </c>
-      <c r="B23" s="40">
+      <c r="B25" s="40">
         <f>E16</f>
         <v/>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Si Vmax &gt; cette valeur → le niveau dépasse la limite patron</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Si Vmax_A ou Vmax_B &gt; cette valeur → le niveau dépasse la limite patron</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Comment lire le résultat</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="37" t="inlineStr">
-        <is>
-          <t>Exemple: si Vmax = 5609 m³ et V(37.28)≈558 m³, alors WSEmax est au-dessus de 37.28 m (la table ira vers 39.5 m ou 'Hors table'). Affinez en entrant les vraies surfaces aux cotes intermédiaires (jaune).</t>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28"/>
+    <row r="28">
+      <c r="A28" s="36" t="inlineStr">
+        <is>
+          <t>Exemple: si Vmax_A = 5609 m³ et V(37.28)≈558 m³, alors WSEmax_A est au-dessus de 37.28 m (la table ira vers 39.5 m ou 'Hors table'). Affinez en entrant les vraies surfaces aux cotes intermédiaires (jaune). Parametres montre WSEmax_A (B30) et WSEmax_B (B36) séparément.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A2:G4"/>
+    <mergeCell ref="A28:F30"/>
     <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A26:F28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5773,7 +5881,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8. Niveau d'eau max: Stage_Storage (surfaces levé) + Parametres!B30 = WSEmax.</t>
+          <t>8. Niveau d'eau max: Stage_Storage + Parametres!B30 (WSEmax_A) et B36 (WSEmax_B).</t>
         </is>
       </c>
     </row>

--- a/engineering/drainage-design/retention_volume/Volume_Retention_Ponceau_900.xlsx
+++ b/engineering/drainage-design/retention_volume/Volume_Retention_Ponceau_900.xlsx
@@ -12,9 +12,11 @@
     <sheet name="Calcul_A" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Courbe_QH_900" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Calcul_B" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Stage_Storage" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Fichiers_lies" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Methode" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Compose_900" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Calcul_C" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Stage_Storage" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Fichiers_lies" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Methode" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -123,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -144,6 +146,7 @@
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -166,8 +169,8 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -813,6 +816,188 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:t>Qout composé vs WSE</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Compose_900'!J14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Compose_900'!$A$15:$A$107</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Compose_900'!$J$15:$J$107</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Compose_900'!H14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Compose_900'!$A$15:$A$107</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Compose_900'!$H$15:$H$107</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Compose_900'!I14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Compose_900'!$A$15:$A$107</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Compose_900'!$I$15:$I$107</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>WSE (m)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Q (m³/s)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
               <a:t>V cumulé vs WSE (levé)</a:t>
             </a:r>
           </a:p>
@@ -1023,6 +1208,33 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>12</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -1338,7 +1550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1649,336 +1861,609 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Aire plan d'eau approx. pour H = V/A (Méthode B)</t>
+          <t>Aire plan d'eau approx. pour H = V/A (Méthode B seulement)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Résultats Méthode A — Qout constant (feuille Calcul_A)</t>
+          <t>Débordement Méthode C — fossé trapèze au-dessus du crown (jaune)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Vmax_A (m³)</t>
-        </is>
-      </c>
-      <c r="B27" s="18">
-        <f>Calcul_A!B3</f>
-        <v/>
+          <t>Crest = crown Ø900 (m)</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="n">
+        <v>35.78</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Volume max stocké avec Qout fixe (Parametres B22)</t>
+          <t>34.88+0.90 — overflow starts when WSE &gt;= crest</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>V_dimensionnement_A = Vmax_A × facteur (m³)</t>
-        </is>
-      </c>
-      <c r="B28" s="18">
-        <f>B27*B23</f>
-        <v/>
+          <t>b fond fossé (m)</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hmax approx_A (m) = Vmax_A / Aire</t>
-        </is>
-      </c>
-      <c r="B29" s="19">
-        <f>IF(B24&gt;0,B27/B24,0)</f>
-        <v/>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Estimation grossière si l'aire de bassin est constante (pas le levé)</t>
-        </is>
+          <t>n fossé Manning (-)</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="n">
+        <v>0.035</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>WSEmax_A depuis levé (m) — feuille Stage_Storage</t>
-        </is>
-      </c>
-      <c r="B30" s="20">
-        <f>IF(B27&lt;=Stage_Storage!E11,Stage_Storage!A11,IF(B27&gt;=Stage_Storage!E18,"Hors table (&gt;=39.5 m — étendre levé)",INDEX(Stage_Storage!$A$11:$A$18,MATCH(B27,Stage_Storage!$E$11:$E$18,1))+(B27-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B27,Stage_Storage!$E$11:$E$18,1)))/(INDEX(Stage_Storage!$E$11:$E$18,MATCH(B27,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B27,Stage_Storage!$E$11:$E$18,1)))*(INDEX(Stage_Storage!$A$11:$A$18,MATCH(B27,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(B27,Stage_Storage!$E$11:$E$18,1)))))</f>
-        <v/>
+          <t>z pente talus (H:V)</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="n">
+        <v>2</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cote d'eau max pour le Vmax_A: on lit sur Stage_Storage quelle WSE donne ce volume (courbe volume–cote du levé)</t>
+          <t>z=2 → 2H:1V</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HW max_A = WSEmax_A − radier Ø900 (m)</t>
-        </is>
-      </c>
-      <c r="B31" s="20">
-        <f>IF(ISNUMBER(B30),B30-34.88,"")</f>
-        <v/>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Comparer à 2.40 m (limite patron = +1.5 m au-dessus du crown)</t>
+          <t>S pente fossé (-)</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>L fossé (m)</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Longueur pour V_ditch = A × L et Manning</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Résultats Méthode B — Qout = f(H) FHWA (feuille Calcul_B)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Vmax_B (m³)</t>
-        </is>
-      </c>
-      <c r="B34" s="18">
-        <f>Calcul_B!B7</f>
-        <v/>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Volume max stocké avec Q lu sur Courbe_QH_900 (dépend de Aire B24)</t>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Qout_C</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Q_900(WSE)+Q_overflow(WSE)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>V_C = V_pond(levé) + V_ditch — feuilles Compose_900 + Calcul_C</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>V_dimensionnement_B = Vmax_B × facteur (m³)</t>
-        </is>
-      </c>
-      <c r="B35" s="18">
-        <f>B34*B23</f>
-        <v/>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Résultats Méthode A — Qout constant (feuille Calcul_A)</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>WSEmax_B depuis levé (m) — feuille Stage_Storage</t>
-        </is>
-      </c>
-      <c r="B36" s="20">
-        <f>IF(B34&lt;=Stage_Storage!E11,Stage_Storage!A11,IF(B34&gt;=Stage_Storage!E18,"Hors table (&gt;=39.5 m — étendre levé)",INDEX(Stage_Storage!$A$11:$A$18,MATCH(B34,Stage_Storage!$E$11:$E$18,1))+(B34-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B34,Stage_Storage!$E$11:$E$18,1)))/(INDEX(Stage_Storage!$E$11:$E$18,MATCH(B34,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B34,Stage_Storage!$E$11:$E$18,1)))*(INDEX(Stage_Storage!$A$11:$A$18,MATCH(B34,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(B34,Stage_Storage!$E$11:$E$18,1)))))</f>
+          <t>Vmax_A (m³)</t>
+        </is>
+      </c>
+      <c r="B36" s="19">
+        <f>Calcul_A!B3</f>
         <v/>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Même lecture volume→cote que B30, mais avec Vmax_B au lieu de Vmax_A</t>
+          <t>Volume max stocké avec Qout fixe (Parametres B22)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HW max_B = WSEmax_B − radier Ø900 (m)</t>
-        </is>
-      </c>
-      <c r="B37" s="20">
-        <f>IF(ISNUMBER(B36),B36-34.88,"")</f>
-        <v/>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Comparer à 2.40 m (limite patron)</t>
+          <t>V_dimensionnement_A = Vmax_A × facteur (m³)</t>
+        </is>
+      </c>
+      <c r="B37" s="19">
+        <f>B36*B23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Hmax approx_A (m) = Vmax_A / Aire</t>
+        </is>
+      </c>
+      <c r="B38" s="20">
+        <f>IF(B24&gt;0,B36/B24,0)</f>
+        <v/>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Estimation grossière si l'aire de bassin est constante (pas le levé)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Comment lire WSEmax (A ou B)</t>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>WSEmax_A depuis levé (m) — feuille Stage_Storage</t>
+        </is>
+      </c>
+      <c r="B39" s="21">
+        <f>IF(B36&lt;=Stage_Storage!E11,Stage_Storage!A11,IF(B36&gt;=Stage_Storage!E18,"Hors table (&gt;=39.5 m — étendre levé)",INDEX(Stage_Storage!$A$11:$A$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1))+(B36-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)))/(INDEX(Stage_Storage!$E$11:$E$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)))*(INDEX(Stage_Storage!$A$11:$A$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Cote d'eau max pour le Vmax_A: on lit sur Stage_Storage quelle WSE donne ce volume (courbe volume–cote du levé)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1) Calcul_A (ou B) donne un volume max stocké Vmax pendant l'orage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2) La feuille Stage_Storage convertit vos surfaces de levé en courbe: volume cumulé ↔ cote d'eau (WSE).</t>
+          <t>HW max_A = WSEmax_A − radier Ø900 (m)</t>
+        </is>
+      </c>
+      <c r="B40" s="21">
+        <f>IF(ISNUMBER(B39),B39-34.88,"")</f>
+        <v/>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Comparer à 2.40 m (limite patron = +1.5 m au-dessus du crown)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>3) WSEmax = la cote sur cette courbe qui correspond à ce Vmax (interpolation).</t>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Résultats Méthode B — Qout = f(H) FHWA pipe seul (feuille Calcul_B)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Exemple: si Vmax_A ≈ volume entre 37.28 m et 39.5 m sur le levé → WSEmax_A ≈ 38.75 m.</t>
+          <t>Vmax_B (m³)</t>
+        </is>
+      </c>
+      <c r="B43" s="19">
+        <f>Calcul_B!B7</f>
+        <v/>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Volume max stocké avec Q lu sur Courbe_QH_900 (dépend de Aire B24)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4) Ce n'est PAS une cote saisie à la main: c'est Vmax lu sur le levé. Hmax≈V/Aire (B29) est plus grossier.</t>
+          <t>V_dimensionnement_B = Vmax_B × facteur (m³)</t>
+        </is>
+      </c>
+      <c r="B44" s="19">
+        <f>B43*B23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>WSEmax_B depuis levé (m) — feuille Stage_Storage</t>
+        </is>
+      </c>
+      <c r="B45" s="21">
+        <f>IF(B43&lt;=Stage_Storage!E11,Stage_Storage!A11,IF(B43&gt;=Stage_Storage!E18,"Hors table (&gt;=39.5 m — étendre levé)",INDEX(Stage_Storage!$A$11:$A$18,MATCH(B43,Stage_Storage!$E$11:$E$18,1))+(B43-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B43,Stage_Storage!$E$11:$E$18,1)))/(INDEX(Stage_Storage!$E$11:$E$18,MATCH(B43,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B43,Stage_Storage!$E$11:$E$18,1)))*(INDEX(Stage_Storage!$A$11:$A$18,MATCH(B43,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(B43,Stage_Storage!$E$11:$E$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Même lecture volume→cote que B39, mais avec Vmax_B</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Inlet control vs outlet control — qu'est-ce que ça veut dire?</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>• Inlet control (contrôle à l'entrée): le débit est limité par l'entrée du ponceau (forme d'entrée, HW/D).</t>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>HW max_B = WSEmax_B − radier Ø900 (m)</t>
+        </is>
+      </c>
+      <c r="B46" s="21">
+        <f>IF(ISNUMBER(B45),B45-34.88,"")</f>
+        <v/>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Comparer à 2.40 m (limite patron)</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Le tuyau aval « n'aspire » pas assez pour influencer — Q dépend surtout de la charge amont H, pas de L ni de n.</t>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Résultats Méthode C — Ø900 + fossé trapèze (Compose_900 + Calcul_C)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>• Outlet control (contrôle à la sortie / frottement): le débit dépend de la longueur, de n, de la pente et de la charge</t>
+          <t>Vmax_C (m³) = max(V_pond + V_ditch)</t>
+        </is>
+      </c>
+      <c r="B49" s="19">
+        <f>Calcul_C!B7</f>
+        <v/>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Stockage total routé (levé + fossé)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (énergie amont → aval). Manning pleine section est une hypothèse de type outlet/frottement à section pleine.</t>
-        </is>
+          <t>V_dimensionnement_C = Vmax_C × facteur (m³)</t>
+        </is>
+      </c>
+      <c r="B50" s="19">
+        <f>B49*B23</f>
+        <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>• Ici L/D = 56 (tuyau assez long) → le contrôle par frottement (outlet) est souvent plausible,</t>
+          <t>WSEmax_C (m) — du routage Calcul_C</t>
+        </is>
+      </c>
+      <c r="B51" s="21">
+        <f>Calcul_C!B8</f>
+        <v/>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Directement du niveau dans Calcul_C (V inclut le fossé)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">  mais sans analyse FHWA/HY-8 on ne peut pas l'affirmer. Pour dimensionner la rétention, Q_plein constant est</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  en général prudent (si la charge monte, le débit réel peut être un peu plus élevé → Vmax un peu plus bas).</t>
+          <t>HW max_C = WSEmax_C − radier Ø900 (m)</t>
+        </is>
+      </c>
+      <c r="B52" s="21">
+        <f>IF(ISNUMBER(B51),B51-34.88,"")</f>
+        <v/>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Comparer à 2.40 m (limite patron); overflow actif si WSE&gt;crest</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>• On n'a pas besoin de trancher IC/OC pour utiliser ce classeur: garder Qout = Q_plein (ou 1.77) suffit pour une 1re estimation.</t>
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Comment lire WSEmax (A / B / C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1) A et B: Vmax = volume pondé; WSEmax lu sur Stage_Storage (levé seul).</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Notes</t>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2) C: Qout = Q_900(WSE) + Q_overflow(WSE); V = V_pond + V_ditch; WSEmax_C vient de Calcul_C.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>• Méthode A: Qout fixe = Q_plein Manning Ø900 (n=0,013). Pas un jugement IC/OC complet.</t>
+          <t>3) Crest = crown = 35.78 m → au-dessus, le fossé trapèze (b, n, z, S, L) ajoute débit et volume.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>• Le stockage commence quand Qin dépasse Qout; Vmax = max du volume stocké (pas (Qp−Qout)×durée).</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>• Méthode B: Qout = f(H) depuis feuille Courbe_QH_900 (FHWA inlet+outlet) — résultats en B34–B37.</t>
+          <t>4) Ne pas comparer Vmax_C à V_pond seul sans retirer V_ditch; comparer plutôt les WSEmax.</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>• Voir feuille Fichiers_lies pour les anciens Excel HY-8 / ponceau+fossé.</t>
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Inlet control vs outlet control — qu'est-ce que ça veut dire?</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>• Vérifier que le radier amont Ø900 (34.88) est bien le fond de la zone de rétention étudiée.</t>
+          <t>• Inlet control (contrôle à l'entrée): le débit est limité par l'entrée du ponceau (forme d'entrée, HW/D).</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>• WSEmax_A = B30 (depuis Vmax_A); WSEmax_B = B36 (depuis Vmax_B); les deux lisent Stage_Storage.</t>
+          <t xml:space="preserve">  Le tuyau aval « n'aspire » pas assez pour influencer — Q dépend surtout de la charge amont H, pas de L ni de n.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>• Outlet control (contrôle à la sortie / frottement): le débit dépend de la longueur, de n, de la pente et de la charge</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (énergie amont → aval). Manning pleine section est une hypothèse de type outlet/frottement à section pleine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>• Ici L/D = 56 (tuyau assez long) → le contrôle par frottement (outlet) est souvent plausible,</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  mais sans analyse FHWA/HY-8 on ne peut pas l'affirmer. Pour dimensionner la rétention, Q_plein constant est</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  en général prudent (si la charge monte, le débit réel peut être un peu plus élevé → Vmax un peu plus bas).</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>• On n'a pas besoin de trancher IC/OC pour utiliser ce classeur: garder Qout = Q_plein (ou 1.77) suffit pour une 1re estimation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>• Méthode A: Qout fixe = Q_plein Manning Ø900 (n=0,013).</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>• Méthode B: Qout = f(H) pipe seul (Courbe_QH_900) — résultats B43–B46.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>• Méthode C: Qout = Q_900 + Q_overflow; V = V_pond + V_ditch — Compose_900 + Calcul_C (B49–B52).</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>• Le stockage commence quand Qin dépasse Qout; Vmax = max du volume stocké.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>• Vérifier que le radier amont Ø900 (34.88) est bien le fond de la zone de rétention étudiée.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="A48:H48"/>
-    <mergeCell ref="A59:H59"/>
-    <mergeCell ref="A51:H51"/>
-    <mergeCell ref="A60:H60"/>
-    <mergeCell ref="A49:H49"/>
+  <mergeCells count="19">
+    <mergeCell ref="A67:H67"/>
+    <mergeCell ref="A73:H73"/>
+    <mergeCell ref="A64:H64"/>
     <mergeCell ref="A61:H61"/>
-    <mergeCell ref="A54:H54"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="A65:H65"/>
+    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="A75:H75"/>
+    <mergeCell ref="A74:H74"/>
+    <mergeCell ref="A56:H56"/>
     <mergeCell ref="A9:H10"/>
+    <mergeCell ref="A55:H55"/>
     <mergeCell ref="A57:H57"/>
-    <mergeCell ref="A42:H42"/>
-    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A71:H71"/>
     <mergeCell ref="A62:H62"/>
-    <mergeCell ref="A53:H53"/>
-    <mergeCell ref="A43:H43"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="A63:H63"/>
+    <mergeCell ref="A72:H72"/>
+    <mergeCell ref="A68:H68"/>
     <mergeCell ref="A58:H58"/>
-    <mergeCell ref="A40:H40"/>
   </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="110" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="43" t="inlineStr">
+        <is>
+          <t>Méthode — volume de rétention</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1. Hydrogramme Qin(t) à l'entrée de la zone de rétention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2. Débit sortant contrôlé par le Ø900 (en série avant le Ø1200).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3. Capacité Ø900 — trois niveaux:</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   A) Q_plein Manning (n=0.013) ≈ 1.668 m³/s → Méthode A (constant).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   B) Courbe Q=f(H) FHWA HDS-5 (inlet + outlet) → feuille Courbe_QH_900 + Calcul_B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   C) Qout = Q_900(WSE) + Q_overflow(WSE); V = V_pond + V_ditch → Compose_900 + Calcul_C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>4. Méthode A: Qout = constante = Q_plein (jaune Parametres). Bon pour 1re estimation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>5. Méthode B: Qout lu sur la courbe selon H=V/Aire (charge amont), pipe seul.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>6. Méthode C: crest = crown; fossé trapèze (b,n,z,S,L) au-dessus; stockage levé + fossé.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>7. Sur ce Ø900 (L/D≈56), le calcul FHWA indique surtout un contrôle outlet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>8. Le Ø1200 est aval: n'augmente pas la sortie de la rétention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>9. Niveau d'eau max: A/B via Stage_Storage; C via Calcul_C (Parametres B39 / B45 / B51).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Fichiers liés / anciens Excel: voir feuille Fichiers_lies.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1999,7 +2484,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>Hydrogramme d'entrée (point Ø1500 / entrée rétention) — FORMULES LIVE</t>
         </is>
@@ -2008,7 +2493,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Qin(t) = ratio(t) × Qpointe. Changez Qpointe (jaune B4) : toute la colonne Qin et Calcul_A/B se mettent à jour. Les ratios viennent de votre hydrogramme d'origine (pointe 9,6). À t=0, ratio≈0,081 → Qin=0,778 si Qpointe=9,6 (débit de départ du projet, pas zéro).</t>
+          <t>Qin(t) = ratio(t) × Qpointe. Changez Qpointe (jaune B4) : toute la colonne Qin et Calcul_A/B/C se mettent à jour. Les ratios viennent de votre hydrogramme d'origine (pointe 9,6). À t=0, ratio≈0,081 → Qin=0,778 si Qpointe=9,6 (débit de départ du projet, pas zéro).</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2519,7 @@
           <t>t pointe (min)</t>
         </is>
       </c>
-      <c r="B5" s="22" t="n">
+      <c r="B5" s="23" t="n">
         <v>22.5</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -2066,10 +2551,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="n">
+      <c r="A8" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="B8" s="24" t="n">
+      <c r="B8" s="25" t="n">
         <v>0.081042</v>
       </c>
       <c r="C8" s="5">
@@ -2083,10 +2568,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="n">
+      <c r="A9" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="24" t="n">
+      <c r="B9" s="25" t="n">
         <v>0.121875</v>
       </c>
       <c r="C9" s="5">
@@ -2096,10 +2581,10 @@
       <c r="D9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="n">
+      <c r="A10" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="B10" s="24" t="n">
+      <c r="B10" s="25" t="n">
         <v>0.193438</v>
       </c>
       <c r="C10" s="5">
@@ -2109,10 +2594,10 @@
       <c r="D10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="23" t="n">
+      <c r="A11" s="24" t="n">
         <v>15</v>
       </c>
-      <c r="B11" s="24" t="n">
+      <c r="B11" s="25" t="n">
         <v>0.333542</v>
       </c>
       <c r="C11" s="5">
@@ -2122,10 +2607,10 @@
       <c r="D11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="n">
+      <c r="A12" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="B12" s="24" t="n">
+      <c r="B12" s="25" t="n">
         <v>0.657188</v>
       </c>
       <c r="C12" s="5">
@@ -2135,10 +2620,10 @@
       <c r="D12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="23" t="n">
+      <c r="A13" s="24" t="n">
         <v>22.5</v>
       </c>
-      <c r="B13" s="24" t="n">
+      <c r="B13" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="8">
@@ -2152,10 +2637,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="23" t="n">
+      <c r="A14" s="24" t="n">
         <v>27.5</v>
       </c>
-      <c r="B14" s="24" t="n">
+      <c r="B14" s="25" t="n">
         <v>0.608958</v>
       </c>
       <c r="C14" s="5">
@@ -2165,10 +2650,10 @@
       <c r="D14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="n">
+      <c r="A15" s="24" t="n">
         <v>32.5</v>
       </c>
-      <c r="B15" s="24" t="n">
+      <c r="B15" s="25" t="n">
         <v>0.401771</v>
       </c>
       <c r="C15" s="5">
@@ -2178,10 +2663,10 @@
       <c r="D15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="23" t="n">
+      <c r="A16" s="24" t="n">
         <v>37.5</v>
       </c>
-      <c r="B16" s="24" t="n">
+      <c r="B16" s="25" t="n">
         <v>0.280104</v>
       </c>
       <c r="C16" s="5">
@@ -2191,10 +2676,10 @@
       <c r="D16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="23" t="n">
+      <c r="A17" s="24" t="n">
         <v>42.5</v>
       </c>
-      <c r="B17" s="24" t="n">
+      <c r="B17" s="25" t="n">
         <v>0.203438</v>
       </c>
       <c r="C17" s="5">
@@ -2204,10 +2689,10 @@
       <c r="D17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="23" t="n">
+      <c r="A18" s="24" t="n">
         <v>47.5</v>
       </c>
-      <c r="B18" s="24" t="n">
+      <c r="B18" s="25" t="n">
         <v>0.152292</v>
       </c>
       <c r="C18" s="5">
@@ -2217,10 +2702,10 @@
       <c r="D18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="23" t="n">
+      <c r="A19" s="24" t="n">
         <v>52.5</v>
       </c>
-      <c r="B19" s="24" t="n">
+      <c r="B19" s="25" t="n">
         <v>0.116771</v>
       </c>
       <c r="C19" s="5">
@@ -2230,10 +2715,10 @@
       <c r="D19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="23" t="n">
+      <c r="A20" s="24" t="n">
         <v>57.5</v>
       </c>
-      <c r="B20" s="24" t="n">
+      <c r="B20" s="25" t="n">
         <v>0.091146</v>
       </c>
       <c r="C20" s="5">
@@ -2248,7 +2733,7 @@
           <t>Qin max (contrôle)</t>
         </is>
       </c>
-      <c r="B22" s="25">
+      <c r="B22" s="26">
         <f>MAX(C8:C20)</f>
         <v/>
       </c>
@@ -2299,7 +2784,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>Méthode A — Qout constant = capacité Ø900</t>
         </is>
@@ -2311,7 +2796,7 @@
           <t>Qout (m³/s)</t>
         </is>
       </c>
-      <c r="B2" s="26">
+      <c r="B2" s="27">
         <f>Parametres!B22</f>
         <v/>
       </c>
@@ -2322,7 +2807,7 @@
           <t>Vmax (m³)</t>
         </is>
       </c>
-      <c r="B3" s="27">
+      <c r="B3" s="28">
         <f>MAX(H8:H20)</f>
         <v/>
       </c>
@@ -2404,7 +2889,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="23">
+      <c r="A8" s="24">
         <f>Hydrogramme!A8</f>
         <v/>
       </c>
@@ -2412,7 +2897,7 @@
         <f>Hydrogramme!C8</f>
         <v/>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="29">
         <f>$B$2</f>
         <v/>
       </c>
@@ -2429,7 +2914,7 @@
       <c r="G8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="29" t="n">
+      <c r="H8" s="30" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="4">
@@ -2438,7 +2923,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="23">
+      <c r="A9" s="24">
         <f>Hydrogramme!A9</f>
         <v/>
       </c>
@@ -2446,7 +2931,7 @@
         <f>Hydrogramme!C9</f>
         <v/>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="29">
         <f>$B$2</f>
         <v/>
       </c>
@@ -2454,19 +2939,19 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="24">
         <f>(A9-A8)*60</f>
         <v/>
       </c>
-      <c r="F9" s="23">
+      <c r="F9" s="24">
         <f>0.5*(B8+B9)*E9</f>
         <v/>
       </c>
-      <c r="G9" s="23">
+      <c r="G9" s="24">
         <f>F9-(H9-H8)</f>
         <v/>
       </c>
-      <c r="H9" s="30">
+      <c r="H9" s="31">
         <f>MAX(0,H8+0.5*(D8+D9)*E9)</f>
         <v/>
       </c>
@@ -2476,7 +2961,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="23">
+      <c r="A10" s="24">
         <f>Hydrogramme!A10</f>
         <v/>
       </c>
@@ -2484,7 +2969,7 @@
         <f>Hydrogramme!C10</f>
         <v/>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="29">
         <f>$B$2</f>
         <v/>
       </c>
@@ -2492,19 +2977,19 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="24">
         <f>(A10-A9)*60</f>
         <v/>
       </c>
-      <c r="F10" s="23">
+      <c r="F10" s="24">
         <f>0.5*(B9+B10)*E10</f>
         <v/>
       </c>
-      <c r="G10" s="23">
+      <c r="G10" s="24">
         <f>F10-(H10-H9)</f>
         <v/>
       </c>
-      <c r="H10" s="30">
+      <c r="H10" s="31">
         <f>MAX(0,H9+0.5*(D9+D10)*E10)</f>
         <v/>
       </c>
@@ -2514,7 +2999,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="23">
+      <c r="A11" s="24">
         <f>Hydrogramme!A11</f>
         <v/>
       </c>
@@ -2522,7 +3007,7 @@
         <f>Hydrogramme!C11</f>
         <v/>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="29">
         <f>$B$2</f>
         <v/>
       </c>
@@ -2530,19 +3015,19 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="24">
         <f>(A11-A10)*60</f>
         <v/>
       </c>
-      <c r="F11" s="23">
+      <c r="F11" s="24">
         <f>0.5*(B10+B11)*E11</f>
         <v/>
       </c>
-      <c r="G11" s="23">
+      <c r="G11" s="24">
         <f>F11-(H11-H10)</f>
         <v/>
       </c>
-      <c r="H11" s="30">
+      <c r="H11" s="31">
         <f>MAX(0,H10+0.5*(D10+D11)*E11)</f>
         <v/>
       </c>
@@ -2552,7 +3037,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="23">
+      <c r="A12" s="24">
         <f>Hydrogramme!A12</f>
         <v/>
       </c>
@@ -2560,7 +3045,7 @@
         <f>Hydrogramme!C12</f>
         <v/>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="29">
         <f>$B$2</f>
         <v/>
       </c>
@@ -2568,19 +3053,19 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="24">
         <f>(A12-A11)*60</f>
         <v/>
       </c>
-      <c r="F12" s="23">
+      <c r="F12" s="24">
         <f>0.5*(B11+B12)*E12</f>
         <v/>
       </c>
-      <c r="G12" s="23">
+      <c r="G12" s="24">
         <f>F12-(H12-H11)</f>
         <v/>
       </c>
-      <c r="H12" s="30">
+      <c r="H12" s="31">
         <f>MAX(0,H11+0.5*(D11+D12)*E12)</f>
         <v/>
       </c>
@@ -2590,7 +3075,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="23">
+      <c r="A13" s="24">
         <f>Hydrogramme!A13</f>
         <v/>
       </c>
@@ -2598,7 +3083,7 @@
         <f>Hydrogramme!C13</f>
         <v/>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="29">
         <f>$B$2</f>
         <v/>
       </c>
@@ -2606,19 +3091,19 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="23">
+      <c r="E13" s="24">
         <f>(A13-A12)*60</f>
         <v/>
       </c>
-      <c r="F13" s="23">
+      <c r="F13" s="24">
         <f>0.5*(B12+B13)*E13</f>
         <v/>
       </c>
-      <c r="G13" s="23">
+      <c r="G13" s="24">
         <f>F13-(H13-H12)</f>
         <v/>
       </c>
-      <c r="H13" s="30">
+      <c r="H13" s="31">
         <f>MAX(0,H12+0.5*(D12+D13)*E13)</f>
         <v/>
       </c>
@@ -2628,7 +3113,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="23">
+      <c r="A14" s="24">
         <f>Hydrogramme!A14</f>
         <v/>
       </c>
@@ -2636,7 +3121,7 @@
         <f>Hydrogramme!C14</f>
         <v/>
       </c>
-      <c r="C14" s="28">
+      <c r="C14" s="29">
         <f>$B$2</f>
         <v/>
       </c>
@@ -2644,19 +3129,19 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="23">
+      <c r="E14" s="24">
         <f>(A14-A13)*60</f>
         <v/>
       </c>
-      <c r="F14" s="23">
+      <c r="F14" s="24">
         <f>0.5*(B13+B14)*E14</f>
         <v/>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="24">
         <f>F14-(H14-H13)</f>
         <v/>
       </c>
-      <c r="H14" s="30">
+      <c r="H14" s="31">
         <f>MAX(0,H13+0.5*(D13+D14)*E14)</f>
         <v/>
       </c>
@@ -2666,7 +3151,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="23">
+      <c r="A15" s="24">
         <f>Hydrogramme!A15</f>
         <v/>
       </c>
@@ -2674,7 +3159,7 @@
         <f>Hydrogramme!C15</f>
         <v/>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="29">
         <f>$B$2</f>
         <v/>
       </c>
@@ -2682,19 +3167,19 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="23">
+      <c r="E15" s="24">
         <f>(A15-A14)*60</f>
         <v/>
       </c>
-      <c r="F15" s="23">
+      <c r="F15" s="24">
         <f>0.5*(B14+B15)*E15</f>
         <v/>
       </c>
-      <c r="G15" s="23">
+      <c r="G15" s="24">
         <f>F15-(H15-H14)</f>
         <v/>
       </c>
-      <c r="H15" s="30">
+      <c r="H15" s="31">
         <f>MAX(0,H14+0.5*(D14+D15)*E15)</f>
         <v/>
       </c>
@@ -2704,7 +3189,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="23">
+      <c r="A16" s="24">
         <f>Hydrogramme!A16</f>
         <v/>
       </c>
@@ -2712,7 +3197,7 @@
         <f>Hydrogramme!C16</f>
         <v/>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="29">
         <f>$B$2</f>
         <v/>
       </c>
@@ -2720,19 +3205,19 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="23">
+      <c r="E16" s="24">
         <f>(A16-A15)*60</f>
         <v/>
       </c>
-      <c r="F16" s="23">
+      <c r="F16" s="24">
         <f>0.5*(B15+B16)*E16</f>
         <v/>
       </c>
-      <c r="G16" s="23">
+      <c r="G16" s="24">
         <f>F16-(H16-H15)</f>
         <v/>
       </c>
-      <c r="H16" s="30">
+      <c r="H16" s="31">
         <f>MAX(0,H15+0.5*(D15+D16)*E16)</f>
         <v/>
       </c>
@@ -2742,7 +3227,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="23">
+      <c r="A17" s="24">
         <f>Hydrogramme!A17</f>
         <v/>
       </c>
@@ -2750,7 +3235,7 @@
         <f>Hydrogramme!C17</f>
         <v/>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="29">
         <f>$B$2</f>
         <v/>
       </c>
@@ -2758,19 +3243,19 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="24">
         <f>(A17-A16)*60</f>
         <v/>
       </c>
-      <c r="F17" s="23">
+      <c r="F17" s="24">
         <f>0.5*(B16+B17)*E17</f>
         <v/>
       </c>
-      <c r="G17" s="23">
+      <c r="G17" s="24">
         <f>F17-(H17-H16)</f>
         <v/>
       </c>
-      <c r="H17" s="30">
+      <c r="H17" s="31">
         <f>MAX(0,H16+0.5*(D16+D17)*E17)</f>
         <v/>
       </c>
@@ -2780,7 +3265,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="23">
+      <c r="A18" s="24">
         <f>Hydrogramme!A18</f>
         <v/>
       </c>
@@ -2788,7 +3273,7 @@
         <f>Hydrogramme!C18</f>
         <v/>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="29">
         <f>$B$2</f>
         <v/>
       </c>
@@ -2796,19 +3281,19 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="23">
+      <c r="E18" s="24">
         <f>(A18-A17)*60</f>
         <v/>
       </c>
-      <c r="F18" s="23">
+      <c r="F18" s="24">
         <f>0.5*(B17+B18)*E18</f>
         <v/>
       </c>
-      <c r="G18" s="23">
+      <c r="G18" s="24">
         <f>F18-(H18-H17)</f>
         <v/>
       </c>
-      <c r="H18" s="30">
+      <c r="H18" s="31">
         <f>MAX(0,H17+0.5*(D17+D18)*E18)</f>
         <v/>
       </c>
@@ -2818,7 +3303,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="23">
+      <c r="A19" s="24">
         <f>Hydrogramme!A19</f>
         <v/>
       </c>
@@ -2826,7 +3311,7 @@
         <f>Hydrogramme!C19</f>
         <v/>
       </c>
-      <c r="C19" s="28">
+      <c r="C19" s="29">
         <f>$B$2</f>
         <v/>
       </c>
@@ -2834,19 +3319,19 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="23">
+      <c r="E19" s="24">
         <f>(A19-A18)*60</f>
         <v/>
       </c>
-      <c r="F19" s="23">
+      <c r="F19" s="24">
         <f>0.5*(B18+B19)*E19</f>
         <v/>
       </c>
-      <c r="G19" s="23">
+      <c r="G19" s="24">
         <f>F19-(H19-H18)</f>
         <v/>
       </c>
-      <c r="H19" s="30">
+      <c r="H19" s="31">
         <f>MAX(0,H18+0.5*(D18+D19)*E19)</f>
         <v/>
       </c>
@@ -2856,7 +3341,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="23">
+      <c r="A20" s="24">
         <f>Hydrogramme!A20</f>
         <v/>
       </c>
@@ -2864,7 +3349,7 @@
         <f>Hydrogramme!C20</f>
         <v/>
       </c>
-      <c r="C20" s="28">
+      <c r="C20" s="29">
         <f>$B$2</f>
         <v/>
       </c>
@@ -2872,19 +3357,19 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="23">
+      <c r="E20" s="24">
         <f>(A20-A19)*60</f>
         <v/>
       </c>
-      <c r="F20" s="23">
+      <c r="F20" s="24">
         <f>0.5*(B19+B20)*E20</f>
         <v/>
       </c>
-      <c r="G20" s="23">
+      <c r="G20" s="24">
         <f>F20-(H20-H19)</f>
         <v/>
       </c>
-      <c r="H20" s="30">
+      <c r="H20" s="31">
         <f>MAX(0,H19+0.5*(D19+D20)*E20)</f>
         <v/>
       </c>
@@ -2918,7 +3403,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>Courbe de capacité Ø900 — Q = f(H) (FHWA HDS-5 inlet + outlet) — FORMULES LIVE</t>
         </is>
@@ -2958,32 +3443,32 @@
           <t>béton typ. 0.012–0.015</t>
         </is>
       </c>
-      <c r="E6" s="31" t="inlineStr">
+      <c r="E6" s="32" t="inlineStr">
         <is>
           <t>entrée</t>
         </is>
       </c>
-      <c r="F6" s="31" t="inlineStr">
+      <c r="F6" s="32" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="G6" s="31" t="inlineStr">
+      <c r="G6" s="32" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H6" s="31" t="inlineStr">
+      <c r="H6" s="32" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="I6" s="31" t="inlineStr">
+      <c r="I6" s="32" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J6" s="31" t="inlineStr">
+      <c r="J6" s="32" t="inlineStr">
         <is>
           <t>Ke</t>
         </is>
@@ -3099,7 +3584,7 @@
           <t>S0 = (Zin-Zout)/L</t>
         </is>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="33">
         <f>(B9-B10)/B8</f>
         <v/>
       </c>
@@ -3130,7 +3615,7 @@
           <t>Entrée (texte exact)</t>
         </is>
       </c>
-      <c r="B13" s="33" t="inlineStr">
+      <c r="B13" s="34" t="inlineStr">
         <is>
           <t>square_edge</t>
         </is>
@@ -3147,7 +3632,7 @@
           <t>Q_plein Manning (réf.)</t>
         </is>
       </c>
-      <c r="B15" s="25">
+      <c r="B15" s="26">
         <f>(1/B6)*(PI()*B7^2/4)*((B7/4)^(2/3))*SQRT(B11)</f>
         <v/>
       </c>
@@ -3163,7 +3648,7 @@
           <t>K (lu)</t>
         </is>
       </c>
-      <c r="B17" s="34">
+      <c r="B17" s="35">
         <f>IFERROR(VLOOKUP(B13,$E$7:$J$9,2,FALSE),0.0098)</f>
         <v/>
       </c>
@@ -3174,7 +3659,7 @@
           <t>M (lu)</t>
         </is>
       </c>
-      <c r="B18" s="34">
+      <c r="B18" s="35">
         <f>IFERROR(VLOOKUP(B13,$E$7:$J$9,3,FALSE),2)</f>
         <v/>
       </c>
@@ -3185,7 +3670,7 @@
           <t>c (lu)</t>
         </is>
       </c>
-      <c r="B19" s="34">
+      <c r="B19" s="35">
         <f>IFERROR(VLOOKUP(B13,$E$7:$J$9,4,FALSE),0.0398)</f>
         <v/>
       </c>
@@ -3196,7 +3681,7 @@
           <t>Y (lu)</t>
         </is>
       </c>
-      <c r="B20" s="34">
+      <c r="B20" s="35">
         <f>IFERROR(VLOOKUP(B13,$E$7:$J$9,5,FALSE),0.67)</f>
         <v/>
       </c>
@@ -3207,7 +3692,7 @@
           <t>Ke (lu)</t>
         </is>
       </c>
-      <c r="B21" s="34">
+      <c r="B21" s="35">
         <f>IFERROR(VLOOKUP(B13,$E$7:$J$9,6,FALSE),0.5)</f>
         <v/>
       </c>
@@ -3245,10 +3730,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="28" t="n">
+      <c r="A24" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="B24" s="28">
+      <c r="B24" s="29">
         <f>$B$9+A24</f>
         <v/>
       </c>
@@ -3270,10 +3755,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="28" t="n">
+      <c r="A25" s="29" t="n">
         <v>0.05</v>
       </c>
-      <c r="B25" s="28">
+      <c r="B25" s="29">
         <f>$B$9+A25</f>
         <v/>
       </c>
@@ -3295,10 +3780,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="28" t="n">
+      <c r="A26" s="29" t="n">
         <v>0.1</v>
       </c>
-      <c r="B26" s="28">
+      <c r="B26" s="29">
         <f>$B$9+A26</f>
         <v/>
       </c>
@@ -3320,10 +3805,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="28" t="n">
+      <c r="A27" s="29" t="n">
         <v>0.15</v>
       </c>
-      <c r="B27" s="28">
+      <c r="B27" s="29">
         <f>$B$9+A27</f>
         <v/>
       </c>
@@ -3345,10 +3830,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="28" t="n">
+      <c r="A28" s="29" t="n">
         <v>0.2</v>
       </c>
-      <c r="B28" s="28">
+      <c r="B28" s="29">
         <f>$B$9+A28</f>
         <v/>
       </c>
@@ -3370,10 +3855,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="28" t="n">
+      <c r="A29" s="29" t="n">
         <v>0.25</v>
       </c>
-      <c r="B29" s="28">
+      <c r="B29" s="29">
         <f>$B$9+A29</f>
         <v/>
       </c>
@@ -3395,10 +3880,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="28" t="n">
+      <c r="A30" s="29" t="n">
         <v>0.3</v>
       </c>
-      <c r="B30" s="28">
+      <c r="B30" s="29">
         <f>$B$9+A30</f>
         <v/>
       </c>
@@ -3420,10 +3905,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="28" t="n">
+      <c r="A31" s="29" t="n">
         <v>0.35</v>
       </c>
-      <c r="B31" s="28">
+      <c r="B31" s="29">
         <f>$B$9+A31</f>
         <v/>
       </c>
@@ -3445,10 +3930,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="28" t="n">
+      <c r="A32" s="29" t="n">
         <v>0.4</v>
       </c>
-      <c r="B32" s="28">
+      <c r="B32" s="29">
         <f>$B$9+A32</f>
         <v/>
       </c>
@@ -3470,10 +3955,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="28" t="n">
+      <c r="A33" s="29" t="n">
         <v>0.45</v>
       </c>
-      <c r="B33" s="28">
+      <c r="B33" s="29">
         <f>$B$9+A33</f>
         <v/>
       </c>
@@ -3495,10 +3980,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="28" t="n">
+      <c r="A34" s="29" t="n">
         <v>0.5</v>
       </c>
-      <c r="B34" s="28">
+      <c r="B34" s="29">
         <f>$B$9+A34</f>
         <v/>
       </c>
@@ -3520,10 +4005,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="28" t="n">
+      <c r="A35" s="29" t="n">
         <v>0.55</v>
       </c>
-      <c r="B35" s="28">
+      <c r="B35" s="29">
         <f>$B$9+A35</f>
         <v/>
       </c>
@@ -3545,10 +4030,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="28" t="n">
+      <c r="A36" s="29" t="n">
         <v>0.6</v>
       </c>
-      <c r="B36" s="28">
+      <c r="B36" s="29">
         <f>$B$9+A36</f>
         <v/>
       </c>
@@ -3570,10 +4055,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="28" t="n">
+      <c r="A37" s="29" t="n">
         <v>0.65</v>
       </c>
-      <c r="B37" s="28">
+      <c r="B37" s="29">
         <f>$B$9+A37</f>
         <v/>
       </c>
@@ -3595,10 +4080,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="28" t="n">
+      <c r="A38" s="29" t="n">
         <v>0.7</v>
       </c>
-      <c r="B38" s="28">
+      <c r="B38" s="29">
         <f>$B$9+A38</f>
         <v/>
       </c>
@@ -3620,10 +4105,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="28" t="n">
+      <c r="A39" s="29" t="n">
         <v>0.75</v>
       </c>
-      <c r="B39" s="28">
+      <c r="B39" s="29">
         <f>$B$9+A39</f>
         <v/>
       </c>
@@ -3645,10 +4130,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="28" t="n">
+      <c r="A40" s="29" t="n">
         <v>0.8</v>
       </c>
-      <c r="B40" s="28">
+      <c r="B40" s="29">
         <f>$B$9+A40</f>
         <v/>
       </c>
@@ -3670,10 +4155,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="28" t="n">
+      <c r="A41" s="29" t="n">
         <v>0.85</v>
       </c>
-      <c r="B41" s="28">
+      <c r="B41" s="29">
         <f>$B$9+A41</f>
         <v/>
       </c>
@@ -3695,10 +4180,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="28" t="n">
+      <c r="A42" s="29" t="n">
         <v>0.9</v>
       </c>
-      <c r="B42" s="28">
+      <c r="B42" s="29">
         <f>$B$9+A42</f>
         <v/>
       </c>
@@ -3720,10 +4205,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="28" t="n">
+      <c r="A43" s="29" t="n">
         <v>0.95</v>
       </c>
-      <c r="B43" s="28">
+      <c r="B43" s="29">
         <f>$B$9+A43</f>
         <v/>
       </c>
@@ -3745,10 +4230,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="28" t="n">
+      <c r="A44" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B44" s="28">
+      <c r="B44" s="29">
         <f>$B$9+A44</f>
         <v/>
       </c>
@@ -3770,10 +4255,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="28" t="n">
+      <c r="A45" s="29" t="n">
         <v>1.05</v>
       </c>
-      <c r="B45" s="28">
+      <c r="B45" s="29">
         <f>$B$9+A45</f>
         <v/>
       </c>
@@ -3795,10 +4280,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="28" t="n">
+      <c r="A46" s="29" t="n">
         <v>1.1</v>
       </c>
-      <c r="B46" s="28">
+      <c r="B46" s="29">
         <f>$B$9+A46</f>
         <v/>
       </c>
@@ -3820,10 +4305,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="28" t="n">
+      <c r="A47" s="29" t="n">
         <v>1.15</v>
       </c>
-      <c r="B47" s="28">
+      <c r="B47" s="29">
         <f>$B$9+A47</f>
         <v/>
       </c>
@@ -3845,10 +4330,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="28" t="n">
+      <c r="A48" s="29" t="n">
         <v>1.2</v>
       </c>
-      <c r="B48" s="28">
+      <c r="B48" s="29">
         <f>$B$9+A48</f>
         <v/>
       </c>
@@ -3870,10 +4355,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="28" t="n">
+      <c r="A49" s="29" t="n">
         <v>1.25</v>
       </c>
-      <c r="B49" s="28">
+      <c r="B49" s="29">
         <f>$B$9+A49</f>
         <v/>
       </c>
@@ -3895,10 +4380,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="28" t="n">
+      <c r="A50" s="29" t="n">
         <v>1.3</v>
       </c>
-      <c r="B50" s="28">
+      <c r="B50" s="29">
         <f>$B$9+A50</f>
         <v/>
       </c>
@@ -3920,10 +4405,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="28" t="n">
+      <c r="A51" s="29" t="n">
         <v>1.35</v>
       </c>
-      <c r="B51" s="28">
+      <c r="B51" s="29">
         <f>$B$9+A51</f>
         <v/>
       </c>
@@ -3945,10 +4430,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="28" t="n">
+      <c r="A52" s="29" t="n">
         <v>1.4</v>
       </c>
-      <c r="B52" s="28">
+      <c r="B52" s="29">
         <f>$B$9+A52</f>
         <v/>
       </c>
@@ -3970,10 +4455,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="28" t="n">
+      <c r="A53" s="29" t="n">
         <v>1.45</v>
       </c>
-      <c r="B53" s="28">
+      <c r="B53" s="29">
         <f>$B$9+A53</f>
         <v/>
       </c>
@@ -3995,10 +4480,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="28" t="n">
+      <c r="A54" s="29" t="n">
         <v>1.5</v>
       </c>
-      <c r="B54" s="28">
+      <c r="B54" s="29">
         <f>$B$9+A54</f>
         <v/>
       </c>
@@ -4020,10 +4505,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="28" t="n">
+      <c r="A55" s="29" t="n">
         <v>1.55</v>
       </c>
-      <c r="B55" s="28">
+      <c r="B55" s="29">
         <f>$B$9+A55</f>
         <v/>
       </c>
@@ -4045,10 +4530,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="28" t="n">
+      <c r="A56" s="29" t="n">
         <v>1.6</v>
       </c>
-      <c r="B56" s="28">
+      <c r="B56" s="29">
         <f>$B$9+A56</f>
         <v/>
       </c>
@@ -4070,10 +4555,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="28" t="n">
+      <c r="A57" s="29" t="n">
         <v>1.65</v>
       </c>
-      <c r="B57" s="28">
+      <c r="B57" s="29">
         <f>$B$9+A57</f>
         <v/>
       </c>
@@ -4095,10 +4580,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="28" t="n">
+      <c r="A58" s="29" t="n">
         <v>1.7</v>
       </c>
-      <c r="B58" s="28">
+      <c r="B58" s="29">
         <f>$B$9+A58</f>
         <v/>
       </c>
@@ -4120,10 +4605,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="28" t="n">
+      <c r="A59" s="29" t="n">
         <v>1.75</v>
       </c>
-      <c r="B59" s="28">
+      <c r="B59" s="29">
         <f>$B$9+A59</f>
         <v/>
       </c>
@@ -4145,10 +4630,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="28" t="n">
+      <c r="A60" s="29" t="n">
         <v>1.8</v>
       </c>
-      <c r="B60" s="28">
+      <c r="B60" s="29">
         <f>$B$9+A60</f>
         <v/>
       </c>
@@ -4170,10 +4655,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="28" t="n">
+      <c r="A61" s="29" t="n">
         <v>1.85</v>
       </c>
-      <c r="B61" s="28">
+      <c r="B61" s="29">
         <f>$B$9+A61</f>
         <v/>
       </c>
@@ -4195,10 +4680,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="28" t="n">
+      <c r="A62" s="29" t="n">
         <v>1.9</v>
       </c>
-      <c r="B62" s="28">
+      <c r="B62" s="29">
         <f>$B$9+A62</f>
         <v/>
       </c>
@@ -4220,10 +4705,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="28" t="n">
+      <c r="A63" s="29" t="n">
         <v>1.95</v>
       </c>
-      <c r="B63" s="28">
+      <c r="B63" s="29">
         <f>$B$9+A63</f>
         <v/>
       </c>
@@ -4245,10 +4730,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="28" t="n">
+      <c r="A64" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B64" s="28">
+      <c r="B64" s="29">
         <f>$B$9+A64</f>
         <v/>
       </c>
@@ -4270,10 +4755,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="28" t="n">
+      <c r="A65" s="29" t="n">
         <v>2.05</v>
       </c>
-      <c r="B65" s="28">
+      <c r="B65" s="29">
         <f>$B$9+A65</f>
         <v/>
       </c>
@@ -4295,10 +4780,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="28" t="n">
+      <c r="A66" s="29" t="n">
         <v>2.1</v>
       </c>
-      <c r="B66" s="28">
+      <c r="B66" s="29">
         <f>$B$9+A66</f>
         <v/>
       </c>
@@ -4320,10 +4805,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="28" t="n">
+      <c r="A67" s="29" t="n">
         <v>2.15</v>
       </c>
-      <c r="B67" s="28">
+      <c r="B67" s="29">
         <f>$B$9+A67</f>
         <v/>
       </c>
@@ -4345,10 +4830,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="28" t="n">
+      <c r="A68" s="29" t="n">
         <v>2.2</v>
       </c>
-      <c r="B68" s="28">
+      <c r="B68" s="29">
         <f>$B$9+A68</f>
         <v/>
       </c>
@@ -4370,10 +4855,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="28" t="n">
+      <c r="A69" s="29" t="n">
         <v>2.25</v>
       </c>
-      <c r="B69" s="28">
+      <c r="B69" s="29">
         <f>$B$9+A69</f>
         <v/>
       </c>
@@ -4395,10 +4880,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="28" t="n">
+      <c r="A70" s="29" t="n">
         <v>2.3</v>
       </c>
-      <c r="B70" s="28">
+      <c r="B70" s="29">
         <f>$B$9+A70</f>
         <v/>
       </c>
@@ -4420,10 +4905,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="28" t="n">
+      <c r="A71" s="29" t="n">
         <v>2.35</v>
       </c>
-      <c r="B71" s="28">
+      <c r="B71" s="29">
         <f>$B$9+A71</f>
         <v/>
       </c>
@@ -4445,10 +4930,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="35" t="n">
+      <c r="A72" s="36" t="n">
         <v>2.4</v>
       </c>
-      <c r="B72" s="35">
+      <c r="B72" s="36">
         <f>$B$9+A72</f>
         <v/>
       </c>
@@ -4470,10 +4955,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="28" t="n">
+      <c r="A73" s="29" t="n">
         <v>2.45</v>
       </c>
-      <c r="B73" s="28">
+      <c r="B73" s="29">
         <f>$B$9+A73</f>
         <v/>
       </c>
@@ -4495,10 +4980,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="28" t="n">
+      <c r="A74" s="29" t="n">
         <v>2.5</v>
       </c>
-      <c r="B74" s="28">
+      <c r="B74" s="29">
         <f>$B$9+A74</f>
         <v/>
       </c>
@@ -4520,10 +5005,10 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="28" t="n">
+      <c r="A75" s="29" t="n">
         <v>2.55</v>
       </c>
-      <c r="B75" s="28">
+      <c r="B75" s="29">
         <f>$B$9+A75</f>
         <v/>
       </c>
@@ -4545,10 +5030,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="28" t="n">
+      <c r="A76" s="29" t="n">
         <v>2.6</v>
       </c>
-      <c r="B76" s="28">
+      <c r="B76" s="29">
         <f>$B$9+A76</f>
         <v/>
       </c>
@@ -4570,10 +5055,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="28" t="n">
+      <c r="A77" s="29" t="n">
         <v>2.65</v>
       </c>
-      <c r="B77" s="28">
+      <c r="B77" s="29">
         <f>$B$9+A77</f>
         <v/>
       </c>
@@ -4595,10 +5080,10 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="28" t="n">
+      <c r="A78" s="29" t="n">
         <v>2.7</v>
       </c>
-      <c r="B78" s="28">
+      <c r="B78" s="29">
         <f>$B$9+A78</f>
         <v/>
       </c>
@@ -4620,10 +5105,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="28" t="n">
+      <c r="A79" s="29" t="n">
         <v>2.75</v>
       </c>
-      <c r="B79" s="28">
+      <c r="B79" s="29">
         <f>$B$9+A79</f>
         <v/>
       </c>
@@ -4645,10 +5130,10 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="28" t="n">
+      <c r="A80" s="29" t="n">
         <v>2.8</v>
       </c>
-      <c r="B80" s="28">
+      <c r="B80" s="29">
         <f>$B$9+A80</f>
         <v/>
       </c>
@@ -4670,10 +5155,10 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="28" t="n">
+      <c r="A81" s="29" t="n">
         <v>2.85</v>
       </c>
-      <c r="B81" s="28">
+      <c r="B81" s="29">
         <f>$B$9+A81</f>
         <v/>
       </c>
@@ -4695,10 +5180,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="28" t="n">
+      <c r="A82" s="29" t="n">
         <v>2.9</v>
       </c>
-      <c r="B82" s="28">
+      <c r="B82" s="29">
         <f>$B$9+A82</f>
         <v/>
       </c>
@@ -4720,10 +5205,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="28" t="n">
+      <c r="A83" s="29" t="n">
         <v>2.95</v>
       </c>
-      <c r="B83" s="28">
+      <c r="B83" s="29">
         <f>$B$9+A83</f>
         <v/>
       </c>
@@ -4745,10 +5230,10 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="28" t="n">
+      <c r="A84" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B84" s="28">
+      <c r="B84" s="29">
         <f>$B$9+A84</f>
         <v/>
       </c>
@@ -4797,14 +5282,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>Méthode B — routage avec Qout = f(H) depuis Courbe_QH_900 (FHWA)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="36" t="inlineStr">
+      <c r="A2" s="37" t="inlineStr">
         <is>
           <t>H = V / Aire_bassin. Qout interpolé sur Courbe_QH_900!E (Q gouvernant). Si V≈0, Qout = MIN(Qin, Q_plein). ΔV = (Qin_moy - Qout)*Δt. La courbe Courbe_QH_900 est en formules live (changer n/L/entrée/TW).</t>
         </is>
@@ -4817,7 +5302,7 @@
           <t>Aire (m²)</t>
         </is>
       </c>
-      <c r="B5" s="37">
+      <c r="B5" s="38">
         <f>Parametres!B24</f>
         <v/>
       </c>
@@ -4828,7 +5313,7 @@
           <t>Q_plein réf. (m³/s)</t>
         </is>
       </c>
-      <c r="B6" s="37">
+      <c r="B6" s="38">
         <f>Parametres!B22</f>
         <v/>
       </c>
@@ -4839,7 +5324,7 @@
           <t>Vmax_B (m³)</t>
         </is>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="28">
         <f>MAX(G12:G24)</f>
         <v/>
       </c>
@@ -4850,7 +5335,7 @@
           <t>Hmax_B (m)</t>
         </is>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="20">
         <f>IF(B5&gt;0,B7/B5,0)</f>
         <v/>
       </c>
@@ -4911,10 +5396,10 @@
         <f>MIN(B12,$B$6)</f>
         <v/>
       </c>
-      <c r="F12" s="23" t="n">
+      <c r="F12" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="30" t="n">
+      <c r="G12" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4939,11 +5424,11 @@
         <f>IF(G12&lt;=0.01,MIN(0.5*(B12+B13),$B$6),D13)</f>
         <v/>
       </c>
-      <c r="F13" s="23">
+      <c r="F13" s="24">
         <f>(A13-A12)*60</f>
         <v/>
       </c>
-      <c r="G13" s="30">
+      <c r="G13" s="31">
         <f>MAX(0,G12+(0.5*(B12+B13)-E13)*F13)</f>
         <v/>
       </c>
@@ -4969,11 +5454,11 @@
         <f>IF(G13&lt;=0.01,MIN(0.5*(B13+B14),$B$6),D14)</f>
         <v/>
       </c>
-      <c r="F14" s="23">
+      <c r="F14" s="24">
         <f>(A14-A13)*60</f>
         <v/>
       </c>
-      <c r="G14" s="30">
+      <c r="G14" s="31">
         <f>MAX(0,G13+(0.5*(B13+B14)-E14)*F14)</f>
         <v/>
       </c>
@@ -4999,11 +5484,11 @@
         <f>IF(G14&lt;=0.01,MIN(0.5*(B14+B15),$B$6),D15)</f>
         <v/>
       </c>
-      <c r="F15" s="23">
+      <c r="F15" s="24">
         <f>(A15-A14)*60</f>
         <v/>
       </c>
-      <c r="G15" s="30">
+      <c r="G15" s="31">
         <f>MAX(0,G14+(0.5*(B14+B15)-E15)*F15)</f>
         <v/>
       </c>
@@ -5029,11 +5514,11 @@
         <f>IF(G15&lt;=0.01,MIN(0.5*(B15+B16),$B$6),D16)</f>
         <v/>
       </c>
-      <c r="F16" s="23">
+      <c r="F16" s="24">
         <f>(A16-A15)*60</f>
         <v/>
       </c>
-      <c r="G16" s="30">
+      <c r="G16" s="31">
         <f>MAX(0,G15+(0.5*(B15+B16)-E16)*F16)</f>
         <v/>
       </c>
@@ -5059,11 +5544,11 @@
         <f>IF(G16&lt;=0.01,MIN(0.5*(B16+B17),$B$6),D17)</f>
         <v/>
       </c>
-      <c r="F17" s="23">
+      <c r="F17" s="24">
         <f>(A17-A16)*60</f>
         <v/>
       </c>
-      <c r="G17" s="30">
+      <c r="G17" s="31">
         <f>MAX(0,G16+(0.5*(B16+B17)-E17)*F17)</f>
         <v/>
       </c>
@@ -5089,11 +5574,11 @@
         <f>IF(G17&lt;=0.01,MIN(0.5*(B17+B18),$B$6),D18)</f>
         <v/>
       </c>
-      <c r="F18" s="23">
+      <c r="F18" s="24">
         <f>(A18-A17)*60</f>
         <v/>
       </c>
-      <c r="G18" s="30">
+      <c r="G18" s="31">
         <f>MAX(0,G17+(0.5*(B17+B18)-E18)*F18)</f>
         <v/>
       </c>
@@ -5119,11 +5604,11 @@
         <f>IF(G18&lt;=0.01,MIN(0.5*(B18+B19),$B$6),D19)</f>
         <v/>
       </c>
-      <c r="F19" s="23">
+      <c r="F19" s="24">
         <f>(A19-A18)*60</f>
         <v/>
       </c>
-      <c r="G19" s="30">
+      <c r="G19" s="31">
         <f>MAX(0,G18+(0.5*(B18+B19)-E19)*F19)</f>
         <v/>
       </c>
@@ -5149,11 +5634,11 @@
         <f>IF(G19&lt;=0.01,MIN(0.5*(B19+B20),$B$6),D20)</f>
         <v/>
       </c>
-      <c r="F20" s="23">
+      <c r="F20" s="24">
         <f>(A20-A19)*60</f>
         <v/>
       </c>
-      <c r="G20" s="30">
+      <c r="G20" s="31">
         <f>MAX(0,G19+(0.5*(B19+B20)-E20)*F20)</f>
         <v/>
       </c>
@@ -5179,11 +5664,11 @@
         <f>IF(G20&lt;=0.01,MIN(0.5*(B20+B21),$B$6),D21)</f>
         <v/>
       </c>
-      <c r="F21" s="23">
+      <c r="F21" s="24">
         <f>(A21-A20)*60</f>
         <v/>
       </c>
-      <c r="G21" s="30">
+      <c r="G21" s="31">
         <f>MAX(0,G20+(0.5*(B20+B21)-E21)*F21)</f>
         <v/>
       </c>
@@ -5209,11 +5694,11 @@
         <f>IF(G21&lt;=0.01,MIN(0.5*(B21+B22),$B$6),D22)</f>
         <v/>
       </c>
-      <c r="F22" s="23">
+      <c r="F22" s="24">
         <f>(A22-A21)*60</f>
         <v/>
       </c>
-      <c r="G22" s="30">
+      <c r="G22" s="31">
         <f>MAX(0,G21+(0.5*(B21+B22)-E22)*F22)</f>
         <v/>
       </c>
@@ -5239,11 +5724,11 @@
         <f>IF(G22&lt;=0.01,MIN(0.5*(B22+B23),$B$6),D23)</f>
         <v/>
       </c>
-      <c r="F23" s="23">
+      <c r="F23" s="24">
         <f>(A23-A22)*60</f>
         <v/>
       </c>
-      <c r="G23" s="30">
+      <c r="G23" s="31">
         <f>MAX(0,G22+(0.5*(B22+B23)-E23)*F23)</f>
         <v/>
       </c>
@@ -5269,11 +5754,11 @@
         <f>IF(G23&lt;=0.01,MIN(0.5*(B23+B24),$B$6),D24)</f>
         <v/>
       </c>
-      <c r="F24" s="23">
+      <c r="F24" s="24">
         <f>(A24-A23)*60</f>
         <v/>
       </c>
-      <c r="G24" s="30">
+      <c r="G24" s="31">
         <f>MAX(0,G23+(0.5*(B23+B24)-E24)*F24)</f>
         <v/>
       </c>
@@ -5292,365 +5777,4366 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:L107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="inlineStr">
-        <is>
-          <t>Stage–storage du levé — V = f(WSE) → lire le niveau max</t>
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>Méthode C — courbe composée Ø900 + fossé trapèze (crest = crown)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>PROCÉDURE (dans CE fichier): 1) Routage → Vmax_A / Vmax_B sur Parametres (Calcul_A et Calcul_B). 2) Cette feuille calcule V cumulé vs NSE/WSE à partir des surfaces du levé (jaune). 3) Parametres!B30 = WSEmax_A (depuis Vmax_A); B36 = WSEmax_B (depuis Vmax_B). Remplacez les surfaces jaunes par vos polygones; 543 m² @ 37.28 et 1932 m² @ 39.5 sont vos mesures.</t>
+          <t>Qout = Q_900(WSE) + Q_overflow(WSE). V_total = V_pond(Stage_Storage) + V_ditch. Overflow: trapèze au-dessus du crown, Manning. Paramètres jaunes = Parametres!B27–B32.</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Paramètres (liés à Parametres)</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Formule d'un pas</t>
-        </is>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Crest (m)</t>
+        </is>
+      </c>
+      <c r="B6" s="16">
+        <f>Parametres!B27</f>
+        <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="38" t="inlineStr">
-        <is>
-          <t>V_pas (m³) = (A_basse + A_haute) / 2 × (WSE_haute − WSE_basse)</t>
-        </is>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>b (m)</t>
+        </is>
+      </c>
+      <c r="B7" s="16">
+        <f>Parametres!B28</f>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V_cumulatif = somme des V_pas depuis le radier</t>
-        </is>
+          <t>n fossé</t>
+        </is>
+      </c>
+      <c r="B8" s="11">
+        <f>Parametres!B29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>z (-)</t>
+        </is>
+      </c>
+      <c r="B9" s="18">
+        <f>Parametres!B30</f>
+        <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>WSE / NSE (m)</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Surface A (m²) ← ÉDITER</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>ΔWSE (m)</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>V_pas (m³)</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>V_cumulatif (m³)</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Rôle</t>
-        </is>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>S fossé</t>
+        </is>
+      </c>
+      <c r="B10" s="11">
+        <f>Parametres!B31</f>
+        <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="n">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>L fossé (m)</t>
+        </is>
+      </c>
+      <c r="B11" s="18">
+        <f>Parametres!B32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Zin Ø900 (m)</t>
+        </is>
+      </c>
+      <c r="B12" s="16">
+        <f>34.88</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>WSE (m)</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>HW (m)</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>y_ov (m)</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>A_ditch (m²)</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>V_ditch (m³)</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>V_pond (m³)</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>V_total (m³)</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Q_900</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Q_overflow</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Qout</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Overflow?</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="29" t="n">
         <v>34.88</v>
       </c>
-      <c r="B11" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Radier Ø900 — départ</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="28" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="B12" s="17" t="n">
-        <v>80</v>
-      </c>
-      <c r="C12" s="28">
-        <f>A12-A11</f>
-        <v/>
-      </c>
-      <c r="D12" s="23">
-        <f>0.5*(B11+B12)*C12</f>
-        <v/>
-      </c>
-      <c r="E12" s="30">
-        <f>E11+D12</f>
-        <v/>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Placeholder — remplacer par levé</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="28" t="n">
-        <v>36</v>
-      </c>
-      <c r="B13" s="17" t="n">
-        <v>180</v>
-      </c>
-      <c r="C13" s="28">
-        <f>A13-A12</f>
-        <v/>
-      </c>
-      <c r="D13" s="23">
-        <f>0.5*(B12+B13)*C13</f>
-        <v/>
-      </c>
-      <c r="E13" s="30">
-        <f>E12+D13</f>
-        <v/>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Placeholder — remplacer par levé</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="28" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="B14" s="17" t="n">
-        <v>320</v>
-      </c>
-      <c r="C14" s="28">
-        <f>A14-A13</f>
-        <v/>
-      </c>
-      <c r="D14" s="23">
-        <f>0.5*(B13+B14)*C14</f>
-        <v/>
-      </c>
-      <c r="E14" s="30">
-        <f>E13+D14</f>
-        <v/>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Placeholder — remplacer par levé</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="28" t="n">
-        <v>37</v>
-      </c>
-      <c r="B15" s="17" t="n">
-        <v>480</v>
-      </c>
-      <c r="C15" s="28">
-        <f>A15-A14</f>
-        <v/>
-      </c>
-      <c r="D15" s="23">
-        <f>0.5*(B14+B15)*C15</f>
-        <v/>
-      </c>
-      <c r="E15" s="30">
-        <f>E14+D15</f>
-        <v/>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Placeholder — remplacer par levé</t>
-        </is>
+      <c r="B15" s="29">
+        <f>A15-$B$12</f>
+        <v/>
+      </c>
+      <c r="C15" s="29">
+        <f>MAX(0,A15-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D15" s="5">
+        <f>IF(C15&lt;=0,0,($B$7+$B$9*C15)*C15)</f>
+        <v/>
+      </c>
+      <c r="E15" s="24">
+        <f>D15*$B$11</f>
+        <v/>
+      </c>
+      <c r="F15" s="24">
+        <f>IF(A15&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A15&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A15,Stage_Storage!$A$11:$A$18,1))+(A15-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A15,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A15,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A15,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A15,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A15,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G15" s="31">
+        <f>E15+F15</f>
+        <v/>
+      </c>
+      <c r="H15" s="5">
+        <f>IF(B15&lt;=0,0,IF(B15&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B15,Courbe_QH_900!$A$24:$A$84,1))+(B15-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B15,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B15,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B15,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B15,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B15,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I15" s="5">
+        <f>IF(C15&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D15*IF(($B$7+2*C15*SQRT(1+$B$9^2))&lt;=0,0,((D15/($B$7+2*C15*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J15" s="15">
+        <f>H15+I15</f>
+        <v/>
+      </c>
+      <c r="K15" s="4">
+        <f>IF(C15&gt;0,"oui","non")</f>
+        <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="35" t="n">
+      <c r="A16" s="29" t="n">
+        <v>34.93</v>
+      </c>
+      <c r="B16" s="29">
+        <f>A16-$B$12</f>
+        <v/>
+      </c>
+      <c r="C16" s="29">
+        <f>MAX(0,A16-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D16" s="5">
+        <f>IF(C16&lt;=0,0,($B$7+$B$9*C16)*C16)</f>
+        <v/>
+      </c>
+      <c r="E16" s="24">
+        <f>D16*$B$11</f>
+        <v/>
+      </c>
+      <c r="F16" s="24">
+        <f>IF(A16&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A16&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A16,Stage_Storage!$A$11:$A$18,1))+(A16-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A16,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A16,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A16,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A16,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A16,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G16" s="31">
+        <f>E16+F16</f>
+        <v/>
+      </c>
+      <c r="H16" s="5">
+        <f>IF(B16&lt;=0,0,IF(B16&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B16,Courbe_QH_900!$A$24:$A$84,1))+(B16-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B16,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B16,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B16,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B16,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B16,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I16" s="5">
+        <f>IF(C16&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D16*IF(($B$7+2*C16*SQRT(1+$B$9^2))&lt;=0,0,((D16/($B$7+2*C16*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J16" s="15">
+        <f>H16+I16</f>
+        <v/>
+      </c>
+      <c r="K16" s="4">
+        <f>IF(C16&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="29" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="B17" s="29">
+        <f>A17-$B$12</f>
+        <v/>
+      </c>
+      <c r="C17" s="29">
+        <f>MAX(0,A17-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D17" s="5">
+        <f>IF(C17&lt;=0,0,($B$7+$B$9*C17)*C17)</f>
+        <v/>
+      </c>
+      <c r="E17" s="24">
+        <f>D17*$B$11</f>
+        <v/>
+      </c>
+      <c r="F17" s="24">
+        <f>IF(A17&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A17&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A17,Stage_Storage!$A$11:$A$18,1))+(A17-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A17,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A17,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A17,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A17,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A17,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G17" s="31">
+        <f>E17+F17</f>
+        <v/>
+      </c>
+      <c r="H17" s="5">
+        <f>IF(B17&lt;=0,0,IF(B17&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B17,Courbe_QH_900!$A$24:$A$84,1))+(B17-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B17,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B17,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B17,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B17,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B17,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I17" s="5">
+        <f>IF(C17&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D17*IF(($B$7+2*C17*SQRT(1+$B$9^2))&lt;=0,0,((D17/($B$7+2*C17*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J17" s="15">
+        <f>H17+I17</f>
+        <v/>
+      </c>
+      <c r="K17" s="4">
+        <f>IF(C17&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="n">
+        <v>35.03</v>
+      </c>
+      <c r="B18" s="29">
+        <f>A18-$B$12</f>
+        <v/>
+      </c>
+      <c r="C18" s="29">
+        <f>MAX(0,A18-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D18" s="5">
+        <f>IF(C18&lt;=0,0,($B$7+$B$9*C18)*C18)</f>
+        <v/>
+      </c>
+      <c r="E18" s="24">
+        <f>D18*$B$11</f>
+        <v/>
+      </c>
+      <c r="F18" s="24">
+        <f>IF(A18&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A18&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A18,Stage_Storage!$A$11:$A$18,1))+(A18-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A18,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A18,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A18,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A18,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A18,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G18" s="31">
+        <f>E18+F18</f>
+        <v/>
+      </c>
+      <c r="H18" s="5">
+        <f>IF(B18&lt;=0,0,IF(B18&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B18,Courbe_QH_900!$A$24:$A$84,1))+(B18-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B18,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B18,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B18,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B18,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B18,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I18" s="5">
+        <f>IF(C18&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D18*IF(($B$7+2*C18*SQRT(1+$B$9^2))&lt;=0,0,((D18/($B$7+2*C18*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J18" s="15">
+        <f>H18+I18</f>
+        <v/>
+      </c>
+      <c r="K18" s="4">
+        <f>IF(C18&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="29" t="n">
+        <v>35.08</v>
+      </c>
+      <c r="B19" s="29">
+        <f>A19-$B$12</f>
+        <v/>
+      </c>
+      <c r="C19" s="29">
+        <f>MAX(0,A19-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D19" s="5">
+        <f>IF(C19&lt;=0,0,($B$7+$B$9*C19)*C19)</f>
+        <v/>
+      </c>
+      <c r="E19" s="24">
+        <f>D19*$B$11</f>
+        <v/>
+      </c>
+      <c r="F19" s="24">
+        <f>IF(A19&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A19&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A19,Stage_Storage!$A$11:$A$18,1))+(A19-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A19,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A19,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A19,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A19,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A19,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G19" s="31">
+        <f>E19+F19</f>
+        <v/>
+      </c>
+      <c r="H19" s="5">
+        <f>IF(B19&lt;=0,0,IF(B19&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B19,Courbe_QH_900!$A$24:$A$84,1))+(B19-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B19,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B19,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B19,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B19,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B19,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I19" s="5">
+        <f>IF(C19&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D19*IF(($B$7+2*C19*SQRT(1+$B$9^2))&lt;=0,0,((D19/($B$7+2*C19*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J19" s="15">
+        <f>H19+I19</f>
+        <v/>
+      </c>
+      <c r="K19" s="4">
+        <f>IF(C19&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="29" t="n">
+        <v>35.13</v>
+      </c>
+      <c r="B20" s="29">
+        <f>A20-$B$12</f>
+        <v/>
+      </c>
+      <c r="C20" s="29">
+        <f>MAX(0,A20-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D20" s="5">
+        <f>IF(C20&lt;=0,0,($B$7+$B$9*C20)*C20)</f>
+        <v/>
+      </c>
+      <c r="E20" s="24">
+        <f>D20*$B$11</f>
+        <v/>
+      </c>
+      <c r="F20" s="24">
+        <f>IF(A20&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A20&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A20,Stage_Storage!$A$11:$A$18,1))+(A20-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A20,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A20,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A20,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A20,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A20,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G20" s="31">
+        <f>E20+F20</f>
+        <v/>
+      </c>
+      <c r="H20" s="5">
+        <f>IF(B20&lt;=0,0,IF(B20&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B20,Courbe_QH_900!$A$24:$A$84,1))+(B20-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B20,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B20,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B20,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B20,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B20,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I20" s="5">
+        <f>IF(C20&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D20*IF(($B$7+2*C20*SQRT(1+$B$9^2))&lt;=0,0,((D20/($B$7+2*C20*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J20" s="15">
+        <f>H20+I20</f>
+        <v/>
+      </c>
+      <c r="K20" s="4">
+        <f>IF(C20&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="29" t="n">
+        <v>35.18</v>
+      </c>
+      <c r="B21" s="29">
+        <f>A21-$B$12</f>
+        <v/>
+      </c>
+      <c r="C21" s="29">
+        <f>MAX(0,A21-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D21" s="5">
+        <f>IF(C21&lt;=0,0,($B$7+$B$9*C21)*C21)</f>
+        <v/>
+      </c>
+      <c r="E21" s="24">
+        <f>D21*$B$11</f>
+        <v/>
+      </c>
+      <c r="F21" s="24">
+        <f>IF(A21&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A21&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A21,Stage_Storage!$A$11:$A$18,1))+(A21-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A21,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A21,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A21,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A21,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A21,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G21" s="31">
+        <f>E21+F21</f>
+        <v/>
+      </c>
+      <c r="H21" s="5">
+        <f>IF(B21&lt;=0,0,IF(B21&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B21,Courbe_QH_900!$A$24:$A$84,1))+(B21-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B21,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B21,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B21,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B21,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B21,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I21" s="5">
+        <f>IF(C21&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D21*IF(($B$7+2*C21*SQRT(1+$B$9^2))&lt;=0,0,((D21/($B$7+2*C21*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J21" s="15">
+        <f>H21+I21</f>
+        <v/>
+      </c>
+      <c r="K21" s="4">
+        <f>IF(C21&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="29" t="n">
+        <v>35.23</v>
+      </c>
+      <c r="B22" s="29">
+        <f>A22-$B$12</f>
+        <v/>
+      </c>
+      <c r="C22" s="29">
+        <f>MAX(0,A22-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D22" s="5">
+        <f>IF(C22&lt;=0,0,($B$7+$B$9*C22)*C22)</f>
+        <v/>
+      </c>
+      <c r="E22" s="24">
+        <f>D22*$B$11</f>
+        <v/>
+      </c>
+      <c r="F22" s="24">
+        <f>IF(A22&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A22&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A22,Stage_Storage!$A$11:$A$18,1))+(A22-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A22,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A22,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A22,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A22,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A22,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G22" s="31">
+        <f>E22+F22</f>
+        <v/>
+      </c>
+      <c r="H22" s="5">
+        <f>IF(B22&lt;=0,0,IF(B22&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B22,Courbe_QH_900!$A$24:$A$84,1))+(B22-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B22,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B22,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B22,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B22,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B22,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I22" s="5">
+        <f>IF(C22&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D22*IF(($B$7+2*C22*SQRT(1+$B$9^2))&lt;=0,0,((D22/($B$7+2*C22*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J22" s="15">
+        <f>H22+I22</f>
+        <v/>
+      </c>
+      <c r="K22" s="4">
+        <f>IF(C22&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="29" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="B23" s="29">
+        <f>A23-$B$12</f>
+        <v/>
+      </c>
+      <c r="C23" s="29">
+        <f>MAX(0,A23-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D23" s="5">
+        <f>IF(C23&lt;=0,0,($B$7+$B$9*C23)*C23)</f>
+        <v/>
+      </c>
+      <c r="E23" s="24">
+        <f>D23*$B$11</f>
+        <v/>
+      </c>
+      <c r="F23" s="24">
+        <f>IF(A23&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A23&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A23,Stage_Storage!$A$11:$A$18,1))+(A23-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A23,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A23,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A23,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A23,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A23,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G23" s="31">
+        <f>E23+F23</f>
+        <v/>
+      </c>
+      <c r="H23" s="5">
+        <f>IF(B23&lt;=0,0,IF(B23&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B23,Courbe_QH_900!$A$24:$A$84,1))+(B23-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B23,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B23,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B23,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B23,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B23,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I23" s="5">
+        <f>IF(C23&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D23*IF(($B$7+2*C23*SQRT(1+$B$9^2))&lt;=0,0,((D23/($B$7+2*C23*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J23" s="15">
+        <f>H23+I23</f>
+        <v/>
+      </c>
+      <c r="K23" s="4">
+        <f>IF(C23&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="29" t="n">
+        <v>35.33</v>
+      </c>
+      <c r="B24" s="29">
+        <f>A24-$B$12</f>
+        <v/>
+      </c>
+      <c r="C24" s="29">
+        <f>MAX(0,A24-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D24" s="5">
+        <f>IF(C24&lt;=0,0,($B$7+$B$9*C24)*C24)</f>
+        <v/>
+      </c>
+      <c r="E24" s="24">
+        <f>D24*$B$11</f>
+        <v/>
+      </c>
+      <c r="F24" s="24">
+        <f>IF(A24&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A24&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A24,Stage_Storage!$A$11:$A$18,1))+(A24-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A24,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A24,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A24,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A24,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A24,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G24" s="31">
+        <f>E24+F24</f>
+        <v/>
+      </c>
+      <c r="H24" s="5">
+        <f>IF(B24&lt;=0,0,IF(B24&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B24,Courbe_QH_900!$A$24:$A$84,1))+(B24-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B24,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B24,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B24,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B24,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B24,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I24" s="5">
+        <f>IF(C24&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D24*IF(($B$7+2*C24*SQRT(1+$B$9^2))&lt;=0,0,((D24/($B$7+2*C24*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J24" s="15">
+        <f>H24+I24</f>
+        <v/>
+      </c>
+      <c r="K24" s="4">
+        <f>IF(C24&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="29" t="n">
+        <v>35.38</v>
+      </c>
+      <c r="B25" s="29">
+        <f>A25-$B$12</f>
+        <v/>
+      </c>
+      <c r="C25" s="29">
+        <f>MAX(0,A25-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D25" s="5">
+        <f>IF(C25&lt;=0,0,($B$7+$B$9*C25)*C25)</f>
+        <v/>
+      </c>
+      <c r="E25" s="24">
+        <f>D25*$B$11</f>
+        <v/>
+      </c>
+      <c r="F25" s="24">
+        <f>IF(A25&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A25&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A25,Stage_Storage!$A$11:$A$18,1))+(A25-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A25,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A25,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A25,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A25,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A25,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G25" s="31">
+        <f>E25+F25</f>
+        <v/>
+      </c>
+      <c r="H25" s="5">
+        <f>IF(B25&lt;=0,0,IF(B25&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B25,Courbe_QH_900!$A$24:$A$84,1))+(B25-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B25,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B25,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B25,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B25,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B25,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I25" s="5">
+        <f>IF(C25&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D25*IF(($B$7+2*C25*SQRT(1+$B$9^2))&lt;=0,0,((D25/($B$7+2*C25*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J25" s="15">
+        <f>H25+I25</f>
+        <v/>
+      </c>
+      <c r="K25" s="4">
+        <f>IF(C25&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="29" t="n">
+        <v>35.43</v>
+      </c>
+      <c r="B26" s="29">
+        <f>A26-$B$12</f>
+        <v/>
+      </c>
+      <c r="C26" s="29">
+        <f>MAX(0,A26-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D26" s="5">
+        <f>IF(C26&lt;=0,0,($B$7+$B$9*C26)*C26)</f>
+        <v/>
+      </c>
+      <c r="E26" s="24">
+        <f>D26*$B$11</f>
+        <v/>
+      </c>
+      <c r="F26" s="24">
+        <f>IF(A26&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A26&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A26,Stage_Storage!$A$11:$A$18,1))+(A26-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A26,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A26,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A26,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A26,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A26,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G26" s="31">
+        <f>E26+F26</f>
+        <v/>
+      </c>
+      <c r="H26" s="5">
+        <f>IF(B26&lt;=0,0,IF(B26&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B26,Courbe_QH_900!$A$24:$A$84,1))+(B26-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B26,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B26,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B26,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B26,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B26,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I26" s="5">
+        <f>IF(C26&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D26*IF(($B$7+2*C26*SQRT(1+$B$9^2))&lt;=0,0,((D26/($B$7+2*C26*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J26" s="15">
+        <f>H26+I26</f>
+        <v/>
+      </c>
+      <c r="K26" s="4">
+        <f>IF(C26&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="29" t="n">
+        <v>35.48</v>
+      </c>
+      <c r="B27" s="29">
+        <f>A27-$B$12</f>
+        <v/>
+      </c>
+      <c r="C27" s="29">
+        <f>MAX(0,A27-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D27" s="5">
+        <f>IF(C27&lt;=0,0,($B$7+$B$9*C27)*C27)</f>
+        <v/>
+      </c>
+      <c r="E27" s="24">
+        <f>D27*$B$11</f>
+        <v/>
+      </c>
+      <c r="F27" s="24">
+        <f>IF(A27&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A27&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A27,Stage_Storage!$A$11:$A$18,1))+(A27-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A27,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A27,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A27,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A27,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A27,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G27" s="31">
+        <f>E27+F27</f>
+        <v/>
+      </c>
+      <c r="H27" s="5">
+        <f>IF(B27&lt;=0,0,IF(B27&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B27,Courbe_QH_900!$A$24:$A$84,1))+(B27-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B27,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B27,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B27,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B27,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B27,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I27" s="5">
+        <f>IF(C27&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D27*IF(($B$7+2*C27*SQRT(1+$B$9^2))&lt;=0,0,((D27/($B$7+2*C27*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J27" s="15">
+        <f>H27+I27</f>
+        <v/>
+      </c>
+      <c r="K27" s="4">
+        <f>IF(C27&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="29" t="n">
+        <v>35.53</v>
+      </c>
+      <c r="B28" s="29">
+        <f>A28-$B$12</f>
+        <v/>
+      </c>
+      <c r="C28" s="29">
+        <f>MAX(0,A28-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D28" s="5">
+        <f>IF(C28&lt;=0,0,($B$7+$B$9*C28)*C28)</f>
+        <v/>
+      </c>
+      <c r="E28" s="24">
+        <f>D28*$B$11</f>
+        <v/>
+      </c>
+      <c r="F28" s="24">
+        <f>IF(A28&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A28&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A28,Stage_Storage!$A$11:$A$18,1))+(A28-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A28,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A28,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A28,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A28,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A28,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G28" s="31">
+        <f>E28+F28</f>
+        <v/>
+      </c>
+      <c r="H28" s="5">
+        <f>IF(B28&lt;=0,0,IF(B28&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B28,Courbe_QH_900!$A$24:$A$84,1))+(B28-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B28,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B28,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B28,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B28,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B28,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I28" s="5">
+        <f>IF(C28&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D28*IF(($B$7+2*C28*SQRT(1+$B$9^2))&lt;=0,0,((D28/($B$7+2*C28*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J28" s="15">
+        <f>H28+I28</f>
+        <v/>
+      </c>
+      <c r="K28" s="4">
+        <f>IF(C28&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="29" t="n">
+        <v>35.58</v>
+      </c>
+      <c r="B29" s="29">
+        <f>A29-$B$12</f>
+        <v/>
+      </c>
+      <c r="C29" s="29">
+        <f>MAX(0,A29-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D29" s="5">
+        <f>IF(C29&lt;=0,0,($B$7+$B$9*C29)*C29)</f>
+        <v/>
+      </c>
+      <c r="E29" s="24">
+        <f>D29*$B$11</f>
+        <v/>
+      </c>
+      <c r="F29" s="24">
+        <f>IF(A29&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A29&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A29,Stage_Storage!$A$11:$A$18,1))+(A29-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A29,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A29,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A29,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A29,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A29,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G29" s="31">
+        <f>E29+F29</f>
+        <v/>
+      </c>
+      <c r="H29" s="5">
+        <f>IF(B29&lt;=0,0,IF(B29&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B29,Courbe_QH_900!$A$24:$A$84,1))+(B29-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B29,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B29,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B29,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B29,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B29,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I29" s="5">
+        <f>IF(C29&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D29*IF(($B$7+2*C29*SQRT(1+$B$9^2))&lt;=0,0,((D29/($B$7+2*C29*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J29" s="15">
+        <f>H29+I29</f>
+        <v/>
+      </c>
+      <c r="K29" s="4">
+        <f>IF(C29&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="29" t="n">
+        <v>35.63</v>
+      </c>
+      <c r="B30" s="29">
+        <f>A30-$B$12</f>
+        <v/>
+      </c>
+      <c r="C30" s="29">
+        <f>MAX(0,A30-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D30" s="5">
+        <f>IF(C30&lt;=0,0,($B$7+$B$9*C30)*C30)</f>
+        <v/>
+      </c>
+      <c r="E30" s="24">
+        <f>D30*$B$11</f>
+        <v/>
+      </c>
+      <c r="F30" s="24">
+        <f>IF(A30&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A30&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A30,Stage_Storage!$A$11:$A$18,1))+(A30-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A30,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A30,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A30,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A30,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A30,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G30" s="31">
+        <f>E30+F30</f>
+        <v/>
+      </c>
+      <c r="H30" s="5">
+        <f>IF(B30&lt;=0,0,IF(B30&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B30,Courbe_QH_900!$A$24:$A$84,1))+(B30-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B30,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B30,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B30,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B30,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B30,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I30" s="5">
+        <f>IF(C30&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D30*IF(($B$7+2*C30*SQRT(1+$B$9^2))&lt;=0,0,((D30/($B$7+2*C30*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J30" s="15">
+        <f>H30+I30</f>
+        <v/>
+      </c>
+      <c r="K30" s="4">
+        <f>IF(C30&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="29" t="n">
+        <v>35.68</v>
+      </c>
+      <c r="B31" s="29">
+        <f>A31-$B$12</f>
+        <v/>
+      </c>
+      <c r="C31" s="29">
+        <f>MAX(0,A31-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D31" s="5">
+        <f>IF(C31&lt;=0,0,($B$7+$B$9*C31)*C31)</f>
+        <v/>
+      </c>
+      <c r="E31" s="24">
+        <f>D31*$B$11</f>
+        <v/>
+      </c>
+      <c r="F31" s="24">
+        <f>IF(A31&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A31&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A31,Stage_Storage!$A$11:$A$18,1))+(A31-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A31,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A31,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A31,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A31,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A31,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G31" s="31">
+        <f>E31+F31</f>
+        <v/>
+      </c>
+      <c r="H31" s="5">
+        <f>IF(B31&lt;=0,0,IF(B31&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B31,Courbe_QH_900!$A$24:$A$84,1))+(B31-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B31,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B31,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B31,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B31,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B31,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I31" s="5">
+        <f>IF(C31&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D31*IF(($B$7+2*C31*SQRT(1+$B$9^2))&lt;=0,0,((D31/($B$7+2*C31*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J31" s="15">
+        <f>H31+I31</f>
+        <v/>
+      </c>
+      <c r="K31" s="4">
+        <f>IF(C31&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="29" t="n">
+        <v>35.73</v>
+      </c>
+      <c r="B32" s="29">
+        <f>A32-$B$12</f>
+        <v/>
+      </c>
+      <c r="C32" s="29">
+        <f>MAX(0,A32-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D32" s="5">
+        <f>IF(C32&lt;=0,0,($B$7+$B$9*C32)*C32)</f>
+        <v/>
+      </c>
+      <c r="E32" s="24">
+        <f>D32*$B$11</f>
+        <v/>
+      </c>
+      <c r="F32" s="24">
+        <f>IF(A32&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A32&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A32,Stage_Storage!$A$11:$A$18,1))+(A32-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A32,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A32,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A32,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A32,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A32,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G32" s="31">
+        <f>E32+F32</f>
+        <v/>
+      </c>
+      <c r="H32" s="5">
+        <f>IF(B32&lt;=0,0,IF(B32&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B32,Courbe_QH_900!$A$24:$A$84,1))+(B32-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B32,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B32,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B32,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B32,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B32,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I32" s="5">
+        <f>IF(C32&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D32*IF(($B$7+2*C32*SQRT(1+$B$9^2))&lt;=0,0,((D32/($B$7+2*C32*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J32" s="15">
+        <f>H32+I32</f>
+        <v/>
+      </c>
+      <c r="K32" s="4">
+        <f>IF(C32&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="36" t="n">
+        <v>35.78</v>
+      </c>
+      <c r="B33" s="36">
+        <f>A33-$B$12</f>
+        <v/>
+      </c>
+      <c r="C33" s="36">
+        <f>MAX(0,A33-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D33" s="8">
+        <f>IF(C33&lt;=0,0,($B$7+$B$9*C33)*C33)</f>
+        <v/>
+      </c>
+      <c r="E33" s="39">
+        <f>D33*$B$11</f>
+        <v/>
+      </c>
+      <c r="F33" s="39">
+        <f>IF(A33&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A33&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A33,Stage_Storage!$A$11:$A$18,1))+(A33-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A33,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A33,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A33,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A33,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A33,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G33" s="31">
+        <f>E33+F33</f>
+        <v/>
+      </c>
+      <c r="H33" s="8">
+        <f>IF(B33&lt;=0,0,IF(B33&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B33,Courbe_QH_900!$A$24:$A$84,1))+(B33-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B33,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B33,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B33,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B33,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B33,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I33" s="8">
+        <f>IF(C33&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D33*IF(($B$7+2*C33*SQRT(1+$B$9^2))&lt;=0,0,((D33/($B$7+2*C33*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J33" s="15">
+        <f>H33+I33</f>
+        <v/>
+      </c>
+      <c r="K33" s="7">
+        <f>IF(C33&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="29" t="n">
+        <v>35.83</v>
+      </c>
+      <c r="B34" s="29">
+        <f>A34-$B$12</f>
+        <v/>
+      </c>
+      <c r="C34" s="29">
+        <f>MAX(0,A34-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D34" s="5">
+        <f>IF(C34&lt;=0,0,($B$7+$B$9*C34)*C34)</f>
+        <v/>
+      </c>
+      <c r="E34" s="24">
+        <f>D34*$B$11</f>
+        <v/>
+      </c>
+      <c r="F34" s="24">
+        <f>IF(A34&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A34&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A34,Stage_Storage!$A$11:$A$18,1))+(A34-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A34,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A34,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A34,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A34,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A34,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G34" s="31">
+        <f>E34+F34</f>
+        <v/>
+      </c>
+      <c r="H34" s="5">
+        <f>IF(B34&lt;=0,0,IF(B34&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B34,Courbe_QH_900!$A$24:$A$84,1))+(B34-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B34,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B34,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B34,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B34,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B34,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I34" s="5">
+        <f>IF(C34&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D34*IF(($B$7+2*C34*SQRT(1+$B$9^2))&lt;=0,0,((D34/($B$7+2*C34*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J34" s="15">
+        <f>H34+I34</f>
+        <v/>
+      </c>
+      <c r="K34" s="4">
+        <f>IF(C34&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="29" t="n">
+        <v>35.88</v>
+      </c>
+      <c r="B35" s="29">
+        <f>A35-$B$12</f>
+        <v/>
+      </c>
+      <c r="C35" s="29">
+        <f>MAX(0,A35-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D35" s="5">
+        <f>IF(C35&lt;=0,0,($B$7+$B$9*C35)*C35)</f>
+        <v/>
+      </c>
+      <c r="E35" s="24">
+        <f>D35*$B$11</f>
+        <v/>
+      </c>
+      <c r="F35" s="24">
+        <f>IF(A35&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A35&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A35,Stage_Storage!$A$11:$A$18,1))+(A35-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A35,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A35,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A35,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A35,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A35,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G35" s="31">
+        <f>E35+F35</f>
+        <v/>
+      </c>
+      <c r="H35" s="5">
+        <f>IF(B35&lt;=0,0,IF(B35&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B35,Courbe_QH_900!$A$24:$A$84,1))+(B35-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B35,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B35,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B35,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B35,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B35,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I35" s="5">
+        <f>IF(C35&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D35*IF(($B$7+2*C35*SQRT(1+$B$9^2))&lt;=0,0,((D35/($B$7+2*C35*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J35" s="15">
+        <f>H35+I35</f>
+        <v/>
+      </c>
+      <c r="K35" s="4">
+        <f>IF(C35&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="29" t="n">
+        <v>35.93</v>
+      </c>
+      <c r="B36" s="29">
+        <f>A36-$B$12</f>
+        <v/>
+      </c>
+      <c r="C36" s="29">
+        <f>MAX(0,A36-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D36" s="5">
+        <f>IF(C36&lt;=0,0,($B$7+$B$9*C36)*C36)</f>
+        <v/>
+      </c>
+      <c r="E36" s="24">
+        <f>D36*$B$11</f>
+        <v/>
+      </c>
+      <c r="F36" s="24">
+        <f>IF(A36&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A36&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A36,Stage_Storage!$A$11:$A$18,1))+(A36-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A36,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A36,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A36,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A36,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A36,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G36" s="31">
+        <f>E36+F36</f>
+        <v/>
+      </c>
+      <c r="H36" s="5">
+        <f>IF(B36&lt;=0,0,IF(B36&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B36,Courbe_QH_900!$A$24:$A$84,1))+(B36-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B36,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B36,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B36,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B36,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B36,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I36" s="5">
+        <f>IF(C36&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D36*IF(($B$7+2*C36*SQRT(1+$B$9^2))&lt;=0,0,((D36/($B$7+2*C36*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J36" s="15">
+        <f>H36+I36</f>
+        <v/>
+      </c>
+      <c r="K36" s="4">
+        <f>IF(C36&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="29" t="n">
+        <v>35.98</v>
+      </c>
+      <c r="B37" s="29">
+        <f>A37-$B$12</f>
+        <v/>
+      </c>
+      <c r="C37" s="29">
+        <f>MAX(0,A37-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D37" s="5">
+        <f>IF(C37&lt;=0,0,($B$7+$B$9*C37)*C37)</f>
+        <v/>
+      </c>
+      <c r="E37" s="24">
+        <f>D37*$B$11</f>
+        <v/>
+      </c>
+      <c r="F37" s="24">
+        <f>IF(A37&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A37&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A37,Stage_Storage!$A$11:$A$18,1))+(A37-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A37,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A37,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A37,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A37,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A37,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G37" s="31">
+        <f>E37+F37</f>
+        <v/>
+      </c>
+      <c r="H37" s="5">
+        <f>IF(B37&lt;=0,0,IF(B37&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B37,Courbe_QH_900!$A$24:$A$84,1))+(B37-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B37,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B37,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B37,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B37,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B37,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I37" s="5">
+        <f>IF(C37&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D37*IF(($B$7+2*C37*SQRT(1+$B$9^2))&lt;=0,0,((D37/($B$7+2*C37*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J37" s="15">
+        <f>H37+I37</f>
+        <v/>
+      </c>
+      <c r="K37" s="4">
+        <f>IF(C37&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="29" t="n">
+        <v>36.03</v>
+      </c>
+      <c r="B38" s="29">
+        <f>A38-$B$12</f>
+        <v/>
+      </c>
+      <c r="C38" s="29">
+        <f>MAX(0,A38-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D38" s="5">
+        <f>IF(C38&lt;=0,0,($B$7+$B$9*C38)*C38)</f>
+        <v/>
+      </c>
+      <c r="E38" s="24">
+        <f>D38*$B$11</f>
+        <v/>
+      </c>
+      <c r="F38" s="24">
+        <f>IF(A38&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A38&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A38,Stage_Storage!$A$11:$A$18,1))+(A38-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A38,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A38,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A38,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A38,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A38,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G38" s="31">
+        <f>E38+F38</f>
+        <v/>
+      </c>
+      <c r="H38" s="5">
+        <f>IF(B38&lt;=0,0,IF(B38&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B38,Courbe_QH_900!$A$24:$A$84,1))+(B38-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B38,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B38,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B38,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B38,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B38,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I38" s="5">
+        <f>IF(C38&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D38*IF(($B$7+2*C38*SQRT(1+$B$9^2))&lt;=0,0,((D38/($B$7+2*C38*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J38" s="15">
+        <f>H38+I38</f>
+        <v/>
+      </c>
+      <c r="K38" s="4">
+        <f>IF(C38&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="29" t="n">
+        <v>36.08</v>
+      </c>
+      <c r="B39" s="29">
+        <f>A39-$B$12</f>
+        <v/>
+      </c>
+      <c r="C39" s="29">
+        <f>MAX(0,A39-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D39" s="5">
+        <f>IF(C39&lt;=0,0,($B$7+$B$9*C39)*C39)</f>
+        <v/>
+      </c>
+      <c r="E39" s="24">
+        <f>D39*$B$11</f>
+        <v/>
+      </c>
+      <c r="F39" s="24">
+        <f>IF(A39&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A39&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A39,Stage_Storage!$A$11:$A$18,1))+(A39-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A39,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A39,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A39,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A39,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A39,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G39" s="31">
+        <f>E39+F39</f>
+        <v/>
+      </c>
+      <c r="H39" s="5">
+        <f>IF(B39&lt;=0,0,IF(B39&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B39,Courbe_QH_900!$A$24:$A$84,1))+(B39-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B39,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B39,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B39,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B39,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B39,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I39" s="5">
+        <f>IF(C39&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D39*IF(($B$7+2*C39*SQRT(1+$B$9^2))&lt;=0,0,((D39/($B$7+2*C39*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J39" s="15">
+        <f>H39+I39</f>
+        <v/>
+      </c>
+      <c r="K39" s="4">
+        <f>IF(C39&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="29" t="n">
+        <v>36.13</v>
+      </c>
+      <c r="B40" s="29">
+        <f>A40-$B$12</f>
+        <v/>
+      </c>
+      <c r="C40" s="29">
+        <f>MAX(0,A40-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D40" s="5">
+        <f>IF(C40&lt;=0,0,($B$7+$B$9*C40)*C40)</f>
+        <v/>
+      </c>
+      <c r="E40" s="24">
+        <f>D40*$B$11</f>
+        <v/>
+      </c>
+      <c r="F40" s="24">
+        <f>IF(A40&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A40&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A40,Stage_Storage!$A$11:$A$18,1))+(A40-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A40,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A40,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A40,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A40,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A40,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G40" s="31">
+        <f>E40+F40</f>
+        <v/>
+      </c>
+      <c r="H40" s="5">
+        <f>IF(B40&lt;=0,0,IF(B40&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B40,Courbe_QH_900!$A$24:$A$84,1))+(B40-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B40,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B40,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B40,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B40,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B40,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I40" s="5">
+        <f>IF(C40&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D40*IF(($B$7+2*C40*SQRT(1+$B$9^2))&lt;=0,0,((D40/($B$7+2*C40*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J40" s="15">
+        <f>H40+I40</f>
+        <v/>
+      </c>
+      <c r="K40" s="4">
+        <f>IF(C40&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="29" t="n">
+        <v>36.18</v>
+      </c>
+      <c r="B41" s="29">
+        <f>A41-$B$12</f>
+        <v/>
+      </c>
+      <c r="C41" s="29">
+        <f>MAX(0,A41-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D41" s="5">
+        <f>IF(C41&lt;=0,0,($B$7+$B$9*C41)*C41)</f>
+        <v/>
+      </c>
+      <c r="E41" s="24">
+        <f>D41*$B$11</f>
+        <v/>
+      </c>
+      <c r="F41" s="24">
+        <f>IF(A41&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A41&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A41,Stage_Storage!$A$11:$A$18,1))+(A41-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A41,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A41,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A41,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A41,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A41,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G41" s="31">
+        <f>E41+F41</f>
+        <v/>
+      </c>
+      <c r="H41" s="5">
+        <f>IF(B41&lt;=0,0,IF(B41&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B41,Courbe_QH_900!$A$24:$A$84,1))+(B41-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B41,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B41,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B41,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B41,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B41,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I41" s="5">
+        <f>IF(C41&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D41*IF(($B$7+2*C41*SQRT(1+$B$9^2))&lt;=0,0,((D41/($B$7+2*C41*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J41" s="15">
+        <f>H41+I41</f>
+        <v/>
+      </c>
+      <c r="K41" s="4">
+        <f>IF(C41&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="29" t="n">
+        <v>36.23</v>
+      </c>
+      <c r="B42" s="29">
+        <f>A42-$B$12</f>
+        <v/>
+      </c>
+      <c r="C42" s="29">
+        <f>MAX(0,A42-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D42" s="5">
+        <f>IF(C42&lt;=0,0,($B$7+$B$9*C42)*C42)</f>
+        <v/>
+      </c>
+      <c r="E42" s="24">
+        <f>D42*$B$11</f>
+        <v/>
+      </c>
+      <c r="F42" s="24">
+        <f>IF(A42&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A42&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A42,Stage_Storage!$A$11:$A$18,1))+(A42-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A42,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A42,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A42,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A42,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A42,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G42" s="31">
+        <f>E42+F42</f>
+        <v/>
+      </c>
+      <c r="H42" s="5">
+        <f>IF(B42&lt;=0,0,IF(B42&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B42,Courbe_QH_900!$A$24:$A$84,1))+(B42-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B42,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B42,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B42,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B42,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B42,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I42" s="5">
+        <f>IF(C42&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D42*IF(($B$7+2*C42*SQRT(1+$B$9^2))&lt;=0,0,((D42/($B$7+2*C42*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J42" s="15">
+        <f>H42+I42</f>
+        <v/>
+      </c>
+      <c r="K42" s="4">
+        <f>IF(C42&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="29" t="n">
+        <v>36.28</v>
+      </c>
+      <c r="B43" s="29">
+        <f>A43-$B$12</f>
+        <v/>
+      </c>
+      <c r="C43" s="29">
+        <f>MAX(0,A43-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D43" s="5">
+        <f>IF(C43&lt;=0,0,($B$7+$B$9*C43)*C43)</f>
+        <v/>
+      </c>
+      <c r="E43" s="24">
+        <f>D43*$B$11</f>
+        <v/>
+      </c>
+      <c r="F43" s="24">
+        <f>IF(A43&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A43&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A43,Stage_Storage!$A$11:$A$18,1))+(A43-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A43,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A43,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A43,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A43,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A43,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G43" s="31">
+        <f>E43+F43</f>
+        <v/>
+      </c>
+      <c r="H43" s="5">
+        <f>IF(B43&lt;=0,0,IF(B43&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B43,Courbe_QH_900!$A$24:$A$84,1))+(B43-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B43,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B43,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B43,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B43,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B43,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I43" s="5">
+        <f>IF(C43&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D43*IF(($B$7+2*C43*SQRT(1+$B$9^2))&lt;=0,0,((D43/($B$7+2*C43*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J43" s="15">
+        <f>H43+I43</f>
+        <v/>
+      </c>
+      <c r="K43" s="4">
+        <f>IF(C43&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="29" t="n">
+        <v>36.33</v>
+      </c>
+      <c r="B44" s="29">
+        <f>A44-$B$12</f>
+        <v/>
+      </c>
+      <c r="C44" s="29">
+        <f>MAX(0,A44-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D44" s="5">
+        <f>IF(C44&lt;=0,0,($B$7+$B$9*C44)*C44)</f>
+        <v/>
+      </c>
+      <c r="E44" s="24">
+        <f>D44*$B$11</f>
+        <v/>
+      </c>
+      <c r="F44" s="24">
+        <f>IF(A44&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A44&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A44,Stage_Storage!$A$11:$A$18,1))+(A44-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A44,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A44,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A44,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A44,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A44,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G44" s="31">
+        <f>E44+F44</f>
+        <v/>
+      </c>
+      <c r="H44" s="5">
+        <f>IF(B44&lt;=0,0,IF(B44&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B44,Courbe_QH_900!$A$24:$A$84,1))+(B44-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B44,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B44,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B44,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B44,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B44,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I44" s="5">
+        <f>IF(C44&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D44*IF(($B$7+2*C44*SQRT(1+$B$9^2))&lt;=0,0,((D44/($B$7+2*C44*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J44" s="15">
+        <f>H44+I44</f>
+        <v/>
+      </c>
+      <c r="K44" s="4">
+        <f>IF(C44&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="29" t="n">
+        <v>36.38</v>
+      </c>
+      <c r="B45" s="29">
+        <f>A45-$B$12</f>
+        <v/>
+      </c>
+      <c r="C45" s="29">
+        <f>MAX(0,A45-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D45" s="5">
+        <f>IF(C45&lt;=0,0,($B$7+$B$9*C45)*C45)</f>
+        <v/>
+      </c>
+      <c r="E45" s="24">
+        <f>D45*$B$11</f>
+        <v/>
+      </c>
+      <c r="F45" s="24">
+        <f>IF(A45&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A45&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A45,Stage_Storage!$A$11:$A$18,1))+(A45-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A45,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A45,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A45,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A45,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A45,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G45" s="31">
+        <f>E45+F45</f>
+        <v/>
+      </c>
+      <c r="H45" s="5">
+        <f>IF(B45&lt;=0,0,IF(B45&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B45,Courbe_QH_900!$A$24:$A$84,1))+(B45-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B45,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B45,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B45,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B45,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B45,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I45" s="5">
+        <f>IF(C45&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D45*IF(($B$7+2*C45*SQRT(1+$B$9^2))&lt;=0,0,((D45/($B$7+2*C45*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J45" s="15">
+        <f>H45+I45</f>
+        <v/>
+      </c>
+      <c r="K45" s="4">
+        <f>IF(C45&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="29" t="n">
+        <v>36.43</v>
+      </c>
+      <c r="B46" s="29">
+        <f>A46-$B$12</f>
+        <v/>
+      </c>
+      <c r="C46" s="29">
+        <f>MAX(0,A46-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D46" s="5">
+        <f>IF(C46&lt;=0,0,($B$7+$B$9*C46)*C46)</f>
+        <v/>
+      </c>
+      <c r="E46" s="24">
+        <f>D46*$B$11</f>
+        <v/>
+      </c>
+      <c r="F46" s="24">
+        <f>IF(A46&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A46&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A46,Stage_Storage!$A$11:$A$18,1))+(A46-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A46,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A46,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A46,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A46,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A46,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G46" s="31">
+        <f>E46+F46</f>
+        <v/>
+      </c>
+      <c r="H46" s="5">
+        <f>IF(B46&lt;=0,0,IF(B46&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B46,Courbe_QH_900!$A$24:$A$84,1))+(B46-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B46,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B46,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B46,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B46,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B46,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I46" s="5">
+        <f>IF(C46&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D46*IF(($B$7+2*C46*SQRT(1+$B$9^2))&lt;=0,0,((D46/($B$7+2*C46*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J46" s="15">
+        <f>H46+I46</f>
+        <v/>
+      </c>
+      <c r="K46" s="4">
+        <f>IF(C46&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="29" t="n">
+        <v>36.48</v>
+      </c>
+      <c r="B47" s="29">
+        <f>A47-$B$12</f>
+        <v/>
+      </c>
+      <c r="C47" s="29">
+        <f>MAX(0,A47-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D47" s="5">
+        <f>IF(C47&lt;=0,0,($B$7+$B$9*C47)*C47)</f>
+        <v/>
+      </c>
+      <c r="E47" s="24">
+        <f>D47*$B$11</f>
+        <v/>
+      </c>
+      <c r="F47" s="24">
+        <f>IF(A47&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A47&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A47,Stage_Storage!$A$11:$A$18,1))+(A47-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A47,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A47,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A47,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A47,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A47,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G47" s="31">
+        <f>E47+F47</f>
+        <v/>
+      </c>
+      <c r="H47" s="5">
+        <f>IF(B47&lt;=0,0,IF(B47&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B47,Courbe_QH_900!$A$24:$A$84,1))+(B47-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B47,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B47,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B47,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B47,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B47,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I47" s="5">
+        <f>IF(C47&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D47*IF(($B$7+2*C47*SQRT(1+$B$9^2))&lt;=0,0,((D47/($B$7+2*C47*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J47" s="15">
+        <f>H47+I47</f>
+        <v/>
+      </c>
+      <c r="K47" s="4">
+        <f>IF(C47&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="29" t="n">
+        <v>36.53</v>
+      </c>
+      <c r="B48" s="29">
+        <f>A48-$B$12</f>
+        <v/>
+      </c>
+      <c r="C48" s="29">
+        <f>MAX(0,A48-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D48" s="5">
+        <f>IF(C48&lt;=0,0,($B$7+$B$9*C48)*C48)</f>
+        <v/>
+      </c>
+      <c r="E48" s="24">
+        <f>D48*$B$11</f>
+        <v/>
+      </c>
+      <c r="F48" s="24">
+        <f>IF(A48&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A48&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A48,Stage_Storage!$A$11:$A$18,1))+(A48-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A48,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A48,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A48,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A48,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A48,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G48" s="31">
+        <f>E48+F48</f>
+        <v/>
+      </c>
+      <c r="H48" s="5">
+        <f>IF(B48&lt;=0,0,IF(B48&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B48,Courbe_QH_900!$A$24:$A$84,1))+(B48-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B48,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B48,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B48,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B48,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B48,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I48" s="5">
+        <f>IF(C48&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D48*IF(($B$7+2*C48*SQRT(1+$B$9^2))&lt;=0,0,((D48/($B$7+2*C48*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J48" s="15">
+        <f>H48+I48</f>
+        <v/>
+      </c>
+      <c r="K48" s="4">
+        <f>IF(C48&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="29" t="n">
+        <v>36.58</v>
+      </c>
+      <c r="B49" s="29">
+        <f>A49-$B$12</f>
+        <v/>
+      </c>
+      <c r="C49" s="29">
+        <f>MAX(0,A49-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D49" s="5">
+        <f>IF(C49&lt;=0,0,($B$7+$B$9*C49)*C49)</f>
+        <v/>
+      </c>
+      <c r="E49" s="24">
+        <f>D49*$B$11</f>
+        <v/>
+      </c>
+      <c r="F49" s="24">
+        <f>IF(A49&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A49&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A49,Stage_Storage!$A$11:$A$18,1))+(A49-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A49,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A49,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A49,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A49,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A49,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G49" s="31">
+        <f>E49+F49</f>
+        <v/>
+      </c>
+      <c r="H49" s="5">
+        <f>IF(B49&lt;=0,0,IF(B49&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B49,Courbe_QH_900!$A$24:$A$84,1))+(B49-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B49,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B49,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B49,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B49,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B49,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I49" s="5">
+        <f>IF(C49&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D49*IF(($B$7+2*C49*SQRT(1+$B$9^2))&lt;=0,0,((D49/($B$7+2*C49*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J49" s="15">
+        <f>H49+I49</f>
+        <v/>
+      </c>
+      <c r="K49" s="4">
+        <f>IF(C49&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="29" t="n">
+        <v>36.63</v>
+      </c>
+      <c r="B50" s="29">
+        <f>A50-$B$12</f>
+        <v/>
+      </c>
+      <c r="C50" s="29">
+        <f>MAX(0,A50-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D50" s="5">
+        <f>IF(C50&lt;=0,0,($B$7+$B$9*C50)*C50)</f>
+        <v/>
+      </c>
+      <c r="E50" s="24">
+        <f>D50*$B$11</f>
+        <v/>
+      </c>
+      <c r="F50" s="24">
+        <f>IF(A50&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A50&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A50,Stage_Storage!$A$11:$A$18,1))+(A50-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A50,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A50,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A50,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A50,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A50,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G50" s="31">
+        <f>E50+F50</f>
+        <v/>
+      </c>
+      <c r="H50" s="5">
+        <f>IF(B50&lt;=0,0,IF(B50&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B50,Courbe_QH_900!$A$24:$A$84,1))+(B50-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B50,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B50,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B50,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B50,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B50,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I50" s="5">
+        <f>IF(C50&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D50*IF(($B$7+2*C50*SQRT(1+$B$9^2))&lt;=0,0,((D50/($B$7+2*C50*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J50" s="15">
+        <f>H50+I50</f>
+        <v/>
+      </c>
+      <c r="K50" s="4">
+        <f>IF(C50&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="29" t="n">
+        <v>36.68</v>
+      </c>
+      <c r="B51" s="29">
+        <f>A51-$B$12</f>
+        <v/>
+      </c>
+      <c r="C51" s="29">
+        <f>MAX(0,A51-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D51" s="5">
+        <f>IF(C51&lt;=0,0,($B$7+$B$9*C51)*C51)</f>
+        <v/>
+      </c>
+      <c r="E51" s="24">
+        <f>D51*$B$11</f>
+        <v/>
+      </c>
+      <c r="F51" s="24">
+        <f>IF(A51&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A51&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A51,Stage_Storage!$A$11:$A$18,1))+(A51-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A51,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A51,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A51,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A51,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A51,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G51" s="31">
+        <f>E51+F51</f>
+        <v/>
+      </c>
+      <c r="H51" s="5">
+        <f>IF(B51&lt;=0,0,IF(B51&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B51,Courbe_QH_900!$A$24:$A$84,1))+(B51-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B51,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B51,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B51,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B51,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B51,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I51" s="5">
+        <f>IF(C51&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D51*IF(($B$7+2*C51*SQRT(1+$B$9^2))&lt;=0,0,((D51/($B$7+2*C51*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J51" s="15">
+        <f>H51+I51</f>
+        <v/>
+      </c>
+      <c r="K51" s="4">
+        <f>IF(C51&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="29" t="n">
+        <v>36.73</v>
+      </c>
+      <c r="B52" s="29">
+        <f>A52-$B$12</f>
+        <v/>
+      </c>
+      <c r="C52" s="29">
+        <f>MAX(0,A52-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D52" s="5">
+        <f>IF(C52&lt;=0,0,($B$7+$B$9*C52)*C52)</f>
+        <v/>
+      </c>
+      <c r="E52" s="24">
+        <f>D52*$B$11</f>
+        <v/>
+      </c>
+      <c r="F52" s="24">
+        <f>IF(A52&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A52&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A52,Stage_Storage!$A$11:$A$18,1))+(A52-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A52,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A52,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A52,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A52,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A52,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G52" s="31">
+        <f>E52+F52</f>
+        <v/>
+      </c>
+      <c r="H52" s="5">
+        <f>IF(B52&lt;=0,0,IF(B52&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B52,Courbe_QH_900!$A$24:$A$84,1))+(B52-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B52,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B52,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B52,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B52,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B52,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I52" s="5">
+        <f>IF(C52&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D52*IF(($B$7+2*C52*SQRT(1+$B$9^2))&lt;=0,0,((D52/($B$7+2*C52*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J52" s="15">
+        <f>H52+I52</f>
+        <v/>
+      </c>
+      <c r="K52" s="4">
+        <f>IF(C52&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="29" t="n">
+        <v>36.78</v>
+      </c>
+      <c r="B53" s="29">
+        <f>A53-$B$12</f>
+        <v/>
+      </c>
+      <c r="C53" s="29">
+        <f>MAX(0,A53-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D53" s="5">
+        <f>IF(C53&lt;=0,0,($B$7+$B$9*C53)*C53)</f>
+        <v/>
+      </c>
+      <c r="E53" s="24">
+        <f>D53*$B$11</f>
+        <v/>
+      </c>
+      <c r="F53" s="24">
+        <f>IF(A53&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A53&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A53,Stage_Storage!$A$11:$A$18,1))+(A53-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A53,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A53,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A53,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A53,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A53,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G53" s="31">
+        <f>E53+F53</f>
+        <v/>
+      </c>
+      <c r="H53" s="5">
+        <f>IF(B53&lt;=0,0,IF(B53&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B53,Courbe_QH_900!$A$24:$A$84,1))+(B53-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B53,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B53,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B53,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B53,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B53,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I53" s="5">
+        <f>IF(C53&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D53*IF(($B$7+2*C53*SQRT(1+$B$9^2))&lt;=0,0,((D53/($B$7+2*C53*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J53" s="15">
+        <f>H53+I53</f>
+        <v/>
+      </c>
+      <c r="K53" s="4">
+        <f>IF(C53&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="29" t="n">
+        <v>36.83</v>
+      </c>
+      <c r="B54" s="29">
+        <f>A54-$B$12</f>
+        <v/>
+      </c>
+      <c r="C54" s="29">
+        <f>MAX(0,A54-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D54" s="5">
+        <f>IF(C54&lt;=0,0,($B$7+$B$9*C54)*C54)</f>
+        <v/>
+      </c>
+      <c r="E54" s="24">
+        <f>D54*$B$11</f>
+        <v/>
+      </c>
+      <c r="F54" s="24">
+        <f>IF(A54&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A54&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A54,Stage_Storage!$A$11:$A$18,1))+(A54-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A54,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A54,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A54,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A54,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A54,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G54" s="31">
+        <f>E54+F54</f>
+        <v/>
+      </c>
+      <c r="H54" s="5">
+        <f>IF(B54&lt;=0,0,IF(B54&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B54,Courbe_QH_900!$A$24:$A$84,1))+(B54-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B54,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B54,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B54,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B54,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B54,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I54" s="5">
+        <f>IF(C54&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D54*IF(($B$7+2*C54*SQRT(1+$B$9^2))&lt;=0,0,((D54/($B$7+2*C54*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J54" s="15">
+        <f>H54+I54</f>
+        <v/>
+      </c>
+      <c r="K54" s="4">
+        <f>IF(C54&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="29" t="n">
+        <v>36.88</v>
+      </c>
+      <c r="B55" s="29">
+        <f>A55-$B$12</f>
+        <v/>
+      </c>
+      <c r="C55" s="29">
+        <f>MAX(0,A55-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D55" s="5">
+        <f>IF(C55&lt;=0,0,($B$7+$B$9*C55)*C55)</f>
+        <v/>
+      </c>
+      <c r="E55" s="24">
+        <f>D55*$B$11</f>
+        <v/>
+      </c>
+      <c r="F55" s="24">
+        <f>IF(A55&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A55&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A55,Stage_Storage!$A$11:$A$18,1))+(A55-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A55,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A55,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A55,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A55,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A55,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G55" s="31">
+        <f>E55+F55</f>
+        <v/>
+      </c>
+      <c r="H55" s="5">
+        <f>IF(B55&lt;=0,0,IF(B55&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B55,Courbe_QH_900!$A$24:$A$84,1))+(B55-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B55,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B55,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B55,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B55,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B55,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I55" s="5">
+        <f>IF(C55&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D55*IF(($B$7+2*C55*SQRT(1+$B$9^2))&lt;=0,0,((D55/($B$7+2*C55*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J55" s="15">
+        <f>H55+I55</f>
+        <v/>
+      </c>
+      <c r="K55" s="4">
+        <f>IF(C55&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="29" t="n">
+        <v>36.93</v>
+      </c>
+      <c r="B56" s="29">
+        <f>A56-$B$12</f>
+        <v/>
+      </c>
+      <c r="C56" s="29">
+        <f>MAX(0,A56-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D56" s="5">
+        <f>IF(C56&lt;=0,0,($B$7+$B$9*C56)*C56)</f>
+        <v/>
+      </c>
+      <c r="E56" s="24">
+        <f>D56*$B$11</f>
+        <v/>
+      </c>
+      <c r="F56" s="24">
+        <f>IF(A56&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A56&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A56,Stage_Storage!$A$11:$A$18,1))+(A56-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A56,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A56,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A56,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A56,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A56,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G56" s="31">
+        <f>E56+F56</f>
+        <v/>
+      </c>
+      <c r="H56" s="5">
+        <f>IF(B56&lt;=0,0,IF(B56&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B56,Courbe_QH_900!$A$24:$A$84,1))+(B56-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B56,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B56,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B56,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B56,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B56,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I56" s="5">
+        <f>IF(C56&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D56*IF(($B$7+2*C56*SQRT(1+$B$9^2))&lt;=0,0,((D56/($B$7+2*C56*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J56" s="15">
+        <f>H56+I56</f>
+        <v/>
+      </c>
+      <c r="K56" s="4">
+        <f>IF(C56&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="29" t="n">
+        <v>36.98</v>
+      </c>
+      <c r="B57" s="29">
+        <f>A57-$B$12</f>
+        <v/>
+      </c>
+      <c r="C57" s="29">
+        <f>MAX(0,A57-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D57" s="5">
+        <f>IF(C57&lt;=0,0,($B$7+$B$9*C57)*C57)</f>
+        <v/>
+      </c>
+      <c r="E57" s="24">
+        <f>D57*$B$11</f>
+        <v/>
+      </c>
+      <c r="F57" s="24">
+        <f>IF(A57&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A57&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A57,Stage_Storage!$A$11:$A$18,1))+(A57-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A57,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A57,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A57,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A57,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A57,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G57" s="31">
+        <f>E57+F57</f>
+        <v/>
+      </c>
+      <c r="H57" s="5">
+        <f>IF(B57&lt;=0,0,IF(B57&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B57,Courbe_QH_900!$A$24:$A$84,1))+(B57-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B57,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B57,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B57,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B57,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B57,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I57" s="5">
+        <f>IF(C57&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D57*IF(($B$7+2*C57*SQRT(1+$B$9^2))&lt;=0,0,((D57/($B$7+2*C57*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J57" s="15">
+        <f>H57+I57</f>
+        <v/>
+      </c>
+      <c r="K57" s="4">
+        <f>IF(C57&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="29" t="n">
+        <v>37.03</v>
+      </c>
+      <c r="B58" s="29">
+        <f>A58-$B$12</f>
+        <v/>
+      </c>
+      <c r="C58" s="29">
+        <f>MAX(0,A58-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D58" s="5">
+        <f>IF(C58&lt;=0,0,($B$7+$B$9*C58)*C58)</f>
+        <v/>
+      </c>
+      <c r="E58" s="24">
+        <f>D58*$B$11</f>
+        <v/>
+      </c>
+      <c r="F58" s="24">
+        <f>IF(A58&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A58&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A58,Stage_Storage!$A$11:$A$18,1))+(A58-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A58,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A58,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A58,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A58,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A58,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G58" s="31">
+        <f>E58+F58</f>
+        <v/>
+      </c>
+      <c r="H58" s="5">
+        <f>IF(B58&lt;=0,0,IF(B58&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B58,Courbe_QH_900!$A$24:$A$84,1))+(B58-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B58,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B58,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B58,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B58,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B58,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I58" s="5">
+        <f>IF(C58&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D58*IF(($B$7+2*C58*SQRT(1+$B$9^2))&lt;=0,0,((D58/($B$7+2*C58*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J58" s="15">
+        <f>H58+I58</f>
+        <v/>
+      </c>
+      <c r="K58" s="4">
+        <f>IF(C58&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="29" t="n">
+        <v>37.08</v>
+      </c>
+      <c r="B59" s="29">
+        <f>A59-$B$12</f>
+        <v/>
+      </c>
+      <c r="C59" s="29">
+        <f>MAX(0,A59-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D59" s="5">
+        <f>IF(C59&lt;=0,0,($B$7+$B$9*C59)*C59)</f>
+        <v/>
+      </c>
+      <c r="E59" s="24">
+        <f>D59*$B$11</f>
+        <v/>
+      </c>
+      <c r="F59" s="24">
+        <f>IF(A59&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A59&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A59,Stage_Storage!$A$11:$A$18,1))+(A59-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A59,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A59,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A59,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A59,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A59,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G59" s="31">
+        <f>E59+F59</f>
+        <v/>
+      </c>
+      <c r="H59" s="5">
+        <f>IF(B59&lt;=0,0,IF(B59&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B59,Courbe_QH_900!$A$24:$A$84,1))+(B59-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B59,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B59,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B59,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B59,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B59,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I59" s="5">
+        <f>IF(C59&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D59*IF(($B$7+2*C59*SQRT(1+$B$9^2))&lt;=0,0,((D59/($B$7+2*C59*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J59" s="15">
+        <f>H59+I59</f>
+        <v/>
+      </c>
+      <c r="K59" s="4">
+        <f>IF(C59&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="29" t="n">
+        <v>37.13</v>
+      </c>
+      <c r="B60" s="29">
+        <f>A60-$B$12</f>
+        <v/>
+      </c>
+      <c r="C60" s="29">
+        <f>MAX(0,A60-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D60" s="5">
+        <f>IF(C60&lt;=0,0,($B$7+$B$9*C60)*C60)</f>
+        <v/>
+      </c>
+      <c r="E60" s="24">
+        <f>D60*$B$11</f>
+        <v/>
+      </c>
+      <c r="F60" s="24">
+        <f>IF(A60&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A60&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1))+(A60-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G60" s="31">
+        <f>E60+F60</f>
+        <v/>
+      </c>
+      <c r="H60" s="5">
+        <f>IF(B60&lt;=0,0,IF(B60&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B60,Courbe_QH_900!$A$24:$A$84,1))+(B60-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B60,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B60,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B60,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B60,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B60,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I60" s="5">
+        <f>IF(C60&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D60*IF(($B$7+2*C60*SQRT(1+$B$9^2))&lt;=0,0,((D60/($B$7+2*C60*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J60" s="15">
+        <f>H60+I60</f>
+        <v/>
+      </c>
+      <c r="K60" s="4">
+        <f>IF(C60&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="29" t="n">
+        <v>37.18</v>
+      </c>
+      <c r="B61" s="29">
+        <f>A61-$B$12</f>
+        <v/>
+      </c>
+      <c r="C61" s="29">
+        <f>MAX(0,A61-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D61" s="5">
+        <f>IF(C61&lt;=0,0,($B$7+$B$9*C61)*C61)</f>
+        <v/>
+      </c>
+      <c r="E61" s="24">
+        <f>D61*$B$11</f>
+        <v/>
+      </c>
+      <c r="F61" s="24">
+        <f>IF(A61&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A61&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1))+(A61-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G61" s="31">
+        <f>E61+F61</f>
+        <v/>
+      </c>
+      <c r="H61" s="5">
+        <f>IF(B61&lt;=0,0,IF(B61&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B61,Courbe_QH_900!$A$24:$A$84,1))+(B61-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B61,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B61,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B61,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B61,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B61,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I61" s="5">
+        <f>IF(C61&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D61*IF(($B$7+2*C61*SQRT(1+$B$9^2))&lt;=0,0,((D61/($B$7+2*C61*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J61" s="15">
+        <f>H61+I61</f>
+        <v/>
+      </c>
+      <c r="K61" s="4">
+        <f>IF(C61&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="29" t="n">
+        <v>37.23</v>
+      </c>
+      <c r="B62" s="29">
+        <f>A62-$B$12</f>
+        <v/>
+      </c>
+      <c r="C62" s="29">
+        <f>MAX(0,A62-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D62" s="5">
+        <f>IF(C62&lt;=0,0,($B$7+$B$9*C62)*C62)</f>
+        <v/>
+      </c>
+      <c r="E62" s="24">
+        <f>D62*$B$11</f>
+        <v/>
+      </c>
+      <c r="F62" s="24">
+        <f>IF(A62&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A62&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1))+(A62-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G62" s="31">
+        <f>E62+F62</f>
+        <v/>
+      </c>
+      <c r="H62" s="5">
+        <f>IF(B62&lt;=0,0,IF(B62&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B62,Courbe_QH_900!$A$24:$A$84,1))+(B62-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B62,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B62,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B62,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B62,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B62,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I62" s="5">
+        <f>IF(C62&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D62*IF(($B$7+2*C62*SQRT(1+$B$9^2))&lt;=0,0,((D62/($B$7+2*C62*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J62" s="15">
+        <f>H62+I62</f>
+        <v/>
+      </c>
+      <c r="K62" s="4">
+        <f>IF(C62&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="29" t="n">
         <v>37.28</v>
       </c>
-      <c r="B16" s="17" t="n">
-        <v>543</v>
-      </c>
-      <c r="C16" s="35">
-        <f>A16-A15</f>
-        <v/>
-      </c>
-      <c r="D16" s="39">
-        <f>0.5*(B15+B16)*C16</f>
-        <v/>
-      </c>
-      <c r="E16" s="39">
-        <f>E15+D16</f>
-        <v/>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>LIMITE PATRON (+1.5 m crown) — votre levé</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="28" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="B17" s="17" t="n">
-        <v>700</v>
-      </c>
-      <c r="C17" s="28">
-        <f>A17-A16</f>
-        <v/>
-      </c>
-      <c r="D17" s="23">
-        <f>0.5*(B16+B17)*C17</f>
-        <v/>
-      </c>
-      <c r="E17" s="30">
-        <f>E16+D17</f>
-        <v/>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Placeholder — remplacer par levé</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="28" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="B18" s="17" t="n">
-        <v>1932</v>
-      </c>
-      <c r="C18" s="28">
-        <f>A18-A17</f>
-        <v/>
-      </c>
-      <c r="D18" s="23">
-        <f>0.5*(B17+B18)*C18</f>
-        <v/>
-      </c>
-      <c r="E18" s="30">
-        <f>E17+D18</f>
-        <v/>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>Votre levé 1932 m² — niveau optionnel plus haut</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Vmax_A (Calcul_A)</t>
-        </is>
-      </c>
-      <c r="B21" s="18">
-        <f>Parametres!B27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>WSEmax_A (m)</t>
-        </is>
-      </c>
-      <c r="B22" s="38">
-        <f>Parametres!B30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Vmax_B (Calcul_B)</t>
-        </is>
-      </c>
-      <c r="B23" s="18">
-        <f>Parametres!B34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>WSEmax_B (m)</t>
-        </is>
-      </c>
-      <c r="B24" s="38">
-        <f>Parametres!B36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>V disponible à 37.28 m (m³)</t>
-        </is>
-      </c>
-      <c r="B25" s="40">
-        <f>E16</f>
-        <v/>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Si Vmax_A ou Vmax_B &gt; cette valeur → le niveau dépasse la limite patron</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Comment lire le résultat</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="36" t="inlineStr">
-        <is>
-          <t>Exemple: si Vmax_A = 5609 m³ et V(37.28)≈558 m³, alors WSEmax_A est au-dessus de 37.28 m (la table ira vers 39.5 m ou 'Hors table'). Affinez en entrant les vraies surfaces aux cotes intermédiaires (jaune). Parametres montre WSEmax_A (B30) et WSEmax_B (B36) séparément.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30"/>
+      <c r="B63" s="29">
+        <f>A63-$B$12</f>
+        <v/>
+      </c>
+      <c r="C63" s="29">
+        <f>MAX(0,A63-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D63" s="5">
+        <f>IF(C63&lt;=0,0,($B$7+$B$9*C63)*C63)</f>
+        <v/>
+      </c>
+      <c r="E63" s="24">
+        <f>D63*$B$11</f>
+        <v/>
+      </c>
+      <c r="F63" s="24">
+        <f>IF(A63&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A63&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1))+(A63-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G63" s="31">
+        <f>E63+F63</f>
+        <v/>
+      </c>
+      <c r="H63" s="5">
+        <f>IF(B63&lt;=0,0,IF(B63&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B63,Courbe_QH_900!$A$24:$A$84,1))+(B63-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B63,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B63,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B63,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B63,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B63,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I63" s="5">
+        <f>IF(C63&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D63*IF(($B$7+2*C63*SQRT(1+$B$9^2))&lt;=0,0,((D63/($B$7+2*C63*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J63" s="15">
+        <f>H63+I63</f>
+        <v/>
+      </c>
+      <c r="K63" s="4">
+        <f>IF(C63&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="29" t="n">
+        <v>37.33</v>
+      </c>
+      <c r="B64" s="29">
+        <f>A64-$B$12</f>
+        <v/>
+      </c>
+      <c r="C64" s="29">
+        <f>MAX(0,A64-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D64" s="5">
+        <f>IF(C64&lt;=0,0,($B$7+$B$9*C64)*C64)</f>
+        <v/>
+      </c>
+      <c r="E64" s="24">
+        <f>D64*$B$11</f>
+        <v/>
+      </c>
+      <c r="F64" s="24">
+        <f>IF(A64&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A64&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1))+(A64-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G64" s="31">
+        <f>E64+F64</f>
+        <v/>
+      </c>
+      <c r="H64" s="5">
+        <f>IF(B64&lt;=0,0,IF(B64&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B64,Courbe_QH_900!$A$24:$A$84,1))+(B64-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B64,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B64,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B64,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B64,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B64,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I64" s="5">
+        <f>IF(C64&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D64*IF(($B$7+2*C64*SQRT(1+$B$9^2))&lt;=0,0,((D64/($B$7+2*C64*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J64" s="15">
+        <f>H64+I64</f>
+        <v/>
+      </c>
+      <c r="K64" s="4">
+        <f>IF(C64&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="29" t="n">
+        <v>37.38</v>
+      </c>
+      <c r="B65" s="29">
+        <f>A65-$B$12</f>
+        <v/>
+      </c>
+      <c r="C65" s="29">
+        <f>MAX(0,A65-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D65" s="5">
+        <f>IF(C65&lt;=0,0,($B$7+$B$9*C65)*C65)</f>
+        <v/>
+      </c>
+      <c r="E65" s="24">
+        <f>D65*$B$11</f>
+        <v/>
+      </c>
+      <c r="F65" s="24">
+        <f>IF(A65&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A65&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1))+(A65-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G65" s="31">
+        <f>E65+F65</f>
+        <v/>
+      </c>
+      <c r="H65" s="5">
+        <f>IF(B65&lt;=0,0,IF(B65&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B65,Courbe_QH_900!$A$24:$A$84,1))+(B65-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B65,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B65,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B65,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B65,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B65,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I65" s="5">
+        <f>IF(C65&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D65*IF(($B$7+2*C65*SQRT(1+$B$9^2))&lt;=0,0,((D65/($B$7+2*C65*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J65" s="15">
+        <f>H65+I65</f>
+        <v/>
+      </c>
+      <c r="K65" s="4">
+        <f>IF(C65&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="29" t="n">
+        <v>37.43</v>
+      </c>
+      <c r="B66" s="29">
+        <f>A66-$B$12</f>
+        <v/>
+      </c>
+      <c r="C66" s="29">
+        <f>MAX(0,A66-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D66" s="5">
+        <f>IF(C66&lt;=0,0,($B$7+$B$9*C66)*C66)</f>
+        <v/>
+      </c>
+      <c r="E66" s="24">
+        <f>D66*$B$11</f>
+        <v/>
+      </c>
+      <c r="F66" s="24">
+        <f>IF(A66&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A66&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1))+(A66-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G66" s="31">
+        <f>E66+F66</f>
+        <v/>
+      </c>
+      <c r="H66" s="5">
+        <f>IF(B66&lt;=0,0,IF(B66&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B66,Courbe_QH_900!$A$24:$A$84,1))+(B66-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B66,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B66,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B66,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B66,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B66,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I66" s="5">
+        <f>IF(C66&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D66*IF(($B$7+2*C66*SQRT(1+$B$9^2))&lt;=0,0,((D66/($B$7+2*C66*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J66" s="15">
+        <f>H66+I66</f>
+        <v/>
+      </c>
+      <c r="K66" s="4">
+        <f>IF(C66&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="29" t="n">
+        <v>37.48</v>
+      </c>
+      <c r="B67" s="29">
+        <f>A67-$B$12</f>
+        <v/>
+      </c>
+      <c r="C67" s="29">
+        <f>MAX(0,A67-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D67" s="5">
+        <f>IF(C67&lt;=0,0,($B$7+$B$9*C67)*C67)</f>
+        <v/>
+      </c>
+      <c r="E67" s="24">
+        <f>D67*$B$11</f>
+        <v/>
+      </c>
+      <c r="F67" s="24">
+        <f>IF(A67&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A67&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A67,Stage_Storage!$A$11:$A$18,1))+(A67-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A67,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A67,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A67,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A67,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A67,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G67" s="31">
+        <f>E67+F67</f>
+        <v/>
+      </c>
+      <c r="H67" s="5">
+        <f>IF(B67&lt;=0,0,IF(B67&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B67,Courbe_QH_900!$A$24:$A$84,1))+(B67-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B67,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B67,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B67,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B67,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B67,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I67" s="5">
+        <f>IF(C67&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D67*IF(($B$7+2*C67*SQRT(1+$B$9^2))&lt;=0,0,((D67/($B$7+2*C67*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J67" s="15">
+        <f>H67+I67</f>
+        <v/>
+      </c>
+      <c r="K67" s="4">
+        <f>IF(C67&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="29" t="n">
+        <v>37.53</v>
+      </c>
+      <c r="B68" s="29">
+        <f>A68-$B$12</f>
+        <v/>
+      </c>
+      <c r="C68" s="29">
+        <f>MAX(0,A68-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D68" s="5">
+        <f>IF(C68&lt;=0,0,($B$7+$B$9*C68)*C68)</f>
+        <v/>
+      </c>
+      <c r="E68" s="24">
+        <f>D68*$B$11</f>
+        <v/>
+      </c>
+      <c r="F68" s="24">
+        <f>IF(A68&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A68&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A68,Stage_Storage!$A$11:$A$18,1))+(A68-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A68,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A68,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A68,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A68,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A68,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G68" s="31">
+        <f>E68+F68</f>
+        <v/>
+      </c>
+      <c r="H68" s="5">
+        <f>IF(B68&lt;=0,0,IF(B68&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B68,Courbe_QH_900!$A$24:$A$84,1))+(B68-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B68,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B68,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B68,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B68,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B68,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I68" s="5">
+        <f>IF(C68&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D68*IF(($B$7+2*C68*SQRT(1+$B$9^2))&lt;=0,0,((D68/($B$7+2*C68*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J68" s="15">
+        <f>H68+I68</f>
+        <v/>
+      </c>
+      <c r="K68" s="4">
+        <f>IF(C68&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="29" t="n">
+        <v>37.58</v>
+      </c>
+      <c r="B69" s="29">
+        <f>A69-$B$12</f>
+        <v/>
+      </c>
+      <c r="C69" s="29">
+        <f>MAX(0,A69-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D69" s="5">
+        <f>IF(C69&lt;=0,0,($B$7+$B$9*C69)*C69)</f>
+        <v/>
+      </c>
+      <c r="E69" s="24">
+        <f>D69*$B$11</f>
+        <v/>
+      </c>
+      <c r="F69" s="24">
+        <f>IF(A69&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A69&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A69,Stage_Storage!$A$11:$A$18,1))+(A69-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A69,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A69,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A69,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A69,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A69,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G69" s="31">
+        <f>E69+F69</f>
+        <v/>
+      </c>
+      <c r="H69" s="5">
+        <f>IF(B69&lt;=0,0,IF(B69&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B69,Courbe_QH_900!$A$24:$A$84,1))+(B69-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B69,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B69,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B69,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B69,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B69,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I69" s="5">
+        <f>IF(C69&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D69*IF(($B$7+2*C69*SQRT(1+$B$9^2))&lt;=0,0,((D69/($B$7+2*C69*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J69" s="15">
+        <f>H69+I69</f>
+        <v/>
+      </c>
+      <c r="K69" s="4">
+        <f>IF(C69&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="29" t="n">
+        <v>37.63</v>
+      </c>
+      <c r="B70" s="29">
+        <f>A70-$B$12</f>
+        <v/>
+      </c>
+      <c r="C70" s="29">
+        <f>MAX(0,A70-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D70" s="5">
+        <f>IF(C70&lt;=0,0,($B$7+$B$9*C70)*C70)</f>
+        <v/>
+      </c>
+      <c r="E70" s="24">
+        <f>D70*$B$11</f>
+        <v/>
+      </c>
+      <c r="F70" s="24">
+        <f>IF(A70&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A70&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A70,Stage_Storage!$A$11:$A$18,1))+(A70-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A70,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A70,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A70,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A70,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A70,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G70" s="31">
+        <f>E70+F70</f>
+        <v/>
+      </c>
+      <c r="H70" s="5">
+        <f>IF(B70&lt;=0,0,IF(B70&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B70,Courbe_QH_900!$A$24:$A$84,1))+(B70-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B70,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B70,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B70,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B70,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B70,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I70" s="5">
+        <f>IF(C70&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D70*IF(($B$7+2*C70*SQRT(1+$B$9^2))&lt;=0,0,((D70/($B$7+2*C70*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J70" s="15">
+        <f>H70+I70</f>
+        <v/>
+      </c>
+      <c r="K70" s="4">
+        <f>IF(C70&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="29" t="n">
+        <v>37.68</v>
+      </c>
+      <c r="B71" s="29">
+        <f>A71-$B$12</f>
+        <v/>
+      </c>
+      <c r="C71" s="29">
+        <f>MAX(0,A71-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D71" s="5">
+        <f>IF(C71&lt;=0,0,($B$7+$B$9*C71)*C71)</f>
+        <v/>
+      </c>
+      <c r="E71" s="24">
+        <f>D71*$B$11</f>
+        <v/>
+      </c>
+      <c r="F71" s="24">
+        <f>IF(A71&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A71&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A71,Stage_Storage!$A$11:$A$18,1))+(A71-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A71,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A71,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A71,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A71,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A71,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G71" s="31">
+        <f>E71+F71</f>
+        <v/>
+      </c>
+      <c r="H71" s="5">
+        <f>IF(B71&lt;=0,0,IF(B71&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B71,Courbe_QH_900!$A$24:$A$84,1))+(B71-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B71,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B71,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B71,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B71,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B71,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I71" s="5">
+        <f>IF(C71&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D71*IF(($B$7+2*C71*SQRT(1+$B$9^2))&lt;=0,0,((D71/($B$7+2*C71*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J71" s="15">
+        <f>H71+I71</f>
+        <v/>
+      </c>
+      <c r="K71" s="4">
+        <f>IF(C71&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="29" t="n">
+        <v>37.73</v>
+      </c>
+      <c r="B72" s="29">
+        <f>A72-$B$12</f>
+        <v/>
+      </c>
+      <c r="C72" s="29">
+        <f>MAX(0,A72-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D72" s="5">
+        <f>IF(C72&lt;=0,0,($B$7+$B$9*C72)*C72)</f>
+        <v/>
+      </c>
+      <c r="E72" s="24">
+        <f>D72*$B$11</f>
+        <v/>
+      </c>
+      <c r="F72" s="24">
+        <f>IF(A72&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A72&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A72,Stage_Storage!$A$11:$A$18,1))+(A72-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A72,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A72,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A72,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A72,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A72,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G72" s="31">
+        <f>E72+F72</f>
+        <v/>
+      </c>
+      <c r="H72" s="5">
+        <f>IF(B72&lt;=0,0,IF(B72&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B72,Courbe_QH_900!$A$24:$A$84,1))+(B72-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B72,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B72,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B72,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B72,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B72,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I72" s="5">
+        <f>IF(C72&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D72*IF(($B$7+2*C72*SQRT(1+$B$9^2))&lt;=0,0,((D72/($B$7+2*C72*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J72" s="15">
+        <f>H72+I72</f>
+        <v/>
+      </c>
+      <c r="K72" s="4">
+        <f>IF(C72&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="29" t="n">
+        <v>37.78</v>
+      </c>
+      <c r="B73" s="29">
+        <f>A73-$B$12</f>
+        <v/>
+      </c>
+      <c r="C73" s="29">
+        <f>MAX(0,A73-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D73" s="5">
+        <f>IF(C73&lt;=0,0,($B$7+$B$9*C73)*C73)</f>
+        <v/>
+      </c>
+      <c r="E73" s="24">
+        <f>D73*$B$11</f>
+        <v/>
+      </c>
+      <c r="F73" s="24">
+        <f>IF(A73&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A73&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A73,Stage_Storage!$A$11:$A$18,1))+(A73-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A73,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A73,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A73,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A73,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A73,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G73" s="31">
+        <f>E73+F73</f>
+        <v/>
+      </c>
+      <c r="H73" s="5">
+        <f>IF(B73&lt;=0,0,IF(B73&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B73,Courbe_QH_900!$A$24:$A$84,1))+(B73-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B73,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B73,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B73,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B73,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B73,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I73" s="5">
+        <f>IF(C73&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D73*IF(($B$7+2*C73*SQRT(1+$B$9^2))&lt;=0,0,((D73/($B$7+2*C73*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J73" s="15">
+        <f>H73+I73</f>
+        <v/>
+      </c>
+      <c r="K73" s="4">
+        <f>IF(C73&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="29" t="n">
+        <v>37.83</v>
+      </c>
+      <c r="B74" s="29">
+        <f>A74-$B$12</f>
+        <v/>
+      </c>
+      <c r="C74" s="29">
+        <f>MAX(0,A74-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D74" s="5">
+        <f>IF(C74&lt;=0,0,($B$7+$B$9*C74)*C74)</f>
+        <v/>
+      </c>
+      <c r="E74" s="24">
+        <f>D74*$B$11</f>
+        <v/>
+      </c>
+      <c r="F74" s="24">
+        <f>IF(A74&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A74&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A74,Stage_Storage!$A$11:$A$18,1))+(A74-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A74,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A74,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A74,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A74,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A74,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G74" s="31">
+        <f>E74+F74</f>
+        <v/>
+      </c>
+      <c r="H74" s="5">
+        <f>IF(B74&lt;=0,0,IF(B74&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B74,Courbe_QH_900!$A$24:$A$84,1))+(B74-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B74,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B74,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B74,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B74,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B74,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I74" s="5">
+        <f>IF(C74&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D74*IF(($B$7+2*C74*SQRT(1+$B$9^2))&lt;=0,0,((D74/($B$7+2*C74*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J74" s="15">
+        <f>H74+I74</f>
+        <v/>
+      </c>
+      <c r="K74" s="4">
+        <f>IF(C74&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="29" t="n">
+        <v>37.88</v>
+      </c>
+      <c r="B75" s="29">
+        <f>A75-$B$12</f>
+        <v/>
+      </c>
+      <c r="C75" s="29">
+        <f>MAX(0,A75-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D75" s="5">
+        <f>IF(C75&lt;=0,0,($B$7+$B$9*C75)*C75)</f>
+        <v/>
+      </c>
+      <c r="E75" s="24">
+        <f>D75*$B$11</f>
+        <v/>
+      </c>
+      <c r="F75" s="24">
+        <f>IF(A75&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A75&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A75,Stage_Storage!$A$11:$A$18,1))+(A75-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A75,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A75,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A75,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A75,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A75,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G75" s="31">
+        <f>E75+F75</f>
+        <v/>
+      </c>
+      <c r="H75" s="5">
+        <f>IF(B75&lt;=0,0,IF(B75&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B75,Courbe_QH_900!$A$24:$A$84,1))+(B75-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B75,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B75,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B75,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B75,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B75,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I75" s="5">
+        <f>IF(C75&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D75*IF(($B$7+2*C75*SQRT(1+$B$9^2))&lt;=0,0,((D75/($B$7+2*C75*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J75" s="15">
+        <f>H75+I75</f>
+        <v/>
+      </c>
+      <c r="K75" s="4">
+        <f>IF(C75&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="29" t="n">
+        <v>37.93</v>
+      </c>
+      <c r="B76" s="29">
+        <f>A76-$B$12</f>
+        <v/>
+      </c>
+      <c r="C76" s="29">
+        <f>MAX(0,A76-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D76" s="5">
+        <f>IF(C76&lt;=0,0,($B$7+$B$9*C76)*C76)</f>
+        <v/>
+      </c>
+      <c r="E76" s="24">
+        <f>D76*$B$11</f>
+        <v/>
+      </c>
+      <c r="F76" s="24">
+        <f>IF(A76&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A76&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A76,Stage_Storage!$A$11:$A$18,1))+(A76-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A76,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A76,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A76,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A76,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A76,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G76" s="31">
+        <f>E76+F76</f>
+        <v/>
+      </c>
+      <c r="H76" s="5">
+        <f>IF(B76&lt;=0,0,IF(B76&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B76,Courbe_QH_900!$A$24:$A$84,1))+(B76-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B76,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B76,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B76,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B76,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B76,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I76" s="5">
+        <f>IF(C76&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D76*IF(($B$7+2*C76*SQRT(1+$B$9^2))&lt;=0,0,((D76/($B$7+2*C76*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J76" s="15">
+        <f>H76+I76</f>
+        <v/>
+      </c>
+      <c r="K76" s="4">
+        <f>IF(C76&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="29" t="n">
+        <v>37.98</v>
+      </c>
+      <c r="B77" s="29">
+        <f>A77-$B$12</f>
+        <v/>
+      </c>
+      <c r="C77" s="29">
+        <f>MAX(0,A77-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D77" s="5">
+        <f>IF(C77&lt;=0,0,($B$7+$B$9*C77)*C77)</f>
+        <v/>
+      </c>
+      <c r="E77" s="24">
+        <f>D77*$B$11</f>
+        <v/>
+      </c>
+      <c r="F77" s="24">
+        <f>IF(A77&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A77&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A77,Stage_Storage!$A$11:$A$18,1))+(A77-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A77,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A77,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A77,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A77,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A77,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G77" s="31">
+        <f>E77+F77</f>
+        <v/>
+      </c>
+      <c r="H77" s="5">
+        <f>IF(B77&lt;=0,0,IF(B77&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B77,Courbe_QH_900!$A$24:$A$84,1))+(B77-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B77,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B77,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B77,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B77,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B77,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I77" s="5">
+        <f>IF(C77&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D77*IF(($B$7+2*C77*SQRT(1+$B$9^2))&lt;=0,0,((D77/($B$7+2*C77*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J77" s="15">
+        <f>H77+I77</f>
+        <v/>
+      </c>
+      <c r="K77" s="4">
+        <f>IF(C77&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="29" t="n">
+        <v>38.03</v>
+      </c>
+      <c r="B78" s="29">
+        <f>A78-$B$12</f>
+        <v/>
+      </c>
+      <c r="C78" s="29">
+        <f>MAX(0,A78-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D78" s="5">
+        <f>IF(C78&lt;=0,0,($B$7+$B$9*C78)*C78)</f>
+        <v/>
+      </c>
+      <c r="E78" s="24">
+        <f>D78*$B$11</f>
+        <v/>
+      </c>
+      <c r="F78" s="24">
+        <f>IF(A78&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A78&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A78,Stage_Storage!$A$11:$A$18,1))+(A78-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A78,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A78,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A78,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A78,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A78,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G78" s="31">
+        <f>E78+F78</f>
+        <v/>
+      </c>
+      <c r="H78" s="5">
+        <f>IF(B78&lt;=0,0,IF(B78&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B78,Courbe_QH_900!$A$24:$A$84,1))+(B78-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B78,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B78,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B78,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B78,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B78,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I78" s="5">
+        <f>IF(C78&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D78*IF(($B$7+2*C78*SQRT(1+$B$9^2))&lt;=0,0,((D78/($B$7+2*C78*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J78" s="15">
+        <f>H78+I78</f>
+        <v/>
+      </c>
+      <c r="K78" s="4">
+        <f>IF(C78&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="29" t="n">
+        <v>38.08</v>
+      </c>
+      <c r="B79" s="29">
+        <f>A79-$B$12</f>
+        <v/>
+      </c>
+      <c r="C79" s="29">
+        <f>MAX(0,A79-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D79" s="5">
+        <f>IF(C79&lt;=0,0,($B$7+$B$9*C79)*C79)</f>
+        <v/>
+      </c>
+      <c r="E79" s="24">
+        <f>D79*$B$11</f>
+        <v/>
+      </c>
+      <c r="F79" s="24">
+        <f>IF(A79&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A79&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A79,Stage_Storage!$A$11:$A$18,1))+(A79-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A79,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A79,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A79,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A79,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A79,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G79" s="31">
+        <f>E79+F79</f>
+        <v/>
+      </c>
+      <c r="H79" s="5">
+        <f>IF(B79&lt;=0,0,IF(B79&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B79,Courbe_QH_900!$A$24:$A$84,1))+(B79-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B79,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B79,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B79,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B79,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B79,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I79" s="5">
+        <f>IF(C79&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D79*IF(($B$7+2*C79*SQRT(1+$B$9^2))&lt;=0,0,((D79/($B$7+2*C79*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J79" s="15">
+        <f>H79+I79</f>
+        <v/>
+      </c>
+      <c r="K79" s="4">
+        <f>IF(C79&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="29" t="n">
+        <v>38.13</v>
+      </c>
+      <c r="B80" s="29">
+        <f>A80-$B$12</f>
+        <v/>
+      </c>
+      <c r="C80" s="29">
+        <f>MAX(0,A80-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D80" s="5">
+        <f>IF(C80&lt;=0,0,($B$7+$B$9*C80)*C80)</f>
+        <v/>
+      </c>
+      <c r="E80" s="24">
+        <f>D80*$B$11</f>
+        <v/>
+      </c>
+      <c r="F80" s="24">
+        <f>IF(A80&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A80&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A80,Stage_Storage!$A$11:$A$18,1))+(A80-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A80,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A80,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A80,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A80,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A80,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G80" s="31">
+        <f>E80+F80</f>
+        <v/>
+      </c>
+      <c r="H80" s="5">
+        <f>IF(B80&lt;=0,0,IF(B80&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B80,Courbe_QH_900!$A$24:$A$84,1))+(B80-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B80,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B80,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B80,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B80,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B80,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I80" s="5">
+        <f>IF(C80&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D80*IF(($B$7+2*C80*SQRT(1+$B$9^2))&lt;=0,0,((D80/($B$7+2*C80*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J80" s="15">
+        <f>H80+I80</f>
+        <v/>
+      </c>
+      <c r="K80" s="4">
+        <f>IF(C80&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="29" t="n">
+        <v>38.18</v>
+      </c>
+      <c r="B81" s="29">
+        <f>A81-$B$12</f>
+        <v/>
+      </c>
+      <c r="C81" s="29">
+        <f>MAX(0,A81-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D81" s="5">
+        <f>IF(C81&lt;=0,0,($B$7+$B$9*C81)*C81)</f>
+        <v/>
+      </c>
+      <c r="E81" s="24">
+        <f>D81*$B$11</f>
+        <v/>
+      </c>
+      <c r="F81" s="24">
+        <f>IF(A81&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A81&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A81,Stage_Storage!$A$11:$A$18,1))+(A81-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A81,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A81,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A81,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A81,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A81,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G81" s="31">
+        <f>E81+F81</f>
+        <v/>
+      </c>
+      <c r="H81" s="5">
+        <f>IF(B81&lt;=0,0,IF(B81&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B81,Courbe_QH_900!$A$24:$A$84,1))+(B81-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B81,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B81,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B81,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B81,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B81,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I81" s="5">
+        <f>IF(C81&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D81*IF(($B$7+2*C81*SQRT(1+$B$9^2))&lt;=0,0,((D81/($B$7+2*C81*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J81" s="15">
+        <f>H81+I81</f>
+        <v/>
+      </c>
+      <c r="K81" s="4">
+        <f>IF(C81&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="29" t="n">
+        <v>38.23</v>
+      </c>
+      <c r="B82" s="29">
+        <f>A82-$B$12</f>
+        <v/>
+      </c>
+      <c r="C82" s="29">
+        <f>MAX(0,A82-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D82" s="5">
+        <f>IF(C82&lt;=0,0,($B$7+$B$9*C82)*C82)</f>
+        <v/>
+      </c>
+      <c r="E82" s="24">
+        <f>D82*$B$11</f>
+        <v/>
+      </c>
+      <c r="F82" s="24">
+        <f>IF(A82&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A82&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A82,Stage_Storage!$A$11:$A$18,1))+(A82-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A82,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A82,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A82,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A82,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A82,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G82" s="31">
+        <f>E82+F82</f>
+        <v/>
+      </c>
+      <c r="H82" s="5">
+        <f>IF(B82&lt;=0,0,IF(B82&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B82,Courbe_QH_900!$A$24:$A$84,1))+(B82-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B82,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B82,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B82,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B82,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B82,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I82" s="5">
+        <f>IF(C82&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D82*IF(($B$7+2*C82*SQRT(1+$B$9^2))&lt;=0,0,((D82/($B$7+2*C82*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J82" s="15">
+        <f>H82+I82</f>
+        <v/>
+      </c>
+      <c r="K82" s="4">
+        <f>IF(C82&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="29" t="n">
+        <v>38.28</v>
+      </c>
+      <c r="B83" s="29">
+        <f>A83-$B$12</f>
+        <v/>
+      </c>
+      <c r="C83" s="29">
+        <f>MAX(0,A83-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D83" s="5">
+        <f>IF(C83&lt;=0,0,($B$7+$B$9*C83)*C83)</f>
+        <v/>
+      </c>
+      <c r="E83" s="24">
+        <f>D83*$B$11</f>
+        <v/>
+      </c>
+      <c r="F83" s="24">
+        <f>IF(A83&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A83&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A83,Stage_Storage!$A$11:$A$18,1))+(A83-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A83,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A83,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A83,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A83,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A83,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G83" s="31">
+        <f>E83+F83</f>
+        <v/>
+      </c>
+      <c r="H83" s="5">
+        <f>IF(B83&lt;=0,0,IF(B83&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B83,Courbe_QH_900!$A$24:$A$84,1))+(B83-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B83,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B83,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B83,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B83,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B83,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I83" s="5">
+        <f>IF(C83&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D83*IF(($B$7+2*C83*SQRT(1+$B$9^2))&lt;=0,0,((D83/($B$7+2*C83*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J83" s="15">
+        <f>H83+I83</f>
+        <v/>
+      </c>
+      <c r="K83" s="4">
+        <f>IF(C83&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="29" t="n">
+        <v>38.33</v>
+      </c>
+      <c r="B84" s="29">
+        <f>A84-$B$12</f>
+        <v/>
+      </c>
+      <c r="C84" s="29">
+        <f>MAX(0,A84-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D84" s="5">
+        <f>IF(C84&lt;=0,0,($B$7+$B$9*C84)*C84)</f>
+        <v/>
+      </c>
+      <c r="E84" s="24">
+        <f>D84*$B$11</f>
+        <v/>
+      </c>
+      <c r="F84" s="24">
+        <f>IF(A84&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A84&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A84,Stage_Storage!$A$11:$A$18,1))+(A84-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A84,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A84,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A84,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A84,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A84,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G84" s="31">
+        <f>E84+F84</f>
+        <v/>
+      </c>
+      <c r="H84" s="5">
+        <f>IF(B84&lt;=0,0,IF(B84&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B84,Courbe_QH_900!$A$24:$A$84,1))+(B84-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B84,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B84,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B84,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B84,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B84,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I84" s="5">
+        <f>IF(C84&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D84*IF(($B$7+2*C84*SQRT(1+$B$9^2))&lt;=0,0,((D84/($B$7+2*C84*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J84" s="15">
+        <f>H84+I84</f>
+        <v/>
+      </c>
+      <c r="K84" s="4">
+        <f>IF(C84&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="29" t="n">
+        <v>38.38</v>
+      </c>
+      <c r="B85" s="29">
+        <f>A85-$B$12</f>
+        <v/>
+      </c>
+      <c r="C85" s="29">
+        <f>MAX(0,A85-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D85" s="5">
+        <f>IF(C85&lt;=0,0,($B$7+$B$9*C85)*C85)</f>
+        <v/>
+      </c>
+      <c r="E85" s="24">
+        <f>D85*$B$11</f>
+        <v/>
+      </c>
+      <c r="F85" s="24">
+        <f>IF(A85&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A85&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A85,Stage_Storage!$A$11:$A$18,1))+(A85-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A85,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A85,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A85,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A85,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A85,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G85" s="31">
+        <f>E85+F85</f>
+        <v/>
+      </c>
+      <c r="H85" s="5">
+        <f>IF(B85&lt;=0,0,IF(B85&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B85,Courbe_QH_900!$A$24:$A$84,1))+(B85-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B85,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B85,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B85,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B85,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B85,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I85" s="5">
+        <f>IF(C85&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D85*IF(($B$7+2*C85*SQRT(1+$B$9^2))&lt;=0,0,((D85/($B$7+2*C85*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J85" s="15">
+        <f>H85+I85</f>
+        <v/>
+      </c>
+      <c r="K85" s="4">
+        <f>IF(C85&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="29" t="n">
+        <v>38.43</v>
+      </c>
+      <c r="B86" s="29">
+        <f>A86-$B$12</f>
+        <v/>
+      </c>
+      <c r="C86" s="29">
+        <f>MAX(0,A86-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D86" s="5">
+        <f>IF(C86&lt;=0,0,($B$7+$B$9*C86)*C86)</f>
+        <v/>
+      </c>
+      <c r="E86" s="24">
+        <f>D86*$B$11</f>
+        <v/>
+      </c>
+      <c r="F86" s="24">
+        <f>IF(A86&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A86&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A86,Stage_Storage!$A$11:$A$18,1))+(A86-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A86,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A86,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A86,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A86,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A86,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G86" s="31">
+        <f>E86+F86</f>
+        <v/>
+      </c>
+      <c r="H86" s="5">
+        <f>IF(B86&lt;=0,0,IF(B86&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B86,Courbe_QH_900!$A$24:$A$84,1))+(B86-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B86,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B86,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B86,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B86,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B86,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I86" s="5">
+        <f>IF(C86&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D86*IF(($B$7+2*C86*SQRT(1+$B$9^2))&lt;=0,0,((D86/($B$7+2*C86*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J86" s="15">
+        <f>H86+I86</f>
+        <v/>
+      </c>
+      <c r="K86" s="4">
+        <f>IF(C86&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="29" t="n">
+        <v>38.48</v>
+      </c>
+      <c r="B87" s="29">
+        <f>A87-$B$12</f>
+        <v/>
+      </c>
+      <c r="C87" s="29">
+        <f>MAX(0,A87-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D87" s="5">
+        <f>IF(C87&lt;=0,0,($B$7+$B$9*C87)*C87)</f>
+        <v/>
+      </c>
+      <c r="E87" s="24">
+        <f>D87*$B$11</f>
+        <v/>
+      </c>
+      <c r="F87" s="24">
+        <f>IF(A87&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A87&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A87,Stage_Storage!$A$11:$A$18,1))+(A87-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A87,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A87,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A87,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A87,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A87,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G87" s="31">
+        <f>E87+F87</f>
+        <v/>
+      </c>
+      <c r="H87" s="5">
+        <f>IF(B87&lt;=0,0,IF(B87&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B87,Courbe_QH_900!$A$24:$A$84,1))+(B87-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B87,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B87,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B87,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B87,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B87,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I87" s="5">
+        <f>IF(C87&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D87*IF(($B$7+2*C87*SQRT(1+$B$9^2))&lt;=0,0,((D87/($B$7+2*C87*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J87" s="15">
+        <f>H87+I87</f>
+        <v/>
+      </c>
+      <c r="K87" s="4">
+        <f>IF(C87&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="29" t="n">
+        <v>38.53</v>
+      </c>
+      <c r="B88" s="29">
+        <f>A88-$B$12</f>
+        <v/>
+      </c>
+      <c r="C88" s="29">
+        <f>MAX(0,A88-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D88" s="5">
+        <f>IF(C88&lt;=0,0,($B$7+$B$9*C88)*C88)</f>
+        <v/>
+      </c>
+      <c r="E88" s="24">
+        <f>D88*$B$11</f>
+        <v/>
+      </c>
+      <c r="F88" s="24">
+        <f>IF(A88&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A88&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A88,Stage_Storage!$A$11:$A$18,1))+(A88-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A88,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A88,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A88,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A88,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A88,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G88" s="31">
+        <f>E88+F88</f>
+        <v/>
+      </c>
+      <c r="H88" s="5">
+        <f>IF(B88&lt;=0,0,IF(B88&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B88,Courbe_QH_900!$A$24:$A$84,1))+(B88-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B88,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B88,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B88,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B88,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B88,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I88" s="5">
+        <f>IF(C88&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D88*IF(($B$7+2*C88*SQRT(1+$B$9^2))&lt;=0,0,((D88/($B$7+2*C88*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J88" s="15">
+        <f>H88+I88</f>
+        <v/>
+      </c>
+      <c r="K88" s="4">
+        <f>IF(C88&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="29" t="n">
+        <v>38.58</v>
+      </c>
+      <c r="B89" s="29">
+        <f>A89-$B$12</f>
+        <v/>
+      </c>
+      <c r="C89" s="29">
+        <f>MAX(0,A89-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D89" s="5">
+        <f>IF(C89&lt;=0,0,($B$7+$B$9*C89)*C89)</f>
+        <v/>
+      </c>
+      <c r="E89" s="24">
+        <f>D89*$B$11</f>
+        <v/>
+      </c>
+      <c r="F89" s="24">
+        <f>IF(A89&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A89&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A89,Stage_Storage!$A$11:$A$18,1))+(A89-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A89,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A89,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A89,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A89,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A89,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G89" s="31">
+        <f>E89+F89</f>
+        <v/>
+      </c>
+      <c r="H89" s="5">
+        <f>IF(B89&lt;=0,0,IF(B89&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B89,Courbe_QH_900!$A$24:$A$84,1))+(B89-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B89,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B89,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B89,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B89,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B89,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I89" s="5">
+        <f>IF(C89&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D89*IF(($B$7+2*C89*SQRT(1+$B$9^2))&lt;=0,0,((D89/($B$7+2*C89*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J89" s="15">
+        <f>H89+I89</f>
+        <v/>
+      </c>
+      <c r="K89" s="4">
+        <f>IF(C89&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="29" t="n">
+        <v>38.63</v>
+      </c>
+      <c r="B90" s="29">
+        <f>A90-$B$12</f>
+        <v/>
+      </c>
+      <c r="C90" s="29">
+        <f>MAX(0,A90-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D90" s="5">
+        <f>IF(C90&lt;=0,0,($B$7+$B$9*C90)*C90)</f>
+        <v/>
+      </c>
+      <c r="E90" s="24">
+        <f>D90*$B$11</f>
+        <v/>
+      </c>
+      <c r="F90" s="24">
+        <f>IF(A90&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A90&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A90,Stage_Storage!$A$11:$A$18,1))+(A90-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A90,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A90,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A90,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A90,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A90,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G90" s="31">
+        <f>E90+F90</f>
+        <v/>
+      </c>
+      <c r="H90" s="5">
+        <f>IF(B90&lt;=0,0,IF(B90&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B90,Courbe_QH_900!$A$24:$A$84,1))+(B90-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B90,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B90,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B90,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B90,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B90,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I90" s="5">
+        <f>IF(C90&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D90*IF(($B$7+2*C90*SQRT(1+$B$9^2))&lt;=0,0,((D90/($B$7+2*C90*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J90" s="15">
+        <f>H90+I90</f>
+        <v/>
+      </c>
+      <c r="K90" s="4">
+        <f>IF(C90&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="29" t="n">
+        <v>38.68</v>
+      </c>
+      <c r="B91" s="29">
+        <f>A91-$B$12</f>
+        <v/>
+      </c>
+      <c r="C91" s="29">
+        <f>MAX(0,A91-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D91" s="5">
+        <f>IF(C91&lt;=0,0,($B$7+$B$9*C91)*C91)</f>
+        <v/>
+      </c>
+      <c r="E91" s="24">
+        <f>D91*$B$11</f>
+        <v/>
+      </c>
+      <c r="F91" s="24">
+        <f>IF(A91&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A91&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A91,Stage_Storage!$A$11:$A$18,1))+(A91-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A91,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A91,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A91,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A91,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A91,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G91" s="31">
+        <f>E91+F91</f>
+        <v/>
+      </c>
+      <c r="H91" s="5">
+        <f>IF(B91&lt;=0,0,IF(B91&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B91,Courbe_QH_900!$A$24:$A$84,1))+(B91-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B91,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B91,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B91,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B91,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B91,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I91" s="5">
+        <f>IF(C91&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D91*IF(($B$7+2*C91*SQRT(1+$B$9^2))&lt;=0,0,((D91/($B$7+2*C91*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J91" s="15">
+        <f>H91+I91</f>
+        <v/>
+      </c>
+      <c r="K91" s="4">
+        <f>IF(C91&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="29" t="n">
+        <v>38.73</v>
+      </c>
+      <c r="B92" s="29">
+        <f>A92-$B$12</f>
+        <v/>
+      </c>
+      <c r="C92" s="29">
+        <f>MAX(0,A92-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D92" s="5">
+        <f>IF(C92&lt;=0,0,($B$7+$B$9*C92)*C92)</f>
+        <v/>
+      </c>
+      <c r="E92" s="24">
+        <f>D92*$B$11</f>
+        <v/>
+      </c>
+      <c r="F92" s="24">
+        <f>IF(A92&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A92&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A92,Stage_Storage!$A$11:$A$18,1))+(A92-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A92,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A92,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A92,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A92,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A92,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G92" s="31">
+        <f>E92+F92</f>
+        <v/>
+      </c>
+      <c r="H92" s="5">
+        <f>IF(B92&lt;=0,0,IF(B92&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B92,Courbe_QH_900!$A$24:$A$84,1))+(B92-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B92,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B92,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B92,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B92,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B92,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I92" s="5">
+        <f>IF(C92&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D92*IF(($B$7+2*C92*SQRT(1+$B$9^2))&lt;=0,0,((D92/($B$7+2*C92*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J92" s="15">
+        <f>H92+I92</f>
+        <v/>
+      </c>
+      <c r="K92" s="4">
+        <f>IF(C92&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="29" t="n">
+        <v>38.78</v>
+      </c>
+      <c r="B93" s="29">
+        <f>A93-$B$12</f>
+        <v/>
+      </c>
+      <c r="C93" s="29">
+        <f>MAX(0,A93-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D93" s="5">
+        <f>IF(C93&lt;=0,0,($B$7+$B$9*C93)*C93)</f>
+        <v/>
+      </c>
+      <c r="E93" s="24">
+        <f>D93*$B$11</f>
+        <v/>
+      </c>
+      <c r="F93" s="24">
+        <f>IF(A93&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A93&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A93,Stage_Storage!$A$11:$A$18,1))+(A93-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A93,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A93,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A93,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A93,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A93,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G93" s="31">
+        <f>E93+F93</f>
+        <v/>
+      </c>
+      <c r="H93" s="5">
+        <f>IF(B93&lt;=0,0,IF(B93&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B93,Courbe_QH_900!$A$24:$A$84,1))+(B93-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B93,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B93,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B93,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B93,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B93,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I93" s="5">
+        <f>IF(C93&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D93*IF(($B$7+2*C93*SQRT(1+$B$9^2))&lt;=0,0,((D93/($B$7+2*C93*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J93" s="15">
+        <f>H93+I93</f>
+        <v/>
+      </c>
+      <c r="K93" s="4">
+        <f>IF(C93&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="29" t="n">
+        <v>38.83</v>
+      </c>
+      <c r="B94" s="29">
+        <f>A94-$B$12</f>
+        <v/>
+      </c>
+      <c r="C94" s="29">
+        <f>MAX(0,A94-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D94" s="5">
+        <f>IF(C94&lt;=0,0,($B$7+$B$9*C94)*C94)</f>
+        <v/>
+      </c>
+      <c r="E94" s="24">
+        <f>D94*$B$11</f>
+        <v/>
+      </c>
+      <c r="F94" s="24">
+        <f>IF(A94&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A94&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A94,Stage_Storage!$A$11:$A$18,1))+(A94-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A94,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A94,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A94,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A94,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A94,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G94" s="31">
+        <f>E94+F94</f>
+        <v/>
+      </c>
+      <c r="H94" s="5">
+        <f>IF(B94&lt;=0,0,IF(B94&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B94,Courbe_QH_900!$A$24:$A$84,1))+(B94-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B94,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B94,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B94,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B94,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B94,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I94" s="5">
+        <f>IF(C94&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D94*IF(($B$7+2*C94*SQRT(1+$B$9^2))&lt;=0,0,((D94/($B$7+2*C94*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J94" s="15">
+        <f>H94+I94</f>
+        <v/>
+      </c>
+      <c r="K94" s="4">
+        <f>IF(C94&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="29" t="n">
+        <v>38.88</v>
+      </c>
+      <c r="B95" s="29">
+        <f>A95-$B$12</f>
+        <v/>
+      </c>
+      <c r="C95" s="29">
+        <f>MAX(0,A95-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D95" s="5">
+        <f>IF(C95&lt;=0,0,($B$7+$B$9*C95)*C95)</f>
+        <v/>
+      </c>
+      <c r="E95" s="24">
+        <f>D95*$B$11</f>
+        <v/>
+      </c>
+      <c r="F95" s="24">
+        <f>IF(A95&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A95&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A95,Stage_Storage!$A$11:$A$18,1))+(A95-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A95,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A95,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A95,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A95,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A95,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G95" s="31">
+        <f>E95+F95</f>
+        <v/>
+      </c>
+      <c r="H95" s="5">
+        <f>IF(B95&lt;=0,0,IF(B95&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B95,Courbe_QH_900!$A$24:$A$84,1))+(B95-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B95,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B95,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B95,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B95,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B95,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I95" s="5">
+        <f>IF(C95&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D95*IF(($B$7+2*C95*SQRT(1+$B$9^2))&lt;=0,0,((D95/($B$7+2*C95*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J95" s="15">
+        <f>H95+I95</f>
+        <v/>
+      </c>
+      <c r="K95" s="4">
+        <f>IF(C95&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="29" t="n">
+        <v>38.93</v>
+      </c>
+      <c r="B96" s="29">
+        <f>A96-$B$12</f>
+        <v/>
+      </c>
+      <c r="C96" s="29">
+        <f>MAX(0,A96-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D96" s="5">
+        <f>IF(C96&lt;=0,0,($B$7+$B$9*C96)*C96)</f>
+        <v/>
+      </c>
+      <c r="E96" s="24">
+        <f>D96*$B$11</f>
+        <v/>
+      </c>
+      <c r="F96" s="24">
+        <f>IF(A96&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A96&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A96,Stage_Storage!$A$11:$A$18,1))+(A96-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A96,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A96,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A96,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A96,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A96,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G96" s="31">
+        <f>E96+F96</f>
+        <v/>
+      </c>
+      <c r="H96" s="5">
+        <f>IF(B96&lt;=0,0,IF(B96&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B96,Courbe_QH_900!$A$24:$A$84,1))+(B96-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B96,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B96,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B96,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B96,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B96,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I96" s="5">
+        <f>IF(C96&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D96*IF(($B$7+2*C96*SQRT(1+$B$9^2))&lt;=0,0,((D96/($B$7+2*C96*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J96" s="15">
+        <f>H96+I96</f>
+        <v/>
+      </c>
+      <c r="K96" s="4">
+        <f>IF(C96&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="29" t="n">
+        <v>38.98</v>
+      </c>
+      <c r="B97" s="29">
+        <f>A97-$B$12</f>
+        <v/>
+      </c>
+      <c r="C97" s="29">
+        <f>MAX(0,A97-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D97" s="5">
+        <f>IF(C97&lt;=0,0,($B$7+$B$9*C97)*C97)</f>
+        <v/>
+      </c>
+      <c r="E97" s="24">
+        <f>D97*$B$11</f>
+        <v/>
+      </c>
+      <c r="F97" s="24">
+        <f>IF(A97&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A97&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A97,Stage_Storage!$A$11:$A$18,1))+(A97-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A97,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A97,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A97,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A97,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A97,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G97" s="31">
+        <f>E97+F97</f>
+        <v/>
+      </c>
+      <c r="H97" s="5">
+        <f>IF(B97&lt;=0,0,IF(B97&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B97,Courbe_QH_900!$A$24:$A$84,1))+(B97-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B97,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B97,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B97,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B97,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B97,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I97" s="5">
+        <f>IF(C97&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D97*IF(($B$7+2*C97*SQRT(1+$B$9^2))&lt;=0,0,((D97/($B$7+2*C97*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J97" s="15">
+        <f>H97+I97</f>
+        <v/>
+      </c>
+      <c r="K97" s="4">
+        <f>IF(C97&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="29" t="n">
+        <v>39.03</v>
+      </c>
+      <c r="B98" s="29">
+        <f>A98-$B$12</f>
+        <v/>
+      </c>
+      <c r="C98" s="29">
+        <f>MAX(0,A98-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D98" s="5">
+        <f>IF(C98&lt;=0,0,($B$7+$B$9*C98)*C98)</f>
+        <v/>
+      </c>
+      <c r="E98" s="24">
+        <f>D98*$B$11</f>
+        <v/>
+      </c>
+      <c r="F98" s="24">
+        <f>IF(A98&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A98&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A98,Stage_Storage!$A$11:$A$18,1))+(A98-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A98,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A98,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A98,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A98,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A98,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G98" s="31">
+        <f>E98+F98</f>
+        <v/>
+      </c>
+      <c r="H98" s="5">
+        <f>IF(B98&lt;=0,0,IF(B98&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B98,Courbe_QH_900!$A$24:$A$84,1))+(B98-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B98,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B98,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B98,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B98,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B98,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I98" s="5">
+        <f>IF(C98&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D98*IF(($B$7+2*C98*SQRT(1+$B$9^2))&lt;=0,0,((D98/($B$7+2*C98*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J98" s="15">
+        <f>H98+I98</f>
+        <v/>
+      </c>
+      <c r="K98" s="4">
+        <f>IF(C98&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="29" t="n">
+        <v>39.08</v>
+      </c>
+      <c r="B99" s="29">
+        <f>A99-$B$12</f>
+        <v/>
+      </c>
+      <c r="C99" s="29">
+        <f>MAX(0,A99-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D99" s="5">
+        <f>IF(C99&lt;=0,0,($B$7+$B$9*C99)*C99)</f>
+        <v/>
+      </c>
+      <c r="E99" s="24">
+        <f>D99*$B$11</f>
+        <v/>
+      </c>
+      <c r="F99" s="24">
+        <f>IF(A99&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A99&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A99,Stage_Storage!$A$11:$A$18,1))+(A99-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A99,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A99,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A99,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A99,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A99,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G99" s="31">
+        <f>E99+F99</f>
+        <v/>
+      </c>
+      <c r="H99" s="5">
+        <f>IF(B99&lt;=0,0,IF(B99&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B99,Courbe_QH_900!$A$24:$A$84,1))+(B99-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B99,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B99,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B99,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B99,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B99,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I99" s="5">
+        <f>IF(C99&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D99*IF(($B$7+2*C99*SQRT(1+$B$9^2))&lt;=0,0,((D99/($B$7+2*C99*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J99" s="15">
+        <f>H99+I99</f>
+        <v/>
+      </c>
+      <c r="K99" s="4">
+        <f>IF(C99&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="29" t="n">
+        <v>39.13</v>
+      </c>
+      <c r="B100" s="29">
+        <f>A100-$B$12</f>
+        <v/>
+      </c>
+      <c r="C100" s="29">
+        <f>MAX(0,A100-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D100" s="5">
+        <f>IF(C100&lt;=0,0,($B$7+$B$9*C100)*C100)</f>
+        <v/>
+      </c>
+      <c r="E100" s="24">
+        <f>D100*$B$11</f>
+        <v/>
+      </c>
+      <c r="F100" s="24">
+        <f>IF(A100&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A100&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A100,Stage_Storage!$A$11:$A$18,1))+(A100-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A100,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A100,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A100,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A100,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A100,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G100" s="31">
+        <f>E100+F100</f>
+        <v/>
+      </c>
+      <c r="H100" s="5">
+        <f>IF(B100&lt;=0,0,IF(B100&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B100,Courbe_QH_900!$A$24:$A$84,1))+(B100-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B100,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B100,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B100,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B100,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B100,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I100" s="5">
+        <f>IF(C100&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D100*IF(($B$7+2*C100*SQRT(1+$B$9^2))&lt;=0,0,((D100/($B$7+2*C100*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J100" s="15">
+        <f>H100+I100</f>
+        <v/>
+      </c>
+      <c r="K100" s="4">
+        <f>IF(C100&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="29" t="n">
+        <v>39.18</v>
+      </c>
+      <c r="B101" s="29">
+        <f>A101-$B$12</f>
+        <v/>
+      </c>
+      <c r="C101" s="29">
+        <f>MAX(0,A101-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D101" s="5">
+        <f>IF(C101&lt;=0,0,($B$7+$B$9*C101)*C101)</f>
+        <v/>
+      </c>
+      <c r="E101" s="24">
+        <f>D101*$B$11</f>
+        <v/>
+      </c>
+      <c r="F101" s="24">
+        <f>IF(A101&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A101&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A101,Stage_Storage!$A$11:$A$18,1))+(A101-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A101,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A101,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A101,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A101,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A101,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G101" s="31">
+        <f>E101+F101</f>
+        <v/>
+      </c>
+      <c r="H101" s="5">
+        <f>IF(B101&lt;=0,0,IF(B101&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B101,Courbe_QH_900!$A$24:$A$84,1))+(B101-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B101,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B101,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B101,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B101,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B101,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I101" s="5">
+        <f>IF(C101&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D101*IF(($B$7+2*C101*SQRT(1+$B$9^2))&lt;=0,0,((D101/($B$7+2*C101*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J101" s="15">
+        <f>H101+I101</f>
+        <v/>
+      </c>
+      <c r="K101" s="4">
+        <f>IF(C101&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="29" t="n">
+        <v>39.23</v>
+      </c>
+      <c r="B102" s="29">
+        <f>A102-$B$12</f>
+        <v/>
+      </c>
+      <c r="C102" s="29">
+        <f>MAX(0,A102-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D102" s="5">
+        <f>IF(C102&lt;=0,0,($B$7+$B$9*C102)*C102)</f>
+        <v/>
+      </c>
+      <c r="E102" s="24">
+        <f>D102*$B$11</f>
+        <v/>
+      </c>
+      <c r="F102" s="24">
+        <f>IF(A102&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A102&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A102,Stage_Storage!$A$11:$A$18,1))+(A102-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A102,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A102,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A102,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A102,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A102,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G102" s="31">
+        <f>E102+F102</f>
+        <v/>
+      </c>
+      <c r="H102" s="5">
+        <f>IF(B102&lt;=0,0,IF(B102&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B102,Courbe_QH_900!$A$24:$A$84,1))+(B102-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B102,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B102,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B102,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B102,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B102,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I102" s="5">
+        <f>IF(C102&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D102*IF(($B$7+2*C102*SQRT(1+$B$9^2))&lt;=0,0,((D102/($B$7+2*C102*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J102" s="15">
+        <f>H102+I102</f>
+        <v/>
+      </c>
+      <c r="K102" s="4">
+        <f>IF(C102&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="29" t="n">
+        <v>39.28</v>
+      </c>
+      <c r="B103" s="29">
+        <f>A103-$B$12</f>
+        <v/>
+      </c>
+      <c r="C103" s="29">
+        <f>MAX(0,A103-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D103" s="5">
+        <f>IF(C103&lt;=0,0,($B$7+$B$9*C103)*C103)</f>
+        <v/>
+      </c>
+      <c r="E103" s="24">
+        <f>D103*$B$11</f>
+        <v/>
+      </c>
+      <c r="F103" s="24">
+        <f>IF(A103&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A103&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A103,Stage_Storage!$A$11:$A$18,1))+(A103-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A103,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A103,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A103,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A103,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A103,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G103" s="31">
+        <f>E103+F103</f>
+        <v/>
+      </c>
+      <c r="H103" s="5">
+        <f>IF(B103&lt;=0,0,IF(B103&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B103,Courbe_QH_900!$A$24:$A$84,1))+(B103-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B103,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B103,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B103,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B103,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B103,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I103" s="5">
+        <f>IF(C103&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D103*IF(($B$7+2*C103*SQRT(1+$B$9^2))&lt;=0,0,((D103/($B$7+2*C103*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J103" s="15">
+        <f>H103+I103</f>
+        <v/>
+      </c>
+      <c r="K103" s="4">
+        <f>IF(C103&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="29" t="n">
+        <v>39.33</v>
+      </c>
+      <c r="B104" s="29">
+        <f>A104-$B$12</f>
+        <v/>
+      </c>
+      <c r="C104" s="29">
+        <f>MAX(0,A104-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D104" s="5">
+        <f>IF(C104&lt;=0,0,($B$7+$B$9*C104)*C104)</f>
+        <v/>
+      </c>
+      <c r="E104" s="24">
+        <f>D104*$B$11</f>
+        <v/>
+      </c>
+      <c r="F104" s="24">
+        <f>IF(A104&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A104&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A104,Stage_Storage!$A$11:$A$18,1))+(A104-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A104,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A104,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A104,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A104,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A104,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G104" s="31">
+        <f>E104+F104</f>
+        <v/>
+      </c>
+      <c r="H104" s="5">
+        <f>IF(B104&lt;=0,0,IF(B104&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B104,Courbe_QH_900!$A$24:$A$84,1))+(B104-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B104,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B104,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B104,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B104,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B104,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I104" s="5">
+        <f>IF(C104&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D104*IF(($B$7+2*C104*SQRT(1+$B$9^2))&lt;=0,0,((D104/($B$7+2*C104*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J104" s="15">
+        <f>H104+I104</f>
+        <v/>
+      </c>
+      <c r="K104" s="4">
+        <f>IF(C104&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="29" t="n">
+        <v>39.38</v>
+      </c>
+      <c r="B105" s="29">
+        <f>A105-$B$12</f>
+        <v/>
+      </c>
+      <c r="C105" s="29">
+        <f>MAX(0,A105-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D105" s="5">
+        <f>IF(C105&lt;=0,0,($B$7+$B$9*C105)*C105)</f>
+        <v/>
+      </c>
+      <c r="E105" s="24">
+        <f>D105*$B$11</f>
+        <v/>
+      </c>
+      <c r="F105" s="24">
+        <f>IF(A105&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A105&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A105,Stage_Storage!$A$11:$A$18,1))+(A105-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A105,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A105,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A105,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A105,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A105,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G105" s="31">
+        <f>E105+F105</f>
+        <v/>
+      </c>
+      <c r="H105" s="5">
+        <f>IF(B105&lt;=0,0,IF(B105&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B105,Courbe_QH_900!$A$24:$A$84,1))+(B105-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B105,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B105,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B105,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B105,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B105,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I105" s="5">
+        <f>IF(C105&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D105*IF(($B$7+2*C105*SQRT(1+$B$9^2))&lt;=0,0,((D105/($B$7+2*C105*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J105" s="15">
+        <f>H105+I105</f>
+        <v/>
+      </c>
+      <c r="K105" s="4">
+        <f>IF(C105&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="29" t="n">
+        <v>39.43</v>
+      </c>
+      <c r="B106" s="29">
+        <f>A106-$B$12</f>
+        <v/>
+      </c>
+      <c r="C106" s="29">
+        <f>MAX(0,A106-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D106" s="5">
+        <f>IF(C106&lt;=0,0,($B$7+$B$9*C106)*C106)</f>
+        <v/>
+      </c>
+      <c r="E106" s="24">
+        <f>D106*$B$11</f>
+        <v/>
+      </c>
+      <c r="F106" s="24">
+        <f>IF(A106&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A106&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A106,Stage_Storage!$A$11:$A$18,1))+(A106-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A106,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A106,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A106,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A106,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A106,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G106" s="31">
+        <f>E106+F106</f>
+        <v/>
+      </c>
+      <c r="H106" s="5">
+        <f>IF(B106&lt;=0,0,IF(B106&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B106,Courbe_QH_900!$A$24:$A$84,1))+(B106-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B106,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B106,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B106,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B106,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B106,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I106" s="5">
+        <f>IF(C106&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D106*IF(($B$7+2*C106*SQRT(1+$B$9^2))&lt;=0,0,((D106/($B$7+2*C106*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J106" s="15">
+        <f>H106+I106</f>
+        <v/>
+      </c>
+      <c r="K106" s="4">
+        <f>IF(C106&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="29" t="n">
+        <v>39.48</v>
+      </c>
+      <c r="B107" s="29">
+        <f>A107-$B$12</f>
+        <v/>
+      </c>
+      <c r="C107" s="29">
+        <f>MAX(0,A107-$B$6)</f>
+        <v/>
+      </c>
+      <c r="D107" s="5">
+        <f>IF(C107&lt;=0,0,($B$7+$B$9*C107)*C107)</f>
+        <v/>
+      </c>
+      <c r="E107" s="24">
+        <f>D107*$B$11</f>
+        <v/>
+      </c>
+      <c r="F107" s="24">
+        <f>IF(A107&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A107&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A107,Stage_Storage!$A$11:$A$18,1))+(A107-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A107,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A107,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A107,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A107,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A107,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G107" s="31">
+        <f>E107+F107</f>
+        <v/>
+      </c>
+      <c r="H107" s="5">
+        <f>IF(B107&lt;=0,0,IF(B107&gt;=INDEX(Courbe_QH_900!$A$24:$A$84,ROWS(Courbe_QH_900!$A$24:$A$84)),INDEX(Courbe_QH_900!$E$24:$E$84,ROWS(Courbe_QH_900!$E$24:$E$84)),INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B107,Courbe_QH_900!$A$24:$A$84,1))+(B107-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B107,Courbe_QH_900!$A$24:$A$84,1)))/(INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B107,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$A$24:$A$84,MATCH(B107,Courbe_QH_900!$A$24:$A$84,1)))*(INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B107,Courbe_QH_900!$A$24:$A$84,1)+1)-INDEX(Courbe_QH_900!$E$24:$E$84,MATCH(B107,Courbe_QH_900!$A$24:$A$84,1)))))</f>
+        <v/>
+      </c>
+      <c r="I107" s="5">
+        <f>IF(C107&lt;=0,0,IF($B$8&lt;=0,0,(1/$B$8)*D107*IF(($B$7+2*C107*SQRT(1+$B$9^2))&lt;=0,0,((D107/($B$7+2*C107*SQRT(1+$B$9^2)))^(2/3)))*SQRT($B$10)))</f>
+        <v/>
+      </c>
+      <c r="J107" s="15">
+        <f>H107+I107</f>
+        <v/>
+      </c>
+      <c r="K107" s="4">
+        <f>IF(C107&gt;0,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A2:G4"/>
-    <mergeCell ref="A28:F30"/>
-    <mergeCell ref="A7:F7"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:L3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5663,129 +10149,518 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="41" t="inlineStr">
-        <is>
-          <t>Où sont les fichiers HY-8 / capacité ?</t>
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>Méthode C — routage avec Qout composé + V = V_pond + V_ditch</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Ce classeur (rétention Ø900) :</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  engineering/drainage-design/retention_volume/Volume_Retention_Ponceau_900.xlsx</t>
-        </is>
-      </c>
-    </row>
+      <c r="A2" s="37" t="inlineStr">
+        <is>
+          <t>À chaque pas: WSE lu sur Compose_900!V_total → Qout sur Compose_900. ΔV = (Qin_moy − Qout)×Δt. Si V≈0, Qout = MIN(Qin, Q_plein).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Q_plein réf. (m³/s)</t>
+        </is>
+      </c>
+      <c r="B5" s="38">
+        <f>Parametres!B22</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Courbe Q=f(H) FHWA pour CE Ø900 : feuille Courbe_QH_900 (ci-dessus).</t>
-        </is>
+          <t>Crest (m)</t>
+        </is>
+      </c>
+      <c r="B6" s="38">
+        <f>Parametres!B27</f>
+        <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Vmax_C (m³)</t>
+        </is>
+      </c>
+      <c r="B7" s="28">
+        <f>MAX(F12:F24)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ancien Excel « type HY-8 / inlet-outlet » (autre projet / Ste-Thérèse) :</t>
-        </is>
+          <t>WSEmax_C (m)</t>
+        </is>
+      </c>
+      <c r="B8" s="21">
+        <f>MAX(C12:C24)</f>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  engineering/drainage-design/Ponceau_Capacite_Inlet_Outlet.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Branche git: cursor/culvert-excel-capacity-model-d87f</t>
-        </is>
+          <t>Overflow atteint?</t>
+        </is>
+      </c>
+      <c r="B9">
+        <f>IF(B8&gt;$B$6,"oui — WSE &gt; crest","non — pipe seul")</f>
+        <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>t (min)</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Qin</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>WSE (m)</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Qout</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Δt (s)</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>V (m³)</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Overflow?</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Modèle composé ponceau Ø1050 + fossé (FHWA + remblai) — PAS le Ø900 de rétention :</t>
+      <c r="A12" s="4">
+        <f>Hydrogramme!A8</f>
+        <v/>
+      </c>
+      <c r="B12" s="5">
+        <f>Hydrogramme!C8</f>
+        <v/>
+      </c>
+      <c r="C12" s="5">
+        <f>34.88</f>
+        <v/>
+      </c>
+      <c r="D12" s="5">
+        <f>MIN(B12,$B$5)</f>
+        <v/>
+      </c>
+      <c r="E12" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>non</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  engineering/drainage-design/ponceau_fosse_model/Ponceau_Fosse_Modele_Hydraulique.xlsx</t>
-        </is>
+      <c r="A13" s="4">
+        <f>Hydrogramme!A9</f>
+        <v/>
+      </c>
+      <c r="B13" s="5">
+        <f>Hydrogramme!C9</f>
+        <v/>
+      </c>
+      <c r="C13" s="5">
+        <f>IF(F12&lt;=INDEX(Compose_900!$G$15:$G$107,1),INDEX(Compose_900!$A$15:$A$107,1),IF(F12&gt;=INDEX(Compose_900!$G$15:$G$107,ROWS(Compose_900!$G$15:$G$107)),INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$A$15:$A$107,MATCH(F12,Compose_900!$G$15:$G$107,1))+(F12-INDEX(Compose_900!$G$15:$G$107,MATCH(F12,Compose_900!$G$15:$G$107,1)))/(INDEX(Compose_900!$G$15:$G$107,MATCH(F12,Compose_900!$G$15:$G$107,1)+1)-INDEX(Compose_900!$G$15:$G$107,MATCH(F12,Compose_900!$G$15:$G$107,1)))*(INDEX(Compose_900!$A$15:$A$107,MATCH(F12,Compose_900!$G$15:$G$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(F12,Compose_900!$G$15:$G$107,1)))))</f>
+        <v/>
+      </c>
+      <c r="D13" s="5">
+        <f>IF(F12&lt;=0.01,MIN(0.5*(B12+B13),$B$5),IF(C13&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C13&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C13,Compose_900!$A$15:$A$107,1))+(C13-INDEX(Compose_900!$A$15:$A$107,MATCH(C13,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C13,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C13,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C13,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C13,Compose_900!$A$15:$A$107,1))))))</f>
+        <v/>
+      </c>
+      <c r="E13" s="24">
+        <f>(A13-A12)*60</f>
+        <v/>
+      </c>
+      <c r="F13" s="31">
+        <f>MAX(0,F12+(0.5*(B12+B13)-D13)*E13)</f>
+        <v/>
+      </c>
+      <c r="G13" s="4">
+        <f>IF(C13&gt;$B$6,"oui","non")</f>
+        <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Branche git: cursor/ponceau-fosse-hydraulic-model-d87f</t>
-        </is>
+      <c r="A14" s="4">
+        <f>Hydrogramme!A10</f>
+        <v/>
+      </c>
+      <c r="B14" s="5">
+        <f>Hydrogramme!C10</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IF(F13&lt;=INDEX(Compose_900!$G$15:$G$107,1),INDEX(Compose_900!$A$15:$A$107,1),IF(F13&gt;=INDEX(Compose_900!$G$15:$G$107,ROWS(Compose_900!$G$15:$G$107)),INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$A$15:$A$107,MATCH(F13,Compose_900!$G$15:$G$107,1))+(F13-INDEX(Compose_900!$G$15:$G$107,MATCH(F13,Compose_900!$G$15:$G$107,1)))/(INDEX(Compose_900!$G$15:$G$107,MATCH(F13,Compose_900!$G$15:$G$107,1)+1)-INDEX(Compose_900!$G$15:$G$107,MATCH(F13,Compose_900!$G$15:$G$107,1)))*(INDEX(Compose_900!$A$15:$A$107,MATCH(F13,Compose_900!$G$15:$G$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(F13,Compose_900!$G$15:$G$107,1)))))</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IF(F13&lt;=0.01,MIN(0.5*(B13+B14),$B$5),IF(C14&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C14&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C14,Compose_900!$A$15:$A$107,1))+(C14-INDEX(Compose_900!$A$15:$A$107,MATCH(C14,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C14,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C14,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C14,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C14,Compose_900!$A$15:$A$107,1))))))</f>
+        <v/>
+      </c>
+      <c r="E14" s="24">
+        <f>(A14-A13)*60</f>
+        <v/>
+      </c>
+      <c r="F14" s="31">
+        <f>MAX(0,F13+(0.5*(B13+B14)-D14)*E14)</f>
+        <v/>
+      </c>
+      <c r="G14" s="4">
+        <f>IF(C14&gt;$B$6,"oui","non")</f>
+        <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" s="4">
+        <f>Hydrogramme!A11</f>
+        <v/>
+      </c>
+      <c r="B15" s="5">
+        <f>Hydrogramme!C11</f>
+        <v/>
+      </c>
+      <c r="C15" s="5">
+        <f>IF(F14&lt;=INDEX(Compose_900!$G$15:$G$107,1),INDEX(Compose_900!$A$15:$A$107,1),IF(F14&gt;=INDEX(Compose_900!$G$15:$G$107,ROWS(Compose_900!$G$15:$G$107)),INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$A$15:$A$107,MATCH(F14,Compose_900!$G$15:$G$107,1))+(F14-INDEX(Compose_900!$G$15:$G$107,MATCH(F14,Compose_900!$G$15:$G$107,1)))/(INDEX(Compose_900!$G$15:$G$107,MATCH(F14,Compose_900!$G$15:$G$107,1)+1)-INDEX(Compose_900!$G$15:$G$107,MATCH(F14,Compose_900!$G$15:$G$107,1)))*(INDEX(Compose_900!$A$15:$A$107,MATCH(F14,Compose_900!$G$15:$G$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(F14,Compose_900!$G$15:$G$107,1)))))</f>
+        <v/>
+      </c>
+      <c r="D15" s="5">
+        <f>IF(F14&lt;=0.01,MIN(0.5*(B14+B15),$B$5),IF(C15&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C15&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C15,Compose_900!$A$15:$A$107,1))+(C15-INDEX(Compose_900!$A$15:$A$107,MATCH(C15,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C15,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C15,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C15,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C15,Compose_900!$A$15:$A$107,1))))))</f>
+        <v/>
+      </c>
+      <c r="E15" s="24">
+        <f>(A15-A14)*60</f>
+        <v/>
+      </c>
+      <c r="F15" s="31">
+        <f>MAX(0,F14+(0.5*(B14+B15)-D15)*E15)</f>
+        <v/>
+      </c>
+      <c r="G15" s="4">
+        <f>IF(C15&gt;$B$6,"oui","non")</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>HEC-RAS : pas de projet .ras/.hdf pour ce Ø900. Un DEM Ste-Thérèse est dans</t>
-        </is>
+      <c r="A16" s="4">
+        <f>Hydrogramme!A12</f>
+        <v/>
+      </c>
+      <c r="B16" s="5">
+        <f>Hydrogramme!C12</f>
+        <v/>
+      </c>
+      <c r="C16" s="5">
+        <f>IF(F15&lt;=INDEX(Compose_900!$G$15:$G$107,1),INDEX(Compose_900!$A$15:$A$107,1),IF(F15&gt;=INDEX(Compose_900!$G$15:$G$107,ROWS(Compose_900!$G$15:$G$107)),INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$A$15:$A$107,MATCH(F15,Compose_900!$G$15:$G$107,1))+(F15-INDEX(Compose_900!$G$15:$G$107,MATCH(F15,Compose_900!$G$15:$G$107,1)))/(INDEX(Compose_900!$G$15:$G$107,MATCH(F15,Compose_900!$G$15:$G$107,1)+1)-INDEX(Compose_900!$G$15:$G$107,MATCH(F15,Compose_900!$G$15:$G$107,1)))*(INDEX(Compose_900!$A$15:$A$107,MATCH(F15,Compose_900!$G$15:$G$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(F15,Compose_900!$G$15:$G$107,1)))))</f>
+        <v/>
+      </c>
+      <c r="D16" s="5">
+        <f>IF(F15&lt;=0.01,MIN(0.5*(B15+B16),$B$5),IF(C16&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C16&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C16,Compose_900!$A$15:$A$107,1))+(C16-INDEX(Compose_900!$A$15:$A$107,MATCH(C16,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C16,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C16,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C16,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C16,Compose_900!$A$15:$A$107,1))))))</f>
+        <v/>
+      </c>
+      <c r="E16" s="24">
+        <f>(A16-A15)*60</f>
+        <v/>
+      </c>
+      <c r="F16" s="31">
+        <f>MAX(0,F15+(0.5*(B15+B16)-D16)*E16)</f>
+        <v/>
+      </c>
+      <c r="G16" s="4">
+        <f>IF(C16&gt;$B$6,"oui","non")</f>
+        <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  engineering/hec-ras-data/ (données topo seulement).</t>
-        </is>
+      <c r="A17" s="4">
+        <f>Hydrogramme!A13</f>
+        <v/>
+      </c>
+      <c r="B17" s="5">
+        <f>Hydrogramme!C13</f>
+        <v/>
+      </c>
+      <c r="C17" s="5">
+        <f>IF(F16&lt;=INDEX(Compose_900!$G$15:$G$107,1),INDEX(Compose_900!$A$15:$A$107,1),IF(F16&gt;=INDEX(Compose_900!$G$15:$G$107,ROWS(Compose_900!$G$15:$G$107)),INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$A$15:$A$107,MATCH(F16,Compose_900!$G$15:$G$107,1))+(F16-INDEX(Compose_900!$G$15:$G$107,MATCH(F16,Compose_900!$G$15:$G$107,1)))/(INDEX(Compose_900!$G$15:$G$107,MATCH(F16,Compose_900!$G$15:$G$107,1)+1)-INDEX(Compose_900!$G$15:$G$107,MATCH(F16,Compose_900!$G$15:$G$107,1)))*(INDEX(Compose_900!$A$15:$A$107,MATCH(F16,Compose_900!$G$15:$G$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(F16,Compose_900!$G$15:$G$107,1)))))</f>
+        <v/>
+      </c>
+      <c r="D17" s="5">
+        <f>IF(F16&lt;=0.01,MIN(0.5*(B16+B17),$B$5),IF(C17&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C17&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C17,Compose_900!$A$15:$A$107,1))+(C17-INDEX(Compose_900!$A$15:$A$107,MATCH(C17,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C17,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C17,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C17,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C17,Compose_900!$A$15:$A$107,1))))))</f>
+        <v/>
+      </c>
+      <c r="E17" s="24">
+        <f>(A17-A16)*60</f>
+        <v/>
+      </c>
+      <c r="F17" s="31">
+        <f>MAX(0,F16+(0.5*(B16+B17)-D17)*E17)</f>
+        <v/>
+      </c>
+      <c r="G17" s="4">
+        <f>IF(C17&gt;$B$6,"oui","non")</f>
+        <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" s="4">
+        <f>Hydrogramme!A14</f>
+        <v/>
+      </c>
+      <c r="B18" s="5">
+        <f>Hydrogramme!C14</f>
+        <v/>
+      </c>
+      <c r="C18" s="5">
+        <f>IF(F17&lt;=INDEX(Compose_900!$G$15:$G$107,1),INDEX(Compose_900!$A$15:$A$107,1),IF(F17&gt;=INDEX(Compose_900!$G$15:$G$107,ROWS(Compose_900!$G$15:$G$107)),INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$A$15:$A$107,MATCH(F17,Compose_900!$G$15:$G$107,1))+(F17-INDEX(Compose_900!$G$15:$G$107,MATCH(F17,Compose_900!$G$15:$G$107,1)))/(INDEX(Compose_900!$G$15:$G$107,MATCH(F17,Compose_900!$G$15:$G$107,1)+1)-INDEX(Compose_900!$G$15:$G$107,MATCH(F17,Compose_900!$G$15:$G$107,1)))*(INDEX(Compose_900!$A$15:$A$107,MATCH(F17,Compose_900!$G$15:$G$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(F17,Compose_900!$G$15:$G$107,1)))))</f>
+        <v/>
+      </c>
+      <c r="D18" s="5">
+        <f>IF(F17&lt;=0.01,MIN(0.5*(B17+B18),$B$5),IF(C18&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C18&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C18,Compose_900!$A$15:$A$107,1))+(C18-INDEX(Compose_900!$A$15:$A$107,MATCH(C18,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C18,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C18,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C18,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C18,Compose_900!$A$15:$A$107,1))))))</f>
+        <v/>
+      </c>
+      <c r="E18" s="24">
+        <f>(A18-A17)*60</f>
+        <v/>
+      </c>
+      <c r="F18" s="31">
+        <f>MAX(0,F17+(0.5*(B17+B18)-D18)*E18)</f>
+        <v/>
+      </c>
+      <c r="G18" s="4">
+        <f>IF(C18&gt;$B$6,"oui","non")</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Donc: on n'avait pas perdu un HY-8 pour ce bassin Ø900 — on avait des outils</t>
-        </is>
+      <c r="A19" s="4">
+        <f>Hydrogramme!A15</f>
+        <v/>
+      </c>
+      <c r="B19" s="5">
+        <f>Hydrogramme!C15</f>
+        <v/>
+      </c>
+      <c r="C19" s="5">
+        <f>IF(F18&lt;=INDEX(Compose_900!$G$15:$G$107,1),INDEX(Compose_900!$A$15:$A$107,1),IF(F18&gt;=INDEX(Compose_900!$G$15:$G$107,ROWS(Compose_900!$G$15:$G$107)),INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$A$15:$A$107,MATCH(F18,Compose_900!$G$15:$G$107,1))+(F18-INDEX(Compose_900!$G$15:$G$107,MATCH(F18,Compose_900!$G$15:$G$107,1)))/(INDEX(Compose_900!$G$15:$G$107,MATCH(F18,Compose_900!$G$15:$G$107,1)+1)-INDEX(Compose_900!$G$15:$G$107,MATCH(F18,Compose_900!$G$15:$G$107,1)))*(INDEX(Compose_900!$A$15:$A$107,MATCH(F18,Compose_900!$G$15:$G$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(F18,Compose_900!$G$15:$G$107,1)))))</f>
+        <v/>
+      </c>
+      <c r="D19" s="5">
+        <f>IF(F18&lt;=0.01,MIN(0.5*(B18+B19),$B$5),IF(C19&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C19&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C19,Compose_900!$A$15:$A$107,1))+(C19-INDEX(Compose_900!$A$15:$A$107,MATCH(C19,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C19,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C19,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C19,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C19,Compose_900!$A$15:$A$107,1))))))</f>
+        <v/>
+      </c>
+      <c r="E19" s="24">
+        <f>(A19-A18)*60</f>
+        <v/>
+      </c>
+      <c r="F19" s="31">
+        <f>MAX(0,F18+(0.5*(B18+B19)-D19)*E19)</f>
+        <v/>
+      </c>
+      <c r="G19" s="4">
+        <f>IF(C19&gt;$B$6,"oui","non")</f>
+        <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>similaires pour d'autres sites. La courbe de CE classeur remplace ça pour le Ø900.</t>
-        </is>
+      <c r="A20" s="4">
+        <f>Hydrogramme!A16</f>
+        <v/>
+      </c>
+      <c r="B20" s="5">
+        <f>Hydrogramme!C16</f>
+        <v/>
+      </c>
+      <c r="C20" s="5">
+        <f>IF(F19&lt;=INDEX(Compose_900!$G$15:$G$107,1),INDEX(Compose_900!$A$15:$A$107,1),IF(F19&gt;=INDEX(Compose_900!$G$15:$G$107,ROWS(Compose_900!$G$15:$G$107)),INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$A$15:$A$107,MATCH(F19,Compose_900!$G$15:$G$107,1))+(F19-INDEX(Compose_900!$G$15:$G$107,MATCH(F19,Compose_900!$G$15:$G$107,1)))/(INDEX(Compose_900!$G$15:$G$107,MATCH(F19,Compose_900!$G$15:$G$107,1)+1)-INDEX(Compose_900!$G$15:$G$107,MATCH(F19,Compose_900!$G$15:$G$107,1)))*(INDEX(Compose_900!$A$15:$A$107,MATCH(F19,Compose_900!$G$15:$G$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(F19,Compose_900!$G$15:$G$107,1)))))</f>
+        <v/>
+      </c>
+      <c r="D20" s="5">
+        <f>IF(F19&lt;=0.01,MIN(0.5*(B19+B20),$B$5),IF(C20&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C20&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C20,Compose_900!$A$15:$A$107,1))+(C20-INDEX(Compose_900!$A$15:$A$107,MATCH(C20,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C20,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C20,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C20,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C20,Compose_900!$A$15:$A$107,1))))))</f>
+        <v/>
+      </c>
+      <c r="E20" s="24">
+        <f>(A20-A19)*60</f>
+        <v/>
+      </c>
+      <c r="F20" s="31">
+        <f>MAX(0,F19+(0.5*(B19+B20)-D20)*E20)</f>
+        <v/>
+      </c>
+      <c r="G20" s="4">
+        <f>IF(C20&gt;$B$6,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4">
+        <f>Hydrogramme!A17</f>
+        <v/>
+      </c>
+      <c r="B21" s="5">
+        <f>Hydrogramme!C17</f>
+        <v/>
+      </c>
+      <c r="C21" s="5">
+        <f>IF(F20&lt;=INDEX(Compose_900!$G$15:$G$107,1),INDEX(Compose_900!$A$15:$A$107,1),IF(F20&gt;=INDEX(Compose_900!$G$15:$G$107,ROWS(Compose_900!$G$15:$G$107)),INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$A$15:$A$107,MATCH(F20,Compose_900!$G$15:$G$107,1))+(F20-INDEX(Compose_900!$G$15:$G$107,MATCH(F20,Compose_900!$G$15:$G$107,1)))/(INDEX(Compose_900!$G$15:$G$107,MATCH(F20,Compose_900!$G$15:$G$107,1)+1)-INDEX(Compose_900!$G$15:$G$107,MATCH(F20,Compose_900!$G$15:$G$107,1)))*(INDEX(Compose_900!$A$15:$A$107,MATCH(F20,Compose_900!$G$15:$G$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(F20,Compose_900!$G$15:$G$107,1)))))</f>
+        <v/>
+      </c>
+      <c r="D21" s="5">
+        <f>IF(F20&lt;=0.01,MIN(0.5*(B20+B21),$B$5),IF(C21&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C21&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C21,Compose_900!$A$15:$A$107,1))+(C21-INDEX(Compose_900!$A$15:$A$107,MATCH(C21,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C21,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C21,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C21,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C21,Compose_900!$A$15:$A$107,1))))))</f>
+        <v/>
+      </c>
+      <c r="E21" s="24">
+        <f>(A21-A20)*60</f>
+        <v/>
+      </c>
+      <c r="F21" s="31">
+        <f>MAX(0,F20+(0.5*(B20+B21)-D21)*E21)</f>
+        <v/>
+      </c>
+      <c r="G21" s="4">
+        <f>IF(C21&gt;$B$6,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4">
+        <f>Hydrogramme!A18</f>
+        <v/>
+      </c>
+      <c r="B22" s="5">
+        <f>Hydrogramme!C18</f>
+        <v/>
+      </c>
+      <c r="C22" s="5">
+        <f>IF(F21&lt;=INDEX(Compose_900!$G$15:$G$107,1),INDEX(Compose_900!$A$15:$A$107,1),IF(F21&gt;=INDEX(Compose_900!$G$15:$G$107,ROWS(Compose_900!$G$15:$G$107)),INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$A$15:$A$107,MATCH(F21,Compose_900!$G$15:$G$107,1))+(F21-INDEX(Compose_900!$G$15:$G$107,MATCH(F21,Compose_900!$G$15:$G$107,1)))/(INDEX(Compose_900!$G$15:$G$107,MATCH(F21,Compose_900!$G$15:$G$107,1)+1)-INDEX(Compose_900!$G$15:$G$107,MATCH(F21,Compose_900!$G$15:$G$107,1)))*(INDEX(Compose_900!$A$15:$A$107,MATCH(F21,Compose_900!$G$15:$G$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(F21,Compose_900!$G$15:$G$107,1)))))</f>
+        <v/>
+      </c>
+      <c r="D22" s="5">
+        <f>IF(F21&lt;=0.01,MIN(0.5*(B21+B22),$B$5),IF(C22&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C22&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C22,Compose_900!$A$15:$A$107,1))+(C22-INDEX(Compose_900!$A$15:$A$107,MATCH(C22,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C22,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C22,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C22,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C22,Compose_900!$A$15:$A$107,1))))))</f>
+        <v/>
+      </c>
+      <c r="E22" s="24">
+        <f>(A22-A21)*60</f>
+        <v/>
+      </c>
+      <c r="F22" s="31">
+        <f>MAX(0,F21+(0.5*(B21+B22)-D22)*E22)</f>
+        <v/>
+      </c>
+      <c r="G22" s="4">
+        <f>IF(C22&gt;$B$6,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4">
+        <f>Hydrogramme!A19</f>
+        <v/>
+      </c>
+      <c r="B23" s="5">
+        <f>Hydrogramme!C19</f>
+        <v/>
+      </c>
+      <c r="C23" s="5">
+        <f>IF(F22&lt;=INDEX(Compose_900!$G$15:$G$107,1),INDEX(Compose_900!$A$15:$A$107,1),IF(F22&gt;=INDEX(Compose_900!$G$15:$G$107,ROWS(Compose_900!$G$15:$G$107)),INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$A$15:$A$107,MATCH(F22,Compose_900!$G$15:$G$107,1))+(F22-INDEX(Compose_900!$G$15:$G$107,MATCH(F22,Compose_900!$G$15:$G$107,1)))/(INDEX(Compose_900!$G$15:$G$107,MATCH(F22,Compose_900!$G$15:$G$107,1)+1)-INDEX(Compose_900!$G$15:$G$107,MATCH(F22,Compose_900!$G$15:$G$107,1)))*(INDEX(Compose_900!$A$15:$A$107,MATCH(F22,Compose_900!$G$15:$G$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(F22,Compose_900!$G$15:$G$107,1)))))</f>
+        <v/>
+      </c>
+      <c r="D23" s="5">
+        <f>IF(F22&lt;=0.01,MIN(0.5*(B22+B23),$B$5),IF(C23&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C23&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C23,Compose_900!$A$15:$A$107,1))+(C23-INDEX(Compose_900!$A$15:$A$107,MATCH(C23,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C23,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C23,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C23,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C23,Compose_900!$A$15:$A$107,1))))))</f>
+        <v/>
+      </c>
+      <c r="E23" s="24">
+        <f>(A23-A22)*60</f>
+        <v/>
+      </c>
+      <c r="F23" s="31">
+        <f>MAX(0,F22+(0.5*(B22+B23)-D23)*E23)</f>
+        <v/>
+      </c>
+      <c r="G23" s="4">
+        <f>IF(C23&gt;$B$6,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4">
+        <f>Hydrogramme!A20</f>
+        <v/>
+      </c>
+      <c r="B24" s="5">
+        <f>Hydrogramme!C20</f>
+        <v/>
+      </c>
+      <c r="C24" s="5">
+        <f>IF(F23&lt;=INDEX(Compose_900!$G$15:$G$107,1),INDEX(Compose_900!$A$15:$A$107,1),IF(F23&gt;=INDEX(Compose_900!$G$15:$G$107,ROWS(Compose_900!$G$15:$G$107)),INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$A$15:$A$107,MATCH(F23,Compose_900!$G$15:$G$107,1))+(F23-INDEX(Compose_900!$G$15:$G$107,MATCH(F23,Compose_900!$G$15:$G$107,1)))/(INDEX(Compose_900!$G$15:$G$107,MATCH(F23,Compose_900!$G$15:$G$107,1)+1)-INDEX(Compose_900!$G$15:$G$107,MATCH(F23,Compose_900!$G$15:$G$107,1)))*(INDEX(Compose_900!$A$15:$A$107,MATCH(F23,Compose_900!$G$15:$G$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(F23,Compose_900!$G$15:$G$107,1)))))</f>
+        <v/>
+      </c>
+      <c r="D24" s="5">
+        <f>IF(F23&lt;=0.01,MIN(0.5*(B23+B24),$B$5),IF(C24&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C24&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C24,Compose_900!$A$15:$A$107,1))+(C24-INDEX(Compose_900!$A$15:$A$107,MATCH(C24,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C24,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C24,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C24,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C24,Compose_900!$A$15:$A$107,1))))))</f>
+        <v/>
+      </c>
+      <c r="E24" s="24">
+        <f>(A24-A23)*60</f>
+        <v/>
+      </c>
+      <c r="F24" s="31">
+        <f>MAX(0,F23+(0.5*(B23+B24)-D24)*E24)</f>
+        <v/>
+      </c>
+      <c r="G24" s="4">
+        <f>IF(C24&gt;$B$6,"oui","non")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:H3"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5796,16 +10671,407 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>Stage–storage du levé — V = f(WSE) → lire le niveau max</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>PROCÉDURE (dans CE fichier): 1) Routage → Vmax_A / Vmax_B / Vmax_C sur Parametres. 2) Cette feuille = V_pond vs WSE (levé seul). 3) Parametres!B39 = WSEmax_A; B45 = WSEmax_B (levé). 4) Méthode C: V_pond + V_ditch et WSEmax_C sont sur Compose_900 / Calcul_C (B51). Remplacez les surfaces jaunes; 543 m² @ 37.28 et 1932 m² @ 39.5 sont vos mesures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Formule d'un pas</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="40" t="inlineStr">
+        <is>
+          <t>V_pas (m³) = (A_basse + A_haute) / 2 × (WSE_haute − WSE_basse)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>V_cumulatif = somme des V_pas depuis le radier</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>WSE / NSE (m)</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Surface A (m²) ← ÉDITER</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>ΔWSE (m)</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>V_pas (m³)</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>V_cumulatif (m³)</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Rôle</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="29" t="n">
+        <v>34.88</v>
+      </c>
+      <c r="B11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Radier Ø900 — départ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="B12" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="C12" s="29">
+        <f>A12-A11</f>
+        <v/>
+      </c>
+      <c r="D12" s="24">
+        <f>0.5*(B11+B12)*C12</f>
+        <v/>
+      </c>
+      <c r="E12" s="31">
+        <f>E11+D12</f>
+        <v/>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Placeholder — remplacer par levé</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="n">
+        <v>36</v>
+      </c>
+      <c r="B13" s="17" t="n">
+        <v>180</v>
+      </c>
+      <c r="C13" s="29">
+        <f>A13-A12</f>
+        <v/>
+      </c>
+      <c r="D13" s="24">
+        <f>0.5*(B12+B13)*C13</f>
+        <v/>
+      </c>
+      <c r="E13" s="31">
+        <f>E12+D13</f>
+        <v/>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Placeholder — remplacer par levé</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="B14" s="17" t="n">
+        <v>320</v>
+      </c>
+      <c r="C14" s="29">
+        <f>A14-A13</f>
+        <v/>
+      </c>
+      <c r="D14" s="24">
+        <f>0.5*(B13+B14)*C14</f>
+        <v/>
+      </c>
+      <c r="E14" s="31">
+        <f>E13+D14</f>
+        <v/>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Placeholder — remplacer par levé</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="29" t="n">
+        <v>37</v>
+      </c>
+      <c r="B15" s="17" t="n">
+        <v>480</v>
+      </c>
+      <c r="C15" s="29">
+        <f>A15-A14</f>
+        <v/>
+      </c>
+      <c r="D15" s="24">
+        <f>0.5*(B14+B15)*C15</f>
+        <v/>
+      </c>
+      <c r="E15" s="31">
+        <f>E14+D15</f>
+        <v/>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Placeholder — remplacer par levé</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="36" t="n">
+        <v>37.28</v>
+      </c>
+      <c r="B16" s="17" t="n">
+        <v>543</v>
+      </c>
+      <c r="C16" s="36">
+        <f>A16-A15</f>
+        <v/>
+      </c>
+      <c r="D16" s="39">
+        <f>0.5*(B15+B16)*C16</f>
+        <v/>
+      </c>
+      <c r="E16" s="39">
+        <f>E15+D16</f>
+        <v/>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>LIMITE PATRON (+1.5 m crown) — votre levé</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="29" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="B17" s="17" t="n">
+        <v>700</v>
+      </c>
+      <c r="C17" s="29">
+        <f>A17-A16</f>
+        <v/>
+      </c>
+      <c r="D17" s="24">
+        <f>0.5*(B16+B17)*C17</f>
+        <v/>
+      </c>
+      <c r="E17" s="31">
+        <f>E16+D17</f>
+        <v/>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Placeholder — remplacer par levé</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="B18" s="17" t="n">
+        <v>1932</v>
+      </c>
+      <c r="C18" s="29">
+        <f>A18-A17</f>
+        <v/>
+      </c>
+      <c r="D18" s="24">
+        <f>0.5*(B17+B18)*C18</f>
+        <v/>
+      </c>
+      <c r="E18" s="31">
+        <f>E17+D18</f>
+        <v/>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Votre levé 1932 m² — niveau optionnel plus haut</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Vmax_A (Calcul_A)</t>
+        </is>
+      </c>
+      <c r="B21" s="19">
+        <f>Parametres!B36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>WSEmax_A (m)</t>
+        </is>
+      </c>
+      <c r="B22" s="40">
+        <f>Parametres!B39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Vmax_B (Calcul_B)</t>
+        </is>
+      </c>
+      <c r="B23" s="19">
+        <f>Parametres!B43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>WSEmax_B (m)</t>
+        </is>
+      </c>
+      <c r="B24" s="40">
+        <f>Parametres!B45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Vmax_C / WSEmax_C</t>
+        </is>
+      </c>
+      <c r="B25" s="19">
+        <f>Parametres!B49</f>
+        <v/>
+      </c>
+      <c r="C25">
+        <f>Parametres!B51</f>
+        <v/>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Vmax_C inclut V_ditch — WSEmax_C = Parametres B51</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>V disponible à 37.28 m (m³)</t>
+        </is>
+      </c>
+      <c r="B26" s="41">
+        <f>E16</f>
+        <v/>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Si Vmax_A ou Vmax_B &gt; cette valeur → le niveau dépasse la limite patron</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Comment lire le résultat</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="37" t="inlineStr">
+        <is>
+          <t>Exemple: si Vmax_A = 5609 m³ et V(37.28)≈558 m³, alors WSEmax_A est au-dessus de 37.28 m (la table ira vers 39.5 m ou 'Hors table'). Affinez en entrant les vraies surfaces aux cotes intermédiaires (jaune). Méthode C: voir Parametres B49–B52 et Calcul_C (fossé inclus).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31"/>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A2:G4"/>
+    <mergeCell ref="A29:F31"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="42" t="inlineStr">
         <is>
-          <t>Méthode — volume de rétention</t>
+          <t>Où sont les fichiers HY-8 / capacité ?</t>
         </is>
       </c>
     </row>
@@ -5815,83 +11081,106 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1. Hydrogramme Qin(t) à l'entrée de la zone de rétention.</t>
+          <t>Ce classeur (rétention Ø900) :</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2. Débit sortant contrôlé par le Ø900 (en série avant le Ø1200).</t>
+          <t xml:space="preserve">  engineering/drainage-design/retention_volume/Volume_Retention_Ponceau_900.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>3. Capacité Ø900 — deux niveaux:</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">   A) Q_plein Manning (n=0.013) ≈ 1.668 m³/s → Méthode A (constant).</t>
+          <t>Courbe Q=f(H) FHWA pour CE Ø900 : feuille Courbe_QH_900 (ci-dessus).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   B) Courbe Q=f(H) FHWA HDS-5 (inlet + outlet) → feuille Courbe_QH_900 + Calcul_B.</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4. Méthode A: Qout = constante = Q_plein (jaune Parametres). Bon pour 1re estimation.</t>
+          <t>Ancien Excel « type HY-8 / inlet-outlet » (autre projet / Ste-Thérèse) :</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5. Méthode B: Qout lu sur la courbe selon H=V/Aire (charge amont).</t>
+          <t xml:space="preserve">  engineering/drainage-design/Ponceau_Capacite_Inlet_Outlet.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6. Sur ce Ø900 (L/D≈56), le calcul FHWA indique surtout un contrôle outlet.</t>
+          <t xml:space="preserve">  Branche git: cursor/culvert-excel-capacity-model-d87f</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>7. Le Ø1200 est aval: n'augmente pas la sortie de la rétention.</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Modèle composé ponceau Ø1050 + fossé (FHWA + remblai) — PAS le Ø900 de rétention :</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8. Niveau d'eau max: Stage_Storage + Parametres!B30 (WSEmax_A) et B36 (WSEmax_B).</t>
+          <t xml:space="preserve">  engineering/drainage-design/ponceau_fosse_model/Ponceau_Fosse_Modele_Hydraulique.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Branche git: cursor/ponceau-fosse-hydraulic-model-d87f</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Fichiers liés / anciens Excel: voir feuille Fichiers_lies.</t>
+      <c r="A15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>HEC-RAS : pas de projet .ras/.hdf pour ce Ø900. Un DEM Ste-Thérèse est dans</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  engineering/hec-ras-data/ (données topo seulement).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Donc: on n'avait pas perdu un HY-8 pour ce bassin Ø900 — on avait des outils</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>similaires pour d'autres sites. La courbe de CE classeur remplace ça pour le Ø900.</t>
         </is>
       </c>
     </row>

--- a/engineering/drainage-design/retention_volume/Volume_Retention_Ponceau_900.xlsx
+++ b/engineering/drainage-design/retention_volume/Volume_Retention_Ponceau_900.xlsx
@@ -90,12 +90,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D1FAE5"/>
+        <fgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DBEAFE"/>
+        <fgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -140,38 +140,39 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -1752,15 +1753,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S0 = (Zamont−Zaval)/L</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="n">
-        <v>0.008489634748272452</v>
-      </c>
-      <c r="C15">
+          <t>S0 = (Zamont-Zaval)/L</t>
+        </is>
+      </c>
+      <c r="B15" s="13">
         <f>(D6-E6)/F6</f>
         <v/>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Formule live depuis tableau géométrie Ø900</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1769,8 +1772,9 @@
           <t>A = πD²/4 (m²)</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n">
-        <v>0.6361725123519332</v>
+      <c r="B16" s="14">
+        <f>PI()*B14^2/4</f>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -1779,8 +1783,9 @@
           <t>R = D/4 (m)</t>
         </is>
       </c>
-      <c r="B17" s="14" t="n">
-        <v>0.225</v>
+      <c r="B17" s="14">
+        <f>B14/4</f>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -1789,12 +1794,13 @@
           <t>Q_plein = (1/n)·A·R^(2/3)·√S0</t>
         </is>
       </c>
-      <c r="B18" s="15" t="n">
-        <v>1.668006465155198</v>
+      <c r="B18" s="15">
+        <f>(1/B13)*B16*(B17^(2/3))*SQRT(B15)</f>
+        <v/>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>m³/s — capacité pleine section (hypothèse actuelle)</t>
+          <t>m³/s — formule live (changez n ou géométrie → Q se met à jour)</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1810,7 @@
           <t>Q utilisé avant (m³/s)</t>
         </is>
       </c>
-      <c r="B19" s="12" t="n">
+      <c r="B19" s="16" t="n">
         <v>1.77</v>
       </c>
       <c r="C19" t="inlineStr">
@@ -1826,12 +1832,13 @@
           <t>Qout_cap_900 (m³/s)</t>
         </is>
       </c>
-      <c r="B22" s="11" t="n">
-        <v>1.668</v>
+      <c r="B22" s="11">
+        <f>B18</f>
+        <v/>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Par défaut = Q_plein Manning. Mettre 1.77 pour retrouver l'ancien calcul.</t>
+          <t>Par défaut = Q_plein (B18). Écraser par 1.77 si besoin (ancien calcul).</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1848,7 @@
           <t>Facteur_securite (-)</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
+      <c r="B23" s="12" t="n">
         <v>1.2</v>
       </c>
       <c r="C23" t="inlineStr">
@@ -1878,7 +1885,7 @@
           <t>Crest = crown Ø900 (m)</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n">
+      <c r="B27" s="12" t="n">
         <v>35.78</v>
       </c>
       <c r="C27" t="inlineStr">
@@ -1893,7 +1900,7 @@
           <t>b fond fossé (m)</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n">
+      <c r="B28" s="12" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1929,7 +1936,12 @@
         </is>
       </c>
       <c r="B31" s="11" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>≈0.0085 (corrigé; pente type lit Ø900 — pas 0.085)</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -2357,7 +2369,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="43" t="inlineStr">
+      <c r="A1" s="44" t="inlineStr">
         <is>
           <t>Méthode — volume de rétention</t>
         </is>
@@ -2749,7 +2761,7 @@
           <t>Qcap Ø900 (réf.)</t>
         </is>
       </c>
-      <c r="B23" s="14">
+      <c r="B23" s="27">
         <f>Parametres!B22</f>
         <v/>
       </c>
@@ -2796,7 +2808,7 @@
           <t>Qout (m³/s)</t>
         </is>
       </c>
-      <c r="B2" s="27">
+      <c r="B2" s="28">
         <f>Parametres!B22</f>
         <v/>
       </c>
@@ -2807,7 +2819,7 @@
           <t>Vmax (m³)</t>
         </is>
       </c>
-      <c r="B3" s="28">
+      <c r="B3" s="29">
         <f>MAX(H8:H20)</f>
         <v/>
       </c>
@@ -2897,7 +2909,7 @@
         <f>Hydrogramme!C8</f>
         <v/>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <f>$B$2</f>
         <v/>
       </c>
@@ -2914,7 +2926,7 @@
       <c r="G8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="30" t="n">
+      <c r="H8" s="31" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="4">
@@ -2931,7 +2943,7 @@
         <f>Hydrogramme!C9</f>
         <v/>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <f>$B$2</f>
         <v/>
       </c>
@@ -2951,7 +2963,7 @@
         <f>F9-(H9-H8)</f>
         <v/>
       </c>
-      <c r="H9" s="31">
+      <c r="H9" s="32">
         <f>MAX(0,H8+0.5*(D8+D9)*E9)</f>
         <v/>
       </c>
@@ -2969,7 +2981,7 @@
         <f>Hydrogramme!C10</f>
         <v/>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="30">
         <f>$B$2</f>
         <v/>
       </c>
@@ -2989,7 +3001,7 @@
         <f>F10-(H10-H9)</f>
         <v/>
       </c>
-      <c r="H10" s="31">
+      <c r="H10" s="32">
         <f>MAX(0,H9+0.5*(D9+D10)*E10)</f>
         <v/>
       </c>
@@ -3007,7 +3019,7 @@
         <f>Hydrogramme!C11</f>
         <v/>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="30">
         <f>$B$2</f>
         <v/>
       </c>
@@ -3027,7 +3039,7 @@
         <f>F11-(H11-H10)</f>
         <v/>
       </c>
-      <c r="H11" s="31">
+      <c r="H11" s="32">
         <f>MAX(0,H10+0.5*(D10+D11)*E11)</f>
         <v/>
       </c>
@@ -3045,7 +3057,7 @@
         <f>Hydrogramme!C12</f>
         <v/>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="30">
         <f>$B$2</f>
         <v/>
       </c>
@@ -3065,7 +3077,7 @@
         <f>F12-(H12-H11)</f>
         <v/>
       </c>
-      <c r="H12" s="31">
+      <c r="H12" s="32">
         <f>MAX(0,H11+0.5*(D11+D12)*E12)</f>
         <v/>
       </c>
@@ -3083,7 +3095,7 @@
         <f>Hydrogramme!C13</f>
         <v/>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="30">
         <f>$B$2</f>
         <v/>
       </c>
@@ -3103,7 +3115,7 @@
         <f>F13-(H13-H12)</f>
         <v/>
       </c>
-      <c r="H13" s="31">
+      <c r="H13" s="32">
         <f>MAX(0,H12+0.5*(D12+D13)*E13)</f>
         <v/>
       </c>
@@ -3121,7 +3133,7 @@
         <f>Hydrogramme!C14</f>
         <v/>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="30">
         <f>$B$2</f>
         <v/>
       </c>
@@ -3141,7 +3153,7 @@
         <f>F14-(H14-H13)</f>
         <v/>
       </c>
-      <c r="H14" s="31">
+      <c r="H14" s="32">
         <f>MAX(0,H13+0.5*(D13+D14)*E14)</f>
         <v/>
       </c>
@@ -3159,7 +3171,7 @@
         <f>Hydrogramme!C15</f>
         <v/>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="30">
         <f>$B$2</f>
         <v/>
       </c>
@@ -3179,7 +3191,7 @@
         <f>F15-(H15-H14)</f>
         <v/>
       </c>
-      <c r="H15" s="31">
+      <c r="H15" s="32">
         <f>MAX(0,H14+0.5*(D14+D15)*E15)</f>
         <v/>
       </c>
@@ -3197,7 +3209,7 @@
         <f>Hydrogramme!C16</f>
         <v/>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="30">
         <f>$B$2</f>
         <v/>
       </c>
@@ -3217,7 +3229,7 @@
         <f>F16-(H16-H15)</f>
         <v/>
       </c>
-      <c r="H16" s="31">
+      <c r="H16" s="32">
         <f>MAX(0,H15+0.5*(D15+D16)*E16)</f>
         <v/>
       </c>
@@ -3235,7 +3247,7 @@
         <f>Hydrogramme!C17</f>
         <v/>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="30">
         <f>$B$2</f>
         <v/>
       </c>
@@ -3255,7 +3267,7 @@
         <f>F17-(H17-H16)</f>
         <v/>
       </c>
-      <c r="H17" s="31">
+      <c r="H17" s="32">
         <f>MAX(0,H16+0.5*(D16+D17)*E17)</f>
         <v/>
       </c>
@@ -3273,7 +3285,7 @@
         <f>Hydrogramme!C18</f>
         <v/>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="30">
         <f>$B$2</f>
         <v/>
       </c>
@@ -3293,7 +3305,7 @@
         <f>F18-(H18-H17)</f>
         <v/>
       </c>
-      <c r="H18" s="31">
+      <c r="H18" s="32">
         <f>MAX(0,H17+0.5*(D17+D18)*E18)</f>
         <v/>
       </c>
@@ -3311,7 +3323,7 @@
         <f>Hydrogramme!C19</f>
         <v/>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="30">
         <f>$B$2</f>
         <v/>
       </c>
@@ -3331,7 +3343,7 @@
         <f>F19-(H19-H18)</f>
         <v/>
       </c>
-      <c r="H19" s="31">
+      <c r="H19" s="32">
         <f>MAX(0,H18+0.5*(D18+D19)*E19)</f>
         <v/>
       </c>
@@ -3349,7 +3361,7 @@
         <f>Hydrogramme!C20</f>
         <v/>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="30">
         <f>$B$2</f>
         <v/>
       </c>
@@ -3369,7 +3381,7 @@
         <f>F20-(H20-H19)</f>
         <v/>
       </c>
-      <c r="H20" s="31">
+      <c r="H20" s="32">
         <f>MAX(0,H19+0.5*(D19+D20)*E20)</f>
         <v/>
       </c>
@@ -3443,32 +3455,32 @@
           <t>béton typ. 0.012–0.015</t>
         </is>
       </c>
-      <c r="E6" s="32" t="inlineStr">
+      <c r="E6" s="33" t="inlineStr">
         <is>
           <t>entrée</t>
         </is>
       </c>
-      <c r="F6" s="32" t="inlineStr">
+      <c r="F6" s="33" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="G6" s="32" t="inlineStr">
+      <c r="G6" s="33" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H6" s="32" t="inlineStr">
+      <c r="H6" s="33" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="I6" s="32" t="inlineStr">
+      <c r="I6" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J6" s="32" t="inlineStr">
+      <c r="J6" s="33" t="inlineStr">
         <is>
           <t>Ke</t>
         </is>
@@ -3480,7 +3492,7 @@
           <t>D (m)</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="12" t="n">
         <v>0.9</v>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -3511,7 +3523,7 @@
           <t>L (m)</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="12" t="n">
         <v>50.65</v>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -3542,7 +3554,7 @@
           <t>Radier amont Zin (m)</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="12" t="n">
         <v>34.88</v>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -3573,7 +3585,7 @@
           <t>Radier aval Zout (m)</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="12" t="n">
         <v>34.45</v>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -3584,7 +3596,7 @@
           <t>S0 = (Zin-Zout)/L</t>
         </is>
       </c>
-      <c r="B11" s="33">
+      <c r="B11" s="34">
         <f>(B9-B10)/B8</f>
         <v/>
       </c>
@@ -3600,7 +3612,7 @@
           <t>TW (m au-dessus Zout)</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -3615,7 +3627,7 @@
           <t>Entrée (texte exact)</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>square_edge</t>
         </is>
@@ -3648,7 +3660,7 @@
           <t>K (lu)</t>
         </is>
       </c>
-      <c r="B17" s="35">
+      <c r="B17" s="36">
         <f>IFERROR(VLOOKUP(B13,$E$7:$J$9,2,FALSE),0.0098)</f>
         <v/>
       </c>
@@ -3659,7 +3671,7 @@
           <t>M (lu)</t>
         </is>
       </c>
-      <c r="B18" s="35">
+      <c r="B18" s="36">
         <f>IFERROR(VLOOKUP(B13,$E$7:$J$9,3,FALSE),2)</f>
         <v/>
       </c>
@@ -3670,7 +3682,7 @@
           <t>c (lu)</t>
         </is>
       </c>
-      <c r="B19" s="35">
+      <c r="B19" s="36">
         <f>IFERROR(VLOOKUP(B13,$E$7:$J$9,4,FALSE),0.0398)</f>
         <v/>
       </c>
@@ -3681,7 +3693,7 @@
           <t>Y (lu)</t>
         </is>
       </c>
-      <c r="B20" s="35">
+      <c r="B20" s="36">
         <f>IFERROR(VLOOKUP(B13,$E$7:$J$9,5,FALSE),0.67)</f>
         <v/>
       </c>
@@ -3692,7 +3704,7 @@
           <t>Ke (lu)</t>
         </is>
       </c>
-      <c r="B21" s="35">
+      <c r="B21" s="36">
         <f>IFERROR(VLOOKUP(B13,$E$7:$J$9,6,FALSE),0.5)</f>
         <v/>
       </c>
@@ -3730,10 +3742,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="29" t="n">
+      <c r="A24" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="B24" s="29">
+      <c r="B24" s="30">
         <f>$B$9+A24</f>
         <v/>
       </c>
@@ -3755,10 +3767,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="29" t="n">
+      <c r="A25" s="30" t="n">
         <v>0.05</v>
       </c>
-      <c r="B25" s="29">
+      <c r="B25" s="30">
         <f>$B$9+A25</f>
         <v/>
       </c>
@@ -3780,10 +3792,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="29" t="n">
+      <c r="A26" s="30" t="n">
         <v>0.1</v>
       </c>
-      <c r="B26" s="29">
+      <c r="B26" s="30">
         <f>$B$9+A26</f>
         <v/>
       </c>
@@ -3805,10 +3817,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="29" t="n">
+      <c r="A27" s="30" t="n">
         <v>0.15</v>
       </c>
-      <c r="B27" s="29">
+      <c r="B27" s="30">
         <f>$B$9+A27</f>
         <v/>
       </c>
@@ -3830,10 +3842,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="29" t="n">
+      <c r="A28" s="30" t="n">
         <v>0.2</v>
       </c>
-      <c r="B28" s="29">
+      <c r="B28" s="30">
         <f>$B$9+A28</f>
         <v/>
       </c>
@@ -3855,10 +3867,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="29" t="n">
+      <c r="A29" s="30" t="n">
         <v>0.25</v>
       </c>
-      <c r="B29" s="29">
+      <c r="B29" s="30">
         <f>$B$9+A29</f>
         <v/>
       </c>
@@ -3880,10 +3892,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="29" t="n">
+      <c r="A30" s="30" t="n">
         <v>0.3</v>
       </c>
-      <c r="B30" s="29">
+      <c r="B30" s="30">
         <f>$B$9+A30</f>
         <v/>
       </c>
@@ -3905,10 +3917,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="29" t="n">
+      <c r="A31" s="30" t="n">
         <v>0.35</v>
       </c>
-      <c r="B31" s="29">
+      <c r="B31" s="30">
         <f>$B$9+A31</f>
         <v/>
       </c>
@@ -3930,10 +3942,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="29" t="n">
+      <c r="A32" s="30" t="n">
         <v>0.4</v>
       </c>
-      <c r="B32" s="29">
+      <c r="B32" s="30">
         <f>$B$9+A32</f>
         <v/>
       </c>
@@ -3955,10 +3967,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="29" t="n">
+      <c r="A33" s="30" t="n">
         <v>0.45</v>
       </c>
-      <c r="B33" s="29">
+      <c r="B33" s="30">
         <f>$B$9+A33</f>
         <v/>
       </c>
@@ -3980,10 +3992,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="29" t="n">
+      <c r="A34" s="30" t="n">
         <v>0.5</v>
       </c>
-      <c r="B34" s="29">
+      <c r="B34" s="30">
         <f>$B$9+A34</f>
         <v/>
       </c>
@@ -4005,10 +4017,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="29" t="n">
+      <c r="A35" s="30" t="n">
         <v>0.55</v>
       </c>
-      <c r="B35" s="29">
+      <c r="B35" s="30">
         <f>$B$9+A35</f>
         <v/>
       </c>
@@ -4030,10 +4042,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="29" t="n">
+      <c r="A36" s="30" t="n">
         <v>0.6</v>
       </c>
-      <c r="B36" s="29">
+      <c r="B36" s="30">
         <f>$B$9+A36</f>
         <v/>
       </c>
@@ -4055,10 +4067,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="29" t="n">
+      <c r="A37" s="30" t="n">
         <v>0.65</v>
       </c>
-      <c r="B37" s="29">
+      <c r="B37" s="30">
         <f>$B$9+A37</f>
         <v/>
       </c>
@@ -4080,10 +4092,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="29" t="n">
+      <c r="A38" s="30" t="n">
         <v>0.7</v>
       </c>
-      <c r="B38" s="29">
+      <c r="B38" s="30">
         <f>$B$9+A38</f>
         <v/>
       </c>
@@ -4105,10 +4117,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="29" t="n">
+      <c r="A39" s="30" t="n">
         <v>0.75</v>
       </c>
-      <c r="B39" s="29">
+      <c r="B39" s="30">
         <f>$B$9+A39</f>
         <v/>
       </c>
@@ -4130,10 +4142,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="29" t="n">
+      <c r="A40" s="30" t="n">
         <v>0.8</v>
       </c>
-      <c r="B40" s="29">
+      <c r="B40" s="30">
         <f>$B$9+A40</f>
         <v/>
       </c>
@@ -4155,10 +4167,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="29" t="n">
+      <c r="A41" s="30" t="n">
         <v>0.85</v>
       </c>
-      <c r="B41" s="29">
+      <c r="B41" s="30">
         <f>$B$9+A41</f>
         <v/>
       </c>
@@ -4180,10 +4192,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="29" t="n">
+      <c r="A42" s="30" t="n">
         <v>0.9</v>
       </c>
-      <c r="B42" s="29">
+      <c r="B42" s="30">
         <f>$B$9+A42</f>
         <v/>
       </c>
@@ -4205,10 +4217,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="29" t="n">
+      <c r="A43" s="30" t="n">
         <v>0.95</v>
       </c>
-      <c r="B43" s="29">
+      <c r="B43" s="30">
         <f>$B$9+A43</f>
         <v/>
       </c>
@@ -4230,10 +4242,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="29" t="n">
+      <c r="A44" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="B44" s="29">
+      <c r="B44" s="30">
         <f>$B$9+A44</f>
         <v/>
       </c>
@@ -4255,10 +4267,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="29" t="n">
+      <c r="A45" s="30" t="n">
         <v>1.05</v>
       </c>
-      <c r="B45" s="29">
+      <c r="B45" s="30">
         <f>$B$9+A45</f>
         <v/>
       </c>
@@ -4280,10 +4292,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="29" t="n">
+      <c r="A46" s="30" t="n">
         <v>1.1</v>
       </c>
-      <c r="B46" s="29">
+      <c r="B46" s="30">
         <f>$B$9+A46</f>
         <v/>
       </c>
@@ -4305,10 +4317,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="29" t="n">
+      <c r="A47" s="30" t="n">
         <v>1.15</v>
       </c>
-      <c r="B47" s="29">
+      <c r="B47" s="30">
         <f>$B$9+A47</f>
         <v/>
       </c>
@@ -4330,10 +4342,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="29" t="n">
+      <c r="A48" s="30" t="n">
         <v>1.2</v>
       </c>
-      <c r="B48" s="29">
+      <c r="B48" s="30">
         <f>$B$9+A48</f>
         <v/>
       </c>
@@ -4355,10 +4367,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="29" t="n">
+      <c r="A49" s="30" t="n">
         <v>1.25</v>
       </c>
-      <c r="B49" s="29">
+      <c r="B49" s="30">
         <f>$B$9+A49</f>
         <v/>
       </c>
@@ -4380,10 +4392,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="29" t="n">
+      <c r="A50" s="30" t="n">
         <v>1.3</v>
       </c>
-      <c r="B50" s="29">
+      <c r="B50" s="30">
         <f>$B$9+A50</f>
         <v/>
       </c>
@@ -4405,10 +4417,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="29" t="n">
+      <c r="A51" s="30" t="n">
         <v>1.35</v>
       </c>
-      <c r="B51" s="29">
+      <c r="B51" s="30">
         <f>$B$9+A51</f>
         <v/>
       </c>
@@ -4430,10 +4442,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="29" t="n">
+      <c r="A52" s="30" t="n">
         <v>1.4</v>
       </c>
-      <c r="B52" s="29">
+      <c r="B52" s="30">
         <f>$B$9+A52</f>
         <v/>
       </c>
@@ -4455,10 +4467,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="29" t="n">
+      <c r="A53" s="30" t="n">
         <v>1.45</v>
       </c>
-      <c r="B53" s="29">
+      <c r="B53" s="30">
         <f>$B$9+A53</f>
         <v/>
       </c>
@@ -4480,10 +4492,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="29" t="n">
+      <c r="A54" s="30" t="n">
         <v>1.5</v>
       </c>
-      <c r="B54" s="29">
+      <c r="B54" s="30">
         <f>$B$9+A54</f>
         <v/>
       </c>
@@ -4505,10 +4517,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="29" t="n">
+      <c r="A55" s="30" t="n">
         <v>1.55</v>
       </c>
-      <c r="B55" s="29">
+      <c r="B55" s="30">
         <f>$B$9+A55</f>
         <v/>
       </c>
@@ -4530,10 +4542,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="29" t="n">
+      <c r="A56" s="30" t="n">
         <v>1.6</v>
       </c>
-      <c r="B56" s="29">
+      <c r="B56" s="30">
         <f>$B$9+A56</f>
         <v/>
       </c>
@@ -4555,10 +4567,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="29" t="n">
+      <c r="A57" s="30" t="n">
         <v>1.65</v>
       </c>
-      <c r="B57" s="29">
+      <c r="B57" s="30">
         <f>$B$9+A57</f>
         <v/>
       </c>
@@ -4580,10 +4592,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="29" t="n">
+      <c r="A58" s="30" t="n">
         <v>1.7</v>
       </c>
-      <c r="B58" s="29">
+      <c r="B58" s="30">
         <f>$B$9+A58</f>
         <v/>
       </c>
@@ -4605,10 +4617,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="29" t="n">
+      <c r="A59" s="30" t="n">
         <v>1.75</v>
       </c>
-      <c r="B59" s="29">
+      <c r="B59" s="30">
         <f>$B$9+A59</f>
         <v/>
       </c>
@@ -4630,10 +4642,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="29" t="n">
+      <c r="A60" s="30" t="n">
         <v>1.8</v>
       </c>
-      <c r="B60" s="29">
+      <c r="B60" s="30">
         <f>$B$9+A60</f>
         <v/>
       </c>
@@ -4655,10 +4667,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="29" t="n">
+      <c r="A61" s="30" t="n">
         <v>1.85</v>
       </c>
-      <c r="B61" s="29">
+      <c r="B61" s="30">
         <f>$B$9+A61</f>
         <v/>
       </c>
@@ -4680,10 +4692,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="29" t="n">
+      <c r="A62" s="30" t="n">
         <v>1.9</v>
       </c>
-      <c r="B62" s="29">
+      <c r="B62" s="30">
         <f>$B$9+A62</f>
         <v/>
       </c>
@@ -4705,10 +4717,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="29" t="n">
+      <c r="A63" s="30" t="n">
         <v>1.95</v>
       </c>
-      <c r="B63" s="29">
+      <c r="B63" s="30">
         <f>$B$9+A63</f>
         <v/>
       </c>
@@ -4730,10 +4742,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="29" t="n">
+      <c r="A64" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="B64" s="29">
+      <c r="B64" s="30">
         <f>$B$9+A64</f>
         <v/>
       </c>
@@ -4755,10 +4767,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="29" t="n">
+      <c r="A65" s="30" t="n">
         <v>2.05</v>
       </c>
-      <c r="B65" s="29">
+      <c r="B65" s="30">
         <f>$B$9+A65</f>
         <v/>
       </c>
@@ -4780,10 +4792,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="29" t="n">
+      <c r="A66" s="30" t="n">
         <v>2.1</v>
       </c>
-      <c r="B66" s="29">
+      <c r="B66" s="30">
         <f>$B$9+A66</f>
         <v/>
       </c>
@@ -4805,10 +4817,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="29" t="n">
+      <c r="A67" s="30" t="n">
         <v>2.15</v>
       </c>
-      <c r="B67" s="29">
+      <c r="B67" s="30">
         <f>$B$9+A67</f>
         <v/>
       </c>
@@ -4830,10 +4842,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="29" t="n">
+      <c r="A68" s="30" t="n">
         <v>2.2</v>
       </c>
-      <c r="B68" s="29">
+      <c r="B68" s="30">
         <f>$B$9+A68</f>
         <v/>
       </c>
@@ -4855,10 +4867,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="29" t="n">
+      <c r="A69" s="30" t="n">
         <v>2.25</v>
       </c>
-      <c r="B69" s="29">
+      <c r="B69" s="30">
         <f>$B$9+A69</f>
         <v/>
       </c>
@@ -4880,10 +4892,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="29" t="n">
+      <c r="A70" s="30" t="n">
         <v>2.3</v>
       </c>
-      <c r="B70" s="29">
+      <c r="B70" s="30">
         <f>$B$9+A70</f>
         <v/>
       </c>
@@ -4905,10 +4917,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="29" t="n">
+      <c r="A71" s="30" t="n">
         <v>2.35</v>
       </c>
-      <c r="B71" s="29">
+      <c r="B71" s="30">
         <f>$B$9+A71</f>
         <v/>
       </c>
@@ -4930,10 +4942,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="36" t="n">
+      <c r="A72" s="37" t="n">
         <v>2.4</v>
       </c>
-      <c r="B72" s="36">
+      <c r="B72" s="37">
         <f>$B$9+A72</f>
         <v/>
       </c>
@@ -4955,10 +4967,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="29" t="n">
+      <c r="A73" s="30" t="n">
         <v>2.45</v>
       </c>
-      <c r="B73" s="29">
+      <c r="B73" s="30">
         <f>$B$9+A73</f>
         <v/>
       </c>
@@ -4980,10 +4992,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="29" t="n">
+      <c r="A74" s="30" t="n">
         <v>2.5</v>
       </c>
-      <c r="B74" s="29">
+      <c r="B74" s="30">
         <f>$B$9+A74</f>
         <v/>
       </c>
@@ -5005,10 +5017,10 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="29" t="n">
+      <c r="A75" s="30" t="n">
         <v>2.55</v>
       </c>
-      <c r="B75" s="29">
+      <c r="B75" s="30">
         <f>$B$9+A75</f>
         <v/>
       </c>
@@ -5030,10 +5042,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="29" t="n">
+      <c r="A76" s="30" t="n">
         <v>2.6</v>
       </c>
-      <c r="B76" s="29">
+      <c r="B76" s="30">
         <f>$B$9+A76</f>
         <v/>
       </c>
@@ -5055,10 +5067,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="29" t="n">
+      <c r="A77" s="30" t="n">
         <v>2.65</v>
       </c>
-      <c r="B77" s="29">
+      <c r="B77" s="30">
         <f>$B$9+A77</f>
         <v/>
       </c>
@@ -5080,10 +5092,10 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="29" t="n">
+      <c r="A78" s="30" t="n">
         <v>2.7</v>
       </c>
-      <c r="B78" s="29">
+      <c r="B78" s="30">
         <f>$B$9+A78</f>
         <v/>
       </c>
@@ -5105,10 +5117,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="29" t="n">
+      <c r="A79" s="30" t="n">
         <v>2.75</v>
       </c>
-      <c r="B79" s="29">
+      <c r="B79" s="30">
         <f>$B$9+A79</f>
         <v/>
       </c>
@@ -5130,10 +5142,10 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="29" t="n">
+      <c r="A80" s="30" t="n">
         <v>2.8</v>
       </c>
-      <c r="B80" s="29">
+      <c r="B80" s="30">
         <f>$B$9+A80</f>
         <v/>
       </c>
@@ -5155,10 +5167,10 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="29" t="n">
+      <c r="A81" s="30" t="n">
         <v>2.85</v>
       </c>
-      <c r="B81" s="29">
+      <c r="B81" s="30">
         <f>$B$9+A81</f>
         <v/>
       </c>
@@ -5180,10 +5192,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="29" t="n">
+      <c r="A82" s="30" t="n">
         <v>2.9</v>
       </c>
-      <c r="B82" s="29">
+      <c r="B82" s="30">
         <f>$B$9+A82</f>
         <v/>
       </c>
@@ -5205,10 +5217,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="29" t="n">
+      <c r="A83" s="30" t="n">
         <v>2.95</v>
       </c>
-      <c r="B83" s="29">
+      <c r="B83" s="30">
         <f>$B$9+A83</f>
         <v/>
       </c>
@@ -5230,10 +5242,10 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="29" t="n">
+      <c r="A84" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="B84" s="29">
+      <c r="B84" s="30">
         <f>$B$9+A84</f>
         <v/>
       </c>
@@ -5289,7 +5301,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="37" t="inlineStr">
+      <c r="A2" s="38" t="inlineStr">
         <is>
           <t>H = V / Aire_bassin. Qout interpolé sur Courbe_QH_900!E (Q gouvernant). Si V≈0, Qout = MIN(Qin, Q_plein). ΔV = (Qin_moy - Qout)*Δt. La courbe Courbe_QH_900 est en formules live (changer n/L/entrée/TW).</t>
         </is>
@@ -5302,7 +5314,7 @@
           <t>Aire (m²)</t>
         </is>
       </c>
-      <c r="B5" s="38">
+      <c r="B5" s="39">
         <f>Parametres!B24</f>
         <v/>
       </c>
@@ -5313,7 +5325,7 @@
           <t>Q_plein réf. (m³/s)</t>
         </is>
       </c>
-      <c r="B6" s="38">
+      <c r="B6" s="39">
         <f>Parametres!B22</f>
         <v/>
       </c>
@@ -5324,7 +5336,7 @@
           <t>Vmax_B (m³)</t>
         </is>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="29">
         <f>MAX(G12:G24)</f>
         <v/>
       </c>
@@ -5399,7 +5411,7 @@
       <c r="F12" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="31" t="n">
+      <c r="G12" s="32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5428,7 +5440,7 @@
         <f>(A13-A12)*60</f>
         <v/>
       </c>
-      <c r="G13" s="31">
+      <c r="G13" s="32">
         <f>MAX(0,G12+(0.5*(B12+B13)-E13)*F13)</f>
         <v/>
       </c>
@@ -5458,7 +5470,7 @@
         <f>(A14-A13)*60</f>
         <v/>
       </c>
-      <c r="G14" s="31">
+      <c r="G14" s="32">
         <f>MAX(0,G13+(0.5*(B13+B14)-E14)*F14)</f>
         <v/>
       </c>
@@ -5488,7 +5500,7 @@
         <f>(A15-A14)*60</f>
         <v/>
       </c>
-      <c r="G15" s="31">
+      <c r="G15" s="32">
         <f>MAX(0,G14+(0.5*(B14+B15)-E15)*F15)</f>
         <v/>
       </c>
@@ -5518,7 +5530,7 @@
         <f>(A16-A15)*60</f>
         <v/>
       </c>
-      <c r="G16" s="31">
+      <c r="G16" s="32">
         <f>MAX(0,G15+(0.5*(B15+B16)-E16)*F16)</f>
         <v/>
       </c>
@@ -5548,7 +5560,7 @@
         <f>(A17-A16)*60</f>
         <v/>
       </c>
-      <c r="G17" s="31">
+      <c r="G17" s="32">
         <f>MAX(0,G16+(0.5*(B16+B17)-E17)*F17)</f>
         <v/>
       </c>
@@ -5578,7 +5590,7 @@
         <f>(A18-A17)*60</f>
         <v/>
       </c>
-      <c r="G18" s="31">
+      <c r="G18" s="32">
         <f>MAX(0,G17+(0.5*(B17+B18)-E18)*F18)</f>
         <v/>
       </c>
@@ -5608,7 +5620,7 @@
         <f>(A19-A18)*60</f>
         <v/>
       </c>
-      <c r="G19" s="31">
+      <c r="G19" s="32">
         <f>MAX(0,G18+(0.5*(B18+B19)-E19)*F19)</f>
         <v/>
       </c>
@@ -5638,7 +5650,7 @@
         <f>(A20-A19)*60</f>
         <v/>
       </c>
-      <c r="G20" s="31">
+      <c r="G20" s="32">
         <f>MAX(0,G19+(0.5*(B19+B20)-E20)*F20)</f>
         <v/>
       </c>
@@ -5668,7 +5680,7 @@
         <f>(A21-A20)*60</f>
         <v/>
       </c>
-      <c r="G21" s="31">
+      <c r="G21" s="32">
         <f>MAX(0,G20+(0.5*(B20+B21)-E21)*F21)</f>
         <v/>
       </c>
@@ -5698,7 +5710,7 @@
         <f>(A22-A21)*60</f>
         <v/>
       </c>
-      <c r="G22" s="31">
+      <c r="G22" s="32">
         <f>MAX(0,G21+(0.5*(B21+B22)-E22)*F22)</f>
         <v/>
       </c>
@@ -5728,7 +5740,7 @@
         <f>(A23-A22)*60</f>
         <v/>
       </c>
-      <c r="G23" s="31">
+      <c r="G23" s="32">
         <f>MAX(0,G22+(0.5*(B22+B23)-E23)*F23)</f>
         <v/>
       </c>
@@ -5758,7 +5770,7 @@
         <f>(A24-A23)*60</f>
         <v/>
       </c>
-      <c r="G24" s="31">
+      <c r="G24" s="32">
         <f>MAX(0,G23+(0.5*(B23+B24)-E24)*F24)</f>
         <v/>
       </c>
@@ -5821,7 +5833,7 @@
           <t>Crest (m)</t>
         </is>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="12">
         <f>Parametres!B27</f>
         <v/>
       </c>
@@ -5832,7 +5844,7 @@
           <t>b (m)</t>
         </is>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="12">
         <f>Parametres!B28</f>
         <v/>
       </c>
@@ -5887,7 +5899,7 @@
           <t>Zin Ø900 (m)</t>
         </is>
       </c>
-      <c r="B12" s="16">
+      <c r="B12" s="12">
         <f>34.88</f>
         <v/>
       </c>
@@ -5950,14 +5962,14 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="29" t="n">
+      <c r="A15" s="30" t="n">
         <v>34.88</v>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="30">
         <f>A15-$B$12</f>
         <v/>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="30">
         <f>MAX(0,A15-$B$6)</f>
         <v/>
       </c>
@@ -5973,7 +5985,7 @@
         <f>IF(A15&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A15&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A15,Stage_Storage!$A$11:$A$18,1))+(A15-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A15,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A15,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A15,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A15,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A15,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G15" s="31">
+      <c r="G15" s="32">
         <f>E15+F15</f>
         <v/>
       </c>
@@ -5995,14 +6007,14 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="29" t="n">
+      <c r="A16" s="30" t="n">
         <v>34.93</v>
       </c>
-      <c r="B16" s="29">
+      <c r="B16" s="30">
         <f>A16-$B$12</f>
         <v/>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="30">
         <f>MAX(0,A16-$B$6)</f>
         <v/>
       </c>
@@ -6018,7 +6030,7 @@
         <f>IF(A16&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A16&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A16,Stage_Storage!$A$11:$A$18,1))+(A16-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A16,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A16,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A16,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A16,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A16,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G16" s="31">
+      <c r="G16" s="32">
         <f>E16+F16</f>
         <v/>
       </c>
@@ -6040,14 +6052,14 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="29" t="n">
+      <c r="A17" s="30" t="n">
         <v>34.98</v>
       </c>
-      <c r="B17" s="29">
+      <c r="B17" s="30">
         <f>A17-$B$12</f>
         <v/>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="30">
         <f>MAX(0,A17-$B$6)</f>
         <v/>
       </c>
@@ -6063,7 +6075,7 @@
         <f>IF(A17&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A17&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A17,Stage_Storage!$A$11:$A$18,1))+(A17-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A17,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A17,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A17,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A17,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A17,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G17" s="31">
+      <c r="G17" s="32">
         <f>E17+F17</f>
         <v/>
       </c>
@@ -6085,14 +6097,14 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="29" t="n">
+      <c r="A18" s="30" t="n">
         <v>35.03</v>
       </c>
-      <c r="B18" s="29">
+      <c r="B18" s="30">
         <f>A18-$B$12</f>
         <v/>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="30">
         <f>MAX(0,A18-$B$6)</f>
         <v/>
       </c>
@@ -6108,7 +6120,7 @@
         <f>IF(A18&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A18&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A18,Stage_Storage!$A$11:$A$18,1))+(A18-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A18,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A18,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A18,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A18,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A18,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G18" s="31">
+      <c r="G18" s="32">
         <f>E18+F18</f>
         <v/>
       </c>
@@ -6130,14 +6142,14 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="29" t="n">
+      <c r="A19" s="30" t="n">
         <v>35.08</v>
       </c>
-      <c r="B19" s="29">
+      <c r="B19" s="30">
         <f>A19-$B$12</f>
         <v/>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="30">
         <f>MAX(0,A19-$B$6)</f>
         <v/>
       </c>
@@ -6153,7 +6165,7 @@
         <f>IF(A19&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A19&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A19,Stage_Storage!$A$11:$A$18,1))+(A19-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A19,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A19,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A19,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A19,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A19,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G19" s="31">
+      <c r="G19" s="32">
         <f>E19+F19</f>
         <v/>
       </c>
@@ -6175,14 +6187,14 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="n">
+      <c r="A20" s="30" t="n">
         <v>35.13</v>
       </c>
-      <c r="B20" s="29">
+      <c r="B20" s="30">
         <f>A20-$B$12</f>
         <v/>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="30">
         <f>MAX(0,A20-$B$6)</f>
         <v/>
       </c>
@@ -6198,7 +6210,7 @@
         <f>IF(A20&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A20&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A20,Stage_Storage!$A$11:$A$18,1))+(A20-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A20,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A20,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A20,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A20,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A20,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G20" s="31">
+      <c r="G20" s="32">
         <f>E20+F20</f>
         <v/>
       </c>
@@ -6220,14 +6232,14 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="29" t="n">
+      <c r="A21" s="30" t="n">
         <v>35.18</v>
       </c>
-      <c r="B21" s="29">
+      <c r="B21" s="30">
         <f>A21-$B$12</f>
         <v/>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="30">
         <f>MAX(0,A21-$B$6)</f>
         <v/>
       </c>
@@ -6243,7 +6255,7 @@
         <f>IF(A21&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A21&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A21,Stage_Storage!$A$11:$A$18,1))+(A21-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A21,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A21,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A21,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A21,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A21,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G21" s="31">
+      <c r="G21" s="32">
         <f>E21+F21</f>
         <v/>
       </c>
@@ -6265,14 +6277,14 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="29" t="n">
+      <c r="A22" s="30" t="n">
         <v>35.23</v>
       </c>
-      <c r="B22" s="29">
+      <c r="B22" s="30">
         <f>A22-$B$12</f>
         <v/>
       </c>
-      <c r="C22" s="29">
+      <c r="C22" s="30">
         <f>MAX(0,A22-$B$6)</f>
         <v/>
       </c>
@@ -6288,7 +6300,7 @@
         <f>IF(A22&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A22&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A22,Stage_Storage!$A$11:$A$18,1))+(A22-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A22,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A22,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A22,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A22,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A22,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G22" s="31">
+      <c r="G22" s="32">
         <f>E22+F22</f>
         <v/>
       </c>
@@ -6310,14 +6322,14 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="29" t="n">
+      <c r="A23" s="30" t="n">
         <v>35.28</v>
       </c>
-      <c r="B23" s="29">
+      <c r="B23" s="30">
         <f>A23-$B$12</f>
         <v/>
       </c>
-      <c r="C23" s="29">
+      <c r="C23" s="30">
         <f>MAX(0,A23-$B$6)</f>
         <v/>
       </c>
@@ -6333,7 +6345,7 @@
         <f>IF(A23&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A23&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A23,Stage_Storage!$A$11:$A$18,1))+(A23-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A23,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A23,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A23,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A23,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A23,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G23" s="31">
+      <c r="G23" s="32">
         <f>E23+F23</f>
         <v/>
       </c>
@@ -6355,14 +6367,14 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="29" t="n">
+      <c r="A24" s="30" t="n">
         <v>35.33</v>
       </c>
-      <c r="B24" s="29">
+      <c r="B24" s="30">
         <f>A24-$B$12</f>
         <v/>
       </c>
-      <c r="C24" s="29">
+      <c r="C24" s="30">
         <f>MAX(0,A24-$B$6)</f>
         <v/>
       </c>
@@ -6378,7 +6390,7 @@
         <f>IF(A24&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A24&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A24,Stage_Storage!$A$11:$A$18,1))+(A24-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A24,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A24,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A24,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A24,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A24,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G24" s="31">
+      <c r="G24" s="32">
         <f>E24+F24</f>
         <v/>
       </c>
@@ -6400,14 +6412,14 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="29" t="n">
+      <c r="A25" s="30" t="n">
         <v>35.38</v>
       </c>
-      <c r="B25" s="29">
+      <c r="B25" s="30">
         <f>A25-$B$12</f>
         <v/>
       </c>
-      <c r="C25" s="29">
+      <c r="C25" s="30">
         <f>MAX(0,A25-$B$6)</f>
         <v/>
       </c>
@@ -6423,7 +6435,7 @@
         <f>IF(A25&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A25&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A25,Stage_Storage!$A$11:$A$18,1))+(A25-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A25,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A25,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A25,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A25,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A25,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G25" s="31">
+      <c r="G25" s="32">
         <f>E25+F25</f>
         <v/>
       </c>
@@ -6445,14 +6457,14 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="29" t="n">
+      <c r="A26" s="30" t="n">
         <v>35.43</v>
       </c>
-      <c r="B26" s="29">
+      <c r="B26" s="30">
         <f>A26-$B$12</f>
         <v/>
       </c>
-      <c r="C26" s="29">
+      <c r="C26" s="30">
         <f>MAX(0,A26-$B$6)</f>
         <v/>
       </c>
@@ -6468,7 +6480,7 @@
         <f>IF(A26&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A26&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A26,Stage_Storage!$A$11:$A$18,1))+(A26-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A26,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A26,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A26,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A26,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A26,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G26" s="31">
+      <c r="G26" s="32">
         <f>E26+F26</f>
         <v/>
       </c>
@@ -6490,14 +6502,14 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="29" t="n">
+      <c r="A27" s="30" t="n">
         <v>35.48</v>
       </c>
-      <c r="B27" s="29">
+      <c r="B27" s="30">
         <f>A27-$B$12</f>
         <v/>
       </c>
-      <c r="C27" s="29">
+      <c r="C27" s="30">
         <f>MAX(0,A27-$B$6)</f>
         <v/>
       </c>
@@ -6513,7 +6525,7 @@
         <f>IF(A27&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A27&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A27,Stage_Storage!$A$11:$A$18,1))+(A27-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A27,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A27,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A27,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A27,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A27,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G27" s="31">
+      <c r="G27" s="32">
         <f>E27+F27</f>
         <v/>
       </c>
@@ -6535,14 +6547,14 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="29" t="n">
+      <c r="A28" s="30" t="n">
         <v>35.53</v>
       </c>
-      <c r="B28" s="29">
+      <c r="B28" s="30">
         <f>A28-$B$12</f>
         <v/>
       </c>
-      <c r="C28" s="29">
+      <c r="C28" s="30">
         <f>MAX(0,A28-$B$6)</f>
         <v/>
       </c>
@@ -6558,7 +6570,7 @@
         <f>IF(A28&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A28&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A28,Stage_Storage!$A$11:$A$18,1))+(A28-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A28,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A28,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A28,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A28,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A28,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G28" s="31">
+      <c r="G28" s="32">
         <f>E28+F28</f>
         <v/>
       </c>
@@ -6580,14 +6592,14 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="29" t="n">
+      <c r="A29" s="30" t="n">
         <v>35.58</v>
       </c>
-      <c r="B29" s="29">
+      <c r="B29" s="30">
         <f>A29-$B$12</f>
         <v/>
       </c>
-      <c r="C29" s="29">
+      <c r="C29" s="30">
         <f>MAX(0,A29-$B$6)</f>
         <v/>
       </c>
@@ -6603,7 +6615,7 @@
         <f>IF(A29&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A29&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A29,Stage_Storage!$A$11:$A$18,1))+(A29-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A29,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A29,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A29,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A29,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A29,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G29" s="31">
+      <c r="G29" s="32">
         <f>E29+F29</f>
         <v/>
       </c>
@@ -6625,14 +6637,14 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="29" t="n">
+      <c r="A30" s="30" t="n">
         <v>35.63</v>
       </c>
-      <c r="B30" s="29">
+      <c r="B30" s="30">
         <f>A30-$B$12</f>
         <v/>
       </c>
-      <c r="C30" s="29">
+      <c r="C30" s="30">
         <f>MAX(0,A30-$B$6)</f>
         <v/>
       </c>
@@ -6648,7 +6660,7 @@
         <f>IF(A30&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A30&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A30,Stage_Storage!$A$11:$A$18,1))+(A30-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A30,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A30,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A30,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A30,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A30,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G30" s="31">
+      <c r="G30" s="32">
         <f>E30+F30</f>
         <v/>
       </c>
@@ -6670,14 +6682,14 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="29" t="n">
+      <c r="A31" s="30" t="n">
         <v>35.68</v>
       </c>
-      <c r="B31" s="29">
+      <c r="B31" s="30">
         <f>A31-$B$12</f>
         <v/>
       </c>
-      <c r="C31" s="29">
+      <c r="C31" s="30">
         <f>MAX(0,A31-$B$6)</f>
         <v/>
       </c>
@@ -6693,7 +6705,7 @@
         <f>IF(A31&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A31&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A31,Stage_Storage!$A$11:$A$18,1))+(A31-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A31,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A31,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A31,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A31,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A31,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G31" s="31">
+      <c r="G31" s="32">
         <f>E31+F31</f>
         <v/>
       </c>
@@ -6715,14 +6727,14 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="29" t="n">
+      <c r="A32" s="30" t="n">
         <v>35.73</v>
       </c>
-      <c r="B32" s="29">
+      <c r="B32" s="30">
         <f>A32-$B$12</f>
         <v/>
       </c>
-      <c r="C32" s="29">
+      <c r="C32" s="30">
         <f>MAX(0,A32-$B$6)</f>
         <v/>
       </c>
@@ -6738,7 +6750,7 @@
         <f>IF(A32&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A32&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A32,Stage_Storage!$A$11:$A$18,1))+(A32-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A32,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A32,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A32,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A32,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A32,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G32" s="31">
+      <c r="G32" s="32">
         <f>E32+F32</f>
         <v/>
       </c>
@@ -6760,14 +6772,14 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="36" t="n">
+      <c r="A33" s="37" t="n">
         <v>35.78</v>
       </c>
-      <c r="B33" s="36">
+      <c r="B33" s="37">
         <f>A33-$B$12</f>
         <v/>
       </c>
-      <c r="C33" s="36">
+      <c r="C33" s="37">
         <f>MAX(0,A33-$B$6)</f>
         <v/>
       </c>
@@ -6775,15 +6787,15 @@
         <f>IF(C33&lt;=0,0,($B$7+$B$9*C33)*C33)</f>
         <v/>
       </c>
-      <c r="E33" s="39">
+      <c r="E33" s="40">
         <f>D33*$B$11</f>
         <v/>
       </c>
-      <c r="F33" s="39">
+      <c r="F33" s="40">
         <f>IF(A33&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A33&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A33,Stage_Storage!$A$11:$A$18,1))+(A33-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A33,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A33,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A33,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A33,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A33,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G33" s="31">
+      <c r="G33" s="32">
         <f>E33+F33</f>
         <v/>
       </c>
@@ -6805,14 +6817,14 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="29" t="n">
+      <c r="A34" s="30" t="n">
         <v>35.83</v>
       </c>
-      <c r="B34" s="29">
+      <c r="B34" s="30">
         <f>A34-$B$12</f>
         <v/>
       </c>
-      <c r="C34" s="29">
+      <c r="C34" s="30">
         <f>MAX(0,A34-$B$6)</f>
         <v/>
       </c>
@@ -6828,7 +6840,7 @@
         <f>IF(A34&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A34&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A34,Stage_Storage!$A$11:$A$18,1))+(A34-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A34,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A34,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A34,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A34,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A34,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G34" s="31">
+      <c r="G34" s="32">
         <f>E34+F34</f>
         <v/>
       </c>
@@ -6850,14 +6862,14 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="29" t="n">
+      <c r="A35" s="30" t="n">
         <v>35.88</v>
       </c>
-      <c r="B35" s="29">
+      <c r="B35" s="30">
         <f>A35-$B$12</f>
         <v/>
       </c>
-      <c r="C35" s="29">
+      <c r="C35" s="30">
         <f>MAX(0,A35-$B$6)</f>
         <v/>
       </c>
@@ -6873,7 +6885,7 @@
         <f>IF(A35&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A35&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A35,Stage_Storage!$A$11:$A$18,1))+(A35-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A35,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A35,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A35,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A35,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A35,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G35" s="31">
+      <c r="G35" s="32">
         <f>E35+F35</f>
         <v/>
       </c>
@@ -6895,14 +6907,14 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="29" t="n">
+      <c r="A36" s="30" t="n">
         <v>35.93</v>
       </c>
-      <c r="B36" s="29">
+      <c r="B36" s="30">
         <f>A36-$B$12</f>
         <v/>
       </c>
-      <c r="C36" s="29">
+      <c r="C36" s="30">
         <f>MAX(0,A36-$B$6)</f>
         <v/>
       </c>
@@ -6918,7 +6930,7 @@
         <f>IF(A36&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A36&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A36,Stage_Storage!$A$11:$A$18,1))+(A36-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A36,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A36,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A36,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A36,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A36,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G36" s="31">
+      <c r="G36" s="32">
         <f>E36+F36</f>
         <v/>
       </c>
@@ -6940,14 +6952,14 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="29" t="n">
+      <c r="A37" s="30" t="n">
         <v>35.98</v>
       </c>
-      <c r="B37" s="29">
+      <c r="B37" s="30">
         <f>A37-$B$12</f>
         <v/>
       </c>
-      <c r="C37" s="29">
+      <c r="C37" s="30">
         <f>MAX(0,A37-$B$6)</f>
         <v/>
       </c>
@@ -6963,7 +6975,7 @@
         <f>IF(A37&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A37&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A37,Stage_Storage!$A$11:$A$18,1))+(A37-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A37,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A37,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A37,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A37,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A37,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G37" s="31">
+      <c r="G37" s="32">
         <f>E37+F37</f>
         <v/>
       </c>
@@ -6985,14 +6997,14 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="29" t="n">
+      <c r="A38" s="30" t="n">
         <v>36.03</v>
       </c>
-      <c r="B38" s="29">
+      <c r="B38" s="30">
         <f>A38-$B$12</f>
         <v/>
       </c>
-      <c r="C38" s="29">
+      <c r="C38" s="30">
         <f>MAX(0,A38-$B$6)</f>
         <v/>
       </c>
@@ -7008,7 +7020,7 @@
         <f>IF(A38&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A38&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A38,Stage_Storage!$A$11:$A$18,1))+(A38-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A38,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A38,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A38,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A38,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A38,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G38" s="31">
+      <c r="G38" s="32">
         <f>E38+F38</f>
         <v/>
       </c>
@@ -7030,14 +7042,14 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="29" t="n">
+      <c r="A39" s="30" t="n">
         <v>36.08</v>
       </c>
-      <c r="B39" s="29">
+      <c r="B39" s="30">
         <f>A39-$B$12</f>
         <v/>
       </c>
-      <c r="C39" s="29">
+      <c r="C39" s="30">
         <f>MAX(0,A39-$B$6)</f>
         <v/>
       </c>
@@ -7053,7 +7065,7 @@
         <f>IF(A39&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A39&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A39,Stage_Storage!$A$11:$A$18,1))+(A39-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A39,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A39,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A39,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A39,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A39,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G39" s="31">
+      <c r="G39" s="32">
         <f>E39+F39</f>
         <v/>
       </c>
@@ -7075,14 +7087,14 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="29" t="n">
+      <c r="A40" s="30" t="n">
         <v>36.13</v>
       </c>
-      <c r="B40" s="29">
+      <c r="B40" s="30">
         <f>A40-$B$12</f>
         <v/>
       </c>
-      <c r="C40" s="29">
+      <c r="C40" s="30">
         <f>MAX(0,A40-$B$6)</f>
         <v/>
       </c>
@@ -7098,7 +7110,7 @@
         <f>IF(A40&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A40&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A40,Stage_Storage!$A$11:$A$18,1))+(A40-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A40,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A40,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A40,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A40,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A40,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G40" s="31">
+      <c r="G40" s="32">
         <f>E40+F40</f>
         <v/>
       </c>
@@ -7120,14 +7132,14 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="29" t="n">
+      <c r="A41" s="30" t="n">
         <v>36.18</v>
       </c>
-      <c r="B41" s="29">
+      <c r="B41" s="30">
         <f>A41-$B$12</f>
         <v/>
       </c>
-      <c r="C41" s="29">
+      <c r="C41" s="30">
         <f>MAX(0,A41-$B$6)</f>
         <v/>
       </c>
@@ -7143,7 +7155,7 @@
         <f>IF(A41&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A41&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A41,Stage_Storage!$A$11:$A$18,1))+(A41-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A41,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A41,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A41,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A41,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A41,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G41" s="31">
+      <c r="G41" s="32">
         <f>E41+F41</f>
         <v/>
       </c>
@@ -7165,14 +7177,14 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="29" t="n">
+      <c r="A42" s="30" t="n">
         <v>36.23</v>
       </c>
-      <c r="B42" s="29">
+      <c r="B42" s="30">
         <f>A42-$B$12</f>
         <v/>
       </c>
-      <c r="C42" s="29">
+      <c r="C42" s="30">
         <f>MAX(0,A42-$B$6)</f>
         <v/>
       </c>
@@ -7188,7 +7200,7 @@
         <f>IF(A42&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A42&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A42,Stage_Storage!$A$11:$A$18,1))+(A42-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A42,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A42,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A42,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A42,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A42,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G42" s="31">
+      <c r="G42" s="32">
         <f>E42+F42</f>
         <v/>
       </c>
@@ -7210,14 +7222,14 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="29" t="n">
+      <c r="A43" s="30" t="n">
         <v>36.28</v>
       </c>
-      <c r="B43" s="29">
+      <c r="B43" s="30">
         <f>A43-$B$12</f>
         <v/>
       </c>
-      <c r="C43" s="29">
+      <c r="C43" s="30">
         <f>MAX(0,A43-$B$6)</f>
         <v/>
       </c>
@@ -7233,7 +7245,7 @@
         <f>IF(A43&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A43&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A43,Stage_Storage!$A$11:$A$18,1))+(A43-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A43,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A43,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A43,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A43,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A43,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G43" s="31">
+      <c r="G43" s="32">
         <f>E43+F43</f>
         <v/>
       </c>
@@ -7255,14 +7267,14 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="29" t="n">
+      <c r="A44" s="30" t="n">
         <v>36.33</v>
       </c>
-      <c r="B44" s="29">
+      <c r="B44" s="30">
         <f>A44-$B$12</f>
         <v/>
       </c>
-      <c r="C44" s="29">
+      <c r="C44" s="30">
         <f>MAX(0,A44-$B$6)</f>
         <v/>
       </c>
@@ -7278,7 +7290,7 @@
         <f>IF(A44&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A44&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A44,Stage_Storage!$A$11:$A$18,1))+(A44-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A44,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A44,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A44,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A44,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A44,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G44" s="31">
+      <c r="G44" s="32">
         <f>E44+F44</f>
         <v/>
       </c>
@@ -7300,14 +7312,14 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="29" t="n">
+      <c r="A45" s="30" t="n">
         <v>36.38</v>
       </c>
-      <c r="B45" s="29">
+      <c r="B45" s="30">
         <f>A45-$B$12</f>
         <v/>
       </c>
-      <c r="C45" s="29">
+      <c r="C45" s="30">
         <f>MAX(0,A45-$B$6)</f>
         <v/>
       </c>
@@ -7323,7 +7335,7 @@
         <f>IF(A45&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A45&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A45,Stage_Storage!$A$11:$A$18,1))+(A45-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A45,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A45,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A45,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A45,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A45,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G45" s="31">
+      <c r="G45" s="32">
         <f>E45+F45</f>
         <v/>
       </c>
@@ -7345,14 +7357,14 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="29" t="n">
+      <c r="A46" s="30" t="n">
         <v>36.43</v>
       </c>
-      <c r="B46" s="29">
+      <c r="B46" s="30">
         <f>A46-$B$12</f>
         <v/>
       </c>
-      <c r="C46" s="29">
+      <c r="C46" s="30">
         <f>MAX(0,A46-$B$6)</f>
         <v/>
       </c>
@@ -7368,7 +7380,7 @@
         <f>IF(A46&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A46&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A46,Stage_Storage!$A$11:$A$18,1))+(A46-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A46,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A46,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A46,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A46,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A46,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G46" s="31">
+      <c r="G46" s="32">
         <f>E46+F46</f>
         <v/>
       </c>
@@ -7390,14 +7402,14 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="29" t="n">
+      <c r="A47" s="30" t="n">
         <v>36.48</v>
       </c>
-      <c r="B47" s="29">
+      <c r="B47" s="30">
         <f>A47-$B$12</f>
         <v/>
       </c>
-      <c r="C47" s="29">
+      <c r="C47" s="30">
         <f>MAX(0,A47-$B$6)</f>
         <v/>
       </c>
@@ -7413,7 +7425,7 @@
         <f>IF(A47&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A47&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A47,Stage_Storage!$A$11:$A$18,1))+(A47-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A47,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A47,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A47,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A47,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A47,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G47" s="31">
+      <c r="G47" s="32">
         <f>E47+F47</f>
         <v/>
       </c>
@@ -7435,14 +7447,14 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="29" t="n">
+      <c r="A48" s="30" t="n">
         <v>36.53</v>
       </c>
-      <c r="B48" s="29">
+      <c r="B48" s="30">
         <f>A48-$B$12</f>
         <v/>
       </c>
-      <c r="C48" s="29">
+      <c r="C48" s="30">
         <f>MAX(0,A48-$B$6)</f>
         <v/>
       </c>
@@ -7458,7 +7470,7 @@
         <f>IF(A48&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A48&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A48,Stage_Storage!$A$11:$A$18,1))+(A48-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A48,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A48,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A48,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A48,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A48,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G48" s="31">
+      <c r="G48" s="32">
         <f>E48+F48</f>
         <v/>
       </c>
@@ -7480,14 +7492,14 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="29" t="n">
+      <c r="A49" s="30" t="n">
         <v>36.58</v>
       </c>
-      <c r="B49" s="29">
+      <c r="B49" s="30">
         <f>A49-$B$12</f>
         <v/>
       </c>
-      <c r="C49" s="29">
+      <c r="C49" s="30">
         <f>MAX(0,A49-$B$6)</f>
         <v/>
       </c>
@@ -7503,7 +7515,7 @@
         <f>IF(A49&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A49&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A49,Stage_Storage!$A$11:$A$18,1))+(A49-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A49,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A49,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A49,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A49,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A49,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G49" s="31">
+      <c r="G49" s="32">
         <f>E49+F49</f>
         <v/>
       </c>
@@ -7525,14 +7537,14 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="29" t="n">
+      <c r="A50" s="30" t="n">
         <v>36.63</v>
       </c>
-      <c r="B50" s="29">
+      <c r="B50" s="30">
         <f>A50-$B$12</f>
         <v/>
       </c>
-      <c r="C50" s="29">
+      <c r="C50" s="30">
         <f>MAX(0,A50-$B$6)</f>
         <v/>
       </c>
@@ -7548,7 +7560,7 @@
         <f>IF(A50&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A50&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A50,Stage_Storage!$A$11:$A$18,1))+(A50-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A50,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A50,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A50,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A50,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A50,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G50" s="31">
+      <c r="G50" s="32">
         <f>E50+F50</f>
         <v/>
       </c>
@@ -7570,14 +7582,14 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="29" t="n">
+      <c r="A51" s="30" t="n">
         <v>36.68</v>
       </c>
-      <c r="B51" s="29">
+      <c r="B51" s="30">
         <f>A51-$B$12</f>
         <v/>
       </c>
-      <c r="C51" s="29">
+      <c r="C51" s="30">
         <f>MAX(0,A51-$B$6)</f>
         <v/>
       </c>
@@ -7593,7 +7605,7 @@
         <f>IF(A51&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A51&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A51,Stage_Storage!$A$11:$A$18,1))+(A51-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A51,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A51,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A51,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A51,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A51,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G51" s="31">
+      <c r="G51" s="32">
         <f>E51+F51</f>
         <v/>
       </c>
@@ -7615,14 +7627,14 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="29" t="n">
+      <c r="A52" s="30" t="n">
         <v>36.73</v>
       </c>
-      <c r="B52" s="29">
+      <c r="B52" s="30">
         <f>A52-$B$12</f>
         <v/>
       </c>
-      <c r="C52" s="29">
+      <c r="C52" s="30">
         <f>MAX(0,A52-$B$6)</f>
         <v/>
       </c>
@@ -7638,7 +7650,7 @@
         <f>IF(A52&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A52&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A52,Stage_Storage!$A$11:$A$18,1))+(A52-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A52,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A52,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A52,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A52,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A52,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G52" s="31">
+      <c r="G52" s="32">
         <f>E52+F52</f>
         <v/>
       </c>
@@ -7660,14 +7672,14 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="29" t="n">
+      <c r="A53" s="30" t="n">
         <v>36.78</v>
       </c>
-      <c r="B53" s="29">
+      <c r="B53" s="30">
         <f>A53-$B$12</f>
         <v/>
       </c>
-      <c r="C53" s="29">
+      <c r="C53" s="30">
         <f>MAX(0,A53-$B$6)</f>
         <v/>
       </c>
@@ -7683,7 +7695,7 @@
         <f>IF(A53&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A53&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A53,Stage_Storage!$A$11:$A$18,1))+(A53-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A53,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A53,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A53,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A53,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A53,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G53" s="31">
+      <c r="G53" s="32">
         <f>E53+F53</f>
         <v/>
       </c>
@@ -7705,14 +7717,14 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="29" t="n">
+      <c r="A54" s="30" t="n">
         <v>36.83</v>
       </c>
-      <c r="B54" s="29">
+      <c r="B54" s="30">
         <f>A54-$B$12</f>
         <v/>
       </c>
-      <c r="C54" s="29">
+      <c r="C54" s="30">
         <f>MAX(0,A54-$B$6)</f>
         <v/>
       </c>
@@ -7728,7 +7740,7 @@
         <f>IF(A54&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A54&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A54,Stage_Storage!$A$11:$A$18,1))+(A54-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A54,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A54,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A54,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A54,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A54,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G54" s="31">
+      <c r="G54" s="32">
         <f>E54+F54</f>
         <v/>
       </c>
@@ -7750,14 +7762,14 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="29" t="n">
+      <c r="A55" s="30" t="n">
         <v>36.88</v>
       </c>
-      <c r="B55" s="29">
+      <c r="B55" s="30">
         <f>A55-$B$12</f>
         <v/>
       </c>
-      <c r="C55" s="29">
+      <c r="C55" s="30">
         <f>MAX(0,A55-$B$6)</f>
         <v/>
       </c>
@@ -7773,7 +7785,7 @@
         <f>IF(A55&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A55&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A55,Stage_Storage!$A$11:$A$18,1))+(A55-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A55,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A55,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A55,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A55,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A55,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G55" s="31">
+      <c r="G55" s="32">
         <f>E55+F55</f>
         <v/>
       </c>
@@ -7795,14 +7807,14 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="29" t="n">
+      <c r="A56" s="30" t="n">
         <v>36.93</v>
       </c>
-      <c r="B56" s="29">
+      <c r="B56" s="30">
         <f>A56-$B$12</f>
         <v/>
       </c>
-      <c r="C56" s="29">
+      <c r="C56" s="30">
         <f>MAX(0,A56-$B$6)</f>
         <v/>
       </c>
@@ -7818,7 +7830,7 @@
         <f>IF(A56&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A56&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A56,Stage_Storage!$A$11:$A$18,1))+(A56-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A56,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A56,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A56,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A56,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A56,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G56" s="31">
+      <c r="G56" s="32">
         <f>E56+F56</f>
         <v/>
       </c>
@@ -7840,14 +7852,14 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="29" t="n">
+      <c r="A57" s="30" t="n">
         <v>36.98</v>
       </c>
-      <c r="B57" s="29">
+      <c r="B57" s="30">
         <f>A57-$B$12</f>
         <v/>
       </c>
-      <c r="C57" s="29">
+      <c r="C57" s="30">
         <f>MAX(0,A57-$B$6)</f>
         <v/>
       </c>
@@ -7863,7 +7875,7 @@
         <f>IF(A57&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A57&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A57,Stage_Storage!$A$11:$A$18,1))+(A57-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A57,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A57,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A57,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A57,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A57,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G57" s="31">
+      <c r="G57" s="32">
         <f>E57+F57</f>
         <v/>
       </c>
@@ -7885,14 +7897,14 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="29" t="n">
+      <c r="A58" s="30" t="n">
         <v>37.03</v>
       </c>
-      <c r="B58" s="29">
+      <c r="B58" s="30">
         <f>A58-$B$12</f>
         <v/>
       </c>
-      <c r="C58" s="29">
+      <c r="C58" s="30">
         <f>MAX(0,A58-$B$6)</f>
         <v/>
       </c>
@@ -7908,7 +7920,7 @@
         <f>IF(A58&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A58&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A58,Stage_Storage!$A$11:$A$18,1))+(A58-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A58,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A58,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A58,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A58,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A58,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G58" s="31">
+      <c r="G58" s="32">
         <f>E58+F58</f>
         <v/>
       </c>
@@ -7930,14 +7942,14 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="29" t="n">
+      <c r="A59" s="30" t="n">
         <v>37.08</v>
       </c>
-      <c r="B59" s="29">
+      <c r="B59" s="30">
         <f>A59-$B$12</f>
         <v/>
       </c>
-      <c r="C59" s="29">
+      <c r="C59" s="30">
         <f>MAX(0,A59-$B$6)</f>
         <v/>
       </c>
@@ -7953,7 +7965,7 @@
         <f>IF(A59&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A59&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A59,Stage_Storage!$A$11:$A$18,1))+(A59-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A59,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A59,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A59,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A59,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A59,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G59" s="31">
+      <c r="G59" s="32">
         <f>E59+F59</f>
         <v/>
       </c>
@@ -7975,14 +7987,14 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="29" t="n">
+      <c r="A60" s="30" t="n">
         <v>37.13</v>
       </c>
-      <c r="B60" s="29">
+      <c r="B60" s="30">
         <f>A60-$B$12</f>
         <v/>
       </c>
-      <c r="C60" s="29">
+      <c r="C60" s="30">
         <f>MAX(0,A60-$B$6)</f>
         <v/>
       </c>
@@ -7998,7 +8010,7 @@
         <f>IF(A60&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A60&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1))+(A60-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G60" s="31">
+      <c r="G60" s="32">
         <f>E60+F60</f>
         <v/>
       </c>
@@ -8020,14 +8032,14 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="29" t="n">
+      <c r="A61" s="30" t="n">
         <v>37.18</v>
       </c>
-      <c r="B61" s="29">
+      <c r="B61" s="30">
         <f>A61-$B$12</f>
         <v/>
       </c>
-      <c r="C61" s="29">
+      <c r="C61" s="30">
         <f>MAX(0,A61-$B$6)</f>
         <v/>
       </c>
@@ -8043,7 +8055,7 @@
         <f>IF(A61&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A61&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1))+(A61-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G61" s="31">
+      <c r="G61" s="32">
         <f>E61+F61</f>
         <v/>
       </c>
@@ -8065,14 +8077,14 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="29" t="n">
+      <c r="A62" s="30" t="n">
         <v>37.23</v>
       </c>
-      <c r="B62" s="29">
+      <c r="B62" s="30">
         <f>A62-$B$12</f>
         <v/>
       </c>
-      <c r="C62" s="29">
+      <c r="C62" s="30">
         <f>MAX(0,A62-$B$6)</f>
         <v/>
       </c>
@@ -8088,7 +8100,7 @@
         <f>IF(A62&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A62&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1))+(A62-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G62" s="31">
+      <c r="G62" s="32">
         <f>E62+F62</f>
         <v/>
       </c>
@@ -8110,14 +8122,14 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="29" t="n">
+      <c r="A63" s="30" t="n">
         <v>37.28</v>
       </c>
-      <c r="B63" s="29">
+      <c r="B63" s="30">
         <f>A63-$B$12</f>
         <v/>
       </c>
-      <c r="C63" s="29">
+      <c r="C63" s="30">
         <f>MAX(0,A63-$B$6)</f>
         <v/>
       </c>
@@ -8133,7 +8145,7 @@
         <f>IF(A63&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A63&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1))+(A63-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G63" s="31">
+      <c r="G63" s="32">
         <f>E63+F63</f>
         <v/>
       </c>
@@ -8155,14 +8167,14 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="29" t="n">
+      <c r="A64" s="30" t="n">
         <v>37.33</v>
       </c>
-      <c r="B64" s="29">
+      <c r="B64" s="30">
         <f>A64-$B$12</f>
         <v/>
       </c>
-      <c r="C64" s="29">
+      <c r="C64" s="30">
         <f>MAX(0,A64-$B$6)</f>
         <v/>
       </c>
@@ -8178,7 +8190,7 @@
         <f>IF(A64&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A64&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1))+(A64-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G64" s="31">
+      <c r="G64" s="32">
         <f>E64+F64</f>
         <v/>
       </c>
@@ -8200,14 +8212,14 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="29" t="n">
+      <c r="A65" s="30" t="n">
         <v>37.38</v>
       </c>
-      <c r="B65" s="29">
+      <c r="B65" s="30">
         <f>A65-$B$12</f>
         <v/>
       </c>
-      <c r="C65" s="29">
+      <c r="C65" s="30">
         <f>MAX(0,A65-$B$6)</f>
         <v/>
       </c>
@@ -8223,7 +8235,7 @@
         <f>IF(A65&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A65&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1))+(A65-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G65" s="31">
+      <c r="G65" s="32">
         <f>E65+F65</f>
         <v/>
       </c>
@@ -8245,14 +8257,14 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="29" t="n">
+      <c r="A66" s="30" t="n">
         <v>37.43</v>
       </c>
-      <c r="B66" s="29">
+      <c r="B66" s="30">
         <f>A66-$B$12</f>
         <v/>
       </c>
-      <c r="C66" s="29">
+      <c r="C66" s="30">
         <f>MAX(0,A66-$B$6)</f>
         <v/>
       </c>
@@ -8268,7 +8280,7 @@
         <f>IF(A66&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A66&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1))+(A66-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G66" s="31">
+      <c r="G66" s="32">
         <f>E66+F66</f>
         <v/>
       </c>
@@ -8290,14 +8302,14 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="29" t="n">
+      <c r="A67" s="30" t="n">
         <v>37.48</v>
       </c>
-      <c r="B67" s="29">
+      <c r="B67" s="30">
         <f>A67-$B$12</f>
         <v/>
       </c>
-      <c r="C67" s="29">
+      <c r="C67" s="30">
         <f>MAX(0,A67-$B$6)</f>
         <v/>
       </c>
@@ -8313,7 +8325,7 @@
         <f>IF(A67&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A67&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A67,Stage_Storage!$A$11:$A$18,1))+(A67-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A67,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A67,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A67,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A67,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A67,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G67" s="31">
+      <c r="G67" s="32">
         <f>E67+F67</f>
         <v/>
       </c>
@@ -8335,14 +8347,14 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="29" t="n">
+      <c r="A68" s="30" t="n">
         <v>37.53</v>
       </c>
-      <c r="B68" s="29">
+      <c r="B68" s="30">
         <f>A68-$B$12</f>
         <v/>
       </c>
-      <c r="C68" s="29">
+      <c r="C68" s="30">
         <f>MAX(0,A68-$B$6)</f>
         <v/>
       </c>
@@ -8358,7 +8370,7 @@
         <f>IF(A68&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A68&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A68,Stage_Storage!$A$11:$A$18,1))+(A68-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A68,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A68,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A68,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A68,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A68,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G68" s="31">
+      <c r="G68" s="32">
         <f>E68+F68</f>
         <v/>
       </c>
@@ -8380,14 +8392,14 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="29" t="n">
+      <c r="A69" s="30" t="n">
         <v>37.58</v>
       </c>
-      <c r="B69" s="29">
+      <c r="B69" s="30">
         <f>A69-$B$12</f>
         <v/>
       </c>
-      <c r="C69" s="29">
+      <c r="C69" s="30">
         <f>MAX(0,A69-$B$6)</f>
         <v/>
       </c>
@@ -8403,7 +8415,7 @@
         <f>IF(A69&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A69&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A69,Stage_Storage!$A$11:$A$18,1))+(A69-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A69,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A69,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A69,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A69,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A69,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G69" s="31">
+      <c r="G69" s="32">
         <f>E69+F69</f>
         <v/>
       </c>
@@ -8425,14 +8437,14 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="29" t="n">
+      <c r="A70" s="30" t="n">
         <v>37.63</v>
       </c>
-      <c r="B70" s="29">
+      <c r="B70" s="30">
         <f>A70-$B$12</f>
         <v/>
       </c>
-      <c r="C70" s="29">
+      <c r="C70" s="30">
         <f>MAX(0,A70-$B$6)</f>
         <v/>
       </c>
@@ -8448,7 +8460,7 @@
         <f>IF(A70&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A70&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A70,Stage_Storage!$A$11:$A$18,1))+(A70-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A70,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A70,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A70,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A70,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A70,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G70" s="31">
+      <c r="G70" s="32">
         <f>E70+F70</f>
         <v/>
       </c>
@@ -8470,14 +8482,14 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="29" t="n">
+      <c r="A71" s="30" t="n">
         <v>37.68</v>
       </c>
-      <c r="B71" s="29">
+      <c r="B71" s="30">
         <f>A71-$B$12</f>
         <v/>
       </c>
-      <c r="C71" s="29">
+      <c r="C71" s="30">
         <f>MAX(0,A71-$B$6)</f>
         <v/>
       </c>
@@ -8493,7 +8505,7 @@
         <f>IF(A71&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A71&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A71,Stage_Storage!$A$11:$A$18,1))+(A71-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A71,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A71,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A71,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A71,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A71,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G71" s="31">
+      <c r="G71" s="32">
         <f>E71+F71</f>
         <v/>
       </c>
@@ -8515,14 +8527,14 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="29" t="n">
+      <c r="A72" s="30" t="n">
         <v>37.73</v>
       </c>
-      <c r="B72" s="29">
+      <c r="B72" s="30">
         <f>A72-$B$12</f>
         <v/>
       </c>
-      <c r="C72" s="29">
+      <c r="C72" s="30">
         <f>MAX(0,A72-$B$6)</f>
         <v/>
       </c>
@@ -8538,7 +8550,7 @@
         <f>IF(A72&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A72&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A72,Stage_Storage!$A$11:$A$18,1))+(A72-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A72,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A72,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A72,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A72,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A72,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G72" s="31">
+      <c r="G72" s="32">
         <f>E72+F72</f>
         <v/>
       </c>
@@ -8560,14 +8572,14 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="29" t="n">
+      <c r="A73" s="30" t="n">
         <v>37.78</v>
       </c>
-      <c r="B73" s="29">
+      <c r="B73" s="30">
         <f>A73-$B$12</f>
         <v/>
       </c>
-      <c r="C73" s="29">
+      <c r="C73" s="30">
         <f>MAX(0,A73-$B$6)</f>
         <v/>
       </c>
@@ -8583,7 +8595,7 @@
         <f>IF(A73&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A73&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A73,Stage_Storage!$A$11:$A$18,1))+(A73-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A73,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A73,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A73,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A73,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A73,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G73" s="31">
+      <c r="G73" s="32">
         <f>E73+F73</f>
         <v/>
       </c>
@@ -8605,14 +8617,14 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="29" t="n">
+      <c r="A74" s="30" t="n">
         <v>37.83</v>
       </c>
-      <c r="B74" s="29">
+      <c r="B74" s="30">
         <f>A74-$B$12</f>
         <v/>
       </c>
-      <c r="C74" s="29">
+      <c r="C74" s="30">
         <f>MAX(0,A74-$B$6)</f>
         <v/>
       </c>
@@ -8628,7 +8640,7 @@
         <f>IF(A74&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A74&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A74,Stage_Storage!$A$11:$A$18,1))+(A74-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A74,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A74,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A74,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A74,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A74,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G74" s="31">
+      <c r="G74" s="32">
         <f>E74+F74</f>
         <v/>
       </c>
@@ -8650,14 +8662,14 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="29" t="n">
+      <c r="A75" s="30" t="n">
         <v>37.88</v>
       </c>
-      <c r="B75" s="29">
+      <c r="B75" s="30">
         <f>A75-$B$12</f>
         <v/>
       </c>
-      <c r="C75" s="29">
+      <c r="C75" s="30">
         <f>MAX(0,A75-$B$6)</f>
         <v/>
       </c>
@@ -8673,7 +8685,7 @@
         <f>IF(A75&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A75&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A75,Stage_Storage!$A$11:$A$18,1))+(A75-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A75,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A75,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A75,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A75,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A75,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G75" s="31">
+      <c r="G75" s="32">
         <f>E75+F75</f>
         <v/>
       </c>
@@ -8695,14 +8707,14 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="29" t="n">
+      <c r="A76" s="30" t="n">
         <v>37.93</v>
       </c>
-      <c r="B76" s="29">
+      <c r="B76" s="30">
         <f>A76-$B$12</f>
         <v/>
       </c>
-      <c r="C76" s="29">
+      <c r="C76" s="30">
         <f>MAX(0,A76-$B$6)</f>
         <v/>
       </c>
@@ -8718,7 +8730,7 @@
         <f>IF(A76&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A76&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A76,Stage_Storage!$A$11:$A$18,1))+(A76-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A76,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A76,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A76,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A76,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A76,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G76" s="31">
+      <c r="G76" s="32">
         <f>E76+F76</f>
         <v/>
       </c>
@@ -8740,14 +8752,14 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="29" t="n">
+      <c r="A77" s="30" t="n">
         <v>37.98</v>
       </c>
-      <c r="B77" s="29">
+      <c r="B77" s="30">
         <f>A77-$B$12</f>
         <v/>
       </c>
-      <c r="C77" s="29">
+      <c r="C77" s="30">
         <f>MAX(0,A77-$B$6)</f>
         <v/>
       </c>
@@ -8763,7 +8775,7 @@
         <f>IF(A77&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A77&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A77,Stage_Storage!$A$11:$A$18,1))+(A77-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A77,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A77,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A77,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A77,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A77,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G77" s="31">
+      <c r="G77" s="32">
         <f>E77+F77</f>
         <v/>
       </c>
@@ -8785,14 +8797,14 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="29" t="n">
+      <c r="A78" s="30" t="n">
         <v>38.03</v>
       </c>
-      <c r="B78" s="29">
+      <c r="B78" s="30">
         <f>A78-$B$12</f>
         <v/>
       </c>
-      <c r="C78" s="29">
+      <c r="C78" s="30">
         <f>MAX(0,A78-$B$6)</f>
         <v/>
       </c>
@@ -8808,7 +8820,7 @@
         <f>IF(A78&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A78&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A78,Stage_Storage!$A$11:$A$18,1))+(A78-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A78,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A78,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A78,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A78,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A78,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G78" s="31">
+      <c r="G78" s="32">
         <f>E78+F78</f>
         <v/>
       </c>
@@ -8830,14 +8842,14 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="29" t="n">
+      <c r="A79" s="30" t="n">
         <v>38.08</v>
       </c>
-      <c r="B79" s="29">
+      <c r="B79" s="30">
         <f>A79-$B$12</f>
         <v/>
       </c>
-      <c r="C79" s="29">
+      <c r="C79" s="30">
         <f>MAX(0,A79-$B$6)</f>
         <v/>
       </c>
@@ -8853,7 +8865,7 @@
         <f>IF(A79&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A79&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A79,Stage_Storage!$A$11:$A$18,1))+(A79-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A79,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A79,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A79,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A79,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A79,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G79" s="31">
+      <c r="G79" s="32">
         <f>E79+F79</f>
         <v/>
       </c>
@@ -8875,14 +8887,14 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="29" t="n">
+      <c r="A80" s="30" t="n">
         <v>38.13</v>
       </c>
-      <c r="B80" s="29">
+      <c r="B80" s="30">
         <f>A80-$B$12</f>
         <v/>
       </c>
-      <c r="C80" s="29">
+      <c r="C80" s="30">
         <f>MAX(0,A80-$B$6)</f>
         <v/>
       </c>
@@ -8898,7 +8910,7 @@
         <f>IF(A80&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A80&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A80,Stage_Storage!$A$11:$A$18,1))+(A80-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A80,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A80,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A80,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A80,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A80,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G80" s="31">
+      <c r="G80" s="32">
         <f>E80+F80</f>
         <v/>
       </c>
@@ -8920,14 +8932,14 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="29" t="n">
+      <c r="A81" s="30" t="n">
         <v>38.18</v>
       </c>
-      <c r="B81" s="29">
+      <c r="B81" s="30">
         <f>A81-$B$12</f>
         <v/>
       </c>
-      <c r="C81" s="29">
+      <c r="C81" s="30">
         <f>MAX(0,A81-$B$6)</f>
         <v/>
       </c>
@@ -8943,7 +8955,7 @@
         <f>IF(A81&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A81&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A81,Stage_Storage!$A$11:$A$18,1))+(A81-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A81,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A81,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A81,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A81,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A81,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G81" s="31">
+      <c r="G81" s="32">
         <f>E81+F81</f>
         <v/>
       </c>
@@ -8965,14 +8977,14 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="29" t="n">
+      <c r="A82" s="30" t="n">
         <v>38.23</v>
       </c>
-      <c r="B82" s="29">
+      <c r="B82" s="30">
         <f>A82-$B$12</f>
         <v/>
       </c>
-      <c r="C82" s="29">
+      <c r="C82" s="30">
         <f>MAX(0,A82-$B$6)</f>
         <v/>
       </c>
@@ -8988,7 +9000,7 @@
         <f>IF(A82&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A82&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A82,Stage_Storage!$A$11:$A$18,1))+(A82-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A82,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A82,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A82,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A82,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A82,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G82" s="31">
+      <c r="G82" s="32">
         <f>E82+F82</f>
         <v/>
       </c>
@@ -9010,14 +9022,14 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="29" t="n">
+      <c r="A83" s="30" t="n">
         <v>38.28</v>
       </c>
-      <c r="B83" s="29">
+      <c r="B83" s="30">
         <f>A83-$B$12</f>
         <v/>
       </c>
-      <c r="C83" s="29">
+      <c r="C83" s="30">
         <f>MAX(0,A83-$B$6)</f>
         <v/>
       </c>
@@ -9033,7 +9045,7 @@
         <f>IF(A83&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A83&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A83,Stage_Storage!$A$11:$A$18,1))+(A83-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A83,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A83,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A83,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A83,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A83,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G83" s="31">
+      <c r="G83" s="32">
         <f>E83+F83</f>
         <v/>
       </c>
@@ -9055,14 +9067,14 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="29" t="n">
+      <c r="A84" s="30" t="n">
         <v>38.33</v>
       </c>
-      <c r="B84" s="29">
+      <c r="B84" s="30">
         <f>A84-$B$12</f>
         <v/>
       </c>
-      <c r="C84" s="29">
+      <c r="C84" s="30">
         <f>MAX(0,A84-$B$6)</f>
         <v/>
       </c>
@@ -9078,7 +9090,7 @@
         <f>IF(A84&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A84&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A84,Stage_Storage!$A$11:$A$18,1))+(A84-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A84,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A84,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A84,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A84,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A84,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G84" s="31">
+      <c r="G84" s="32">
         <f>E84+F84</f>
         <v/>
       </c>
@@ -9100,14 +9112,14 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="29" t="n">
+      <c r="A85" s="30" t="n">
         <v>38.38</v>
       </c>
-      <c r="B85" s="29">
+      <c r="B85" s="30">
         <f>A85-$B$12</f>
         <v/>
       </c>
-      <c r="C85" s="29">
+      <c r="C85" s="30">
         <f>MAX(0,A85-$B$6)</f>
         <v/>
       </c>
@@ -9123,7 +9135,7 @@
         <f>IF(A85&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A85&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A85,Stage_Storage!$A$11:$A$18,1))+(A85-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A85,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A85,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A85,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A85,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A85,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G85" s="31">
+      <c r="G85" s="32">
         <f>E85+F85</f>
         <v/>
       </c>
@@ -9145,14 +9157,14 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="29" t="n">
+      <c r="A86" s="30" t="n">
         <v>38.43</v>
       </c>
-      <c r="B86" s="29">
+      <c r="B86" s="30">
         <f>A86-$B$12</f>
         <v/>
       </c>
-      <c r="C86" s="29">
+      <c r="C86" s="30">
         <f>MAX(0,A86-$B$6)</f>
         <v/>
       </c>
@@ -9168,7 +9180,7 @@
         <f>IF(A86&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A86&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A86,Stage_Storage!$A$11:$A$18,1))+(A86-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A86,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A86,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A86,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A86,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A86,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G86" s="31">
+      <c r="G86" s="32">
         <f>E86+F86</f>
         <v/>
       </c>
@@ -9190,14 +9202,14 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="29" t="n">
+      <c r="A87" s="30" t="n">
         <v>38.48</v>
       </c>
-      <c r="B87" s="29">
+      <c r="B87" s="30">
         <f>A87-$B$12</f>
         <v/>
       </c>
-      <c r="C87" s="29">
+      <c r="C87" s="30">
         <f>MAX(0,A87-$B$6)</f>
         <v/>
       </c>
@@ -9213,7 +9225,7 @@
         <f>IF(A87&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A87&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A87,Stage_Storage!$A$11:$A$18,1))+(A87-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A87,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A87,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A87,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A87,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A87,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G87" s="31">
+      <c r="G87" s="32">
         <f>E87+F87</f>
         <v/>
       </c>
@@ -9235,14 +9247,14 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="29" t="n">
+      <c r="A88" s="30" t="n">
         <v>38.53</v>
       </c>
-      <c r="B88" s="29">
+      <c r="B88" s="30">
         <f>A88-$B$12</f>
         <v/>
       </c>
-      <c r="C88" s="29">
+      <c r="C88" s="30">
         <f>MAX(0,A88-$B$6)</f>
         <v/>
       </c>
@@ -9258,7 +9270,7 @@
         <f>IF(A88&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A88&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A88,Stage_Storage!$A$11:$A$18,1))+(A88-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A88,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A88,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A88,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A88,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A88,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G88" s="31">
+      <c r="G88" s="32">
         <f>E88+F88</f>
         <v/>
       </c>
@@ -9280,14 +9292,14 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="29" t="n">
+      <c r="A89" s="30" t="n">
         <v>38.58</v>
       </c>
-      <c r="B89" s="29">
+      <c r="B89" s="30">
         <f>A89-$B$12</f>
         <v/>
       </c>
-      <c r="C89" s="29">
+      <c r="C89" s="30">
         <f>MAX(0,A89-$B$6)</f>
         <v/>
       </c>
@@ -9303,7 +9315,7 @@
         <f>IF(A89&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A89&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A89,Stage_Storage!$A$11:$A$18,1))+(A89-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A89,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A89,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A89,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A89,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A89,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G89" s="31">
+      <c r="G89" s="32">
         <f>E89+F89</f>
         <v/>
       </c>
@@ -9325,14 +9337,14 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="29" t="n">
+      <c r="A90" s="30" t="n">
         <v>38.63</v>
       </c>
-      <c r="B90" s="29">
+      <c r="B90" s="30">
         <f>A90-$B$12</f>
         <v/>
       </c>
-      <c r="C90" s="29">
+      <c r="C90" s="30">
         <f>MAX(0,A90-$B$6)</f>
         <v/>
       </c>
@@ -9348,7 +9360,7 @@
         <f>IF(A90&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A90&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A90,Stage_Storage!$A$11:$A$18,1))+(A90-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A90,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A90,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A90,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A90,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A90,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G90" s="31">
+      <c r="G90" s="32">
         <f>E90+F90</f>
         <v/>
       </c>
@@ -9370,14 +9382,14 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="29" t="n">
+      <c r="A91" s="30" t="n">
         <v>38.68</v>
       </c>
-      <c r="B91" s="29">
+      <c r="B91" s="30">
         <f>A91-$B$12</f>
         <v/>
       </c>
-      <c r="C91" s="29">
+      <c r="C91" s="30">
         <f>MAX(0,A91-$B$6)</f>
         <v/>
       </c>
@@ -9393,7 +9405,7 @@
         <f>IF(A91&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A91&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A91,Stage_Storage!$A$11:$A$18,1))+(A91-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A91,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A91,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A91,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A91,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A91,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G91" s="31">
+      <c r="G91" s="32">
         <f>E91+F91</f>
         <v/>
       </c>
@@ -9415,14 +9427,14 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="29" t="n">
+      <c r="A92" s="30" t="n">
         <v>38.73</v>
       </c>
-      <c r="B92" s="29">
+      <c r="B92" s="30">
         <f>A92-$B$12</f>
         <v/>
       </c>
-      <c r="C92" s="29">
+      <c r="C92" s="30">
         <f>MAX(0,A92-$B$6)</f>
         <v/>
       </c>
@@ -9438,7 +9450,7 @@
         <f>IF(A92&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A92&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A92,Stage_Storage!$A$11:$A$18,1))+(A92-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A92,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A92,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A92,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A92,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A92,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G92" s="31">
+      <c r="G92" s="32">
         <f>E92+F92</f>
         <v/>
       </c>
@@ -9460,14 +9472,14 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="29" t="n">
+      <c r="A93" s="30" t="n">
         <v>38.78</v>
       </c>
-      <c r="B93" s="29">
+      <c r="B93" s="30">
         <f>A93-$B$12</f>
         <v/>
       </c>
-      <c r="C93" s="29">
+      <c r="C93" s="30">
         <f>MAX(0,A93-$B$6)</f>
         <v/>
       </c>
@@ -9483,7 +9495,7 @@
         <f>IF(A93&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A93&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A93,Stage_Storage!$A$11:$A$18,1))+(A93-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A93,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A93,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A93,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A93,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A93,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G93" s="31">
+      <c r="G93" s="32">
         <f>E93+F93</f>
         <v/>
       </c>
@@ -9505,14 +9517,14 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="29" t="n">
+      <c r="A94" s="30" t="n">
         <v>38.83</v>
       </c>
-      <c r="B94" s="29">
+      <c r="B94" s="30">
         <f>A94-$B$12</f>
         <v/>
       </c>
-      <c r="C94" s="29">
+      <c r="C94" s="30">
         <f>MAX(0,A94-$B$6)</f>
         <v/>
       </c>
@@ -9528,7 +9540,7 @@
         <f>IF(A94&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A94&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A94,Stage_Storage!$A$11:$A$18,1))+(A94-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A94,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A94,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A94,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A94,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A94,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G94" s="31">
+      <c r="G94" s="32">
         <f>E94+F94</f>
         <v/>
       </c>
@@ -9550,14 +9562,14 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="29" t="n">
+      <c r="A95" s="30" t="n">
         <v>38.88</v>
       </c>
-      <c r="B95" s="29">
+      <c r="B95" s="30">
         <f>A95-$B$12</f>
         <v/>
       </c>
-      <c r="C95" s="29">
+      <c r="C95" s="30">
         <f>MAX(0,A95-$B$6)</f>
         <v/>
       </c>
@@ -9573,7 +9585,7 @@
         <f>IF(A95&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A95&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A95,Stage_Storage!$A$11:$A$18,1))+(A95-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A95,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A95,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A95,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A95,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A95,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G95" s="31">
+      <c r="G95" s="32">
         <f>E95+F95</f>
         <v/>
       </c>
@@ -9595,14 +9607,14 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="29" t="n">
+      <c r="A96" s="30" t="n">
         <v>38.93</v>
       </c>
-      <c r="B96" s="29">
+      <c r="B96" s="30">
         <f>A96-$B$12</f>
         <v/>
       </c>
-      <c r="C96" s="29">
+      <c r="C96" s="30">
         <f>MAX(0,A96-$B$6)</f>
         <v/>
       </c>
@@ -9618,7 +9630,7 @@
         <f>IF(A96&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A96&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A96,Stage_Storage!$A$11:$A$18,1))+(A96-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A96,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A96,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A96,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A96,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A96,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G96" s="31">
+      <c r="G96" s="32">
         <f>E96+F96</f>
         <v/>
       </c>
@@ -9640,14 +9652,14 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="29" t="n">
+      <c r="A97" s="30" t="n">
         <v>38.98</v>
       </c>
-      <c r="B97" s="29">
+      <c r="B97" s="30">
         <f>A97-$B$12</f>
         <v/>
       </c>
-      <c r="C97" s="29">
+      <c r="C97" s="30">
         <f>MAX(0,A97-$B$6)</f>
         <v/>
       </c>
@@ -9663,7 +9675,7 @@
         <f>IF(A97&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A97&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A97,Stage_Storage!$A$11:$A$18,1))+(A97-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A97,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A97,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A97,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A97,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A97,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G97" s="31">
+      <c r="G97" s="32">
         <f>E97+F97</f>
         <v/>
       </c>
@@ -9685,14 +9697,14 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="29" t="n">
+      <c r="A98" s="30" t="n">
         <v>39.03</v>
       </c>
-      <c r="B98" s="29">
+      <c r="B98" s="30">
         <f>A98-$B$12</f>
         <v/>
       </c>
-      <c r="C98" s="29">
+      <c r="C98" s="30">
         <f>MAX(0,A98-$B$6)</f>
         <v/>
       </c>
@@ -9708,7 +9720,7 @@
         <f>IF(A98&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A98&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A98,Stage_Storage!$A$11:$A$18,1))+(A98-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A98,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A98,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A98,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A98,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A98,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G98" s="31">
+      <c r="G98" s="32">
         <f>E98+F98</f>
         <v/>
       </c>
@@ -9730,14 +9742,14 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="29" t="n">
+      <c r="A99" s="30" t="n">
         <v>39.08</v>
       </c>
-      <c r="B99" s="29">
+      <c r="B99" s="30">
         <f>A99-$B$12</f>
         <v/>
       </c>
-      <c r="C99" s="29">
+      <c r="C99" s="30">
         <f>MAX(0,A99-$B$6)</f>
         <v/>
       </c>
@@ -9753,7 +9765,7 @@
         <f>IF(A99&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A99&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A99,Stage_Storage!$A$11:$A$18,1))+(A99-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A99,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A99,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A99,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A99,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A99,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G99" s="31">
+      <c r="G99" s="32">
         <f>E99+F99</f>
         <v/>
       </c>
@@ -9775,14 +9787,14 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="29" t="n">
+      <c r="A100" s="30" t="n">
         <v>39.13</v>
       </c>
-      <c r="B100" s="29">
+      <c r="B100" s="30">
         <f>A100-$B$12</f>
         <v/>
       </c>
-      <c r="C100" s="29">
+      <c r="C100" s="30">
         <f>MAX(0,A100-$B$6)</f>
         <v/>
       </c>
@@ -9798,7 +9810,7 @@
         <f>IF(A100&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A100&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A100,Stage_Storage!$A$11:$A$18,1))+(A100-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A100,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A100,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A100,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A100,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A100,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G100" s="31">
+      <c r="G100" s="32">
         <f>E100+F100</f>
         <v/>
       </c>
@@ -9820,14 +9832,14 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="29" t="n">
+      <c r="A101" s="30" t="n">
         <v>39.18</v>
       </c>
-      <c r="B101" s="29">
+      <c r="B101" s="30">
         <f>A101-$B$12</f>
         <v/>
       </c>
-      <c r="C101" s="29">
+      <c r="C101" s="30">
         <f>MAX(0,A101-$B$6)</f>
         <v/>
       </c>
@@ -9843,7 +9855,7 @@
         <f>IF(A101&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A101&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A101,Stage_Storage!$A$11:$A$18,1))+(A101-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A101,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A101,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A101,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A101,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A101,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G101" s="31">
+      <c r="G101" s="32">
         <f>E101+F101</f>
         <v/>
       </c>
@@ -9865,14 +9877,14 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="29" t="n">
+      <c r="A102" s="30" t="n">
         <v>39.23</v>
       </c>
-      <c r="B102" s="29">
+      <c r="B102" s="30">
         <f>A102-$B$12</f>
         <v/>
       </c>
-      <c r="C102" s="29">
+      <c r="C102" s="30">
         <f>MAX(0,A102-$B$6)</f>
         <v/>
       </c>
@@ -9888,7 +9900,7 @@
         <f>IF(A102&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A102&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A102,Stage_Storage!$A$11:$A$18,1))+(A102-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A102,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A102,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A102,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A102,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A102,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G102" s="31">
+      <c r="G102" s="32">
         <f>E102+F102</f>
         <v/>
       </c>
@@ -9910,14 +9922,14 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="29" t="n">
+      <c r="A103" s="30" t="n">
         <v>39.28</v>
       </c>
-      <c r="B103" s="29">
+      <c r="B103" s="30">
         <f>A103-$B$12</f>
         <v/>
       </c>
-      <c r="C103" s="29">
+      <c r="C103" s="30">
         <f>MAX(0,A103-$B$6)</f>
         <v/>
       </c>
@@ -9933,7 +9945,7 @@
         <f>IF(A103&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A103&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A103,Stage_Storage!$A$11:$A$18,1))+(A103-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A103,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A103,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A103,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A103,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A103,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G103" s="31">
+      <c r="G103" s="32">
         <f>E103+F103</f>
         <v/>
       </c>
@@ -9955,14 +9967,14 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="29" t="n">
+      <c r="A104" s="30" t="n">
         <v>39.33</v>
       </c>
-      <c r="B104" s="29">
+      <c r="B104" s="30">
         <f>A104-$B$12</f>
         <v/>
       </c>
-      <c r="C104" s="29">
+      <c r="C104" s="30">
         <f>MAX(0,A104-$B$6)</f>
         <v/>
       </c>
@@ -9978,7 +9990,7 @@
         <f>IF(A104&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A104&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A104,Stage_Storage!$A$11:$A$18,1))+(A104-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A104,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A104,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A104,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A104,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A104,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G104" s="31">
+      <c r="G104" s="32">
         <f>E104+F104</f>
         <v/>
       </c>
@@ -10000,14 +10012,14 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="29" t="n">
+      <c r="A105" s="30" t="n">
         <v>39.38</v>
       </c>
-      <c r="B105" s="29">
+      <c r="B105" s="30">
         <f>A105-$B$12</f>
         <v/>
       </c>
-      <c r="C105" s="29">
+      <c r="C105" s="30">
         <f>MAX(0,A105-$B$6)</f>
         <v/>
       </c>
@@ -10023,7 +10035,7 @@
         <f>IF(A105&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A105&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A105,Stage_Storage!$A$11:$A$18,1))+(A105-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A105,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A105,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A105,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A105,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A105,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G105" s="31">
+      <c r="G105" s="32">
         <f>E105+F105</f>
         <v/>
       </c>
@@ -10045,14 +10057,14 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="29" t="n">
+      <c r="A106" s="30" t="n">
         <v>39.43</v>
       </c>
-      <c r="B106" s="29">
+      <c r="B106" s="30">
         <f>A106-$B$12</f>
         <v/>
       </c>
-      <c r="C106" s="29">
+      <c r="C106" s="30">
         <f>MAX(0,A106-$B$6)</f>
         <v/>
       </c>
@@ -10068,7 +10080,7 @@
         <f>IF(A106&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A106&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A106,Stage_Storage!$A$11:$A$18,1))+(A106-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A106,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A106,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A106,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A106,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A106,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G106" s="31">
+      <c r="G106" s="32">
         <f>E106+F106</f>
         <v/>
       </c>
@@ -10090,14 +10102,14 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="29" t="n">
+      <c r="A107" s="30" t="n">
         <v>39.48</v>
       </c>
-      <c r="B107" s="29">
+      <c r="B107" s="30">
         <f>A107-$B$12</f>
         <v/>
       </c>
-      <c r="C107" s="29">
+      <c r="C107" s="30">
         <f>MAX(0,A107-$B$6)</f>
         <v/>
       </c>
@@ -10113,7 +10125,7 @@
         <f>IF(A107&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A107&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A107,Stage_Storage!$A$11:$A$18,1))+(A107-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A107,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A107,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A107,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A107,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A107,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G107" s="31">
+      <c r="G107" s="32">
         <f>E107+F107</f>
         <v/>
       </c>
@@ -10169,7 +10181,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="37" t="inlineStr">
+      <c r="A2" s="38" t="inlineStr">
         <is>
           <t>À chaque pas: WSE lu sur Compose_900!V_total → Qout sur Compose_900. ΔV = (Qin_moy − Qout)×Δt. Si V≈0, Qout = MIN(Qin, Q_plein).</t>
         </is>
@@ -10182,7 +10194,7 @@
           <t>Q_plein réf. (m³/s)</t>
         </is>
       </c>
-      <c r="B5" s="38">
+      <c r="B5" s="39">
         <f>Parametres!B22</f>
         <v/>
       </c>
@@ -10193,7 +10205,7 @@
           <t>Crest (m)</t>
         </is>
       </c>
-      <c r="B6" s="38">
+      <c r="B6" s="39">
         <f>Parametres!B27</f>
         <v/>
       </c>
@@ -10204,7 +10216,7 @@
           <t>Vmax_C (m³)</t>
         </is>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="29">
         <f>MAX(F12:F24)</f>
         <v/>
       </c>
@@ -10288,7 +10300,7 @@
       <c r="E12" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="31" t="n">
+      <c r="F12" s="32" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -10318,7 +10330,7 @@
         <f>(A13-A12)*60</f>
         <v/>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="32">
         <f>MAX(0,F12+(0.5*(B12+B13)-D13)*E13)</f>
         <v/>
       </c>
@@ -10348,7 +10360,7 @@
         <f>(A14-A13)*60</f>
         <v/>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="32">
         <f>MAX(0,F13+(0.5*(B13+B14)-D14)*E14)</f>
         <v/>
       </c>
@@ -10378,7 +10390,7 @@
         <f>(A15-A14)*60</f>
         <v/>
       </c>
-      <c r="F15" s="31">
+      <c r="F15" s="32">
         <f>MAX(0,F14+(0.5*(B14+B15)-D15)*E15)</f>
         <v/>
       </c>
@@ -10408,7 +10420,7 @@
         <f>(A16-A15)*60</f>
         <v/>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="32">
         <f>MAX(0,F15+(0.5*(B15+B16)-D16)*E16)</f>
         <v/>
       </c>
@@ -10438,7 +10450,7 @@
         <f>(A17-A16)*60</f>
         <v/>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="32">
         <f>MAX(0,F16+(0.5*(B16+B17)-D17)*E17)</f>
         <v/>
       </c>
@@ -10468,7 +10480,7 @@
         <f>(A18-A17)*60</f>
         <v/>
       </c>
-      <c r="F18" s="31">
+      <c r="F18" s="32">
         <f>MAX(0,F17+(0.5*(B17+B18)-D18)*E18)</f>
         <v/>
       </c>
@@ -10498,7 +10510,7 @@
         <f>(A19-A18)*60</f>
         <v/>
       </c>
-      <c r="F19" s="31">
+      <c r="F19" s="32">
         <f>MAX(0,F18+(0.5*(B18+B19)-D19)*E19)</f>
         <v/>
       </c>
@@ -10528,7 +10540,7 @@
         <f>(A20-A19)*60</f>
         <v/>
       </c>
-      <c r="F20" s="31">
+      <c r="F20" s="32">
         <f>MAX(0,F19+(0.5*(B19+B20)-D20)*E20)</f>
         <v/>
       </c>
@@ -10558,7 +10570,7 @@
         <f>(A21-A20)*60</f>
         <v/>
       </c>
-      <c r="F21" s="31">
+      <c r="F21" s="32">
         <f>MAX(0,F20+(0.5*(B20+B21)-D21)*E21)</f>
         <v/>
       </c>
@@ -10588,7 +10600,7 @@
         <f>(A22-A21)*60</f>
         <v/>
       </c>
-      <c r="F22" s="31">
+      <c r="F22" s="32">
         <f>MAX(0,F21+(0.5*(B21+B22)-D22)*E22)</f>
         <v/>
       </c>
@@ -10618,7 +10630,7 @@
         <f>(A23-A22)*60</f>
         <v/>
       </c>
-      <c r="F23" s="31">
+      <c r="F23" s="32">
         <f>MAX(0,F22+(0.5*(B22+B23)-D23)*E23)</f>
         <v/>
       </c>
@@ -10648,7 +10660,7 @@
         <f>(A24-A23)*60</f>
         <v/>
       </c>
-      <c r="F24" s="31">
+      <c r="F24" s="32">
         <f>MAX(0,F23+(0.5*(B23+B24)-D24)*E24)</f>
         <v/>
       </c>
@@ -10706,7 +10718,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="40" t="inlineStr">
+      <c r="A7" s="41" t="inlineStr">
         <is>
           <t>V_pas (m³) = (A_basse + A_haute) / 2 × (WSE_haute − WSE_basse)</t>
         </is>
@@ -10752,7 +10764,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="n">
+      <c r="A11" s="30" t="n">
         <v>34.88</v>
       </c>
       <c r="B11" s="17" t="n">
@@ -10774,13 +10786,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="29" t="n">
+      <c r="A12" s="30" t="n">
         <v>35.5</v>
       </c>
       <c r="B12" s="17" t="n">
         <v>80</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="30">
         <f>A12-A11</f>
         <v/>
       </c>
@@ -10788,7 +10800,7 @@
         <f>0.5*(B11+B12)*C12</f>
         <v/>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="32">
         <f>E11+D12</f>
         <v/>
       </c>
@@ -10799,13 +10811,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="n">
+      <c r="A13" s="30" t="n">
         <v>36</v>
       </c>
       <c r="B13" s="17" t="n">
         <v>180</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="30">
         <f>A13-A12</f>
         <v/>
       </c>
@@ -10813,7 +10825,7 @@
         <f>0.5*(B12+B13)*C13</f>
         <v/>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="32">
         <f>E12+D13</f>
         <v/>
       </c>
@@ -10824,13 +10836,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="29" t="n">
+      <c r="A14" s="30" t="n">
         <v>36.5</v>
       </c>
       <c r="B14" s="17" t="n">
         <v>320</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="30">
         <f>A14-A13</f>
         <v/>
       </c>
@@ -10838,7 +10850,7 @@
         <f>0.5*(B13+B14)*C14</f>
         <v/>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="32">
         <f>E13+D14</f>
         <v/>
       </c>
@@ -10849,13 +10861,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="29" t="n">
+      <c r="A15" s="30" t="n">
         <v>37</v>
       </c>
       <c r="B15" s="17" t="n">
         <v>480</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="30">
         <f>A15-A14</f>
         <v/>
       </c>
@@ -10863,7 +10875,7 @@
         <f>0.5*(B14+B15)*C15</f>
         <v/>
       </c>
-      <c r="E15" s="31">
+      <c r="E15" s="32">
         <f>E14+D15</f>
         <v/>
       </c>
@@ -10874,21 +10886,21 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="36" t="n">
+      <c r="A16" s="37" t="n">
         <v>37.28</v>
       </c>
       <c r="B16" s="17" t="n">
         <v>543</v>
       </c>
-      <c r="C16" s="36">
+      <c r="C16" s="37">
         <f>A16-A15</f>
         <v/>
       </c>
-      <c r="D16" s="39">
+      <c r="D16" s="40">
         <f>0.5*(B15+B16)*C16</f>
         <v/>
       </c>
-      <c r="E16" s="39">
+      <c r="E16" s="40">
         <f>E15+D16</f>
         <v/>
       </c>
@@ -10899,13 +10911,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="29" t="n">
+      <c r="A17" s="30" t="n">
         <v>37.5</v>
       </c>
       <c r="B17" s="17" t="n">
         <v>700</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="30">
         <f>A17-A16</f>
         <v/>
       </c>
@@ -10913,7 +10925,7 @@
         <f>0.5*(B16+B17)*C17</f>
         <v/>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="32">
         <f>E16+D17</f>
         <v/>
       </c>
@@ -10924,13 +10936,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="29" t="n">
+      <c r="A18" s="30" t="n">
         <v>39.5</v>
       </c>
       <c r="B18" s="17" t="n">
         <v>1932</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="30">
         <f>A18-A17</f>
         <v/>
       </c>
@@ -10938,7 +10950,7 @@
         <f>0.5*(B17+B18)*C18</f>
         <v/>
       </c>
-      <c r="E18" s="31">
+      <c r="E18" s="32">
         <f>E17+D18</f>
         <v/>
       </c>
@@ -10965,7 +10977,7 @@
           <t>WSEmax_A (m)</t>
         </is>
       </c>
-      <c r="B22" s="40">
+      <c r="B22" s="41">
         <f>Parametres!B39</f>
         <v/>
       </c>
@@ -10987,7 +10999,7 @@
           <t>WSEmax_B (m)</t>
         </is>
       </c>
-      <c r="B24" s="40">
+      <c r="B24" s="41">
         <f>Parametres!B45</f>
         <v/>
       </c>
@@ -11018,7 +11030,7 @@
           <t>V disponible à 37.28 m (m³)</t>
         </is>
       </c>
-      <c r="B26" s="41">
+      <c r="B26" s="42">
         <f>E16</f>
         <v/>
       </c>
@@ -11036,7 +11048,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="37" t="inlineStr">
+      <c r="A29" s="38" t="inlineStr">
         <is>
           <t>Exemple: si Vmax_A = 5609 m³ et V(37.28)≈558 m³, alors WSEmax_A est au-dessus de 37.28 m (la table ira vers 39.5 m ou 'Hors table'). Affinez en entrant les vraies surfaces aux cotes intermédiaires (jaune). Méthode C: voir Parametres B49–B52 et Calcul_C (fossé inclus).</t>
         </is>
@@ -11069,7 +11081,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="42" t="inlineStr">
+      <c r="A1" s="43" t="inlineStr">
         <is>
           <t>Où sont les fichiers HY-8 / capacité ?</t>
         </is>

--- a/engineering/drainage-design/retention_volume/Volume_Retention_Ponceau_900.xlsx
+++ b/engineering/drainage-design/retention_volume/Volume_Retention_Ponceau_900.xlsx
@@ -125,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -147,6 +147,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1935,7 +1936,7 @@
           <t>S pente fossé (-)</t>
         </is>
       </c>
-      <c r="B31" s="11" t="n">
+      <c r="B31" s="19" t="n">
         <v>0.008500000000000001</v>
       </c>
       <c r="C31" t="inlineStr">
@@ -1962,17 +1963,34 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Qout_C</t>
+          <t>Qout_C (débit sortie)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Q_900(WSE)+Q_overflow(WSE)</t>
+          <t>Q_900(WSE) + Q_overflow(WSE)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>V_C = V_pond(levé) + V_ditch — feuilles Compose_900 + Calcul_C</t>
+          <t>Débit = pipe + fossé (Compose_900). Ceci n'est PAS un volume.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Stockage_C (volume)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>V_pond(levé) + V_ditch</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Volume = bassin (levé) + fossé — Compose_900 + Calcul_C</t>
         </is>
       </c>
     </row>
@@ -1989,7 +2007,7 @@
           <t>Vmax_A (m³)</t>
         </is>
       </c>
-      <c r="B36" s="19">
+      <c r="B36" s="20">
         <f>Calcul_A!B3</f>
         <v/>
       </c>
@@ -2005,7 +2023,7 @@
           <t>V_dimensionnement_A = Vmax_A × facteur (m³)</t>
         </is>
       </c>
-      <c r="B37" s="19">
+      <c r="B37" s="20">
         <f>B36*B23</f>
         <v/>
       </c>
@@ -2016,7 +2034,7 @@
           <t>Hmax approx_A (m) = Vmax_A / Aire</t>
         </is>
       </c>
-      <c r="B38" s="20">
+      <c r="B38" s="21">
         <f>IF(B24&gt;0,B36/B24,0)</f>
         <v/>
       </c>
@@ -2032,7 +2050,7 @@
           <t>WSEmax_A depuis levé (m) — feuille Stage_Storage</t>
         </is>
       </c>
-      <c r="B39" s="21">
+      <c r="B39" s="22">
         <f>IF(B36&lt;=Stage_Storage!E11,Stage_Storage!A11,IF(B36&gt;=Stage_Storage!E18,"Hors table (&gt;=39.5 m — étendre levé)",INDEX(Stage_Storage!$A$11:$A$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1))+(B36-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)))/(INDEX(Stage_Storage!$E$11:$E$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)))*(INDEX(Stage_Storage!$A$11:$A$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)))))</f>
         <v/>
       </c>
@@ -2048,7 +2066,7 @@
           <t>HW max_A = WSEmax_A − radier Ø900 (m)</t>
         </is>
       </c>
-      <c r="B40" s="21">
+      <c r="B40" s="22">
         <f>IF(ISNUMBER(B39),B39-34.88,"")</f>
         <v/>
       </c>
@@ -2071,7 +2089,7 @@
           <t>Vmax_B (m³)</t>
         </is>
       </c>
-      <c r="B43" s="19">
+      <c r="B43" s="20">
         <f>Calcul_B!B7</f>
         <v/>
       </c>
@@ -2087,7 +2105,7 @@
           <t>V_dimensionnement_B = Vmax_B × facteur (m³)</t>
         </is>
       </c>
-      <c r="B44" s="19">
+      <c r="B44" s="20">
         <f>B43*B23</f>
         <v/>
       </c>
@@ -2098,7 +2116,7 @@
           <t>WSEmax_B depuis levé (m) — feuille Stage_Storage</t>
         </is>
       </c>
-      <c r="B45" s="21">
+      <c r="B45" s="22">
         <f>IF(B43&lt;=Stage_Storage!E11,Stage_Storage!A11,IF(B43&gt;=Stage_Storage!E18,"Hors table (&gt;=39.5 m — étendre levé)",INDEX(Stage_Storage!$A$11:$A$18,MATCH(B43,Stage_Storage!$E$11:$E$18,1))+(B43-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B43,Stage_Storage!$E$11:$E$18,1)))/(INDEX(Stage_Storage!$E$11:$E$18,MATCH(B43,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B43,Stage_Storage!$E$11:$E$18,1)))*(INDEX(Stage_Storage!$A$11:$A$18,MATCH(B43,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(B43,Stage_Storage!$E$11:$E$18,1)))))</f>
         <v/>
       </c>
@@ -2114,7 +2132,7 @@
           <t>HW max_B = WSEmax_B − radier Ø900 (m)</t>
         </is>
       </c>
-      <c r="B46" s="21">
+      <c r="B46" s="22">
         <f>IF(ISNUMBER(B45),B45-34.88,"")</f>
         <v/>
       </c>
@@ -2137,7 +2155,7 @@
           <t>Vmax_C (m³) = max(V_pond + V_ditch)</t>
         </is>
       </c>
-      <c r="B49" s="19">
+      <c r="B49" s="20">
         <f>Calcul_C!B7</f>
         <v/>
       </c>
@@ -2153,7 +2171,7 @@
           <t>V_dimensionnement_C = Vmax_C × facteur (m³)</t>
         </is>
       </c>
-      <c r="B50" s="19">
+      <c r="B50" s="20">
         <f>B49*B23</f>
         <v/>
       </c>
@@ -2164,7 +2182,7 @@
           <t>WSEmax_C (m) — du routage Calcul_C</t>
         </is>
       </c>
-      <c r="B51" s="21">
+      <c r="B51" s="22">
         <f>Calcul_C!B8</f>
         <v/>
       </c>
@@ -2180,7 +2198,7 @@
           <t>HW max_C = WSEmax_C − radier Ø900 (m)</t>
         </is>
       </c>
-      <c r="B52" s="21">
+      <c r="B52" s="22">
         <f>IF(ISNUMBER(B51),B51-34.88,"")</f>
         <v/>
       </c>
@@ -2369,7 +2387,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="44" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>Méthode — volume de rétention</t>
         </is>
@@ -2496,7 +2514,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Hydrogramme d'entrée (point Ø1500 / entrée rétention) — FORMULES LIVE</t>
         </is>
@@ -2531,7 +2549,7 @@
           <t>t pointe (min)</t>
         </is>
       </c>
-      <c r="B5" s="23" t="n">
+      <c r="B5" s="24" t="n">
         <v>22.5</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -2563,10 +2581,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="n">
+      <c r="A8" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="B8" s="25" t="n">
+      <c r="B8" s="26" t="n">
         <v>0.081042</v>
       </c>
       <c r="C8" s="5">
@@ -2580,10 +2598,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="n">
+      <c r="A9" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="25" t="n">
+      <c r="B9" s="26" t="n">
         <v>0.121875</v>
       </c>
       <c r="C9" s="5">
@@ -2593,10 +2611,10 @@
       <c r="D9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="n">
+      <c r="A10" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="B10" s="25" t="n">
+      <c r="B10" s="26" t="n">
         <v>0.193438</v>
       </c>
       <c r="C10" s="5">
@@ -2606,10 +2624,10 @@
       <c r="D10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="n">
+      <c r="A11" s="25" t="n">
         <v>15</v>
       </c>
-      <c r="B11" s="25" t="n">
+      <c r="B11" s="26" t="n">
         <v>0.333542</v>
       </c>
       <c r="C11" s="5">
@@ -2619,10 +2637,10 @@
       <c r="D11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="n">
+      <c r="A12" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="B12" s="25" t="n">
+      <c r="B12" s="26" t="n">
         <v>0.657188</v>
       </c>
       <c r="C12" s="5">
@@ -2632,10 +2650,10 @@
       <c r="D12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="n">
+      <c r="A13" s="25" t="n">
         <v>22.5</v>
       </c>
-      <c r="B13" s="25" t="n">
+      <c r="B13" s="26" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="8">
@@ -2649,10 +2667,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="n">
+      <c r="A14" s="25" t="n">
         <v>27.5</v>
       </c>
-      <c r="B14" s="25" t="n">
+      <c r="B14" s="26" t="n">
         <v>0.608958</v>
       </c>
       <c r="C14" s="5">
@@ -2662,10 +2680,10 @@
       <c r="D14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="n">
+      <c r="A15" s="25" t="n">
         <v>32.5</v>
       </c>
-      <c r="B15" s="25" t="n">
+      <c r="B15" s="26" t="n">
         <v>0.401771</v>
       </c>
       <c r="C15" s="5">
@@ -2675,10 +2693,10 @@
       <c r="D15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="n">
+      <c r="A16" s="25" t="n">
         <v>37.5</v>
       </c>
-      <c r="B16" s="25" t="n">
+      <c r="B16" s="26" t="n">
         <v>0.280104</v>
       </c>
       <c r="C16" s="5">
@@ -2688,10 +2706,10 @@
       <c r="D16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="n">
+      <c r="A17" s="25" t="n">
         <v>42.5</v>
       </c>
-      <c r="B17" s="25" t="n">
+      <c r="B17" s="26" t="n">
         <v>0.203438</v>
       </c>
       <c r="C17" s="5">
@@ -2701,10 +2719,10 @@
       <c r="D17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="n">
+      <c r="A18" s="25" t="n">
         <v>47.5</v>
       </c>
-      <c r="B18" s="25" t="n">
+      <c r="B18" s="26" t="n">
         <v>0.152292</v>
       </c>
       <c r="C18" s="5">
@@ -2714,10 +2732,10 @@
       <c r="D18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="24" t="n">
+      <c r="A19" s="25" t="n">
         <v>52.5</v>
       </c>
-      <c r="B19" s="25" t="n">
+      <c r="B19" s="26" t="n">
         <v>0.116771</v>
       </c>
       <c r="C19" s="5">
@@ -2727,10 +2745,10 @@
       <c r="D19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="24" t="n">
+      <c r="A20" s="25" t="n">
         <v>57.5</v>
       </c>
-      <c r="B20" s="25" t="n">
+      <c r="B20" s="26" t="n">
         <v>0.091146</v>
       </c>
       <c r="C20" s="5">
@@ -2745,7 +2763,7 @@
           <t>Qin max (contrôle)</t>
         </is>
       </c>
-      <c r="B22" s="26">
+      <c r="B22" s="27">
         <f>MAX(C8:C20)</f>
         <v/>
       </c>
@@ -2761,7 +2779,7 @@
           <t>Qcap Ø900 (réf.)</t>
         </is>
       </c>
-      <c r="B23" s="27">
+      <c r="B23" s="28">
         <f>Parametres!B22</f>
         <v/>
       </c>
@@ -2796,7 +2814,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Méthode A — Qout constant = capacité Ø900</t>
         </is>
@@ -2808,7 +2826,7 @@
           <t>Qout (m³/s)</t>
         </is>
       </c>
-      <c r="B2" s="28">
+      <c r="B2" s="29">
         <f>Parametres!B22</f>
         <v/>
       </c>
@@ -2819,7 +2837,7 @@
           <t>Vmax (m³)</t>
         </is>
       </c>
-      <c r="B3" s="29">
+      <c r="B3" s="30">
         <f>MAX(H8:H20)</f>
         <v/>
       </c>
@@ -2901,7 +2919,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24">
+      <c r="A8" s="25">
         <f>Hydrogramme!A8</f>
         <v/>
       </c>
@@ -2909,7 +2927,7 @@
         <f>Hydrogramme!C8</f>
         <v/>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <f>$B$2</f>
         <v/>
       </c>
@@ -2926,7 +2944,7 @@
       <c r="G8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="31" t="n">
+      <c r="H8" s="32" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="4">
@@ -2935,7 +2953,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24">
+      <c r="A9" s="25">
         <f>Hydrogramme!A9</f>
         <v/>
       </c>
@@ -2943,7 +2961,7 @@
         <f>Hydrogramme!C9</f>
         <v/>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <f>$B$2</f>
         <v/>
       </c>
@@ -2951,19 +2969,19 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="25">
         <f>(A9-A8)*60</f>
         <v/>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="25">
         <f>0.5*(B8+B9)*E9</f>
         <v/>
       </c>
-      <c r="G9" s="24">
+      <c r="G9" s="25">
         <f>F9-(H9-H8)</f>
         <v/>
       </c>
-      <c r="H9" s="32">
+      <c r="H9" s="33">
         <f>MAX(0,H8+0.5*(D8+D9)*E9)</f>
         <v/>
       </c>
@@ -2973,7 +2991,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24">
+      <c r="A10" s="25">
         <f>Hydrogramme!A10</f>
         <v/>
       </c>
@@ -2981,7 +2999,7 @@
         <f>Hydrogramme!C10</f>
         <v/>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="31">
         <f>$B$2</f>
         <v/>
       </c>
@@ -2989,19 +3007,19 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="25">
         <f>(A10-A9)*60</f>
         <v/>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="25">
         <f>0.5*(B9+B10)*E10</f>
         <v/>
       </c>
-      <c r="G10" s="24">
+      <c r="G10" s="25">
         <f>F10-(H10-H9)</f>
         <v/>
       </c>
-      <c r="H10" s="32">
+      <c r="H10" s="33">
         <f>MAX(0,H9+0.5*(D9+D10)*E10)</f>
         <v/>
       </c>
@@ -3011,7 +3029,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24">
+      <c r="A11" s="25">
         <f>Hydrogramme!A11</f>
         <v/>
       </c>
@@ -3019,7 +3037,7 @@
         <f>Hydrogramme!C11</f>
         <v/>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="31">
         <f>$B$2</f>
         <v/>
       </c>
@@ -3027,19 +3045,19 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="25">
         <f>(A11-A10)*60</f>
         <v/>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="25">
         <f>0.5*(B10+B11)*E11</f>
         <v/>
       </c>
-      <c r="G11" s="24">
+      <c r="G11" s="25">
         <f>F11-(H11-H10)</f>
         <v/>
       </c>
-      <c r="H11" s="32">
+      <c r="H11" s="33">
         <f>MAX(0,H10+0.5*(D10+D11)*E11)</f>
         <v/>
       </c>
@@ -3049,7 +3067,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="24">
+      <c r="A12" s="25">
         <f>Hydrogramme!A12</f>
         <v/>
       </c>
@@ -3057,7 +3075,7 @@
         <f>Hydrogramme!C12</f>
         <v/>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="31">
         <f>$B$2</f>
         <v/>
       </c>
@@ -3065,19 +3083,19 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="25">
         <f>(A12-A11)*60</f>
         <v/>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="25">
         <f>0.5*(B11+B12)*E12</f>
         <v/>
       </c>
-      <c r="G12" s="24">
+      <c r="G12" s="25">
         <f>F12-(H12-H11)</f>
         <v/>
       </c>
-      <c r="H12" s="32">
+      <c r="H12" s="33">
         <f>MAX(0,H11+0.5*(D11+D12)*E12)</f>
         <v/>
       </c>
@@ -3087,7 +3105,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24">
+      <c r="A13" s="25">
         <f>Hydrogramme!A13</f>
         <v/>
       </c>
@@ -3095,7 +3113,7 @@
         <f>Hydrogramme!C13</f>
         <v/>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <f>$B$2</f>
         <v/>
       </c>
@@ -3103,19 +3121,19 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="25">
         <f>(A13-A12)*60</f>
         <v/>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="25">
         <f>0.5*(B12+B13)*E13</f>
         <v/>
       </c>
-      <c r="G13" s="24">
+      <c r="G13" s="25">
         <f>F13-(H13-H12)</f>
         <v/>
       </c>
-      <c r="H13" s="32">
+      <c r="H13" s="33">
         <f>MAX(0,H12+0.5*(D12+D13)*E13)</f>
         <v/>
       </c>
@@ -3125,7 +3143,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="24">
+      <c r="A14" s="25">
         <f>Hydrogramme!A14</f>
         <v/>
       </c>
@@ -3133,7 +3151,7 @@
         <f>Hydrogramme!C14</f>
         <v/>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="31">
         <f>$B$2</f>
         <v/>
       </c>
@@ -3141,19 +3159,19 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="25">
         <f>(A14-A13)*60</f>
         <v/>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="25">
         <f>0.5*(B13+B14)*E14</f>
         <v/>
       </c>
-      <c r="G14" s="24">
+      <c r="G14" s="25">
         <f>F14-(H14-H13)</f>
         <v/>
       </c>
-      <c r="H14" s="32">
+      <c r="H14" s="33">
         <f>MAX(0,H13+0.5*(D13+D14)*E14)</f>
         <v/>
       </c>
@@ -3163,7 +3181,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="24">
+      <c r="A15" s="25">
         <f>Hydrogramme!A15</f>
         <v/>
       </c>
@@ -3171,7 +3189,7 @@
         <f>Hydrogramme!C15</f>
         <v/>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="31">
         <f>$B$2</f>
         <v/>
       </c>
@@ -3179,19 +3197,19 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="25">
         <f>(A15-A14)*60</f>
         <v/>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="25">
         <f>0.5*(B14+B15)*E15</f>
         <v/>
       </c>
-      <c r="G15" s="24">
+      <c r="G15" s="25">
         <f>F15-(H15-H14)</f>
         <v/>
       </c>
-      <c r="H15" s="32">
+      <c r="H15" s="33">
         <f>MAX(0,H14+0.5*(D14+D15)*E15)</f>
         <v/>
       </c>
@@ -3201,7 +3219,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="24">
+      <c r="A16" s="25">
         <f>Hydrogramme!A16</f>
         <v/>
       </c>
@@ -3209,7 +3227,7 @@
         <f>Hydrogramme!C16</f>
         <v/>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="31">
         <f>$B$2</f>
         <v/>
       </c>
@@ -3217,19 +3235,19 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="25">
         <f>(A16-A15)*60</f>
         <v/>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="25">
         <f>0.5*(B15+B16)*E16</f>
         <v/>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="25">
         <f>F16-(H16-H15)</f>
         <v/>
       </c>
-      <c r="H16" s="32">
+      <c r="H16" s="33">
         <f>MAX(0,H15+0.5*(D15+D16)*E16)</f>
         <v/>
       </c>
@@ -3239,7 +3257,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24">
+      <c r="A17" s="25">
         <f>Hydrogramme!A17</f>
         <v/>
       </c>
@@ -3247,7 +3265,7 @@
         <f>Hydrogramme!C17</f>
         <v/>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="31">
         <f>$B$2</f>
         <v/>
       </c>
@@ -3255,19 +3273,19 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="25">
         <f>(A17-A16)*60</f>
         <v/>
       </c>
-      <c r="F17" s="24">
+      <c r="F17" s="25">
         <f>0.5*(B16+B17)*E17</f>
         <v/>
       </c>
-      <c r="G17" s="24">
+      <c r="G17" s="25">
         <f>F17-(H17-H16)</f>
         <v/>
       </c>
-      <c r="H17" s="32">
+      <c r="H17" s="33">
         <f>MAX(0,H16+0.5*(D16+D17)*E17)</f>
         <v/>
       </c>
@@ -3277,7 +3295,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="24">
+      <c r="A18" s="25">
         <f>Hydrogramme!A18</f>
         <v/>
       </c>
@@ -3285,7 +3303,7 @@
         <f>Hydrogramme!C18</f>
         <v/>
       </c>
-      <c r="C18" s="30">
+      <c r="C18" s="31">
         <f>$B$2</f>
         <v/>
       </c>
@@ -3293,19 +3311,19 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="25">
         <f>(A18-A17)*60</f>
         <v/>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="25">
         <f>0.5*(B17+B18)*E18</f>
         <v/>
       </c>
-      <c r="G18" s="24">
+      <c r="G18" s="25">
         <f>F18-(H18-H17)</f>
         <v/>
       </c>
-      <c r="H18" s="32">
+      <c r="H18" s="33">
         <f>MAX(0,H17+0.5*(D17+D18)*E18)</f>
         <v/>
       </c>
@@ -3315,7 +3333,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="24">
+      <c r="A19" s="25">
         <f>Hydrogramme!A19</f>
         <v/>
       </c>
@@ -3323,7 +3341,7 @@
         <f>Hydrogramme!C19</f>
         <v/>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="31">
         <f>$B$2</f>
         <v/>
       </c>
@@ -3331,19 +3349,19 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="25">
         <f>(A19-A18)*60</f>
         <v/>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="25">
         <f>0.5*(B18+B19)*E19</f>
         <v/>
       </c>
-      <c r="G19" s="24">
+      <c r="G19" s="25">
         <f>F19-(H19-H18)</f>
         <v/>
       </c>
-      <c r="H19" s="32">
+      <c r="H19" s="33">
         <f>MAX(0,H18+0.5*(D18+D19)*E19)</f>
         <v/>
       </c>
@@ -3353,7 +3371,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="24">
+      <c r="A20" s="25">
         <f>Hydrogramme!A20</f>
         <v/>
       </c>
@@ -3361,7 +3379,7 @@
         <f>Hydrogramme!C20</f>
         <v/>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="31">
         <f>$B$2</f>
         <v/>
       </c>
@@ -3369,19 +3387,19 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="24">
+      <c r="E20" s="25">
         <f>(A20-A19)*60</f>
         <v/>
       </c>
-      <c r="F20" s="24">
+      <c r="F20" s="25">
         <f>0.5*(B19+B20)*E20</f>
         <v/>
       </c>
-      <c r="G20" s="24">
+      <c r="G20" s="25">
         <f>F20-(H20-H19)</f>
         <v/>
       </c>
-      <c r="H20" s="32">
+      <c r="H20" s="33">
         <f>MAX(0,H19+0.5*(D19+D20)*E20)</f>
         <v/>
       </c>
@@ -3415,7 +3433,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Courbe de capacité Ø900 — Q = f(H) (FHWA HDS-5 inlet + outlet) — FORMULES LIVE</t>
         </is>
@@ -3455,32 +3473,32 @@
           <t>béton typ. 0.012–0.015</t>
         </is>
       </c>
-      <c r="E6" s="33" t="inlineStr">
+      <c r="E6" s="34" t="inlineStr">
         <is>
           <t>entrée</t>
         </is>
       </c>
-      <c r="F6" s="33" t="inlineStr">
+      <c r="F6" s="34" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="G6" s="33" t="inlineStr">
+      <c r="G6" s="34" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H6" s="33" t="inlineStr">
+      <c r="H6" s="34" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="I6" s="33" t="inlineStr">
+      <c r="I6" s="34" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J6" s="33" t="inlineStr">
+      <c r="J6" s="34" t="inlineStr">
         <is>
           <t>Ke</t>
         </is>
@@ -3596,7 +3614,7 @@
           <t>S0 = (Zin-Zout)/L</t>
         </is>
       </c>
-      <c r="B11" s="34">
+      <c r="B11" s="35">
         <f>(B9-B10)/B8</f>
         <v/>
       </c>
@@ -3627,7 +3645,7 @@
           <t>Entrée (texte exact)</t>
         </is>
       </c>
-      <c r="B13" s="35" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>square_edge</t>
         </is>
@@ -3644,7 +3662,7 @@
           <t>Q_plein Manning (réf.)</t>
         </is>
       </c>
-      <c r="B15" s="26">
+      <c r="B15" s="27">
         <f>(1/B6)*(PI()*B7^2/4)*((B7/4)^(2/3))*SQRT(B11)</f>
         <v/>
       </c>
@@ -3660,7 +3678,7 @@
           <t>K (lu)</t>
         </is>
       </c>
-      <c r="B17" s="36">
+      <c r="B17" s="37">
         <f>IFERROR(VLOOKUP(B13,$E$7:$J$9,2,FALSE),0.0098)</f>
         <v/>
       </c>
@@ -3671,7 +3689,7 @@
           <t>M (lu)</t>
         </is>
       </c>
-      <c r="B18" s="36">
+      <c r="B18" s="37">
         <f>IFERROR(VLOOKUP(B13,$E$7:$J$9,3,FALSE),2)</f>
         <v/>
       </c>
@@ -3682,7 +3700,7 @@
           <t>c (lu)</t>
         </is>
       </c>
-      <c r="B19" s="36">
+      <c r="B19" s="37">
         <f>IFERROR(VLOOKUP(B13,$E$7:$J$9,4,FALSE),0.0398)</f>
         <v/>
       </c>
@@ -3693,7 +3711,7 @@
           <t>Y (lu)</t>
         </is>
       </c>
-      <c r="B20" s="36">
+      <c r="B20" s="37">
         <f>IFERROR(VLOOKUP(B13,$E$7:$J$9,5,FALSE),0.67)</f>
         <v/>
       </c>
@@ -3704,7 +3722,7 @@
           <t>Ke (lu)</t>
         </is>
       </c>
-      <c r="B21" s="36">
+      <c r="B21" s="37">
         <f>IFERROR(VLOOKUP(B13,$E$7:$J$9,6,FALSE),0.5)</f>
         <v/>
       </c>
@@ -3742,10 +3760,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="30" t="n">
+      <c r="A24" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="B24" s="30">
+      <c r="B24" s="31">
         <f>$B$9+A24</f>
         <v/>
       </c>
@@ -3767,10 +3785,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="30" t="n">
+      <c r="A25" s="31" t="n">
         <v>0.05</v>
       </c>
-      <c r="B25" s="30">
+      <c r="B25" s="31">
         <f>$B$9+A25</f>
         <v/>
       </c>
@@ -3792,10 +3810,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="30" t="n">
+      <c r="A26" s="31" t="n">
         <v>0.1</v>
       </c>
-      <c r="B26" s="30">
+      <c r="B26" s="31">
         <f>$B$9+A26</f>
         <v/>
       </c>
@@ -3817,10 +3835,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="30" t="n">
+      <c r="A27" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="B27" s="30">
+      <c r="B27" s="31">
         <f>$B$9+A27</f>
         <v/>
       </c>
@@ -3842,10 +3860,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="30" t="n">
+      <c r="A28" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="B28" s="30">
+      <c r="B28" s="31">
         <f>$B$9+A28</f>
         <v/>
       </c>
@@ -3867,10 +3885,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="30" t="n">
+      <c r="A29" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="B29" s="30">
+      <c r="B29" s="31">
         <f>$B$9+A29</f>
         <v/>
       </c>
@@ -3892,10 +3910,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="30" t="n">
+      <c r="A30" s="31" t="n">
         <v>0.3</v>
       </c>
-      <c r="B30" s="30">
+      <c r="B30" s="31">
         <f>$B$9+A30</f>
         <v/>
       </c>
@@ -3917,10 +3935,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="30" t="n">
+      <c r="A31" s="31" t="n">
         <v>0.35</v>
       </c>
-      <c r="B31" s="30">
+      <c r="B31" s="31">
         <f>$B$9+A31</f>
         <v/>
       </c>
@@ -3942,10 +3960,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="30" t="n">
+      <c r="A32" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="B32" s="30">
+      <c r="B32" s="31">
         <f>$B$9+A32</f>
         <v/>
       </c>
@@ -3967,10 +3985,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="30" t="n">
+      <c r="A33" s="31" t="n">
         <v>0.45</v>
       </c>
-      <c r="B33" s="30">
+      <c r="B33" s="31">
         <f>$B$9+A33</f>
         <v/>
       </c>
@@ -3992,10 +4010,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="30" t="n">
+      <c r="A34" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="B34" s="30">
+      <c r="B34" s="31">
         <f>$B$9+A34</f>
         <v/>
       </c>
@@ -4017,10 +4035,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="30" t="n">
+      <c r="A35" s="31" t="n">
         <v>0.55</v>
       </c>
-      <c r="B35" s="30">
+      <c r="B35" s="31">
         <f>$B$9+A35</f>
         <v/>
       </c>
@@ -4042,10 +4060,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="30" t="n">
+      <c r="A36" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="B36" s="30">
+      <c r="B36" s="31">
         <f>$B$9+A36</f>
         <v/>
       </c>
@@ -4067,10 +4085,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="30" t="n">
+      <c r="A37" s="31" t="n">
         <v>0.65</v>
       </c>
-      <c r="B37" s="30">
+      <c r="B37" s="31">
         <f>$B$9+A37</f>
         <v/>
       </c>
@@ -4092,10 +4110,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="30" t="n">
+      <c r="A38" s="31" t="n">
         <v>0.7</v>
       </c>
-      <c r="B38" s="30">
+      <c r="B38" s="31">
         <f>$B$9+A38</f>
         <v/>
       </c>
@@ -4117,10 +4135,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="30" t="n">
+      <c r="A39" s="31" t="n">
         <v>0.75</v>
       </c>
-      <c r="B39" s="30">
+      <c r="B39" s="31">
         <f>$B$9+A39</f>
         <v/>
       </c>
@@ -4142,10 +4160,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="30" t="n">
+      <c r="A40" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="B40" s="30">
+      <c r="B40" s="31">
         <f>$B$9+A40</f>
         <v/>
       </c>
@@ -4167,10 +4185,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="30" t="n">
+      <c r="A41" s="31" t="n">
         <v>0.85</v>
       </c>
-      <c r="B41" s="30">
+      <c r="B41" s="31">
         <f>$B$9+A41</f>
         <v/>
       </c>
@@ -4192,10 +4210,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="30" t="n">
+      <c r="A42" s="31" t="n">
         <v>0.9</v>
       </c>
-      <c r="B42" s="30">
+      <c r="B42" s="31">
         <f>$B$9+A42</f>
         <v/>
       </c>
@@ -4217,10 +4235,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="30" t="n">
+      <c r="A43" s="31" t="n">
         <v>0.95</v>
       </c>
-      <c r="B43" s="30">
+      <c r="B43" s="31">
         <f>$B$9+A43</f>
         <v/>
       </c>
@@ -4242,10 +4260,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="30" t="n">
+      <c r="A44" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="B44" s="30">
+      <c r="B44" s="31">
         <f>$B$9+A44</f>
         <v/>
       </c>
@@ -4267,10 +4285,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="30" t="n">
+      <c r="A45" s="31" t="n">
         <v>1.05</v>
       </c>
-      <c r="B45" s="30">
+      <c r="B45" s="31">
         <f>$B$9+A45</f>
         <v/>
       </c>
@@ -4292,10 +4310,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="30" t="n">
+      <c r="A46" s="31" t="n">
         <v>1.1</v>
       </c>
-      <c r="B46" s="30">
+      <c r="B46" s="31">
         <f>$B$9+A46</f>
         <v/>
       </c>
@@ -4317,10 +4335,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="30" t="n">
+      <c r="A47" s="31" t="n">
         <v>1.15</v>
       </c>
-      <c r="B47" s="30">
+      <c r="B47" s="31">
         <f>$B$9+A47</f>
         <v/>
       </c>
@@ -4342,10 +4360,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="30" t="n">
+      <c r="A48" s="31" t="n">
         <v>1.2</v>
       </c>
-      <c r="B48" s="30">
+      <c r="B48" s="31">
         <f>$B$9+A48</f>
         <v/>
       </c>
@@ -4367,10 +4385,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="30" t="n">
+      <c r="A49" s="31" t="n">
         <v>1.25</v>
       </c>
-      <c r="B49" s="30">
+      <c r="B49" s="31">
         <f>$B$9+A49</f>
         <v/>
       </c>
@@ -4392,10 +4410,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="30" t="n">
+      <c r="A50" s="31" t="n">
         <v>1.3</v>
       </c>
-      <c r="B50" s="30">
+      <c r="B50" s="31">
         <f>$B$9+A50</f>
         <v/>
       </c>
@@ -4417,10 +4435,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="30" t="n">
+      <c r="A51" s="31" t="n">
         <v>1.35</v>
       </c>
-      <c r="B51" s="30">
+      <c r="B51" s="31">
         <f>$B$9+A51</f>
         <v/>
       </c>
@@ -4442,10 +4460,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="30" t="n">
+      <c r="A52" s="31" t="n">
         <v>1.4</v>
       </c>
-      <c r="B52" s="30">
+      <c r="B52" s="31">
         <f>$B$9+A52</f>
         <v/>
       </c>
@@ -4467,10 +4485,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="30" t="n">
+      <c r="A53" s="31" t="n">
         <v>1.45</v>
       </c>
-      <c r="B53" s="30">
+      <c r="B53" s="31">
         <f>$B$9+A53</f>
         <v/>
       </c>
@@ -4492,10 +4510,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="30" t="n">
+      <c r="A54" s="31" t="n">
         <v>1.5</v>
       </c>
-      <c r="B54" s="30">
+      <c r="B54" s="31">
         <f>$B$9+A54</f>
         <v/>
       </c>
@@ -4517,10 +4535,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="30" t="n">
+      <c r="A55" s="31" t="n">
         <v>1.55</v>
       </c>
-      <c r="B55" s="30">
+      <c r="B55" s="31">
         <f>$B$9+A55</f>
         <v/>
       </c>
@@ -4542,10 +4560,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="30" t="n">
+      <c r="A56" s="31" t="n">
         <v>1.6</v>
       </c>
-      <c r="B56" s="30">
+      <c r="B56" s="31">
         <f>$B$9+A56</f>
         <v/>
       </c>
@@ -4567,10 +4585,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="30" t="n">
+      <c r="A57" s="31" t="n">
         <v>1.65</v>
       </c>
-      <c r="B57" s="30">
+      <c r="B57" s="31">
         <f>$B$9+A57</f>
         <v/>
       </c>
@@ -4592,10 +4610,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="30" t="n">
+      <c r="A58" s="31" t="n">
         <v>1.7</v>
       </c>
-      <c r="B58" s="30">
+      <c r="B58" s="31">
         <f>$B$9+A58</f>
         <v/>
       </c>
@@ -4617,10 +4635,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="30" t="n">
+      <c r="A59" s="31" t="n">
         <v>1.75</v>
       </c>
-      <c r="B59" s="30">
+      <c r="B59" s="31">
         <f>$B$9+A59</f>
         <v/>
       </c>
@@ -4642,10 +4660,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="30" t="n">
+      <c r="A60" s="31" t="n">
         <v>1.8</v>
       </c>
-      <c r="B60" s="30">
+      <c r="B60" s="31">
         <f>$B$9+A60</f>
         <v/>
       </c>
@@ -4667,10 +4685,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="30" t="n">
+      <c r="A61" s="31" t="n">
         <v>1.85</v>
       </c>
-      <c r="B61" s="30">
+      <c r="B61" s="31">
         <f>$B$9+A61</f>
         <v/>
       </c>
@@ -4692,10 +4710,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="30" t="n">
+      <c r="A62" s="31" t="n">
         <v>1.9</v>
       </c>
-      <c r="B62" s="30">
+      <c r="B62" s="31">
         <f>$B$9+A62</f>
         <v/>
       </c>
@@ -4717,10 +4735,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="30" t="n">
+      <c r="A63" s="31" t="n">
         <v>1.95</v>
       </c>
-      <c r="B63" s="30">
+      <c r="B63" s="31">
         <f>$B$9+A63</f>
         <v/>
       </c>
@@ -4742,10 +4760,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="30" t="n">
+      <c r="A64" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B64" s="30">
+      <c r="B64" s="31">
         <f>$B$9+A64</f>
         <v/>
       </c>
@@ -4767,10 +4785,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="30" t="n">
+      <c r="A65" s="31" t="n">
         <v>2.05</v>
       </c>
-      <c r="B65" s="30">
+      <c r="B65" s="31">
         <f>$B$9+A65</f>
         <v/>
       </c>
@@ -4792,10 +4810,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="30" t="n">
+      <c r="A66" s="31" t="n">
         <v>2.1</v>
       </c>
-      <c r="B66" s="30">
+      <c r="B66" s="31">
         <f>$B$9+A66</f>
         <v/>
       </c>
@@ -4817,10 +4835,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="30" t="n">
+      <c r="A67" s="31" t="n">
         <v>2.15</v>
       </c>
-      <c r="B67" s="30">
+      <c r="B67" s="31">
         <f>$B$9+A67</f>
         <v/>
       </c>
@@ -4842,10 +4860,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="30" t="n">
+      <c r="A68" s="31" t="n">
         <v>2.2</v>
       </c>
-      <c r="B68" s="30">
+      <c r="B68" s="31">
         <f>$B$9+A68</f>
         <v/>
       </c>
@@ -4867,10 +4885,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="30" t="n">
+      <c r="A69" s="31" t="n">
         <v>2.25</v>
       </c>
-      <c r="B69" s="30">
+      <c r="B69" s="31">
         <f>$B$9+A69</f>
         <v/>
       </c>
@@ -4892,10 +4910,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30" t="n">
+      <c r="A70" s="31" t="n">
         <v>2.3</v>
       </c>
-      <c r="B70" s="30">
+      <c r="B70" s="31">
         <f>$B$9+A70</f>
         <v/>
       </c>
@@ -4917,10 +4935,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="30" t="n">
+      <c r="A71" s="31" t="n">
         <v>2.35</v>
       </c>
-      <c r="B71" s="30">
+      <c r="B71" s="31">
         <f>$B$9+A71</f>
         <v/>
       </c>
@@ -4942,10 +4960,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="37" t="n">
+      <c r="A72" s="38" t="n">
         <v>2.4</v>
       </c>
-      <c r="B72" s="37">
+      <c r="B72" s="38">
         <f>$B$9+A72</f>
         <v/>
       </c>
@@ -4967,10 +4985,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="30" t="n">
+      <c r="A73" s="31" t="n">
         <v>2.45</v>
       </c>
-      <c r="B73" s="30">
+      <c r="B73" s="31">
         <f>$B$9+A73</f>
         <v/>
       </c>
@@ -4992,10 +5010,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="30" t="n">
+      <c r="A74" s="31" t="n">
         <v>2.5</v>
       </c>
-      <c r="B74" s="30">
+      <c r="B74" s="31">
         <f>$B$9+A74</f>
         <v/>
       </c>
@@ -5017,10 +5035,10 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="30" t="n">
+      <c r="A75" s="31" t="n">
         <v>2.55</v>
       </c>
-      <c r="B75" s="30">
+      <c r="B75" s="31">
         <f>$B$9+A75</f>
         <v/>
       </c>
@@ -5042,10 +5060,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="30" t="n">
+      <c r="A76" s="31" t="n">
         <v>2.6</v>
       </c>
-      <c r="B76" s="30">
+      <c r="B76" s="31">
         <f>$B$9+A76</f>
         <v/>
       </c>
@@ -5067,10 +5085,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="30" t="n">
+      <c r="A77" s="31" t="n">
         <v>2.65</v>
       </c>
-      <c r="B77" s="30">
+      <c r="B77" s="31">
         <f>$B$9+A77</f>
         <v/>
       </c>
@@ -5092,10 +5110,10 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="30" t="n">
+      <c r="A78" s="31" t="n">
         <v>2.7</v>
       </c>
-      <c r="B78" s="30">
+      <c r="B78" s="31">
         <f>$B$9+A78</f>
         <v/>
       </c>
@@ -5117,10 +5135,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="30" t="n">
+      <c r="A79" s="31" t="n">
         <v>2.75</v>
       </c>
-      <c r="B79" s="30">
+      <c r="B79" s="31">
         <f>$B$9+A79</f>
         <v/>
       </c>
@@ -5142,10 +5160,10 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="30" t="n">
+      <c r="A80" s="31" t="n">
         <v>2.8</v>
       </c>
-      <c r="B80" s="30">
+      <c r="B80" s="31">
         <f>$B$9+A80</f>
         <v/>
       </c>
@@ -5167,10 +5185,10 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="30" t="n">
+      <c r="A81" s="31" t="n">
         <v>2.85</v>
       </c>
-      <c r="B81" s="30">
+      <c r="B81" s="31">
         <f>$B$9+A81</f>
         <v/>
       </c>
@@ -5192,10 +5210,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="30" t="n">
+      <c r="A82" s="31" t="n">
         <v>2.9</v>
       </c>
-      <c r="B82" s="30">
+      <c r="B82" s="31">
         <f>$B$9+A82</f>
         <v/>
       </c>
@@ -5217,10 +5235,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="30" t="n">
+      <c r="A83" s="31" t="n">
         <v>2.95</v>
       </c>
-      <c r="B83" s="30">
+      <c r="B83" s="31">
         <f>$B$9+A83</f>
         <v/>
       </c>
@@ -5242,10 +5260,10 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="30" t="n">
+      <c r="A84" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="B84" s="30">
+      <c r="B84" s="31">
         <f>$B$9+A84</f>
         <v/>
       </c>
@@ -5294,14 +5312,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Méthode B — routage avec Qout = f(H) depuis Courbe_QH_900 (FHWA)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="38" t="inlineStr">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>H = V / Aire_bassin. Qout interpolé sur Courbe_QH_900!E (Q gouvernant). Si V≈0, Qout = MIN(Qin, Q_plein). ΔV = (Qin_moy - Qout)*Δt. La courbe Courbe_QH_900 est en formules live (changer n/L/entrée/TW).</t>
         </is>
@@ -5314,7 +5332,7 @@
           <t>Aire (m²)</t>
         </is>
       </c>
-      <c r="B5" s="39">
+      <c r="B5" s="40">
         <f>Parametres!B24</f>
         <v/>
       </c>
@@ -5325,7 +5343,7 @@
           <t>Q_plein réf. (m³/s)</t>
         </is>
       </c>
-      <c r="B6" s="39">
+      <c r="B6" s="40">
         <f>Parametres!B22</f>
         <v/>
       </c>
@@ -5336,7 +5354,7 @@
           <t>Vmax_B (m³)</t>
         </is>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="30">
         <f>MAX(G12:G24)</f>
         <v/>
       </c>
@@ -5347,7 +5365,7 @@
           <t>Hmax_B (m)</t>
         </is>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="21">
         <f>IF(B5&gt;0,B7/B5,0)</f>
         <v/>
       </c>
@@ -5408,10 +5426,10 @@
         <f>MIN(B12,$B$6)</f>
         <v/>
       </c>
-      <c r="F12" s="24" t="n">
+      <c r="F12" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="32" t="n">
+      <c r="G12" s="33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5436,11 +5454,11 @@
         <f>IF(G12&lt;=0.01,MIN(0.5*(B12+B13),$B$6),D13)</f>
         <v/>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="25">
         <f>(A13-A12)*60</f>
         <v/>
       </c>
-      <c r="G13" s="32">
+      <c r="G13" s="33">
         <f>MAX(0,G12+(0.5*(B12+B13)-E13)*F13)</f>
         <v/>
       </c>
@@ -5466,11 +5484,11 @@
         <f>IF(G13&lt;=0.01,MIN(0.5*(B13+B14),$B$6),D14)</f>
         <v/>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="25">
         <f>(A14-A13)*60</f>
         <v/>
       </c>
-      <c r="G14" s="32">
+      <c r="G14" s="33">
         <f>MAX(0,G13+(0.5*(B13+B14)-E14)*F14)</f>
         <v/>
       </c>
@@ -5496,11 +5514,11 @@
         <f>IF(G14&lt;=0.01,MIN(0.5*(B14+B15),$B$6),D15)</f>
         <v/>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="25">
         <f>(A15-A14)*60</f>
         <v/>
       </c>
-      <c r="G15" s="32">
+      <c r="G15" s="33">
         <f>MAX(0,G14+(0.5*(B14+B15)-E15)*F15)</f>
         <v/>
       </c>
@@ -5526,11 +5544,11 @@
         <f>IF(G15&lt;=0.01,MIN(0.5*(B15+B16),$B$6),D16)</f>
         <v/>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="25">
         <f>(A16-A15)*60</f>
         <v/>
       </c>
-      <c r="G16" s="32">
+      <c r="G16" s="33">
         <f>MAX(0,G15+(0.5*(B15+B16)-E16)*F16)</f>
         <v/>
       </c>
@@ -5556,11 +5574,11 @@
         <f>IF(G16&lt;=0.01,MIN(0.5*(B16+B17),$B$6),D17)</f>
         <v/>
       </c>
-      <c r="F17" s="24">
+      <c r="F17" s="25">
         <f>(A17-A16)*60</f>
         <v/>
       </c>
-      <c r="G17" s="32">
+      <c r="G17" s="33">
         <f>MAX(0,G16+(0.5*(B16+B17)-E17)*F17)</f>
         <v/>
       </c>
@@ -5586,11 +5604,11 @@
         <f>IF(G17&lt;=0.01,MIN(0.5*(B17+B18),$B$6),D18)</f>
         <v/>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="25">
         <f>(A18-A17)*60</f>
         <v/>
       </c>
-      <c r="G18" s="32">
+      <c r="G18" s="33">
         <f>MAX(0,G17+(0.5*(B17+B18)-E18)*F18)</f>
         <v/>
       </c>
@@ -5616,11 +5634,11 @@
         <f>IF(G18&lt;=0.01,MIN(0.5*(B18+B19),$B$6),D19)</f>
         <v/>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="25">
         <f>(A19-A18)*60</f>
         <v/>
       </c>
-      <c r="G19" s="32">
+      <c r="G19" s="33">
         <f>MAX(0,G18+(0.5*(B18+B19)-E19)*F19)</f>
         <v/>
       </c>
@@ -5646,11 +5664,11 @@
         <f>IF(G19&lt;=0.01,MIN(0.5*(B19+B20),$B$6),D20)</f>
         <v/>
       </c>
-      <c r="F20" s="24">
+      <c r="F20" s="25">
         <f>(A20-A19)*60</f>
         <v/>
       </c>
-      <c r="G20" s="32">
+      <c r="G20" s="33">
         <f>MAX(0,G19+(0.5*(B19+B20)-E20)*F20)</f>
         <v/>
       </c>
@@ -5676,11 +5694,11 @@
         <f>IF(G20&lt;=0.01,MIN(0.5*(B20+B21),$B$6),D21)</f>
         <v/>
       </c>
-      <c r="F21" s="24">
+      <c r="F21" s="25">
         <f>(A21-A20)*60</f>
         <v/>
       </c>
-      <c r="G21" s="32">
+      <c r="G21" s="33">
         <f>MAX(0,G20+(0.5*(B20+B21)-E21)*F21)</f>
         <v/>
       </c>
@@ -5706,11 +5724,11 @@
         <f>IF(G21&lt;=0.01,MIN(0.5*(B21+B22),$B$6),D22)</f>
         <v/>
       </c>
-      <c r="F22" s="24">
+      <c r="F22" s="25">
         <f>(A22-A21)*60</f>
         <v/>
       </c>
-      <c r="G22" s="32">
+      <c r="G22" s="33">
         <f>MAX(0,G21+(0.5*(B21+B22)-E22)*F22)</f>
         <v/>
       </c>
@@ -5736,11 +5754,11 @@
         <f>IF(G22&lt;=0.01,MIN(0.5*(B22+B23),$B$6),D23)</f>
         <v/>
       </c>
-      <c r="F23" s="24">
+      <c r="F23" s="25">
         <f>(A23-A22)*60</f>
         <v/>
       </c>
-      <c r="G23" s="32">
+      <c r="G23" s="33">
         <f>MAX(0,G22+(0.5*(B22+B23)-E23)*F23)</f>
         <v/>
       </c>
@@ -5766,11 +5784,11 @@
         <f>IF(G23&lt;=0.01,MIN(0.5*(B23+B24),$B$6),D24)</f>
         <v/>
       </c>
-      <c r="F24" s="24">
+      <c r="F24" s="25">
         <f>(A24-A23)*60</f>
         <v/>
       </c>
-      <c r="G24" s="32">
+      <c r="G24" s="33">
         <f>MAX(0,G23+(0.5*(B23+B24)-E24)*F24)</f>
         <v/>
       </c>
@@ -5806,7 +5824,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Méthode C — courbe composée Ø900 + fossé trapèze (crest = crown)</t>
         </is>
@@ -5962,14 +5980,14 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="30" t="n">
+      <c r="A15" s="31" t="n">
         <v>34.88</v>
       </c>
-      <c r="B15" s="30">
+      <c r="B15" s="31">
         <f>A15-$B$12</f>
         <v/>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="31">
         <f>MAX(0,A15-$B$6)</f>
         <v/>
       </c>
@@ -5977,15 +5995,15 @@
         <f>IF(C15&lt;=0,0,($B$7+$B$9*C15)*C15)</f>
         <v/>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="25">
         <f>D15*$B$11</f>
         <v/>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="25">
         <f>IF(A15&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A15&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A15,Stage_Storage!$A$11:$A$18,1))+(A15-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A15,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A15,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A15,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A15,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A15,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G15" s="32">
+      <c r="G15" s="33">
         <f>E15+F15</f>
         <v/>
       </c>
@@ -6007,14 +6025,14 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="30" t="n">
+      <c r="A16" s="31" t="n">
         <v>34.93</v>
       </c>
-      <c r="B16" s="30">
+      <c r="B16" s="31">
         <f>A16-$B$12</f>
         <v/>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="31">
         <f>MAX(0,A16-$B$6)</f>
         <v/>
       </c>
@@ -6022,15 +6040,15 @@
         <f>IF(C16&lt;=0,0,($B$7+$B$9*C16)*C16)</f>
         <v/>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="25">
         <f>D16*$B$11</f>
         <v/>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="25">
         <f>IF(A16&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A16&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A16,Stage_Storage!$A$11:$A$18,1))+(A16-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A16,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A16,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A16,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A16,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A16,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G16" s="32">
+      <c r="G16" s="33">
         <f>E16+F16</f>
         <v/>
       </c>
@@ -6052,14 +6070,14 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="30" t="n">
+      <c r="A17" s="31" t="n">
         <v>34.98</v>
       </c>
-      <c r="B17" s="30">
+      <c r="B17" s="31">
         <f>A17-$B$12</f>
         <v/>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="31">
         <f>MAX(0,A17-$B$6)</f>
         <v/>
       </c>
@@ -6067,15 +6085,15 @@
         <f>IF(C17&lt;=0,0,($B$7+$B$9*C17)*C17)</f>
         <v/>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="25">
         <f>D17*$B$11</f>
         <v/>
       </c>
-      <c r="F17" s="24">
+      <c r="F17" s="25">
         <f>IF(A17&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A17&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A17,Stage_Storage!$A$11:$A$18,1))+(A17-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A17,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A17,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A17,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A17,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A17,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G17" s="32">
+      <c r="G17" s="33">
         <f>E17+F17</f>
         <v/>
       </c>
@@ -6097,14 +6115,14 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="30" t="n">
+      <c r="A18" s="31" t="n">
         <v>35.03</v>
       </c>
-      <c r="B18" s="30">
+      <c r="B18" s="31">
         <f>A18-$B$12</f>
         <v/>
       </c>
-      <c r="C18" s="30">
+      <c r="C18" s="31">
         <f>MAX(0,A18-$B$6)</f>
         <v/>
       </c>
@@ -6112,15 +6130,15 @@
         <f>IF(C18&lt;=0,0,($B$7+$B$9*C18)*C18)</f>
         <v/>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="25">
         <f>D18*$B$11</f>
         <v/>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="25">
         <f>IF(A18&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A18&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A18,Stage_Storage!$A$11:$A$18,1))+(A18-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A18,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A18,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A18,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A18,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A18,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G18" s="32">
+      <c r="G18" s="33">
         <f>E18+F18</f>
         <v/>
       </c>
@@ -6142,14 +6160,14 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="30" t="n">
+      <c r="A19" s="31" t="n">
         <v>35.08</v>
       </c>
-      <c r="B19" s="30">
+      <c r="B19" s="31">
         <f>A19-$B$12</f>
         <v/>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="31">
         <f>MAX(0,A19-$B$6)</f>
         <v/>
       </c>
@@ -6157,15 +6175,15 @@
         <f>IF(C19&lt;=0,0,($B$7+$B$9*C19)*C19)</f>
         <v/>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="25">
         <f>D19*$B$11</f>
         <v/>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="25">
         <f>IF(A19&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A19&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A19,Stage_Storage!$A$11:$A$18,1))+(A19-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A19,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A19,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A19,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A19,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A19,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G19" s="32">
+      <c r="G19" s="33">
         <f>E19+F19</f>
         <v/>
       </c>
@@ -6187,14 +6205,14 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="30" t="n">
+      <c r="A20" s="31" t="n">
         <v>35.13</v>
       </c>
-      <c r="B20" s="30">
+      <c r="B20" s="31">
         <f>A20-$B$12</f>
         <v/>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="31">
         <f>MAX(0,A20-$B$6)</f>
         <v/>
       </c>
@@ -6202,15 +6220,15 @@
         <f>IF(C20&lt;=0,0,($B$7+$B$9*C20)*C20)</f>
         <v/>
       </c>
-      <c r="E20" s="24">
+      <c r="E20" s="25">
         <f>D20*$B$11</f>
         <v/>
       </c>
-      <c r="F20" s="24">
+      <c r="F20" s="25">
         <f>IF(A20&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A20&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A20,Stage_Storage!$A$11:$A$18,1))+(A20-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A20,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A20,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A20,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A20,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A20,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G20" s="32">
+      <c r="G20" s="33">
         <f>E20+F20</f>
         <v/>
       </c>
@@ -6232,14 +6250,14 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="30" t="n">
+      <c r="A21" s="31" t="n">
         <v>35.18</v>
       </c>
-      <c r="B21" s="30">
+      <c r="B21" s="31">
         <f>A21-$B$12</f>
         <v/>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="31">
         <f>MAX(0,A21-$B$6)</f>
         <v/>
       </c>
@@ -6247,15 +6265,15 @@
         <f>IF(C21&lt;=0,0,($B$7+$B$9*C21)*C21)</f>
         <v/>
       </c>
-      <c r="E21" s="24">
+      <c r="E21" s="25">
         <f>D21*$B$11</f>
         <v/>
       </c>
-      <c r="F21" s="24">
+      <c r="F21" s="25">
         <f>IF(A21&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A21&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A21,Stage_Storage!$A$11:$A$18,1))+(A21-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A21,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A21,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A21,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A21,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A21,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G21" s="32">
+      <c r="G21" s="33">
         <f>E21+F21</f>
         <v/>
       </c>
@@ -6277,14 +6295,14 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="30" t="n">
+      <c r="A22" s="31" t="n">
         <v>35.23</v>
       </c>
-      <c r="B22" s="30">
+      <c r="B22" s="31">
         <f>A22-$B$12</f>
         <v/>
       </c>
-      <c r="C22" s="30">
+      <c r="C22" s="31">
         <f>MAX(0,A22-$B$6)</f>
         <v/>
       </c>
@@ -6292,15 +6310,15 @@
         <f>IF(C22&lt;=0,0,($B$7+$B$9*C22)*C22)</f>
         <v/>
       </c>
-      <c r="E22" s="24">
+      <c r="E22" s="25">
         <f>D22*$B$11</f>
         <v/>
       </c>
-      <c r="F22" s="24">
+      <c r="F22" s="25">
         <f>IF(A22&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A22&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A22,Stage_Storage!$A$11:$A$18,1))+(A22-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A22,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A22,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A22,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A22,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A22,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G22" s="32">
+      <c r="G22" s="33">
         <f>E22+F22</f>
         <v/>
       </c>
@@ -6322,14 +6340,14 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="30" t="n">
+      <c r="A23" s="31" t="n">
         <v>35.28</v>
       </c>
-      <c r="B23" s="30">
+      <c r="B23" s="31">
         <f>A23-$B$12</f>
         <v/>
       </c>
-      <c r="C23" s="30">
+      <c r="C23" s="31">
         <f>MAX(0,A23-$B$6)</f>
         <v/>
       </c>
@@ -6337,15 +6355,15 @@
         <f>IF(C23&lt;=0,0,($B$7+$B$9*C23)*C23)</f>
         <v/>
       </c>
-      <c r="E23" s="24">
+      <c r="E23" s="25">
         <f>D23*$B$11</f>
         <v/>
       </c>
-      <c r="F23" s="24">
+      <c r="F23" s="25">
         <f>IF(A23&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A23&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A23,Stage_Storage!$A$11:$A$18,1))+(A23-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A23,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A23,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A23,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A23,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A23,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G23" s="32">
+      <c r="G23" s="33">
         <f>E23+F23</f>
         <v/>
       </c>
@@ -6367,14 +6385,14 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="30" t="n">
+      <c r="A24" s="31" t="n">
         <v>35.33</v>
       </c>
-      <c r="B24" s="30">
+      <c r="B24" s="31">
         <f>A24-$B$12</f>
         <v/>
       </c>
-      <c r="C24" s="30">
+      <c r="C24" s="31">
         <f>MAX(0,A24-$B$6)</f>
         <v/>
       </c>
@@ -6382,15 +6400,15 @@
         <f>IF(C24&lt;=0,0,($B$7+$B$9*C24)*C24)</f>
         <v/>
       </c>
-      <c r="E24" s="24">
+      <c r="E24" s="25">
         <f>D24*$B$11</f>
         <v/>
       </c>
-      <c r="F24" s="24">
+      <c r="F24" s="25">
         <f>IF(A24&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A24&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A24,Stage_Storage!$A$11:$A$18,1))+(A24-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A24,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A24,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A24,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A24,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A24,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G24" s="32">
+      <c r="G24" s="33">
         <f>E24+F24</f>
         <v/>
       </c>
@@ -6412,14 +6430,14 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="30" t="n">
+      <c r="A25" s="31" t="n">
         <v>35.38</v>
       </c>
-      <c r="B25" s="30">
+      <c r="B25" s="31">
         <f>A25-$B$12</f>
         <v/>
       </c>
-      <c r="C25" s="30">
+      <c r="C25" s="31">
         <f>MAX(0,A25-$B$6)</f>
         <v/>
       </c>
@@ -6427,15 +6445,15 @@
         <f>IF(C25&lt;=0,0,($B$7+$B$9*C25)*C25)</f>
         <v/>
       </c>
-      <c r="E25" s="24">
+      <c r="E25" s="25">
         <f>D25*$B$11</f>
         <v/>
       </c>
-      <c r="F25" s="24">
+      <c r="F25" s="25">
         <f>IF(A25&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A25&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A25,Stage_Storage!$A$11:$A$18,1))+(A25-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A25,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A25,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A25,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A25,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A25,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G25" s="32">
+      <c r="G25" s="33">
         <f>E25+F25</f>
         <v/>
       </c>
@@ -6457,14 +6475,14 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="30" t="n">
+      <c r="A26" s="31" t="n">
         <v>35.43</v>
       </c>
-      <c r="B26" s="30">
+      <c r="B26" s="31">
         <f>A26-$B$12</f>
         <v/>
       </c>
-      <c r="C26" s="30">
+      <c r="C26" s="31">
         <f>MAX(0,A26-$B$6)</f>
         <v/>
       </c>
@@ -6472,15 +6490,15 @@
         <f>IF(C26&lt;=0,0,($B$7+$B$9*C26)*C26)</f>
         <v/>
       </c>
-      <c r="E26" s="24">
+      <c r="E26" s="25">
         <f>D26*$B$11</f>
         <v/>
       </c>
-      <c r="F26" s="24">
+      <c r="F26" s="25">
         <f>IF(A26&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A26&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A26,Stage_Storage!$A$11:$A$18,1))+(A26-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A26,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A26,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A26,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A26,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A26,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G26" s="32">
+      <c r="G26" s="33">
         <f>E26+F26</f>
         <v/>
       </c>
@@ -6502,14 +6520,14 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="30" t="n">
+      <c r="A27" s="31" t="n">
         <v>35.48</v>
       </c>
-      <c r="B27" s="30">
+      <c r="B27" s="31">
         <f>A27-$B$12</f>
         <v/>
       </c>
-      <c r="C27" s="30">
+      <c r="C27" s="31">
         <f>MAX(0,A27-$B$6)</f>
         <v/>
       </c>
@@ -6517,15 +6535,15 @@
         <f>IF(C27&lt;=0,0,($B$7+$B$9*C27)*C27)</f>
         <v/>
       </c>
-      <c r="E27" s="24">
+      <c r="E27" s="25">
         <f>D27*$B$11</f>
         <v/>
       </c>
-      <c r="F27" s="24">
+      <c r="F27" s="25">
         <f>IF(A27&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A27&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A27,Stage_Storage!$A$11:$A$18,1))+(A27-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A27,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A27,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A27,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A27,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A27,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G27" s="32">
+      <c r="G27" s="33">
         <f>E27+F27</f>
         <v/>
       </c>
@@ -6547,14 +6565,14 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="30" t="n">
+      <c r="A28" s="31" t="n">
         <v>35.53</v>
       </c>
-      <c r="B28" s="30">
+      <c r="B28" s="31">
         <f>A28-$B$12</f>
         <v/>
       </c>
-      <c r="C28" s="30">
+      <c r="C28" s="31">
         <f>MAX(0,A28-$B$6)</f>
         <v/>
       </c>
@@ -6562,15 +6580,15 @@
         <f>IF(C28&lt;=0,0,($B$7+$B$9*C28)*C28)</f>
         <v/>
       </c>
-      <c r="E28" s="24">
+      <c r="E28" s="25">
         <f>D28*$B$11</f>
         <v/>
       </c>
-      <c r="F28" s="24">
+      <c r="F28" s="25">
         <f>IF(A28&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A28&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A28,Stage_Storage!$A$11:$A$18,1))+(A28-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A28,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A28,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A28,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A28,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A28,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G28" s="32">
+      <c r="G28" s="33">
         <f>E28+F28</f>
         <v/>
       </c>
@@ -6592,14 +6610,14 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="30" t="n">
+      <c r="A29" s="31" t="n">
         <v>35.58</v>
       </c>
-      <c r="B29" s="30">
+      <c r="B29" s="31">
         <f>A29-$B$12</f>
         <v/>
       </c>
-      <c r="C29" s="30">
+      <c r="C29" s="31">
         <f>MAX(0,A29-$B$6)</f>
         <v/>
       </c>
@@ -6607,15 +6625,15 @@
         <f>IF(C29&lt;=0,0,($B$7+$B$9*C29)*C29)</f>
         <v/>
       </c>
-      <c r="E29" s="24">
+      <c r="E29" s="25">
         <f>D29*$B$11</f>
         <v/>
       </c>
-      <c r="F29" s="24">
+      <c r="F29" s="25">
         <f>IF(A29&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A29&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A29,Stage_Storage!$A$11:$A$18,1))+(A29-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A29,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A29,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A29,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A29,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A29,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G29" s="32">
+      <c r="G29" s="33">
         <f>E29+F29</f>
         <v/>
       </c>
@@ -6637,14 +6655,14 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="30" t="n">
+      <c r="A30" s="31" t="n">
         <v>35.63</v>
       </c>
-      <c r="B30" s="30">
+      <c r="B30" s="31">
         <f>A30-$B$12</f>
         <v/>
       </c>
-      <c r="C30" s="30">
+      <c r="C30" s="31">
         <f>MAX(0,A30-$B$6)</f>
         <v/>
       </c>
@@ -6652,15 +6670,15 @@
         <f>IF(C30&lt;=0,0,($B$7+$B$9*C30)*C30)</f>
         <v/>
       </c>
-      <c r="E30" s="24">
+      <c r="E30" s="25">
         <f>D30*$B$11</f>
         <v/>
       </c>
-      <c r="F30" s="24">
+      <c r="F30" s="25">
         <f>IF(A30&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A30&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A30,Stage_Storage!$A$11:$A$18,1))+(A30-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A30,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A30,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A30,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A30,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A30,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G30" s="32">
+      <c r="G30" s="33">
         <f>E30+F30</f>
         <v/>
       </c>
@@ -6682,14 +6700,14 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="30" t="n">
+      <c r="A31" s="31" t="n">
         <v>35.68</v>
       </c>
-      <c r="B31" s="30">
+      <c r="B31" s="31">
         <f>A31-$B$12</f>
         <v/>
       </c>
-      <c r="C31" s="30">
+      <c r="C31" s="31">
         <f>MAX(0,A31-$B$6)</f>
         <v/>
       </c>
@@ -6697,15 +6715,15 @@
         <f>IF(C31&lt;=0,0,($B$7+$B$9*C31)*C31)</f>
         <v/>
       </c>
-      <c r="E31" s="24">
+      <c r="E31" s="25">
         <f>D31*$B$11</f>
         <v/>
       </c>
-      <c r="F31" s="24">
+      <c r="F31" s="25">
         <f>IF(A31&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A31&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A31,Stage_Storage!$A$11:$A$18,1))+(A31-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A31,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A31,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A31,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A31,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A31,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G31" s="32">
+      <c r="G31" s="33">
         <f>E31+F31</f>
         <v/>
       </c>
@@ -6727,14 +6745,14 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="30" t="n">
+      <c r="A32" s="31" t="n">
         <v>35.73</v>
       </c>
-      <c r="B32" s="30">
+      <c r="B32" s="31">
         <f>A32-$B$12</f>
         <v/>
       </c>
-      <c r="C32" s="30">
+      <c r="C32" s="31">
         <f>MAX(0,A32-$B$6)</f>
         <v/>
       </c>
@@ -6742,15 +6760,15 @@
         <f>IF(C32&lt;=0,0,($B$7+$B$9*C32)*C32)</f>
         <v/>
       </c>
-      <c r="E32" s="24">
+      <c r="E32" s="25">
         <f>D32*$B$11</f>
         <v/>
       </c>
-      <c r="F32" s="24">
+      <c r="F32" s="25">
         <f>IF(A32&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A32&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A32,Stage_Storage!$A$11:$A$18,1))+(A32-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A32,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A32,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A32,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A32,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A32,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G32" s="32">
+      <c r="G32" s="33">
         <f>E32+F32</f>
         <v/>
       </c>
@@ -6772,14 +6790,14 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="37" t="n">
+      <c r="A33" s="38" t="n">
         <v>35.78</v>
       </c>
-      <c r="B33" s="37">
+      <c r="B33" s="38">
         <f>A33-$B$12</f>
         <v/>
       </c>
-      <c r="C33" s="37">
+      <c r="C33" s="38">
         <f>MAX(0,A33-$B$6)</f>
         <v/>
       </c>
@@ -6787,15 +6805,15 @@
         <f>IF(C33&lt;=0,0,($B$7+$B$9*C33)*C33)</f>
         <v/>
       </c>
-      <c r="E33" s="40">
+      <c r="E33" s="41">
         <f>D33*$B$11</f>
         <v/>
       </c>
-      <c r="F33" s="40">
+      <c r="F33" s="41">
         <f>IF(A33&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A33&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A33,Stage_Storage!$A$11:$A$18,1))+(A33-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A33,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A33,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A33,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A33,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A33,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G33" s="32">
+      <c r="G33" s="33">
         <f>E33+F33</f>
         <v/>
       </c>
@@ -6817,14 +6835,14 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="30" t="n">
+      <c r="A34" s="31" t="n">
         <v>35.83</v>
       </c>
-      <c r="B34" s="30">
+      <c r="B34" s="31">
         <f>A34-$B$12</f>
         <v/>
       </c>
-      <c r="C34" s="30">
+      <c r="C34" s="31">
         <f>MAX(0,A34-$B$6)</f>
         <v/>
       </c>
@@ -6832,15 +6850,15 @@
         <f>IF(C34&lt;=0,0,($B$7+$B$9*C34)*C34)</f>
         <v/>
       </c>
-      <c r="E34" s="24">
+      <c r="E34" s="25">
         <f>D34*$B$11</f>
         <v/>
       </c>
-      <c r="F34" s="24">
+      <c r="F34" s="25">
         <f>IF(A34&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A34&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A34,Stage_Storage!$A$11:$A$18,1))+(A34-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A34,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A34,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A34,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A34,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A34,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G34" s="32">
+      <c r="G34" s="33">
         <f>E34+F34</f>
         <v/>
       </c>
@@ -6862,14 +6880,14 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="30" t="n">
+      <c r="A35" s="31" t="n">
         <v>35.88</v>
       </c>
-      <c r="B35" s="30">
+      <c r="B35" s="31">
         <f>A35-$B$12</f>
         <v/>
       </c>
-      <c r="C35" s="30">
+      <c r="C35" s="31">
         <f>MAX(0,A35-$B$6)</f>
         <v/>
       </c>
@@ -6877,15 +6895,15 @@
         <f>IF(C35&lt;=0,0,($B$7+$B$9*C35)*C35)</f>
         <v/>
       </c>
-      <c r="E35" s="24">
+      <c r="E35" s="25">
         <f>D35*$B$11</f>
         <v/>
       </c>
-      <c r="F35" s="24">
+      <c r="F35" s="25">
         <f>IF(A35&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A35&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A35,Stage_Storage!$A$11:$A$18,1))+(A35-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A35,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A35,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A35,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A35,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A35,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G35" s="32">
+      <c r="G35" s="33">
         <f>E35+F35</f>
         <v/>
       </c>
@@ -6907,14 +6925,14 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="30" t="n">
+      <c r="A36" s="31" t="n">
         <v>35.93</v>
       </c>
-      <c r="B36" s="30">
+      <c r="B36" s="31">
         <f>A36-$B$12</f>
         <v/>
       </c>
-      <c r="C36" s="30">
+      <c r="C36" s="31">
         <f>MAX(0,A36-$B$6)</f>
         <v/>
       </c>
@@ -6922,15 +6940,15 @@
         <f>IF(C36&lt;=0,0,($B$7+$B$9*C36)*C36)</f>
         <v/>
       </c>
-      <c r="E36" s="24">
+      <c r="E36" s="25">
         <f>D36*$B$11</f>
         <v/>
       </c>
-      <c r="F36" s="24">
+      <c r="F36" s="25">
         <f>IF(A36&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A36&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A36,Stage_Storage!$A$11:$A$18,1))+(A36-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A36,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A36,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A36,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A36,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A36,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G36" s="32">
+      <c r="G36" s="33">
         <f>E36+F36</f>
         <v/>
       </c>
@@ -6952,14 +6970,14 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="30" t="n">
+      <c r="A37" s="31" t="n">
         <v>35.98</v>
       </c>
-      <c r="B37" s="30">
+      <c r="B37" s="31">
         <f>A37-$B$12</f>
         <v/>
       </c>
-      <c r="C37" s="30">
+      <c r="C37" s="31">
         <f>MAX(0,A37-$B$6)</f>
         <v/>
       </c>
@@ -6967,15 +6985,15 @@
         <f>IF(C37&lt;=0,0,($B$7+$B$9*C37)*C37)</f>
         <v/>
       </c>
-      <c r="E37" s="24">
+      <c r="E37" s="25">
         <f>D37*$B$11</f>
         <v/>
       </c>
-      <c r="F37" s="24">
+      <c r="F37" s="25">
         <f>IF(A37&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A37&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A37,Stage_Storage!$A$11:$A$18,1))+(A37-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A37,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A37,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A37,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A37,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A37,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G37" s="32">
+      <c r="G37" s="33">
         <f>E37+F37</f>
         <v/>
       </c>
@@ -6997,14 +7015,14 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="30" t="n">
+      <c r="A38" s="31" t="n">
         <v>36.03</v>
       </c>
-      <c r="B38" s="30">
+      <c r="B38" s="31">
         <f>A38-$B$12</f>
         <v/>
       </c>
-      <c r="C38" s="30">
+      <c r="C38" s="31">
         <f>MAX(0,A38-$B$6)</f>
         <v/>
       </c>
@@ -7012,15 +7030,15 @@
         <f>IF(C38&lt;=0,0,($B$7+$B$9*C38)*C38)</f>
         <v/>
       </c>
-      <c r="E38" s="24">
+      <c r="E38" s="25">
         <f>D38*$B$11</f>
         <v/>
       </c>
-      <c r="F38" s="24">
+      <c r="F38" s="25">
         <f>IF(A38&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A38&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A38,Stage_Storage!$A$11:$A$18,1))+(A38-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A38,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A38,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A38,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A38,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A38,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G38" s="32">
+      <c r="G38" s="33">
         <f>E38+F38</f>
         <v/>
       </c>
@@ -7042,14 +7060,14 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="30" t="n">
+      <c r="A39" s="31" t="n">
         <v>36.08</v>
       </c>
-      <c r="B39" s="30">
+      <c r="B39" s="31">
         <f>A39-$B$12</f>
         <v/>
       </c>
-      <c r="C39" s="30">
+      <c r="C39" s="31">
         <f>MAX(0,A39-$B$6)</f>
         <v/>
       </c>
@@ -7057,15 +7075,15 @@
         <f>IF(C39&lt;=0,0,($B$7+$B$9*C39)*C39)</f>
         <v/>
       </c>
-      <c r="E39" s="24">
+      <c r="E39" s="25">
         <f>D39*$B$11</f>
         <v/>
       </c>
-      <c r="F39" s="24">
+      <c r="F39" s="25">
         <f>IF(A39&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A39&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A39,Stage_Storage!$A$11:$A$18,1))+(A39-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A39,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A39,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A39,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A39,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A39,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G39" s="32">
+      <c r="G39" s="33">
         <f>E39+F39</f>
         <v/>
       </c>
@@ -7087,14 +7105,14 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="30" t="n">
+      <c r="A40" s="31" t="n">
         <v>36.13</v>
       </c>
-      <c r="B40" s="30">
+      <c r="B40" s="31">
         <f>A40-$B$12</f>
         <v/>
       </c>
-      <c r="C40" s="30">
+      <c r="C40" s="31">
         <f>MAX(0,A40-$B$6)</f>
         <v/>
       </c>
@@ -7102,15 +7120,15 @@
         <f>IF(C40&lt;=0,0,($B$7+$B$9*C40)*C40)</f>
         <v/>
       </c>
-      <c r="E40" s="24">
+      <c r="E40" s="25">
         <f>D40*$B$11</f>
         <v/>
       </c>
-      <c r="F40" s="24">
+      <c r="F40" s="25">
         <f>IF(A40&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A40&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A40,Stage_Storage!$A$11:$A$18,1))+(A40-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A40,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A40,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A40,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A40,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A40,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G40" s="32">
+      <c r="G40" s="33">
         <f>E40+F40</f>
         <v/>
       </c>
@@ -7132,14 +7150,14 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="30" t="n">
+      <c r="A41" s="31" t="n">
         <v>36.18</v>
       </c>
-      <c r="B41" s="30">
+      <c r="B41" s="31">
         <f>A41-$B$12</f>
         <v/>
       </c>
-      <c r="C41" s="30">
+      <c r="C41" s="31">
         <f>MAX(0,A41-$B$6)</f>
         <v/>
       </c>
@@ -7147,15 +7165,15 @@
         <f>IF(C41&lt;=0,0,($B$7+$B$9*C41)*C41)</f>
         <v/>
       </c>
-      <c r="E41" s="24">
+      <c r="E41" s="25">
         <f>D41*$B$11</f>
         <v/>
       </c>
-      <c r="F41" s="24">
+      <c r="F41" s="25">
         <f>IF(A41&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A41&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A41,Stage_Storage!$A$11:$A$18,1))+(A41-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A41,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A41,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A41,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A41,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A41,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G41" s="32">
+      <c r="G41" s="33">
         <f>E41+F41</f>
         <v/>
       </c>
@@ -7177,14 +7195,14 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="30" t="n">
+      <c r="A42" s="31" t="n">
         <v>36.23</v>
       </c>
-      <c r="B42" s="30">
+      <c r="B42" s="31">
         <f>A42-$B$12</f>
         <v/>
       </c>
-      <c r="C42" s="30">
+      <c r="C42" s="31">
         <f>MAX(0,A42-$B$6)</f>
         <v/>
       </c>
@@ -7192,15 +7210,15 @@
         <f>IF(C42&lt;=0,0,($B$7+$B$9*C42)*C42)</f>
         <v/>
       </c>
-      <c r="E42" s="24">
+      <c r="E42" s="25">
         <f>D42*$B$11</f>
         <v/>
       </c>
-      <c r="F42" s="24">
+      <c r="F42" s="25">
         <f>IF(A42&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A42&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A42,Stage_Storage!$A$11:$A$18,1))+(A42-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A42,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A42,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A42,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A42,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A42,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G42" s="32">
+      <c r="G42" s="33">
         <f>E42+F42</f>
         <v/>
       </c>
@@ -7222,14 +7240,14 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="30" t="n">
+      <c r="A43" s="31" t="n">
         <v>36.28</v>
       </c>
-      <c r="B43" s="30">
+      <c r="B43" s="31">
         <f>A43-$B$12</f>
         <v/>
       </c>
-      <c r="C43" s="30">
+      <c r="C43" s="31">
         <f>MAX(0,A43-$B$6)</f>
         <v/>
       </c>
@@ -7237,15 +7255,15 @@
         <f>IF(C43&lt;=0,0,($B$7+$B$9*C43)*C43)</f>
         <v/>
       </c>
-      <c r="E43" s="24">
+      <c r="E43" s="25">
         <f>D43*$B$11</f>
         <v/>
       </c>
-      <c r="F43" s="24">
+      <c r="F43" s="25">
         <f>IF(A43&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A43&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A43,Stage_Storage!$A$11:$A$18,1))+(A43-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A43,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A43,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A43,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A43,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A43,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G43" s="32">
+      <c r="G43" s="33">
         <f>E43+F43</f>
         <v/>
       </c>
@@ -7267,14 +7285,14 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="30" t="n">
+      <c r="A44" s="31" t="n">
         <v>36.33</v>
       </c>
-      <c r="B44" s="30">
+      <c r="B44" s="31">
         <f>A44-$B$12</f>
         <v/>
       </c>
-      <c r="C44" s="30">
+      <c r="C44" s="31">
         <f>MAX(0,A44-$B$6)</f>
         <v/>
       </c>
@@ -7282,15 +7300,15 @@
         <f>IF(C44&lt;=0,0,($B$7+$B$9*C44)*C44)</f>
         <v/>
       </c>
-      <c r="E44" s="24">
+      <c r="E44" s="25">
         <f>D44*$B$11</f>
         <v/>
       </c>
-      <c r="F44" s="24">
+      <c r="F44" s="25">
         <f>IF(A44&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A44&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A44,Stage_Storage!$A$11:$A$18,1))+(A44-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A44,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A44,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A44,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A44,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A44,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G44" s="32">
+      <c r="G44" s="33">
         <f>E44+F44</f>
         <v/>
       </c>
@@ -7312,14 +7330,14 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="30" t="n">
+      <c r="A45" s="31" t="n">
         <v>36.38</v>
       </c>
-      <c r="B45" s="30">
+      <c r="B45" s="31">
         <f>A45-$B$12</f>
         <v/>
       </c>
-      <c r="C45" s="30">
+      <c r="C45" s="31">
         <f>MAX(0,A45-$B$6)</f>
         <v/>
       </c>
@@ -7327,15 +7345,15 @@
         <f>IF(C45&lt;=0,0,($B$7+$B$9*C45)*C45)</f>
         <v/>
       </c>
-      <c r="E45" s="24">
+      <c r="E45" s="25">
         <f>D45*$B$11</f>
         <v/>
       </c>
-      <c r="F45" s="24">
+      <c r="F45" s="25">
         <f>IF(A45&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A45&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A45,Stage_Storage!$A$11:$A$18,1))+(A45-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A45,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A45,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A45,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A45,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A45,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G45" s="32">
+      <c r="G45" s="33">
         <f>E45+F45</f>
         <v/>
       </c>
@@ -7357,14 +7375,14 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="30" t="n">
+      <c r="A46" s="31" t="n">
         <v>36.43</v>
       </c>
-      <c r="B46" s="30">
+      <c r="B46" s="31">
         <f>A46-$B$12</f>
         <v/>
       </c>
-      <c r="C46" s="30">
+      <c r="C46" s="31">
         <f>MAX(0,A46-$B$6)</f>
         <v/>
       </c>
@@ -7372,15 +7390,15 @@
         <f>IF(C46&lt;=0,0,($B$7+$B$9*C46)*C46)</f>
         <v/>
       </c>
-      <c r="E46" s="24">
+      <c r="E46" s="25">
         <f>D46*$B$11</f>
         <v/>
       </c>
-      <c r="F46" s="24">
+      <c r="F46" s="25">
         <f>IF(A46&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A46&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A46,Stage_Storage!$A$11:$A$18,1))+(A46-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A46,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A46,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A46,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A46,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A46,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G46" s="32">
+      <c r="G46" s="33">
         <f>E46+F46</f>
         <v/>
       </c>
@@ -7402,14 +7420,14 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="30" t="n">
+      <c r="A47" s="31" t="n">
         <v>36.48</v>
       </c>
-      <c r="B47" s="30">
+      <c r="B47" s="31">
         <f>A47-$B$12</f>
         <v/>
       </c>
-      <c r="C47" s="30">
+      <c r="C47" s="31">
         <f>MAX(0,A47-$B$6)</f>
         <v/>
       </c>
@@ -7417,15 +7435,15 @@
         <f>IF(C47&lt;=0,0,($B$7+$B$9*C47)*C47)</f>
         <v/>
       </c>
-      <c r="E47" s="24">
+      <c r="E47" s="25">
         <f>D47*$B$11</f>
         <v/>
       </c>
-      <c r="F47" s="24">
+      <c r="F47" s="25">
         <f>IF(A47&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A47&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A47,Stage_Storage!$A$11:$A$18,1))+(A47-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A47,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A47,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A47,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A47,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A47,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G47" s="32">
+      <c r="G47" s="33">
         <f>E47+F47</f>
         <v/>
       </c>
@@ -7447,14 +7465,14 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="30" t="n">
+      <c r="A48" s="31" t="n">
         <v>36.53</v>
       </c>
-      <c r="B48" s="30">
+      <c r="B48" s="31">
         <f>A48-$B$12</f>
         <v/>
       </c>
-      <c r="C48" s="30">
+      <c r="C48" s="31">
         <f>MAX(0,A48-$B$6)</f>
         <v/>
       </c>
@@ -7462,15 +7480,15 @@
         <f>IF(C48&lt;=0,0,($B$7+$B$9*C48)*C48)</f>
         <v/>
       </c>
-      <c r="E48" s="24">
+      <c r="E48" s="25">
         <f>D48*$B$11</f>
         <v/>
       </c>
-      <c r="F48" s="24">
+      <c r="F48" s="25">
         <f>IF(A48&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A48&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A48,Stage_Storage!$A$11:$A$18,1))+(A48-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A48,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A48,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A48,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A48,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A48,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G48" s="32">
+      <c r="G48" s="33">
         <f>E48+F48</f>
         <v/>
       </c>
@@ -7492,14 +7510,14 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="30" t="n">
+      <c r="A49" s="31" t="n">
         <v>36.58</v>
       </c>
-      <c r="B49" s="30">
+      <c r="B49" s="31">
         <f>A49-$B$12</f>
         <v/>
       </c>
-      <c r="C49" s="30">
+      <c r="C49" s="31">
         <f>MAX(0,A49-$B$6)</f>
         <v/>
       </c>
@@ -7507,15 +7525,15 @@
         <f>IF(C49&lt;=0,0,($B$7+$B$9*C49)*C49)</f>
         <v/>
       </c>
-      <c r="E49" s="24">
+      <c r="E49" s="25">
         <f>D49*$B$11</f>
         <v/>
       </c>
-      <c r="F49" s="24">
+      <c r="F49" s="25">
         <f>IF(A49&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A49&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A49,Stage_Storage!$A$11:$A$18,1))+(A49-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A49,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A49,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A49,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A49,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A49,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G49" s="32">
+      <c r="G49" s="33">
         <f>E49+F49</f>
         <v/>
       </c>
@@ -7537,14 +7555,14 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="30" t="n">
+      <c r="A50" s="31" t="n">
         <v>36.63</v>
       </c>
-      <c r="B50" s="30">
+      <c r="B50" s="31">
         <f>A50-$B$12</f>
         <v/>
       </c>
-      <c r="C50" s="30">
+      <c r="C50" s="31">
         <f>MAX(0,A50-$B$6)</f>
         <v/>
       </c>
@@ -7552,15 +7570,15 @@
         <f>IF(C50&lt;=0,0,($B$7+$B$9*C50)*C50)</f>
         <v/>
       </c>
-      <c r="E50" s="24">
+      <c r="E50" s="25">
         <f>D50*$B$11</f>
         <v/>
       </c>
-      <c r="F50" s="24">
+      <c r="F50" s="25">
         <f>IF(A50&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A50&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A50,Stage_Storage!$A$11:$A$18,1))+(A50-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A50,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A50,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A50,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A50,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A50,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G50" s="32">
+      <c r="G50" s="33">
         <f>E50+F50</f>
         <v/>
       </c>
@@ -7582,14 +7600,14 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="30" t="n">
+      <c r="A51" s="31" t="n">
         <v>36.68</v>
       </c>
-      <c r="B51" s="30">
+      <c r="B51" s="31">
         <f>A51-$B$12</f>
         <v/>
       </c>
-      <c r="C51" s="30">
+      <c r="C51" s="31">
         <f>MAX(0,A51-$B$6)</f>
         <v/>
       </c>
@@ -7597,15 +7615,15 @@
         <f>IF(C51&lt;=0,0,($B$7+$B$9*C51)*C51)</f>
         <v/>
       </c>
-      <c r="E51" s="24">
+      <c r="E51" s="25">
         <f>D51*$B$11</f>
         <v/>
       </c>
-      <c r="F51" s="24">
+      <c r="F51" s="25">
         <f>IF(A51&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A51&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A51,Stage_Storage!$A$11:$A$18,1))+(A51-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A51,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A51,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A51,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A51,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A51,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G51" s="32">
+      <c r="G51" s="33">
         <f>E51+F51</f>
         <v/>
       </c>
@@ -7627,14 +7645,14 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="30" t="n">
+      <c r="A52" s="31" t="n">
         <v>36.73</v>
       </c>
-      <c r="B52" s="30">
+      <c r="B52" s="31">
         <f>A52-$B$12</f>
         <v/>
       </c>
-      <c r="C52" s="30">
+      <c r="C52" s="31">
         <f>MAX(0,A52-$B$6)</f>
         <v/>
       </c>
@@ -7642,15 +7660,15 @@
         <f>IF(C52&lt;=0,0,($B$7+$B$9*C52)*C52)</f>
         <v/>
       </c>
-      <c r="E52" s="24">
+      <c r="E52" s="25">
         <f>D52*$B$11</f>
         <v/>
       </c>
-      <c r="F52" s="24">
+      <c r="F52" s="25">
         <f>IF(A52&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A52&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A52,Stage_Storage!$A$11:$A$18,1))+(A52-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A52,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A52,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A52,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A52,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A52,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G52" s="32">
+      <c r="G52" s="33">
         <f>E52+F52</f>
         <v/>
       </c>
@@ -7672,14 +7690,14 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="30" t="n">
+      <c r="A53" s="31" t="n">
         <v>36.78</v>
       </c>
-      <c r="B53" s="30">
+      <c r="B53" s="31">
         <f>A53-$B$12</f>
         <v/>
       </c>
-      <c r="C53" s="30">
+      <c r="C53" s="31">
         <f>MAX(0,A53-$B$6)</f>
         <v/>
       </c>
@@ -7687,15 +7705,15 @@
         <f>IF(C53&lt;=0,0,($B$7+$B$9*C53)*C53)</f>
         <v/>
       </c>
-      <c r="E53" s="24">
+      <c r="E53" s="25">
         <f>D53*$B$11</f>
         <v/>
       </c>
-      <c r="F53" s="24">
+      <c r="F53" s="25">
         <f>IF(A53&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A53&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A53,Stage_Storage!$A$11:$A$18,1))+(A53-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A53,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A53,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A53,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A53,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A53,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G53" s="32">
+      <c r="G53" s="33">
         <f>E53+F53</f>
         <v/>
       </c>
@@ -7717,14 +7735,14 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="30" t="n">
+      <c r="A54" s="31" t="n">
         <v>36.83</v>
       </c>
-      <c r="B54" s="30">
+      <c r="B54" s="31">
         <f>A54-$B$12</f>
         <v/>
       </c>
-      <c r="C54" s="30">
+      <c r="C54" s="31">
         <f>MAX(0,A54-$B$6)</f>
         <v/>
       </c>
@@ -7732,15 +7750,15 @@
         <f>IF(C54&lt;=0,0,($B$7+$B$9*C54)*C54)</f>
         <v/>
       </c>
-      <c r="E54" s="24">
+      <c r="E54" s="25">
         <f>D54*$B$11</f>
         <v/>
       </c>
-      <c r="F54" s="24">
+      <c r="F54" s="25">
         <f>IF(A54&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A54&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A54,Stage_Storage!$A$11:$A$18,1))+(A54-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A54,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A54,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A54,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A54,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A54,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G54" s="32">
+      <c r="G54" s="33">
         <f>E54+F54</f>
         <v/>
       </c>
@@ -7762,14 +7780,14 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="30" t="n">
+      <c r="A55" s="31" t="n">
         <v>36.88</v>
       </c>
-      <c r="B55" s="30">
+      <c r="B55" s="31">
         <f>A55-$B$12</f>
         <v/>
       </c>
-      <c r="C55" s="30">
+      <c r="C55" s="31">
         <f>MAX(0,A55-$B$6)</f>
         <v/>
       </c>
@@ -7777,15 +7795,15 @@
         <f>IF(C55&lt;=0,0,($B$7+$B$9*C55)*C55)</f>
         <v/>
       </c>
-      <c r="E55" s="24">
+      <c r="E55" s="25">
         <f>D55*$B$11</f>
         <v/>
       </c>
-      <c r="F55" s="24">
+      <c r="F55" s="25">
         <f>IF(A55&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A55&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A55,Stage_Storage!$A$11:$A$18,1))+(A55-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A55,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A55,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A55,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A55,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A55,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G55" s="32">
+      <c r="G55" s="33">
         <f>E55+F55</f>
         <v/>
       </c>
@@ -7807,14 +7825,14 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="30" t="n">
+      <c r="A56" s="31" t="n">
         <v>36.93</v>
       </c>
-      <c r="B56" s="30">
+      <c r="B56" s="31">
         <f>A56-$B$12</f>
         <v/>
       </c>
-      <c r="C56" s="30">
+      <c r="C56" s="31">
         <f>MAX(0,A56-$B$6)</f>
         <v/>
       </c>
@@ -7822,15 +7840,15 @@
         <f>IF(C56&lt;=0,0,($B$7+$B$9*C56)*C56)</f>
         <v/>
       </c>
-      <c r="E56" s="24">
+      <c r="E56" s="25">
         <f>D56*$B$11</f>
         <v/>
       </c>
-      <c r="F56" s="24">
+      <c r="F56" s="25">
         <f>IF(A56&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A56&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A56,Stage_Storage!$A$11:$A$18,1))+(A56-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A56,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A56,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A56,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A56,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A56,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G56" s="32">
+      <c r="G56" s="33">
         <f>E56+F56</f>
         <v/>
       </c>
@@ -7852,14 +7870,14 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="30" t="n">
+      <c r="A57" s="31" t="n">
         <v>36.98</v>
       </c>
-      <c r="B57" s="30">
+      <c r="B57" s="31">
         <f>A57-$B$12</f>
         <v/>
       </c>
-      <c r="C57" s="30">
+      <c r="C57" s="31">
         <f>MAX(0,A57-$B$6)</f>
         <v/>
       </c>
@@ -7867,15 +7885,15 @@
         <f>IF(C57&lt;=0,0,($B$7+$B$9*C57)*C57)</f>
         <v/>
       </c>
-      <c r="E57" s="24">
+      <c r="E57" s="25">
         <f>D57*$B$11</f>
         <v/>
       </c>
-      <c r="F57" s="24">
+      <c r="F57" s="25">
         <f>IF(A57&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A57&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A57,Stage_Storage!$A$11:$A$18,1))+(A57-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A57,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A57,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A57,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A57,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A57,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G57" s="32">
+      <c r="G57" s="33">
         <f>E57+F57</f>
         <v/>
       </c>
@@ -7897,14 +7915,14 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="30" t="n">
+      <c r="A58" s="31" t="n">
         <v>37.03</v>
       </c>
-      <c r="B58" s="30">
+      <c r="B58" s="31">
         <f>A58-$B$12</f>
         <v/>
       </c>
-      <c r="C58" s="30">
+      <c r="C58" s="31">
         <f>MAX(0,A58-$B$6)</f>
         <v/>
       </c>
@@ -7912,15 +7930,15 @@
         <f>IF(C58&lt;=0,0,($B$7+$B$9*C58)*C58)</f>
         <v/>
       </c>
-      <c r="E58" s="24">
+      <c r="E58" s="25">
         <f>D58*$B$11</f>
         <v/>
       </c>
-      <c r="F58" s="24">
+      <c r="F58" s="25">
         <f>IF(A58&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A58&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A58,Stage_Storage!$A$11:$A$18,1))+(A58-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A58,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A58,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A58,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A58,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A58,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G58" s="32">
+      <c r="G58" s="33">
         <f>E58+F58</f>
         <v/>
       </c>
@@ -7942,14 +7960,14 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="30" t="n">
+      <c r="A59" s="31" t="n">
         <v>37.08</v>
       </c>
-      <c r="B59" s="30">
+      <c r="B59" s="31">
         <f>A59-$B$12</f>
         <v/>
       </c>
-      <c r="C59" s="30">
+      <c r="C59" s="31">
         <f>MAX(0,A59-$B$6)</f>
         <v/>
       </c>
@@ -7957,15 +7975,15 @@
         <f>IF(C59&lt;=0,0,($B$7+$B$9*C59)*C59)</f>
         <v/>
       </c>
-      <c r="E59" s="24">
+      <c r="E59" s="25">
         <f>D59*$B$11</f>
         <v/>
       </c>
-      <c r="F59" s="24">
+      <c r="F59" s="25">
         <f>IF(A59&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A59&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A59,Stage_Storage!$A$11:$A$18,1))+(A59-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A59,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A59,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A59,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A59,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A59,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G59" s="32">
+      <c r="G59" s="33">
         <f>E59+F59</f>
         <v/>
       </c>
@@ -7987,14 +8005,14 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="30" t="n">
+      <c r="A60" s="31" t="n">
         <v>37.13</v>
       </c>
-      <c r="B60" s="30">
+      <c r="B60" s="31">
         <f>A60-$B$12</f>
         <v/>
       </c>
-      <c r="C60" s="30">
+      <c r="C60" s="31">
         <f>MAX(0,A60-$B$6)</f>
         <v/>
       </c>
@@ -8002,15 +8020,15 @@
         <f>IF(C60&lt;=0,0,($B$7+$B$9*C60)*C60)</f>
         <v/>
       </c>
-      <c r="E60" s="24">
+      <c r="E60" s="25">
         <f>D60*$B$11</f>
         <v/>
       </c>
-      <c r="F60" s="24">
+      <c r="F60" s="25">
         <f>IF(A60&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A60&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1))+(A60-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G60" s="32">
+      <c r="G60" s="33">
         <f>E60+F60</f>
         <v/>
       </c>
@@ -8032,14 +8050,14 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="30" t="n">
+      <c r="A61" s="31" t="n">
         <v>37.18</v>
       </c>
-      <c r="B61" s="30">
+      <c r="B61" s="31">
         <f>A61-$B$12</f>
         <v/>
       </c>
-      <c r="C61" s="30">
+      <c r="C61" s="31">
         <f>MAX(0,A61-$B$6)</f>
         <v/>
       </c>
@@ -8047,15 +8065,15 @@
         <f>IF(C61&lt;=0,0,($B$7+$B$9*C61)*C61)</f>
         <v/>
       </c>
-      <c r="E61" s="24">
+      <c r="E61" s="25">
         <f>D61*$B$11</f>
         <v/>
       </c>
-      <c r="F61" s="24">
+      <c r="F61" s="25">
         <f>IF(A61&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A61&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1))+(A61-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G61" s="32">
+      <c r="G61" s="33">
         <f>E61+F61</f>
         <v/>
       </c>
@@ -8077,14 +8095,14 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="30" t="n">
+      <c r="A62" s="31" t="n">
         <v>37.23</v>
       </c>
-      <c r="B62" s="30">
+      <c r="B62" s="31">
         <f>A62-$B$12</f>
         <v/>
       </c>
-      <c r="C62" s="30">
+      <c r="C62" s="31">
         <f>MAX(0,A62-$B$6)</f>
         <v/>
       </c>
@@ -8092,15 +8110,15 @@
         <f>IF(C62&lt;=0,0,($B$7+$B$9*C62)*C62)</f>
         <v/>
       </c>
-      <c r="E62" s="24">
+      <c r="E62" s="25">
         <f>D62*$B$11</f>
         <v/>
       </c>
-      <c r="F62" s="24">
+      <c r="F62" s="25">
         <f>IF(A62&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A62&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1))+(A62-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G62" s="32">
+      <c r="G62" s="33">
         <f>E62+F62</f>
         <v/>
       </c>
@@ -8122,14 +8140,14 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="30" t="n">
+      <c r="A63" s="31" t="n">
         <v>37.28</v>
       </c>
-      <c r="B63" s="30">
+      <c r="B63" s="31">
         <f>A63-$B$12</f>
         <v/>
       </c>
-      <c r="C63" s="30">
+      <c r="C63" s="31">
         <f>MAX(0,A63-$B$6)</f>
         <v/>
       </c>
@@ -8137,15 +8155,15 @@
         <f>IF(C63&lt;=0,0,($B$7+$B$9*C63)*C63)</f>
         <v/>
       </c>
-      <c r="E63" s="24">
+      <c r="E63" s="25">
         <f>D63*$B$11</f>
         <v/>
       </c>
-      <c r="F63" s="24">
+      <c r="F63" s="25">
         <f>IF(A63&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A63&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1))+(A63-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G63" s="32">
+      <c r="G63" s="33">
         <f>E63+F63</f>
         <v/>
       </c>
@@ -8167,14 +8185,14 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="30" t="n">
+      <c r="A64" s="31" t="n">
         <v>37.33</v>
       </c>
-      <c r="B64" s="30">
+      <c r="B64" s="31">
         <f>A64-$B$12</f>
         <v/>
       </c>
-      <c r="C64" s="30">
+      <c r="C64" s="31">
         <f>MAX(0,A64-$B$6)</f>
         <v/>
       </c>
@@ -8182,15 +8200,15 @@
         <f>IF(C64&lt;=0,0,($B$7+$B$9*C64)*C64)</f>
         <v/>
       </c>
-      <c r="E64" s="24">
+      <c r="E64" s="25">
         <f>D64*$B$11</f>
         <v/>
       </c>
-      <c r="F64" s="24">
+      <c r="F64" s="25">
         <f>IF(A64&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A64&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1))+(A64-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G64" s="32">
+      <c r="G64" s="33">
         <f>E64+F64</f>
         <v/>
       </c>
@@ -8212,14 +8230,14 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="30" t="n">
+      <c r="A65" s="31" t="n">
         <v>37.38</v>
       </c>
-      <c r="B65" s="30">
+      <c r="B65" s="31">
         <f>A65-$B$12</f>
         <v/>
       </c>
-      <c r="C65" s="30">
+      <c r="C65" s="31">
         <f>MAX(0,A65-$B$6)</f>
         <v/>
       </c>
@@ -8227,15 +8245,15 @@
         <f>IF(C65&lt;=0,0,($B$7+$B$9*C65)*C65)</f>
         <v/>
       </c>
-      <c r="E65" s="24">
+      <c r="E65" s="25">
         <f>D65*$B$11</f>
         <v/>
       </c>
-      <c r="F65" s="24">
+      <c r="F65" s="25">
         <f>IF(A65&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A65&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1))+(A65-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G65" s="32">
+      <c r="G65" s="33">
         <f>E65+F65</f>
         <v/>
       </c>
@@ -8257,14 +8275,14 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="30" t="n">
+      <c r="A66" s="31" t="n">
         <v>37.43</v>
       </c>
-      <c r="B66" s="30">
+      <c r="B66" s="31">
         <f>A66-$B$12</f>
         <v/>
       </c>
-      <c r="C66" s="30">
+      <c r="C66" s="31">
         <f>MAX(0,A66-$B$6)</f>
         <v/>
       </c>
@@ -8272,15 +8290,15 @@
         <f>IF(C66&lt;=0,0,($B$7+$B$9*C66)*C66)</f>
         <v/>
       </c>
-      <c r="E66" s="24">
+      <c r="E66" s="25">
         <f>D66*$B$11</f>
         <v/>
       </c>
-      <c r="F66" s="24">
+      <c r="F66" s="25">
         <f>IF(A66&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A66&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1))+(A66-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G66" s="32">
+      <c r="G66" s="33">
         <f>E66+F66</f>
         <v/>
       </c>
@@ -8302,14 +8320,14 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="30" t="n">
+      <c r="A67" s="31" t="n">
         <v>37.48</v>
       </c>
-      <c r="B67" s="30">
+      <c r="B67" s="31">
         <f>A67-$B$12</f>
         <v/>
       </c>
-      <c r="C67" s="30">
+      <c r="C67" s="31">
         <f>MAX(0,A67-$B$6)</f>
         <v/>
       </c>
@@ -8317,15 +8335,15 @@
         <f>IF(C67&lt;=0,0,($B$7+$B$9*C67)*C67)</f>
         <v/>
       </c>
-      <c r="E67" s="24">
+      <c r="E67" s="25">
         <f>D67*$B$11</f>
         <v/>
       </c>
-      <c r="F67" s="24">
+      <c r="F67" s="25">
         <f>IF(A67&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A67&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A67,Stage_Storage!$A$11:$A$18,1))+(A67-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A67,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A67,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A67,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A67,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A67,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G67" s="32">
+      <c r="G67" s="33">
         <f>E67+F67</f>
         <v/>
       </c>
@@ -8347,14 +8365,14 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="30" t="n">
+      <c r="A68" s="31" t="n">
         <v>37.53</v>
       </c>
-      <c r="B68" s="30">
+      <c r="B68" s="31">
         <f>A68-$B$12</f>
         <v/>
       </c>
-      <c r="C68" s="30">
+      <c r="C68" s="31">
         <f>MAX(0,A68-$B$6)</f>
         <v/>
       </c>
@@ -8362,15 +8380,15 @@
         <f>IF(C68&lt;=0,0,($B$7+$B$9*C68)*C68)</f>
         <v/>
       </c>
-      <c r="E68" s="24">
+      <c r="E68" s="25">
         <f>D68*$B$11</f>
         <v/>
       </c>
-      <c r="F68" s="24">
+      <c r="F68" s="25">
         <f>IF(A68&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A68&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A68,Stage_Storage!$A$11:$A$18,1))+(A68-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A68,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A68,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A68,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A68,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A68,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G68" s="32">
+      <c r="G68" s="33">
         <f>E68+F68</f>
         <v/>
       </c>
@@ -8392,14 +8410,14 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="30" t="n">
+      <c r="A69" s="31" t="n">
         <v>37.58</v>
       </c>
-      <c r="B69" s="30">
+      <c r="B69" s="31">
         <f>A69-$B$12</f>
         <v/>
       </c>
-      <c r="C69" s="30">
+      <c r="C69" s="31">
         <f>MAX(0,A69-$B$6)</f>
         <v/>
       </c>
@@ -8407,15 +8425,15 @@
         <f>IF(C69&lt;=0,0,($B$7+$B$9*C69)*C69)</f>
         <v/>
       </c>
-      <c r="E69" s="24">
+      <c r="E69" s="25">
         <f>D69*$B$11</f>
         <v/>
       </c>
-      <c r="F69" s="24">
+      <c r="F69" s="25">
         <f>IF(A69&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A69&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A69,Stage_Storage!$A$11:$A$18,1))+(A69-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A69,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A69,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A69,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A69,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A69,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G69" s="32">
+      <c r="G69" s="33">
         <f>E69+F69</f>
         <v/>
       </c>
@@ -8437,14 +8455,14 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30" t="n">
+      <c r="A70" s="31" t="n">
         <v>37.63</v>
       </c>
-      <c r="B70" s="30">
+      <c r="B70" s="31">
         <f>A70-$B$12</f>
         <v/>
       </c>
-      <c r="C70" s="30">
+      <c r="C70" s="31">
         <f>MAX(0,A70-$B$6)</f>
         <v/>
       </c>
@@ -8452,15 +8470,15 @@
         <f>IF(C70&lt;=0,0,($B$7+$B$9*C70)*C70)</f>
         <v/>
       </c>
-      <c r="E70" s="24">
+      <c r="E70" s="25">
         <f>D70*$B$11</f>
         <v/>
       </c>
-      <c r="F70" s="24">
+      <c r="F70" s="25">
         <f>IF(A70&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A70&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A70,Stage_Storage!$A$11:$A$18,1))+(A70-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A70,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A70,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A70,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A70,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A70,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G70" s="32">
+      <c r="G70" s="33">
         <f>E70+F70</f>
         <v/>
       </c>
@@ -8482,14 +8500,14 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="30" t="n">
+      <c r="A71" s="31" t="n">
         <v>37.68</v>
       </c>
-      <c r="B71" s="30">
+      <c r="B71" s="31">
         <f>A71-$B$12</f>
         <v/>
       </c>
-      <c r="C71" s="30">
+      <c r="C71" s="31">
         <f>MAX(0,A71-$B$6)</f>
         <v/>
       </c>
@@ -8497,15 +8515,15 @@
         <f>IF(C71&lt;=0,0,($B$7+$B$9*C71)*C71)</f>
         <v/>
       </c>
-      <c r="E71" s="24">
+      <c r="E71" s="25">
         <f>D71*$B$11</f>
         <v/>
       </c>
-      <c r="F71" s="24">
+      <c r="F71" s="25">
         <f>IF(A71&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A71&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A71,Stage_Storage!$A$11:$A$18,1))+(A71-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A71,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A71,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A71,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A71,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A71,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G71" s="32">
+      <c r="G71" s="33">
         <f>E71+F71</f>
         <v/>
       </c>
@@ -8527,14 +8545,14 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="30" t="n">
+      <c r="A72" s="31" t="n">
         <v>37.73</v>
       </c>
-      <c r="B72" s="30">
+      <c r="B72" s="31">
         <f>A72-$B$12</f>
         <v/>
       </c>
-      <c r="C72" s="30">
+      <c r="C72" s="31">
         <f>MAX(0,A72-$B$6)</f>
         <v/>
       </c>
@@ -8542,15 +8560,15 @@
         <f>IF(C72&lt;=0,0,($B$7+$B$9*C72)*C72)</f>
         <v/>
       </c>
-      <c r="E72" s="24">
+      <c r="E72" s="25">
         <f>D72*$B$11</f>
         <v/>
       </c>
-      <c r="F72" s="24">
+      <c r="F72" s="25">
         <f>IF(A72&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A72&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A72,Stage_Storage!$A$11:$A$18,1))+(A72-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A72,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A72,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A72,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A72,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A72,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G72" s="32">
+      <c r="G72" s="33">
         <f>E72+F72</f>
         <v/>
       </c>
@@ -8572,14 +8590,14 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="30" t="n">
+      <c r="A73" s="31" t="n">
         <v>37.78</v>
       </c>
-      <c r="B73" s="30">
+      <c r="B73" s="31">
         <f>A73-$B$12</f>
         <v/>
       </c>
-      <c r="C73" s="30">
+      <c r="C73" s="31">
         <f>MAX(0,A73-$B$6)</f>
         <v/>
       </c>
@@ -8587,15 +8605,15 @@
         <f>IF(C73&lt;=0,0,($B$7+$B$9*C73)*C73)</f>
         <v/>
       </c>
-      <c r="E73" s="24">
+      <c r="E73" s="25">
         <f>D73*$B$11</f>
         <v/>
       </c>
-      <c r="F73" s="24">
+      <c r="F73" s="25">
         <f>IF(A73&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A73&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A73,Stage_Storage!$A$11:$A$18,1))+(A73-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A73,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A73,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A73,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A73,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A73,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G73" s="32">
+      <c r="G73" s="33">
         <f>E73+F73</f>
         <v/>
       </c>
@@ -8617,14 +8635,14 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="30" t="n">
+      <c r="A74" s="31" t="n">
         <v>37.83</v>
       </c>
-      <c r="B74" s="30">
+      <c r="B74" s="31">
         <f>A74-$B$12</f>
         <v/>
       </c>
-      <c r="C74" s="30">
+      <c r="C74" s="31">
         <f>MAX(0,A74-$B$6)</f>
         <v/>
       </c>
@@ -8632,15 +8650,15 @@
         <f>IF(C74&lt;=0,0,($B$7+$B$9*C74)*C74)</f>
         <v/>
       </c>
-      <c r="E74" s="24">
+      <c r="E74" s="25">
         <f>D74*$B$11</f>
         <v/>
       </c>
-      <c r="F74" s="24">
+      <c r="F74" s="25">
         <f>IF(A74&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A74&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A74,Stage_Storage!$A$11:$A$18,1))+(A74-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A74,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A74,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A74,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A74,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A74,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G74" s="32">
+      <c r="G74" s="33">
         <f>E74+F74</f>
         <v/>
       </c>
@@ -8662,14 +8680,14 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="30" t="n">
+      <c r="A75" s="31" t="n">
         <v>37.88</v>
       </c>
-      <c r="B75" s="30">
+      <c r="B75" s="31">
         <f>A75-$B$12</f>
         <v/>
       </c>
-      <c r="C75" s="30">
+      <c r="C75" s="31">
         <f>MAX(0,A75-$B$6)</f>
         <v/>
       </c>
@@ -8677,15 +8695,15 @@
         <f>IF(C75&lt;=0,0,($B$7+$B$9*C75)*C75)</f>
         <v/>
       </c>
-      <c r="E75" s="24">
+      <c r="E75" s="25">
         <f>D75*$B$11</f>
         <v/>
       </c>
-      <c r="F75" s="24">
+      <c r="F75" s="25">
         <f>IF(A75&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A75&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A75,Stage_Storage!$A$11:$A$18,1))+(A75-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A75,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A75,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A75,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A75,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A75,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G75" s="32">
+      <c r="G75" s="33">
         <f>E75+F75</f>
         <v/>
       </c>
@@ -8707,14 +8725,14 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="30" t="n">
+      <c r="A76" s="31" t="n">
         <v>37.93</v>
       </c>
-      <c r="B76" s="30">
+      <c r="B76" s="31">
         <f>A76-$B$12</f>
         <v/>
       </c>
-      <c r="C76" s="30">
+      <c r="C76" s="31">
         <f>MAX(0,A76-$B$6)</f>
         <v/>
       </c>
@@ -8722,15 +8740,15 @@
         <f>IF(C76&lt;=0,0,($B$7+$B$9*C76)*C76)</f>
         <v/>
       </c>
-      <c r="E76" s="24">
+      <c r="E76" s="25">
         <f>D76*$B$11</f>
         <v/>
       </c>
-      <c r="F76" s="24">
+      <c r="F76" s="25">
         <f>IF(A76&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A76&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A76,Stage_Storage!$A$11:$A$18,1))+(A76-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A76,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A76,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A76,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A76,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A76,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G76" s="32">
+      <c r="G76" s="33">
         <f>E76+F76</f>
         <v/>
       </c>
@@ -8752,14 +8770,14 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="30" t="n">
+      <c r="A77" s="31" t="n">
         <v>37.98</v>
       </c>
-      <c r="B77" s="30">
+      <c r="B77" s="31">
         <f>A77-$B$12</f>
         <v/>
       </c>
-      <c r="C77" s="30">
+      <c r="C77" s="31">
         <f>MAX(0,A77-$B$6)</f>
         <v/>
       </c>
@@ -8767,15 +8785,15 @@
         <f>IF(C77&lt;=0,0,($B$7+$B$9*C77)*C77)</f>
         <v/>
       </c>
-      <c r="E77" s="24">
+      <c r="E77" s="25">
         <f>D77*$B$11</f>
         <v/>
       </c>
-      <c r="F77" s="24">
+      <c r="F77" s="25">
         <f>IF(A77&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A77&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A77,Stage_Storage!$A$11:$A$18,1))+(A77-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A77,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A77,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A77,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A77,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A77,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G77" s="32">
+      <c r="G77" s="33">
         <f>E77+F77</f>
         <v/>
       </c>
@@ -8797,14 +8815,14 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="30" t="n">
+      <c r="A78" s="31" t="n">
         <v>38.03</v>
       </c>
-      <c r="B78" s="30">
+      <c r="B78" s="31">
         <f>A78-$B$12</f>
         <v/>
       </c>
-      <c r="C78" s="30">
+      <c r="C78" s="31">
         <f>MAX(0,A78-$B$6)</f>
         <v/>
       </c>
@@ -8812,15 +8830,15 @@
         <f>IF(C78&lt;=0,0,($B$7+$B$9*C78)*C78)</f>
         <v/>
       </c>
-      <c r="E78" s="24">
+      <c r="E78" s="25">
         <f>D78*$B$11</f>
         <v/>
       </c>
-      <c r="F78" s="24">
+      <c r="F78" s="25">
         <f>IF(A78&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A78&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A78,Stage_Storage!$A$11:$A$18,1))+(A78-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A78,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A78,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A78,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A78,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A78,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G78" s="32">
+      <c r="G78" s="33">
         <f>E78+F78</f>
         <v/>
       </c>
@@ -8842,14 +8860,14 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="30" t="n">
+      <c r="A79" s="31" t="n">
         <v>38.08</v>
       </c>
-      <c r="B79" s="30">
+      <c r="B79" s="31">
         <f>A79-$B$12</f>
         <v/>
       </c>
-      <c r="C79" s="30">
+      <c r="C79" s="31">
         <f>MAX(0,A79-$B$6)</f>
         <v/>
       </c>
@@ -8857,15 +8875,15 @@
         <f>IF(C79&lt;=0,0,($B$7+$B$9*C79)*C79)</f>
         <v/>
       </c>
-      <c r="E79" s="24">
+      <c r="E79" s="25">
         <f>D79*$B$11</f>
         <v/>
       </c>
-      <c r="F79" s="24">
+      <c r="F79" s="25">
         <f>IF(A79&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A79&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A79,Stage_Storage!$A$11:$A$18,1))+(A79-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A79,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A79,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A79,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A79,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A79,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G79" s="32">
+      <c r="G79" s="33">
         <f>E79+F79</f>
         <v/>
       </c>
@@ -8887,14 +8905,14 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="30" t="n">
+      <c r="A80" s="31" t="n">
         <v>38.13</v>
       </c>
-      <c r="B80" s="30">
+      <c r="B80" s="31">
         <f>A80-$B$12</f>
         <v/>
       </c>
-      <c r="C80" s="30">
+      <c r="C80" s="31">
         <f>MAX(0,A80-$B$6)</f>
         <v/>
       </c>
@@ -8902,15 +8920,15 @@
         <f>IF(C80&lt;=0,0,($B$7+$B$9*C80)*C80)</f>
         <v/>
       </c>
-      <c r="E80" s="24">
+      <c r="E80" s="25">
         <f>D80*$B$11</f>
         <v/>
       </c>
-      <c r="F80" s="24">
+      <c r="F80" s="25">
         <f>IF(A80&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A80&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A80,Stage_Storage!$A$11:$A$18,1))+(A80-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A80,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A80,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A80,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A80,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A80,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G80" s="32">
+      <c r="G80" s="33">
         <f>E80+F80</f>
         <v/>
       </c>
@@ -8932,14 +8950,14 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="30" t="n">
+      <c r="A81" s="31" t="n">
         <v>38.18</v>
       </c>
-      <c r="B81" s="30">
+      <c r="B81" s="31">
         <f>A81-$B$12</f>
         <v/>
       </c>
-      <c r="C81" s="30">
+      <c r="C81" s="31">
         <f>MAX(0,A81-$B$6)</f>
         <v/>
       </c>
@@ -8947,15 +8965,15 @@
         <f>IF(C81&lt;=0,0,($B$7+$B$9*C81)*C81)</f>
         <v/>
       </c>
-      <c r="E81" s="24">
+      <c r="E81" s="25">
         <f>D81*$B$11</f>
         <v/>
       </c>
-      <c r="F81" s="24">
+      <c r="F81" s="25">
         <f>IF(A81&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A81&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A81,Stage_Storage!$A$11:$A$18,1))+(A81-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A81,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A81,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A81,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A81,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A81,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G81" s="32">
+      <c r="G81" s="33">
         <f>E81+F81</f>
         <v/>
       </c>
@@ -8977,14 +8995,14 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="30" t="n">
+      <c r="A82" s="31" t="n">
         <v>38.23</v>
       </c>
-      <c r="B82" s="30">
+      <c r="B82" s="31">
         <f>A82-$B$12</f>
         <v/>
       </c>
-      <c r="C82" s="30">
+      <c r="C82" s="31">
         <f>MAX(0,A82-$B$6)</f>
         <v/>
       </c>
@@ -8992,15 +9010,15 @@
         <f>IF(C82&lt;=0,0,($B$7+$B$9*C82)*C82)</f>
         <v/>
       </c>
-      <c r="E82" s="24">
+      <c r="E82" s="25">
         <f>D82*$B$11</f>
         <v/>
       </c>
-      <c r="F82" s="24">
+      <c r="F82" s="25">
         <f>IF(A82&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A82&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A82,Stage_Storage!$A$11:$A$18,1))+(A82-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A82,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A82,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A82,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A82,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A82,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G82" s="32">
+      <c r="G82" s="33">
         <f>E82+F82</f>
         <v/>
       </c>
@@ -9022,14 +9040,14 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="30" t="n">
+      <c r="A83" s="31" t="n">
         <v>38.28</v>
       </c>
-      <c r="B83" s="30">
+      <c r="B83" s="31">
         <f>A83-$B$12</f>
         <v/>
       </c>
-      <c r="C83" s="30">
+      <c r="C83" s="31">
         <f>MAX(0,A83-$B$6)</f>
         <v/>
       </c>
@@ -9037,15 +9055,15 @@
         <f>IF(C83&lt;=0,0,($B$7+$B$9*C83)*C83)</f>
         <v/>
       </c>
-      <c r="E83" s="24">
+      <c r="E83" s="25">
         <f>D83*$B$11</f>
         <v/>
       </c>
-      <c r="F83" s="24">
+      <c r="F83" s="25">
         <f>IF(A83&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A83&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A83,Stage_Storage!$A$11:$A$18,1))+(A83-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A83,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A83,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A83,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A83,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A83,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G83" s="32">
+      <c r="G83" s="33">
         <f>E83+F83</f>
         <v/>
       </c>
@@ -9067,14 +9085,14 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="30" t="n">
+      <c r="A84" s="31" t="n">
         <v>38.33</v>
       </c>
-      <c r="B84" s="30">
+      <c r="B84" s="31">
         <f>A84-$B$12</f>
         <v/>
       </c>
-      <c r="C84" s="30">
+      <c r="C84" s="31">
         <f>MAX(0,A84-$B$6)</f>
         <v/>
       </c>
@@ -9082,15 +9100,15 @@
         <f>IF(C84&lt;=0,0,($B$7+$B$9*C84)*C84)</f>
         <v/>
       </c>
-      <c r="E84" s="24">
+      <c r="E84" s="25">
         <f>D84*$B$11</f>
         <v/>
       </c>
-      <c r="F84" s="24">
+      <c r="F84" s="25">
         <f>IF(A84&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A84&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A84,Stage_Storage!$A$11:$A$18,1))+(A84-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A84,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A84,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A84,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A84,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A84,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G84" s="32">
+      <c r="G84" s="33">
         <f>E84+F84</f>
         <v/>
       </c>
@@ -9112,14 +9130,14 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="30" t="n">
+      <c r="A85" s="31" t="n">
         <v>38.38</v>
       </c>
-      <c r="B85" s="30">
+      <c r="B85" s="31">
         <f>A85-$B$12</f>
         <v/>
       </c>
-      <c r="C85" s="30">
+      <c r="C85" s="31">
         <f>MAX(0,A85-$B$6)</f>
         <v/>
       </c>
@@ -9127,15 +9145,15 @@
         <f>IF(C85&lt;=0,0,($B$7+$B$9*C85)*C85)</f>
         <v/>
       </c>
-      <c r="E85" s="24">
+      <c r="E85" s="25">
         <f>D85*$B$11</f>
         <v/>
       </c>
-      <c r="F85" s="24">
+      <c r="F85" s="25">
         <f>IF(A85&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A85&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A85,Stage_Storage!$A$11:$A$18,1))+(A85-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A85,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A85,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A85,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A85,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A85,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G85" s="32">
+      <c r="G85" s="33">
         <f>E85+F85</f>
         <v/>
       </c>
@@ -9157,14 +9175,14 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="30" t="n">
+      <c r="A86" s="31" t="n">
         <v>38.43</v>
       </c>
-      <c r="B86" s="30">
+      <c r="B86" s="31">
         <f>A86-$B$12</f>
         <v/>
       </c>
-      <c r="C86" s="30">
+      <c r="C86" s="31">
         <f>MAX(0,A86-$B$6)</f>
         <v/>
       </c>
@@ -9172,15 +9190,15 @@
         <f>IF(C86&lt;=0,0,($B$7+$B$9*C86)*C86)</f>
         <v/>
       </c>
-      <c r="E86" s="24">
+      <c r="E86" s="25">
         <f>D86*$B$11</f>
         <v/>
       </c>
-      <c r="F86" s="24">
+      <c r="F86" s="25">
         <f>IF(A86&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A86&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A86,Stage_Storage!$A$11:$A$18,1))+(A86-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A86,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A86,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A86,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A86,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A86,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G86" s="32">
+      <c r="G86" s="33">
         <f>E86+F86</f>
         <v/>
       </c>
@@ -9202,14 +9220,14 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="30" t="n">
+      <c r="A87" s="31" t="n">
         <v>38.48</v>
       </c>
-      <c r="B87" s="30">
+      <c r="B87" s="31">
         <f>A87-$B$12</f>
         <v/>
       </c>
-      <c r="C87" s="30">
+      <c r="C87" s="31">
         <f>MAX(0,A87-$B$6)</f>
         <v/>
       </c>
@@ -9217,15 +9235,15 @@
         <f>IF(C87&lt;=0,0,($B$7+$B$9*C87)*C87)</f>
         <v/>
       </c>
-      <c r="E87" s="24">
+      <c r="E87" s="25">
         <f>D87*$B$11</f>
         <v/>
       </c>
-      <c r="F87" s="24">
+      <c r="F87" s="25">
         <f>IF(A87&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A87&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A87,Stage_Storage!$A$11:$A$18,1))+(A87-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A87,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A87,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A87,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A87,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A87,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G87" s="32">
+      <c r="G87" s="33">
         <f>E87+F87</f>
         <v/>
       </c>
@@ -9247,14 +9265,14 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="30" t="n">
+      <c r="A88" s="31" t="n">
         <v>38.53</v>
       </c>
-      <c r="B88" s="30">
+      <c r="B88" s="31">
         <f>A88-$B$12</f>
         <v/>
       </c>
-      <c r="C88" s="30">
+      <c r="C88" s="31">
         <f>MAX(0,A88-$B$6)</f>
         <v/>
       </c>
@@ -9262,15 +9280,15 @@
         <f>IF(C88&lt;=0,0,($B$7+$B$9*C88)*C88)</f>
         <v/>
       </c>
-      <c r="E88" s="24">
+      <c r="E88" s="25">
         <f>D88*$B$11</f>
         <v/>
       </c>
-      <c r="F88" s="24">
+      <c r="F88" s="25">
         <f>IF(A88&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A88&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A88,Stage_Storage!$A$11:$A$18,1))+(A88-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A88,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A88,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A88,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A88,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A88,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G88" s="32">
+      <c r="G88" s="33">
         <f>E88+F88</f>
         <v/>
       </c>
@@ -9292,14 +9310,14 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="30" t="n">
+      <c r="A89" s="31" t="n">
         <v>38.58</v>
       </c>
-      <c r="B89" s="30">
+      <c r="B89" s="31">
         <f>A89-$B$12</f>
         <v/>
       </c>
-      <c r="C89" s="30">
+      <c r="C89" s="31">
         <f>MAX(0,A89-$B$6)</f>
         <v/>
       </c>
@@ -9307,15 +9325,15 @@
         <f>IF(C89&lt;=0,0,($B$7+$B$9*C89)*C89)</f>
         <v/>
       </c>
-      <c r="E89" s="24">
+      <c r="E89" s="25">
         <f>D89*$B$11</f>
         <v/>
       </c>
-      <c r="F89" s="24">
+      <c r="F89" s="25">
         <f>IF(A89&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A89&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A89,Stage_Storage!$A$11:$A$18,1))+(A89-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A89,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A89,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A89,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A89,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A89,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G89" s="32">
+      <c r="G89" s="33">
         <f>E89+F89</f>
         <v/>
       </c>
@@ -9337,14 +9355,14 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="30" t="n">
+      <c r="A90" s="31" t="n">
         <v>38.63</v>
       </c>
-      <c r="B90" s="30">
+      <c r="B90" s="31">
         <f>A90-$B$12</f>
         <v/>
       </c>
-      <c r="C90" s="30">
+      <c r="C90" s="31">
         <f>MAX(0,A90-$B$6)</f>
         <v/>
       </c>
@@ -9352,15 +9370,15 @@
         <f>IF(C90&lt;=0,0,($B$7+$B$9*C90)*C90)</f>
         <v/>
       </c>
-      <c r="E90" s="24">
+      <c r="E90" s="25">
         <f>D90*$B$11</f>
         <v/>
       </c>
-      <c r="F90" s="24">
+      <c r="F90" s="25">
         <f>IF(A90&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A90&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A90,Stage_Storage!$A$11:$A$18,1))+(A90-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A90,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A90,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A90,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A90,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A90,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G90" s="32">
+      <c r="G90" s="33">
         <f>E90+F90</f>
         <v/>
       </c>
@@ -9382,14 +9400,14 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="30" t="n">
+      <c r="A91" s="31" t="n">
         <v>38.68</v>
       </c>
-      <c r="B91" s="30">
+      <c r="B91" s="31">
         <f>A91-$B$12</f>
         <v/>
       </c>
-      <c r="C91" s="30">
+      <c r="C91" s="31">
         <f>MAX(0,A91-$B$6)</f>
         <v/>
       </c>
@@ -9397,15 +9415,15 @@
         <f>IF(C91&lt;=0,0,($B$7+$B$9*C91)*C91)</f>
         <v/>
       </c>
-      <c r="E91" s="24">
+      <c r="E91" s="25">
         <f>D91*$B$11</f>
         <v/>
       </c>
-      <c r="F91" s="24">
+      <c r="F91" s="25">
         <f>IF(A91&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A91&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A91,Stage_Storage!$A$11:$A$18,1))+(A91-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A91,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A91,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A91,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A91,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A91,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G91" s="32">
+      <c r="G91" s="33">
         <f>E91+F91</f>
         <v/>
       </c>
@@ -9427,14 +9445,14 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="30" t="n">
+      <c r="A92" s="31" t="n">
         <v>38.73</v>
       </c>
-      <c r="B92" s="30">
+      <c r="B92" s="31">
         <f>A92-$B$12</f>
         <v/>
       </c>
-      <c r="C92" s="30">
+      <c r="C92" s="31">
         <f>MAX(0,A92-$B$6)</f>
         <v/>
       </c>
@@ -9442,15 +9460,15 @@
         <f>IF(C92&lt;=0,0,($B$7+$B$9*C92)*C92)</f>
         <v/>
       </c>
-      <c r="E92" s="24">
+      <c r="E92" s="25">
         <f>D92*$B$11</f>
         <v/>
       </c>
-      <c r="F92" s="24">
+      <c r="F92" s="25">
         <f>IF(A92&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A92&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A92,Stage_Storage!$A$11:$A$18,1))+(A92-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A92,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A92,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A92,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A92,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A92,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G92" s="32">
+      <c r="G92" s="33">
         <f>E92+F92</f>
         <v/>
       </c>
@@ -9472,14 +9490,14 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="30" t="n">
+      <c r="A93" s="31" t="n">
         <v>38.78</v>
       </c>
-      <c r="B93" s="30">
+      <c r="B93" s="31">
         <f>A93-$B$12</f>
         <v/>
       </c>
-      <c r="C93" s="30">
+      <c r="C93" s="31">
         <f>MAX(0,A93-$B$6)</f>
         <v/>
       </c>
@@ -9487,15 +9505,15 @@
         <f>IF(C93&lt;=0,0,($B$7+$B$9*C93)*C93)</f>
         <v/>
       </c>
-      <c r="E93" s="24">
+      <c r="E93" s="25">
         <f>D93*$B$11</f>
         <v/>
       </c>
-      <c r="F93" s="24">
+      <c r="F93" s="25">
         <f>IF(A93&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A93&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A93,Stage_Storage!$A$11:$A$18,1))+(A93-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A93,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A93,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A93,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A93,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A93,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G93" s="32">
+      <c r="G93" s="33">
         <f>E93+F93</f>
         <v/>
       </c>
@@ -9517,14 +9535,14 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="30" t="n">
+      <c r="A94" s="31" t="n">
         <v>38.83</v>
       </c>
-      <c r="B94" s="30">
+      <c r="B94" s="31">
         <f>A94-$B$12</f>
         <v/>
       </c>
-      <c r="C94" s="30">
+      <c r="C94" s="31">
         <f>MAX(0,A94-$B$6)</f>
         <v/>
       </c>
@@ -9532,15 +9550,15 @@
         <f>IF(C94&lt;=0,0,($B$7+$B$9*C94)*C94)</f>
         <v/>
       </c>
-      <c r="E94" s="24">
+      <c r="E94" s="25">
         <f>D94*$B$11</f>
         <v/>
       </c>
-      <c r="F94" s="24">
+      <c r="F94" s="25">
         <f>IF(A94&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A94&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A94,Stage_Storage!$A$11:$A$18,1))+(A94-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A94,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A94,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A94,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A94,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A94,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G94" s="32">
+      <c r="G94" s="33">
         <f>E94+F94</f>
         <v/>
       </c>
@@ -9562,14 +9580,14 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="30" t="n">
+      <c r="A95" s="31" t="n">
         <v>38.88</v>
       </c>
-      <c r="B95" s="30">
+      <c r="B95" s="31">
         <f>A95-$B$12</f>
         <v/>
       </c>
-      <c r="C95" s="30">
+      <c r="C95" s="31">
         <f>MAX(0,A95-$B$6)</f>
         <v/>
       </c>
@@ -9577,15 +9595,15 @@
         <f>IF(C95&lt;=0,0,($B$7+$B$9*C95)*C95)</f>
         <v/>
       </c>
-      <c r="E95" s="24">
+      <c r="E95" s="25">
         <f>D95*$B$11</f>
         <v/>
       </c>
-      <c r="F95" s="24">
+      <c r="F95" s="25">
         <f>IF(A95&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A95&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A95,Stage_Storage!$A$11:$A$18,1))+(A95-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A95,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A95,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A95,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A95,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A95,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G95" s="32">
+      <c r="G95" s="33">
         <f>E95+F95</f>
         <v/>
       </c>
@@ -9607,14 +9625,14 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="30" t="n">
+      <c r="A96" s="31" t="n">
         <v>38.93</v>
       </c>
-      <c r="B96" s="30">
+      <c r="B96" s="31">
         <f>A96-$B$12</f>
         <v/>
       </c>
-      <c r="C96" s="30">
+      <c r="C96" s="31">
         <f>MAX(0,A96-$B$6)</f>
         <v/>
       </c>
@@ -9622,15 +9640,15 @@
         <f>IF(C96&lt;=0,0,($B$7+$B$9*C96)*C96)</f>
         <v/>
       </c>
-      <c r="E96" s="24">
+      <c r="E96" s="25">
         <f>D96*$B$11</f>
         <v/>
       </c>
-      <c r="F96" s="24">
+      <c r="F96" s="25">
         <f>IF(A96&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A96&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A96,Stage_Storage!$A$11:$A$18,1))+(A96-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A96,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A96,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A96,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A96,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A96,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G96" s="32">
+      <c r="G96" s="33">
         <f>E96+F96</f>
         <v/>
       </c>
@@ -9652,14 +9670,14 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="30" t="n">
+      <c r="A97" s="31" t="n">
         <v>38.98</v>
       </c>
-      <c r="B97" s="30">
+      <c r="B97" s="31">
         <f>A97-$B$12</f>
         <v/>
       </c>
-      <c r="C97" s="30">
+      <c r="C97" s="31">
         <f>MAX(0,A97-$B$6)</f>
         <v/>
       </c>
@@ -9667,15 +9685,15 @@
         <f>IF(C97&lt;=0,0,($B$7+$B$9*C97)*C97)</f>
         <v/>
       </c>
-      <c r="E97" s="24">
+      <c r="E97" s="25">
         <f>D97*$B$11</f>
         <v/>
       </c>
-      <c r="F97" s="24">
+      <c r="F97" s="25">
         <f>IF(A97&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A97&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A97,Stage_Storage!$A$11:$A$18,1))+(A97-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A97,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A97,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A97,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A97,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A97,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G97" s="32">
+      <c r="G97" s="33">
         <f>E97+F97</f>
         <v/>
       </c>
@@ -9697,14 +9715,14 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="30" t="n">
+      <c r="A98" s="31" t="n">
         <v>39.03</v>
       </c>
-      <c r="B98" s="30">
+      <c r="B98" s="31">
         <f>A98-$B$12</f>
         <v/>
       </c>
-      <c r="C98" s="30">
+      <c r="C98" s="31">
         <f>MAX(0,A98-$B$6)</f>
         <v/>
       </c>
@@ -9712,15 +9730,15 @@
         <f>IF(C98&lt;=0,0,($B$7+$B$9*C98)*C98)</f>
         <v/>
       </c>
-      <c r="E98" s="24">
+      <c r="E98" s="25">
         <f>D98*$B$11</f>
         <v/>
       </c>
-      <c r="F98" s="24">
+      <c r="F98" s="25">
         <f>IF(A98&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A98&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A98,Stage_Storage!$A$11:$A$18,1))+(A98-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A98,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A98,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A98,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A98,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A98,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G98" s="32">
+      <c r="G98" s="33">
         <f>E98+F98</f>
         <v/>
       </c>
@@ -9742,14 +9760,14 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="30" t="n">
+      <c r="A99" s="31" t="n">
         <v>39.08</v>
       </c>
-      <c r="B99" s="30">
+      <c r="B99" s="31">
         <f>A99-$B$12</f>
         <v/>
       </c>
-      <c r="C99" s="30">
+      <c r="C99" s="31">
         <f>MAX(0,A99-$B$6)</f>
         <v/>
       </c>
@@ -9757,15 +9775,15 @@
         <f>IF(C99&lt;=0,0,($B$7+$B$9*C99)*C99)</f>
         <v/>
       </c>
-      <c r="E99" s="24">
+      <c r="E99" s="25">
         <f>D99*$B$11</f>
         <v/>
       </c>
-      <c r="F99" s="24">
+      <c r="F99" s="25">
         <f>IF(A99&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A99&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A99,Stage_Storage!$A$11:$A$18,1))+(A99-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A99,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A99,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A99,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A99,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A99,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G99" s="32">
+      <c r="G99" s="33">
         <f>E99+F99</f>
         <v/>
       </c>
@@ -9787,14 +9805,14 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="30" t="n">
+      <c r="A100" s="31" t="n">
         <v>39.13</v>
       </c>
-      <c r="B100" s="30">
+      <c r="B100" s="31">
         <f>A100-$B$12</f>
         <v/>
       </c>
-      <c r="C100" s="30">
+      <c r="C100" s="31">
         <f>MAX(0,A100-$B$6)</f>
         <v/>
       </c>
@@ -9802,15 +9820,15 @@
         <f>IF(C100&lt;=0,0,($B$7+$B$9*C100)*C100)</f>
         <v/>
       </c>
-      <c r="E100" s="24">
+      <c r="E100" s="25">
         <f>D100*$B$11</f>
         <v/>
       </c>
-      <c r="F100" s="24">
+      <c r="F100" s="25">
         <f>IF(A100&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A100&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A100,Stage_Storage!$A$11:$A$18,1))+(A100-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A100,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A100,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A100,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A100,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A100,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G100" s="32">
+      <c r="G100" s="33">
         <f>E100+F100</f>
         <v/>
       </c>
@@ -9832,14 +9850,14 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="30" t="n">
+      <c r="A101" s="31" t="n">
         <v>39.18</v>
       </c>
-      <c r="B101" s="30">
+      <c r="B101" s="31">
         <f>A101-$B$12</f>
         <v/>
       </c>
-      <c r="C101" s="30">
+      <c r="C101" s="31">
         <f>MAX(0,A101-$B$6)</f>
         <v/>
       </c>
@@ -9847,15 +9865,15 @@
         <f>IF(C101&lt;=0,0,($B$7+$B$9*C101)*C101)</f>
         <v/>
       </c>
-      <c r="E101" s="24">
+      <c r="E101" s="25">
         <f>D101*$B$11</f>
         <v/>
       </c>
-      <c r="F101" s="24">
+      <c r="F101" s="25">
         <f>IF(A101&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A101&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A101,Stage_Storage!$A$11:$A$18,1))+(A101-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A101,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A101,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A101,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A101,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A101,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G101" s="32">
+      <c r="G101" s="33">
         <f>E101+F101</f>
         <v/>
       </c>
@@ -9877,14 +9895,14 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="30" t="n">
+      <c r="A102" s="31" t="n">
         <v>39.23</v>
       </c>
-      <c r="B102" s="30">
+      <c r="B102" s="31">
         <f>A102-$B$12</f>
         <v/>
       </c>
-      <c r="C102" s="30">
+      <c r="C102" s="31">
         <f>MAX(0,A102-$B$6)</f>
         <v/>
       </c>
@@ -9892,15 +9910,15 @@
         <f>IF(C102&lt;=0,0,($B$7+$B$9*C102)*C102)</f>
         <v/>
       </c>
-      <c r="E102" s="24">
+      <c r="E102" s="25">
         <f>D102*$B$11</f>
         <v/>
       </c>
-      <c r="F102" s="24">
+      <c r="F102" s="25">
         <f>IF(A102&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A102&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A102,Stage_Storage!$A$11:$A$18,1))+(A102-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A102,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A102,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A102,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A102,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A102,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G102" s="32">
+      <c r="G102" s="33">
         <f>E102+F102</f>
         <v/>
       </c>
@@ -9922,14 +9940,14 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="30" t="n">
+      <c r="A103" s="31" t="n">
         <v>39.28</v>
       </c>
-      <c r="B103" s="30">
+      <c r="B103" s="31">
         <f>A103-$B$12</f>
         <v/>
       </c>
-      <c r="C103" s="30">
+      <c r="C103" s="31">
         <f>MAX(0,A103-$B$6)</f>
         <v/>
       </c>
@@ -9937,15 +9955,15 @@
         <f>IF(C103&lt;=0,0,($B$7+$B$9*C103)*C103)</f>
         <v/>
       </c>
-      <c r="E103" s="24">
+      <c r="E103" s="25">
         <f>D103*$B$11</f>
         <v/>
       </c>
-      <c r="F103" s="24">
+      <c r="F103" s="25">
         <f>IF(A103&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A103&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A103,Stage_Storage!$A$11:$A$18,1))+(A103-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A103,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A103,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A103,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A103,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A103,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G103" s="32">
+      <c r="G103" s="33">
         <f>E103+F103</f>
         <v/>
       </c>
@@ -9967,14 +9985,14 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="30" t="n">
+      <c r="A104" s="31" t="n">
         <v>39.33</v>
       </c>
-      <c r="B104" s="30">
+      <c r="B104" s="31">
         <f>A104-$B$12</f>
         <v/>
       </c>
-      <c r="C104" s="30">
+      <c r="C104" s="31">
         <f>MAX(0,A104-$B$6)</f>
         <v/>
       </c>
@@ -9982,15 +10000,15 @@
         <f>IF(C104&lt;=0,0,($B$7+$B$9*C104)*C104)</f>
         <v/>
       </c>
-      <c r="E104" s="24">
+      <c r="E104" s="25">
         <f>D104*$B$11</f>
         <v/>
       </c>
-      <c r="F104" s="24">
+      <c r="F104" s="25">
         <f>IF(A104&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A104&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A104,Stage_Storage!$A$11:$A$18,1))+(A104-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A104,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A104,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A104,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A104,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A104,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G104" s="32">
+      <c r="G104" s="33">
         <f>E104+F104</f>
         <v/>
       </c>
@@ -10012,14 +10030,14 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="30" t="n">
+      <c r="A105" s="31" t="n">
         <v>39.38</v>
       </c>
-      <c r="B105" s="30">
+      <c r="B105" s="31">
         <f>A105-$B$12</f>
         <v/>
       </c>
-      <c r="C105" s="30">
+      <c r="C105" s="31">
         <f>MAX(0,A105-$B$6)</f>
         <v/>
       </c>
@@ -10027,15 +10045,15 @@
         <f>IF(C105&lt;=0,0,($B$7+$B$9*C105)*C105)</f>
         <v/>
       </c>
-      <c r="E105" s="24">
+      <c r="E105" s="25">
         <f>D105*$B$11</f>
         <v/>
       </c>
-      <c r="F105" s="24">
+      <c r="F105" s="25">
         <f>IF(A105&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A105&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A105,Stage_Storage!$A$11:$A$18,1))+(A105-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A105,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A105,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A105,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A105,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A105,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G105" s="32">
+      <c r="G105" s="33">
         <f>E105+F105</f>
         <v/>
       </c>
@@ -10057,14 +10075,14 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="30" t="n">
+      <c r="A106" s="31" t="n">
         <v>39.43</v>
       </c>
-      <c r="B106" s="30">
+      <c r="B106" s="31">
         <f>A106-$B$12</f>
         <v/>
       </c>
-      <c r="C106" s="30">
+      <c r="C106" s="31">
         <f>MAX(0,A106-$B$6)</f>
         <v/>
       </c>
@@ -10072,15 +10090,15 @@
         <f>IF(C106&lt;=0,0,($B$7+$B$9*C106)*C106)</f>
         <v/>
       </c>
-      <c r="E106" s="24">
+      <c r="E106" s="25">
         <f>D106*$B$11</f>
         <v/>
       </c>
-      <c r="F106" s="24">
+      <c r="F106" s="25">
         <f>IF(A106&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A106&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A106,Stage_Storage!$A$11:$A$18,1))+(A106-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A106,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A106,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A106,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A106,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A106,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G106" s="32">
+      <c r="G106" s="33">
         <f>E106+F106</f>
         <v/>
       </c>
@@ -10102,14 +10120,14 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="30" t="n">
+      <c r="A107" s="31" t="n">
         <v>39.48</v>
       </c>
-      <c r="B107" s="30">
+      <c r="B107" s="31">
         <f>A107-$B$12</f>
         <v/>
       </c>
-      <c r="C107" s="30">
+      <c r="C107" s="31">
         <f>MAX(0,A107-$B$6)</f>
         <v/>
       </c>
@@ -10117,15 +10135,15 @@
         <f>IF(C107&lt;=0,0,($B$7+$B$9*C107)*C107)</f>
         <v/>
       </c>
-      <c r="E107" s="24">
+      <c r="E107" s="25">
         <f>D107*$B$11</f>
         <v/>
       </c>
-      <c r="F107" s="24">
+      <c r="F107" s="25">
         <f>IF(A107&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A107&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A107,Stage_Storage!$A$11:$A$18,1))+(A107-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A107,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A107,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A107,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A107,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A107,Stage_Storage!$A$11:$A$18,1)))))</f>
         <v/>
       </c>
-      <c r="G107" s="32">
+      <c r="G107" s="33">
         <f>E107+F107</f>
         <v/>
       </c>
@@ -10174,14 +10192,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Méthode C — routage avec Qout composé + V = V_pond + V_ditch</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="38" t="inlineStr">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>À chaque pas: WSE lu sur Compose_900!V_total → Qout sur Compose_900. ΔV = (Qin_moy − Qout)×Δt. Si V≈0, Qout = MIN(Qin, Q_plein).</t>
         </is>
@@ -10194,7 +10212,7 @@
           <t>Q_plein réf. (m³/s)</t>
         </is>
       </c>
-      <c r="B5" s="39">
+      <c r="B5" s="40">
         <f>Parametres!B22</f>
         <v/>
       </c>
@@ -10205,7 +10223,7 @@
           <t>Crest (m)</t>
         </is>
       </c>
-      <c r="B6" s="39">
+      <c r="B6" s="40">
         <f>Parametres!B27</f>
         <v/>
       </c>
@@ -10216,7 +10234,7 @@
           <t>Vmax_C (m³)</t>
         </is>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="30">
         <f>MAX(F12:F24)</f>
         <v/>
       </c>
@@ -10227,7 +10245,7 @@
           <t>WSEmax_C (m)</t>
         </is>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="22">
         <f>MAX(C12:C24)</f>
         <v/>
       </c>
@@ -10297,10 +10315,10 @@
         <f>MIN(B12,$B$5)</f>
         <v/>
       </c>
-      <c r="E12" s="24" t="n">
+      <c r="E12" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="32" t="n">
+      <c r="F12" s="33" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -10326,11 +10344,11 @@
         <f>IF(F12&lt;=0.01,MIN(0.5*(B12+B13),$B$5),IF(C13&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C13&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C13,Compose_900!$A$15:$A$107,1))+(C13-INDEX(Compose_900!$A$15:$A$107,MATCH(C13,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C13,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C13,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C13,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C13,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="25">
         <f>(A13-A12)*60</f>
         <v/>
       </c>
-      <c r="F13" s="32">
+      <c r="F13" s="33">
         <f>MAX(0,F12+(0.5*(B12+B13)-D13)*E13)</f>
         <v/>
       </c>
@@ -10356,11 +10374,11 @@
         <f>IF(F13&lt;=0.01,MIN(0.5*(B13+B14),$B$5),IF(C14&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C14&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C14,Compose_900!$A$15:$A$107,1))+(C14-INDEX(Compose_900!$A$15:$A$107,MATCH(C14,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C14,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C14,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C14,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C14,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="25">
         <f>(A14-A13)*60</f>
         <v/>
       </c>
-      <c r="F14" s="32">
+      <c r="F14" s="33">
         <f>MAX(0,F13+(0.5*(B13+B14)-D14)*E14)</f>
         <v/>
       </c>
@@ -10386,11 +10404,11 @@
         <f>IF(F14&lt;=0.01,MIN(0.5*(B14+B15),$B$5),IF(C15&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C15&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C15,Compose_900!$A$15:$A$107,1))+(C15-INDEX(Compose_900!$A$15:$A$107,MATCH(C15,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C15,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C15,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C15,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C15,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="25">
         <f>(A15-A14)*60</f>
         <v/>
       </c>
-      <c r="F15" s="32">
+      <c r="F15" s="33">
         <f>MAX(0,F14+(0.5*(B14+B15)-D15)*E15)</f>
         <v/>
       </c>
@@ -10416,11 +10434,11 @@
         <f>IF(F15&lt;=0.01,MIN(0.5*(B15+B16),$B$5),IF(C16&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C16&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C16,Compose_900!$A$15:$A$107,1))+(C16-INDEX(Compose_900!$A$15:$A$107,MATCH(C16,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C16,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C16,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C16,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C16,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="25">
         <f>(A16-A15)*60</f>
         <v/>
       </c>
-      <c r="F16" s="32">
+      <c r="F16" s="33">
         <f>MAX(0,F15+(0.5*(B15+B16)-D16)*E16)</f>
         <v/>
       </c>
@@ -10446,11 +10464,11 @@
         <f>IF(F16&lt;=0.01,MIN(0.5*(B16+B17),$B$5),IF(C17&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C17&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C17,Compose_900!$A$15:$A$107,1))+(C17-INDEX(Compose_900!$A$15:$A$107,MATCH(C17,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C17,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C17,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C17,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C17,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="25">
         <f>(A17-A16)*60</f>
         <v/>
       </c>
-      <c r="F17" s="32">
+      <c r="F17" s="33">
         <f>MAX(0,F16+(0.5*(B16+B17)-D17)*E17)</f>
         <v/>
       </c>
@@ -10476,11 +10494,11 @@
         <f>IF(F17&lt;=0.01,MIN(0.5*(B17+B18),$B$5),IF(C18&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C18&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C18,Compose_900!$A$15:$A$107,1))+(C18-INDEX(Compose_900!$A$15:$A$107,MATCH(C18,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C18,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C18,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C18,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C18,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="25">
         <f>(A18-A17)*60</f>
         <v/>
       </c>
-      <c r="F18" s="32">
+      <c r="F18" s="33">
         <f>MAX(0,F17+(0.5*(B17+B18)-D18)*E18)</f>
         <v/>
       </c>
@@ -10506,11 +10524,11 @@
         <f>IF(F18&lt;=0.01,MIN(0.5*(B18+B19),$B$5),IF(C19&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C19&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C19,Compose_900!$A$15:$A$107,1))+(C19-INDEX(Compose_900!$A$15:$A$107,MATCH(C19,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C19,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C19,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C19,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C19,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="25">
         <f>(A19-A18)*60</f>
         <v/>
       </c>
-      <c r="F19" s="32">
+      <c r="F19" s="33">
         <f>MAX(0,F18+(0.5*(B18+B19)-D19)*E19)</f>
         <v/>
       </c>
@@ -10536,11 +10554,11 @@
         <f>IF(F19&lt;=0.01,MIN(0.5*(B19+B20),$B$5),IF(C20&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C20&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C20,Compose_900!$A$15:$A$107,1))+(C20-INDEX(Compose_900!$A$15:$A$107,MATCH(C20,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C20,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C20,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C20,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C20,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E20" s="24">
+      <c r="E20" s="25">
         <f>(A20-A19)*60</f>
         <v/>
       </c>
-      <c r="F20" s="32">
+      <c r="F20" s="33">
         <f>MAX(0,F19+(0.5*(B19+B20)-D20)*E20)</f>
         <v/>
       </c>
@@ -10566,11 +10584,11 @@
         <f>IF(F20&lt;=0.01,MIN(0.5*(B20+B21),$B$5),IF(C21&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C21&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C21,Compose_900!$A$15:$A$107,1))+(C21-INDEX(Compose_900!$A$15:$A$107,MATCH(C21,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C21,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C21,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C21,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C21,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E21" s="24">
+      <c r="E21" s="25">
         <f>(A21-A20)*60</f>
         <v/>
       </c>
-      <c r="F21" s="32">
+      <c r="F21" s="33">
         <f>MAX(0,F20+(0.5*(B20+B21)-D21)*E21)</f>
         <v/>
       </c>
@@ -10596,11 +10614,11 @@
         <f>IF(F21&lt;=0.01,MIN(0.5*(B21+B22),$B$5),IF(C22&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C22&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C22,Compose_900!$A$15:$A$107,1))+(C22-INDEX(Compose_900!$A$15:$A$107,MATCH(C22,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C22,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C22,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C22,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C22,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E22" s="24">
+      <c r="E22" s="25">
         <f>(A22-A21)*60</f>
         <v/>
       </c>
-      <c r="F22" s="32">
+      <c r="F22" s="33">
         <f>MAX(0,F21+(0.5*(B21+B22)-D22)*E22)</f>
         <v/>
       </c>
@@ -10626,11 +10644,11 @@
         <f>IF(F22&lt;=0.01,MIN(0.5*(B22+B23),$B$5),IF(C23&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C23&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C23,Compose_900!$A$15:$A$107,1))+(C23-INDEX(Compose_900!$A$15:$A$107,MATCH(C23,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C23,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C23,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C23,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C23,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E23" s="24">
+      <c r="E23" s="25">
         <f>(A23-A22)*60</f>
         <v/>
       </c>
-      <c r="F23" s="32">
+      <c r="F23" s="33">
         <f>MAX(0,F22+(0.5*(B22+B23)-D23)*E23)</f>
         <v/>
       </c>
@@ -10656,11 +10674,11 @@
         <f>IF(F23&lt;=0.01,MIN(0.5*(B23+B24),$B$5),IF(C24&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C24&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C24,Compose_900!$A$15:$A$107,1))+(C24-INDEX(Compose_900!$A$15:$A$107,MATCH(C24,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C24,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C24,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C24,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C24,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E24" s="24">
+      <c r="E24" s="25">
         <f>(A24-A23)*60</f>
         <v/>
       </c>
-      <c r="F24" s="32">
+      <c r="F24" s="33">
         <f>MAX(0,F23+(0.5*(B23+B24)-D24)*E24)</f>
         <v/>
       </c>
@@ -10695,7 +10713,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Stage–storage du levé — V = f(WSE) → lire le niveau max</t>
         </is>
@@ -10718,7 +10736,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="41" t="inlineStr">
+      <c r="A7" s="42" t="inlineStr">
         <is>
           <t>V_pas (m³) = (A_basse + A_haute) / 2 × (WSE_haute − WSE_basse)</t>
         </is>
@@ -10764,7 +10782,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="n">
+      <c r="A11" s="31" t="n">
         <v>34.88</v>
       </c>
       <c r="B11" s="17" t="n">
@@ -10786,21 +10804,21 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="30" t="n">
+      <c r="A12" s="31" t="n">
         <v>35.5</v>
       </c>
       <c r="B12" s="17" t="n">
         <v>80</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="31">
         <f>A12-A11</f>
         <v/>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="25">
         <f>0.5*(B11+B12)*C12</f>
         <v/>
       </c>
-      <c r="E12" s="32">
+      <c r="E12" s="33">
         <f>E11+D12</f>
         <v/>
       </c>
@@ -10811,21 +10829,21 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="30" t="n">
+      <c r="A13" s="31" t="n">
         <v>36</v>
       </c>
       <c r="B13" s="17" t="n">
         <v>180</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <f>A13-A12</f>
         <v/>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="25">
         <f>0.5*(B12+B13)*C13</f>
         <v/>
       </c>
-      <c r="E13" s="32">
+      <c r="E13" s="33">
         <f>E12+D13</f>
         <v/>
       </c>
@@ -10836,21 +10854,21 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="30" t="n">
+      <c r="A14" s="31" t="n">
         <v>36.5</v>
       </c>
       <c r="B14" s="17" t="n">
         <v>320</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="31">
         <f>A14-A13</f>
         <v/>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="25">
         <f>0.5*(B13+B14)*C14</f>
         <v/>
       </c>
-      <c r="E14" s="32">
+      <c r="E14" s="33">
         <f>E13+D14</f>
         <v/>
       </c>
@@ -10861,21 +10879,21 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="30" t="n">
+      <c r="A15" s="31" t="n">
         <v>37</v>
       </c>
       <c r="B15" s="17" t="n">
         <v>480</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="31">
         <f>A15-A14</f>
         <v/>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="25">
         <f>0.5*(B14+B15)*C15</f>
         <v/>
       </c>
-      <c r="E15" s="32">
+      <c r="E15" s="33">
         <f>E14+D15</f>
         <v/>
       </c>
@@ -10886,21 +10904,21 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="37" t="n">
+      <c r="A16" s="38" t="n">
         <v>37.28</v>
       </c>
       <c r="B16" s="17" t="n">
         <v>543</v>
       </c>
-      <c r="C16" s="37">
+      <c r="C16" s="38">
         <f>A16-A15</f>
         <v/>
       </c>
-      <c r="D16" s="40">
+      <c r="D16" s="41">
         <f>0.5*(B15+B16)*C16</f>
         <v/>
       </c>
-      <c r="E16" s="40">
+      <c r="E16" s="41">
         <f>E15+D16</f>
         <v/>
       </c>
@@ -10911,21 +10929,21 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="30" t="n">
+      <c r="A17" s="31" t="n">
         <v>37.5</v>
       </c>
       <c r="B17" s="17" t="n">
         <v>700</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="31">
         <f>A17-A16</f>
         <v/>
       </c>
-      <c r="D17" s="24">
+      <c r="D17" s="25">
         <f>0.5*(B16+B17)*C17</f>
         <v/>
       </c>
-      <c r="E17" s="32">
+      <c r="E17" s="33">
         <f>E16+D17</f>
         <v/>
       </c>
@@ -10936,21 +10954,21 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="30" t="n">
+      <c r="A18" s="31" t="n">
         <v>39.5</v>
       </c>
       <c r="B18" s="17" t="n">
         <v>1932</v>
       </c>
-      <c r="C18" s="30">
+      <c r="C18" s="31">
         <f>A18-A17</f>
         <v/>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="25">
         <f>0.5*(B17+B18)*C18</f>
         <v/>
       </c>
-      <c r="E18" s="32">
+      <c r="E18" s="33">
         <f>E17+D18</f>
         <v/>
       </c>
@@ -10966,7 +10984,7 @@
           <t>Vmax_A (Calcul_A)</t>
         </is>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="20">
         <f>Parametres!B36</f>
         <v/>
       </c>
@@ -10977,7 +10995,7 @@
           <t>WSEmax_A (m)</t>
         </is>
       </c>
-      <c r="B22" s="41">
+      <c r="B22" s="42">
         <f>Parametres!B39</f>
         <v/>
       </c>
@@ -10988,7 +11006,7 @@
           <t>Vmax_B (Calcul_B)</t>
         </is>
       </c>
-      <c r="B23" s="19">
+      <c r="B23" s="20">
         <f>Parametres!B43</f>
         <v/>
       </c>
@@ -10999,7 +11017,7 @@
           <t>WSEmax_B (m)</t>
         </is>
       </c>
-      <c r="B24" s="41">
+      <c r="B24" s="42">
         <f>Parametres!B45</f>
         <v/>
       </c>
@@ -11010,7 +11028,7 @@
           <t>Vmax_C / WSEmax_C</t>
         </is>
       </c>
-      <c r="B25" s="19">
+      <c r="B25" s="20">
         <f>Parametres!B49</f>
         <v/>
       </c>
@@ -11030,7 +11048,7 @@
           <t>V disponible à 37.28 m (m³)</t>
         </is>
       </c>
-      <c r="B26" s="42">
+      <c r="B26" s="43">
         <f>E16</f>
         <v/>
       </c>
@@ -11048,7 +11066,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="38" t="inlineStr">
+      <c r="A29" s="39" t="inlineStr">
         <is>
           <t>Exemple: si Vmax_A = 5609 m³ et V(37.28)≈558 m³, alors WSEmax_A est au-dessus de 37.28 m (la table ira vers 39.5 m ou 'Hors table'). Affinez en entrant les vraies surfaces aux cotes intermédiaires (jaune). Méthode C: voir Parametres B49–B52 et Calcul_C (fossé inclus).</t>
         </is>
@@ -11081,7 +11099,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="43" t="inlineStr">
+      <c r="A1" s="44" t="inlineStr">
         <is>
           <t>Où sont les fichiers HY-8 / capacité ?</t>
         </is>

--- a/engineering/drainage-design/retention_volume/Volume_Retention_Ponceau_900.xlsx
+++ b/engineering/drainage-design/retention_volume/Volume_Retention_Ponceau_900.xlsx
@@ -1861,7 +1861,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Aire_bassin_m2</t>
+          <t>Aire_constante_B (m²) — PAS le levé</t>
         </is>
       </c>
       <c r="B24" s="17" t="n">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Aire plan d'eau approx. pour H = V/A (Méthode B seulement)</t>
+          <t>Raccourci Méthode B seulement: H≈V/B24 pour lire Q=f(H). Ce n'est PAS un 2e bassin. Le vrai étang = feuille Stage_Storage (surfaces vs WSE).</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="B39" s="22">
-        <f>IF(B36&lt;=Stage_Storage!E11,Stage_Storage!A11,IF(B36&gt;=Stage_Storage!E18,"Hors table (&gt;=39.5 m — étendre levé)",INDEX(Stage_Storage!$A$11:$A$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1))+(B36-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)))/(INDEX(Stage_Storage!$E$11:$E$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)))*(INDEX(Stage_Storage!$A$11:$A$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)))))</f>
+        <f>IF(B36&lt;=Stage_Storage!E11,Stage_Storage!A11,IF(B36&gt;=Stage_Storage!E18,"Hors table (&gt;=40.0 m — étendre levé)",INDEX(Stage_Storage!$A$11:$A$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1))+(B36-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)))/(INDEX(Stage_Storage!$E$11:$E$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)))*(INDEX(Stage_Storage!$A$11:$A$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)))))</f>
         <v/>
       </c>
       <c r="C39" t="inlineStr">
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B45" s="22">
-        <f>IF(B43&lt;=Stage_Storage!E11,Stage_Storage!A11,IF(B43&gt;=Stage_Storage!E18,"Hors table (&gt;=39.5 m — étendre levé)",INDEX(Stage_Storage!$A$11:$A$18,MATCH(B43,Stage_Storage!$E$11:$E$18,1))+(B43-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B43,Stage_Storage!$E$11:$E$18,1)))/(INDEX(Stage_Storage!$E$11:$E$18,MATCH(B43,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B43,Stage_Storage!$E$11:$E$18,1)))*(INDEX(Stage_Storage!$A$11:$A$18,MATCH(B43,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(B43,Stage_Storage!$E$11:$E$18,1)))))</f>
+        <f>IF(B43&lt;=Stage_Storage!E11,Stage_Storage!A11,IF(B43&gt;=Stage_Storage!E18,"Hors table (&gt;=40.0 m — étendre levé)",INDEX(Stage_Storage!$A$11:$A$18,MATCH(B43,Stage_Storage!$E$11:$E$18,1))+(B43-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B43,Stage_Storage!$E$11:$E$18,1)))/(INDEX(Stage_Storage!$E$11:$E$18,MATCH(B43,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B43,Stage_Storage!$E$11:$E$18,1)))*(INDEX(Stage_Storage!$A$11:$A$18,MATCH(B43,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(B43,Stage_Storage!$E$11:$E$18,1)))))</f>
         <v/>
       </c>
       <c r="C45" t="inlineStr">
@@ -5321,7 +5321,7 @@
     <row r="2">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>H = V / Aire_bassin. Qout interpolé sur Courbe_QH_900!E (Q gouvernant). Si V≈0, Qout = MIN(Qin, Q_plein). ΔV = (Qin_moy - Qout)*Δt. La courbe Courbe_QH_900 est en formules live (changer n/L/entrée/TW).</t>
+          <t>H = V / Aire_constante (Parametres!B24) — raccourci, PAS le levé Stage_Storage. Qout interpolé sur Courbe_QH_900!E (Q gouvernant). Si V≈0, Qout = MIN(Qin, Q_plein). ΔV = (Qin_moy - Qout)*Δt. Après routage, WSEmax_B réel est lu sur Stage_Storage via Vmax_B (Parametres B45).</t>
         </is>
       </c>
     </row>
@@ -10722,7 +10722,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>PROCÉDURE (dans CE fichier): 1) Routage → Vmax_A / Vmax_B / Vmax_C sur Parametres. 2) Cette feuille = V_pond vs WSE (levé seul). 3) Parametres!B39 = WSEmax_A; B45 = WSEmax_B (levé). 4) Méthode C: V_pond + V_ditch et WSEmax_C sont sur Compose_900 / Calcul_C (B51). Remplacez les surfaces jaunes; 543 m² @ 37.28 et 1932 m² @ 39.5 sont vos mesures.</t>
+          <t>PROCÉDURE (dans CE fichier): 1) Routage → Vmax_A / Vmax_B / Vmax_C sur Parametres. 2) Cette feuille = V_pond vs WSE (levé topographique — le vrai bassin). 3) Parametres!B39 = WSEmax_A; B45 = WSEmax_B (lus sur CE tableau). 4) Méthode C: V_pond + V_ditch et WSEmax_C sur Compose_900 / Calcul_C (B51). 5) Parametres!B24 (2500 m²) n'est PAS ici: c'est seulement le raccourci H=V/A de Méthode B. Surfaces ci-dessous = votre levé (pas des placeholders).</t>
         </is>
       </c>
     </row>
@@ -10799,7 +10799,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Radier Ø900 — départ</t>
+          <t>Fond bassin / radier Ø900</t>
         </is>
       </c>
     </row>
@@ -10808,7 +10808,7 @@
         <v>35.5</v>
       </c>
       <c r="B12" s="17" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="C12" s="31">
         <f>A12-A11</f>
@@ -10824,16 +10824,16 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Placeholder — remplacer par levé</t>
+          <t>Levé</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="31" t="n">
-        <v>36</v>
+        <v>36.01</v>
       </c>
       <c r="B13" s="17" t="n">
-        <v>180</v>
+        <v>419</v>
       </c>
       <c r="C13" s="31">
         <f>A13-A12</f>
@@ -10849,7 +10849,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Placeholder — remplacer par levé</t>
+          <t>Levé</t>
         </is>
       </c>
     </row>
@@ -10858,7 +10858,7 @@
         <v>36.5</v>
       </c>
       <c r="B14" s="17" t="n">
-        <v>320</v>
+        <v>480</v>
       </c>
       <c r="C14" s="31">
         <f>A14-A13</f>
@@ -10874,7 +10874,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Placeholder — remplacer par levé</t>
+          <t>Levé</t>
         </is>
       </c>
     </row>
@@ -10883,7 +10883,7 @@
         <v>37</v>
       </c>
       <c r="B15" s="17" t="n">
-        <v>480</v>
+        <v>720</v>
       </c>
       <c r="C15" s="31">
         <f>A15-A14</f>
@@ -10899,7 +10899,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Placeholder — remplacer par levé</t>
+          <t>Levé</t>
         </is>
       </c>
     </row>
@@ -10908,7 +10908,7 @@
         <v>37.28</v>
       </c>
       <c r="B16" s="17" t="n">
-        <v>543</v>
+        <v>2198</v>
       </c>
       <c r="C16" s="38">
         <f>A16-A15</f>
@@ -10924,16 +10924,16 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>LIMITE PATRON (+1.5 m crown) — votre levé</t>
+          <t>LIMITE PATRON (+1.5 m crown) — levé</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="31" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="B17" s="17" t="n">
-        <v>700</v>
+        <v>1516</v>
       </c>
       <c r="C17" s="31">
         <f>A17-A16</f>
@@ -10949,16 +10949,16 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Placeholder — remplacer par levé</t>
+          <t>Levé (A↓ vs 37.28 — vérifier si voulu)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="31" t="n">
-        <v>39.5</v>
+        <v>40</v>
       </c>
       <c r="B18" s="17" t="n">
-        <v>1932</v>
+        <v>3746</v>
       </c>
       <c r="C18" s="31">
         <f>A18-A17</f>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Votre levé 1932 m² — niveau optionnel plus haut</t>
+          <t>Levé — sommet table</t>
         </is>
       </c>
     </row>
@@ -11068,7 +11068,7 @@
     <row r="29">
       <c r="A29" s="39" t="inlineStr">
         <is>
-          <t>Exemple: si Vmax_A = 5609 m³ et V(37.28)≈558 m³, alors WSEmax_A est au-dessus de 37.28 m (la table ira vers 39.5 m ou 'Hors table'). Affinez en entrant les vraies surfaces aux cotes intermédiaires (jaune). Méthode C: voir Parametres B49–B52 et Calcul_C (fossé inclus).</t>
+          <t>Exemple: si Vmax_A &gt; V_cumul @ 37.28 (colonne E, ligne orange), alors WSEmax_A &gt; 37.28 m (la table monte vers 37.40 / 40.00 ou 'Hors table'). Jaune = surfaces du levé (éditables). Méthode C: Parametres B49–B52 et Calcul_C (fossé inclus). Note: A(37.40)=1516 &lt; A(37.28)=2198 — inhabituel; confirmer sur plan.</t>
         </is>
       </c>
     </row>

--- a/engineering/drainage-design/retention_volume/Volume_Retention_Ponceau_900.xlsx
+++ b/engineering/drainage-design/retention_volume/Volume_Retention_Ponceau_900.xlsx
@@ -14,9 +14,12 @@
     <sheet name="Calcul_B" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Compose_900" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Calcul_C" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Stage_Storage" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Fichiers_lies" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Methode" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="SS_Amont" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="SS_Aval" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Stage_Storage" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Calcul_Aval_A" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Fichiers_lies" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Methode" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -151,6 +154,7 @@
     <xf numFmtId="1" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -173,7 +177,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -1000,7 +1006,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>V cumulé vs WSE (levé)</a:t>
+              <a:t>Zone 1 — V cumulé vs WSE</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1014,7 +1020,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Stage_Storage'!E10</f>
+              <f>'SS_Amont'!E10</f>
             </strRef>
           </tx>
           <spPr>
@@ -1032,12 +1038,130 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Stage_Storage'!$A$11:$A$18</f>
+              <f>'SS_Amont'!$A$11:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Stage_Storage'!$E$11:$E$18</f>
+              <f>'SS_Amont'!$E$11:$E$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>WSE (m)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>V (m³)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Zone 2 — V cumulé vs WSE</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'SS_Aval'!E10</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'SS_Aval'!$A$11:$A$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'SS_Aval'!$E$11:$E$18</f>
             </numRef>
           </val>
         </ser>
@@ -1237,6 +1361,33 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -1552,7 +1703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1869,7 +2020,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Raccourci Méthode B seulement: H≈V/B24 pour lire Q=f(H). Ce n'est PAS un 2e bassin. Le vrai étang = feuille Stage_Storage (surfaces vs WSE).</t>
+          <t>Raccourci Méthode B seulement: H≈V/B24 pour lire Q=f(H). Ce n'est PAS un 2e bassin. Levé Zone 1 = feuille SS_Amont; Zone 2 = SS_Aval.</t>
         </is>
       </c>
     </row>
@@ -2047,16 +2198,16 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>WSEmax_A depuis levé (m) — feuille Stage_Storage</t>
+          <t>WSEmax_A depuis levé Zone 1 (m) — SS_Amont</t>
         </is>
       </c>
       <c r="B39" s="22">
-        <f>IF(B36&lt;=Stage_Storage!E11,Stage_Storage!A11,IF(B36&gt;=Stage_Storage!E18,"Hors table (&gt;=40.0 m — étendre levé)",INDEX(Stage_Storage!$A$11:$A$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1))+(B36-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)))/(INDEX(Stage_Storage!$E$11:$E$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)))*(INDEX(Stage_Storage!$A$11:$A$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)))))</f>
+        <f>IF(B36&lt;=SS_Amont!E11,SS_Amont!A11,IF(B36&gt;=SS_Amont!E18,"Hors table (&gt;=40.0 m — étendre levé)",INDEX(SS_Amont!$A$11:$A$18,MATCH(B36,SS_Amont!$E$11:$E$18,1))+(B36-INDEX(SS_Amont!$E$11:$E$18,MATCH(B36,SS_Amont!$E$11:$E$18,1)))/(INDEX(SS_Amont!$E$11:$E$18,MATCH(B36,SS_Amont!$E$11:$E$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(B36,SS_Amont!$E$11:$E$18,1)))*(INDEX(SS_Amont!$A$11:$A$18,MATCH(B36,SS_Amont!$E$11:$E$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(B36,SS_Amont!$E$11:$E$18,1)))))</f>
         <v/>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cote d'eau max pour le Vmax_A: on lit sur Stage_Storage quelle WSE donne ce volume (courbe volume–cote du levé)</t>
+          <t>Cote d'eau max pour Vmax_A: lecture sur SS_Amont (Ø1500→Ø900), pas Zone 2</t>
         </is>
       </c>
     </row>
@@ -2113,16 +2264,16 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>WSEmax_B depuis levé (m) — feuille Stage_Storage</t>
+          <t>WSEmax_B depuis levé Zone 1 (m) — SS_Amont</t>
         </is>
       </c>
       <c r="B45" s="22">
-        <f>IF(B43&lt;=Stage_Storage!E11,Stage_Storage!A11,IF(B43&gt;=Stage_Storage!E18,"Hors table (&gt;=40.0 m — étendre levé)",INDEX(Stage_Storage!$A$11:$A$18,MATCH(B43,Stage_Storage!$E$11:$E$18,1))+(B43-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B43,Stage_Storage!$E$11:$E$18,1)))/(INDEX(Stage_Storage!$E$11:$E$18,MATCH(B43,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B43,Stage_Storage!$E$11:$E$18,1)))*(INDEX(Stage_Storage!$A$11:$A$18,MATCH(B43,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(B43,Stage_Storage!$E$11:$E$18,1)))))</f>
+        <f>IF(B43&lt;=SS_Amont!E11,SS_Amont!A11,IF(B43&gt;=SS_Amont!E18,"Hors table (&gt;=40.0 m — étendre levé)",INDEX(SS_Amont!$A$11:$A$18,MATCH(B43,SS_Amont!$E$11:$E$18,1))+(B43-INDEX(SS_Amont!$E$11:$E$18,MATCH(B43,SS_Amont!$E$11:$E$18,1)))/(INDEX(SS_Amont!$E$11:$E$18,MATCH(B43,SS_Amont!$E$11:$E$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(B43,SS_Amont!$E$11:$E$18,1)))*(INDEX(SS_Amont!$A$11:$A$18,MATCH(B43,SS_Amont!$E$11:$E$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(B43,SS_Amont!$E$11:$E$18,1)))))</f>
         <v/>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Même lecture volume→cote que B39, mais avec Vmax_B</t>
+          <t>Même lecture volume→cote que B39 (SS_Amont), avec Vmax_B</t>
         </is>
       </c>
     </row>
@@ -2211,170 +2362,1302 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Comment lire WSEmax (A / B / C)</t>
+          <t>Résultats Zone 2 — Ø900 → Ø1200 (SS_Aval + Calcul_Aval_A)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1) A et B: Vmax = volume pondé; WSEmax lu sur Stage_Storage (levé seul).</t>
+          <t>V @ 37.28 m Zone 2 (m³) — SS_Aval</t>
+        </is>
+      </c>
+      <c r="B55" s="23">
+        <f>SS_Aval!B21</f>
+        <v/>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Volume levé Zone 2 à la cote patron</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2) C: Qout = Q_900(WSE) + Q_overflow(WSE); V = V_pond + V_ditch; WSEmax_C vient de Calcul_C.</t>
+          <t>Vmax_Aval_A (m³)</t>
+        </is>
+      </c>
+      <c r="B56" s="20">
+        <f>Calcul_Aval_A!B6</f>
+        <v/>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Routage Aval: Qin≈Qcap Ø900; Qout=Q_plein Ø1200</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3) Crest = crown = 35.78 m → au-dessus, le fossé trapèze (b, n, z, S, L) ajoute débit et volume.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>4) Ne pas comparer Vmax_C à V_pond seul sans retirer V_ditch; comparer plutôt les WSEmax.</t>
+          <t>WSEmax_Aval_A (m) — SS_Aval</t>
+        </is>
+      </c>
+      <c r="B57" s="22">
+        <f>Calcul_Aval_A!B7</f>
+        <v/>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Lecture volume→cote sur levé Zone 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Comment lire WSEmax (zones + méthodes)</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Inlet control vs outlet control — qu'est-ce que ça veut dire?</t>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1) Zone 1 (Ø1500→Ø900): A/B → Vmax puis WSEmax sur SS_Amont. Zone 2: SS_Aval + Calcul_Aval_A (B55–B57).</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>• Inlet control (contrôle à l'entrée): le débit est limité par l'entrée du ponceau (forme d'entrée, HW/D).</t>
+          <t>2) C (Zone 1): Qout = Q_900(WSE)+Q_overflow; V = V_pond(SS_Amont)+V_ditch; WSEmax_C = Calcul_C.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Le tuyau aval « n'aspire » pas assez pour influencer — Q dépend surtout de la charge amont H, pas de L ni de n.</t>
+          <t>3) Crest = crown = 35.78 m → au-dessus, le fossé trapèze ajoute débit et volume (Zone 1).</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>• Outlet control (contrôle à la sortie / frottement): le débit dépend de la longueur, de n, de la pente et de la charge</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (énergie amont → aval). Manning pleine section est une hypothèse de type outlet/frottement à section pleine.</t>
+          <t>4) Ne pas additionner Zone 1+2 dans un seul routage. Éditer WSE/Surface jaunes dans SS_Amont et SS_Aval.</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>• Ici L/D = 56 (tuyau assez long) → le contrôle par frottement (outlet) est souvent plausible,</t>
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Inlet control vs outlet control — qu'est-ce que ça veut dire?</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">  mais sans analyse FHWA/HY-8 on ne peut pas l'affirmer. Pour dimensionner la rétention, Q_plein constant est</t>
+          <t>• Inlet control (contrôle à l'entrée): le débit est limité par l'entrée du ponceau (forme d'entrée, HW/D).</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">  en général prudent (si la charge monte, le débit réel peut être un peu plus élevé → Vmax un peu plus bas).</t>
+          <t xml:space="preserve">  Le tuyau aval « n'aspire » pas assez pour influencer — Q dépend surtout de la charge amont H, pas de L ni de n.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>• On n'a pas besoin de trancher IC/OC pour utiliser ce classeur: garder Qout = Q_plein (ou 1.77) suffit pour une 1re estimation.</t>
+          <t>• Outlet control (contrôle à la sortie / frottement): le débit dépend de la longueur, de n, de la pente et de la charge</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (énergie amont → aval). Manning pleine section est une hypothèse de type outlet/frottement à section pleine.</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>Notes</t>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>• Ici L/D = 56 (tuyau assez long) → le contrôle par frottement (outlet) est souvent plausible,</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>• Méthode A: Qout fixe = Q_plein Manning Ø900 (n=0,013).</t>
+          <t xml:space="preserve">  mais sans analyse FHWA/HY-8 on ne peut pas l'affirmer. Pour dimensionner la rétention, Q_plein constant est</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>• Méthode B: Qout = f(H) pipe seul (Courbe_QH_900) — résultats B43–B46.</t>
+          <t xml:space="preserve">  en général prudent (si la charge monte, le débit réel peut être un peu plus élevé → Vmax un peu plus bas).</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>• On n'a pas besoin de trancher IC/OC pour utiliser ce classeur: garder Qout = Q_plein (ou 1.77) suffit pour une 1re estimation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>• Méthode A: Qout fixe = Q_plein Manning Ø900 (n=0,013).</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>• Méthode B: Qout = f(H) pipe seul (Courbe_QH_900) — résultats B43–B46.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
           <t>• Méthode C: Qout = Q_900 + Q_overflow; V = V_pond + V_ditch — Compose_900 + Calcul_C (B49–B52).</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>• Le stockage commence quand Qin dépasse Qout; Vmax = max du volume stocké.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>• Vérifier que le radier amont Ø900 (34.88) est bien le fond de la zone de rétention étudiée.</t>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>• Zone 2: SS_Aval + Calcul_Aval_A — résultats B55–B57.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>• SS_Amont / SS_Aval: WSE et Surface en jaune — corriger depuis AutoCAD; ΔWSE et V_pas se recalculent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>• Vérifier que le radier amont Ø900 (34.88) est bien le fond de Zone 1.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
     <mergeCell ref="A67:H67"/>
+    <mergeCell ref="A77:H77"/>
     <mergeCell ref="A73:H73"/>
-    <mergeCell ref="A64:H64"/>
+    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="A79:H79"/>
     <mergeCell ref="A61:H61"/>
-    <mergeCell ref="A65:H65"/>
+    <mergeCell ref="A70:H70"/>
+    <mergeCell ref="A78:H78"/>
+    <mergeCell ref="A69:H69"/>
     <mergeCell ref="A66:H66"/>
-    <mergeCell ref="A75:H75"/>
-    <mergeCell ref="A74:H74"/>
-    <mergeCell ref="A56:H56"/>
+    <mergeCell ref="A80:H80"/>
     <mergeCell ref="A9:H10"/>
-    <mergeCell ref="A55:H55"/>
-    <mergeCell ref="A57:H57"/>
     <mergeCell ref="A71:H71"/>
+    <mergeCell ref="A76:H76"/>
     <mergeCell ref="A62:H62"/>
+    <mergeCell ref="A81:H81"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A63:H63"/>
     <mergeCell ref="A72:H72"/>
     <mergeCell ref="A68:H68"/>
-    <mergeCell ref="A58:H58"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>Index levé — Zone 1 (SS_Amont) + Zone 2 (SS_Aval)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Éditez les surfaces dans SS_Amont et SS_Aval (pas ici). Ce tableau compare A1+A2 vs total pour détecter un double comptage. GIS export = option pour sortir des polygones d'eau depuis AutoCAD/Civil 3D; vous n'en avez pas besoin si vous tapez les aires à la main depuis le plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>WSE (m)</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>A_Zone1 (m²)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>A_Zone2 (m²)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>A1+A2 (m²)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>V1 (m³)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>V2 (m³)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>V1+V2 (m³)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="32">
+        <f>SS_Amont!A11</f>
+        <v/>
+      </c>
+      <c r="B6" s="45">
+        <f>SS_Amont!B11</f>
+        <v/>
+      </c>
+      <c r="C6" s="45">
+        <f>SS_Aval!B11</f>
+        <v/>
+      </c>
+      <c r="D6" s="46">
+        <f>B6+C6</f>
+        <v/>
+      </c>
+      <c r="E6" s="26">
+        <f>SS_Amont!E11</f>
+        <v/>
+      </c>
+      <c r="F6" s="26">
+        <f>SS_Aval!E11</f>
+        <v/>
+      </c>
+      <c r="G6" s="34">
+        <f>E6+F6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="32">
+        <f>SS_Amont!A12</f>
+        <v/>
+      </c>
+      <c r="B7" s="45">
+        <f>SS_Amont!B12</f>
+        <v/>
+      </c>
+      <c r="C7" s="45">
+        <f>SS_Aval!B12</f>
+        <v/>
+      </c>
+      <c r="D7" s="46">
+        <f>B7+C7</f>
+        <v/>
+      </c>
+      <c r="E7" s="26">
+        <f>SS_Amont!E12</f>
+        <v/>
+      </c>
+      <c r="F7" s="26">
+        <f>SS_Aval!E12</f>
+        <v/>
+      </c>
+      <c r="G7" s="34">
+        <f>E7+F7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="32">
+        <f>SS_Amont!A13</f>
+        <v/>
+      </c>
+      <c r="B8" s="45">
+        <f>SS_Amont!B13</f>
+        <v/>
+      </c>
+      <c r="C8" s="45">
+        <f>SS_Aval!B13</f>
+        <v/>
+      </c>
+      <c r="D8" s="46">
+        <f>B8+C8</f>
+        <v/>
+      </c>
+      <c r="E8" s="26">
+        <f>SS_Amont!E13</f>
+        <v/>
+      </c>
+      <c r="F8" s="26">
+        <f>SS_Aval!E13</f>
+        <v/>
+      </c>
+      <c r="G8" s="34">
+        <f>E8+F8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="32">
+        <f>SS_Amont!A14</f>
+        <v/>
+      </c>
+      <c r="B9" s="45">
+        <f>SS_Amont!B14</f>
+        <v/>
+      </c>
+      <c r="C9" s="45">
+        <f>SS_Aval!B14</f>
+        <v/>
+      </c>
+      <c r="D9" s="46">
+        <f>B9+C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="26">
+        <f>SS_Amont!E14</f>
+        <v/>
+      </c>
+      <c r="F9" s="26">
+        <f>SS_Aval!E14</f>
+        <v/>
+      </c>
+      <c r="G9" s="34">
+        <f>E9+F9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="32">
+        <f>SS_Amont!A15</f>
+        <v/>
+      </c>
+      <c r="B10" s="45">
+        <f>SS_Amont!B15</f>
+        <v/>
+      </c>
+      <c r="C10" s="45">
+        <f>SS_Aval!B15</f>
+        <v/>
+      </c>
+      <c r="D10" s="46">
+        <f>B10+C10</f>
+        <v/>
+      </c>
+      <c r="E10" s="26">
+        <f>SS_Amont!E15</f>
+        <v/>
+      </c>
+      <c r="F10" s="26">
+        <f>SS_Aval!E15</f>
+        <v/>
+      </c>
+      <c r="G10" s="34">
+        <f>E10+F10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="32">
+        <f>SS_Amont!A16</f>
+        <v/>
+      </c>
+      <c r="B11" s="45">
+        <f>SS_Amont!B16</f>
+        <v/>
+      </c>
+      <c r="C11" s="45">
+        <f>SS_Aval!B16</f>
+        <v/>
+      </c>
+      <c r="D11" s="46">
+        <f>B11+C11</f>
+        <v/>
+      </c>
+      <c r="E11" s="26">
+        <f>SS_Amont!E16</f>
+        <v/>
+      </c>
+      <c r="F11" s="26">
+        <f>SS_Aval!E16</f>
+        <v/>
+      </c>
+      <c r="G11" s="34">
+        <f>E11+F11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="32">
+        <f>SS_Amont!A17</f>
+        <v/>
+      </c>
+      <c r="B12" s="45">
+        <f>SS_Amont!B17</f>
+        <v/>
+      </c>
+      <c r="C12" s="45">
+        <f>SS_Aval!B17</f>
+        <v/>
+      </c>
+      <c r="D12" s="46">
+        <f>B12+C12</f>
+        <v/>
+      </c>
+      <c r="E12" s="26">
+        <f>SS_Amont!E17</f>
+        <v/>
+      </c>
+      <c r="F12" s="26">
+        <f>SS_Aval!E17</f>
+        <v/>
+      </c>
+      <c r="G12" s="34">
+        <f>E12+F12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="32">
+        <f>SS_Amont!A18</f>
+        <v/>
+      </c>
+      <c r="B13" s="45">
+        <f>SS_Amont!B18</f>
+        <v/>
+      </c>
+      <c r="C13" s="45">
+        <f>SS_Aval!B18</f>
+        <v/>
+      </c>
+      <c r="D13" s="46">
+        <f>B13+C13</f>
+        <v/>
+      </c>
+      <c r="E13" s="26">
+        <f>SS_Amont!E18</f>
+        <v/>
+      </c>
+      <c r="F13" s="26">
+        <f>SS_Aval!E18</f>
+        <v/>
+      </c>
+      <c r="G13" s="34">
+        <f>E13+F13</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:H3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>Zone 2 — Méthode A: Qin = sortie Ø900; Qout = Q_plein Ø1200</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="40" t="inlineStr">
+        <is>
+          <t>Qin_aval ≈ débit livré par le Ø900 (Calcul_A colonne C = Qcap Ø900 quand le bassin amont stocke). Qout_aval = Parametres capacité Ø1200. Stockage sur SS_Aval. Souvent Vmax_Aval faible si Q_1200 ≫ Q_900.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Qout_Aval (m³/s)</t>
+        </is>
+      </c>
+      <c r="B5" s="30">
+        <f>4.93</f>
+        <v/>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Par défaut Q_plein Ø1200 — éditable</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Vmax_Aval_A (m³)</t>
+        </is>
+      </c>
+      <c r="B6" s="31">
+        <f>MAX(H10:H22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>WSEmax_Aval (m)</t>
+        </is>
+      </c>
+      <c r="B7" s="22">
+        <f>IF(B6&lt;=SS_Aval!E11,SS_Aval!A11,IF(B6&gt;=SS_Aval!E18,"Hors table (&gt;=40.0 m — étendre levé)",INDEX(SS_Aval!$A$11:$A$18,MATCH(B6,SS_Aval!$E$11:$E$18,1))+(B6-INDEX(SS_Aval!$E$11:$E$18,MATCH(B6,SS_Aval!$E$11:$E$18,1)))/(INDEX(SS_Aval!$E$11:$E$18,MATCH(B6,SS_Aval!$E$11:$E$18,1)+1)-INDEX(SS_Aval!$E$11:$E$18,MATCH(B6,SS_Aval!$E$11:$E$18,1)))*(INDEX(SS_Aval!$A$11:$A$18,MATCH(B6,SS_Aval!$E$11:$E$18,1)+1)-INDEX(SS_Aval!$A$11:$A$18,MATCH(B6,SS_Aval!$E$11:$E$18,1)))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>t (min)</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Qin_aval (m³/s)</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Qout_aval (m³/s)</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Qin−Qout</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Δt (s)</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>ΔVin (m³)</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>ΔVout (m³)</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>V stocké (m³)</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Stockage?</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="26">
+        <f>Calcul_A!A8</f>
+        <v/>
+      </c>
+      <c r="B10" s="5">
+        <f>Calcul_A!C8</f>
+        <v/>
+      </c>
+      <c r="C10" s="32">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="D10" s="5">
+        <f>B10-C10</f>
+        <v/>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4">
+        <f>IF(H10&gt;0.5,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="26">
+        <f>Calcul_A!A9</f>
+        <v/>
+      </c>
+      <c r="B11" s="5">
+        <f>Calcul_A!C9</f>
+        <v/>
+      </c>
+      <c r="C11" s="32">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="D11" s="5">
+        <f>B11-C11</f>
+        <v/>
+      </c>
+      <c r="E11" s="26">
+        <f>(A11-A10)*60</f>
+        <v/>
+      </c>
+      <c r="F11" s="26">
+        <f>0.5*(B10+B11)*E11</f>
+        <v/>
+      </c>
+      <c r="G11" s="26">
+        <f>F11-(H11-H10)</f>
+        <v/>
+      </c>
+      <c r="H11" s="34">
+        <f>MAX(0,H10+0.5*(D10+D11)*E11)</f>
+        <v/>
+      </c>
+      <c r="I11" s="4">
+        <f>IF(H11&gt;0.5,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="26">
+        <f>Calcul_A!A10</f>
+        <v/>
+      </c>
+      <c r="B12" s="5">
+        <f>Calcul_A!C10</f>
+        <v/>
+      </c>
+      <c r="C12" s="32">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="D12" s="5">
+        <f>B12-C12</f>
+        <v/>
+      </c>
+      <c r="E12" s="26">
+        <f>(A12-A11)*60</f>
+        <v/>
+      </c>
+      <c r="F12" s="26">
+        <f>0.5*(B11+B12)*E12</f>
+        <v/>
+      </c>
+      <c r="G12" s="26">
+        <f>F12-(H12-H11)</f>
+        <v/>
+      </c>
+      <c r="H12" s="34">
+        <f>MAX(0,H11+0.5*(D11+D12)*E12)</f>
+        <v/>
+      </c>
+      <c r="I12" s="4">
+        <f>IF(H12&gt;0.5,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="26">
+        <f>Calcul_A!A11</f>
+        <v/>
+      </c>
+      <c r="B13" s="5">
+        <f>Calcul_A!C11</f>
+        <v/>
+      </c>
+      <c r="C13" s="32">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="D13" s="5">
+        <f>B13-C13</f>
+        <v/>
+      </c>
+      <c r="E13" s="26">
+        <f>(A13-A12)*60</f>
+        <v/>
+      </c>
+      <c r="F13" s="26">
+        <f>0.5*(B12+B13)*E13</f>
+        <v/>
+      </c>
+      <c r="G13" s="26">
+        <f>F13-(H13-H12)</f>
+        <v/>
+      </c>
+      <c r="H13" s="34">
+        <f>MAX(0,H12+0.5*(D12+D13)*E13)</f>
+        <v/>
+      </c>
+      <c r="I13" s="4">
+        <f>IF(H13&gt;0.5,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="26">
+        <f>Calcul_A!A12</f>
+        <v/>
+      </c>
+      <c r="B14" s="5">
+        <f>Calcul_A!C12</f>
+        <v/>
+      </c>
+      <c r="C14" s="32">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>B14-C14</f>
+        <v/>
+      </c>
+      <c r="E14" s="26">
+        <f>(A14-A13)*60</f>
+        <v/>
+      </c>
+      <c r="F14" s="26">
+        <f>0.5*(B13+B14)*E14</f>
+        <v/>
+      </c>
+      <c r="G14" s="26">
+        <f>F14-(H14-H13)</f>
+        <v/>
+      </c>
+      <c r="H14" s="34">
+        <f>MAX(0,H13+0.5*(D13+D14)*E14)</f>
+        <v/>
+      </c>
+      <c r="I14" s="4">
+        <f>IF(H14&gt;0.5,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="26">
+        <f>Calcul_A!A13</f>
+        <v/>
+      </c>
+      <c r="B15" s="5">
+        <f>Calcul_A!C13</f>
+        <v/>
+      </c>
+      <c r="C15" s="32">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="D15" s="5">
+        <f>B15-C15</f>
+        <v/>
+      </c>
+      <c r="E15" s="26">
+        <f>(A15-A14)*60</f>
+        <v/>
+      </c>
+      <c r="F15" s="26">
+        <f>0.5*(B14+B15)*E15</f>
+        <v/>
+      </c>
+      <c r="G15" s="26">
+        <f>F15-(H15-H14)</f>
+        <v/>
+      </c>
+      <c r="H15" s="34">
+        <f>MAX(0,H14+0.5*(D14+D15)*E15)</f>
+        <v/>
+      </c>
+      <c r="I15" s="4">
+        <f>IF(H15&gt;0.5,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="26">
+        <f>Calcul_A!A14</f>
+        <v/>
+      </c>
+      <c r="B16" s="5">
+        <f>Calcul_A!C14</f>
+        <v/>
+      </c>
+      <c r="C16" s="32">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="D16" s="5">
+        <f>B16-C16</f>
+        <v/>
+      </c>
+      <c r="E16" s="26">
+        <f>(A16-A15)*60</f>
+        <v/>
+      </c>
+      <c r="F16" s="26">
+        <f>0.5*(B15+B16)*E16</f>
+        <v/>
+      </c>
+      <c r="G16" s="26">
+        <f>F16-(H16-H15)</f>
+        <v/>
+      </c>
+      <c r="H16" s="34">
+        <f>MAX(0,H15+0.5*(D15+D16)*E16)</f>
+        <v/>
+      </c>
+      <c r="I16" s="4">
+        <f>IF(H16&gt;0.5,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="26">
+        <f>Calcul_A!A15</f>
+        <v/>
+      </c>
+      <c r="B17" s="5">
+        <f>Calcul_A!C15</f>
+        <v/>
+      </c>
+      <c r="C17" s="32">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="D17" s="5">
+        <f>B17-C17</f>
+        <v/>
+      </c>
+      <c r="E17" s="26">
+        <f>(A17-A16)*60</f>
+        <v/>
+      </c>
+      <c r="F17" s="26">
+        <f>0.5*(B16+B17)*E17</f>
+        <v/>
+      </c>
+      <c r="G17" s="26">
+        <f>F17-(H17-H16)</f>
+        <v/>
+      </c>
+      <c r="H17" s="34">
+        <f>MAX(0,H16+0.5*(D16+D17)*E17)</f>
+        <v/>
+      </c>
+      <c r="I17" s="4">
+        <f>IF(H17&gt;0.5,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="26">
+        <f>Calcul_A!A16</f>
+        <v/>
+      </c>
+      <c r="B18" s="5">
+        <f>Calcul_A!C16</f>
+        <v/>
+      </c>
+      <c r="C18" s="32">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="D18" s="5">
+        <f>B18-C18</f>
+        <v/>
+      </c>
+      <c r="E18" s="26">
+        <f>(A18-A17)*60</f>
+        <v/>
+      </c>
+      <c r="F18" s="26">
+        <f>0.5*(B17+B18)*E18</f>
+        <v/>
+      </c>
+      <c r="G18" s="26">
+        <f>F18-(H18-H17)</f>
+        <v/>
+      </c>
+      <c r="H18" s="34">
+        <f>MAX(0,H17+0.5*(D17+D18)*E18)</f>
+        <v/>
+      </c>
+      <c r="I18" s="4">
+        <f>IF(H18&gt;0.5,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="26">
+        <f>Calcul_A!A17</f>
+        <v/>
+      </c>
+      <c r="B19" s="5">
+        <f>Calcul_A!C17</f>
+        <v/>
+      </c>
+      <c r="C19" s="32">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="D19" s="5">
+        <f>B19-C19</f>
+        <v/>
+      </c>
+      <c r="E19" s="26">
+        <f>(A19-A18)*60</f>
+        <v/>
+      </c>
+      <c r="F19" s="26">
+        <f>0.5*(B18+B19)*E19</f>
+        <v/>
+      </c>
+      <c r="G19" s="26">
+        <f>F19-(H19-H18)</f>
+        <v/>
+      </c>
+      <c r="H19" s="34">
+        <f>MAX(0,H18+0.5*(D18+D19)*E19)</f>
+        <v/>
+      </c>
+      <c r="I19" s="4">
+        <f>IF(H19&gt;0.5,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="26">
+        <f>Calcul_A!A18</f>
+        <v/>
+      </c>
+      <c r="B20" s="5">
+        <f>Calcul_A!C18</f>
+        <v/>
+      </c>
+      <c r="C20" s="32">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="D20" s="5">
+        <f>B20-C20</f>
+        <v/>
+      </c>
+      <c r="E20" s="26">
+        <f>(A20-A19)*60</f>
+        <v/>
+      </c>
+      <c r="F20" s="26">
+        <f>0.5*(B19+B20)*E20</f>
+        <v/>
+      </c>
+      <c r="G20" s="26">
+        <f>F20-(H20-H19)</f>
+        <v/>
+      </c>
+      <c r="H20" s="34">
+        <f>MAX(0,H19+0.5*(D19+D20)*E20)</f>
+        <v/>
+      </c>
+      <c r="I20" s="4">
+        <f>IF(H20&gt;0.5,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="26">
+        <f>Calcul_A!A19</f>
+        <v/>
+      </c>
+      <c r="B21" s="5">
+        <f>Calcul_A!C19</f>
+        <v/>
+      </c>
+      <c r="C21" s="32">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="D21" s="5">
+        <f>B21-C21</f>
+        <v/>
+      </c>
+      <c r="E21" s="26">
+        <f>(A21-A20)*60</f>
+        <v/>
+      </c>
+      <c r="F21" s="26">
+        <f>0.5*(B20+B21)*E21</f>
+        <v/>
+      </c>
+      <c r="G21" s="26">
+        <f>F21-(H21-H20)</f>
+        <v/>
+      </c>
+      <c r="H21" s="34">
+        <f>MAX(0,H20+0.5*(D20+D21)*E21)</f>
+        <v/>
+      </c>
+      <c r="I21" s="4">
+        <f>IF(H21&gt;0.5,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="26">
+        <f>Calcul_A!A20</f>
+        <v/>
+      </c>
+      <c r="B22" s="5">
+        <f>Calcul_A!C20</f>
+        <v/>
+      </c>
+      <c r="C22" s="32">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="D22" s="5">
+        <f>B22-C22</f>
+        <v/>
+      </c>
+      <c r="E22" s="26">
+        <f>(A22-A21)*60</f>
+        <v/>
+      </c>
+      <c r="F22" s="26">
+        <f>0.5*(B21+B22)*E22</f>
+        <v/>
+      </c>
+      <c r="G22" s="26">
+        <f>F22-(H22-H21)</f>
+        <v/>
+      </c>
+      <c r="H22" s="34">
+        <f>MAX(0,H21+0.5*(D21+D22)*E22)</f>
+        <v/>
+      </c>
+      <c r="I22" s="4">
+        <f>IF(H22&gt;0.5,"oui","non")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:I3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="100" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="47" t="inlineStr">
+        <is>
+          <t>Où sont les fichiers HY-8 / capacité ?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ce classeur (rétention Ø900) :</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  engineering/drainage-design/retention_volume/Volume_Retention_Ponceau_900.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Courbe Q=f(H) FHWA pour CE Ø900 : feuille Courbe_QH_900 (ci-dessus).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ancien Excel « type HY-8 / inlet-outlet » (autre projet / Ste-Thérèse) :</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  engineering/drainage-design/Ponceau_Capacite_Inlet_Outlet.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Branche git: cursor/culvert-excel-capacity-model-d87f</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Modèle composé ponceau Ø1050 + fossé (FHWA + remblai) — PAS le Ø900 de rétention :</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  engineering/drainage-design/ponceau_fosse_model/Ponceau_Fosse_Modele_Hydraulique.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Branche git: cursor/ponceau-fosse-hydraulic-model-d87f</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>HEC-RAS : pas de projet .ras/.hdf pour ce Ø900. Un DEM Ste-Thérèse est dans</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  engineering/hec-ras-data/ (données topo seulement).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Donc: on n'avait pas perdu un HY-8 pour ce bassin Ø900 — on avait des outils</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>similaires pour d'autres sites. La courbe de CE classeur remplace ça pour le Ø900.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2387,7 +3670,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="45" t="inlineStr">
+      <c r="A1" s="48" t="inlineStr">
         <is>
           <t>Méthode — volume de rétention</t>
         </is>
@@ -2479,7 +3762,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9. Niveau d'eau max: A/B via Stage_Storage; C via Calcul_C (Parametres B39 / B45 / B51).</t>
+          <t>9. Niveau d'eau max Zone 1: A/B via SS_Amont; C via Calcul_C. Zone 2: SS_Aval + Calcul_Aval_A (B55–B57).</t>
         </is>
       </c>
     </row>
@@ -2514,7 +3797,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Hydrogramme d'entrée (point Ø1500 / entrée rétention) — FORMULES LIVE</t>
         </is>
@@ -2549,7 +3832,7 @@
           <t>t pointe (min)</t>
         </is>
       </c>
-      <c r="B5" s="24" t="n">
+      <c r="B5" s="25" t="n">
         <v>22.5</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -2581,10 +3864,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="n">
+      <c r="A8" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="B8" s="26" t="n">
+      <c r="B8" s="27" t="n">
         <v>0.081042</v>
       </c>
       <c r="C8" s="5">
@@ -2598,10 +3881,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="25" t="n">
+      <c r="A9" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="26" t="n">
+      <c r="B9" s="27" t="n">
         <v>0.121875</v>
       </c>
       <c r="C9" s="5">
@@ -2611,10 +3894,10 @@
       <c r="D9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="n">
+      <c r="A10" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="B10" s="26" t="n">
+      <c r="B10" s="27" t="n">
         <v>0.193438</v>
       </c>
       <c r="C10" s="5">
@@ -2624,10 +3907,10 @@
       <c r="D10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="25" t="n">
+      <c r="A11" s="26" t="n">
         <v>15</v>
       </c>
-      <c r="B11" s="26" t="n">
+      <c r="B11" s="27" t="n">
         <v>0.333542</v>
       </c>
       <c r="C11" s="5">
@@ -2637,10 +3920,10 @@
       <c r="D11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="n">
+      <c r="A12" s="26" t="n">
         <v>20</v>
       </c>
-      <c r="B12" s="26" t="n">
+      <c r="B12" s="27" t="n">
         <v>0.657188</v>
       </c>
       <c r="C12" s="5">
@@ -2650,10 +3933,10 @@
       <c r="D12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="25" t="n">
+      <c r="A13" s="26" t="n">
         <v>22.5</v>
       </c>
-      <c r="B13" s="26" t="n">
+      <c r="B13" s="27" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="8">
@@ -2667,10 +3950,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="n">
+      <c r="A14" s="26" t="n">
         <v>27.5</v>
       </c>
-      <c r="B14" s="26" t="n">
+      <c r="B14" s="27" t="n">
         <v>0.608958</v>
       </c>
       <c r="C14" s="5">
@@ -2680,10 +3963,10 @@
       <c r="D14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="25" t="n">
+      <c r="A15" s="26" t="n">
         <v>32.5</v>
       </c>
-      <c r="B15" s="26" t="n">
+      <c r="B15" s="27" t="n">
         <v>0.401771</v>
       </c>
       <c r="C15" s="5">
@@ -2693,10 +3976,10 @@
       <c r="D15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="25" t="n">
+      <c r="A16" s="26" t="n">
         <v>37.5</v>
       </c>
-      <c r="B16" s="26" t="n">
+      <c r="B16" s="27" t="n">
         <v>0.280104</v>
       </c>
       <c r="C16" s="5">
@@ -2706,10 +3989,10 @@
       <c r="D16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="25" t="n">
+      <c r="A17" s="26" t="n">
         <v>42.5</v>
       </c>
-      <c r="B17" s="26" t="n">
+      <c r="B17" s="27" t="n">
         <v>0.203438</v>
       </c>
       <c r="C17" s="5">
@@ -2719,10 +4002,10 @@
       <c r="D17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="n">
+      <c r="A18" s="26" t="n">
         <v>47.5</v>
       </c>
-      <c r="B18" s="26" t="n">
+      <c r="B18" s="27" t="n">
         <v>0.152292</v>
       </c>
       <c r="C18" s="5">
@@ -2732,10 +4015,10 @@
       <c r="D18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="25" t="n">
+      <c r="A19" s="26" t="n">
         <v>52.5</v>
       </c>
-      <c r="B19" s="26" t="n">
+      <c r="B19" s="27" t="n">
         <v>0.116771</v>
       </c>
       <c r="C19" s="5">
@@ -2745,10 +4028,10 @@
       <c r="D19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="25" t="n">
+      <c r="A20" s="26" t="n">
         <v>57.5</v>
       </c>
-      <c r="B20" s="26" t="n">
+      <c r="B20" s="27" t="n">
         <v>0.091146</v>
       </c>
       <c r="C20" s="5">
@@ -2763,7 +4046,7 @@
           <t>Qin max (contrôle)</t>
         </is>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="28">
         <f>MAX(C8:C20)</f>
         <v/>
       </c>
@@ -2779,7 +4062,7 @@
           <t>Qcap Ø900 (réf.)</t>
         </is>
       </c>
-      <c r="B23" s="28">
+      <c r="B23" s="29">
         <f>Parametres!B22</f>
         <v/>
       </c>
@@ -2814,7 +4097,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Méthode A — Qout constant = capacité Ø900</t>
         </is>
@@ -2826,7 +4109,7 @@
           <t>Qout (m³/s)</t>
         </is>
       </c>
-      <c r="B2" s="29">
+      <c r="B2" s="30">
         <f>Parametres!B22</f>
         <v/>
       </c>
@@ -2837,7 +4120,7 @@
           <t>Vmax (m³)</t>
         </is>
       </c>
-      <c r="B3" s="30">
+      <c r="B3" s="31">
         <f>MAX(H8:H20)</f>
         <v/>
       </c>
@@ -2919,7 +4202,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="25">
+      <c r="A8" s="26">
         <f>Hydrogramme!A8</f>
         <v/>
       </c>
@@ -2927,7 +4210,7 @@
         <f>Hydrogramme!C8</f>
         <v/>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="32">
         <f>$B$2</f>
         <v/>
       </c>
@@ -2944,7 +4227,7 @@
       <c r="G8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="32" t="n">
+      <c r="H8" s="33" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="4">
@@ -2953,7 +4236,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="25">
+      <c r="A9" s="26">
         <f>Hydrogramme!A9</f>
         <v/>
       </c>
@@ -2961,7 +4244,7 @@
         <f>Hydrogramme!C9</f>
         <v/>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="32">
         <f>$B$2</f>
         <v/>
       </c>
@@ -2969,19 +4252,19 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="26">
         <f>(A9-A8)*60</f>
         <v/>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="26">
         <f>0.5*(B8+B9)*E9</f>
         <v/>
       </c>
-      <c r="G9" s="25">
+      <c r="G9" s="26">
         <f>F9-(H9-H8)</f>
         <v/>
       </c>
-      <c r="H9" s="33">
+      <c r="H9" s="34">
         <f>MAX(0,H8+0.5*(D8+D9)*E9)</f>
         <v/>
       </c>
@@ -2991,7 +4274,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="25">
+      <c r="A10" s="26">
         <f>Hydrogramme!A10</f>
         <v/>
       </c>
@@ -2999,7 +4282,7 @@
         <f>Hydrogramme!C10</f>
         <v/>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="32">
         <f>$B$2</f>
         <v/>
       </c>
@@ -3007,19 +4290,19 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="26">
         <f>(A10-A9)*60</f>
         <v/>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="26">
         <f>0.5*(B9+B10)*E10</f>
         <v/>
       </c>
-      <c r="G10" s="25">
+      <c r="G10" s="26">
         <f>F10-(H10-H9)</f>
         <v/>
       </c>
-      <c r="H10" s="33">
+      <c r="H10" s="34">
         <f>MAX(0,H9+0.5*(D9+D10)*E10)</f>
         <v/>
       </c>
@@ -3029,7 +4312,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="25">
+      <c r="A11" s="26">
         <f>Hydrogramme!A11</f>
         <v/>
       </c>
@@ -3037,7 +4320,7 @@
         <f>Hydrogramme!C11</f>
         <v/>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="32">
         <f>$B$2</f>
         <v/>
       </c>
@@ -3045,19 +4328,19 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="26">
         <f>(A11-A10)*60</f>
         <v/>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="26">
         <f>0.5*(B10+B11)*E11</f>
         <v/>
       </c>
-      <c r="G11" s="25">
+      <c r="G11" s="26">
         <f>F11-(H11-H10)</f>
         <v/>
       </c>
-      <c r="H11" s="33">
+      <c r="H11" s="34">
         <f>MAX(0,H10+0.5*(D10+D11)*E11)</f>
         <v/>
       </c>
@@ -3067,7 +4350,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="25">
+      <c r="A12" s="26">
         <f>Hydrogramme!A12</f>
         <v/>
       </c>
@@ -3075,7 +4358,7 @@
         <f>Hydrogramme!C12</f>
         <v/>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="32">
         <f>$B$2</f>
         <v/>
       </c>
@@ -3083,19 +4366,19 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="26">
         <f>(A12-A11)*60</f>
         <v/>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="26">
         <f>0.5*(B11+B12)*E12</f>
         <v/>
       </c>
-      <c r="G12" s="25">
+      <c r="G12" s="26">
         <f>F12-(H12-H11)</f>
         <v/>
       </c>
-      <c r="H12" s="33">
+      <c r="H12" s="34">
         <f>MAX(0,H11+0.5*(D11+D12)*E12)</f>
         <v/>
       </c>
@@ -3105,7 +4388,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="25">
+      <c r="A13" s="26">
         <f>Hydrogramme!A13</f>
         <v/>
       </c>
@@ -3113,7 +4396,7 @@
         <f>Hydrogramme!C13</f>
         <v/>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="32">
         <f>$B$2</f>
         <v/>
       </c>
@@ -3121,19 +4404,19 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="26">
         <f>(A13-A12)*60</f>
         <v/>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="26">
         <f>0.5*(B12+B13)*E13</f>
         <v/>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="26">
         <f>F13-(H13-H12)</f>
         <v/>
       </c>
-      <c r="H13" s="33">
+      <c r="H13" s="34">
         <f>MAX(0,H12+0.5*(D12+D13)*E13)</f>
         <v/>
       </c>
@@ -3143,7 +4426,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="25">
+      <c r="A14" s="26">
         <f>Hydrogramme!A14</f>
         <v/>
       </c>
@@ -3151,7 +4434,7 @@
         <f>Hydrogramme!C14</f>
         <v/>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="32">
         <f>$B$2</f>
         <v/>
       </c>
@@ -3159,19 +4442,19 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="26">
         <f>(A14-A13)*60</f>
         <v/>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="26">
         <f>0.5*(B13+B14)*E14</f>
         <v/>
       </c>
-      <c r="G14" s="25">
+      <c r="G14" s="26">
         <f>F14-(H14-H13)</f>
         <v/>
       </c>
-      <c r="H14" s="33">
+      <c r="H14" s="34">
         <f>MAX(0,H13+0.5*(D13+D14)*E14)</f>
         <v/>
       </c>
@@ -3181,7 +4464,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="25">
+      <c r="A15" s="26">
         <f>Hydrogramme!A15</f>
         <v/>
       </c>
@@ -3189,7 +4472,7 @@
         <f>Hydrogramme!C15</f>
         <v/>
       </c>
-      <c r="C15" s="31">
+      <c r="C15" s="32">
         <f>$B$2</f>
         <v/>
       </c>
@@ -3197,19 +4480,19 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="26">
         <f>(A15-A14)*60</f>
         <v/>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="26">
         <f>0.5*(B14+B15)*E15</f>
         <v/>
       </c>
-      <c r="G15" s="25">
+      <c r="G15" s="26">
         <f>F15-(H15-H14)</f>
         <v/>
       </c>
-      <c r="H15" s="33">
+      <c r="H15" s="34">
         <f>MAX(0,H14+0.5*(D14+D15)*E15)</f>
         <v/>
       </c>
@@ -3219,7 +4502,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="25">
+      <c r="A16" s="26">
         <f>Hydrogramme!A16</f>
         <v/>
       </c>
@@ -3227,7 +4510,7 @@
         <f>Hydrogramme!C16</f>
         <v/>
       </c>
-      <c r="C16" s="31">
+      <c r="C16" s="32">
         <f>$B$2</f>
         <v/>
       </c>
@@ -3235,19 +4518,19 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="26">
         <f>(A16-A15)*60</f>
         <v/>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="26">
         <f>0.5*(B15+B16)*E16</f>
         <v/>
       </c>
-      <c r="G16" s="25">
+      <c r="G16" s="26">
         <f>F16-(H16-H15)</f>
         <v/>
       </c>
-      <c r="H16" s="33">
+      <c r="H16" s="34">
         <f>MAX(0,H15+0.5*(D15+D16)*E16)</f>
         <v/>
       </c>
@@ -3257,7 +4540,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="25">
+      <c r="A17" s="26">
         <f>Hydrogramme!A17</f>
         <v/>
       </c>
@@ -3265,7 +4548,7 @@
         <f>Hydrogramme!C17</f>
         <v/>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="32">
         <f>$B$2</f>
         <v/>
       </c>
@@ -3273,19 +4556,19 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="26">
         <f>(A17-A16)*60</f>
         <v/>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="26">
         <f>0.5*(B16+B17)*E17</f>
         <v/>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="26">
         <f>F17-(H17-H16)</f>
         <v/>
       </c>
-      <c r="H17" s="33">
+      <c r="H17" s="34">
         <f>MAX(0,H16+0.5*(D16+D17)*E17)</f>
         <v/>
       </c>
@@ -3295,7 +4578,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="25">
+      <c r="A18" s="26">
         <f>Hydrogramme!A18</f>
         <v/>
       </c>
@@ -3303,7 +4586,7 @@
         <f>Hydrogramme!C18</f>
         <v/>
       </c>
-      <c r="C18" s="31">
+      <c r="C18" s="32">
         <f>$B$2</f>
         <v/>
       </c>
@@ -3311,19 +4594,19 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="25">
+      <c r="E18" s="26">
         <f>(A18-A17)*60</f>
         <v/>
       </c>
-      <c r="F18" s="25">
+      <c r="F18" s="26">
         <f>0.5*(B17+B18)*E18</f>
         <v/>
       </c>
-      <c r="G18" s="25">
+      <c r="G18" s="26">
         <f>F18-(H18-H17)</f>
         <v/>
       </c>
-      <c r="H18" s="33">
+      <c r="H18" s="34">
         <f>MAX(0,H17+0.5*(D17+D18)*E18)</f>
         <v/>
       </c>
@@ -3333,7 +4616,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="25">
+      <c r="A19" s="26">
         <f>Hydrogramme!A19</f>
         <v/>
       </c>
@@ -3341,7 +4624,7 @@
         <f>Hydrogramme!C19</f>
         <v/>
       </c>
-      <c r="C19" s="31">
+      <c r="C19" s="32">
         <f>$B$2</f>
         <v/>
       </c>
@@ -3349,19 +4632,19 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="25">
+      <c r="E19" s="26">
         <f>(A19-A18)*60</f>
         <v/>
       </c>
-      <c r="F19" s="25">
+      <c r="F19" s="26">
         <f>0.5*(B18+B19)*E19</f>
         <v/>
       </c>
-      <c r="G19" s="25">
+      <c r="G19" s="26">
         <f>F19-(H19-H18)</f>
         <v/>
       </c>
-      <c r="H19" s="33">
+      <c r="H19" s="34">
         <f>MAX(0,H18+0.5*(D18+D19)*E19)</f>
         <v/>
       </c>
@@ -3371,7 +4654,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="25">
+      <c r="A20" s="26">
         <f>Hydrogramme!A20</f>
         <v/>
       </c>
@@ -3379,7 +4662,7 @@
         <f>Hydrogramme!C20</f>
         <v/>
       </c>
-      <c r="C20" s="31">
+      <c r="C20" s="32">
         <f>$B$2</f>
         <v/>
       </c>
@@ -3387,19 +4670,19 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="25">
+      <c r="E20" s="26">
         <f>(A20-A19)*60</f>
         <v/>
       </c>
-      <c r="F20" s="25">
+      <c r="F20" s="26">
         <f>0.5*(B19+B20)*E20</f>
         <v/>
       </c>
-      <c r="G20" s="25">
+      <c r="G20" s="26">
         <f>F20-(H20-H19)</f>
         <v/>
       </c>
-      <c r="H20" s="33">
+      <c r="H20" s="34">
         <f>MAX(0,H19+0.5*(D19+D20)*E20)</f>
         <v/>
       </c>
@@ -3433,7 +4716,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Courbe de capacité Ø900 — Q = f(H) (FHWA HDS-5 inlet + outlet) — FORMULES LIVE</t>
         </is>
@@ -3473,32 +4756,32 @@
           <t>béton typ. 0.012–0.015</t>
         </is>
       </c>
-      <c r="E6" s="34" t="inlineStr">
+      <c r="E6" s="35" t="inlineStr">
         <is>
           <t>entrée</t>
         </is>
       </c>
-      <c r="F6" s="34" t="inlineStr">
+      <c r="F6" s="35" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="G6" s="34" t="inlineStr">
+      <c r="G6" s="35" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H6" s="34" t="inlineStr">
+      <c r="H6" s="35" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="I6" s="34" t="inlineStr">
+      <c r="I6" s="35" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J6" s="34" t="inlineStr">
+      <c r="J6" s="35" t="inlineStr">
         <is>
           <t>Ke</t>
         </is>
@@ -3614,7 +4897,7 @@
           <t>S0 = (Zin-Zout)/L</t>
         </is>
       </c>
-      <c r="B11" s="35">
+      <c r="B11" s="36">
         <f>(B9-B10)/B8</f>
         <v/>
       </c>
@@ -3645,7 +4928,7 @@
           <t>Entrée (texte exact)</t>
         </is>
       </c>
-      <c r="B13" s="36" t="inlineStr">
+      <c r="B13" s="37" t="inlineStr">
         <is>
           <t>square_edge</t>
         </is>
@@ -3662,7 +4945,7 @@
           <t>Q_plein Manning (réf.)</t>
         </is>
       </c>
-      <c r="B15" s="27">
+      <c r="B15" s="28">
         <f>(1/B6)*(PI()*B7^2/4)*((B7/4)^(2/3))*SQRT(B11)</f>
         <v/>
       </c>
@@ -3678,7 +4961,7 @@
           <t>K (lu)</t>
         </is>
       </c>
-      <c r="B17" s="37">
+      <c r="B17" s="38">
         <f>IFERROR(VLOOKUP(B13,$E$7:$J$9,2,FALSE),0.0098)</f>
         <v/>
       </c>
@@ -3689,7 +4972,7 @@
           <t>M (lu)</t>
         </is>
       </c>
-      <c r="B18" s="37">
+      <c r="B18" s="38">
         <f>IFERROR(VLOOKUP(B13,$E$7:$J$9,3,FALSE),2)</f>
         <v/>
       </c>
@@ -3700,7 +4983,7 @@
           <t>c (lu)</t>
         </is>
       </c>
-      <c r="B19" s="37">
+      <c r="B19" s="38">
         <f>IFERROR(VLOOKUP(B13,$E$7:$J$9,4,FALSE),0.0398)</f>
         <v/>
       </c>
@@ -3711,7 +4994,7 @@
           <t>Y (lu)</t>
         </is>
       </c>
-      <c r="B20" s="37">
+      <c r="B20" s="38">
         <f>IFERROR(VLOOKUP(B13,$E$7:$J$9,5,FALSE),0.67)</f>
         <v/>
       </c>
@@ -3722,7 +5005,7 @@
           <t>Ke (lu)</t>
         </is>
       </c>
-      <c r="B21" s="37">
+      <c r="B21" s="38">
         <f>IFERROR(VLOOKUP(B13,$E$7:$J$9,6,FALSE),0.5)</f>
         <v/>
       </c>
@@ -3760,10 +5043,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="31" t="n">
+      <c r="A24" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="B24" s="31">
+      <c r="B24" s="32">
         <f>$B$9+A24</f>
         <v/>
       </c>
@@ -3785,10 +5068,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="31" t="n">
+      <c r="A25" s="32" t="n">
         <v>0.05</v>
       </c>
-      <c r="B25" s="31">
+      <c r="B25" s="32">
         <f>$B$9+A25</f>
         <v/>
       </c>
@@ -3810,10 +5093,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="31" t="n">
+      <c r="A26" s="32" t="n">
         <v>0.1</v>
       </c>
-      <c r="B26" s="31">
+      <c r="B26" s="32">
         <f>$B$9+A26</f>
         <v/>
       </c>
@@ -3835,10 +5118,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="31" t="n">
+      <c r="A27" s="32" t="n">
         <v>0.15</v>
       </c>
-      <c r="B27" s="31">
+      <c r="B27" s="32">
         <f>$B$9+A27</f>
         <v/>
       </c>
@@ -3860,10 +5143,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="31" t="n">
+      <c r="A28" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="B28" s="31">
+      <c r="B28" s="32">
         <f>$B$9+A28</f>
         <v/>
       </c>
@@ -3885,10 +5168,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="31" t="n">
+      <c r="A29" s="32" t="n">
         <v>0.25</v>
       </c>
-      <c r="B29" s="31">
+      <c r="B29" s="32">
         <f>$B$9+A29</f>
         <v/>
       </c>
@@ -3910,10 +5193,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="31" t="n">
+      <c r="A30" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="B30" s="31">
+      <c r="B30" s="32">
         <f>$B$9+A30</f>
         <v/>
       </c>
@@ -3935,10 +5218,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="31" t="n">
+      <c r="A31" s="32" t="n">
         <v>0.35</v>
       </c>
-      <c r="B31" s="31">
+      <c r="B31" s="32">
         <f>$B$9+A31</f>
         <v/>
       </c>
@@ -3960,10 +5243,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="31" t="n">
+      <c r="A32" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="B32" s="31">
+      <c r="B32" s="32">
         <f>$B$9+A32</f>
         <v/>
       </c>
@@ -3985,10 +5268,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="31" t="n">
+      <c r="A33" s="32" t="n">
         <v>0.45</v>
       </c>
-      <c r="B33" s="31">
+      <c r="B33" s="32">
         <f>$B$9+A33</f>
         <v/>
       </c>
@@ -4010,10 +5293,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="31" t="n">
+      <c r="A34" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="B34" s="31">
+      <c r="B34" s="32">
         <f>$B$9+A34</f>
         <v/>
       </c>
@@ -4035,10 +5318,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="31" t="n">
+      <c r="A35" s="32" t="n">
         <v>0.55</v>
       </c>
-      <c r="B35" s="31">
+      <c r="B35" s="32">
         <f>$B$9+A35</f>
         <v/>
       </c>
@@ -4060,10 +5343,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="31" t="n">
+      <c r="A36" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="B36" s="31">
+      <c r="B36" s="32">
         <f>$B$9+A36</f>
         <v/>
       </c>
@@ -4085,10 +5368,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="31" t="n">
+      <c r="A37" s="32" t="n">
         <v>0.65</v>
       </c>
-      <c r="B37" s="31">
+      <c r="B37" s="32">
         <f>$B$9+A37</f>
         <v/>
       </c>
@@ -4110,10 +5393,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="31" t="n">
+      <c r="A38" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="B38" s="31">
+      <c r="B38" s="32">
         <f>$B$9+A38</f>
         <v/>
       </c>
@@ -4135,10 +5418,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="31" t="n">
+      <c r="A39" s="32" t="n">
         <v>0.75</v>
       </c>
-      <c r="B39" s="31">
+      <c r="B39" s="32">
         <f>$B$9+A39</f>
         <v/>
       </c>
@@ -4160,10 +5443,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="31" t="n">
+      <c r="A40" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="B40" s="31">
+      <c r="B40" s="32">
         <f>$B$9+A40</f>
         <v/>
       </c>
@@ -4185,10 +5468,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="31" t="n">
+      <c r="A41" s="32" t="n">
         <v>0.85</v>
       </c>
-      <c r="B41" s="31">
+      <c r="B41" s="32">
         <f>$B$9+A41</f>
         <v/>
       </c>
@@ -4210,10 +5493,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="31" t="n">
+      <c r="A42" s="32" t="n">
         <v>0.9</v>
       </c>
-      <c r="B42" s="31">
+      <c r="B42" s="32">
         <f>$B$9+A42</f>
         <v/>
       </c>
@@ -4235,10 +5518,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="31" t="n">
+      <c r="A43" s="32" t="n">
         <v>0.95</v>
       </c>
-      <c r="B43" s="31">
+      <c r="B43" s="32">
         <f>$B$9+A43</f>
         <v/>
       </c>
@@ -4260,10 +5543,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="31" t="n">
+      <c r="A44" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="B44" s="31">
+      <c r="B44" s="32">
         <f>$B$9+A44</f>
         <v/>
       </c>
@@ -4285,10 +5568,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="31" t="n">
+      <c r="A45" s="32" t="n">
         <v>1.05</v>
       </c>
-      <c r="B45" s="31">
+      <c r="B45" s="32">
         <f>$B$9+A45</f>
         <v/>
       </c>
@@ -4310,10 +5593,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="31" t="n">
+      <c r="A46" s="32" t="n">
         <v>1.1</v>
       </c>
-      <c r="B46" s="31">
+      <c r="B46" s="32">
         <f>$B$9+A46</f>
         <v/>
       </c>
@@ -4335,10 +5618,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="31" t="n">
+      <c r="A47" s="32" t="n">
         <v>1.15</v>
       </c>
-      <c r="B47" s="31">
+      <c r="B47" s="32">
         <f>$B$9+A47</f>
         <v/>
       </c>
@@ -4360,10 +5643,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="31" t="n">
+      <c r="A48" s="32" t="n">
         <v>1.2</v>
       </c>
-      <c r="B48" s="31">
+      <c r="B48" s="32">
         <f>$B$9+A48</f>
         <v/>
       </c>
@@ -4385,10 +5668,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="31" t="n">
+      <c r="A49" s="32" t="n">
         <v>1.25</v>
       </c>
-      <c r="B49" s="31">
+      <c r="B49" s="32">
         <f>$B$9+A49</f>
         <v/>
       </c>
@@ -4410,10 +5693,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="31" t="n">
+      <c r="A50" s="32" t="n">
         <v>1.3</v>
       </c>
-      <c r="B50" s="31">
+      <c r="B50" s="32">
         <f>$B$9+A50</f>
         <v/>
       </c>
@@ -4435,10 +5718,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="31" t="n">
+      <c r="A51" s="32" t="n">
         <v>1.35</v>
       </c>
-      <c r="B51" s="31">
+      <c r="B51" s="32">
         <f>$B$9+A51</f>
         <v/>
       </c>
@@ -4460,10 +5743,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="31" t="n">
+      <c r="A52" s="32" t="n">
         <v>1.4</v>
       </c>
-      <c r="B52" s="31">
+      <c r="B52" s="32">
         <f>$B$9+A52</f>
         <v/>
       </c>
@@ -4485,10 +5768,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="31" t="n">
+      <c r="A53" s="32" t="n">
         <v>1.45</v>
       </c>
-      <c r="B53" s="31">
+      <c r="B53" s="32">
         <f>$B$9+A53</f>
         <v/>
       </c>
@@ -4510,10 +5793,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="31" t="n">
+      <c r="A54" s="32" t="n">
         <v>1.5</v>
       </c>
-      <c r="B54" s="31">
+      <c r="B54" s="32">
         <f>$B$9+A54</f>
         <v/>
       </c>
@@ -4535,10 +5818,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="31" t="n">
+      <c r="A55" s="32" t="n">
         <v>1.55</v>
       </c>
-      <c r="B55" s="31">
+      <c r="B55" s="32">
         <f>$B$9+A55</f>
         <v/>
       </c>
@@ -4560,10 +5843,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="31" t="n">
+      <c r="A56" s="32" t="n">
         <v>1.6</v>
       </c>
-      <c r="B56" s="31">
+      <c r="B56" s="32">
         <f>$B$9+A56</f>
         <v/>
       </c>
@@ -4585,10 +5868,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="31" t="n">
+      <c r="A57" s="32" t="n">
         <v>1.65</v>
       </c>
-      <c r="B57" s="31">
+      <c r="B57" s="32">
         <f>$B$9+A57</f>
         <v/>
       </c>
@@ -4610,10 +5893,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="31" t="n">
+      <c r="A58" s="32" t="n">
         <v>1.7</v>
       </c>
-      <c r="B58" s="31">
+      <c r="B58" s="32">
         <f>$B$9+A58</f>
         <v/>
       </c>
@@ -4635,10 +5918,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="31" t="n">
+      <c r="A59" s="32" t="n">
         <v>1.75</v>
       </c>
-      <c r="B59" s="31">
+      <c r="B59" s="32">
         <f>$B$9+A59</f>
         <v/>
       </c>
@@ -4660,10 +5943,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="31" t="n">
+      <c r="A60" s="32" t="n">
         <v>1.8</v>
       </c>
-      <c r="B60" s="31">
+      <c r="B60" s="32">
         <f>$B$9+A60</f>
         <v/>
       </c>
@@ -4685,10 +5968,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="31" t="n">
+      <c r="A61" s="32" t="n">
         <v>1.85</v>
       </c>
-      <c r="B61" s="31">
+      <c r="B61" s="32">
         <f>$B$9+A61</f>
         <v/>
       </c>
@@ -4710,10 +5993,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="31" t="n">
+      <c r="A62" s="32" t="n">
         <v>1.9</v>
       </c>
-      <c r="B62" s="31">
+      <c r="B62" s="32">
         <f>$B$9+A62</f>
         <v/>
       </c>
@@ -4735,10 +6018,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="31" t="n">
+      <c r="A63" s="32" t="n">
         <v>1.95</v>
       </c>
-      <c r="B63" s="31">
+      <c r="B63" s="32">
         <f>$B$9+A63</f>
         <v/>
       </c>
@@ -4760,10 +6043,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="31" t="n">
+      <c r="A64" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="B64" s="31">
+      <c r="B64" s="32">
         <f>$B$9+A64</f>
         <v/>
       </c>
@@ -4785,10 +6068,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="31" t="n">
+      <c r="A65" s="32" t="n">
         <v>2.05</v>
       </c>
-      <c r="B65" s="31">
+      <c r="B65" s="32">
         <f>$B$9+A65</f>
         <v/>
       </c>
@@ -4810,10 +6093,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="31" t="n">
+      <c r="A66" s="32" t="n">
         <v>2.1</v>
       </c>
-      <c r="B66" s="31">
+      <c r="B66" s="32">
         <f>$B$9+A66</f>
         <v/>
       </c>
@@ -4835,10 +6118,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="31" t="n">
+      <c r="A67" s="32" t="n">
         <v>2.15</v>
       </c>
-      <c r="B67" s="31">
+      <c r="B67" s="32">
         <f>$B$9+A67</f>
         <v/>
       </c>
@@ -4860,10 +6143,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="31" t="n">
+      <c r="A68" s="32" t="n">
         <v>2.2</v>
       </c>
-      <c r="B68" s="31">
+      <c r="B68" s="32">
         <f>$B$9+A68</f>
         <v/>
       </c>
@@ -4885,10 +6168,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="31" t="n">
+      <c r="A69" s="32" t="n">
         <v>2.25</v>
       </c>
-      <c r="B69" s="31">
+      <c r="B69" s="32">
         <f>$B$9+A69</f>
         <v/>
       </c>
@@ -4910,10 +6193,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="31" t="n">
+      <c r="A70" s="32" t="n">
         <v>2.3</v>
       </c>
-      <c r="B70" s="31">
+      <c r="B70" s="32">
         <f>$B$9+A70</f>
         <v/>
       </c>
@@ -4935,10 +6218,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="31" t="n">
+      <c r="A71" s="32" t="n">
         <v>2.35</v>
       </c>
-      <c r="B71" s="31">
+      <c r="B71" s="32">
         <f>$B$9+A71</f>
         <v/>
       </c>
@@ -4960,10 +6243,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="38" t="n">
+      <c r="A72" s="39" t="n">
         <v>2.4</v>
       </c>
-      <c r="B72" s="38">
+      <c r="B72" s="39">
         <f>$B$9+A72</f>
         <v/>
       </c>
@@ -4985,10 +6268,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="31" t="n">
+      <c r="A73" s="32" t="n">
         <v>2.45</v>
       </c>
-      <c r="B73" s="31">
+      <c r="B73" s="32">
         <f>$B$9+A73</f>
         <v/>
       </c>
@@ -5010,10 +6293,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="31" t="n">
+      <c r="A74" s="32" t="n">
         <v>2.5</v>
       </c>
-      <c r="B74" s="31">
+      <c r="B74" s="32">
         <f>$B$9+A74</f>
         <v/>
       </c>
@@ -5035,10 +6318,10 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="31" t="n">
+      <c r="A75" s="32" t="n">
         <v>2.55</v>
       </c>
-      <c r="B75" s="31">
+      <c r="B75" s="32">
         <f>$B$9+A75</f>
         <v/>
       </c>
@@ -5060,10 +6343,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="31" t="n">
+      <c r="A76" s="32" t="n">
         <v>2.6</v>
       </c>
-      <c r="B76" s="31">
+      <c r="B76" s="32">
         <f>$B$9+A76</f>
         <v/>
       </c>
@@ -5085,10 +6368,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="31" t="n">
+      <c r="A77" s="32" t="n">
         <v>2.65</v>
       </c>
-      <c r="B77" s="31">
+      <c r="B77" s="32">
         <f>$B$9+A77</f>
         <v/>
       </c>
@@ -5110,10 +6393,10 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="31" t="n">
+      <c r="A78" s="32" t="n">
         <v>2.7</v>
       </c>
-      <c r="B78" s="31">
+      <c r="B78" s="32">
         <f>$B$9+A78</f>
         <v/>
       </c>
@@ -5135,10 +6418,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="31" t="n">
+      <c r="A79" s="32" t="n">
         <v>2.75</v>
       </c>
-      <c r="B79" s="31">
+      <c r="B79" s="32">
         <f>$B$9+A79</f>
         <v/>
       </c>
@@ -5160,10 +6443,10 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="31" t="n">
+      <c r="A80" s="32" t="n">
         <v>2.8</v>
       </c>
-      <c r="B80" s="31">
+      <c r="B80" s="32">
         <f>$B$9+A80</f>
         <v/>
       </c>
@@ -5185,10 +6468,10 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="31" t="n">
+      <c r="A81" s="32" t="n">
         <v>2.85</v>
       </c>
-      <c r="B81" s="31">
+      <c r="B81" s="32">
         <f>$B$9+A81</f>
         <v/>
       </c>
@@ -5210,10 +6493,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="31" t="n">
+      <c r="A82" s="32" t="n">
         <v>2.9</v>
       </c>
-      <c r="B82" s="31">
+      <c r="B82" s="32">
         <f>$B$9+A82</f>
         <v/>
       </c>
@@ -5235,10 +6518,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="31" t="n">
+      <c r="A83" s="32" t="n">
         <v>2.95</v>
       </c>
-      <c r="B83" s="31">
+      <c r="B83" s="32">
         <f>$B$9+A83</f>
         <v/>
       </c>
@@ -5260,10 +6543,10 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="31" t="n">
+      <c r="A84" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="B84" s="31">
+      <c r="B84" s="32">
         <f>$B$9+A84</f>
         <v/>
       </c>
@@ -5312,16 +6595,16 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Méthode B — routage avec Qout = f(H) depuis Courbe_QH_900 (FHWA)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="39" t="inlineStr">
-        <is>
-          <t>H = V / Aire_constante (Parametres!B24) — raccourci, PAS le levé Stage_Storage. Qout interpolé sur Courbe_QH_900!E (Q gouvernant). Si V≈0, Qout = MIN(Qin, Q_plein). ΔV = (Qin_moy - Qout)*Δt. Après routage, WSEmax_B réel est lu sur Stage_Storage via Vmax_B (Parametres B45).</t>
+      <c r="A2" s="40" t="inlineStr">
+        <is>
+          <t>H = V / Aire_constante (Parametres!B24) — raccourci, PAS le levé SS_Amont. Qout interpolé sur Courbe_QH_900!E (Q gouvernant). Si V≈0, Qout = MIN(Qin, Q_plein). ΔV = (Qin_moy - Qout)*Δt. Après routage, WSEmax_B réel est lu sur SS_Amont via Vmax_B (Parametres B45).</t>
         </is>
       </c>
     </row>
@@ -5332,7 +6615,7 @@
           <t>Aire (m²)</t>
         </is>
       </c>
-      <c r="B5" s="40">
+      <c r="B5" s="41">
         <f>Parametres!B24</f>
         <v/>
       </c>
@@ -5343,7 +6626,7 @@
           <t>Q_plein réf. (m³/s)</t>
         </is>
       </c>
-      <c r="B6" s="40">
+      <c r="B6" s="41">
         <f>Parametres!B22</f>
         <v/>
       </c>
@@ -5354,7 +6637,7 @@
           <t>Vmax_B (m³)</t>
         </is>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="31">
         <f>MAX(G12:G24)</f>
         <v/>
       </c>
@@ -5426,10 +6709,10 @@
         <f>MIN(B12,$B$6)</f>
         <v/>
       </c>
-      <c r="F12" s="25" t="n">
+      <c r="F12" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="33" t="n">
+      <c r="G12" s="34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5454,11 +6737,11 @@
         <f>IF(G12&lt;=0.01,MIN(0.5*(B12+B13),$B$6),D13)</f>
         <v/>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="26">
         <f>(A13-A12)*60</f>
         <v/>
       </c>
-      <c r="G13" s="33">
+      <c r="G13" s="34">
         <f>MAX(0,G12+(0.5*(B12+B13)-E13)*F13)</f>
         <v/>
       </c>
@@ -5484,11 +6767,11 @@
         <f>IF(G13&lt;=0.01,MIN(0.5*(B13+B14),$B$6),D14)</f>
         <v/>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="26">
         <f>(A14-A13)*60</f>
         <v/>
       </c>
-      <c r="G14" s="33">
+      <c r="G14" s="34">
         <f>MAX(0,G13+(0.5*(B13+B14)-E14)*F14)</f>
         <v/>
       </c>
@@ -5514,11 +6797,11 @@
         <f>IF(G14&lt;=0.01,MIN(0.5*(B14+B15),$B$6),D15)</f>
         <v/>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="26">
         <f>(A15-A14)*60</f>
         <v/>
       </c>
-      <c r="G15" s="33">
+      <c r="G15" s="34">
         <f>MAX(0,G14+(0.5*(B14+B15)-E15)*F15)</f>
         <v/>
       </c>
@@ -5544,11 +6827,11 @@
         <f>IF(G15&lt;=0.01,MIN(0.5*(B15+B16),$B$6),D16)</f>
         <v/>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="26">
         <f>(A16-A15)*60</f>
         <v/>
       </c>
-      <c r="G16" s="33">
+      <c r="G16" s="34">
         <f>MAX(0,G15+(0.5*(B15+B16)-E16)*F16)</f>
         <v/>
       </c>
@@ -5574,11 +6857,11 @@
         <f>IF(G16&lt;=0.01,MIN(0.5*(B16+B17),$B$6),D17)</f>
         <v/>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="26">
         <f>(A17-A16)*60</f>
         <v/>
       </c>
-      <c r="G17" s="33">
+      <c r="G17" s="34">
         <f>MAX(0,G16+(0.5*(B16+B17)-E17)*F17)</f>
         <v/>
       </c>
@@ -5604,11 +6887,11 @@
         <f>IF(G17&lt;=0.01,MIN(0.5*(B17+B18),$B$6),D18)</f>
         <v/>
       </c>
-      <c r="F18" s="25">
+      <c r="F18" s="26">
         <f>(A18-A17)*60</f>
         <v/>
       </c>
-      <c r="G18" s="33">
+      <c r="G18" s="34">
         <f>MAX(0,G17+(0.5*(B17+B18)-E18)*F18)</f>
         <v/>
       </c>
@@ -5634,11 +6917,11 @@
         <f>IF(G18&lt;=0.01,MIN(0.5*(B18+B19),$B$6),D19)</f>
         <v/>
       </c>
-      <c r="F19" s="25">
+      <c r="F19" s="26">
         <f>(A19-A18)*60</f>
         <v/>
       </c>
-      <c r="G19" s="33">
+      <c r="G19" s="34">
         <f>MAX(0,G18+(0.5*(B18+B19)-E19)*F19)</f>
         <v/>
       </c>
@@ -5664,11 +6947,11 @@
         <f>IF(G19&lt;=0.01,MIN(0.5*(B19+B20),$B$6),D20)</f>
         <v/>
       </c>
-      <c r="F20" s="25">
+      <c r="F20" s="26">
         <f>(A20-A19)*60</f>
         <v/>
       </c>
-      <c r="G20" s="33">
+      <c r="G20" s="34">
         <f>MAX(0,G19+(0.5*(B19+B20)-E20)*F20)</f>
         <v/>
       </c>
@@ -5694,11 +6977,11 @@
         <f>IF(G20&lt;=0.01,MIN(0.5*(B20+B21),$B$6),D21)</f>
         <v/>
       </c>
-      <c r="F21" s="25">
+      <c r="F21" s="26">
         <f>(A21-A20)*60</f>
         <v/>
       </c>
-      <c r="G21" s="33">
+      <c r="G21" s="34">
         <f>MAX(0,G20+(0.5*(B20+B21)-E21)*F21)</f>
         <v/>
       </c>
@@ -5724,11 +7007,11 @@
         <f>IF(G21&lt;=0.01,MIN(0.5*(B21+B22),$B$6),D22)</f>
         <v/>
       </c>
-      <c r="F22" s="25">
+      <c r="F22" s="26">
         <f>(A22-A21)*60</f>
         <v/>
       </c>
-      <c r="G22" s="33">
+      <c r="G22" s="34">
         <f>MAX(0,G21+(0.5*(B21+B22)-E22)*F22)</f>
         <v/>
       </c>
@@ -5754,11 +7037,11 @@
         <f>IF(G22&lt;=0.01,MIN(0.5*(B22+B23),$B$6),D23)</f>
         <v/>
       </c>
-      <c r="F23" s="25">
+      <c r="F23" s="26">
         <f>(A23-A22)*60</f>
         <v/>
       </c>
-      <c r="G23" s="33">
+      <c r="G23" s="34">
         <f>MAX(0,G22+(0.5*(B22+B23)-E23)*F23)</f>
         <v/>
       </c>
@@ -5784,11 +7067,11 @@
         <f>IF(G23&lt;=0.01,MIN(0.5*(B23+B24),$B$6),D24)</f>
         <v/>
       </c>
-      <c r="F24" s="25">
+      <c r="F24" s="26">
         <f>(A24-A23)*60</f>
         <v/>
       </c>
-      <c r="G24" s="33">
+      <c r="G24" s="34">
         <f>MAX(0,G23+(0.5*(B23+B24)-E24)*F24)</f>
         <v/>
       </c>
@@ -5824,7 +7107,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Méthode C — courbe composée Ø900 + fossé trapèze (crest = crown)</t>
         </is>
@@ -5833,7 +7116,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Qout = Q_900(WSE) + Q_overflow(WSE). V_total = V_pond(Stage_Storage) + V_ditch. Overflow: trapèze au-dessus du crown, Manning. Paramètres jaunes = Parametres!B27–B32.</t>
+          <t>Qout = Q_900(WSE) + Q_overflow(WSE). V_total = V_pond(SS_Amont) + V_ditch. Overflow: trapèze au-dessus du crown, Manning. Paramètres jaunes = Parametres!B27–B32.</t>
         </is>
       </c>
     </row>
@@ -5980,14 +7263,14 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="31" t="n">
+      <c r="A15" s="32" t="n">
         <v>34.88</v>
       </c>
-      <c r="B15" s="31">
+      <c r="B15" s="32">
         <f>A15-$B$12</f>
         <v/>
       </c>
-      <c r="C15" s="31">
+      <c r="C15" s="32">
         <f>MAX(0,A15-$B$6)</f>
         <v/>
       </c>
@@ -5995,15 +7278,15 @@
         <f>IF(C15&lt;=0,0,($B$7+$B$9*C15)*C15)</f>
         <v/>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="26">
         <f>D15*$B$11</f>
         <v/>
       </c>
-      <c r="F15" s="25">
-        <f>IF(A15&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A15&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A15,Stage_Storage!$A$11:$A$18,1))+(A15-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A15,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A15,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A15,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A15,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A15,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G15" s="33">
+      <c r="F15" s="26">
+        <f>IF(A15&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A15&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A15,SS_Amont!$A$11:$A$18,1))+(A15-INDEX(SS_Amont!$A$11:$A$18,MATCH(A15,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A15,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A15,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A15,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A15,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G15" s="34">
         <f>E15+F15</f>
         <v/>
       </c>
@@ -6025,14 +7308,14 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="31" t="n">
+      <c r="A16" s="32" t="n">
         <v>34.93</v>
       </c>
-      <c r="B16" s="31">
+      <c r="B16" s="32">
         <f>A16-$B$12</f>
         <v/>
       </c>
-      <c r="C16" s="31">
+      <c r="C16" s="32">
         <f>MAX(0,A16-$B$6)</f>
         <v/>
       </c>
@@ -6040,15 +7323,15 @@
         <f>IF(C16&lt;=0,0,($B$7+$B$9*C16)*C16)</f>
         <v/>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="26">
         <f>D16*$B$11</f>
         <v/>
       </c>
-      <c r="F16" s="25">
-        <f>IF(A16&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A16&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A16,Stage_Storage!$A$11:$A$18,1))+(A16-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A16,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A16,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A16,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A16,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A16,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G16" s="33">
+      <c r="F16" s="26">
+        <f>IF(A16&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A16&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A16,SS_Amont!$A$11:$A$18,1))+(A16-INDEX(SS_Amont!$A$11:$A$18,MATCH(A16,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A16,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A16,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A16,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A16,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G16" s="34">
         <f>E16+F16</f>
         <v/>
       </c>
@@ -6070,14 +7353,14 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="31" t="n">
+      <c r="A17" s="32" t="n">
         <v>34.98</v>
       </c>
-      <c r="B17" s="31">
+      <c r="B17" s="32">
         <f>A17-$B$12</f>
         <v/>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="32">
         <f>MAX(0,A17-$B$6)</f>
         <v/>
       </c>
@@ -6085,15 +7368,15 @@
         <f>IF(C17&lt;=0,0,($B$7+$B$9*C17)*C17)</f>
         <v/>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="26">
         <f>D17*$B$11</f>
         <v/>
       </c>
-      <c r="F17" s="25">
-        <f>IF(A17&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A17&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A17,Stage_Storage!$A$11:$A$18,1))+(A17-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A17,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A17,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A17,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A17,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A17,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G17" s="33">
+      <c r="F17" s="26">
+        <f>IF(A17&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A17&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A17,SS_Amont!$A$11:$A$18,1))+(A17-INDEX(SS_Amont!$A$11:$A$18,MATCH(A17,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A17,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A17,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A17,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A17,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G17" s="34">
         <f>E17+F17</f>
         <v/>
       </c>
@@ -6115,14 +7398,14 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="31" t="n">
+      <c r="A18" s="32" t="n">
         <v>35.03</v>
       </c>
-      <c r="B18" s="31">
+      <c r="B18" s="32">
         <f>A18-$B$12</f>
         <v/>
       </c>
-      <c r="C18" s="31">
+      <c r="C18" s="32">
         <f>MAX(0,A18-$B$6)</f>
         <v/>
       </c>
@@ -6130,15 +7413,15 @@
         <f>IF(C18&lt;=0,0,($B$7+$B$9*C18)*C18)</f>
         <v/>
       </c>
-      <c r="E18" s="25">
+      <c r="E18" s="26">
         <f>D18*$B$11</f>
         <v/>
       </c>
-      <c r="F18" s="25">
-        <f>IF(A18&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A18&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A18,Stage_Storage!$A$11:$A$18,1))+(A18-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A18,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A18,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A18,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A18,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A18,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G18" s="33">
+      <c r="F18" s="26">
+        <f>IF(A18&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A18&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A18,SS_Amont!$A$11:$A$18,1))+(A18-INDEX(SS_Amont!$A$11:$A$18,MATCH(A18,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A18,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A18,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A18,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A18,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G18" s="34">
         <f>E18+F18</f>
         <v/>
       </c>
@@ -6160,14 +7443,14 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="31" t="n">
+      <c r="A19" s="32" t="n">
         <v>35.08</v>
       </c>
-      <c r="B19" s="31">
+      <c r="B19" s="32">
         <f>A19-$B$12</f>
         <v/>
       </c>
-      <c r="C19" s="31">
+      <c r="C19" s="32">
         <f>MAX(0,A19-$B$6)</f>
         <v/>
       </c>
@@ -6175,15 +7458,15 @@
         <f>IF(C19&lt;=0,0,($B$7+$B$9*C19)*C19)</f>
         <v/>
       </c>
-      <c r="E19" s="25">
+      <c r="E19" s="26">
         <f>D19*$B$11</f>
         <v/>
       </c>
-      <c r="F19" s="25">
-        <f>IF(A19&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A19&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A19,Stage_Storage!$A$11:$A$18,1))+(A19-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A19,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A19,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A19,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A19,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A19,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G19" s="33">
+      <c r="F19" s="26">
+        <f>IF(A19&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A19&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A19,SS_Amont!$A$11:$A$18,1))+(A19-INDEX(SS_Amont!$A$11:$A$18,MATCH(A19,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A19,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A19,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A19,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A19,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G19" s="34">
         <f>E19+F19</f>
         <v/>
       </c>
@@ -6205,14 +7488,14 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="31" t="n">
+      <c r="A20" s="32" t="n">
         <v>35.13</v>
       </c>
-      <c r="B20" s="31">
+      <c r="B20" s="32">
         <f>A20-$B$12</f>
         <v/>
       </c>
-      <c r="C20" s="31">
+      <c r="C20" s="32">
         <f>MAX(0,A20-$B$6)</f>
         <v/>
       </c>
@@ -6220,15 +7503,15 @@
         <f>IF(C20&lt;=0,0,($B$7+$B$9*C20)*C20)</f>
         <v/>
       </c>
-      <c r="E20" s="25">
+      <c r="E20" s="26">
         <f>D20*$B$11</f>
         <v/>
       </c>
-      <c r="F20" s="25">
-        <f>IF(A20&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A20&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A20,Stage_Storage!$A$11:$A$18,1))+(A20-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A20,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A20,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A20,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A20,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A20,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G20" s="33">
+      <c r="F20" s="26">
+        <f>IF(A20&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A20&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A20,SS_Amont!$A$11:$A$18,1))+(A20-INDEX(SS_Amont!$A$11:$A$18,MATCH(A20,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A20,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A20,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A20,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A20,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G20" s="34">
         <f>E20+F20</f>
         <v/>
       </c>
@@ -6250,14 +7533,14 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="31" t="n">
+      <c r="A21" s="32" t="n">
         <v>35.18</v>
       </c>
-      <c r="B21" s="31">
+      <c r="B21" s="32">
         <f>A21-$B$12</f>
         <v/>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="32">
         <f>MAX(0,A21-$B$6)</f>
         <v/>
       </c>
@@ -6265,15 +7548,15 @@
         <f>IF(C21&lt;=0,0,($B$7+$B$9*C21)*C21)</f>
         <v/>
       </c>
-      <c r="E21" s="25">
+      <c r="E21" s="26">
         <f>D21*$B$11</f>
         <v/>
       </c>
-      <c r="F21" s="25">
-        <f>IF(A21&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A21&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A21,Stage_Storage!$A$11:$A$18,1))+(A21-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A21,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A21,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A21,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A21,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A21,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G21" s="33">
+      <c r="F21" s="26">
+        <f>IF(A21&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A21&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A21,SS_Amont!$A$11:$A$18,1))+(A21-INDEX(SS_Amont!$A$11:$A$18,MATCH(A21,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A21,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A21,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A21,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A21,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G21" s="34">
         <f>E21+F21</f>
         <v/>
       </c>
@@ -6295,14 +7578,14 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="31" t="n">
+      <c r="A22" s="32" t="n">
         <v>35.23</v>
       </c>
-      <c r="B22" s="31">
+      <c r="B22" s="32">
         <f>A22-$B$12</f>
         <v/>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="32">
         <f>MAX(0,A22-$B$6)</f>
         <v/>
       </c>
@@ -6310,15 +7593,15 @@
         <f>IF(C22&lt;=0,0,($B$7+$B$9*C22)*C22)</f>
         <v/>
       </c>
-      <c r="E22" s="25">
+      <c r="E22" s="26">
         <f>D22*$B$11</f>
         <v/>
       </c>
-      <c r="F22" s="25">
-        <f>IF(A22&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A22&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A22,Stage_Storage!$A$11:$A$18,1))+(A22-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A22,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A22,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A22,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A22,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A22,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G22" s="33">
+      <c r="F22" s="26">
+        <f>IF(A22&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A22&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A22,SS_Amont!$A$11:$A$18,1))+(A22-INDEX(SS_Amont!$A$11:$A$18,MATCH(A22,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A22,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A22,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A22,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A22,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G22" s="34">
         <f>E22+F22</f>
         <v/>
       </c>
@@ -6340,14 +7623,14 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="31" t="n">
+      <c r="A23" s="32" t="n">
         <v>35.28</v>
       </c>
-      <c r="B23" s="31">
+      <c r="B23" s="32">
         <f>A23-$B$12</f>
         <v/>
       </c>
-      <c r="C23" s="31">
+      <c r="C23" s="32">
         <f>MAX(0,A23-$B$6)</f>
         <v/>
       </c>
@@ -6355,15 +7638,15 @@
         <f>IF(C23&lt;=0,0,($B$7+$B$9*C23)*C23)</f>
         <v/>
       </c>
-      <c r="E23" s="25">
+      <c r="E23" s="26">
         <f>D23*$B$11</f>
         <v/>
       </c>
-      <c r="F23" s="25">
-        <f>IF(A23&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A23&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A23,Stage_Storage!$A$11:$A$18,1))+(A23-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A23,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A23,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A23,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A23,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A23,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G23" s="33">
+      <c r="F23" s="26">
+        <f>IF(A23&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A23&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A23,SS_Amont!$A$11:$A$18,1))+(A23-INDEX(SS_Amont!$A$11:$A$18,MATCH(A23,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A23,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A23,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A23,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A23,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G23" s="34">
         <f>E23+F23</f>
         <v/>
       </c>
@@ -6385,14 +7668,14 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="31" t="n">
+      <c r="A24" s="32" t="n">
         <v>35.33</v>
       </c>
-      <c r="B24" s="31">
+      <c r="B24" s="32">
         <f>A24-$B$12</f>
         <v/>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="32">
         <f>MAX(0,A24-$B$6)</f>
         <v/>
       </c>
@@ -6400,15 +7683,15 @@
         <f>IF(C24&lt;=0,0,($B$7+$B$9*C24)*C24)</f>
         <v/>
       </c>
-      <c r="E24" s="25">
+      <c r="E24" s="26">
         <f>D24*$B$11</f>
         <v/>
       </c>
-      <c r="F24" s="25">
-        <f>IF(A24&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A24&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A24,Stage_Storage!$A$11:$A$18,1))+(A24-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A24,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A24,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A24,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A24,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A24,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G24" s="33">
+      <c r="F24" s="26">
+        <f>IF(A24&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A24&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A24,SS_Amont!$A$11:$A$18,1))+(A24-INDEX(SS_Amont!$A$11:$A$18,MATCH(A24,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A24,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A24,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A24,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A24,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G24" s="34">
         <f>E24+F24</f>
         <v/>
       </c>
@@ -6430,14 +7713,14 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="31" t="n">
+      <c r="A25" s="32" t="n">
         <v>35.38</v>
       </c>
-      <c r="B25" s="31">
+      <c r="B25" s="32">
         <f>A25-$B$12</f>
         <v/>
       </c>
-      <c r="C25" s="31">
+      <c r="C25" s="32">
         <f>MAX(0,A25-$B$6)</f>
         <v/>
       </c>
@@ -6445,15 +7728,15 @@
         <f>IF(C25&lt;=0,0,($B$7+$B$9*C25)*C25)</f>
         <v/>
       </c>
-      <c r="E25" s="25">
+      <c r="E25" s="26">
         <f>D25*$B$11</f>
         <v/>
       </c>
-      <c r="F25" s="25">
-        <f>IF(A25&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A25&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A25,Stage_Storage!$A$11:$A$18,1))+(A25-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A25,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A25,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A25,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A25,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A25,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G25" s="33">
+      <c r="F25" s="26">
+        <f>IF(A25&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A25&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A25,SS_Amont!$A$11:$A$18,1))+(A25-INDEX(SS_Amont!$A$11:$A$18,MATCH(A25,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A25,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A25,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A25,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A25,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G25" s="34">
         <f>E25+F25</f>
         <v/>
       </c>
@@ -6475,14 +7758,14 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="31" t="n">
+      <c r="A26" s="32" t="n">
         <v>35.43</v>
       </c>
-      <c r="B26" s="31">
+      <c r="B26" s="32">
         <f>A26-$B$12</f>
         <v/>
       </c>
-      <c r="C26" s="31">
+      <c r="C26" s="32">
         <f>MAX(0,A26-$B$6)</f>
         <v/>
       </c>
@@ -6490,15 +7773,15 @@
         <f>IF(C26&lt;=0,0,($B$7+$B$9*C26)*C26)</f>
         <v/>
       </c>
-      <c r="E26" s="25">
+      <c r="E26" s="26">
         <f>D26*$B$11</f>
         <v/>
       </c>
-      <c r="F26" s="25">
-        <f>IF(A26&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A26&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A26,Stage_Storage!$A$11:$A$18,1))+(A26-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A26,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A26,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A26,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A26,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A26,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G26" s="33">
+      <c r="F26" s="26">
+        <f>IF(A26&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A26&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A26,SS_Amont!$A$11:$A$18,1))+(A26-INDEX(SS_Amont!$A$11:$A$18,MATCH(A26,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A26,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A26,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A26,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A26,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G26" s="34">
         <f>E26+F26</f>
         <v/>
       </c>
@@ -6520,14 +7803,14 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="31" t="n">
+      <c r="A27" s="32" t="n">
         <v>35.48</v>
       </c>
-      <c r="B27" s="31">
+      <c r="B27" s="32">
         <f>A27-$B$12</f>
         <v/>
       </c>
-      <c r="C27" s="31">
+      <c r="C27" s="32">
         <f>MAX(0,A27-$B$6)</f>
         <v/>
       </c>
@@ -6535,15 +7818,15 @@
         <f>IF(C27&lt;=0,0,($B$7+$B$9*C27)*C27)</f>
         <v/>
       </c>
-      <c r="E27" s="25">
+      <c r="E27" s="26">
         <f>D27*$B$11</f>
         <v/>
       </c>
-      <c r="F27" s="25">
-        <f>IF(A27&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A27&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A27,Stage_Storage!$A$11:$A$18,1))+(A27-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A27,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A27,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A27,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A27,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A27,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G27" s="33">
+      <c r="F27" s="26">
+        <f>IF(A27&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A27&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A27,SS_Amont!$A$11:$A$18,1))+(A27-INDEX(SS_Amont!$A$11:$A$18,MATCH(A27,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A27,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A27,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A27,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A27,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G27" s="34">
         <f>E27+F27</f>
         <v/>
       </c>
@@ -6565,14 +7848,14 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="31" t="n">
+      <c r="A28" s="32" t="n">
         <v>35.53</v>
       </c>
-      <c r="B28" s="31">
+      <c r="B28" s="32">
         <f>A28-$B$12</f>
         <v/>
       </c>
-      <c r="C28" s="31">
+      <c r="C28" s="32">
         <f>MAX(0,A28-$B$6)</f>
         <v/>
       </c>
@@ -6580,15 +7863,15 @@
         <f>IF(C28&lt;=0,0,($B$7+$B$9*C28)*C28)</f>
         <v/>
       </c>
-      <c r="E28" s="25">
+      <c r="E28" s="26">
         <f>D28*$B$11</f>
         <v/>
       </c>
-      <c r="F28" s="25">
-        <f>IF(A28&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A28&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A28,Stage_Storage!$A$11:$A$18,1))+(A28-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A28,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A28,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A28,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A28,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A28,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G28" s="33">
+      <c r="F28" s="26">
+        <f>IF(A28&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A28&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A28,SS_Amont!$A$11:$A$18,1))+(A28-INDEX(SS_Amont!$A$11:$A$18,MATCH(A28,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A28,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A28,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A28,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A28,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G28" s="34">
         <f>E28+F28</f>
         <v/>
       </c>
@@ -6610,14 +7893,14 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="31" t="n">
+      <c r="A29" s="32" t="n">
         <v>35.58</v>
       </c>
-      <c r="B29" s="31">
+      <c r="B29" s="32">
         <f>A29-$B$12</f>
         <v/>
       </c>
-      <c r="C29" s="31">
+      <c r="C29" s="32">
         <f>MAX(0,A29-$B$6)</f>
         <v/>
       </c>
@@ -6625,15 +7908,15 @@
         <f>IF(C29&lt;=0,0,($B$7+$B$9*C29)*C29)</f>
         <v/>
       </c>
-      <c r="E29" s="25">
+      <c r="E29" s="26">
         <f>D29*$B$11</f>
         <v/>
       </c>
-      <c r="F29" s="25">
-        <f>IF(A29&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A29&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A29,Stage_Storage!$A$11:$A$18,1))+(A29-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A29,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A29,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A29,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A29,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A29,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G29" s="33">
+      <c r="F29" s="26">
+        <f>IF(A29&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A29&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A29,SS_Amont!$A$11:$A$18,1))+(A29-INDEX(SS_Amont!$A$11:$A$18,MATCH(A29,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A29,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A29,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A29,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A29,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G29" s="34">
         <f>E29+F29</f>
         <v/>
       </c>
@@ -6655,14 +7938,14 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="31" t="n">
+      <c r="A30" s="32" t="n">
         <v>35.63</v>
       </c>
-      <c r="B30" s="31">
+      <c r="B30" s="32">
         <f>A30-$B$12</f>
         <v/>
       </c>
-      <c r="C30" s="31">
+      <c r="C30" s="32">
         <f>MAX(0,A30-$B$6)</f>
         <v/>
       </c>
@@ -6670,15 +7953,15 @@
         <f>IF(C30&lt;=0,0,($B$7+$B$9*C30)*C30)</f>
         <v/>
       </c>
-      <c r="E30" s="25">
+      <c r="E30" s="26">
         <f>D30*$B$11</f>
         <v/>
       </c>
-      <c r="F30" s="25">
-        <f>IF(A30&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A30&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A30,Stage_Storage!$A$11:$A$18,1))+(A30-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A30,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A30,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A30,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A30,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A30,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G30" s="33">
+      <c r="F30" s="26">
+        <f>IF(A30&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A30&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A30,SS_Amont!$A$11:$A$18,1))+(A30-INDEX(SS_Amont!$A$11:$A$18,MATCH(A30,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A30,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A30,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A30,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A30,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G30" s="34">
         <f>E30+F30</f>
         <v/>
       </c>
@@ -6700,14 +7983,14 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="31" t="n">
+      <c r="A31" s="32" t="n">
         <v>35.68</v>
       </c>
-      <c r="B31" s="31">
+      <c r="B31" s="32">
         <f>A31-$B$12</f>
         <v/>
       </c>
-      <c r="C31" s="31">
+      <c r="C31" s="32">
         <f>MAX(0,A31-$B$6)</f>
         <v/>
       </c>
@@ -6715,15 +7998,15 @@
         <f>IF(C31&lt;=0,0,($B$7+$B$9*C31)*C31)</f>
         <v/>
       </c>
-      <c r="E31" s="25">
+      <c r="E31" s="26">
         <f>D31*$B$11</f>
         <v/>
       </c>
-      <c r="F31" s="25">
-        <f>IF(A31&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A31&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A31,Stage_Storage!$A$11:$A$18,1))+(A31-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A31,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A31,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A31,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A31,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A31,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G31" s="33">
+      <c r="F31" s="26">
+        <f>IF(A31&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A31&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A31,SS_Amont!$A$11:$A$18,1))+(A31-INDEX(SS_Amont!$A$11:$A$18,MATCH(A31,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A31,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A31,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A31,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A31,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G31" s="34">
         <f>E31+F31</f>
         <v/>
       </c>
@@ -6745,14 +8028,14 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="31" t="n">
+      <c r="A32" s="32" t="n">
         <v>35.73</v>
       </c>
-      <c r="B32" s="31">
+      <c r="B32" s="32">
         <f>A32-$B$12</f>
         <v/>
       </c>
-      <c r="C32" s="31">
+      <c r="C32" s="32">
         <f>MAX(0,A32-$B$6)</f>
         <v/>
       </c>
@@ -6760,15 +8043,15 @@
         <f>IF(C32&lt;=0,0,($B$7+$B$9*C32)*C32)</f>
         <v/>
       </c>
-      <c r="E32" s="25">
+      <c r="E32" s="26">
         <f>D32*$B$11</f>
         <v/>
       </c>
-      <c r="F32" s="25">
-        <f>IF(A32&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A32&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A32,Stage_Storage!$A$11:$A$18,1))+(A32-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A32,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A32,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A32,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A32,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A32,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G32" s="33">
+      <c r="F32" s="26">
+        <f>IF(A32&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A32&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A32,SS_Amont!$A$11:$A$18,1))+(A32-INDEX(SS_Amont!$A$11:$A$18,MATCH(A32,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A32,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A32,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A32,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A32,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G32" s="34">
         <f>E32+F32</f>
         <v/>
       </c>
@@ -6790,14 +8073,14 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="38" t="n">
+      <c r="A33" s="39" t="n">
         <v>35.78</v>
       </c>
-      <c r="B33" s="38">
+      <c r="B33" s="39">
         <f>A33-$B$12</f>
         <v/>
       </c>
-      <c r="C33" s="38">
+      <c r="C33" s="39">
         <f>MAX(0,A33-$B$6)</f>
         <v/>
       </c>
@@ -6805,15 +8088,15 @@
         <f>IF(C33&lt;=0,0,($B$7+$B$9*C33)*C33)</f>
         <v/>
       </c>
-      <c r="E33" s="41">
+      <c r="E33" s="42">
         <f>D33*$B$11</f>
         <v/>
       </c>
-      <c r="F33" s="41">
-        <f>IF(A33&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A33&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A33,Stage_Storage!$A$11:$A$18,1))+(A33-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A33,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A33,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A33,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A33,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A33,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G33" s="33">
+      <c r="F33" s="42">
+        <f>IF(A33&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A33&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A33,SS_Amont!$A$11:$A$18,1))+(A33-INDEX(SS_Amont!$A$11:$A$18,MATCH(A33,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A33,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A33,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A33,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A33,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G33" s="34">
         <f>E33+F33</f>
         <v/>
       </c>
@@ -6835,14 +8118,14 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="31" t="n">
+      <c r="A34" s="32" t="n">
         <v>35.83</v>
       </c>
-      <c r="B34" s="31">
+      <c r="B34" s="32">
         <f>A34-$B$12</f>
         <v/>
       </c>
-      <c r="C34" s="31">
+      <c r="C34" s="32">
         <f>MAX(0,A34-$B$6)</f>
         <v/>
       </c>
@@ -6850,15 +8133,15 @@
         <f>IF(C34&lt;=0,0,($B$7+$B$9*C34)*C34)</f>
         <v/>
       </c>
-      <c r="E34" s="25">
+      <c r="E34" s="26">
         <f>D34*$B$11</f>
         <v/>
       </c>
-      <c r="F34" s="25">
-        <f>IF(A34&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A34&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A34,Stage_Storage!$A$11:$A$18,1))+(A34-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A34,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A34,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A34,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A34,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A34,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G34" s="33">
+      <c r="F34" s="26">
+        <f>IF(A34&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A34&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A34,SS_Amont!$A$11:$A$18,1))+(A34-INDEX(SS_Amont!$A$11:$A$18,MATCH(A34,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A34,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A34,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A34,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A34,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G34" s="34">
         <f>E34+F34</f>
         <v/>
       </c>
@@ -6880,14 +8163,14 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="31" t="n">
+      <c r="A35" s="32" t="n">
         <v>35.88</v>
       </c>
-      <c r="B35" s="31">
+      <c r="B35" s="32">
         <f>A35-$B$12</f>
         <v/>
       </c>
-      <c r="C35" s="31">
+      <c r="C35" s="32">
         <f>MAX(0,A35-$B$6)</f>
         <v/>
       </c>
@@ -6895,15 +8178,15 @@
         <f>IF(C35&lt;=0,0,($B$7+$B$9*C35)*C35)</f>
         <v/>
       </c>
-      <c r="E35" s="25">
+      <c r="E35" s="26">
         <f>D35*$B$11</f>
         <v/>
       </c>
-      <c r="F35" s="25">
-        <f>IF(A35&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A35&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A35,Stage_Storage!$A$11:$A$18,1))+(A35-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A35,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A35,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A35,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A35,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A35,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G35" s="33">
+      <c r="F35" s="26">
+        <f>IF(A35&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A35&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A35,SS_Amont!$A$11:$A$18,1))+(A35-INDEX(SS_Amont!$A$11:$A$18,MATCH(A35,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A35,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A35,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A35,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A35,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G35" s="34">
         <f>E35+F35</f>
         <v/>
       </c>
@@ -6925,14 +8208,14 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="31" t="n">
+      <c r="A36" s="32" t="n">
         <v>35.93</v>
       </c>
-      <c r="B36" s="31">
+      <c r="B36" s="32">
         <f>A36-$B$12</f>
         <v/>
       </c>
-      <c r="C36" s="31">
+      <c r="C36" s="32">
         <f>MAX(0,A36-$B$6)</f>
         <v/>
       </c>
@@ -6940,15 +8223,15 @@
         <f>IF(C36&lt;=0,0,($B$7+$B$9*C36)*C36)</f>
         <v/>
       </c>
-      <c r="E36" s="25">
+      <c r="E36" s="26">
         <f>D36*$B$11</f>
         <v/>
       </c>
-      <c r="F36" s="25">
-        <f>IF(A36&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A36&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A36,Stage_Storage!$A$11:$A$18,1))+(A36-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A36,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A36,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A36,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A36,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A36,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G36" s="33">
+      <c r="F36" s="26">
+        <f>IF(A36&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A36&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A36,SS_Amont!$A$11:$A$18,1))+(A36-INDEX(SS_Amont!$A$11:$A$18,MATCH(A36,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A36,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A36,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A36,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A36,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G36" s="34">
         <f>E36+F36</f>
         <v/>
       </c>
@@ -6970,14 +8253,14 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="31" t="n">
+      <c r="A37" s="32" t="n">
         <v>35.98</v>
       </c>
-      <c r="B37" s="31">
+      <c r="B37" s="32">
         <f>A37-$B$12</f>
         <v/>
       </c>
-      <c r="C37" s="31">
+      <c r="C37" s="32">
         <f>MAX(0,A37-$B$6)</f>
         <v/>
       </c>
@@ -6985,15 +8268,15 @@
         <f>IF(C37&lt;=0,0,($B$7+$B$9*C37)*C37)</f>
         <v/>
       </c>
-      <c r="E37" s="25">
+      <c r="E37" s="26">
         <f>D37*$B$11</f>
         <v/>
       </c>
-      <c r="F37" s="25">
-        <f>IF(A37&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A37&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A37,Stage_Storage!$A$11:$A$18,1))+(A37-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A37,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A37,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A37,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A37,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A37,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G37" s="33">
+      <c r="F37" s="26">
+        <f>IF(A37&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A37&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A37,SS_Amont!$A$11:$A$18,1))+(A37-INDEX(SS_Amont!$A$11:$A$18,MATCH(A37,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A37,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A37,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A37,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A37,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G37" s="34">
         <f>E37+F37</f>
         <v/>
       </c>
@@ -7015,14 +8298,14 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="31" t="n">
+      <c r="A38" s="32" t="n">
         <v>36.03</v>
       </c>
-      <c r="B38" s="31">
+      <c r="B38" s="32">
         <f>A38-$B$12</f>
         <v/>
       </c>
-      <c r="C38" s="31">
+      <c r="C38" s="32">
         <f>MAX(0,A38-$B$6)</f>
         <v/>
       </c>
@@ -7030,15 +8313,15 @@
         <f>IF(C38&lt;=0,0,($B$7+$B$9*C38)*C38)</f>
         <v/>
       </c>
-      <c r="E38" s="25">
+      <c r="E38" s="26">
         <f>D38*$B$11</f>
         <v/>
       </c>
-      <c r="F38" s="25">
-        <f>IF(A38&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A38&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A38,Stage_Storage!$A$11:$A$18,1))+(A38-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A38,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A38,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A38,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A38,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A38,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G38" s="33">
+      <c r="F38" s="26">
+        <f>IF(A38&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A38&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A38,SS_Amont!$A$11:$A$18,1))+(A38-INDEX(SS_Amont!$A$11:$A$18,MATCH(A38,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A38,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A38,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A38,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A38,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G38" s="34">
         <f>E38+F38</f>
         <v/>
       </c>
@@ -7060,14 +8343,14 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="31" t="n">
+      <c r="A39" s="32" t="n">
         <v>36.08</v>
       </c>
-      <c r="B39" s="31">
+      <c r="B39" s="32">
         <f>A39-$B$12</f>
         <v/>
       </c>
-      <c r="C39" s="31">
+      <c r="C39" s="32">
         <f>MAX(0,A39-$B$6)</f>
         <v/>
       </c>
@@ -7075,15 +8358,15 @@
         <f>IF(C39&lt;=0,0,($B$7+$B$9*C39)*C39)</f>
         <v/>
       </c>
-      <c r="E39" s="25">
+      <c r="E39" s="26">
         <f>D39*$B$11</f>
         <v/>
       </c>
-      <c r="F39" s="25">
-        <f>IF(A39&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A39&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A39,Stage_Storage!$A$11:$A$18,1))+(A39-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A39,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A39,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A39,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A39,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A39,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G39" s="33">
+      <c r="F39" s="26">
+        <f>IF(A39&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A39&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A39,SS_Amont!$A$11:$A$18,1))+(A39-INDEX(SS_Amont!$A$11:$A$18,MATCH(A39,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A39,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A39,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A39,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A39,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G39" s="34">
         <f>E39+F39</f>
         <v/>
       </c>
@@ -7105,14 +8388,14 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="31" t="n">
+      <c r="A40" s="32" t="n">
         <v>36.13</v>
       </c>
-      <c r="B40" s="31">
+      <c r="B40" s="32">
         <f>A40-$B$12</f>
         <v/>
       </c>
-      <c r="C40" s="31">
+      <c r="C40" s="32">
         <f>MAX(0,A40-$B$6)</f>
         <v/>
       </c>
@@ -7120,15 +8403,15 @@
         <f>IF(C40&lt;=0,0,($B$7+$B$9*C40)*C40)</f>
         <v/>
       </c>
-      <c r="E40" s="25">
+      <c r="E40" s="26">
         <f>D40*$B$11</f>
         <v/>
       </c>
-      <c r="F40" s="25">
-        <f>IF(A40&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A40&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A40,Stage_Storage!$A$11:$A$18,1))+(A40-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A40,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A40,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A40,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A40,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A40,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G40" s="33">
+      <c r="F40" s="26">
+        <f>IF(A40&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A40&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A40,SS_Amont!$A$11:$A$18,1))+(A40-INDEX(SS_Amont!$A$11:$A$18,MATCH(A40,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A40,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A40,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A40,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A40,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G40" s="34">
         <f>E40+F40</f>
         <v/>
       </c>
@@ -7150,14 +8433,14 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="31" t="n">
+      <c r="A41" s="32" t="n">
         <v>36.18</v>
       </c>
-      <c r="B41" s="31">
+      <c r="B41" s="32">
         <f>A41-$B$12</f>
         <v/>
       </c>
-      <c r="C41" s="31">
+      <c r="C41" s="32">
         <f>MAX(0,A41-$B$6)</f>
         <v/>
       </c>
@@ -7165,15 +8448,15 @@
         <f>IF(C41&lt;=0,0,($B$7+$B$9*C41)*C41)</f>
         <v/>
       </c>
-      <c r="E41" s="25">
+      <c r="E41" s="26">
         <f>D41*$B$11</f>
         <v/>
       </c>
-      <c r="F41" s="25">
-        <f>IF(A41&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A41&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A41,Stage_Storage!$A$11:$A$18,1))+(A41-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A41,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A41,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A41,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A41,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A41,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G41" s="33">
+      <c r="F41" s="26">
+        <f>IF(A41&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A41&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A41,SS_Amont!$A$11:$A$18,1))+(A41-INDEX(SS_Amont!$A$11:$A$18,MATCH(A41,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A41,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A41,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A41,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A41,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G41" s="34">
         <f>E41+F41</f>
         <v/>
       </c>
@@ -7195,14 +8478,14 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="31" t="n">
+      <c r="A42" s="32" t="n">
         <v>36.23</v>
       </c>
-      <c r="B42" s="31">
+      <c r="B42" s="32">
         <f>A42-$B$12</f>
         <v/>
       </c>
-      <c r="C42" s="31">
+      <c r="C42" s="32">
         <f>MAX(0,A42-$B$6)</f>
         <v/>
       </c>
@@ -7210,15 +8493,15 @@
         <f>IF(C42&lt;=0,0,($B$7+$B$9*C42)*C42)</f>
         <v/>
       </c>
-      <c r="E42" s="25">
+      <c r="E42" s="26">
         <f>D42*$B$11</f>
         <v/>
       </c>
-      <c r="F42" s="25">
-        <f>IF(A42&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A42&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A42,Stage_Storage!$A$11:$A$18,1))+(A42-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A42,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A42,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A42,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A42,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A42,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G42" s="33">
+      <c r="F42" s="26">
+        <f>IF(A42&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A42&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A42,SS_Amont!$A$11:$A$18,1))+(A42-INDEX(SS_Amont!$A$11:$A$18,MATCH(A42,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A42,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A42,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A42,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A42,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G42" s="34">
         <f>E42+F42</f>
         <v/>
       </c>
@@ -7240,14 +8523,14 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="31" t="n">
+      <c r="A43" s="32" t="n">
         <v>36.28</v>
       </c>
-      <c r="B43" s="31">
+      <c r="B43" s="32">
         <f>A43-$B$12</f>
         <v/>
       </c>
-      <c r="C43" s="31">
+      <c r="C43" s="32">
         <f>MAX(0,A43-$B$6)</f>
         <v/>
       </c>
@@ -7255,15 +8538,15 @@
         <f>IF(C43&lt;=0,0,($B$7+$B$9*C43)*C43)</f>
         <v/>
       </c>
-      <c r="E43" s="25">
+      <c r="E43" s="26">
         <f>D43*$B$11</f>
         <v/>
       </c>
-      <c r="F43" s="25">
-        <f>IF(A43&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A43&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A43,Stage_Storage!$A$11:$A$18,1))+(A43-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A43,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A43,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A43,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A43,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A43,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G43" s="33">
+      <c r="F43" s="26">
+        <f>IF(A43&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A43&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A43,SS_Amont!$A$11:$A$18,1))+(A43-INDEX(SS_Amont!$A$11:$A$18,MATCH(A43,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A43,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A43,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A43,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A43,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G43" s="34">
         <f>E43+F43</f>
         <v/>
       </c>
@@ -7285,14 +8568,14 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="31" t="n">
+      <c r="A44" s="32" t="n">
         <v>36.33</v>
       </c>
-      <c r="B44" s="31">
+      <c r="B44" s="32">
         <f>A44-$B$12</f>
         <v/>
       </c>
-      <c r="C44" s="31">
+      <c r="C44" s="32">
         <f>MAX(0,A44-$B$6)</f>
         <v/>
       </c>
@@ -7300,15 +8583,15 @@
         <f>IF(C44&lt;=0,0,($B$7+$B$9*C44)*C44)</f>
         <v/>
       </c>
-      <c r="E44" s="25">
+      <c r="E44" s="26">
         <f>D44*$B$11</f>
         <v/>
       </c>
-      <c r="F44" s="25">
-        <f>IF(A44&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A44&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A44,Stage_Storage!$A$11:$A$18,1))+(A44-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A44,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A44,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A44,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A44,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A44,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G44" s="33">
+      <c r="F44" s="26">
+        <f>IF(A44&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A44&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A44,SS_Amont!$A$11:$A$18,1))+(A44-INDEX(SS_Amont!$A$11:$A$18,MATCH(A44,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A44,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A44,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A44,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A44,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G44" s="34">
         <f>E44+F44</f>
         <v/>
       </c>
@@ -7330,14 +8613,14 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="31" t="n">
+      <c r="A45" s="32" t="n">
         <v>36.38</v>
       </c>
-      <c r="B45" s="31">
+      <c r="B45" s="32">
         <f>A45-$B$12</f>
         <v/>
       </c>
-      <c r="C45" s="31">
+      <c r="C45" s="32">
         <f>MAX(0,A45-$B$6)</f>
         <v/>
       </c>
@@ -7345,15 +8628,15 @@
         <f>IF(C45&lt;=0,0,($B$7+$B$9*C45)*C45)</f>
         <v/>
       </c>
-      <c r="E45" s="25">
+      <c r="E45" s="26">
         <f>D45*$B$11</f>
         <v/>
       </c>
-      <c r="F45" s="25">
-        <f>IF(A45&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A45&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A45,Stage_Storage!$A$11:$A$18,1))+(A45-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A45,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A45,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A45,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A45,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A45,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G45" s="33">
+      <c r="F45" s="26">
+        <f>IF(A45&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A45&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A45,SS_Amont!$A$11:$A$18,1))+(A45-INDEX(SS_Amont!$A$11:$A$18,MATCH(A45,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A45,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A45,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A45,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A45,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G45" s="34">
         <f>E45+F45</f>
         <v/>
       </c>
@@ -7375,14 +8658,14 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="31" t="n">
+      <c r="A46" s="32" t="n">
         <v>36.43</v>
       </c>
-      <c r="B46" s="31">
+      <c r="B46" s="32">
         <f>A46-$B$12</f>
         <v/>
       </c>
-      <c r="C46" s="31">
+      <c r="C46" s="32">
         <f>MAX(0,A46-$B$6)</f>
         <v/>
       </c>
@@ -7390,15 +8673,15 @@
         <f>IF(C46&lt;=0,0,($B$7+$B$9*C46)*C46)</f>
         <v/>
       </c>
-      <c r="E46" s="25">
+      <c r="E46" s="26">
         <f>D46*$B$11</f>
         <v/>
       </c>
-      <c r="F46" s="25">
-        <f>IF(A46&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A46&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A46,Stage_Storage!$A$11:$A$18,1))+(A46-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A46,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A46,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A46,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A46,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A46,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G46" s="33">
+      <c r="F46" s="26">
+        <f>IF(A46&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A46&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A46,SS_Amont!$A$11:$A$18,1))+(A46-INDEX(SS_Amont!$A$11:$A$18,MATCH(A46,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A46,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A46,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A46,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A46,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G46" s="34">
         <f>E46+F46</f>
         <v/>
       </c>
@@ -7420,14 +8703,14 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="31" t="n">
+      <c r="A47" s="32" t="n">
         <v>36.48</v>
       </c>
-      <c r="B47" s="31">
+      <c r="B47" s="32">
         <f>A47-$B$12</f>
         <v/>
       </c>
-      <c r="C47" s="31">
+      <c r="C47" s="32">
         <f>MAX(0,A47-$B$6)</f>
         <v/>
       </c>
@@ -7435,15 +8718,15 @@
         <f>IF(C47&lt;=0,0,($B$7+$B$9*C47)*C47)</f>
         <v/>
       </c>
-      <c r="E47" s="25">
+      <c r="E47" s="26">
         <f>D47*$B$11</f>
         <v/>
       </c>
-      <c r="F47" s="25">
-        <f>IF(A47&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A47&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A47,Stage_Storage!$A$11:$A$18,1))+(A47-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A47,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A47,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A47,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A47,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A47,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G47" s="33">
+      <c r="F47" s="26">
+        <f>IF(A47&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A47&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A47,SS_Amont!$A$11:$A$18,1))+(A47-INDEX(SS_Amont!$A$11:$A$18,MATCH(A47,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A47,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A47,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A47,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A47,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G47" s="34">
         <f>E47+F47</f>
         <v/>
       </c>
@@ -7465,14 +8748,14 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="31" t="n">
+      <c r="A48" s="32" t="n">
         <v>36.53</v>
       </c>
-      <c r="B48" s="31">
+      <c r="B48" s="32">
         <f>A48-$B$12</f>
         <v/>
       </c>
-      <c r="C48" s="31">
+      <c r="C48" s="32">
         <f>MAX(0,A48-$B$6)</f>
         <v/>
       </c>
@@ -7480,15 +8763,15 @@
         <f>IF(C48&lt;=0,0,($B$7+$B$9*C48)*C48)</f>
         <v/>
       </c>
-      <c r="E48" s="25">
+      <c r="E48" s="26">
         <f>D48*$B$11</f>
         <v/>
       </c>
-      <c r="F48" s="25">
-        <f>IF(A48&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A48&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A48,Stage_Storage!$A$11:$A$18,1))+(A48-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A48,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A48,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A48,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A48,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A48,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G48" s="33">
+      <c r="F48" s="26">
+        <f>IF(A48&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A48&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A48,SS_Amont!$A$11:$A$18,1))+(A48-INDEX(SS_Amont!$A$11:$A$18,MATCH(A48,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A48,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A48,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A48,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A48,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G48" s="34">
         <f>E48+F48</f>
         <v/>
       </c>
@@ -7510,14 +8793,14 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="31" t="n">
+      <c r="A49" s="32" t="n">
         <v>36.58</v>
       </c>
-      <c r="B49" s="31">
+      <c r="B49" s="32">
         <f>A49-$B$12</f>
         <v/>
       </c>
-      <c r="C49" s="31">
+      <c r="C49" s="32">
         <f>MAX(0,A49-$B$6)</f>
         <v/>
       </c>
@@ -7525,15 +8808,15 @@
         <f>IF(C49&lt;=0,0,($B$7+$B$9*C49)*C49)</f>
         <v/>
       </c>
-      <c r="E49" s="25">
+      <c r="E49" s="26">
         <f>D49*$B$11</f>
         <v/>
       </c>
-      <c r="F49" s="25">
-        <f>IF(A49&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A49&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A49,Stage_Storage!$A$11:$A$18,1))+(A49-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A49,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A49,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A49,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A49,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A49,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G49" s="33">
+      <c r="F49" s="26">
+        <f>IF(A49&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A49&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A49,SS_Amont!$A$11:$A$18,1))+(A49-INDEX(SS_Amont!$A$11:$A$18,MATCH(A49,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A49,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A49,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A49,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A49,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G49" s="34">
         <f>E49+F49</f>
         <v/>
       </c>
@@ -7555,14 +8838,14 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="31" t="n">
+      <c r="A50" s="32" t="n">
         <v>36.63</v>
       </c>
-      <c r="B50" s="31">
+      <c r="B50" s="32">
         <f>A50-$B$12</f>
         <v/>
       </c>
-      <c r="C50" s="31">
+      <c r="C50" s="32">
         <f>MAX(0,A50-$B$6)</f>
         <v/>
       </c>
@@ -7570,15 +8853,15 @@
         <f>IF(C50&lt;=0,0,($B$7+$B$9*C50)*C50)</f>
         <v/>
       </c>
-      <c r="E50" s="25">
+      <c r="E50" s="26">
         <f>D50*$B$11</f>
         <v/>
       </c>
-      <c r="F50" s="25">
-        <f>IF(A50&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A50&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A50,Stage_Storage!$A$11:$A$18,1))+(A50-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A50,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A50,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A50,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A50,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A50,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G50" s="33">
+      <c r="F50" s="26">
+        <f>IF(A50&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A50&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A50,SS_Amont!$A$11:$A$18,1))+(A50-INDEX(SS_Amont!$A$11:$A$18,MATCH(A50,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A50,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A50,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A50,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A50,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G50" s="34">
         <f>E50+F50</f>
         <v/>
       </c>
@@ -7600,14 +8883,14 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="31" t="n">
+      <c r="A51" s="32" t="n">
         <v>36.68</v>
       </c>
-      <c r="B51" s="31">
+      <c r="B51" s="32">
         <f>A51-$B$12</f>
         <v/>
       </c>
-      <c r="C51" s="31">
+      <c r="C51" s="32">
         <f>MAX(0,A51-$B$6)</f>
         <v/>
       </c>
@@ -7615,15 +8898,15 @@
         <f>IF(C51&lt;=0,0,($B$7+$B$9*C51)*C51)</f>
         <v/>
       </c>
-      <c r="E51" s="25">
+      <c r="E51" s="26">
         <f>D51*$B$11</f>
         <v/>
       </c>
-      <c r="F51" s="25">
-        <f>IF(A51&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A51&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A51,Stage_Storage!$A$11:$A$18,1))+(A51-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A51,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A51,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A51,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A51,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A51,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G51" s="33">
+      <c r="F51" s="26">
+        <f>IF(A51&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A51&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A51,SS_Amont!$A$11:$A$18,1))+(A51-INDEX(SS_Amont!$A$11:$A$18,MATCH(A51,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A51,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A51,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A51,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A51,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G51" s="34">
         <f>E51+F51</f>
         <v/>
       </c>
@@ -7645,14 +8928,14 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="31" t="n">
+      <c r="A52" s="32" t="n">
         <v>36.73</v>
       </c>
-      <c r="B52" s="31">
+      <c r="B52" s="32">
         <f>A52-$B$12</f>
         <v/>
       </c>
-      <c r="C52" s="31">
+      <c r="C52" s="32">
         <f>MAX(0,A52-$B$6)</f>
         <v/>
       </c>
@@ -7660,15 +8943,15 @@
         <f>IF(C52&lt;=0,0,($B$7+$B$9*C52)*C52)</f>
         <v/>
       </c>
-      <c r="E52" s="25">
+      <c r="E52" s="26">
         <f>D52*$B$11</f>
         <v/>
       </c>
-      <c r="F52" s="25">
-        <f>IF(A52&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A52&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A52,Stage_Storage!$A$11:$A$18,1))+(A52-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A52,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A52,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A52,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A52,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A52,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G52" s="33">
+      <c r="F52" s="26">
+        <f>IF(A52&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A52&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A52,SS_Amont!$A$11:$A$18,1))+(A52-INDEX(SS_Amont!$A$11:$A$18,MATCH(A52,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A52,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A52,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A52,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A52,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G52" s="34">
         <f>E52+F52</f>
         <v/>
       </c>
@@ -7690,14 +8973,14 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="31" t="n">
+      <c r="A53" s="32" t="n">
         <v>36.78</v>
       </c>
-      <c r="B53" s="31">
+      <c r="B53" s="32">
         <f>A53-$B$12</f>
         <v/>
       </c>
-      <c r="C53" s="31">
+      <c r="C53" s="32">
         <f>MAX(0,A53-$B$6)</f>
         <v/>
       </c>
@@ -7705,15 +8988,15 @@
         <f>IF(C53&lt;=0,0,($B$7+$B$9*C53)*C53)</f>
         <v/>
       </c>
-      <c r="E53" s="25">
+      <c r="E53" s="26">
         <f>D53*$B$11</f>
         <v/>
       </c>
-      <c r="F53" s="25">
-        <f>IF(A53&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A53&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A53,Stage_Storage!$A$11:$A$18,1))+(A53-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A53,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A53,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A53,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A53,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A53,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G53" s="33">
+      <c r="F53" s="26">
+        <f>IF(A53&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A53&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A53,SS_Amont!$A$11:$A$18,1))+(A53-INDEX(SS_Amont!$A$11:$A$18,MATCH(A53,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A53,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A53,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A53,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A53,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G53" s="34">
         <f>E53+F53</f>
         <v/>
       </c>
@@ -7735,14 +9018,14 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="31" t="n">
+      <c r="A54" s="32" t="n">
         <v>36.83</v>
       </c>
-      <c r="B54" s="31">
+      <c r="B54" s="32">
         <f>A54-$B$12</f>
         <v/>
       </c>
-      <c r="C54" s="31">
+      <c r="C54" s="32">
         <f>MAX(0,A54-$B$6)</f>
         <v/>
       </c>
@@ -7750,15 +9033,15 @@
         <f>IF(C54&lt;=0,0,($B$7+$B$9*C54)*C54)</f>
         <v/>
       </c>
-      <c r="E54" s="25">
+      <c r="E54" s="26">
         <f>D54*$B$11</f>
         <v/>
       </c>
-      <c r="F54" s="25">
-        <f>IF(A54&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A54&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A54,Stage_Storage!$A$11:$A$18,1))+(A54-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A54,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A54,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A54,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A54,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A54,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G54" s="33">
+      <c r="F54" s="26">
+        <f>IF(A54&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A54&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A54,SS_Amont!$A$11:$A$18,1))+(A54-INDEX(SS_Amont!$A$11:$A$18,MATCH(A54,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A54,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A54,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A54,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A54,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G54" s="34">
         <f>E54+F54</f>
         <v/>
       </c>
@@ -7780,14 +9063,14 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="31" t="n">
+      <c r="A55" s="32" t="n">
         <v>36.88</v>
       </c>
-      <c r="B55" s="31">
+      <c r="B55" s="32">
         <f>A55-$B$12</f>
         <v/>
       </c>
-      <c r="C55" s="31">
+      <c r="C55" s="32">
         <f>MAX(0,A55-$B$6)</f>
         <v/>
       </c>
@@ -7795,15 +9078,15 @@
         <f>IF(C55&lt;=0,0,($B$7+$B$9*C55)*C55)</f>
         <v/>
       </c>
-      <c r="E55" s="25">
+      <c r="E55" s="26">
         <f>D55*$B$11</f>
         <v/>
       </c>
-      <c r="F55" s="25">
-        <f>IF(A55&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A55&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A55,Stage_Storage!$A$11:$A$18,1))+(A55-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A55,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A55,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A55,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A55,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A55,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G55" s="33">
+      <c r="F55" s="26">
+        <f>IF(A55&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A55&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A55,SS_Amont!$A$11:$A$18,1))+(A55-INDEX(SS_Amont!$A$11:$A$18,MATCH(A55,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A55,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A55,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A55,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A55,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G55" s="34">
         <f>E55+F55</f>
         <v/>
       </c>
@@ -7825,14 +9108,14 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="31" t="n">
+      <c r="A56" s="32" t="n">
         <v>36.93</v>
       </c>
-      <c r="B56" s="31">
+      <c r="B56" s="32">
         <f>A56-$B$12</f>
         <v/>
       </c>
-      <c r="C56" s="31">
+      <c r="C56" s="32">
         <f>MAX(0,A56-$B$6)</f>
         <v/>
       </c>
@@ -7840,15 +9123,15 @@
         <f>IF(C56&lt;=0,0,($B$7+$B$9*C56)*C56)</f>
         <v/>
       </c>
-      <c r="E56" s="25">
+      <c r="E56" s="26">
         <f>D56*$B$11</f>
         <v/>
       </c>
-      <c r="F56" s="25">
-        <f>IF(A56&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A56&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A56,Stage_Storage!$A$11:$A$18,1))+(A56-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A56,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A56,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A56,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A56,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A56,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G56" s="33">
+      <c r="F56" s="26">
+        <f>IF(A56&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A56&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A56,SS_Amont!$A$11:$A$18,1))+(A56-INDEX(SS_Amont!$A$11:$A$18,MATCH(A56,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A56,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A56,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A56,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A56,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G56" s="34">
         <f>E56+F56</f>
         <v/>
       </c>
@@ -7870,14 +9153,14 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="31" t="n">
+      <c r="A57" s="32" t="n">
         <v>36.98</v>
       </c>
-      <c r="B57" s="31">
+      <c r="B57" s="32">
         <f>A57-$B$12</f>
         <v/>
       </c>
-      <c r="C57" s="31">
+      <c r="C57" s="32">
         <f>MAX(0,A57-$B$6)</f>
         <v/>
       </c>
@@ -7885,15 +9168,15 @@
         <f>IF(C57&lt;=0,0,($B$7+$B$9*C57)*C57)</f>
         <v/>
       </c>
-      <c r="E57" s="25">
+      <c r="E57" s="26">
         <f>D57*$B$11</f>
         <v/>
       </c>
-      <c r="F57" s="25">
-        <f>IF(A57&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A57&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A57,Stage_Storage!$A$11:$A$18,1))+(A57-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A57,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A57,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A57,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A57,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A57,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G57" s="33">
+      <c r="F57" s="26">
+        <f>IF(A57&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A57&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A57,SS_Amont!$A$11:$A$18,1))+(A57-INDEX(SS_Amont!$A$11:$A$18,MATCH(A57,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A57,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A57,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A57,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A57,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G57" s="34">
         <f>E57+F57</f>
         <v/>
       </c>
@@ -7915,14 +9198,14 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="31" t="n">
+      <c r="A58" s="32" t="n">
         <v>37.03</v>
       </c>
-      <c r="B58" s="31">
+      <c r="B58" s="32">
         <f>A58-$B$12</f>
         <v/>
       </c>
-      <c r="C58" s="31">
+      <c r="C58" s="32">
         <f>MAX(0,A58-$B$6)</f>
         <v/>
       </c>
@@ -7930,15 +9213,15 @@
         <f>IF(C58&lt;=0,0,($B$7+$B$9*C58)*C58)</f>
         <v/>
       </c>
-      <c r="E58" s="25">
+      <c r="E58" s="26">
         <f>D58*$B$11</f>
         <v/>
       </c>
-      <c r="F58" s="25">
-        <f>IF(A58&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A58&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A58,Stage_Storage!$A$11:$A$18,1))+(A58-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A58,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A58,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A58,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A58,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A58,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G58" s="33">
+      <c r="F58" s="26">
+        <f>IF(A58&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A58&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A58,SS_Amont!$A$11:$A$18,1))+(A58-INDEX(SS_Amont!$A$11:$A$18,MATCH(A58,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A58,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A58,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A58,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A58,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G58" s="34">
         <f>E58+F58</f>
         <v/>
       </c>
@@ -7960,14 +9243,14 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="31" t="n">
+      <c r="A59" s="32" t="n">
         <v>37.08</v>
       </c>
-      <c r="B59" s="31">
+      <c r="B59" s="32">
         <f>A59-$B$12</f>
         <v/>
       </c>
-      <c r="C59" s="31">
+      <c r="C59" s="32">
         <f>MAX(0,A59-$B$6)</f>
         <v/>
       </c>
@@ -7975,15 +9258,15 @@
         <f>IF(C59&lt;=0,0,($B$7+$B$9*C59)*C59)</f>
         <v/>
       </c>
-      <c r="E59" s="25">
+      <c r="E59" s="26">
         <f>D59*$B$11</f>
         <v/>
       </c>
-      <c r="F59" s="25">
-        <f>IF(A59&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A59&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A59,Stage_Storage!$A$11:$A$18,1))+(A59-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A59,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A59,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A59,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A59,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A59,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G59" s="33">
+      <c r="F59" s="26">
+        <f>IF(A59&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A59&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A59,SS_Amont!$A$11:$A$18,1))+(A59-INDEX(SS_Amont!$A$11:$A$18,MATCH(A59,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A59,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A59,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A59,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A59,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G59" s="34">
         <f>E59+F59</f>
         <v/>
       </c>
@@ -8005,14 +9288,14 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="31" t="n">
+      <c r="A60" s="32" t="n">
         <v>37.13</v>
       </c>
-      <c r="B60" s="31">
+      <c r="B60" s="32">
         <f>A60-$B$12</f>
         <v/>
       </c>
-      <c r="C60" s="31">
+      <c r="C60" s="32">
         <f>MAX(0,A60-$B$6)</f>
         <v/>
       </c>
@@ -8020,15 +9303,15 @@
         <f>IF(C60&lt;=0,0,($B$7+$B$9*C60)*C60)</f>
         <v/>
       </c>
-      <c r="E60" s="25">
+      <c r="E60" s="26">
         <f>D60*$B$11</f>
         <v/>
       </c>
-      <c r="F60" s="25">
-        <f>IF(A60&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A60&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1))+(A60-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G60" s="33">
+      <c r="F60" s="26">
+        <f>IF(A60&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A60&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A60,SS_Amont!$A$11:$A$18,1))+(A60-INDEX(SS_Amont!$A$11:$A$18,MATCH(A60,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A60,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A60,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A60,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A60,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G60" s="34">
         <f>E60+F60</f>
         <v/>
       </c>
@@ -8050,14 +9333,14 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="31" t="n">
+      <c r="A61" s="32" t="n">
         <v>37.18</v>
       </c>
-      <c r="B61" s="31">
+      <c r="B61" s="32">
         <f>A61-$B$12</f>
         <v/>
       </c>
-      <c r="C61" s="31">
+      <c r="C61" s="32">
         <f>MAX(0,A61-$B$6)</f>
         <v/>
       </c>
@@ -8065,15 +9348,15 @@
         <f>IF(C61&lt;=0,0,($B$7+$B$9*C61)*C61)</f>
         <v/>
       </c>
-      <c r="E61" s="25">
+      <c r="E61" s="26">
         <f>D61*$B$11</f>
         <v/>
       </c>
-      <c r="F61" s="25">
-        <f>IF(A61&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A61&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1))+(A61-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G61" s="33">
+      <c r="F61" s="26">
+        <f>IF(A61&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A61&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A61,SS_Amont!$A$11:$A$18,1))+(A61-INDEX(SS_Amont!$A$11:$A$18,MATCH(A61,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A61,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A61,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A61,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A61,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G61" s="34">
         <f>E61+F61</f>
         <v/>
       </c>
@@ -8095,14 +9378,14 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="31" t="n">
+      <c r="A62" s="32" t="n">
         <v>37.23</v>
       </c>
-      <c r="B62" s="31">
+      <c r="B62" s="32">
         <f>A62-$B$12</f>
         <v/>
       </c>
-      <c r="C62" s="31">
+      <c r="C62" s="32">
         <f>MAX(0,A62-$B$6)</f>
         <v/>
       </c>
@@ -8110,15 +9393,15 @@
         <f>IF(C62&lt;=0,0,($B$7+$B$9*C62)*C62)</f>
         <v/>
       </c>
-      <c r="E62" s="25">
+      <c r="E62" s="26">
         <f>D62*$B$11</f>
         <v/>
       </c>
-      <c r="F62" s="25">
-        <f>IF(A62&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A62&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1))+(A62-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G62" s="33">
+      <c r="F62" s="26">
+        <f>IF(A62&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A62&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A62,SS_Amont!$A$11:$A$18,1))+(A62-INDEX(SS_Amont!$A$11:$A$18,MATCH(A62,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A62,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A62,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A62,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A62,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G62" s="34">
         <f>E62+F62</f>
         <v/>
       </c>
@@ -8140,14 +9423,14 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="31" t="n">
+      <c r="A63" s="32" t="n">
         <v>37.28</v>
       </c>
-      <c r="B63" s="31">
+      <c r="B63" s="32">
         <f>A63-$B$12</f>
         <v/>
       </c>
-      <c r="C63" s="31">
+      <c r="C63" s="32">
         <f>MAX(0,A63-$B$6)</f>
         <v/>
       </c>
@@ -8155,15 +9438,15 @@
         <f>IF(C63&lt;=0,0,($B$7+$B$9*C63)*C63)</f>
         <v/>
       </c>
-      <c r="E63" s="25">
+      <c r="E63" s="26">
         <f>D63*$B$11</f>
         <v/>
       </c>
-      <c r="F63" s="25">
-        <f>IF(A63&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A63&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1))+(A63-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G63" s="33">
+      <c r="F63" s="26">
+        <f>IF(A63&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A63&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A63,SS_Amont!$A$11:$A$18,1))+(A63-INDEX(SS_Amont!$A$11:$A$18,MATCH(A63,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A63,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A63,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A63,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A63,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G63" s="34">
         <f>E63+F63</f>
         <v/>
       </c>
@@ -8185,14 +9468,14 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="31" t="n">
+      <c r="A64" s="32" t="n">
         <v>37.33</v>
       </c>
-      <c r="B64" s="31">
+      <c r="B64" s="32">
         <f>A64-$B$12</f>
         <v/>
       </c>
-      <c r="C64" s="31">
+      <c r="C64" s="32">
         <f>MAX(0,A64-$B$6)</f>
         <v/>
       </c>
@@ -8200,15 +9483,15 @@
         <f>IF(C64&lt;=0,0,($B$7+$B$9*C64)*C64)</f>
         <v/>
       </c>
-      <c r="E64" s="25">
+      <c r="E64" s="26">
         <f>D64*$B$11</f>
         <v/>
       </c>
-      <c r="F64" s="25">
-        <f>IF(A64&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A64&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1))+(A64-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G64" s="33">
+      <c r="F64" s="26">
+        <f>IF(A64&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A64&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A64,SS_Amont!$A$11:$A$18,1))+(A64-INDEX(SS_Amont!$A$11:$A$18,MATCH(A64,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A64,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A64,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A64,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A64,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G64" s="34">
         <f>E64+F64</f>
         <v/>
       </c>
@@ -8230,14 +9513,14 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="31" t="n">
+      <c r="A65" s="32" t="n">
         <v>37.38</v>
       </c>
-      <c r="B65" s="31">
+      <c r="B65" s="32">
         <f>A65-$B$12</f>
         <v/>
       </c>
-      <c r="C65" s="31">
+      <c r="C65" s="32">
         <f>MAX(0,A65-$B$6)</f>
         <v/>
       </c>
@@ -8245,15 +9528,15 @@
         <f>IF(C65&lt;=0,0,($B$7+$B$9*C65)*C65)</f>
         <v/>
       </c>
-      <c r="E65" s="25">
+      <c r="E65" s="26">
         <f>D65*$B$11</f>
         <v/>
       </c>
-      <c r="F65" s="25">
-        <f>IF(A65&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A65&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1))+(A65-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G65" s="33">
+      <c r="F65" s="26">
+        <f>IF(A65&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A65&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A65,SS_Amont!$A$11:$A$18,1))+(A65-INDEX(SS_Amont!$A$11:$A$18,MATCH(A65,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A65,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A65,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A65,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A65,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G65" s="34">
         <f>E65+F65</f>
         <v/>
       </c>
@@ -8275,14 +9558,14 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="31" t="n">
+      <c r="A66" s="32" t="n">
         <v>37.43</v>
       </c>
-      <c r="B66" s="31">
+      <c r="B66" s="32">
         <f>A66-$B$12</f>
         <v/>
       </c>
-      <c r="C66" s="31">
+      <c r="C66" s="32">
         <f>MAX(0,A66-$B$6)</f>
         <v/>
       </c>
@@ -8290,15 +9573,15 @@
         <f>IF(C66&lt;=0,0,($B$7+$B$9*C66)*C66)</f>
         <v/>
       </c>
-      <c r="E66" s="25">
+      <c r="E66" s="26">
         <f>D66*$B$11</f>
         <v/>
       </c>
-      <c r="F66" s="25">
-        <f>IF(A66&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A66&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1))+(A66-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G66" s="33">
+      <c r="F66" s="26">
+        <f>IF(A66&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A66&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A66,SS_Amont!$A$11:$A$18,1))+(A66-INDEX(SS_Amont!$A$11:$A$18,MATCH(A66,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A66,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A66,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A66,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A66,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G66" s="34">
         <f>E66+F66</f>
         <v/>
       </c>
@@ -8320,14 +9603,14 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="31" t="n">
+      <c r="A67" s="32" t="n">
         <v>37.48</v>
       </c>
-      <c r="B67" s="31">
+      <c r="B67" s="32">
         <f>A67-$B$12</f>
         <v/>
       </c>
-      <c r="C67" s="31">
+      <c r="C67" s="32">
         <f>MAX(0,A67-$B$6)</f>
         <v/>
       </c>
@@ -8335,15 +9618,15 @@
         <f>IF(C67&lt;=0,0,($B$7+$B$9*C67)*C67)</f>
         <v/>
       </c>
-      <c r="E67" s="25">
+      <c r="E67" s="26">
         <f>D67*$B$11</f>
         <v/>
       </c>
-      <c r="F67" s="25">
-        <f>IF(A67&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A67&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A67,Stage_Storage!$A$11:$A$18,1))+(A67-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A67,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A67,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A67,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A67,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A67,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G67" s="33">
+      <c r="F67" s="26">
+        <f>IF(A67&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A67&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A67,SS_Amont!$A$11:$A$18,1))+(A67-INDEX(SS_Amont!$A$11:$A$18,MATCH(A67,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A67,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A67,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A67,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A67,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G67" s="34">
         <f>E67+F67</f>
         <v/>
       </c>
@@ -8365,14 +9648,14 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="31" t="n">
+      <c r="A68" s="32" t="n">
         <v>37.53</v>
       </c>
-      <c r="B68" s="31">
+      <c r="B68" s="32">
         <f>A68-$B$12</f>
         <v/>
       </c>
-      <c r="C68" s="31">
+      <c r="C68" s="32">
         <f>MAX(0,A68-$B$6)</f>
         <v/>
       </c>
@@ -8380,15 +9663,15 @@
         <f>IF(C68&lt;=0,0,($B$7+$B$9*C68)*C68)</f>
         <v/>
       </c>
-      <c r="E68" s="25">
+      <c r="E68" s="26">
         <f>D68*$B$11</f>
         <v/>
       </c>
-      <c r="F68" s="25">
-        <f>IF(A68&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A68&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A68,Stage_Storage!$A$11:$A$18,1))+(A68-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A68,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A68,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A68,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A68,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A68,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G68" s="33">
+      <c r="F68" s="26">
+        <f>IF(A68&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A68&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A68,SS_Amont!$A$11:$A$18,1))+(A68-INDEX(SS_Amont!$A$11:$A$18,MATCH(A68,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A68,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A68,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A68,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A68,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G68" s="34">
         <f>E68+F68</f>
         <v/>
       </c>
@@ -8410,14 +9693,14 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="31" t="n">
+      <c r="A69" s="32" t="n">
         <v>37.58</v>
       </c>
-      <c r="B69" s="31">
+      <c r="B69" s="32">
         <f>A69-$B$12</f>
         <v/>
       </c>
-      <c r="C69" s="31">
+      <c r="C69" s="32">
         <f>MAX(0,A69-$B$6)</f>
         <v/>
       </c>
@@ -8425,15 +9708,15 @@
         <f>IF(C69&lt;=0,0,($B$7+$B$9*C69)*C69)</f>
         <v/>
       </c>
-      <c r="E69" s="25">
+      <c r="E69" s="26">
         <f>D69*$B$11</f>
         <v/>
       </c>
-      <c r="F69" s="25">
-        <f>IF(A69&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A69&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A69,Stage_Storage!$A$11:$A$18,1))+(A69-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A69,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A69,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A69,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A69,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A69,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G69" s="33">
+      <c r="F69" s="26">
+        <f>IF(A69&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A69&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A69,SS_Amont!$A$11:$A$18,1))+(A69-INDEX(SS_Amont!$A$11:$A$18,MATCH(A69,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A69,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A69,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A69,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A69,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G69" s="34">
         <f>E69+F69</f>
         <v/>
       </c>
@@ -8455,14 +9738,14 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="31" t="n">
+      <c r="A70" s="32" t="n">
         <v>37.63</v>
       </c>
-      <c r="B70" s="31">
+      <c r="B70" s="32">
         <f>A70-$B$12</f>
         <v/>
       </c>
-      <c r="C70" s="31">
+      <c r="C70" s="32">
         <f>MAX(0,A70-$B$6)</f>
         <v/>
       </c>
@@ -8470,15 +9753,15 @@
         <f>IF(C70&lt;=0,0,($B$7+$B$9*C70)*C70)</f>
         <v/>
       </c>
-      <c r="E70" s="25">
+      <c r="E70" s="26">
         <f>D70*$B$11</f>
         <v/>
       </c>
-      <c r="F70" s="25">
-        <f>IF(A70&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A70&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A70,Stage_Storage!$A$11:$A$18,1))+(A70-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A70,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A70,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A70,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A70,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A70,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G70" s="33">
+      <c r="F70" s="26">
+        <f>IF(A70&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A70&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A70,SS_Amont!$A$11:$A$18,1))+(A70-INDEX(SS_Amont!$A$11:$A$18,MATCH(A70,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A70,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A70,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A70,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A70,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G70" s="34">
         <f>E70+F70</f>
         <v/>
       </c>
@@ -8500,14 +9783,14 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="31" t="n">
+      <c r="A71" s="32" t="n">
         <v>37.68</v>
       </c>
-      <c r="B71" s="31">
+      <c r="B71" s="32">
         <f>A71-$B$12</f>
         <v/>
       </c>
-      <c r="C71" s="31">
+      <c r="C71" s="32">
         <f>MAX(0,A71-$B$6)</f>
         <v/>
       </c>
@@ -8515,15 +9798,15 @@
         <f>IF(C71&lt;=0,0,($B$7+$B$9*C71)*C71)</f>
         <v/>
       </c>
-      <c r="E71" s="25">
+      <c r="E71" s="26">
         <f>D71*$B$11</f>
         <v/>
       </c>
-      <c r="F71" s="25">
-        <f>IF(A71&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A71&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A71,Stage_Storage!$A$11:$A$18,1))+(A71-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A71,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A71,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A71,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A71,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A71,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G71" s="33">
+      <c r="F71" s="26">
+        <f>IF(A71&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A71&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A71,SS_Amont!$A$11:$A$18,1))+(A71-INDEX(SS_Amont!$A$11:$A$18,MATCH(A71,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A71,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A71,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A71,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A71,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G71" s="34">
         <f>E71+F71</f>
         <v/>
       </c>
@@ -8545,14 +9828,14 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="31" t="n">
+      <c r="A72" s="32" t="n">
         <v>37.73</v>
       </c>
-      <c r="B72" s="31">
+      <c r="B72" s="32">
         <f>A72-$B$12</f>
         <v/>
       </c>
-      <c r="C72" s="31">
+      <c r="C72" s="32">
         <f>MAX(0,A72-$B$6)</f>
         <v/>
       </c>
@@ -8560,15 +9843,15 @@
         <f>IF(C72&lt;=0,0,($B$7+$B$9*C72)*C72)</f>
         <v/>
       </c>
-      <c r="E72" s="25">
+      <c r="E72" s="26">
         <f>D72*$B$11</f>
         <v/>
       </c>
-      <c r="F72" s="25">
-        <f>IF(A72&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A72&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A72,Stage_Storage!$A$11:$A$18,1))+(A72-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A72,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A72,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A72,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A72,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A72,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G72" s="33">
+      <c r="F72" s="26">
+        <f>IF(A72&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A72&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A72,SS_Amont!$A$11:$A$18,1))+(A72-INDEX(SS_Amont!$A$11:$A$18,MATCH(A72,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A72,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A72,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A72,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A72,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G72" s="34">
         <f>E72+F72</f>
         <v/>
       </c>
@@ -8590,14 +9873,14 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="31" t="n">
+      <c r="A73" s="32" t="n">
         <v>37.78</v>
       </c>
-      <c r="B73" s="31">
+      <c r="B73" s="32">
         <f>A73-$B$12</f>
         <v/>
       </c>
-      <c r="C73" s="31">
+      <c r="C73" s="32">
         <f>MAX(0,A73-$B$6)</f>
         <v/>
       </c>
@@ -8605,15 +9888,15 @@
         <f>IF(C73&lt;=0,0,($B$7+$B$9*C73)*C73)</f>
         <v/>
       </c>
-      <c r="E73" s="25">
+      <c r="E73" s="26">
         <f>D73*$B$11</f>
         <v/>
       </c>
-      <c r="F73" s="25">
-        <f>IF(A73&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A73&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A73,Stage_Storage!$A$11:$A$18,1))+(A73-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A73,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A73,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A73,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A73,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A73,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G73" s="33">
+      <c r="F73" s="26">
+        <f>IF(A73&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A73&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A73,SS_Amont!$A$11:$A$18,1))+(A73-INDEX(SS_Amont!$A$11:$A$18,MATCH(A73,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A73,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A73,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A73,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A73,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G73" s="34">
         <f>E73+F73</f>
         <v/>
       </c>
@@ -8635,14 +9918,14 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="31" t="n">
+      <c r="A74" s="32" t="n">
         <v>37.83</v>
       </c>
-      <c r="B74" s="31">
+      <c r="B74" s="32">
         <f>A74-$B$12</f>
         <v/>
       </c>
-      <c r="C74" s="31">
+      <c r="C74" s="32">
         <f>MAX(0,A74-$B$6)</f>
         <v/>
       </c>
@@ -8650,15 +9933,15 @@
         <f>IF(C74&lt;=0,0,($B$7+$B$9*C74)*C74)</f>
         <v/>
       </c>
-      <c r="E74" s="25">
+      <c r="E74" s="26">
         <f>D74*$B$11</f>
         <v/>
       </c>
-      <c r="F74" s="25">
-        <f>IF(A74&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A74&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A74,Stage_Storage!$A$11:$A$18,1))+(A74-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A74,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A74,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A74,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A74,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A74,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G74" s="33">
+      <c r="F74" s="26">
+        <f>IF(A74&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A74&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A74,SS_Amont!$A$11:$A$18,1))+(A74-INDEX(SS_Amont!$A$11:$A$18,MATCH(A74,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A74,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A74,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A74,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A74,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G74" s="34">
         <f>E74+F74</f>
         <v/>
       </c>
@@ -8680,14 +9963,14 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="31" t="n">
+      <c r="A75" s="32" t="n">
         <v>37.88</v>
       </c>
-      <c r="B75" s="31">
+      <c r="B75" s="32">
         <f>A75-$B$12</f>
         <v/>
       </c>
-      <c r="C75" s="31">
+      <c r="C75" s="32">
         <f>MAX(0,A75-$B$6)</f>
         <v/>
       </c>
@@ -8695,15 +9978,15 @@
         <f>IF(C75&lt;=0,0,($B$7+$B$9*C75)*C75)</f>
         <v/>
       </c>
-      <c r="E75" s="25">
+      <c r="E75" s="26">
         <f>D75*$B$11</f>
         <v/>
       </c>
-      <c r="F75" s="25">
-        <f>IF(A75&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A75&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A75,Stage_Storage!$A$11:$A$18,1))+(A75-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A75,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A75,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A75,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A75,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A75,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G75" s="33">
+      <c r="F75" s="26">
+        <f>IF(A75&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A75&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A75,SS_Amont!$A$11:$A$18,1))+(A75-INDEX(SS_Amont!$A$11:$A$18,MATCH(A75,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A75,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A75,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A75,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A75,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G75" s="34">
         <f>E75+F75</f>
         <v/>
       </c>
@@ -8725,14 +10008,14 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="31" t="n">
+      <c r="A76" s="32" t="n">
         <v>37.93</v>
       </c>
-      <c r="B76" s="31">
+      <c r="B76" s="32">
         <f>A76-$B$12</f>
         <v/>
       </c>
-      <c r="C76" s="31">
+      <c r="C76" s="32">
         <f>MAX(0,A76-$B$6)</f>
         <v/>
       </c>
@@ -8740,15 +10023,15 @@
         <f>IF(C76&lt;=0,0,($B$7+$B$9*C76)*C76)</f>
         <v/>
       </c>
-      <c r="E76" s="25">
+      <c r="E76" s="26">
         <f>D76*$B$11</f>
         <v/>
       </c>
-      <c r="F76" s="25">
-        <f>IF(A76&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A76&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A76,Stage_Storage!$A$11:$A$18,1))+(A76-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A76,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A76,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A76,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A76,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A76,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G76" s="33">
+      <c r="F76" s="26">
+        <f>IF(A76&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A76&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A76,SS_Amont!$A$11:$A$18,1))+(A76-INDEX(SS_Amont!$A$11:$A$18,MATCH(A76,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A76,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A76,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A76,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A76,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G76" s="34">
         <f>E76+F76</f>
         <v/>
       </c>
@@ -8770,14 +10053,14 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="31" t="n">
+      <c r="A77" s="32" t="n">
         <v>37.98</v>
       </c>
-      <c r="B77" s="31">
+      <c r="B77" s="32">
         <f>A77-$B$12</f>
         <v/>
       </c>
-      <c r="C77" s="31">
+      <c r="C77" s="32">
         <f>MAX(0,A77-$B$6)</f>
         <v/>
       </c>
@@ -8785,15 +10068,15 @@
         <f>IF(C77&lt;=0,0,($B$7+$B$9*C77)*C77)</f>
         <v/>
       </c>
-      <c r="E77" s="25">
+      <c r="E77" s="26">
         <f>D77*$B$11</f>
         <v/>
       </c>
-      <c r="F77" s="25">
-        <f>IF(A77&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A77&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A77,Stage_Storage!$A$11:$A$18,1))+(A77-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A77,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A77,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A77,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A77,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A77,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G77" s="33">
+      <c r="F77" s="26">
+        <f>IF(A77&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A77&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A77,SS_Amont!$A$11:$A$18,1))+(A77-INDEX(SS_Amont!$A$11:$A$18,MATCH(A77,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A77,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A77,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A77,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A77,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G77" s="34">
         <f>E77+F77</f>
         <v/>
       </c>
@@ -8815,14 +10098,14 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="31" t="n">
+      <c r="A78" s="32" t="n">
         <v>38.03</v>
       </c>
-      <c r="B78" s="31">
+      <c r="B78" s="32">
         <f>A78-$B$12</f>
         <v/>
       </c>
-      <c r="C78" s="31">
+      <c r="C78" s="32">
         <f>MAX(0,A78-$B$6)</f>
         <v/>
       </c>
@@ -8830,15 +10113,15 @@
         <f>IF(C78&lt;=0,0,($B$7+$B$9*C78)*C78)</f>
         <v/>
       </c>
-      <c r="E78" s="25">
+      <c r="E78" s="26">
         <f>D78*$B$11</f>
         <v/>
       </c>
-      <c r="F78" s="25">
-        <f>IF(A78&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A78&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A78,Stage_Storage!$A$11:$A$18,1))+(A78-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A78,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A78,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A78,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A78,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A78,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G78" s="33">
+      <c r="F78" s="26">
+        <f>IF(A78&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A78&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A78,SS_Amont!$A$11:$A$18,1))+(A78-INDEX(SS_Amont!$A$11:$A$18,MATCH(A78,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A78,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A78,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A78,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A78,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G78" s="34">
         <f>E78+F78</f>
         <v/>
       </c>
@@ -8860,14 +10143,14 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="31" t="n">
+      <c r="A79" s="32" t="n">
         <v>38.08</v>
       </c>
-      <c r="B79" s="31">
+      <c r="B79" s="32">
         <f>A79-$B$12</f>
         <v/>
       </c>
-      <c r="C79" s="31">
+      <c r="C79" s="32">
         <f>MAX(0,A79-$B$6)</f>
         <v/>
       </c>
@@ -8875,15 +10158,15 @@
         <f>IF(C79&lt;=0,0,($B$7+$B$9*C79)*C79)</f>
         <v/>
       </c>
-      <c r="E79" s="25">
+      <c r="E79" s="26">
         <f>D79*$B$11</f>
         <v/>
       </c>
-      <c r="F79" s="25">
-        <f>IF(A79&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A79&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A79,Stage_Storage!$A$11:$A$18,1))+(A79-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A79,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A79,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A79,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A79,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A79,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G79" s="33">
+      <c r="F79" s="26">
+        <f>IF(A79&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A79&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A79,SS_Amont!$A$11:$A$18,1))+(A79-INDEX(SS_Amont!$A$11:$A$18,MATCH(A79,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A79,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A79,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A79,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A79,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G79" s="34">
         <f>E79+F79</f>
         <v/>
       </c>
@@ -8905,14 +10188,14 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="31" t="n">
+      <c r="A80" s="32" t="n">
         <v>38.13</v>
       </c>
-      <c r="B80" s="31">
+      <c r="B80" s="32">
         <f>A80-$B$12</f>
         <v/>
       </c>
-      <c r="C80" s="31">
+      <c r="C80" s="32">
         <f>MAX(0,A80-$B$6)</f>
         <v/>
       </c>
@@ -8920,15 +10203,15 @@
         <f>IF(C80&lt;=0,0,($B$7+$B$9*C80)*C80)</f>
         <v/>
       </c>
-      <c r="E80" s="25">
+      <c r="E80" s="26">
         <f>D80*$B$11</f>
         <v/>
       </c>
-      <c r="F80" s="25">
-        <f>IF(A80&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A80&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A80,Stage_Storage!$A$11:$A$18,1))+(A80-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A80,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A80,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A80,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A80,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A80,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G80" s="33">
+      <c r="F80" s="26">
+        <f>IF(A80&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A80&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A80,SS_Amont!$A$11:$A$18,1))+(A80-INDEX(SS_Amont!$A$11:$A$18,MATCH(A80,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A80,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A80,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A80,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A80,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G80" s="34">
         <f>E80+F80</f>
         <v/>
       </c>
@@ -8950,14 +10233,14 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="31" t="n">
+      <c r="A81" s="32" t="n">
         <v>38.18</v>
       </c>
-      <c r="B81" s="31">
+      <c r="B81" s="32">
         <f>A81-$B$12</f>
         <v/>
       </c>
-      <c r="C81" s="31">
+      <c r="C81" s="32">
         <f>MAX(0,A81-$B$6)</f>
         <v/>
       </c>
@@ -8965,15 +10248,15 @@
         <f>IF(C81&lt;=0,0,($B$7+$B$9*C81)*C81)</f>
         <v/>
       </c>
-      <c r="E81" s="25">
+      <c r="E81" s="26">
         <f>D81*$B$11</f>
         <v/>
       </c>
-      <c r="F81" s="25">
-        <f>IF(A81&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A81&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A81,Stage_Storage!$A$11:$A$18,1))+(A81-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A81,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A81,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A81,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A81,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A81,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G81" s="33">
+      <c r="F81" s="26">
+        <f>IF(A81&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A81&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A81,SS_Amont!$A$11:$A$18,1))+(A81-INDEX(SS_Amont!$A$11:$A$18,MATCH(A81,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A81,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A81,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A81,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A81,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G81" s="34">
         <f>E81+F81</f>
         <v/>
       </c>
@@ -8995,14 +10278,14 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="31" t="n">
+      <c r="A82" s="32" t="n">
         <v>38.23</v>
       </c>
-      <c r="B82" s="31">
+      <c r="B82" s="32">
         <f>A82-$B$12</f>
         <v/>
       </c>
-      <c r="C82" s="31">
+      <c r="C82" s="32">
         <f>MAX(0,A82-$B$6)</f>
         <v/>
       </c>
@@ -9010,15 +10293,15 @@
         <f>IF(C82&lt;=0,0,($B$7+$B$9*C82)*C82)</f>
         <v/>
       </c>
-      <c r="E82" s="25">
+      <c r="E82" s="26">
         <f>D82*$B$11</f>
         <v/>
       </c>
-      <c r="F82" s="25">
-        <f>IF(A82&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A82&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A82,Stage_Storage!$A$11:$A$18,1))+(A82-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A82,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A82,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A82,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A82,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A82,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G82" s="33">
+      <c r="F82" s="26">
+        <f>IF(A82&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A82&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A82,SS_Amont!$A$11:$A$18,1))+(A82-INDEX(SS_Amont!$A$11:$A$18,MATCH(A82,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A82,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A82,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A82,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A82,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G82" s="34">
         <f>E82+F82</f>
         <v/>
       </c>
@@ -9040,14 +10323,14 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="31" t="n">
+      <c r="A83" s="32" t="n">
         <v>38.28</v>
       </c>
-      <c r="B83" s="31">
+      <c r="B83" s="32">
         <f>A83-$B$12</f>
         <v/>
       </c>
-      <c r="C83" s="31">
+      <c r="C83" s="32">
         <f>MAX(0,A83-$B$6)</f>
         <v/>
       </c>
@@ -9055,15 +10338,15 @@
         <f>IF(C83&lt;=0,0,($B$7+$B$9*C83)*C83)</f>
         <v/>
       </c>
-      <c r="E83" s="25">
+      <c r="E83" s="26">
         <f>D83*$B$11</f>
         <v/>
       </c>
-      <c r="F83" s="25">
-        <f>IF(A83&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A83&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A83,Stage_Storage!$A$11:$A$18,1))+(A83-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A83,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A83,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A83,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A83,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A83,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G83" s="33">
+      <c r="F83" s="26">
+        <f>IF(A83&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A83&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A83,SS_Amont!$A$11:$A$18,1))+(A83-INDEX(SS_Amont!$A$11:$A$18,MATCH(A83,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A83,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A83,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A83,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A83,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G83" s="34">
         <f>E83+F83</f>
         <v/>
       </c>
@@ -9085,14 +10368,14 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="31" t="n">
+      <c r="A84" s="32" t="n">
         <v>38.33</v>
       </c>
-      <c r="B84" s="31">
+      <c r="B84" s="32">
         <f>A84-$B$12</f>
         <v/>
       </c>
-      <c r="C84" s="31">
+      <c r="C84" s="32">
         <f>MAX(0,A84-$B$6)</f>
         <v/>
       </c>
@@ -9100,15 +10383,15 @@
         <f>IF(C84&lt;=0,0,($B$7+$B$9*C84)*C84)</f>
         <v/>
       </c>
-      <c r="E84" s="25">
+      <c r="E84" s="26">
         <f>D84*$B$11</f>
         <v/>
       </c>
-      <c r="F84" s="25">
-        <f>IF(A84&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A84&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A84,Stage_Storage!$A$11:$A$18,1))+(A84-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A84,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A84,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A84,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A84,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A84,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G84" s="33">
+      <c r="F84" s="26">
+        <f>IF(A84&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A84&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A84,SS_Amont!$A$11:$A$18,1))+(A84-INDEX(SS_Amont!$A$11:$A$18,MATCH(A84,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A84,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A84,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A84,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A84,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G84" s="34">
         <f>E84+F84</f>
         <v/>
       </c>
@@ -9130,14 +10413,14 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="31" t="n">
+      <c r="A85" s="32" t="n">
         <v>38.38</v>
       </c>
-      <c r="B85" s="31">
+      <c r="B85" s="32">
         <f>A85-$B$12</f>
         <v/>
       </c>
-      <c r="C85" s="31">
+      <c r="C85" s="32">
         <f>MAX(0,A85-$B$6)</f>
         <v/>
       </c>
@@ -9145,15 +10428,15 @@
         <f>IF(C85&lt;=0,0,($B$7+$B$9*C85)*C85)</f>
         <v/>
       </c>
-      <c r="E85" s="25">
+      <c r="E85" s="26">
         <f>D85*$B$11</f>
         <v/>
       </c>
-      <c r="F85" s="25">
-        <f>IF(A85&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A85&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A85,Stage_Storage!$A$11:$A$18,1))+(A85-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A85,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A85,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A85,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A85,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A85,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G85" s="33">
+      <c r="F85" s="26">
+        <f>IF(A85&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A85&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A85,SS_Amont!$A$11:$A$18,1))+(A85-INDEX(SS_Amont!$A$11:$A$18,MATCH(A85,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A85,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A85,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A85,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A85,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G85" s="34">
         <f>E85+F85</f>
         <v/>
       </c>
@@ -9175,14 +10458,14 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="31" t="n">
+      <c r="A86" s="32" t="n">
         <v>38.43</v>
       </c>
-      <c r="B86" s="31">
+      <c r="B86" s="32">
         <f>A86-$B$12</f>
         <v/>
       </c>
-      <c r="C86" s="31">
+      <c r="C86" s="32">
         <f>MAX(0,A86-$B$6)</f>
         <v/>
       </c>
@@ -9190,15 +10473,15 @@
         <f>IF(C86&lt;=0,0,($B$7+$B$9*C86)*C86)</f>
         <v/>
       </c>
-      <c r="E86" s="25">
+      <c r="E86" s="26">
         <f>D86*$B$11</f>
         <v/>
       </c>
-      <c r="F86" s="25">
-        <f>IF(A86&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A86&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A86,Stage_Storage!$A$11:$A$18,1))+(A86-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A86,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A86,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A86,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A86,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A86,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G86" s="33">
+      <c r="F86" s="26">
+        <f>IF(A86&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A86&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A86,SS_Amont!$A$11:$A$18,1))+(A86-INDEX(SS_Amont!$A$11:$A$18,MATCH(A86,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A86,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A86,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A86,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A86,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G86" s="34">
         <f>E86+F86</f>
         <v/>
       </c>
@@ -9220,14 +10503,14 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="31" t="n">
+      <c r="A87" s="32" t="n">
         <v>38.48</v>
       </c>
-      <c r="B87" s="31">
+      <c r="B87" s="32">
         <f>A87-$B$12</f>
         <v/>
       </c>
-      <c r="C87" s="31">
+      <c r="C87" s="32">
         <f>MAX(0,A87-$B$6)</f>
         <v/>
       </c>
@@ -9235,15 +10518,15 @@
         <f>IF(C87&lt;=0,0,($B$7+$B$9*C87)*C87)</f>
         <v/>
       </c>
-      <c r="E87" s="25">
+      <c r="E87" s="26">
         <f>D87*$B$11</f>
         <v/>
       </c>
-      <c r="F87" s="25">
-        <f>IF(A87&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A87&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A87,Stage_Storage!$A$11:$A$18,1))+(A87-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A87,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A87,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A87,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A87,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A87,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G87" s="33">
+      <c r="F87" s="26">
+        <f>IF(A87&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A87&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A87,SS_Amont!$A$11:$A$18,1))+(A87-INDEX(SS_Amont!$A$11:$A$18,MATCH(A87,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A87,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A87,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A87,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A87,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G87" s="34">
         <f>E87+F87</f>
         <v/>
       </c>
@@ -9265,14 +10548,14 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="31" t="n">
+      <c r="A88" s="32" t="n">
         <v>38.53</v>
       </c>
-      <c r="B88" s="31">
+      <c r="B88" s="32">
         <f>A88-$B$12</f>
         <v/>
       </c>
-      <c r="C88" s="31">
+      <c r="C88" s="32">
         <f>MAX(0,A88-$B$6)</f>
         <v/>
       </c>
@@ -9280,15 +10563,15 @@
         <f>IF(C88&lt;=0,0,($B$7+$B$9*C88)*C88)</f>
         <v/>
       </c>
-      <c r="E88" s="25">
+      <c r="E88" s="26">
         <f>D88*$B$11</f>
         <v/>
       </c>
-      <c r="F88" s="25">
-        <f>IF(A88&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A88&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A88,Stage_Storage!$A$11:$A$18,1))+(A88-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A88,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A88,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A88,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A88,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A88,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G88" s="33">
+      <c r="F88" s="26">
+        <f>IF(A88&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A88&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A88,SS_Amont!$A$11:$A$18,1))+(A88-INDEX(SS_Amont!$A$11:$A$18,MATCH(A88,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A88,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A88,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A88,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A88,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G88" s="34">
         <f>E88+F88</f>
         <v/>
       </c>
@@ -9310,14 +10593,14 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="31" t="n">
+      <c r="A89" s="32" t="n">
         <v>38.58</v>
       </c>
-      <c r="B89" s="31">
+      <c r="B89" s="32">
         <f>A89-$B$12</f>
         <v/>
       </c>
-      <c r="C89" s="31">
+      <c r="C89" s="32">
         <f>MAX(0,A89-$B$6)</f>
         <v/>
       </c>
@@ -9325,15 +10608,15 @@
         <f>IF(C89&lt;=0,0,($B$7+$B$9*C89)*C89)</f>
         <v/>
       </c>
-      <c r="E89" s="25">
+      <c r="E89" s="26">
         <f>D89*$B$11</f>
         <v/>
       </c>
-      <c r="F89" s="25">
-        <f>IF(A89&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A89&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A89,Stage_Storage!$A$11:$A$18,1))+(A89-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A89,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A89,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A89,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A89,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A89,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G89" s="33">
+      <c r="F89" s="26">
+        <f>IF(A89&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A89&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A89,SS_Amont!$A$11:$A$18,1))+(A89-INDEX(SS_Amont!$A$11:$A$18,MATCH(A89,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A89,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A89,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A89,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A89,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G89" s="34">
         <f>E89+F89</f>
         <v/>
       </c>
@@ -9355,14 +10638,14 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="31" t="n">
+      <c r="A90" s="32" t="n">
         <v>38.63</v>
       </c>
-      <c r="B90" s="31">
+      <c r="B90" s="32">
         <f>A90-$B$12</f>
         <v/>
       </c>
-      <c r="C90" s="31">
+      <c r="C90" s="32">
         <f>MAX(0,A90-$B$6)</f>
         <v/>
       </c>
@@ -9370,15 +10653,15 @@
         <f>IF(C90&lt;=0,0,($B$7+$B$9*C90)*C90)</f>
         <v/>
       </c>
-      <c r="E90" s="25">
+      <c r="E90" s="26">
         <f>D90*$B$11</f>
         <v/>
       </c>
-      <c r="F90" s="25">
-        <f>IF(A90&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A90&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A90,Stage_Storage!$A$11:$A$18,1))+(A90-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A90,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A90,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A90,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A90,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A90,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G90" s="33">
+      <c r="F90" s="26">
+        <f>IF(A90&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A90&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A90,SS_Amont!$A$11:$A$18,1))+(A90-INDEX(SS_Amont!$A$11:$A$18,MATCH(A90,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A90,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A90,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A90,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A90,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G90" s="34">
         <f>E90+F90</f>
         <v/>
       </c>
@@ -9400,14 +10683,14 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="31" t="n">
+      <c r="A91" s="32" t="n">
         <v>38.68</v>
       </c>
-      <c r="B91" s="31">
+      <c r="B91" s="32">
         <f>A91-$B$12</f>
         <v/>
       </c>
-      <c r="C91" s="31">
+      <c r="C91" s="32">
         <f>MAX(0,A91-$B$6)</f>
         <v/>
       </c>
@@ -9415,15 +10698,15 @@
         <f>IF(C91&lt;=0,0,($B$7+$B$9*C91)*C91)</f>
         <v/>
       </c>
-      <c r="E91" s="25">
+      <c r="E91" s="26">
         <f>D91*$B$11</f>
         <v/>
       </c>
-      <c r="F91" s="25">
-        <f>IF(A91&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A91&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A91,Stage_Storage!$A$11:$A$18,1))+(A91-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A91,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A91,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A91,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A91,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A91,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G91" s="33">
+      <c r="F91" s="26">
+        <f>IF(A91&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A91&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A91,SS_Amont!$A$11:$A$18,1))+(A91-INDEX(SS_Amont!$A$11:$A$18,MATCH(A91,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A91,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A91,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A91,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A91,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G91" s="34">
         <f>E91+F91</f>
         <v/>
       </c>
@@ -9445,14 +10728,14 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="31" t="n">
+      <c r="A92" s="32" t="n">
         <v>38.73</v>
       </c>
-      <c r="B92" s="31">
+      <c r="B92" s="32">
         <f>A92-$B$12</f>
         <v/>
       </c>
-      <c r="C92" s="31">
+      <c r="C92" s="32">
         <f>MAX(0,A92-$B$6)</f>
         <v/>
       </c>
@@ -9460,15 +10743,15 @@
         <f>IF(C92&lt;=0,0,($B$7+$B$9*C92)*C92)</f>
         <v/>
       </c>
-      <c r="E92" s="25">
+      <c r="E92" s="26">
         <f>D92*$B$11</f>
         <v/>
       </c>
-      <c r="F92" s="25">
-        <f>IF(A92&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A92&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A92,Stage_Storage!$A$11:$A$18,1))+(A92-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A92,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A92,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A92,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A92,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A92,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G92" s="33">
+      <c r="F92" s="26">
+        <f>IF(A92&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A92&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A92,SS_Amont!$A$11:$A$18,1))+(A92-INDEX(SS_Amont!$A$11:$A$18,MATCH(A92,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A92,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A92,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A92,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A92,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G92" s="34">
         <f>E92+F92</f>
         <v/>
       </c>
@@ -9490,14 +10773,14 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="31" t="n">
+      <c r="A93" s="32" t="n">
         <v>38.78</v>
       </c>
-      <c r="B93" s="31">
+      <c r="B93" s="32">
         <f>A93-$B$12</f>
         <v/>
       </c>
-      <c r="C93" s="31">
+      <c r="C93" s="32">
         <f>MAX(0,A93-$B$6)</f>
         <v/>
       </c>
@@ -9505,15 +10788,15 @@
         <f>IF(C93&lt;=0,0,($B$7+$B$9*C93)*C93)</f>
         <v/>
       </c>
-      <c r="E93" s="25">
+      <c r="E93" s="26">
         <f>D93*$B$11</f>
         <v/>
       </c>
-      <c r="F93" s="25">
-        <f>IF(A93&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A93&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A93,Stage_Storage!$A$11:$A$18,1))+(A93-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A93,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A93,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A93,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A93,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A93,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G93" s="33">
+      <c r="F93" s="26">
+        <f>IF(A93&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A93&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A93,SS_Amont!$A$11:$A$18,1))+(A93-INDEX(SS_Amont!$A$11:$A$18,MATCH(A93,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A93,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A93,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A93,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A93,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G93" s="34">
         <f>E93+F93</f>
         <v/>
       </c>
@@ -9535,14 +10818,14 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="31" t="n">
+      <c r="A94" s="32" t="n">
         <v>38.83</v>
       </c>
-      <c r="B94" s="31">
+      <c r="B94" s="32">
         <f>A94-$B$12</f>
         <v/>
       </c>
-      <c r="C94" s="31">
+      <c r="C94" s="32">
         <f>MAX(0,A94-$B$6)</f>
         <v/>
       </c>
@@ -9550,15 +10833,15 @@
         <f>IF(C94&lt;=0,0,($B$7+$B$9*C94)*C94)</f>
         <v/>
       </c>
-      <c r="E94" s="25">
+      <c r="E94" s="26">
         <f>D94*$B$11</f>
         <v/>
       </c>
-      <c r="F94" s="25">
-        <f>IF(A94&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A94&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A94,Stage_Storage!$A$11:$A$18,1))+(A94-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A94,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A94,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A94,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A94,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A94,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G94" s="33">
+      <c r="F94" s="26">
+        <f>IF(A94&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A94&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A94,SS_Amont!$A$11:$A$18,1))+(A94-INDEX(SS_Amont!$A$11:$A$18,MATCH(A94,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A94,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A94,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A94,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A94,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G94" s="34">
         <f>E94+F94</f>
         <v/>
       </c>
@@ -9580,14 +10863,14 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="31" t="n">
+      <c r="A95" s="32" t="n">
         <v>38.88</v>
       </c>
-      <c r="B95" s="31">
+      <c r="B95" s="32">
         <f>A95-$B$12</f>
         <v/>
       </c>
-      <c r="C95" s="31">
+      <c r="C95" s="32">
         <f>MAX(0,A95-$B$6)</f>
         <v/>
       </c>
@@ -9595,15 +10878,15 @@
         <f>IF(C95&lt;=0,0,($B$7+$B$9*C95)*C95)</f>
         <v/>
       </c>
-      <c r="E95" s="25">
+      <c r="E95" s="26">
         <f>D95*$B$11</f>
         <v/>
       </c>
-      <c r="F95" s="25">
-        <f>IF(A95&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A95&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A95,Stage_Storage!$A$11:$A$18,1))+(A95-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A95,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A95,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A95,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A95,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A95,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G95" s="33">
+      <c r="F95" s="26">
+        <f>IF(A95&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A95&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A95,SS_Amont!$A$11:$A$18,1))+(A95-INDEX(SS_Amont!$A$11:$A$18,MATCH(A95,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A95,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A95,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A95,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A95,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G95" s="34">
         <f>E95+F95</f>
         <v/>
       </c>
@@ -9625,14 +10908,14 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="31" t="n">
+      <c r="A96" s="32" t="n">
         <v>38.93</v>
       </c>
-      <c r="B96" s="31">
+      <c r="B96" s="32">
         <f>A96-$B$12</f>
         <v/>
       </c>
-      <c r="C96" s="31">
+      <c r="C96" s="32">
         <f>MAX(0,A96-$B$6)</f>
         <v/>
       </c>
@@ -9640,15 +10923,15 @@
         <f>IF(C96&lt;=0,0,($B$7+$B$9*C96)*C96)</f>
         <v/>
       </c>
-      <c r="E96" s="25">
+      <c r="E96" s="26">
         <f>D96*$B$11</f>
         <v/>
       </c>
-      <c r="F96" s="25">
-        <f>IF(A96&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A96&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A96,Stage_Storage!$A$11:$A$18,1))+(A96-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A96,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A96,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A96,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A96,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A96,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G96" s="33">
+      <c r="F96" s="26">
+        <f>IF(A96&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A96&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A96,SS_Amont!$A$11:$A$18,1))+(A96-INDEX(SS_Amont!$A$11:$A$18,MATCH(A96,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A96,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A96,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A96,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A96,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G96" s="34">
         <f>E96+F96</f>
         <v/>
       </c>
@@ -9670,14 +10953,14 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="31" t="n">
+      <c r="A97" s="32" t="n">
         <v>38.98</v>
       </c>
-      <c r="B97" s="31">
+      <c r="B97" s="32">
         <f>A97-$B$12</f>
         <v/>
       </c>
-      <c r="C97" s="31">
+      <c r="C97" s="32">
         <f>MAX(0,A97-$B$6)</f>
         <v/>
       </c>
@@ -9685,15 +10968,15 @@
         <f>IF(C97&lt;=0,0,($B$7+$B$9*C97)*C97)</f>
         <v/>
       </c>
-      <c r="E97" s="25">
+      <c r="E97" s="26">
         <f>D97*$B$11</f>
         <v/>
       </c>
-      <c r="F97" s="25">
-        <f>IF(A97&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A97&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A97,Stage_Storage!$A$11:$A$18,1))+(A97-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A97,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A97,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A97,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A97,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A97,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G97" s="33">
+      <c r="F97" s="26">
+        <f>IF(A97&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A97&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A97,SS_Amont!$A$11:$A$18,1))+(A97-INDEX(SS_Amont!$A$11:$A$18,MATCH(A97,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A97,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A97,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A97,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A97,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G97" s="34">
         <f>E97+F97</f>
         <v/>
       </c>
@@ -9715,14 +10998,14 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="31" t="n">
+      <c r="A98" s="32" t="n">
         <v>39.03</v>
       </c>
-      <c r="B98" s="31">
+      <c r="B98" s="32">
         <f>A98-$B$12</f>
         <v/>
       </c>
-      <c r="C98" s="31">
+      <c r="C98" s="32">
         <f>MAX(0,A98-$B$6)</f>
         <v/>
       </c>
@@ -9730,15 +11013,15 @@
         <f>IF(C98&lt;=0,0,($B$7+$B$9*C98)*C98)</f>
         <v/>
       </c>
-      <c r="E98" s="25">
+      <c r="E98" s="26">
         <f>D98*$B$11</f>
         <v/>
       </c>
-      <c r="F98" s="25">
-        <f>IF(A98&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A98&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A98,Stage_Storage!$A$11:$A$18,1))+(A98-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A98,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A98,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A98,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A98,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A98,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G98" s="33">
+      <c r="F98" s="26">
+        <f>IF(A98&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A98&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A98,SS_Amont!$A$11:$A$18,1))+(A98-INDEX(SS_Amont!$A$11:$A$18,MATCH(A98,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A98,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A98,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A98,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A98,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G98" s="34">
         <f>E98+F98</f>
         <v/>
       </c>
@@ -9760,14 +11043,14 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="31" t="n">
+      <c r="A99" s="32" t="n">
         <v>39.08</v>
       </c>
-      <c r="B99" s="31">
+      <c r="B99" s="32">
         <f>A99-$B$12</f>
         <v/>
       </c>
-      <c r="C99" s="31">
+      <c r="C99" s="32">
         <f>MAX(0,A99-$B$6)</f>
         <v/>
       </c>
@@ -9775,15 +11058,15 @@
         <f>IF(C99&lt;=0,0,($B$7+$B$9*C99)*C99)</f>
         <v/>
       </c>
-      <c r="E99" s="25">
+      <c r="E99" s="26">
         <f>D99*$B$11</f>
         <v/>
       </c>
-      <c r="F99" s="25">
-        <f>IF(A99&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A99&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A99,Stage_Storage!$A$11:$A$18,1))+(A99-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A99,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A99,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A99,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A99,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A99,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G99" s="33">
+      <c r="F99" s="26">
+        <f>IF(A99&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A99&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A99,SS_Amont!$A$11:$A$18,1))+(A99-INDEX(SS_Amont!$A$11:$A$18,MATCH(A99,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A99,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A99,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A99,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A99,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G99" s="34">
         <f>E99+F99</f>
         <v/>
       </c>
@@ -9805,14 +11088,14 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="31" t="n">
+      <c r="A100" s="32" t="n">
         <v>39.13</v>
       </c>
-      <c r="B100" s="31">
+      <c r="B100" s="32">
         <f>A100-$B$12</f>
         <v/>
       </c>
-      <c r="C100" s="31">
+      <c r="C100" s="32">
         <f>MAX(0,A100-$B$6)</f>
         <v/>
       </c>
@@ -9820,15 +11103,15 @@
         <f>IF(C100&lt;=0,0,($B$7+$B$9*C100)*C100)</f>
         <v/>
       </c>
-      <c r="E100" s="25">
+      <c r="E100" s="26">
         <f>D100*$B$11</f>
         <v/>
       </c>
-      <c r="F100" s="25">
-        <f>IF(A100&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A100&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A100,Stage_Storage!$A$11:$A$18,1))+(A100-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A100,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A100,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A100,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A100,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A100,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G100" s="33">
+      <c r="F100" s="26">
+        <f>IF(A100&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A100&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A100,SS_Amont!$A$11:$A$18,1))+(A100-INDEX(SS_Amont!$A$11:$A$18,MATCH(A100,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A100,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A100,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A100,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A100,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G100" s="34">
         <f>E100+F100</f>
         <v/>
       </c>
@@ -9850,14 +11133,14 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="31" t="n">
+      <c r="A101" s="32" t="n">
         <v>39.18</v>
       </c>
-      <c r="B101" s="31">
+      <c r="B101" s="32">
         <f>A101-$B$12</f>
         <v/>
       </c>
-      <c r="C101" s="31">
+      <c r="C101" s="32">
         <f>MAX(0,A101-$B$6)</f>
         <v/>
       </c>
@@ -9865,15 +11148,15 @@
         <f>IF(C101&lt;=0,0,($B$7+$B$9*C101)*C101)</f>
         <v/>
       </c>
-      <c r="E101" s="25">
+      <c r="E101" s="26">
         <f>D101*$B$11</f>
         <v/>
       </c>
-      <c r="F101" s="25">
-        <f>IF(A101&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A101&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A101,Stage_Storage!$A$11:$A$18,1))+(A101-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A101,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A101,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A101,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A101,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A101,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G101" s="33">
+      <c r="F101" s="26">
+        <f>IF(A101&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A101&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A101,SS_Amont!$A$11:$A$18,1))+(A101-INDEX(SS_Amont!$A$11:$A$18,MATCH(A101,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A101,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A101,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A101,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A101,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G101" s="34">
         <f>E101+F101</f>
         <v/>
       </c>
@@ -9895,14 +11178,14 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="31" t="n">
+      <c r="A102" s="32" t="n">
         <v>39.23</v>
       </c>
-      <c r="B102" s="31">
+      <c r="B102" s="32">
         <f>A102-$B$12</f>
         <v/>
       </c>
-      <c r="C102" s="31">
+      <c r="C102" s="32">
         <f>MAX(0,A102-$B$6)</f>
         <v/>
       </c>
@@ -9910,15 +11193,15 @@
         <f>IF(C102&lt;=0,0,($B$7+$B$9*C102)*C102)</f>
         <v/>
       </c>
-      <c r="E102" s="25">
+      <c r="E102" s="26">
         <f>D102*$B$11</f>
         <v/>
       </c>
-      <c r="F102" s="25">
-        <f>IF(A102&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A102&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A102,Stage_Storage!$A$11:$A$18,1))+(A102-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A102,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A102,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A102,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A102,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A102,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G102" s="33">
+      <c r="F102" s="26">
+        <f>IF(A102&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A102&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A102,SS_Amont!$A$11:$A$18,1))+(A102-INDEX(SS_Amont!$A$11:$A$18,MATCH(A102,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A102,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A102,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A102,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A102,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G102" s="34">
         <f>E102+F102</f>
         <v/>
       </c>
@@ -9940,14 +11223,14 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="31" t="n">
+      <c r="A103" s="32" t="n">
         <v>39.28</v>
       </c>
-      <c r="B103" s="31">
+      <c r="B103" s="32">
         <f>A103-$B$12</f>
         <v/>
       </c>
-      <c r="C103" s="31">
+      <c r="C103" s="32">
         <f>MAX(0,A103-$B$6)</f>
         <v/>
       </c>
@@ -9955,15 +11238,15 @@
         <f>IF(C103&lt;=0,0,($B$7+$B$9*C103)*C103)</f>
         <v/>
       </c>
-      <c r="E103" s="25">
+      <c r="E103" s="26">
         <f>D103*$B$11</f>
         <v/>
       </c>
-      <c r="F103" s="25">
-        <f>IF(A103&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A103&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A103,Stage_Storage!$A$11:$A$18,1))+(A103-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A103,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A103,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A103,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A103,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A103,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G103" s="33">
+      <c r="F103" s="26">
+        <f>IF(A103&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A103&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A103,SS_Amont!$A$11:$A$18,1))+(A103-INDEX(SS_Amont!$A$11:$A$18,MATCH(A103,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A103,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A103,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A103,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A103,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G103" s="34">
         <f>E103+F103</f>
         <v/>
       </c>
@@ -9985,14 +11268,14 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="31" t="n">
+      <c r="A104" s="32" t="n">
         <v>39.33</v>
       </c>
-      <c r="B104" s="31">
+      <c r="B104" s="32">
         <f>A104-$B$12</f>
         <v/>
       </c>
-      <c r="C104" s="31">
+      <c r="C104" s="32">
         <f>MAX(0,A104-$B$6)</f>
         <v/>
       </c>
@@ -10000,15 +11283,15 @@
         <f>IF(C104&lt;=0,0,($B$7+$B$9*C104)*C104)</f>
         <v/>
       </c>
-      <c r="E104" s="25">
+      <c r="E104" s="26">
         <f>D104*$B$11</f>
         <v/>
       </c>
-      <c r="F104" s="25">
-        <f>IF(A104&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A104&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A104,Stage_Storage!$A$11:$A$18,1))+(A104-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A104,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A104,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A104,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A104,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A104,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G104" s="33">
+      <c r="F104" s="26">
+        <f>IF(A104&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A104&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A104,SS_Amont!$A$11:$A$18,1))+(A104-INDEX(SS_Amont!$A$11:$A$18,MATCH(A104,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A104,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A104,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A104,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A104,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G104" s="34">
         <f>E104+F104</f>
         <v/>
       </c>
@@ -10030,14 +11313,14 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="31" t="n">
+      <c r="A105" s="32" t="n">
         <v>39.38</v>
       </c>
-      <c r="B105" s="31">
+      <c r="B105" s="32">
         <f>A105-$B$12</f>
         <v/>
       </c>
-      <c r="C105" s="31">
+      <c r="C105" s="32">
         <f>MAX(0,A105-$B$6)</f>
         <v/>
       </c>
@@ -10045,15 +11328,15 @@
         <f>IF(C105&lt;=0,0,($B$7+$B$9*C105)*C105)</f>
         <v/>
       </c>
-      <c r="E105" s="25">
+      <c r="E105" s="26">
         <f>D105*$B$11</f>
         <v/>
       </c>
-      <c r="F105" s="25">
-        <f>IF(A105&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A105&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A105,Stage_Storage!$A$11:$A$18,1))+(A105-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A105,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A105,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A105,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A105,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A105,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G105" s="33">
+      <c r="F105" s="26">
+        <f>IF(A105&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A105&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A105,SS_Amont!$A$11:$A$18,1))+(A105-INDEX(SS_Amont!$A$11:$A$18,MATCH(A105,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A105,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A105,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A105,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A105,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G105" s="34">
         <f>E105+F105</f>
         <v/>
       </c>
@@ -10075,14 +11358,14 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="31" t="n">
+      <c r="A106" s="32" t="n">
         <v>39.43</v>
       </c>
-      <c r="B106" s="31">
+      <c r="B106" s="32">
         <f>A106-$B$12</f>
         <v/>
       </c>
-      <c r="C106" s="31">
+      <c r="C106" s="32">
         <f>MAX(0,A106-$B$6)</f>
         <v/>
       </c>
@@ -10090,15 +11373,15 @@
         <f>IF(C106&lt;=0,0,($B$7+$B$9*C106)*C106)</f>
         <v/>
       </c>
-      <c r="E106" s="25">
+      <c r="E106" s="26">
         <f>D106*$B$11</f>
         <v/>
       </c>
-      <c r="F106" s="25">
-        <f>IF(A106&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A106&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A106,Stage_Storage!$A$11:$A$18,1))+(A106-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A106,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A106,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A106,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A106,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A106,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G106" s="33">
+      <c r="F106" s="26">
+        <f>IF(A106&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A106&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A106,SS_Amont!$A$11:$A$18,1))+(A106-INDEX(SS_Amont!$A$11:$A$18,MATCH(A106,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A106,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A106,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A106,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A106,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G106" s="34">
         <f>E106+F106</f>
         <v/>
       </c>
@@ -10120,14 +11403,14 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="31" t="n">
+      <c r="A107" s="32" t="n">
         <v>39.48</v>
       </c>
-      <c r="B107" s="31">
+      <c r="B107" s="32">
         <f>A107-$B$12</f>
         <v/>
       </c>
-      <c r="C107" s="31">
+      <c r="C107" s="32">
         <f>MAX(0,A107-$B$6)</f>
         <v/>
       </c>
@@ -10135,15 +11418,15 @@
         <f>IF(C107&lt;=0,0,($B$7+$B$9*C107)*C107)</f>
         <v/>
       </c>
-      <c r="E107" s="25">
+      <c r="E107" s="26">
         <f>D107*$B$11</f>
         <v/>
       </c>
-      <c r="F107" s="25">
-        <f>IF(A107&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A107&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A107,Stage_Storage!$A$11:$A$18,1))+(A107-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A107,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A107,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A107,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A107,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A107,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G107" s="33">
+      <c r="F107" s="26">
+        <f>IF(A107&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A107&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A107,SS_Amont!$A$11:$A$18,1))+(A107-INDEX(SS_Amont!$A$11:$A$18,MATCH(A107,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A107,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A107,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A107,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A107,SS_Amont!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G107" s="34">
         <f>E107+F107</f>
         <v/>
       </c>
@@ -10192,14 +11475,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Méthode C — routage avec Qout composé + V = V_pond + V_ditch</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="39" t="inlineStr">
+      <c r="A2" s="40" t="inlineStr">
         <is>
           <t>À chaque pas: WSE lu sur Compose_900!V_total → Qout sur Compose_900. ΔV = (Qin_moy − Qout)×Δt. Si V≈0, Qout = MIN(Qin, Q_plein).</t>
         </is>
@@ -10212,7 +11495,7 @@
           <t>Q_plein réf. (m³/s)</t>
         </is>
       </c>
-      <c r="B5" s="40">
+      <c r="B5" s="41">
         <f>Parametres!B22</f>
         <v/>
       </c>
@@ -10223,7 +11506,7 @@
           <t>Crest (m)</t>
         </is>
       </c>
-      <c r="B6" s="40">
+      <c r="B6" s="41">
         <f>Parametres!B27</f>
         <v/>
       </c>
@@ -10234,7 +11517,7 @@
           <t>Vmax_C (m³)</t>
         </is>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="31">
         <f>MAX(F12:F24)</f>
         <v/>
       </c>
@@ -10315,10 +11598,10 @@
         <f>MIN(B12,$B$5)</f>
         <v/>
       </c>
-      <c r="E12" s="25" t="n">
+      <c r="E12" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="33" t="n">
+      <c r="F12" s="34" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -10344,11 +11627,11 @@
         <f>IF(F12&lt;=0.01,MIN(0.5*(B12+B13),$B$5),IF(C13&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C13&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C13,Compose_900!$A$15:$A$107,1))+(C13-INDEX(Compose_900!$A$15:$A$107,MATCH(C13,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C13,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C13,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C13,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C13,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="26">
         <f>(A13-A12)*60</f>
         <v/>
       </c>
-      <c r="F13" s="33">
+      <c r="F13" s="34">
         <f>MAX(0,F12+(0.5*(B12+B13)-D13)*E13)</f>
         <v/>
       </c>
@@ -10374,11 +11657,11 @@
         <f>IF(F13&lt;=0.01,MIN(0.5*(B13+B14),$B$5),IF(C14&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C14&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C14,Compose_900!$A$15:$A$107,1))+(C14-INDEX(Compose_900!$A$15:$A$107,MATCH(C14,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C14,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C14,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C14,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C14,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="26">
         <f>(A14-A13)*60</f>
         <v/>
       </c>
-      <c r="F14" s="33">
+      <c r="F14" s="34">
         <f>MAX(0,F13+(0.5*(B13+B14)-D14)*E14)</f>
         <v/>
       </c>
@@ -10404,11 +11687,11 @@
         <f>IF(F14&lt;=0.01,MIN(0.5*(B14+B15),$B$5),IF(C15&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C15&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C15,Compose_900!$A$15:$A$107,1))+(C15-INDEX(Compose_900!$A$15:$A$107,MATCH(C15,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C15,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C15,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C15,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C15,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="26">
         <f>(A15-A14)*60</f>
         <v/>
       </c>
-      <c r="F15" s="33">
+      <c r="F15" s="34">
         <f>MAX(0,F14+(0.5*(B14+B15)-D15)*E15)</f>
         <v/>
       </c>
@@ -10434,11 +11717,11 @@
         <f>IF(F15&lt;=0.01,MIN(0.5*(B15+B16),$B$5),IF(C16&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C16&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C16,Compose_900!$A$15:$A$107,1))+(C16-INDEX(Compose_900!$A$15:$A$107,MATCH(C16,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C16,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C16,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C16,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C16,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="26">
         <f>(A16-A15)*60</f>
         <v/>
       </c>
-      <c r="F16" s="33">
+      <c r="F16" s="34">
         <f>MAX(0,F15+(0.5*(B15+B16)-D16)*E16)</f>
         <v/>
       </c>
@@ -10464,11 +11747,11 @@
         <f>IF(F16&lt;=0.01,MIN(0.5*(B16+B17),$B$5),IF(C17&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C17&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C17,Compose_900!$A$15:$A$107,1))+(C17-INDEX(Compose_900!$A$15:$A$107,MATCH(C17,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C17,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C17,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C17,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C17,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="26">
         <f>(A17-A16)*60</f>
         <v/>
       </c>
-      <c r="F17" s="33">
+      <c r="F17" s="34">
         <f>MAX(0,F16+(0.5*(B16+B17)-D17)*E17)</f>
         <v/>
       </c>
@@ -10494,11 +11777,11 @@
         <f>IF(F17&lt;=0.01,MIN(0.5*(B17+B18),$B$5),IF(C18&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C18&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C18,Compose_900!$A$15:$A$107,1))+(C18-INDEX(Compose_900!$A$15:$A$107,MATCH(C18,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C18,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C18,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C18,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C18,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E18" s="25">
+      <c r="E18" s="26">
         <f>(A18-A17)*60</f>
         <v/>
       </c>
-      <c r="F18" s="33">
+      <c r="F18" s="34">
         <f>MAX(0,F17+(0.5*(B17+B18)-D18)*E18)</f>
         <v/>
       </c>
@@ -10524,11 +11807,11 @@
         <f>IF(F18&lt;=0.01,MIN(0.5*(B18+B19),$B$5),IF(C19&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C19&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C19,Compose_900!$A$15:$A$107,1))+(C19-INDEX(Compose_900!$A$15:$A$107,MATCH(C19,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C19,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C19,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C19,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C19,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E19" s="25">
+      <c r="E19" s="26">
         <f>(A19-A18)*60</f>
         <v/>
       </c>
-      <c r="F19" s="33">
+      <c r="F19" s="34">
         <f>MAX(0,F18+(0.5*(B18+B19)-D19)*E19)</f>
         <v/>
       </c>
@@ -10554,11 +11837,11 @@
         <f>IF(F19&lt;=0.01,MIN(0.5*(B19+B20),$B$5),IF(C20&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C20&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C20,Compose_900!$A$15:$A$107,1))+(C20-INDEX(Compose_900!$A$15:$A$107,MATCH(C20,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C20,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C20,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C20,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C20,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E20" s="25">
+      <c r="E20" s="26">
         <f>(A20-A19)*60</f>
         <v/>
       </c>
-      <c r="F20" s="33">
+      <c r="F20" s="34">
         <f>MAX(0,F19+(0.5*(B19+B20)-D20)*E20)</f>
         <v/>
       </c>
@@ -10584,11 +11867,11 @@
         <f>IF(F20&lt;=0.01,MIN(0.5*(B20+B21),$B$5),IF(C21&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C21&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C21,Compose_900!$A$15:$A$107,1))+(C21-INDEX(Compose_900!$A$15:$A$107,MATCH(C21,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C21,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C21,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C21,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C21,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E21" s="25">
+      <c r="E21" s="26">
         <f>(A21-A20)*60</f>
         <v/>
       </c>
-      <c r="F21" s="33">
+      <c r="F21" s="34">
         <f>MAX(0,F20+(0.5*(B20+B21)-D21)*E21)</f>
         <v/>
       </c>
@@ -10614,11 +11897,11 @@
         <f>IF(F21&lt;=0.01,MIN(0.5*(B21+B22),$B$5),IF(C22&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C22&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C22,Compose_900!$A$15:$A$107,1))+(C22-INDEX(Compose_900!$A$15:$A$107,MATCH(C22,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C22,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C22,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C22,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C22,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E22" s="25">
+      <c r="E22" s="26">
         <f>(A22-A21)*60</f>
         <v/>
       </c>
-      <c r="F22" s="33">
+      <c r="F22" s="34">
         <f>MAX(0,F21+(0.5*(B21+B22)-D22)*E22)</f>
         <v/>
       </c>
@@ -10644,11 +11927,11 @@
         <f>IF(F22&lt;=0.01,MIN(0.5*(B22+B23),$B$5),IF(C23&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C23&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C23,Compose_900!$A$15:$A$107,1))+(C23-INDEX(Compose_900!$A$15:$A$107,MATCH(C23,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C23,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C23,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C23,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C23,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E23" s="25">
+      <c r="E23" s="26">
         <f>(A23-A22)*60</f>
         <v/>
       </c>
-      <c r="F23" s="33">
+      <c r="F23" s="34">
         <f>MAX(0,F22+(0.5*(B22+B23)-D23)*E23)</f>
         <v/>
       </c>
@@ -10674,11 +11957,11 @@
         <f>IF(F23&lt;=0.01,MIN(0.5*(B23+B24),$B$5),IF(C24&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C24&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C24,Compose_900!$A$15:$A$107,1))+(C24-INDEX(Compose_900!$A$15:$A$107,MATCH(C24,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C24,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C24,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C24,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C24,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E24" s="25">
+      <c r="E24" s="26">
         <f>(A24-A23)*60</f>
         <v/>
       </c>
-      <c r="F24" s="33">
+      <c r="F24" s="34">
         <f>MAX(0,F23+(0.5*(B23+B24)-D24)*E24)</f>
         <v/>
       </c>
@@ -10701,28 +11984,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="23" t="inlineStr">
-        <is>
-          <t>Stage–storage du levé — V = f(WSE) → lire le niveau max</t>
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>Zone 1 — Stage–storage Ø1500 → Ø900 (amont)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>PROCÉDURE (dans CE fichier): 1) Routage → Vmax_A / Vmax_B / Vmax_C sur Parametres. 2) Cette feuille = V_pond vs WSE (levé topographique — le vrai bassin). 3) Parametres!B39 = WSEmax_A; B45 = WSEmax_B (lus sur CE tableau). 4) Méthode C: V_pond + V_ditch et WSEmax_C sur Compose_900 / Calcul_C (B51). 5) Parametres!B24 (2500 m²) n'est PAS ici: c'est seulement le raccourci H=V/A de Méthode B. Surfaces ci-dessous = votre levé (pas des placeholders).</t>
+          <t>Jaune = WSE et Surface éditables (corriger depuis AutoCAD). ΔWSE, V_pas, V_cumul = formules live (aires moyennes). Cette feuille alimente WSEmax_A/B et V_pond Méthode C. Parametres!B24 (2500 m²) n'est PAS ici — raccourci Méthode B seulement. Ne pas y mettre les surfaces de Zone 2.</t>
         </is>
       </c>
     </row>
@@ -10731,12 +12014,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Formule d'un pas</t>
+          <t>Formule d'un pas (aires moyennes)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="42" t="inlineStr">
+      <c r="A7" s="43" t="inlineStr">
         <is>
           <t>V_pas (m³) = (A_basse + A_haute) / 2 × (WSE_haute − WSE_basse)</t>
         </is>
@@ -10745,14 +12028,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V_cumulatif = somme des V_pas depuis le radier</t>
+          <t>V_cumulatif = somme des V_pas depuis le fond de zone. Jaune = éditer (AutoCAD).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>WSE / NSE (m)</t>
+          <t>WSE / NSE (m) ← ÉDITER</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -10782,7 +12065,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="n">
+      <c r="A11" s="12" t="n">
         <v>34.88</v>
       </c>
       <c r="B11" s="17" t="n">
@@ -10799,286 +12082,266 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Fond bassin / radier Ø900</t>
+          <t>Fond Zone 1 / radier amont Ø900</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="31" t="n">
+      <c r="A12" s="12" t="n">
         <v>35.5</v>
       </c>
       <c r="B12" s="17" t="n">
-        <v>120</v>
-      </c>
-      <c r="C12" s="31">
+        <v>56</v>
+      </c>
+      <c r="C12" s="32">
         <f>A12-A11</f>
         <v/>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="26">
         <f>0.5*(B11+B12)*C12</f>
         <v/>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="34">
         <f>E11+D12</f>
         <v/>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Levé</t>
+          <t>Levé Zone 1 — éditer si AutoCAD diffère</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="31" t="n">
+      <c r="A13" s="12" t="n">
         <v>36.01</v>
       </c>
       <c r="B13" s="17" t="n">
-        <v>419</v>
-      </c>
-      <c r="C13" s="31">
+        <v>210</v>
+      </c>
+      <c r="C13" s="32">
         <f>A13-A12</f>
         <v/>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="26">
         <f>0.5*(B12+B13)*C13</f>
         <v/>
       </c>
-      <c r="E13" s="33">
+      <c r="E13" s="34">
         <f>E12+D13</f>
         <v/>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Levé</t>
+          <t>Levé Zone 1</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="31" t="n">
+      <c r="A14" s="12" t="n">
         <v>36.5</v>
       </c>
       <c r="B14" s="17" t="n">
-        <v>480</v>
-      </c>
-      <c r="C14" s="31">
+        <v>380</v>
+      </c>
+      <c r="C14" s="32">
         <f>A14-A13</f>
         <v/>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="26">
         <f>0.5*(B13+B14)*C14</f>
         <v/>
       </c>
-      <c r="E14" s="33">
+      <c r="E14" s="34">
         <f>E13+D14</f>
         <v/>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Levé</t>
+          <t>Levé Zone 1</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="31" t="n">
+      <c r="A15" s="12" t="n">
         <v>37</v>
       </c>
       <c r="B15" s="17" t="n">
-        <v>720</v>
-      </c>
-      <c r="C15" s="31">
+        <v>400</v>
+      </c>
+      <c r="C15" s="32">
         <f>A15-A14</f>
         <v/>
       </c>
-      <c r="D15" s="25">
+      <c r="D15" s="26">
         <f>0.5*(B14+B15)*C15</f>
         <v/>
       </c>
-      <c r="E15" s="33">
+      <c r="E15" s="34">
         <f>E14+D15</f>
         <v/>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Levé</t>
+          <t>Levé Zone 1</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="38" t="n">
+      <c r="A16" s="12" t="n">
         <v>37.28</v>
       </c>
       <c r="B16" s="17" t="n">
-        <v>2198</v>
-      </c>
-      <c r="C16" s="38">
+        <v>500</v>
+      </c>
+      <c r="C16" s="39">
         <f>A16-A15</f>
         <v/>
       </c>
-      <c r="D16" s="41">
+      <c r="D16" s="42">
         <f>0.5*(B15+B16)*C16</f>
         <v/>
       </c>
-      <c r="E16" s="41">
+      <c r="E16" s="42">
         <f>E15+D16</f>
         <v/>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>LIMITE PATRON (+1.5 m crown) — levé</t>
+          <t>LIMITE PATRON Zone 1 (+1.5 m crown)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="31" t="n">
+      <c r="A17" s="12" t="n">
         <v>37.4</v>
       </c>
       <c r="B17" s="17" t="n">
-        <v>1516</v>
-      </c>
-      <c r="C17" s="31">
+        <v>860</v>
+      </c>
+      <c r="C17" s="32">
         <f>A17-A16</f>
         <v/>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="26">
         <f>0.5*(B16+B17)*C17</f>
         <v/>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="34">
         <f>E16+D17</f>
         <v/>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Levé (A↓ vs 37.28 — vérifier si voulu)</t>
+          <t>Levé Zone 1</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="31" t="n">
+      <c r="A18" s="12" t="n">
         <v>40</v>
       </c>
       <c r="B18" s="17" t="n">
-        <v>3746</v>
-      </c>
-      <c r="C18" s="31">
+        <v>2100</v>
+      </c>
+      <c r="C18" s="32">
         <f>A18-A17</f>
         <v/>
       </c>
-      <c r="D18" s="25">
+      <c r="D18" s="26">
         <f>0.5*(B17+B18)*C18</f>
         <v/>
       </c>
-      <c r="E18" s="33">
+      <c r="E18" s="34">
         <f>E17+D18</f>
         <v/>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Levé — sommet table</t>
+          <t>Sommet table Zone 1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Vmax_A (Calcul_A)</t>
-        </is>
-      </c>
-      <c r="B21" s="20">
-        <f>Parametres!B36</f>
-        <v/>
+          <t>V @ 37.28 m (m³)</t>
+        </is>
+      </c>
+      <c r="B21" s="44">
+        <f>E16</f>
+        <v/>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ligne orange — limite patron typique</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>WSEmax_A (m)</t>
-        </is>
-      </c>
-      <c r="B22" s="42">
-        <f>Parametres!B39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Vmax_B (Calcul_B)</t>
-        </is>
-      </c>
-      <c r="B23" s="20">
-        <f>Parametres!B43</f>
+          <t>V @ sommet table (m³)</t>
+        </is>
+      </c>
+      <c r="B22" s="44">
+        <f>E18</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>WSEmax_B (m)</t>
-        </is>
-      </c>
-      <c r="B24" s="42">
-        <f>Parametres!B45</f>
+          <t>Vmax_A / WSEmax_A (Parametres)</t>
+        </is>
+      </c>
+      <c r="B24" s="20">
+        <f>Parametres!B36</f>
+        <v/>
+      </c>
+      <c r="C24">
+        <f>Parametres!B39</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Vmax_C / WSEmax_C</t>
+          <t>Vmax_B / WSEmax_B (Parametres)</t>
         </is>
       </c>
       <c r="B25" s="20">
-        <f>Parametres!B49</f>
+        <f>Parametres!B43</f>
         <v/>
       </c>
       <c r="C25">
-        <f>Parametres!B51</f>
-        <v/>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Vmax_C inclut V_ditch — WSEmax_C = Parametres B51</t>
-        </is>
+        <f>Parametres!B45</f>
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>V disponible à 37.28 m (m³)</t>
-        </is>
-      </c>
-      <c r="B26" s="43">
-        <f>E16</f>
-        <v/>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Si Vmax_A ou Vmax_B &gt; cette valeur → le niveau dépasse la limite patron</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Comment lire le résultat</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="39" t="inlineStr">
-        <is>
-          <t>Exemple: si Vmax_A &gt; V_cumul @ 37.28 (colonne E, ligne orange), alors WSEmax_A &gt; 37.28 m (la table monte vers 37.40 / 40.00 ou 'Hors table'). Jaune = surfaces du levé (éditables). Méthode C: Parametres B49–B52 et Calcul_C (fossé inclus). Note: A(37.40)=1516 &lt; A(37.28)=2198 — inhabituel; confirmer sur plan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31"/>
+          <t>Vmax_C / WSEmax_C (Parametres)</t>
+        </is>
+      </c>
+      <c r="B26" s="20">
+        <f>Parametres!B49</f>
+        <v/>
+      </c>
+      <c r="C26">
+        <f>Parametres!B51</f>
+        <v/>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Vmax_C inclut V_ditch</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A2:G4"/>
-    <mergeCell ref="A29:F31"/>
     <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11092,129 +12355,332 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="44" t="inlineStr">
-        <is>
-          <t>Où sont les fichiers HY-8 / capacité ?</t>
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>Zone 2 — Stage–storage Ø900 → Ø1200 (aval)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Ce classeur (rétention Ø900) :</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  engineering/drainage-design/retention_volume/Volume_Retention_Ponceau_900.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-    </row>
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Jaune = WSE et Surface éditables (corriger depuis AutoCAD). ΔWSE, V_pas, V_cumul = formules live. Qin de cette zone = débit sortant du Ø900 (voir Calcul_Aval_A). Sortie contrôlée par Ø1200 (Q_plein ≈ 4.93 m³/s). Ne pas y mettre les surfaces de Zone 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4"/>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Courbe Q=f(H) FHWA pour CE Ø900 : feuille Courbe_QH_900 (ci-dessus).</t>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Formule d'un pas (aires moyennes)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>V_pas (m³) = (A_basse + A_haute) / 2 × (WSE_haute − WSE_basse)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ancien Excel « type HY-8 / inlet-outlet » (autre projet / Ste-Thérèse) :</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  engineering/drainage-design/Ponceau_Capacite_Inlet_Outlet.xlsx</t>
+          <t>V_cumulatif = somme des V_pas depuis le fond de zone. Jaune = éditer (AutoCAD).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Branche git: cursor/culvert-excel-capacity-model-d87f</t>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>WSE / NSE (m) ← ÉDITER</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Surface A (m²) ← ÉDITER</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>ΔWSE (m)</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>V_pas (m³)</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>V_cumulatif (m³)</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Rôle</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" s="12" t="n">
+        <v>34.88</v>
+      </c>
+      <c r="B11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Fond Zone 2 (même grille WSE — éditer)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Modèle composé ponceau Ø1050 + fossé (FHWA + remblai) — PAS le Ø900 de rétention :</t>
+      <c r="A12" s="12" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="B12" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="C12" s="32">
+        <f>A12-A11</f>
+        <v/>
+      </c>
+      <c r="D12" s="26">
+        <f>0.5*(B11+B12)*C12</f>
+        <v/>
+      </c>
+      <c r="E12" s="34">
+        <f>E11+D12</f>
+        <v/>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Levé Zone 2 — éditer si AutoCAD diffère</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  engineering/drainage-design/ponceau_fosse_model/Ponceau_Fosse_Modele_Hydraulique.xlsx</t>
+      <c r="A13" s="12" t="n">
+        <v>36.01</v>
+      </c>
+      <c r="B13" s="17" t="n">
+        <v>219</v>
+      </c>
+      <c r="C13" s="32">
+        <f>A13-A12</f>
+        <v/>
+      </c>
+      <c r="D13" s="26">
+        <f>0.5*(B12+B13)*C13</f>
+        <v/>
+      </c>
+      <c r="E13" s="34">
+        <f>E12+D13</f>
+        <v/>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Levé Zone 2</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Branche git: cursor/ponceau-fosse-hydraulic-model-d87f</t>
+      <c r="A14" s="12" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="B14" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="C14" s="32">
+        <f>A14-A13</f>
+        <v/>
+      </c>
+      <c r="D14" s="26">
+        <f>0.5*(B13+B14)*C14</f>
+        <v/>
+      </c>
+      <c r="E14" s="34">
+        <f>E13+D14</f>
+        <v/>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Levé Zone 2 (A↓ — vérifier plan)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="B15" s="17" t="n">
+        <v>340</v>
+      </c>
+      <c r="C15" s="32">
+        <f>A15-A14</f>
+        <v/>
+      </c>
+      <c r="D15" s="26">
+        <f>0.5*(B14+B15)*C15</f>
+        <v/>
+      </c>
+      <c r="E15" s="34">
+        <f>E14+D15</f>
+        <v/>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Levé Zone 2</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>HEC-RAS : pas de projet .ras/.hdf pour ce Ø900. Un DEM Ste-Thérèse est dans</t>
+      <c r="A16" s="12" t="n">
+        <v>37.28</v>
+      </c>
+      <c r="B16" s="17" t="n">
+        <v>1700</v>
+      </c>
+      <c r="C16" s="39">
+        <f>A16-A15</f>
+        <v/>
+      </c>
+      <c r="D16" s="42">
+        <f>0.5*(B15+B16)*C16</f>
+        <v/>
+      </c>
+      <c r="E16" s="42">
+        <f>E15+D16</f>
+        <v/>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Levé Zone 2 @ limite patron</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  engineering/hec-ras-data/ (données topo seulement).</t>
+      <c r="A17" s="12" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="B17" s="17" t="n">
+        <v>1460</v>
+      </c>
+      <c r="C17" s="32">
+        <f>A17-A16</f>
+        <v/>
+      </c>
+      <c r="D17" s="26">
+        <f>0.5*(B16+B17)*C17</f>
+        <v/>
+      </c>
+      <c r="E17" s="34">
+        <f>E16+D17</f>
+        <v/>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Levé Zone 2 (A↓ — vérifier plan)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Donc: on n'avait pas perdu un HY-8 pour ce bassin Ø900 — on avait des outils</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>similaires pour d'autres sites. La courbe de CE classeur remplace ça pour le Ø900.</t>
-        </is>
+      <c r="A18" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="B18" s="17" t="n">
+        <v>1632</v>
+      </c>
+      <c r="C18" s="32">
+        <f>A18-A17</f>
+        <v/>
+      </c>
+      <c r="D18" s="26">
+        <f>0.5*(B17+B18)*C18</f>
+        <v/>
+      </c>
+      <c r="E18" s="34">
+        <f>E17+D18</f>
+        <v/>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Sommet table Zone 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>V @ 37.28 m (m³)</t>
+        </is>
+      </c>
+      <c r="B21" s="44">
+        <f>E16</f>
+        <v/>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ligne orange — limite patron typique</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>V @ sommet table (m³)</t>
+        </is>
+      </c>
+      <c r="B22" s="44">
+        <f>E18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Vmax_Aval_A / WSEmax (Parametres)</t>
+        </is>
+      </c>
+      <c r="B24" s="20">
+        <f>Parametres!B56</f>
+        <v/>
+      </c>
+      <c r="C24">
+        <f>Parametres!B57</f>
+        <v/>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A2:G4"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/engineering/drainage-design/retention_volume/Volume_Retention_Ponceau_900.xlsx
+++ b/engineering/drainage-design/retention_volume/Volume_Retention_Ponceau_900.xlsx
@@ -14,12 +14,9 @@
     <sheet name="Calcul_B" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Compose_900" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Calcul_C" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="SS_Amont" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="SS_Aval" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Stage_Storage" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Calcul_Aval_A" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Fichiers_lies" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Methode" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Stage_Storage" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Fichiers_lies" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Methode" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -128,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -154,7 +151,6 @@
     <xf numFmtId="1" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -177,9 +173,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -1006,7 +1000,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Zone 1 — V cumulé vs WSE</a:t>
+              <a:t>V cumulé vs WSE (levé)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1020,7 +1014,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'SS_Amont'!E10</f>
+              <f>'Stage_Storage'!E10</f>
             </strRef>
           </tx>
           <spPr>
@@ -1038,130 +1032,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'SS_Amont'!$A$11:$A$18</f>
+              <f>'Stage_Storage'!$A$11:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'SS_Amont'!$E$11:$E$18</f>
-            </numRef>
-          </val>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>WSE (m)</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>V (m³)</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Zone 2 — V cumulé vs WSE</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'SS_Aval'!E10</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'SS_Aval'!$A$11:$A$18</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'SS_Aval'!$E$11:$E$18</f>
+              <f>'Stage_Storage'!$E$11:$E$18</f>
             </numRef>
           </val>
         </ser>
@@ -1361,33 +1237,6 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="5400000" cy="2700000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -1703,7 +1552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -2020,7 +1869,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Raccourci Méthode B seulement: H≈V/B24 pour lire Q=f(H). Ce n'est PAS un 2e bassin. Levé Zone 1 = feuille SS_Amont; Zone 2 = SS_Aval.</t>
+          <t>Raccourci Méthode B seulement: H≈V/B24 pour lire Q=f(H). Ce n'est PAS un 2e bassin. Le vrai étang = feuille Stage_Storage (surfaces vs WSE).</t>
         </is>
       </c>
     </row>
@@ -2198,16 +2047,16 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>WSEmax_A depuis levé Zone 1 (m) — SS_Amont</t>
+          <t>WSEmax_A depuis levé (m) — feuille Stage_Storage</t>
         </is>
       </c>
       <c r="B39" s="22">
-        <f>IF(B36&lt;=SS_Amont!E11,SS_Amont!A11,IF(B36&gt;=SS_Amont!E18,"Hors table (&gt;=40.0 m — étendre levé)",INDEX(SS_Amont!$A$11:$A$18,MATCH(B36,SS_Amont!$E$11:$E$18,1))+(B36-INDEX(SS_Amont!$E$11:$E$18,MATCH(B36,SS_Amont!$E$11:$E$18,1)))/(INDEX(SS_Amont!$E$11:$E$18,MATCH(B36,SS_Amont!$E$11:$E$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(B36,SS_Amont!$E$11:$E$18,1)))*(INDEX(SS_Amont!$A$11:$A$18,MATCH(B36,SS_Amont!$E$11:$E$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(B36,SS_Amont!$E$11:$E$18,1)))))</f>
+        <f>IF(B36&lt;=Stage_Storage!E11,Stage_Storage!A11,IF(B36&gt;=Stage_Storage!E18,"Hors table (&gt;=40.0 m — étendre levé)",INDEX(Stage_Storage!$A$11:$A$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1))+(B36-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)))/(INDEX(Stage_Storage!$E$11:$E$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)))*(INDEX(Stage_Storage!$A$11:$A$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(B36,Stage_Storage!$E$11:$E$18,1)))))</f>
         <v/>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cote d'eau max pour Vmax_A: lecture sur SS_Amont (Ø1500→Ø900), pas Zone 2</t>
+          <t>Cote d'eau max pour le Vmax_A: on lit sur Stage_Storage quelle WSE donne ce volume (courbe volume–cote du levé)</t>
         </is>
       </c>
     </row>
@@ -2264,16 +2113,16 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>WSEmax_B depuis levé Zone 1 (m) — SS_Amont</t>
+          <t>WSEmax_B depuis levé (m) — feuille Stage_Storage</t>
         </is>
       </c>
       <c r="B45" s="22">
-        <f>IF(B43&lt;=SS_Amont!E11,SS_Amont!A11,IF(B43&gt;=SS_Amont!E18,"Hors table (&gt;=40.0 m — étendre levé)",INDEX(SS_Amont!$A$11:$A$18,MATCH(B43,SS_Amont!$E$11:$E$18,1))+(B43-INDEX(SS_Amont!$E$11:$E$18,MATCH(B43,SS_Amont!$E$11:$E$18,1)))/(INDEX(SS_Amont!$E$11:$E$18,MATCH(B43,SS_Amont!$E$11:$E$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(B43,SS_Amont!$E$11:$E$18,1)))*(INDEX(SS_Amont!$A$11:$A$18,MATCH(B43,SS_Amont!$E$11:$E$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(B43,SS_Amont!$E$11:$E$18,1)))))</f>
+        <f>IF(B43&lt;=Stage_Storage!E11,Stage_Storage!A11,IF(B43&gt;=Stage_Storage!E18,"Hors table (&gt;=40.0 m — étendre levé)",INDEX(Stage_Storage!$A$11:$A$18,MATCH(B43,Stage_Storage!$E$11:$E$18,1))+(B43-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B43,Stage_Storage!$E$11:$E$18,1)))/(INDEX(Stage_Storage!$E$11:$E$18,MATCH(B43,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(B43,Stage_Storage!$E$11:$E$18,1)))*(INDEX(Stage_Storage!$A$11:$A$18,MATCH(B43,Stage_Storage!$E$11:$E$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(B43,Stage_Storage!$E$11:$E$18,1)))))</f>
         <v/>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Même lecture volume→cote que B39 (SS_Amont), avec Vmax_B</t>
+          <t>Même lecture volume→cote que B39, mais avec Vmax_B</t>
         </is>
       </c>
     </row>
@@ -2362,1302 +2211,170 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Résultats Zone 2 — Ø900 → Ø1200 (SS_Aval + Calcul_Aval_A)</t>
+          <t>Comment lire WSEmax (A / B / C)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>V @ 37.28 m Zone 2 (m³) — SS_Aval</t>
-        </is>
-      </c>
-      <c r="B55" s="23">
-        <f>SS_Aval!B21</f>
-        <v/>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Volume levé Zone 2 à la cote patron</t>
+          <t>1) A et B: Vmax = volume pondé; WSEmax lu sur Stage_Storage (levé seul).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Vmax_Aval_A (m³)</t>
-        </is>
-      </c>
-      <c r="B56" s="20">
-        <f>Calcul_Aval_A!B6</f>
-        <v/>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Routage Aval: Qin≈Qcap Ø900; Qout=Q_plein Ø1200</t>
+          <t>2) C: Qout = Q_900(WSE) + Q_overflow(WSE); V = V_pond + V_ditch; WSEmax_C vient de Calcul_C.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>WSEmax_Aval_A (m) — SS_Aval</t>
-        </is>
-      </c>
-      <c r="B57" s="22">
-        <f>Calcul_Aval_A!B7</f>
-        <v/>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Lecture volume→cote sur levé Zone 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>Comment lire WSEmax (zones + méthodes)</t>
+          <t>3) Crest = crown = 35.78 m → au-dessus, le fossé trapèze (b, n, z, S, L) ajoute débit et volume.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>4) Ne pas comparer Vmax_C à V_pond seul sans retirer V_ditch; comparer plutôt les WSEmax.</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>1) Zone 1 (Ø1500→Ø900): A/B → Vmax puis WSEmax sur SS_Amont. Zone 2: SS_Aval + Calcul_Aval_A (B55–B57).</t>
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Inlet control vs outlet control — qu'est-ce que ça veut dire?</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2) C (Zone 1): Qout = Q_900(WSE)+Q_overflow; V = V_pond(SS_Amont)+V_ditch; WSEmax_C = Calcul_C.</t>
+          <t>• Inlet control (contrôle à l'entrée): le débit est limité par l'entrée du ponceau (forme d'entrée, HW/D).</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3) Crest = crown = 35.78 m → au-dessus, le fossé trapèze ajoute débit et volume (Zone 1).</t>
+          <t xml:space="preserve">  Le tuyau aval « n'aspire » pas assez pour influencer — Q dépend surtout de la charge amont H, pas de L ni de n.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>4) Ne pas additionner Zone 1+2 dans un seul routage. Éditer WSE/Surface jaunes dans SS_Amont et SS_Aval.</t>
+          <t>• Outlet control (contrôle à la sortie / frottement): le débit dépend de la longueur, de n, de la pente et de la charge</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (énergie amont → aval). Manning pleine section est une hypothèse de type outlet/frottement à section pleine.</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Inlet control vs outlet control — qu'est-ce que ça veut dire?</t>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>• Ici L/D = 56 (tuyau assez long) → le contrôle par frottement (outlet) est souvent plausible,</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>• Inlet control (contrôle à l'entrée): le débit est limité par l'entrée du ponceau (forme d'entrée, HW/D).</t>
+          <t xml:space="preserve">  mais sans analyse FHWA/HY-8 on ne peut pas l'affirmer. Pour dimensionner la rétention, Q_plein constant est</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Le tuyau aval « n'aspire » pas assez pour influencer — Q dépend surtout de la charge amont H, pas de L ni de n.</t>
+          <t xml:space="preserve">  en général prudent (si la charge monte, le débit réel peut être un peu plus élevé → Vmax un peu plus bas).</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>• Outlet control (contrôle à la sortie / frottement): le débit dépend de la longueur, de n, de la pente et de la charge</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (énergie amont → aval). Manning pleine section est une hypothèse de type outlet/frottement à section pleine.</t>
+          <t>• On n'a pas besoin de trancher IC/OC pour utiliser ce classeur: garder Qout = Q_plein (ou 1.77) suffit pour une 1re estimation.</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>• Ici L/D = 56 (tuyau assez long) → le contrôle par frottement (outlet) est souvent plausible,</t>
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">  mais sans analyse FHWA/HY-8 on ne peut pas l'affirmer. Pour dimensionner la rétention, Q_plein constant est</t>
+          <t>• Méthode A: Qout fixe = Q_plein Manning Ø900 (n=0,013).</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">  en général prudent (si la charge monte, le débit réel peut être un peu plus élevé → Vmax un peu plus bas).</t>
+          <t>• Méthode B: Qout = f(H) pipe seul (Courbe_QH_900) — résultats B43–B46.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>• On n'a pas besoin de trancher IC/OC pour utiliser ce classeur: garder Qout = Q_plein (ou 1.77) suffit pour une 1re estimation.</t>
+          <t>• Méthode C: Qout = Q_900 + Q_overflow; V = V_pond + V_ditch — Compose_900 + Calcul_C (B49–B52).</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>• Le stockage commence quand Qin dépasse Qout; Vmax = max du volume stocké.</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>• Méthode A: Qout fixe = Q_plein Manning Ø900 (n=0,013).</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>• Méthode B: Qout = f(H) pipe seul (Courbe_QH_900) — résultats B43–B46.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>• Méthode C: Qout = Q_900 + Q_overflow; V = V_pond + V_ditch — Compose_900 + Calcul_C (B49–B52).</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>• Zone 2: SS_Aval + Calcul_Aval_A — résultats B55–B57.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>• SS_Amont / SS_Aval: WSE et Surface en jaune — corriger depuis AutoCAD; ΔWSE et V_pas se recalculent.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>• Vérifier que le radier amont Ø900 (34.88) est bien le fond de Zone 1.</t>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>• Vérifier que le radier amont Ø900 (34.88) est bien le fond de la zone de rétention étudiée.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="19">
     <mergeCell ref="A67:H67"/>
-    <mergeCell ref="A77:H77"/>
     <mergeCell ref="A73:H73"/>
-    <mergeCell ref="A60:H60"/>
-    <mergeCell ref="A79:H79"/>
+    <mergeCell ref="A64:H64"/>
     <mergeCell ref="A61:H61"/>
-    <mergeCell ref="A70:H70"/>
-    <mergeCell ref="A78:H78"/>
-    <mergeCell ref="A69:H69"/>
+    <mergeCell ref="A65:H65"/>
     <mergeCell ref="A66:H66"/>
-    <mergeCell ref="A80:H80"/>
+    <mergeCell ref="A75:H75"/>
+    <mergeCell ref="A74:H74"/>
+    <mergeCell ref="A56:H56"/>
     <mergeCell ref="A9:H10"/>
+    <mergeCell ref="A55:H55"/>
+    <mergeCell ref="A57:H57"/>
     <mergeCell ref="A71:H71"/>
-    <mergeCell ref="A76:H76"/>
     <mergeCell ref="A62:H62"/>
-    <mergeCell ref="A81:H81"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A63:H63"/>
     <mergeCell ref="A72:H72"/>
     <mergeCell ref="A68:H68"/>
+    <mergeCell ref="A58:H58"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>Index levé — Zone 1 (SS_Amont) + Zone 2 (SS_Aval)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>Éditez les surfaces dans SS_Amont et SS_Aval (pas ici). Ce tableau compare A1+A2 vs total pour détecter un double comptage. GIS export = option pour sortir des polygones d'eau depuis AutoCAD/Civil 3D; vous n'en avez pas besoin si vous tapez les aires à la main depuis le plan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>WSE (m)</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>A_Zone1 (m²)</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>A_Zone2 (m²)</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>A1+A2 (m²)</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>V1 (m³)</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>V2 (m³)</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>V1+V2 (m³)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="32">
-        <f>SS_Amont!A11</f>
-        <v/>
-      </c>
-      <c r="B6" s="45">
-        <f>SS_Amont!B11</f>
-        <v/>
-      </c>
-      <c r="C6" s="45">
-        <f>SS_Aval!B11</f>
-        <v/>
-      </c>
-      <c r="D6" s="46">
-        <f>B6+C6</f>
-        <v/>
-      </c>
-      <c r="E6" s="26">
-        <f>SS_Amont!E11</f>
-        <v/>
-      </c>
-      <c r="F6" s="26">
-        <f>SS_Aval!E11</f>
-        <v/>
-      </c>
-      <c r="G6" s="34">
-        <f>E6+F6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="32">
-        <f>SS_Amont!A12</f>
-        <v/>
-      </c>
-      <c r="B7" s="45">
-        <f>SS_Amont!B12</f>
-        <v/>
-      </c>
-      <c r="C7" s="45">
-        <f>SS_Aval!B12</f>
-        <v/>
-      </c>
-      <c r="D7" s="46">
-        <f>B7+C7</f>
-        <v/>
-      </c>
-      <c r="E7" s="26">
-        <f>SS_Amont!E12</f>
-        <v/>
-      </c>
-      <c r="F7" s="26">
-        <f>SS_Aval!E12</f>
-        <v/>
-      </c>
-      <c r="G7" s="34">
-        <f>E7+F7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="32">
-        <f>SS_Amont!A13</f>
-        <v/>
-      </c>
-      <c r="B8" s="45">
-        <f>SS_Amont!B13</f>
-        <v/>
-      </c>
-      <c r="C8" s="45">
-        <f>SS_Aval!B13</f>
-        <v/>
-      </c>
-      <c r="D8" s="46">
-        <f>B8+C8</f>
-        <v/>
-      </c>
-      <c r="E8" s="26">
-        <f>SS_Amont!E13</f>
-        <v/>
-      </c>
-      <c r="F8" s="26">
-        <f>SS_Aval!E13</f>
-        <v/>
-      </c>
-      <c r="G8" s="34">
-        <f>E8+F8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="32">
-        <f>SS_Amont!A14</f>
-        <v/>
-      </c>
-      <c r="B9" s="45">
-        <f>SS_Amont!B14</f>
-        <v/>
-      </c>
-      <c r="C9" s="45">
-        <f>SS_Aval!B14</f>
-        <v/>
-      </c>
-      <c r="D9" s="46">
-        <f>B9+C9</f>
-        <v/>
-      </c>
-      <c r="E9" s="26">
-        <f>SS_Amont!E14</f>
-        <v/>
-      </c>
-      <c r="F9" s="26">
-        <f>SS_Aval!E14</f>
-        <v/>
-      </c>
-      <c r="G9" s="34">
-        <f>E9+F9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="32">
-        <f>SS_Amont!A15</f>
-        <v/>
-      </c>
-      <c r="B10" s="45">
-        <f>SS_Amont!B15</f>
-        <v/>
-      </c>
-      <c r="C10" s="45">
-        <f>SS_Aval!B15</f>
-        <v/>
-      </c>
-      <c r="D10" s="46">
-        <f>B10+C10</f>
-        <v/>
-      </c>
-      <c r="E10" s="26">
-        <f>SS_Amont!E15</f>
-        <v/>
-      </c>
-      <c r="F10" s="26">
-        <f>SS_Aval!E15</f>
-        <v/>
-      </c>
-      <c r="G10" s="34">
-        <f>E10+F10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="32">
-        <f>SS_Amont!A16</f>
-        <v/>
-      </c>
-      <c r="B11" s="45">
-        <f>SS_Amont!B16</f>
-        <v/>
-      </c>
-      <c r="C11" s="45">
-        <f>SS_Aval!B16</f>
-        <v/>
-      </c>
-      <c r="D11" s="46">
-        <f>B11+C11</f>
-        <v/>
-      </c>
-      <c r="E11" s="26">
-        <f>SS_Amont!E16</f>
-        <v/>
-      </c>
-      <c r="F11" s="26">
-        <f>SS_Aval!E16</f>
-        <v/>
-      </c>
-      <c r="G11" s="34">
-        <f>E11+F11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="32">
-        <f>SS_Amont!A17</f>
-        <v/>
-      </c>
-      <c r="B12" s="45">
-        <f>SS_Amont!B17</f>
-        <v/>
-      </c>
-      <c r="C12" s="45">
-        <f>SS_Aval!B17</f>
-        <v/>
-      </c>
-      <c r="D12" s="46">
-        <f>B12+C12</f>
-        <v/>
-      </c>
-      <c r="E12" s="26">
-        <f>SS_Amont!E17</f>
-        <v/>
-      </c>
-      <c r="F12" s="26">
-        <f>SS_Aval!E17</f>
-        <v/>
-      </c>
-      <c r="G12" s="34">
-        <f>E12+F12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="32">
-        <f>SS_Amont!A18</f>
-        <v/>
-      </c>
-      <c r="B13" s="45">
-        <f>SS_Amont!B18</f>
-        <v/>
-      </c>
-      <c r="C13" s="45">
-        <f>SS_Aval!B18</f>
-        <v/>
-      </c>
-      <c r="D13" s="46">
-        <f>B13+C13</f>
-        <v/>
-      </c>
-      <c r="E13" s="26">
-        <f>SS_Amont!E18</f>
-        <v/>
-      </c>
-      <c r="F13" s="26">
-        <f>SS_Aval!E18</f>
-        <v/>
-      </c>
-      <c r="G13" s="34">
-        <f>E13+F13</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:H3"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>Zone 2 — Méthode A: Qin = sortie Ø900; Qout = Q_plein Ø1200</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="40" t="inlineStr">
-        <is>
-          <t>Qin_aval ≈ débit livré par le Ø900 (Calcul_A colonne C = Qcap Ø900 quand le bassin amont stocke). Qout_aval = Parametres capacité Ø1200. Stockage sur SS_Aval. Souvent Vmax_Aval faible si Q_1200 ≫ Q_900.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Qout_Aval (m³/s)</t>
-        </is>
-      </c>
-      <c r="B5" s="30">
-        <f>4.93</f>
-        <v/>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Par défaut Q_plein Ø1200 — éditable</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Vmax_Aval_A (m³)</t>
-        </is>
-      </c>
-      <c r="B6" s="31">
-        <f>MAX(H10:H22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>WSEmax_Aval (m)</t>
-        </is>
-      </c>
-      <c r="B7" s="22">
-        <f>IF(B6&lt;=SS_Aval!E11,SS_Aval!A11,IF(B6&gt;=SS_Aval!E18,"Hors table (&gt;=40.0 m — étendre levé)",INDEX(SS_Aval!$A$11:$A$18,MATCH(B6,SS_Aval!$E$11:$E$18,1))+(B6-INDEX(SS_Aval!$E$11:$E$18,MATCH(B6,SS_Aval!$E$11:$E$18,1)))/(INDEX(SS_Aval!$E$11:$E$18,MATCH(B6,SS_Aval!$E$11:$E$18,1)+1)-INDEX(SS_Aval!$E$11:$E$18,MATCH(B6,SS_Aval!$E$11:$E$18,1)))*(INDEX(SS_Aval!$A$11:$A$18,MATCH(B6,SS_Aval!$E$11:$E$18,1)+1)-INDEX(SS_Aval!$A$11:$A$18,MATCH(B6,SS_Aval!$E$11:$E$18,1)))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>t (min)</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Qin_aval (m³/s)</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Qout_aval (m³/s)</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Qin−Qout</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Δt (s)</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>ΔVin (m³)</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>ΔVout (m³)</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>V stocké (m³)</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>Stockage?</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="26">
-        <f>Calcul_A!A8</f>
-        <v/>
-      </c>
-      <c r="B10" s="5">
-        <f>Calcul_A!C8</f>
-        <v/>
-      </c>
-      <c r="C10" s="32">
-        <f>$B$5</f>
-        <v/>
-      </c>
-      <c r="D10" s="5">
-        <f>B10-C10</f>
-        <v/>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="4">
-        <f>IF(H10&gt;0.5,"oui","non")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="26">
-        <f>Calcul_A!A9</f>
-        <v/>
-      </c>
-      <c r="B11" s="5">
-        <f>Calcul_A!C9</f>
-        <v/>
-      </c>
-      <c r="C11" s="32">
-        <f>$B$5</f>
-        <v/>
-      </c>
-      <c r="D11" s="5">
-        <f>B11-C11</f>
-        <v/>
-      </c>
-      <c r="E11" s="26">
-        <f>(A11-A10)*60</f>
-        <v/>
-      </c>
-      <c r="F11" s="26">
-        <f>0.5*(B10+B11)*E11</f>
-        <v/>
-      </c>
-      <c r="G11" s="26">
-        <f>F11-(H11-H10)</f>
-        <v/>
-      </c>
-      <c r="H11" s="34">
-        <f>MAX(0,H10+0.5*(D10+D11)*E11)</f>
-        <v/>
-      </c>
-      <c r="I11" s="4">
-        <f>IF(H11&gt;0.5,"oui","non")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="26">
-        <f>Calcul_A!A10</f>
-        <v/>
-      </c>
-      <c r="B12" s="5">
-        <f>Calcul_A!C10</f>
-        <v/>
-      </c>
-      <c r="C12" s="32">
-        <f>$B$5</f>
-        <v/>
-      </c>
-      <c r="D12" s="5">
-        <f>B12-C12</f>
-        <v/>
-      </c>
-      <c r="E12" s="26">
-        <f>(A12-A11)*60</f>
-        <v/>
-      </c>
-      <c r="F12" s="26">
-        <f>0.5*(B11+B12)*E12</f>
-        <v/>
-      </c>
-      <c r="G12" s="26">
-        <f>F12-(H12-H11)</f>
-        <v/>
-      </c>
-      <c r="H12" s="34">
-        <f>MAX(0,H11+0.5*(D11+D12)*E12)</f>
-        <v/>
-      </c>
-      <c r="I12" s="4">
-        <f>IF(H12&gt;0.5,"oui","non")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="26">
-        <f>Calcul_A!A11</f>
-        <v/>
-      </c>
-      <c r="B13" s="5">
-        <f>Calcul_A!C11</f>
-        <v/>
-      </c>
-      <c r="C13" s="32">
-        <f>$B$5</f>
-        <v/>
-      </c>
-      <c r="D13" s="5">
-        <f>B13-C13</f>
-        <v/>
-      </c>
-      <c r="E13" s="26">
-        <f>(A13-A12)*60</f>
-        <v/>
-      </c>
-      <c r="F13" s="26">
-        <f>0.5*(B12+B13)*E13</f>
-        <v/>
-      </c>
-      <c r="G13" s="26">
-        <f>F13-(H13-H12)</f>
-        <v/>
-      </c>
-      <c r="H13" s="34">
-        <f>MAX(0,H12+0.5*(D12+D13)*E13)</f>
-        <v/>
-      </c>
-      <c r="I13" s="4">
-        <f>IF(H13&gt;0.5,"oui","non")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="26">
-        <f>Calcul_A!A12</f>
-        <v/>
-      </c>
-      <c r="B14" s="5">
-        <f>Calcul_A!C12</f>
-        <v/>
-      </c>
-      <c r="C14" s="32">
-        <f>$B$5</f>
-        <v/>
-      </c>
-      <c r="D14" s="5">
-        <f>B14-C14</f>
-        <v/>
-      </c>
-      <c r="E14" s="26">
-        <f>(A14-A13)*60</f>
-        <v/>
-      </c>
-      <c r="F14" s="26">
-        <f>0.5*(B13+B14)*E14</f>
-        <v/>
-      </c>
-      <c r="G14" s="26">
-        <f>F14-(H14-H13)</f>
-        <v/>
-      </c>
-      <c r="H14" s="34">
-        <f>MAX(0,H13+0.5*(D13+D14)*E14)</f>
-        <v/>
-      </c>
-      <c r="I14" s="4">
-        <f>IF(H14&gt;0.5,"oui","non")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="26">
-        <f>Calcul_A!A13</f>
-        <v/>
-      </c>
-      <c r="B15" s="5">
-        <f>Calcul_A!C13</f>
-        <v/>
-      </c>
-      <c r="C15" s="32">
-        <f>$B$5</f>
-        <v/>
-      </c>
-      <c r="D15" s="5">
-        <f>B15-C15</f>
-        <v/>
-      </c>
-      <c r="E15" s="26">
-        <f>(A15-A14)*60</f>
-        <v/>
-      </c>
-      <c r="F15" s="26">
-        <f>0.5*(B14+B15)*E15</f>
-        <v/>
-      </c>
-      <c r="G15" s="26">
-        <f>F15-(H15-H14)</f>
-        <v/>
-      </c>
-      <c r="H15" s="34">
-        <f>MAX(0,H14+0.5*(D14+D15)*E15)</f>
-        <v/>
-      </c>
-      <c r="I15" s="4">
-        <f>IF(H15&gt;0.5,"oui","non")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="26">
-        <f>Calcul_A!A14</f>
-        <v/>
-      </c>
-      <c r="B16" s="5">
-        <f>Calcul_A!C14</f>
-        <v/>
-      </c>
-      <c r="C16" s="32">
-        <f>$B$5</f>
-        <v/>
-      </c>
-      <c r="D16" s="5">
-        <f>B16-C16</f>
-        <v/>
-      </c>
-      <c r="E16" s="26">
-        <f>(A16-A15)*60</f>
-        <v/>
-      </c>
-      <c r="F16" s="26">
-        <f>0.5*(B15+B16)*E16</f>
-        <v/>
-      </c>
-      <c r="G16" s="26">
-        <f>F16-(H16-H15)</f>
-        <v/>
-      </c>
-      <c r="H16" s="34">
-        <f>MAX(0,H15+0.5*(D15+D16)*E16)</f>
-        <v/>
-      </c>
-      <c r="I16" s="4">
-        <f>IF(H16&gt;0.5,"oui","non")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="26">
-        <f>Calcul_A!A15</f>
-        <v/>
-      </c>
-      <c r="B17" s="5">
-        <f>Calcul_A!C15</f>
-        <v/>
-      </c>
-      <c r="C17" s="32">
-        <f>$B$5</f>
-        <v/>
-      </c>
-      <c r="D17" s="5">
-        <f>B17-C17</f>
-        <v/>
-      </c>
-      <c r="E17" s="26">
-        <f>(A17-A16)*60</f>
-        <v/>
-      </c>
-      <c r="F17" s="26">
-        <f>0.5*(B16+B17)*E17</f>
-        <v/>
-      </c>
-      <c r="G17" s="26">
-        <f>F17-(H17-H16)</f>
-        <v/>
-      </c>
-      <c r="H17" s="34">
-        <f>MAX(0,H16+0.5*(D16+D17)*E17)</f>
-        <v/>
-      </c>
-      <c r="I17" s="4">
-        <f>IF(H17&gt;0.5,"oui","non")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="26">
-        <f>Calcul_A!A16</f>
-        <v/>
-      </c>
-      <c r="B18" s="5">
-        <f>Calcul_A!C16</f>
-        <v/>
-      </c>
-      <c r="C18" s="32">
-        <f>$B$5</f>
-        <v/>
-      </c>
-      <c r="D18" s="5">
-        <f>B18-C18</f>
-        <v/>
-      </c>
-      <c r="E18" s="26">
-        <f>(A18-A17)*60</f>
-        <v/>
-      </c>
-      <c r="F18" s="26">
-        <f>0.5*(B17+B18)*E18</f>
-        <v/>
-      </c>
-      <c r="G18" s="26">
-        <f>F18-(H18-H17)</f>
-        <v/>
-      </c>
-      <c r="H18" s="34">
-        <f>MAX(0,H17+0.5*(D17+D18)*E18)</f>
-        <v/>
-      </c>
-      <c r="I18" s="4">
-        <f>IF(H18&gt;0.5,"oui","non")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="26">
-        <f>Calcul_A!A17</f>
-        <v/>
-      </c>
-      <c r="B19" s="5">
-        <f>Calcul_A!C17</f>
-        <v/>
-      </c>
-      <c r="C19" s="32">
-        <f>$B$5</f>
-        <v/>
-      </c>
-      <c r="D19" s="5">
-        <f>B19-C19</f>
-        <v/>
-      </c>
-      <c r="E19" s="26">
-        <f>(A19-A18)*60</f>
-        <v/>
-      </c>
-      <c r="F19" s="26">
-        <f>0.5*(B18+B19)*E19</f>
-        <v/>
-      </c>
-      <c r="G19" s="26">
-        <f>F19-(H19-H18)</f>
-        <v/>
-      </c>
-      <c r="H19" s="34">
-        <f>MAX(0,H18+0.5*(D18+D19)*E19)</f>
-        <v/>
-      </c>
-      <c r="I19" s="4">
-        <f>IF(H19&gt;0.5,"oui","non")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="26">
-        <f>Calcul_A!A18</f>
-        <v/>
-      </c>
-      <c r="B20" s="5">
-        <f>Calcul_A!C18</f>
-        <v/>
-      </c>
-      <c r="C20" s="32">
-        <f>$B$5</f>
-        <v/>
-      </c>
-      <c r="D20" s="5">
-        <f>B20-C20</f>
-        <v/>
-      </c>
-      <c r="E20" s="26">
-        <f>(A20-A19)*60</f>
-        <v/>
-      </c>
-      <c r="F20" s="26">
-        <f>0.5*(B19+B20)*E20</f>
-        <v/>
-      </c>
-      <c r="G20" s="26">
-        <f>F20-(H20-H19)</f>
-        <v/>
-      </c>
-      <c r="H20" s="34">
-        <f>MAX(0,H19+0.5*(D19+D20)*E20)</f>
-        <v/>
-      </c>
-      <c r="I20" s="4">
-        <f>IF(H20&gt;0.5,"oui","non")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="26">
-        <f>Calcul_A!A19</f>
-        <v/>
-      </c>
-      <c r="B21" s="5">
-        <f>Calcul_A!C19</f>
-        <v/>
-      </c>
-      <c r="C21" s="32">
-        <f>$B$5</f>
-        <v/>
-      </c>
-      <c r="D21" s="5">
-        <f>B21-C21</f>
-        <v/>
-      </c>
-      <c r="E21" s="26">
-        <f>(A21-A20)*60</f>
-        <v/>
-      </c>
-      <c r="F21" s="26">
-        <f>0.5*(B20+B21)*E21</f>
-        <v/>
-      </c>
-      <c r="G21" s="26">
-        <f>F21-(H21-H20)</f>
-        <v/>
-      </c>
-      <c r="H21" s="34">
-        <f>MAX(0,H20+0.5*(D20+D21)*E21)</f>
-        <v/>
-      </c>
-      <c r="I21" s="4">
-        <f>IF(H21&gt;0.5,"oui","non")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="26">
-        <f>Calcul_A!A20</f>
-        <v/>
-      </c>
-      <c r="B22" s="5">
-        <f>Calcul_A!C20</f>
-        <v/>
-      </c>
-      <c r="C22" s="32">
-        <f>$B$5</f>
-        <v/>
-      </c>
-      <c r="D22" s="5">
-        <f>B22-C22</f>
-        <v/>
-      </c>
-      <c r="E22" s="26">
-        <f>(A22-A21)*60</f>
-        <v/>
-      </c>
-      <c r="F22" s="26">
-        <f>0.5*(B21+B22)*E22</f>
-        <v/>
-      </c>
-      <c r="G22" s="26">
-        <f>F22-(H22-H21)</f>
-        <v/>
-      </c>
-      <c r="H22" s="34">
-        <f>MAX(0,H21+0.5*(D21+D22)*E22)</f>
-        <v/>
-      </c>
-      <c r="I22" s="4">
-        <f>IF(H22&gt;0.5,"oui","non")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:I3"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="47" t="inlineStr">
-        <is>
-          <t>Où sont les fichiers HY-8 / capacité ?</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Ce classeur (rétention Ø900) :</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  engineering/drainage-design/retention_volume/Volume_Retention_Ponceau_900.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Courbe Q=f(H) FHWA pour CE Ø900 : feuille Courbe_QH_900 (ci-dessus).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Ancien Excel « type HY-8 / inlet-outlet » (autre projet / Ste-Thérèse) :</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  engineering/drainage-design/Ponceau_Capacite_Inlet_Outlet.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Branche git: cursor/culvert-excel-capacity-model-d87f</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Modèle composé ponceau Ø1050 + fossé (FHWA + remblai) — PAS le Ø900 de rétention :</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  engineering/drainage-design/ponceau_fosse_model/Ponceau_Fosse_Modele_Hydraulique.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Branche git: cursor/ponceau-fosse-hydraulic-model-d87f</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>HEC-RAS : pas de projet .ras/.hdf pour ce Ø900. Un DEM Ste-Thérèse est dans</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  engineering/hec-ras-data/ (données topo seulement).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Donc: on n'avait pas perdu un HY-8 pour ce bassin Ø900 — on avait des outils</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>similaires pour d'autres sites. La courbe de CE classeur remplace ça pour le Ø900.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3670,7 +2387,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="48" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>Méthode — volume de rétention</t>
         </is>
@@ -3762,7 +2479,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9. Niveau d'eau max Zone 1: A/B via SS_Amont; C via Calcul_C. Zone 2: SS_Aval + Calcul_Aval_A (B55–B57).</t>
+          <t>9. Niveau d'eau max: A/B via Stage_Storage; C via Calcul_C (Parametres B39 / B45 / B51).</t>
         </is>
       </c>
     </row>
@@ -3797,7 +2514,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Hydrogramme d'entrée (point Ø1500 / entrée rétention) — FORMULES LIVE</t>
         </is>
@@ -3832,7 +2549,7 @@
           <t>t pointe (min)</t>
         </is>
       </c>
-      <c r="B5" s="25" t="n">
+      <c r="B5" s="24" t="n">
         <v>22.5</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -3864,10 +2581,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="n">
+      <c r="A8" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="B8" s="27" t="n">
+      <c r="B8" s="26" t="n">
         <v>0.081042</v>
       </c>
       <c r="C8" s="5">
@@ -3881,10 +2598,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="n">
+      <c r="A9" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="27" t="n">
+      <c r="B9" s="26" t="n">
         <v>0.121875</v>
       </c>
       <c r="C9" s="5">
@@ -3894,10 +2611,10 @@
       <c r="D9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="n">
+      <c r="A10" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="B10" s="27" t="n">
+      <c r="B10" s="26" t="n">
         <v>0.193438</v>
       </c>
       <c r="C10" s="5">
@@ -3907,10 +2624,10 @@
       <c r="D10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="26" t="n">
+      <c r="A11" s="25" t="n">
         <v>15</v>
       </c>
-      <c r="B11" s="27" t="n">
+      <c r="B11" s="26" t="n">
         <v>0.333542</v>
       </c>
       <c r="C11" s="5">
@@ -3920,10 +2637,10 @@
       <c r="D11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="n">
+      <c r="A12" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="B12" s="27" t="n">
+      <c r="B12" s="26" t="n">
         <v>0.657188</v>
       </c>
       <c r="C12" s="5">
@@ -3933,10 +2650,10 @@
       <c r="D12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="n">
+      <c r="A13" s="25" t="n">
         <v>22.5</v>
       </c>
-      <c r="B13" s="27" t="n">
+      <c r="B13" s="26" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="8">
@@ -3950,10 +2667,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="n">
+      <c r="A14" s="25" t="n">
         <v>27.5</v>
       </c>
-      <c r="B14" s="27" t="n">
+      <c r="B14" s="26" t="n">
         <v>0.608958</v>
       </c>
       <c r="C14" s="5">
@@ -3963,10 +2680,10 @@
       <c r="D14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="n">
+      <c r="A15" s="25" t="n">
         <v>32.5</v>
       </c>
-      <c r="B15" s="27" t="n">
+      <c r="B15" s="26" t="n">
         <v>0.401771</v>
       </c>
       <c r="C15" s="5">
@@ -3976,10 +2693,10 @@
       <c r="D15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="n">
+      <c r="A16" s="25" t="n">
         <v>37.5</v>
       </c>
-      <c r="B16" s="27" t="n">
+      <c r="B16" s="26" t="n">
         <v>0.280104</v>
       </c>
       <c r="C16" s="5">
@@ -3989,10 +2706,10 @@
       <c r="D16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="26" t="n">
+      <c r="A17" s="25" t="n">
         <v>42.5</v>
       </c>
-      <c r="B17" s="27" t="n">
+      <c r="B17" s="26" t="n">
         <v>0.203438</v>
       </c>
       <c r="C17" s="5">
@@ -4002,10 +2719,10 @@
       <c r="D17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="26" t="n">
+      <c r="A18" s="25" t="n">
         <v>47.5</v>
       </c>
-      <c r="B18" s="27" t="n">
+      <c r="B18" s="26" t="n">
         <v>0.152292</v>
       </c>
       <c r="C18" s="5">
@@ -4015,10 +2732,10 @@
       <c r="D18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="26" t="n">
+      <c r="A19" s="25" t="n">
         <v>52.5</v>
       </c>
-      <c r="B19" s="27" t="n">
+      <c r="B19" s="26" t="n">
         <v>0.116771</v>
       </c>
       <c r="C19" s="5">
@@ -4028,10 +2745,10 @@
       <c r="D19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="26" t="n">
+      <c r="A20" s="25" t="n">
         <v>57.5</v>
       </c>
-      <c r="B20" s="27" t="n">
+      <c r="B20" s="26" t="n">
         <v>0.091146</v>
       </c>
       <c r="C20" s="5">
@@ -4046,7 +2763,7 @@
           <t>Qin max (contrôle)</t>
         </is>
       </c>
-      <c r="B22" s="28">
+      <c r="B22" s="27">
         <f>MAX(C8:C20)</f>
         <v/>
       </c>
@@ -4062,7 +2779,7 @@
           <t>Qcap Ø900 (réf.)</t>
         </is>
       </c>
-      <c r="B23" s="29">
+      <c r="B23" s="28">
         <f>Parametres!B22</f>
         <v/>
       </c>
@@ -4097,7 +2814,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Méthode A — Qout constant = capacité Ø900</t>
         </is>
@@ -4109,7 +2826,7 @@
           <t>Qout (m³/s)</t>
         </is>
       </c>
-      <c r="B2" s="30">
+      <c r="B2" s="29">
         <f>Parametres!B22</f>
         <v/>
       </c>
@@ -4120,7 +2837,7 @@
           <t>Vmax (m³)</t>
         </is>
       </c>
-      <c r="B3" s="31">
+      <c r="B3" s="30">
         <f>MAX(H8:H20)</f>
         <v/>
       </c>
@@ -4202,7 +2919,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26">
+      <c r="A8" s="25">
         <f>Hydrogramme!A8</f>
         <v/>
       </c>
@@ -4210,7 +2927,7 @@
         <f>Hydrogramme!C8</f>
         <v/>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="31">
         <f>$B$2</f>
         <v/>
       </c>
@@ -4227,7 +2944,7 @@
       <c r="G8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="33" t="n">
+      <c r="H8" s="32" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="4">
@@ -4236,7 +2953,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="26">
+      <c r="A9" s="25">
         <f>Hydrogramme!A9</f>
         <v/>
       </c>
@@ -4244,7 +2961,7 @@
         <f>Hydrogramme!C9</f>
         <v/>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="31">
         <f>$B$2</f>
         <v/>
       </c>
@@ -4252,19 +2969,19 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="25">
         <f>(A9-A8)*60</f>
         <v/>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="25">
         <f>0.5*(B8+B9)*E9</f>
         <v/>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="25">
         <f>F9-(H9-H8)</f>
         <v/>
       </c>
-      <c r="H9" s="34">
+      <c r="H9" s="33">
         <f>MAX(0,H8+0.5*(D8+D9)*E9)</f>
         <v/>
       </c>
@@ -4274,7 +2991,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="26">
+      <c r="A10" s="25">
         <f>Hydrogramme!A10</f>
         <v/>
       </c>
@@ -4282,7 +2999,7 @@
         <f>Hydrogramme!C10</f>
         <v/>
       </c>
-      <c r="C10" s="32">
+      <c r="C10" s="31">
         <f>$B$2</f>
         <v/>
       </c>
@@ -4290,19 +3007,19 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="25">
         <f>(A10-A9)*60</f>
         <v/>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="25">
         <f>0.5*(B9+B10)*E10</f>
         <v/>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="25">
         <f>F10-(H10-H9)</f>
         <v/>
       </c>
-      <c r="H10" s="34">
+      <c r="H10" s="33">
         <f>MAX(0,H9+0.5*(D9+D10)*E10)</f>
         <v/>
       </c>
@@ -4312,7 +3029,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="26">
+      <c r="A11" s="25">
         <f>Hydrogramme!A11</f>
         <v/>
       </c>
@@ -4320,7 +3037,7 @@
         <f>Hydrogramme!C11</f>
         <v/>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="31">
         <f>$B$2</f>
         <v/>
       </c>
@@ -4328,19 +3045,19 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="25">
         <f>(A11-A10)*60</f>
         <v/>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="25">
         <f>0.5*(B10+B11)*E11</f>
         <v/>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="25">
         <f>F11-(H11-H10)</f>
         <v/>
       </c>
-      <c r="H11" s="34">
+      <c r="H11" s="33">
         <f>MAX(0,H10+0.5*(D10+D11)*E11)</f>
         <v/>
       </c>
@@ -4350,7 +3067,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="26">
+      <c r="A12" s="25">
         <f>Hydrogramme!A12</f>
         <v/>
       </c>
@@ -4358,7 +3075,7 @@
         <f>Hydrogramme!C12</f>
         <v/>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="31">
         <f>$B$2</f>
         <v/>
       </c>
@@ -4366,19 +3083,19 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="25">
         <f>(A12-A11)*60</f>
         <v/>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="25">
         <f>0.5*(B11+B12)*E12</f>
         <v/>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="25">
         <f>F12-(H12-H11)</f>
         <v/>
       </c>
-      <c r="H12" s="34">
+      <c r="H12" s="33">
         <f>MAX(0,H11+0.5*(D11+D12)*E12)</f>
         <v/>
       </c>
@@ -4388,7 +3105,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="26">
+      <c r="A13" s="25">
         <f>Hydrogramme!A13</f>
         <v/>
       </c>
@@ -4396,7 +3113,7 @@
         <f>Hydrogramme!C13</f>
         <v/>
       </c>
-      <c r="C13" s="32">
+      <c r="C13" s="31">
         <f>$B$2</f>
         <v/>
       </c>
@@ -4404,19 +3121,19 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="25">
         <f>(A13-A12)*60</f>
         <v/>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="25">
         <f>0.5*(B12+B13)*E13</f>
         <v/>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="25">
         <f>F13-(H13-H12)</f>
         <v/>
       </c>
-      <c r="H13" s="34">
+      <c r="H13" s="33">
         <f>MAX(0,H12+0.5*(D12+D13)*E13)</f>
         <v/>
       </c>
@@ -4426,7 +3143,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="26">
+      <c r="A14" s="25">
         <f>Hydrogramme!A14</f>
         <v/>
       </c>
@@ -4434,7 +3151,7 @@
         <f>Hydrogramme!C14</f>
         <v/>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="31">
         <f>$B$2</f>
         <v/>
       </c>
@@ -4442,19 +3159,19 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="25">
         <f>(A14-A13)*60</f>
         <v/>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="25">
         <f>0.5*(B13+B14)*E14</f>
         <v/>
       </c>
-      <c r="G14" s="26">
+      <c r="G14" s="25">
         <f>F14-(H14-H13)</f>
         <v/>
       </c>
-      <c r="H14" s="34">
+      <c r="H14" s="33">
         <f>MAX(0,H13+0.5*(D13+D14)*E14)</f>
         <v/>
       </c>
@@ -4464,7 +3181,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="26">
+      <c r="A15" s="25">
         <f>Hydrogramme!A15</f>
         <v/>
       </c>
@@ -4472,7 +3189,7 @@
         <f>Hydrogramme!C15</f>
         <v/>
       </c>
-      <c r="C15" s="32">
+      <c r="C15" s="31">
         <f>$B$2</f>
         <v/>
       </c>
@@ -4480,19 +3197,19 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="25">
         <f>(A15-A14)*60</f>
         <v/>
       </c>
-      <c r="F15" s="26">
+      <c r="F15" s="25">
         <f>0.5*(B14+B15)*E15</f>
         <v/>
       </c>
-      <c r="G15" s="26">
+      <c r="G15" s="25">
         <f>F15-(H15-H14)</f>
         <v/>
       </c>
-      <c r="H15" s="34">
+      <c r="H15" s="33">
         <f>MAX(0,H14+0.5*(D14+D15)*E15)</f>
         <v/>
       </c>
@@ -4502,7 +3219,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="26">
+      <c r="A16" s="25">
         <f>Hydrogramme!A16</f>
         <v/>
       </c>
@@ -4510,7 +3227,7 @@
         <f>Hydrogramme!C16</f>
         <v/>
       </c>
-      <c r="C16" s="32">
+      <c r="C16" s="31">
         <f>$B$2</f>
         <v/>
       </c>
@@ -4518,19 +3235,19 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="25">
         <f>(A16-A15)*60</f>
         <v/>
       </c>
-      <c r="F16" s="26">
+      <c r="F16" s="25">
         <f>0.5*(B15+B16)*E16</f>
         <v/>
       </c>
-      <c r="G16" s="26">
+      <c r="G16" s="25">
         <f>F16-(H16-H15)</f>
         <v/>
       </c>
-      <c r="H16" s="34">
+      <c r="H16" s="33">
         <f>MAX(0,H15+0.5*(D15+D16)*E16)</f>
         <v/>
       </c>
@@ -4540,7 +3257,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="26">
+      <c r="A17" s="25">
         <f>Hydrogramme!A17</f>
         <v/>
       </c>
@@ -4548,7 +3265,7 @@
         <f>Hydrogramme!C17</f>
         <v/>
       </c>
-      <c r="C17" s="32">
+      <c r="C17" s="31">
         <f>$B$2</f>
         <v/>
       </c>
@@ -4556,19 +3273,19 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="25">
         <f>(A17-A16)*60</f>
         <v/>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="25">
         <f>0.5*(B16+B17)*E17</f>
         <v/>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="25">
         <f>F17-(H17-H16)</f>
         <v/>
       </c>
-      <c r="H17" s="34">
+      <c r="H17" s="33">
         <f>MAX(0,H16+0.5*(D16+D17)*E17)</f>
         <v/>
       </c>
@@ -4578,7 +3295,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="26">
+      <c r="A18" s="25">
         <f>Hydrogramme!A18</f>
         <v/>
       </c>
@@ -4586,7 +3303,7 @@
         <f>Hydrogramme!C18</f>
         <v/>
       </c>
-      <c r="C18" s="32">
+      <c r="C18" s="31">
         <f>$B$2</f>
         <v/>
       </c>
@@ -4594,19 +3311,19 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="25">
         <f>(A18-A17)*60</f>
         <v/>
       </c>
-      <c r="F18" s="26">
+      <c r="F18" s="25">
         <f>0.5*(B17+B18)*E18</f>
         <v/>
       </c>
-      <c r="G18" s="26">
+      <c r="G18" s="25">
         <f>F18-(H18-H17)</f>
         <v/>
       </c>
-      <c r="H18" s="34">
+      <c r="H18" s="33">
         <f>MAX(0,H17+0.5*(D17+D18)*E18)</f>
         <v/>
       </c>
@@ -4616,7 +3333,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="26">
+      <c r="A19" s="25">
         <f>Hydrogramme!A19</f>
         <v/>
       </c>
@@ -4624,7 +3341,7 @@
         <f>Hydrogramme!C19</f>
         <v/>
       </c>
-      <c r="C19" s="32">
+      <c r="C19" s="31">
         <f>$B$2</f>
         <v/>
       </c>
@@ -4632,19 +3349,19 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="26">
+      <c r="E19" s="25">
         <f>(A19-A18)*60</f>
         <v/>
       </c>
-      <c r="F19" s="26">
+      <c r="F19" s="25">
         <f>0.5*(B18+B19)*E19</f>
         <v/>
       </c>
-      <c r="G19" s="26">
+      <c r="G19" s="25">
         <f>F19-(H19-H18)</f>
         <v/>
       </c>
-      <c r="H19" s="34">
+      <c r="H19" s="33">
         <f>MAX(0,H18+0.5*(D18+D19)*E19)</f>
         <v/>
       </c>
@@ -4654,7 +3371,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="26">
+      <c r="A20" s="25">
         <f>Hydrogramme!A20</f>
         <v/>
       </c>
@@ -4662,7 +3379,7 @@
         <f>Hydrogramme!C20</f>
         <v/>
       </c>
-      <c r="C20" s="32">
+      <c r="C20" s="31">
         <f>$B$2</f>
         <v/>
       </c>
@@ -4670,19 +3387,19 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="25">
         <f>(A20-A19)*60</f>
         <v/>
       </c>
-      <c r="F20" s="26">
+      <c r="F20" s="25">
         <f>0.5*(B19+B20)*E20</f>
         <v/>
       </c>
-      <c r="G20" s="26">
+      <c r="G20" s="25">
         <f>F20-(H20-H19)</f>
         <v/>
       </c>
-      <c r="H20" s="34">
+      <c r="H20" s="33">
         <f>MAX(0,H19+0.5*(D19+D20)*E20)</f>
         <v/>
       </c>
@@ -4716,7 +3433,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Courbe de capacité Ø900 — Q = f(H) (FHWA HDS-5 inlet + outlet) — FORMULES LIVE</t>
         </is>
@@ -4756,32 +3473,32 @@
           <t>béton typ. 0.012–0.015</t>
         </is>
       </c>
-      <c r="E6" s="35" t="inlineStr">
+      <c r="E6" s="34" t="inlineStr">
         <is>
           <t>entrée</t>
         </is>
       </c>
-      <c r="F6" s="35" t="inlineStr">
+      <c r="F6" s="34" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="G6" s="35" t="inlineStr">
+      <c r="G6" s="34" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H6" s="35" t="inlineStr">
+      <c r="H6" s="34" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="I6" s="35" t="inlineStr">
+      <c r="I6" s="34" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J6" s="35" t="inlineStr">
+      <c r="J6" s="34" t="inlineStr">
         <is>
           <t>Ke</t>
         </is>
@@ -4897,7 +3614,7 @@
           <t>S0 = (Zin-Zout)/L</t>
         </is>
       </c>
-      <c r="B11" s="36">
+      <c r="B11" s="35">
         <f>(B9-B10)/B8</f>
         <v/>
       </c>
@@ -4928,7 +3645,7 @@
           <t>Entrée (texte exact)</t>
         </is>
       </c>
-      <c r="B13" s="37" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>square_edge</t>
         </is>
@@ -4945,7 +3662,7 @@
           <t>Q_plein Manning (réf.)</t>
         </is>
       </c>
-      <c r="B15" s="28">
+      <c r="B15" s="27">
         <f>(1/B6)*(PI()*B7^2/4)*((B7/4)^(2/3))*SQRT(B11)</f>
         <v/>
       </c>
@@ -4961,7 +3678,7 @@
           <t>K (lu)</t>
         </is>
       </c>
-      <c r="B17" s="38">
+      <c r="B17" s="37">
         <f>IFERROR(VLOOKUP(B13,$E$7:$J$9,2,FALSE),0.0098)</f>
         <v/>
       </c>
@@ -4972,7 +3689,7 @@
           <t>M (lu)</t>
         </is>
       </c>
-      <c r="B18" s="38">
+      <c r="B18" s="37">
         <f>IFERROR(VLOOKUP(B13,$E$7:$J$9,3,FALSE),2)</f>
         <v/>
       </c>
@@ -4983,7 +3700,7 @@
           <t>c (lu)</t>
         </is>
       </c>
-      <c r="B19" s="38">
+      <c r="B19" s="37">
         <f>IFERROR(VLOOKUP(B13,$E$7:$J$9,4,FALSE),0.0398)</f>
         <v/>
       </c>
@@ -4994,7 +3711,7 @@
           <t>Y (lu)</t>
         </is>
       </c>
-      <c r="B20" s="38">
+      <c r="B20" s="37">
         <f>IFERROR(VLOOKUP(B13,$E$7:$J$9,5,FALSE),0.67)</f>
         <v/>
       </c>
@@ -5005,7 +3722,7 @@
           <t>Ke (lu)</t>
         </is>
       </c>
-      <c r="B21" s="38">
+      <c r="B21" s="37">
         <f>IFERROR(VLOOKUP(B13,$E$7:$J$9,6,FALSE),0.5)</f>
         <v/>
       </c>
@@ -5043,10 +3760,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="32" t="n">
+      <c r="A24" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="B24" s="32">
+      <c r="B24" s="31">
         <f>$B$9+A24</f>
         <v/>
       </c>
@@ -5068,10 +3785,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="32" t="n">
+      <c r="A25" s="31" t="n">
         <v>0.05</v>
       </c>
-      <c r="B25" s="32">
+      <c r="B25" s="31">
         <f>$B$9+A25</f>
         <v/>
       </c>
@@ -5093,10 +3810,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="32" t="n">
+      <c r="A26" s="31" t="n">
         <v>0.1</v>
       </c>
-      <c r="B26" s="32">
+      <c r="B26" s="31">
         <f>$B$9+A26</f>
         <v/>
       </c>
@@ -5118,10 +3835,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="32" t="n">
+      <c r="A27" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="B27" s="32">
+      <c r="B27" s="31">
         <f>$B$9+A27</f>
         <v/>
       </c>
@@ -5143,10 +3860,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="32" t="n">
+      <c r="A28" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="B28" s="32">
+      <c r="B28" s="31">
         <f>$B$9+A28</f>
         <v/>
       </c>
@@ -5168,10 +3885,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="32" t="n">
+      <c r="A29" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="B29" s="32">
+      <c r="B29" s="31">
         <f>$B$9+A29</f>
         <v/>
       </c>
@@ -5193,10 +3910,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="32" t="n">
+      <c r="A30" s="31" t="n">
         <v>0.3</v>
       </c>
-      <c r="B30" s="32">
+      <c r="B30" s="31">
         <f>$B$9+A30</f>
         <v/>
       </c>
@@ -5218,10 +3935,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="32" t="n">
+      <c r="A31" s="31" t="n">
         <v>0.35</v>
       </c>
-      <c r="B31" s="32">
+      <c r="B31" s="31">
         <f>$B$9+A31</f>
         <v/>
       </c>
@@ -5243,10 +3960,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="32" t="n">
+      <c r="A32" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="B32" s="32">
+      <c r="B32" s="31">
         <f>$B$9+A32</f>
         <v/>
       </c>
@@ -5268,10 +3985,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="32" t="n">
+      <c r="A33" s="31" t="n">
         <v>0.45</v>
       </c>
-      <c r="B33" s="32">
+      <c r="B33" s="31">
         <f>$B$9+A33</f>
         <v/>
       </c>
@@ -5293,10 +4010,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="32" t="n">
+      <c r="A34" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="B34" s="32">
+      <c r="B34" s="31">
         <f>$B$9+A34</f>
         <v/>
       </c>
@@ -5318,10 +4035,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="32" t="n">
+      <c r="A35" s="31" t="n">
         <v>0.55</v>
       </c>
-      <c r="B35" s="32">
+      <c r="B35" s="31">
         <f>$B$9+A35</f>
         <v/>
       </c>
@@ -5343,10 +4060,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="32" t="n">
+      <c r="A36" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="B36" s="32">
+      <c r="B36" s="31">
         <f>$B$9+A36</f>
         <v/>
       </c>
@@ -5368,10 +4085,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="32" t="n">
+      <c r="A37" s="31" t="n">
         <v>0.65</v>
       </c>
-      <c r="B37" s="32">
+      <c r="B37" s="31">
         <f>$B$9+A37</f>
         <v/>
       </c>
@@ -5393,10 +4110,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="32" t="n">
+      <c r="A38" s="31" t="n">
         <v>0.7</v>
       </c>
-      <c r="B38" s="32">
+      <c r="B38" s="31">
         <f>$B$9+A38</f>
         <v/>
       </c>
@@ -5418,10 +4135,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="32" t="n">
+      <c r="A39" s="31" t="n">
         <v>0.75</v>
       </c>
-      <c r="B39" s="32">
+      <c r="B39" s="31">
         <f>$B$9+A39</f>
         <v/>
       </c>
@@ -5443,10 +4160,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="32" t="n">
+      <c r="A40" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="B40" s="32">
+      <c r="B40" s="31">
         <f>$B$9+A40</f>
         <v/>
       </c>
@@ -5468,10 +4185,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="32" t="n">
+      <c r="A41" s="31" t="n">
         <v>0.85</v>
       </c>
-      <c r="B41" s="32">
+      <c r="B41" s="31">
         <f>$B$9+A41</f>
         <v/>
       </c>
@@ -5493,10 +4210,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="32" t="n">
+      <c r="A42" s="31" t="n">
         <v>0.9</v>
       </c>
-      <c r="B42" s="32">
+      <c r="B42" s="31">
         <f>$B$9+A42</f>
         <v/>
       </c>
@@ -5518,10 +4235,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="32" t="n">
+      <c r="A43" s="31" t="n">
         <v>0.95</v>
       </c>
-      <c r="B43" s="32">
+      <c r="B43" s="31">
         <f>$B$9+A43</f>
         <v/>
       </c>
@@ -5543,10 +4260,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="32" t="n">
+      <c r="A44" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="B44" s="32">
+      <c r="B44" s="31">
         <f>$B$9+A44</f>
         <v/>
       </c>
@@ -5568,10 +4285,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="32" t="n">
+      <c r="A45" s="31" t="n">
         <v>1.05</v>
       </c>
-      <c r="B45" s="32">
+      <c r="B45" s="31">
         <f>$B$9+A45</f>
         <v/>
       </c>
@@ -5593,10 +4310,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="32" t="n">
+      <c r="A46" s="31" t="n">
         <v>1.1</v>
       </c>
-      <c r="B46" s="32">
+      <c r="B46" s="31">
         <f>$B$9+A46</f>
         <v/>
       </c>
@@ -5618,10 +4335,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="32" t="n">
+      <c r="A47" s="31" t="n">
         <v>1.15</v>
       </c>
-      <c r="B47" s="32">
+      <c r="B47" s="31">
         <f>$B$9+A47</f>
         <v/>
       </c>
@@ -5643,10 +4360,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="32" t="n">
+      <c r="A48" s="31" t="n">
         <v>1.2</v>
       </c>
-      <c r="B48" s="32">
+      <c r="B48" s="31">
         <f>$B$9+A48</f>
         <v/>
       </c>
@@ -5668,10 +4385,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="32" t="n">
+      <c r="A49" s="31" t="n">
         <v>1.25</v>
       </c>
-      <c r="B49" s="32">
+      <c r="B49" s="31">
         <f>$B$9+A49</f>
         <v/>
       </c>
@@ -5693,10 +4410,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="32" t="n">
+      <c r="A50" s="31" t="n">
         <v>1.3</v>
       </c>
-      <c r="B50" s="32">
+      <c r="B50" s="31">
         <f>$B$9+A50</f>
         <v/>
       </c>
@@ -5718,10 +4435,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="32" t="n">
+      <c r="A51" s="31" t="n">
         <v>1.35</v>
       </c>
-      <c r="B51" s="32">
+      <c r="B51" s="31">
         <f>$B$9+A51</f>
         <v/>
       </c>
@@ -5743,10 +4460,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="32" t="n">
+      <c r="A52" s="31" t="n">
         <v>1.4</v>
       </c>
-      <c r="B52" s="32">
+      <c r="B52" s="31">
         <f>$B$9+A52</f>
         <v/>
       </c>
@@ -5768,10 +4485,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="32" t="n">
+      <c r="A53" s="31" t="n">
         <v>1.45</v>
       </c>
-      <c r="B53" s="32">
+      <c r="B53" s="31">
         <f>$B$9+A53</f>
         <v/>
       </c>
@@ -5793,10 +4510,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="32" t="n">
+      <c r="A54" s="31" t="n">
         <v>1.5</v>
       </c>
-      <c r="B54" s="32">
+      <c r="B54" s="31">
         <f>$B$9+A54</f>
         <v/>
       </c>
@@ -5818,10 +4535,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="32" t="n">
+      <c r="A55" s="31" t="n">
         <v>1.55</v>
       </c>
-      <c r="B55" s="32">
+      <c r="B55" s="31">
         <f>$B$9+A55</f>
         <v/>
       </c>
@@ -5843,10 +4560,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="32" t="n">
+      <c r="A56" s="31" t="n">
         <v>1.6</v>
       </c>
-      <c r="B56" s="32">
+      <c r="B56" s="31">
         <f>$B$9+A56</f>
         <v/>
       </c>
@@ -5868,10 +4585,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="32" t="n">
+      <c r="A57" s="31" t="n">
         <v>1.65</v>
       </c>
-      <c r="B57" s="32">
+      <c r="B57" s="31">
         <f>$B$9+A57</f>
         <v/>
       </c>
@@ -5893,10 +4610,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="32" t="n">
+      <c r="A58" s="31" t="n">
         <v>1.7</v>
       </c>
-      <c r="B58" s="32">
+      <c r="B58" s="31">
         <f>$B$9+A58</f>
         <v/>
       </c>
@@ -5918,10 +4635,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="32" t="n">
+      <c r="A59" s="31" t="n">
         <v>1.75</v>
       </c>
-      <c r="B59" s="32">
+      <c r="B59" s="31">
         <f>$B$9+A59</f>
         <v/>
       </c>
@@ -5943,10 +4660,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="32" t="n">
+      <c r="A60" s="31" t="n">
         <v>1.8</v>
       </c>
-      <c r="B60" s="32">
+      <c r="B60" s="31">
         <f>$B$9+A60</f>
         <v/>
       </c>
@@ -5968,10 +4685,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="32" t="n">
+      <c r="A61" s="31" t="n">
         <v>1.85</v>
       </c>
-      <c r="B61" s="32">
+      <c r="B61" s="31">
         <f>$B$9+A61</f>
         <v/>
       </c>
@@ -5993,10 +4710,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="32" t="n">
+      <c r="A62" s="31" t="n">
         <v>1.9</v>
       </c>
-      <c r="B62" s="32">
+      <c r="B62" s="31">
         <f>$B$9+A62</f>
         <v/>
       </c>
@@ -6018,10 +4735,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="32" t="n">
+      <c r="A63" s="31" t="n">
         <v>1.95</v>
       </c>
-      <c r="B63" s="32">
+      <c r="B63" s="31">
         <f>$B$9+A63</f>
         <v/>
       </c>
@@ -6043,10 +4760,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="32" t="n">
+      <c r="A64" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B64" s="32">
+      <c r="B64" s="31">
         <f>$B$9+A64</f>
         <v/>
       </c>
@@ -6068,10 +4785,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="32" t="n">
+      <c r="A65" s="31" t="n">
         <v>2.05</v>
       </c>
-      <c r="B65" s="32">
+      <c r="B65" s="31">
         <f>$B$9+A65</f>
         <v/>
       </c>
@@ -6093,10 +4810,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="32" t="n">
+      <c r="A66" s="31" t="n">
         <v>2.1</v>
       </c>
-      <c r="B66" s="32">
+      <c r="B66" s="31">
         <f>$B$9+A66</f>
         <v/>
       </c>
@@ -6118,10 +4835,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="32" t="n">
+      <c r="A67" s="31" t="n">
         <v>2.15</v>
       </c>
-      <c r="B67" s="32">
+      <c r="B67" s="31">
         <f>$B$9+A67</f>
         <v/>
       </c>
@@ -6143,10 +4860,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="32" t="n">
+      <c r="A68" s="31" t="n">
         <v>2.2</v>
       </c>
-      <c r="B68" s="32">
+      <c r="B68" s="31">
         <f>$B$9+A68</f>
         <v/>
       </c>
@@ -6168,10 +4885,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="32" t="n">
+      <c r="A69" s="31" t="n">
         <v>2.25</v>
       </c>
-      <c r="B69" s="32">
+      <c r="B69" s="31">
         <f>$B$9+A69</f>
         <v/>
       </c>
@@ -6193,10 +4910,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="32" t="n">
+      <c r="A70" s="31" t="n">
         <v>2.3</v>
       </c>
-      <c r="B70" s="32">
+      <c r="B70" s="31">
         <f>$B$9+A70</f>
         <v/>
       </c>
@@ -6218,10 +4935,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="32" t="n">
+      <c r="A71" s="31" t="n">
         <v>2.35</v>
       </c>
-      <c r="B71" s="32">
+      <c r="B71" s="31">
         <f>$B$9+A71</f>
         <v/>
       </c>
@@ -6243,10 +4960,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="39" t="n">
+      <c r="A72" s="38" t="n">
         <v>2.4</v>
       </c>
-      <c r="B72" s="39">
+      <c r="B72" s="38">
         <f>$B$9+A72</f>
         <v/>
       </c>
@@ -6268,10 +4985,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="32" t="n">
+      <c r="A73" s="31" t="n">
         <v>2.45</v>
       </c>
-      <c r="B73" s="32">
+      <c r="B73" s="31">
         <f>$B$9+A73</f>
         <v/>
       </c>
@@ -6293,10 +5010,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="32" t="n">
+      <c r="A74" s="31" t="n">
         <v>2.5</v>
       </c>
-      <c r="B74" s="32">
+      <c r="B74" s="31">
         <f>$B$9+A74</f>
         <v/>
       </c>
@@ -6318,10 +5035,10 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="32" t="n">
+      <c r="A75" s="31" t="n">
         <v>2.55</v>
       </c>
-      <c r="B75" s="32">
+      <c r="B75" s="31">
         <f>$B$9+A75</f>
         <v/>
       </c>
@@ -6343,10 +5060,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="32" t="n">
+      <c r="A76" s="31" t="n">
         <v>2.6</v>
       </c>
-      <c r="B76" s="32">
+      <c r="B76" s="31">
         <f>$B$9+A76</f>
         <v/>
       </c>
@@ -6368,10 +5085,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="32" t="n">
+      <c r="A77" s="31" t="n">
         <v>2.65</v>
       </c>
-      <c r="B77" s="32">
+      <c r="B77" s="31">
         <f>$B$9+A77</f>
         <v/>
       </c>
@@ -6393,10 +5110,10 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="32" t="n">
+      <c r="A78" s="31" t="n">
         <v>2.7</v>
       </c>
-      <c r="B78" s="32">
+      <c r="B78" s="31">
         <f>$B$9+A78</f>
         <v/>
       </c>
@@ -6418,10 +5135,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="32" t="n">
+      <c r="A79" s="31" t="n">
         <v>2.75</v>
       </c>
-      <c r="B79" s="32">
+      <c r="B79" s="31">
         <f>$B$9+A79</f>
         <v/>
       </c>
@@ -6443,10 +5160,10 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="32" t="n">
+      <c r="A80" s="31" t="n">
         <v>2.8</v>
       </c>
-      <c r="B80" s="32">
+      <c r="B80" s="31">
         <f>$B$9+A80</f>
         <v/>
       </c>
@@ -6468,10 +5185,10 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="32" t="n">
+      <c r="A81" s="31" t="n">
         <v>2.85</v>
       </c>
-      <c r="B81" s="32">
+      <c r="B81" s="31">
         <f>$B$9+A81</f>
         <v/>
       </c>
@@ -6493,10 +5210,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="32" t="n">
+      <c r="A82" s="31" t="n">
         <v>2.9</v>
       </c>
-      <c r="B82" s="32">
+      <c r="B82" s="31">
         <f>$B$9+A82</f>
         <v/>
       </c>
@@ -6518,10 +5235,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="32" t="n">
+      <c r="A83" s="31" t="n">
         <v>2.95</v>
       </c>
-      <c r="B83" s="32">
+      <c r="B83" s="31">
         <f>$B$9+A83</f>
         <v/>
       </c>
@@ -6543,10 +5260,10 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="32" t="n">
+      <c r="A84" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="B84" s="32">
+      <c r="B84" s="31">
         <f>$B$9+A84</f>
         <v/>
       </c>
@@ -6595,16 +5312,16 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Méthode B — routage avec Qout = f(H) depuis Courbe_QH_900 (FHWA)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="40" t="inlineStr">
-        <is>
-          <t>H = V / Aire_constante (Parametres!B24) — raccourci, PAS le levé SS_Amont. Qout interpolé sur Courbe_QH_900!E (Q gouvernant). Si V≈0, Qout = MIN(Qin, Q_plein). ΔV = (Qin_moy - Qout)*Δt. Après routage, WSEmax_B réel est lu sur SS_Amont via Vmax_B (Parametres B45).</t>
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>H = V / Aire_constante (Parametres!B24) — raccourci, PAS le levé Stage_Storage. Qout interpolé sur Courbe_QH_900!E (Q gouvernant). Si V≈0, Qout = MIN(Qin, Q_plein). ΔV = (Qin_moy - Qout)*Δt. Après routage, WSEmax_B réel est lu sur Stage_Storage via Vmax_B (Parametres B45).</t>
         </is>
       </c>
     </row>
@@ -6615,7 +5332,7 @@
           <t>Aire (m²)</t>
         </is>
       </c>
-      <c r="B5" s="41">
+      <c r="B5" s="40">
         <f>Parametres!B24</f>
         <v/>
       </c>
@@ -6626,7 +5343,7 @@
           <t>Q_plein réf. (m³/s)</t>
         </is>
       </c>
-      <c r="B6" s="41">
+      <c r="B6" s="40">
         <f>Parametres!B22</f>
         <v/>
       </c>
@@ -6637,7 +5354,7 @@
           <t>Vmax_B (m³)</t>
         </is>
       </c>
-      <c r="B7" s="31">
+      <c r="B7" s="30">
         <f>MAX(G12:G24)</f>
         <v/>
       </c>
@@ -6709,10 +5426,10 @@
         <f>MIN(B12,$B$6)</f>
         <v/>
       </c>
-      <c r="F12" s="26" t="n">
+      <c r="F12" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="34" t="n">
+      <c r="G12" s="33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6737,11 +5454,11 @@
         <f>IF(G12&lt;=0.01,MIN(0.5*(B12+B13),$B$6),D13)</f>
         <v/>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="25">
         <f>(A13-A12)*60</f>
         <v/>
       </c>
-      <c r="G13" s="34">
+      <c r="G13" s="33">
         <f>MAX(0,G12+(0.5*(B12+B13)-E13)*F13)</f>
         <v/>
       </c>
@@ -6767,11 +5484,11 @@
         <f>IF(G13&lt;=0.01,MIN(0.5*(B13+B14),$B$6),D14)</f>
         <v/>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="25">
         <f>(A14-A13)*60</f>
         <v/>
       </c>
-      <c r="G14" s="34">
+      <c r="G14" s="33">
         <f>MAX(0,G13+(0.5*(B13+B14)-E14)*F14)</f>
         <v/>
       </c>
@@ -6797,11 +5514,11 @@
         <f>IF(G14&lt;=0.01,MIN(0.5*(B14+B15),$B$6),D15)</f>
         <v/>
       </c>
-      <c r="F15" s="26">
+      <c r="F15" s="25">
         <f>(A15-A14)*60</f>
         <v/>
       </c>
-      <c r="G15" s="34">
+      <c r="G15" s="33">
         <f>MAX(0,G14+(0.5*(B14+B15)-E15)*F15)</f>
         <v/>
       </c>
@@ -6827,11 +5544,11 @@
         <f>IF(G15&lt;=0.01,MIN(0.5*(B15+B16),$B$6),D16)</f>
         <v/>
       </c>
-      <c r="F16" s="26">
+      <c r="F16" s="25">
         <f>(A16-A15)*60</f>
         <v/>
       </c>
-      <c r="G16" s="34">
+      <c r="G16" s="33">
         <f>MAX(0,G15+(0.5*(B15+B16)-E16)*F16)</f>
         <v/>
       </c>
@@ -6857,11 +5574,11 @@
         <f>IF(G16&lt;=0.01,MIN(0.5*(B16+B17),$B$6),D17)</f>
         <v/>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="25">
         <f>(A17-A16)*60</f>
         <v/>
       </c>
-      <c r="G17" s="34">
+      <c r="G17" s="33">
         <f>MAX(0,G16+(0.5*(B16+B17)-E17)*F17)</f>
         <v/>
       </c>
@@ -6887,11 +5604,11 @@
         <f>IF(G17&lt;=0.01,MIN(0.5*(B17+B18),$B$6),D18)</f>
         <v/>
       </c>
-      <c r="F18" s="26">
+      <c r="F18" s="25">
         <f>(A18-A17)*60</f>
         <v/>
       </c>
-      <c r="G18" s="34">
+      <c r="G18" s="33">
         <f>MAX(0,G17+(0.5*(B17+B18)-E18)*F18)</f>
         <v/>
       </c>
@@ -6917,11 +5634,11 @@
         <f>IF(G18&lt;=0.01,MIN(0.5*(B18+B19),$B$6),D19)</f>
         <v/>
       </c>
-      <c r="F19" s="26">
+      <c r="F19" s="25">
         <f>(A19-A18)*60</f>
         <v/>
       </c>
-      <c r="G19" s="34">
+      <c r="G19" s="33">
         <f>MAX(0,G18+(0.5*(B18+B19)-E19)*F19)</f>
         <v/>
       </c>
@@ -6947,11 +5664,11 @@
         <f>IF(G19&lt;=0.01,MIN(0.5*(B19+B20),$B$6),D20)</f>
         <v/>
       </c>
-      <c r="F20" s="26">
+      <c r="F20" s="25">
         <f>(A20-A19)*60</f>
         <v/>
       </c>
-      <c r="G20" s="34">
+      <c r="G20" s="33">
         <f>MAX(0,G19+(0.5*(B19+B20)-E20)*F20)</f>
         <v/>
       </c>
@@ -6977,11 +5694,11 @@
         <f>IF(G20&lt;=0.01,MIN(0.5*(B20+B21),$B$6),D21)</f>
         <v/>
       </c>
-      <c r="F21" s="26">
+      <c r="F21" s="25">
         <f>(A21-A20)*60</f>
         <v/>
       </c>
-      <c r="G21" s="34">
+      <c r="G21" s="33">
         <f>MAX(0,G20+(0.5*(B20+B21)-E21)*F21)</f>
         <v/>
       </c>
@@ -7007,11 +5724,11 @@
         <f>IF(G21&lt;=0.01,MIN(0.5*(B21+B22),$B$6),D22)</f>
         <v/>
       </c>
-      <c r="F22" s="26">
+      <c r="F22" s="25">
         <f>(A22-A21)*60</f>
         <v/>
       </c>
-      <c r="G22" s="34">
+      <c r="G22" s="33">
         <f>MAX(0,G21+(0.5*(B21+B22)-E22)*F22)</f>
         <v/>
       </c>
@@ -7037,11 +5754,11 @@
         <f>IF(G22&lt;=0.01,MIN(0.5*(B22+B23),$B$6),D23)</f>
         <v/>
       </c>
-      <c r="F23" s="26">
+      <c r="F23" s="25">
         <f>(A23-A22)*60</f>
         <v/>
       </c>
-      <c r="G23" s="34">
+      <c r="G23" s="33">
         <f>MAX(0,G22+(0.5*(B22+B23)-E23)*F23)</f>
         <v/>
       </c>
@@ -7067,11 +5784,11 @@
         <f>IF(G23&lt;=0.01,MIN(0.5*(B23+B24),$B$6),D24)</f>
         <v/>
       </c>
-      <c r="F24" s="26">
+      <c r="F24" s="25">
         <f>(A24-A23)*60</f>
         <v/>
       </c>
-      <c r="G24" s="34">
+      <c r="G24" s="33">
         <f>MAX(0,G23+(0.5*(B23+B24)-E24)*F24)</f>
         <v/>
       </c>
@@ -7107,7 +5824,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Méthode C — courbe composée Ø900 + fossé trapèze (crest = crown)</t>
         </is>
@@ -7116,7 +5833,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Qout = Q_900(WSE) + Q_overflow(WSE). V_total = V_pond(SS_Amont) + V_ditch. Overflow: trapèze au-dessus du crown, Manning. Paramètres jaunes = Parametres!B27–B32.</t>
+          <t>Qout = Q_900(WSE) + Q_overflow(WSE). V_total = V_pond(Stage_Storage) + V_ditch. Overflow: trapèze au-dessus du crown, Manning. Paramètres jaunes = Parametres!B27–B32.</t>
         </is>
       </c>
     </row>
@@ -7263,14 +5980,14 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="32" t="n">
+      <c r="A15" s="31" t="n">
         <v>34.88</v>
       </c>
-      <c r="B15" s="32">
+      <c r="B15" s="31">
         <f>A15-$B$12</f>
         <v/>
       </c>
-      <c r="C15" s="32">
+      <c r="C15" s="31">
         <f>MAX(0,A15-$B$6)</f>
         <v/>
       </c>
@@ -7278,15 +5995,15 @@
         <f>IF(C15&lt;=0,0,($B$7+$B$9*C15)*C15)</f>
         <v/>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="25">
         <f>D15*$B$11</f>
         <v/>
       </c>
-      <c r="F15" s="26">
-        <f>IF(A15&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A15&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A15,SS_Amont!$A$11:$A$18,1))+(A15-INDEX(SS_Amont!$A$11:$A$18,MATCH(A15,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A15,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A15,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A15,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A15,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G15" s="34">
+      <c r="F15" s="25">
+        <f>IF(A15&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A15&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A15,Stage_Storage!$A$11:$A$18,1))+(A15-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A15,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A15,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A15,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A15,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A15,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G15" s="33">
         <f>E15+F15</f>
         <v/>
       </c>
@@ -7308,14 +6025,14 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="32" t="n">
+      <c r="A16" s="31" t="n">
         <v>34.93</v>
       </c>
-      <c r="B16" s="32">
+      <c r="B16" s="31">
         <f>A16-$B$12</f>
         <v/>
       </c>
-      <c r="C16" s="32">
+      <c r="C16" s="31">
         <f>MAX(0,A16-$B$6)</f>
         <v/>
       </c>
@@ -7323,15 +6040,15 @@
         <f>IF(C16&lt;=0,0,($B$7+$B$9*C16)*C16)</f>
         <v/>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="25">
         <f>D16*$B$11</f>
         <v/>
       </c>
-      <c r="F16" s="26">
-        <f>IF(A16&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A16&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A16,SS_Amont!$A$11:$A$18,1))+(A16-INDEX(SS_Amont!$A$11:$A$18,MATCH(A16,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A16,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A16,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A16,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A16,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G16" s="34">
+      <c r="F16" s="25">
+        <f>IF(A16&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A16&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A16,Stage_Storage!$A$11:$A$18,1))+(A16-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A16,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A16,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A16,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A16,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A16,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G16" s="33">
         <f>E16+F16</f>
         <v/>
       </c>
@@ -7353,14 +6070,14 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="32" t="n">
+      <c r="A17" s="31" t="n">
         <v>34.98</v>
       </c>
-      <c r="B17" s="32">
+      <c r="B17" s="31">
         <f>A17-$B$12</f>
         <v/>
       </c>
-      <c r="C17" s="32">
+      <c r="C17" s="31">
         <f>MAX(0,A17-$B$6)</f>
         <v/>
       </c>
@@ -7368,15 +6085,15 @@
         <f>IF(C17&lt;=0,0,($B$7+$B$9*C17)*C17)</f>
         <v/>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="25">
         <f>D17*$B$11</f>
         <v/>
       </c>
-      <c r="F17" s="26">
-        <f>IF(A17&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A17&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A17,SS_Amont!$A$11:$A$18,1))+(A17-INDEX(SS_Amont!$A$11:$A$18,MATCH(A17,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A17,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A17,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A17,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A17,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G17" s="34">
+      <c r="F17" s="25">
+        <f>IF(A17&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A17&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A17,Stage_Storage!$A$11:$A$18,1))+(A17-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A17,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A17,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A17,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A17,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A17,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G17" s="33">
         <f>E17+F17</f>
         <v/>
       </c>
@@ -7398,14 +6115,14 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="32" t="n">
+      <c r="A18" s="31" t="n">
         <v>35.03</v>
       </c>
-      <c r="B18" s="32">
+      <c r="B18" s="31">
         <f>A18-$B$12</f>
         <v/>
       </c>
-      <c r="C18" s="32">
+      <c r="C18" s="31">
         <f>MAX(0,A18-$B$6)</f>
         <v/>
       </c>
@@ -7413,15 +6130,15 @@
         <f>IF(C18&lt;=0,0,($B$7+$B$9*C18)*C18)</f>
         <v/>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="25">
         <f>D18*$B$11</f>
         <v/>
       </c>
-      <c r="F18" s="26">
-        <f>IF(A18&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A18&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A18,SS_Amont!$A$11:$A$18,1))+(A18-INDEX(SS_Amont!$A$11:$A$18,MATCH(A18,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A18,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A18,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A18,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A18,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G18" s="34">
+      <c r="F18" s="25">
+        <f>IF(A18&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A18&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A18,Stage_Storage!$A$11:$A$18,1))+(A18-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A18,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A18,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A18,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A18,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A18,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G18" s="33">
         <f>E18+F18</f>
         <v/>
       </c>
@@ -7443,14 +6160,14 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="32" t="n">
+      <c r="A19" s="31" t="n">
         <v>35.08</v>
       </c>
-      <c r="B19" s="32">
+      <c r="B19" s="31">
         <f>A19-$B$12</f>
         <v/>
       </c>
-      <c r="C19" s="32">
+      <c r="C19" s="31">
         <f>MAX(0,A19-$B$6)</f>
         <v/>
       </c>
@@ -7458,15 +6175,15 @@
         <f>IF(C19&lt;=0,0,($B$7+$B$9*C19)*C19)</f>
         <v/>
       </c>
-      <c r="E19" s="26">
+      <c r="E19" s="25">
         <f>D19*$B$11</f>
         <v/>
       </c>
-      <c r="F19" s="26">
-        <f>IF(A19&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A19&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A19,SS_Amont!$A$11:$A$18,1))+(A19-INDEX(SS_Amont!$A$11:$A$18,MATCH(A19,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A19,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A19,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A19,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A19,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G19" s="34">
+      <c r="F19" s="25">
+        <f>IF(A19&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A19&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A19,Stage_Storage!$A$11:$A$18,1))+(A19-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A19,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A19,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A19,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A19,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A19,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G19" s="33">
         <f>E19+F19</f>
         <v/>
       </c>
@@ -7488,14 +6205,14 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="32" t="n">
+      <c r="A20" s="31" t="n">
         <v>35.13</v>
       </c>
-      <c r="B20" s="32">
+      <c r="B20" s="31">
         <f>A20-$B$12</f>
         <v/>
       </c>
-      <c r="C20" s="32">
+      <c r="C20" s="31">
         <f>MAX(0,A20-$B$6)</f>
         <v/>
       </c>
@@ -7503,15 +6220,15 @@
         <f>IF(C20&lt;=0,0,($B$7+$B$9*C20)*C20)</f>
         <v/>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="25">
         <f>D20*$B$11</f>
         <v/>
       </c>
-      <c r="F20" s="26">
-        <f>IF(A20&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A20&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A20,SS_Amont!$A$11:$A$18,1))+(A20-INDEX(SS_Amont!$A$11:$A$18,MATCH(A20,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A20,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A20,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A20,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A20,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G20" s="34">
+      <c r="F20" s="25">
+        <f>IF(A20&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A20&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A20,Stage_Storage!$A$11:$A$18,1))+(A20-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A20,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A20,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A20,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A20,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A20,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G20" s="33">
         <f>E20+F20</f>
         <v/>
       </c>
@@ -7533,14 +6250,14 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="32" t="n">
+      <c r="A21" s="31" t="n">
         <v>35.18</v>
       </c>
-      <c r="B21" s="32">
+      <c r="B21" s="31">
         <f>A21-$B$12</f>
         <v/>
       </c>
-      <c r="C21" s="32">
+      <c r="C21" s="31">
         <f>MAX(0,A21-$B$6)</f>
         <v/>
       </c>
@@ -7548,15 +6265,15 @@
         <f>IF(C21&lt;=0,0,($B$7+$B$9*C21)*C21)</f>
         <v/>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="25">
         <f>D21*$B$11</f>
         <v/>
       </c>
-      <c r="F21" s="26">
-        <f>IF(A21&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A21&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A21,SS_Amont!$A$11:$A$18,1))+(A21-INDEX(SS_Amont!$A$11:$A$18,MATCH(A21,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A21,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A21,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A21,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A21,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G21" s="34">
+      <c r="F21" s="25">
+        <f>IF(A21&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A21&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A21,Stage_Storage!$A$11:$A$18,1))+(A21-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A21,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A21,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A21,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A21,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A21,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G21" s="33">
         <f>E21+F21</f>
         <v/>
       </c>
@@ -7578,14 +6295,14 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="32" t="n">
+      <c r="A22" s="31" t="n">
         <v>35.23</v>
       </c>
-      <c r="B22" s="32">
+      <c r="B22" s="31">
         <f>A22-$B$12</f>
         <v/>
       </c>
-      <c r="C22" s="32">
+      <c r="C22" s="31">
         <f>MAX(0,A22-$B$6)</f>
         <v/>
       </c>
@@ -7593,15 +6310,15 @@
         <f>IF(C22&lt;=0,0,($B$7+$B$9*C22)*C22)</f>
         <v/>
       </c>
-      <c r="E22" s="26">
+      <c r="E22" s="25">
         <f>D22*$B$11</f>
         <v/>
       </c>
-      <c r="F22" s="26">
-        <f>IF(A22&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A22&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A22,SS_Amont!$A$11:$A$18,1))+(A22-INDEX(SS_Amont!$A$11:$A$18,MATCH(A22,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A22,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A22,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A22,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A22,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G22" s="34">
+      <c r="F22" s="25">
+        <f>IF(A22&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A22&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A22,Stage_Storage!$A$11:$A$18,1))+(A22-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A22,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A22,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A22,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A22,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A22,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G22" s="33">
         <f>E22+F22</f>
         <v/>
       </c>
@@ -7623,14 +6340,14 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="32" t="n">
+      <c r="A23" s="31" t="n">
         <v>35.28</v>
       </c>
-      <c r="B23" s="32">
+      <c r="B23" s="31">
         <f>A23-$B$12</f>
         <v/>
       </c>
-      <c r="C23" s="32">
+      <c r="C23" s="31">
         <f>MAX(0,A23-$B$6)</f>
         <v/>
       </c>
@@ -7638,15 +6355,15 @@
         <f>IF(C23&lt;=0,0,($B$7+$B$9*C23)*C23)</f>
         <v/>
       </c>
-      <c r="E23" s="26">
+      <c r="E23" s="25">
         <f>D23*$B$11</f>
         <v/>
       </c>
-      <c r="F23" s="26">
-        <f>IF(A23&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A23&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A23,SS_Amont!$A$11:$A$18,1))+(A23-INDEX(SS_Amont!$A$11:$A$18,MATCH(A23,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A23,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A23,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A23,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A23,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G23" s="34">
+      <c r="F23" s="25">
+        <f>IF(A23&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A23&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A23,Stage_Storage!$A$11:$A$18,1))+(A23-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A23,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A23,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A23,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A23,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A23,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G23" s="33">
         <f>E23+F23</f>
         <v/>
       </c>
@@ -7668,14 +6385,14 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="32" t="n">
+      <c r="A24" s="31" t="n">
         <v>35.33</v>
       </c>
-      <c r="B24" s="32">
+      <c r="B24" s="31">
         <f>A24-$B$12</f>
         <v/>
       </c>
-      <c r="C24" s="32">
+      <c r="C24" s="31">
         <f>MAX(0,A24-$B$6)</f>
         <v/>
       </c>
@@ -7683,15 +6400,15 @@
         <f>IF(C24&lt;=0,0,($B$7+$B$9*C24)*C24)</f>
         <v/>
       </c>
-      <c r="E24" s="26">
+      <c r="E24" s="25">
         <f>D24*$B$11</f>
         <v/>
       </c>
-      <c r="F24" s="26">
-        <f>IF(A24&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A24&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A24,SS_Amont!$A$11:$A$18,1))+(A24-INDEX(SS_Amont!$A$11:$A$18,MATCH(A24,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A24,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A24,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A24,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A24,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G24" s="34">
+      <c r="F24" s="25">
+        <f>IF(A24&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A24&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A24,Stage_Storage!$A$11:$A$18,1))+(A24-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A24,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A24,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A24,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A24,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A24,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G24" s="33">
         <f>E24+F24</f>
         <v/>
       </c>
@@ -7713,14 +6430,14 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="32" t="n">
+      <c r="A25" s="31" t="n">
         <v>35.38</v>
       </c>
-      <c r="B25" s="32">
+      <c r="B25" s="31">
         <f>A25-$B$12</f>
         <v/>
       </c>
-      <c r="C25" s="32">
+      <c r="C25" s="31">
         <f>MAX(0,A25-$B$6)</f>
         <v/>
       </c>
@@ -7728,15 +6445,15 @@
         <f>IF(C25&lt;=0,0,($B$7+$B$9*C25)*C25)</f>
         <v/>
       </c>
-      <c r="E25" s="26">
+      <c r="E25" s="25">
         <f>D25*$B$11</f>
         <v/>
       </c>
-      <c r="F25" s="26">
-        <f>IF(A25&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A25&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A25,SS_Amont!$A$11:$A$18,1))+(A25-INDEX(SS_Amont!$A$11:$A$18,MATCH(A25,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A25,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A25,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A25,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A25,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G25" s="34">
+      <c r="F25" s="25">
+        <f>IF(A25&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A25&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A25,Stage_Storage!$A$11:$A$18,1))+(A25-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A25,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A25,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A25,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A25,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A25,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G25" s="33">
         <f>E25+F25</f>
         <v/>
       </c>
@@ -7758,14 +6475,14 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="32" t="n">
+      <c r="A26" s="31" t="n">
         <v>35.43</v>
       </c>
-      <c r="B26" s="32">
+      <c r="B26" s="31">
         <f>A26-$B$12</f>
         <v/>
       </c>
-      <c r="C26" s="32">
+      <c r="C26" s="31">
         <f>MAX(0,A26-$B$6)</f>
         <v/>
       </c>
@@ -7773,15 +6490,15 @@
         <f>IF(C26&lt;=0,0,($B$7+$B$9*C26)*C26)</f>
         <v/>
       </c>
-      <c r="E26" s="26">
+      <c r="E26" s="25">
         <f>D26*$B$11</f>
         <v/>
       </c>
-      <c r="F26" s="26">
-        <f>IF(A26&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A26&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A26,SS_Amont!$A$11:$A$18,1))+(A26-INDEX(SS_Amont!$A$11:$A$18,MATCH(A26,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A26,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A26,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A26,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A26,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G26" s="34">
+      <c r="F26" s="25">
+        <f>IF(A26&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A26&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A26,Stage_Storage!$A$11:$A$18,1))+(A26-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A26,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A26,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A26,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A26,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A26,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G26" s="33">
         <f>E26+F26</f>
         <v/>
       </c>
@@ -7803,14 +6520,14 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="32" t="n">
+      <c r="A27" s="31" t="n">
         <v>35.48</v>
       </c>
-      <c r="B27" s="32">
+      <c r="B27" s="31">
         <f>A27-$B$12</f>
         <v/>
       </c>
-      <c r="C27" s="32">
+      <c r="C27" s="31">
         <f>MAX(0,A27-$B$6)</f>
         <v/>
       </c>
@@ -7818,15 +6535,15 @@
         <f>IF(C27&lt;=0,0,($B$7+$B$9*C27)*C27)</f>
         <v/>
       </c>
-      <c r="E27" s="26">
+      <c r="E27" s="25">
         <f>D27*$B$11</f>
         <v/>
       </c>
-      <c r="F27" s="26">
-        <f>IF(A27&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A27&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A27,SS_Amont!$A$11:$A$18,1))+(A27-INDEX(SS_Amont!$A$11:$A$18,MATCH(A27,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A27,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A27,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A27,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A27,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G27" s="34">
+      <c r="F27" s="25">
+        <f>IF(A27&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A27&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A27,Stage_Storage!$A$11:$A$18,1))+(A27-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A27,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A27,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A27,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A27,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A27,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G27" s="33">
         <f>E27+F27</f>
         <v/>
       </c>
@@ -7848,14 +6565,14 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="32" t="n">
+      <c r="A28" s="31" t="n">
         <v>35.53</v>
       </c>
-      <c r="B28" s="32">
+      <c r="B28" s="31">
         <f>A28-$B$12</f>
         <v/>
       </c>
-      <c r="C28" s="32">
+      <c r="C28" s="31">
         <f>MAX(0,A28-$B$6)</f>
         <v/>
       </c>
@@ -7863,15 +6580,15 @@
         <f>IF(C28&lt;=0,0,($B$7+$B$9*C28)*C28)</f>
         <v/>
       </c>
-      <c r="E28" s="26">
+      <c r="E28" s="25">
         <f>D28*$B$11</f>
         <v/>
       </c>
-      <c r="F28" s="26">
-        <f>IF(A28&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A28&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A28,SS_Amont!$A$11:$A$18,1))+(A28-INDEX(SS_Amont!$A$11:$A$18,MATCH(A28,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A28,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A28,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A28,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A28,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G28" s="34">
+      <c r="F28" s="25">
+        <f>IF(A28&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A28&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A28,Stage_Storage!$A$11:$A$18,1))+(A28-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A28,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A28,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A28,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A28,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A28,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G28" s="33">
         <f>E28+F28</f>
         <v/>
       </c>
@@ -7893,14 +6610,14 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="32" t="n">
+      <c r="A29" s="31" t="n">
         <v>35.58</v>
       </c>
-      <c r="B29" s="32">
+      <c r="B29" s="31">
         <f>A29-$B$12</f>
         <v/>
       </c>
-      <c r="C29" s="32">
+      <c r="C29" s="31">
         <f>MAX(0,A29-$B$6)</f>
         <v/>
       </c>
@@ -7908,15 +6625,15 @@
         <f>IF(C29&lt;=0,0,($B$7+$B$9*C29)*C29)</f>
         <v/>
       </c>
-      <c r="E29" s="26">
+      <c r="E29" s="25">
         <f>D29*$B$11</f>
         <v/>
       </c>
-      <c r="F29" s="26">
-        <f>IF(A29&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A29&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A29,SS_Amont!$A$11:$A$18,1))+(A29-INDEX(SS_Amont!$A$11:$A$18,MATCH(A29,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A29,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A29,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A29,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A29,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G29" s="34">
+      <c r="F29" s="25">
+        <f>IF(A29&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A29&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A29,Stage_Storage!$A$11:$A$18,1))+(A29-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A29,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A29,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A29,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A29,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A29,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G29" s="33">
         <f>E29+F29</f>
         <v/>
       </c>
@@ -7938,14 +6655,14 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="32" t="n">
+      <c r="A30" s="31" t="n">
         <v>35.63</v>
       </c>
-      <c r="B30" s="32">
+      <c r="B30" s="31">
         <f>A30-$B$12</f>
         <v/>
       </c>
-      <c r="C30" s="32">
+      <c r="C30" s="31">
         <f>MAX(0,A30-$B$6)</f>
         <v/>
       </c>
@@ -7953,15 +6670,15 @@
         <f>IF(C30&lt;=0,0,($B$7+$B$9*C30)*C30)</f>
         <v/>
       </c>
-      <c r="E30" s="26">
+      <c r="E30" s="25">
         <f>D30*$B$11</f>
         <v/>
       </c>
-      <c r="F30" s="26">
-        <f>IF(A30&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A30&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A30,SS_Amont!$A$11:$A$18,1))+(A30-INDEX(SS_Amont!$A$11:$A$18,MATCH(A30,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A30,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A30,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A30,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A30,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G30" s="34">
+      <c r="F30" s="25">
+        <f>IF(A30&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A30&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A30,Stage_Storage!$A$11:$A$18,1))+(A30-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A30,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A30,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A30,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A30,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A30,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G30" s="33">
         <f>E30+F30</f>
         <v/>
       </c>
@@ -7983,14 +6700,14 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="32" t="n">
+      <c r="A31" s="31" t="n">
         <v>35.68</v>
       </c>
-      <c r="B31" s="32">
+      <c r="B31" s="31">
         <f>A31-$B$12</f>
         <v/>
       </c>
-      <c r="C31" s="32">
+      <c r="C31" s="31">
         <f>MAX(0,A31-$B$6)</f>
         <v/>
       </c>
@@ -7998,15 +6715,15 @@
         <f>IF(C31&lt;=0,0,($B$7+$B$9*C31)*C31)</f>
         <v/>
       </c>
-      <c r="E31" s="26">
+      <c r="E31" s="25">
         <f>D31*$B$11</f>
         <v/>
       </c>
-      <c r="F31" s="26">
-        <f>IF(A31&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A31&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A31,SS_Amont!$A$11:$A$18,1))+(A31-INDEX(SS_Amont!$A$11:$A$18,MATCH(A31,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A31,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A31,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A31,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A31,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G31" s="34">
+      <c r="F31" s="25">
+        <f>IF(A31&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A31&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A31,Stage_Storage!$A$11:$A$18,1))+(A31-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A31,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A31,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A31,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A31,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A31,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G31" s="33">
         <f>E31+F31</f>
         <v/>
       </c>
@@ -8028,14 +6745,14 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="32" t="n">
+      <c r="A32" s="31" t="n">
         <v>35.73</v>
       </c>
-      <c r="B32" s="32">
+      <c r="B32" s="31">
         <f>A32-$B$12</f>
         <v/>
       </c>
-      <c r="C32" s="32">
+      <c r="C32" s="31">
         <f>MAX(0,A32-$B$6)</f>
         <v/>
       </c>
@@ -8043,15 +6760,15 @@
         <f>IF(C32&lt;=0,0,($B$7+$B$9*C32)*C32)</f>
         <v/>
       </c>
-      <c r="E32" s="26">
+      <c r="E32" s="25">
         <f>D32*$B$11</f>
         <v/>
       </c>
-      <c r="F32" s="26">
-        <f>IF(A32&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A32&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A32,SS_Amont!$A$11:$A$18,1))+(A32-INDEX(SS_Amont!$A$11:$A$18,MATCH(A32,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A32,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A32,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A32,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A32,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G32" s="34">
+      <c r="F32" s="25">
+        <f>IF(A32&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A32&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A32,Stage_Storage!$A$11:$A$18,1))+(A32-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A32,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A32,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A32,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A32,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A32,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G32" s="33">
         <f>E32+F32</f>
         <v/>
       </c>
@@ -8073,14 +6790,14 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="39" t="n">
+      <c r="A33" s="38" t="n">
         <v>35.78</v>
       </c>
-      <c r="B33" s="39">
+      <c r="B33" s="38">
         <f>A33-$B$12</f>
         <v/>
       </c>
-      <c r="C33" s="39">
+      <c r="C33" s="38">
         <f>MAX(0,A33-$B$6)</f>
         <v/>
       </c>
@@ -8088,15 +6805,15 @@
         <f>IF(C33&lt;=0,0,($B$7+$B$9*C33)*C33)</f>
         <v/>
       </c>
-      <c r="E33" s="42">
+      <c r="E33" s="41">
         <f>D33*$B$11</f>
         <v/>
       </c>
-      <c r="F33" s="42">
-        <f>IF(A33&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A33&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A33,SS_Amont!$A$11:$A$18,1))+(A33-INDEX(SS_Amont!$A$11:$A$18,MATCH(A33,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A33,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A33,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A33,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A33,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G33" s="34">
+      <c r="F33" s="41">
+        <f>IF(A33&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A33&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A33,Stage_Storage!$A$11:$A$18,1))+(A33-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A33,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A33,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A33,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A33,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A33,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G33" s="33">
         <f>E33+F33</f>
         <v/>
       </c>
@@ -8118,14 +6835,14 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="32" t="n">
+      <c r="A34" s="31" t="n">
         <v>35.83</v>
       </c>
-      <c r="B34" s="32">
+      <c r="B34" s="31">
         <f>A34-$B$12</f>
         <v/>
       </c>
-      <c r="C34" s="32">
+      <c r="C34" s="31">
         <f>MAX(0,A34-$B$6)</f>
         <v/>
       </c>
@@ -8133,15 +6850,15 @@
         <f>IF(C34&lt;=0,0,($B$7+$B$9*C34)*C34)</f>
         <v/>
       </c>
-      <c r="E34" s="26">
+      <c r="E34" s="25">
         <f>D34*$B$11</f>
         <v/>
       </c>
-      <c r="F34" s="26">
-        <f>IF(A34&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A34&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A34,SS_Amont!$A$11:$A$18,1))+(A34-INDEX(SS_Amont!$A$11:$A$18,MATCH(A34,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A34,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A34,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A34,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A34,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G34" s="34">
+      <c r="F34" s="25">
+        <f>IF(A34&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A34&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A34,Stage_Storage!$A$11:$A$18,1))+(A34-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A34,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A34,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A34,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A34,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A34,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G34" s="33">
         <f>E34+F34</f>
         <v/>
       </c>
@@ -8163,14 +6880,14 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="32" t="n">
+      <c r="A35" s="31" t="n">
         <v>35.88</v>
       </c>
-      <c r="B35" s="32">
+      <c r="B35" s="31">
         <f>A35-$B$12</f>
         <v/>
       </c>
-      <c r="C35" s="32">
+      <c r="C35" s="31">
         <f>MAX(0,A35-$B$6)</f>
         <v/>
       </c>
@@ -8178,15 +6895,15 @@
         <f>IF(C35&lt;=0,0,($B$7+$B$9*C35)*C35)</f>
         <v/>
       </c>
-      <c r="E35" s="26">
+      <c r="E35" s="25">
         <f>D35*$B$11</f>
         <v/>
       </c>
-      <c r="F35" s="26">
-        <f>IF(A35&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A35&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A35,SS_Amont!$A$11:$A$18,1))+(A35-INDEX(SS_Amont!$A$11:$A$18,MATCH(A35,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A35,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A35,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A35,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A35,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G35" s="34">
+      <c r="F35" s="25">
+        <f>IF(A35&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A35&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A35,Stage_Storage!$A$11:$A$18,1))+(A35-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A35,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A35,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A35,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A35,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A35,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G35" s="33">
         <f>E35+F35</f>
         <v/>
       </c>
@@ -8208,14 +6925,14 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="32" t="n">
+      <c r="A36" s="31" t="n">
         <v>35.93</v>
       </c>
-      <c r="B36" s="32">
+      <c r="B36" s="31">
         <f>A36-$B$12</f>
         <v/>
       </c>
-      <c r="C36" s="32">
+      <c r="C36" s="31">
         <f>MAX(0,A36-$B$6)</f>
         <v/>
       </c>
@@ -8223,15 +6940,15 @@
         <f>IF(C36&lt;=0,0,($B$7+$B$9*C36)*C36)</f>
         <v/>
       </c>
-      <c r="E36" s="26">
+      <c r="E36" s="25">
         <f>D36*$B$11</f>
         <v/>
       </c>
-      <c r="F36" s="26">
-        <f>IF(A36&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A36&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A36,SS_Amont!$A$11:$A$18,1))+(A36-INDEX(SS_Amont!$A$11:$A$18,MATCH(A36,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A36,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A36,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A36,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A36,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G36" s="34">
+      <c r="F36" s="25">
+        <f>IF(A36&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A36&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A36,Stage_Storage!$A$11:$A$18,1))+(A36-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A36,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A36,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A36,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A36,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A36,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G36" s="33">
         <f>E36+F36</f>
         <v/>
       </c>
@@ -8253,14 +6970,14 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="32" t="n">
+      <c r="A37" s="31" t="n">
         <v>35.98</v>
       </c>
-      <c r="B37" s="32">
+      <c r="B37" s="31">
         <f>A37-$B$12</f>
         <v/>
       </c>
-      <c r="C37" s="32">
+      <c r="C37" s="31">
         <f>MAX(0,A37-$B$6)</f>
         <v/>
       </c>
@@ -8268,15 +6985,15 @@
         <f>IF(C37&lt;=0,0,($B$7+$B$9*C37)*C37)</f>
         <v/>
       </c>
-      <c r="E37" s="26">
+      <c r="E37" s="25">
         <f>D37*$B$11</f>
         <v/>
       </c>
-      <c r="F37" s="26">
-        <f>IF(A37&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A37&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A37,SS_Amont!$A$11:$A$18,1))+(A37-INDEX(SS_Amont!$A$11:$A$18,MATCH(A37,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A37,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A37,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A37,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A37,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G37" s="34">
+      <c r="F37" s="25">
+        <f>IF(A37&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A37&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A37,Stage_Storage!$A$11:$A$18,1))+(A37-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A37,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A37,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A37,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A37,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A37,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G37" s="33">
         <f>E37+F37</f>
         <v/>
       </c>
@@ -8298,14 +7015,14 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="32" t="n">
+      <c r="A38" s="31" t="n">
         <v>36.03</v>
       </c>
-      <c r="B38" s="32">
+      <c r="B38" s="31">
         <f>A38-$B$12</f>
         <v/>
       </c>
-      <c r="C38" s="32">
+      <c r="C38" s="31">
         <f>MAX(0,A38-$B$6)</f>
         <v/>
       </c>
@@ -8313,15 +7030,15 @@
         <f>IF(C38&lt;=0,0,($B$7+$B$9*C38)*C38)</f>
         <v/>
       </c>
-      <c r="E38" s="26">
+      <c r="E38" s="25">
         <f>D38*$B$11</f>
         <v/>
       </c>
-      <c r="F38" s="26">
-        <f>IF(A38&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A38&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A38,SS_Amont!$A$11:$A$18,1))+(A38-INDEX(SS_Amont!$A$11:$A$18,MATCH(A38,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A38,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A38,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A38,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A38,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G38" s="34">
+      <c r="F38" s="25">
+        <f>IF(A38&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A38&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A38,Stage_Storage!$A$11:$A$18,1))+(A38-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A38,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A38,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A38,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A38,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A38,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G38" s="33">
         <f>E38+F38</f>
         <v/>
       </c>
@@ -8343,14 +7060,14 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="32" t="n">
+      <c r="A39" s="31" t="n">
         <v>36.08</v>
       </c>
-      <c r="B39" s="32">
+      <c r="B39" s="31">
         <f>A39-$B$12</f>
         <v/>
       </c>
-      <c r="C39" s="32">
+      <c r="C39" s="31">
         <f>MAX(0,A39-$B$6)</f>
         <v/>
       </c>
@@ -8358,15 +7075,15 @@
         <f>IF(C39&lt;=0,0,($B$7+$B$9*C39)*C39)</f>
         <v/>
       </c>
-      <c r="E39" s="26">
+      <c r="E39" s="25">
         <f>D39*$B$11</f>
         <v/>
       </c>
-      <c r="F39" s="26">
-        <f>IF(A39&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A39&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A39,SS_Amont!$A$11:$A$18,1))+(A39-INDEX(SS_Amont!$A$11:$A$18,MATCH(A39,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A39,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A39,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A39,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A39,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G39" s="34">
+      <c r="F39" s="25">
+        <f>IF(A39&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A39&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A39,Stage_Storage!$A$11:$A$18,1))+(A39-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A39,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A39,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A39,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A39,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A39,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G39" s="33">
         <f>E39+F39</f>
         <v/>
       </c>
@@ -8388,14 +7105,14 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="32" t="n">
+      <c r="A40" s="31" t="n">
         <v>36.13</v>
       </c>
-      <c r="B40" s="32">
+      <c r="B40" s="31">
         <f>A40-$B$12</f>
         <v/>
       </c>
-      <c r="C40" s="32">
+      <c r="C40" s="31">
         <f>MAX(0,A40-$B$6)</f>
         <v/>
       </c>
@@ -8403,15 +7120,15 @@
         <f>IF(C40&lt;=0,0,($B$7+$B$9*C40)*C40)</f>
         <v/>
       </c>
-      <c r="E40" s="26">
+      <c r="E40" s="25">
         <f>D40*$B$11</f>
         <v/>
       </c>
-      <c r="F40" s="26">
-        <f>IF(A40&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A40&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A40,SS_Amont!$A$11:$A$18,1))+(A40-INDEX(SS_Amont!$A$11:$A$18,MATCH(A40,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A40,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A40,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A40,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A40,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G40" s="34">
+      <c r="F40" s="25">
+        <f>IF(A40&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A40&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A40,Stage_Storage!$A$11:$A$18,1))+(A40-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A40,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A40,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A40,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A40,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A40,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G40" s="33">
         <f>E40+F40</f>
         <v/>
       </c>
@@ -8433,14 +7150,14 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="32" t="n">
+      <c r="A41" s="31" t="n">
         <v>36.18</v>
       </c>
-      <c r="B41" s="32">
+      <c r="B41" s="31">
         <f>A41-$B$12</f>
         <v/>
       </c>
-      <c r="C41" s="32">
+      <c r="C41" s="31">
         <f>MAX(0,A41-$B$6)</f>
         <v/>
       </c>
@@ -8448,15 +7165,15 @@
         <f>IF(C41&lt;=0,0,($B$7+$B$9*C41)*C41)</f>
         <v/>
       </c>
-      <c r="E41" s="26">
+      <c r="E41" s="25">
         <f>D41*$B$11</f>
         <v/>
       </c>
-      <c r="F41" s="26">
-        <f>IF(A41&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A41&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A41,SS_Amont!$A$11:$A$18,1))+(A41-INDEX(SS_Amont!$A$11:$A$18,MATCH(A41,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A41,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A41,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A41,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A41,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G41" s="34">
+      <c r="F41" s="25">
+        <f>IF(A41&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A41&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A41,Stage_Storage!$A$11:$A$18,1))+(A41-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A41,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A41,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A41,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A41,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A41,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G41" s="33">
         <f>E41+F41</f>
         <v/>
       </c>
@@ -8478,14 +7195,14 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="32" t="n">
+      <c r="A42" s="31" t="n">
         <v>36.23</v>
       </c>
-      <c r="B42" s="32">
+      <c r="B42" s="31">
         <f>A42-$B$12</f>
         <v/>
       </c>
-      <c r="C42" s="32">
+      <c r="C42" s="31">
         <f>MAX(0,A42-$B$6)</f>
         <v/>
       </c>
@@ -8493,15 +7210,15 @@
         <f>IF(C42&lt;=0,0,($B$7+$B$9*C42)*C42)</f>
         <v/>
       </c>
-      <c r="E42" s="26">
+      <c r="E42" s="25">
         <f>D42*$B$11</f>
         <v/>
       </c>
-      <c r="F42" s="26">
-        <f>IF(A42&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A42&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A42,SS_Amont!$A$11:$A$18,1))+(A42-INDEX(SS_Amont!$A$11:$A$18,MATCH(A42,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A42,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A42,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A42,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A42,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G42" s="34">
+      <c r="F42" s="25">
+        <f>IF(A42&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A42&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A42,Stage_Storage!$A$11:$A$18,1))+(A42-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A42,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A42,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A42,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A42,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A42,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G42" s="33">
         <f>E42+F42</f>
         <v/>
       </c>
@@ -8523,14 +7240,14 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="32" t="n">
+      <c r="A43" s="31" t="n">
         <v>36.28</v>
       </c>
-      <c r="B43" s="32">
+      <c r="B43" s="31">
         <f>A43-$B$12</f>
         <v/>
       </c>
-      <c r="C43" s="32">
+      <c r="C43" s="31">
         <f>MAX(0,A43-$B$6)</f>
         <v/>
       </c>
@@ -8538,15 +7255,15 @@
         <f>IF(C43&lt;=0,0,($B$7+$B$9*C43)*C43)</f>
         <v/>
       </c>
-      <c r="E43" s="26">
+      <c r="E43" s="25">
         <f>D43*$B$11</f>
         <v/>
       </c>
-      <c r="F43" s="26">
-        <f>IF(A43&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A43&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A43,SS_Amont!$A$11:$A$18,1))+(A43-INDEX(SS_Amont!$A$11:$A$18,MATCH(A43,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A43,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A43,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A43,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A43,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G43" s="34">
+      <c r="F43" s="25">
+        <f>IF(A43&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A43&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A43,Stage_Storage!$A$11:$A$18,1))+(A43-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A43,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A43,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A43,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A43,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A43,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G43" s="33">
         <f>E43+F43</f>
         <v/>
       </c>
@@ -8568,14 +7285,14 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="32" t="n">
+      <c r="A44" s="31" t="n">
         <v>36.33</v>
       </c>
-      <c r="B44" s="32">
+      <c r="B44" s="31">
         <f>A44-$B$12</f>
         <v/>
       </c>
-      <c r="C44" s="32">
+      <c r="C44" s="31">
         <f>MAX(0,A44-$B$6)</f>
         <v/>
       </c>
@@ -8583,15 +7300,15 @@
         <f>IF(C44&lt;=0,0,($B$7+$B$9*C44)*C44)</f>
         <v/>
       </c>
-      <c r="E44" s="26">
+      <c r="E44" s="25">
         <f>D44*$B$11</f>
         <v/>
       </c>
-      <c r="F44" s="26">
-        <f>IF(A44&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A44&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A44,SS_Amont!$A$11:$A$18,1))+(A44-INDEX(SS_Amont!$A$11:$A$18,MATCH(A44,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A44,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A44,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A44,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A44,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G44" s="34">
+      <c r="F44" s="25">
+        <f>IF(A44&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A44&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A44,Stage_Storage!$A$11:$A$18,1))+(A44-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A44,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A44,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A44,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A44,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A44,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G44" s="33">
         <f>E44+F44</f>
         <v/>
       </c>
@@ -8613,14 +7330,14 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="32" t="n">
+      <c r="A45" s="31" t="n">
         <v>36.38</v>
       </c>
-      <c r="B45" s="32">
+      <c r="B45" s="31">
         <f>A45-$B$12</f>
         <v/>
       </c>
-      <c r="C45" s="32">
+      <c r="C45" s="31">
         <f>MAX(0,A45-$B$6)</f>
         <v/>
       </c>
@@ -8628,15 +7345,15 @@
         <f>IF(C45&lt;=0,0,($B$7+$B$9*C45)*C45)</f>
         <v/>
       </c>
-      <c r="E45" s="26">
+      <c r="E45" s="25">
         <f>D45*$B$11</f>
         <v/>
       </c>
-      <c r="F45" s="26">
-        <f>IF(A45&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A45&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A45,SS_Amont!$A$11:$A$18,1))+(A45-INDEX(SS_Amont!$A$11:$A$18,MATCH(A45,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A45,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A45,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A45,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A45,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G45" s="34">
+      <c r="F45" s="25">
+        <f>IF(A45&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A45&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A45,Stage_Storage!$A$11:$A$18,1))+(A45-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A45,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A45,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A45,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A45,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A45,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G45" s="33">
         <f>E45+F45</f>
         <v/>
       </c>
@@ -8658,14 +7375,14 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="32" t="n">
+      <c r="A46" s="31" t="n">
         <v>36.43</v>
       </c>
-      <c r="B46" s="32">
+      <c r="B46" s="31">
         <f>A46-$B$12</f>
         <v/>
       </c>
-      <c r="C46" s="32">
+      <c r="C46" s="31">
         <f>MAX(0,A46-$B$6)</f>
         <v/>
       </c>
@@ -8673,15 +7390,15 @@
         <f>IF(C46&lt;=0,0,($B$7+$B$9*C46)*C46)</f>
         <v/>
       </c>
-      <c r="E46" s="26">
+      <c r="E46" s="25">
         <f>D46*$B$11</f>
         <v/>
       </c>
-      <c r="F46" s="26">
-        <f>IF(A46&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A46&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A46,SS_Amont!$A$11:$A$18,1))+(A46-INDEX(SS_Amont!$A$11:$A$18,MATCH(A46,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A46,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A46,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A46,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A46,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G46" s="34">
+      <c r="F46" s="25">
+        <f>IF(A46&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A46&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A46,Stage_Storage!$A$11:$A$18,1))+(A46-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A46,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A46,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A46,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A46,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A46,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G46" s="33">
         <f>E46+F46</f>
         <v/>
       </c>
@@ -8703,14 +7420,14 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="32" t="n">
+      <c r="A47" s="31" t="n">
         <v>36.48</v>
       </c>
-      <c r="B47" s="32">
+      <c r="B47" s="31">
         <f>A47-$B$12</f>
         <v/>
       </c>
-      <c r="C47" s="32">
+      <c r="C47" s="31">
         <f>MAX(0,A47-$B$6)</f>
         <v/>
       </c>
@@ -8718,15 +7435,15 @@
         <f>IF(C47&lt;=0,0,($B$7+$B$9*C47)*C47)</f>
         <v/>
       </c>
-      <c r="E47" s="26">
+      <c r="E47" s="25">
         <f>D47*$B$11</f>
         <v/>
       </c>
-      <c r="F47" s="26">
-        <f>IF(A47&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A47&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A47,SS_Amont!$A$11:$A$18,1))+(A47-INDEX(SS_Amont!$A$11:$A$18,MATCH(A47,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A47,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A47,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A47,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A47,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G47" s="34">
+      <c r="F47" s="25">
+        <f>IF(A47&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A47&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A47,Stage_Storage!$A$11:$A$18,1))+(A47-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A47,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A47,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A47,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A47,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A47,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G47" s="33">
         <f>E47+F47</f>
         <v/>
       </c>
@@ -8748,14 +7465,14 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="32" t="n">
+      <c r="A48" s="31" t="n">
         <v>36.53</v>
       </c>
-      <c r="B48" s="32">
+      <c r="B48" s="31">
         <f>A48-$B$12</f>
         <v/>
       </c>
-      <c r="C48" s="32">
+      <c r="C48" s="31">
         <f>MAX(0,A48-$B$6)</f>
         <v/>
       </c>
@@ -8763,15 +7480,15 @@
         <f>IF(C48&lt;=0,0,($B$7+$B$9*C48)*C48)</f>
         <v/>
       </c>
-      <c r="E48" s="26">
+      <c r="E48" s="25">
         <f>D48*$B$11</f>
         <v/>
       </c>
-      <c r="F48" s="26">
-        <f>IF(A48&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A48&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A48,SS_Amont!$A$11:$A$18,1))+(A48-INDEX(SS_Amont!$A$11:$A$18,MATCH(A48,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A48,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A48,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A48,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A48,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G48" s="34">
+      <c r="F48" s="25">
+        <f>IF(A48&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A48&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A48,Stage_Storage!$A$11:$A$18,1))+(A48-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A48,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A48,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A48,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A48,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A48,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G48" s="33">
         <f>E48+F48</f>
         <v/>
       </c>
@@ -8793,14 +7510,14 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="32" t="n">
+      <c r="A49" s="31" t="n">
         <v>36.58</v>
       </c>
-      <c r="B49" s="32">
+      <c r="B49" s="31">
         <f>A49-$B$12</f>
         <v/>
       </c>
-      <c r="C49" s="32">
+      <c r="C49" s="31">
         <f>MAX(0,A49-$B$6)</f>
         <v/>
       </c>
@@ -8808,15 +7525,15 @@
         <f>IF(C49&lt;=0,0,($B$7+$B$9*C49)*C49)</f>
         <v/>
       </c>
-      <c r="E49" s="26">
+      <c r="E49" s="25">
         <f>D49*$B$11</f>
         <v/>
       </c>
-      <c r="F49" s="26">
-        <f>IF(A49&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A49&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A49,SS_Amont!$A$11:$A$18,1))+(A49-INDEX(SS_Amont!$A$11:$A$18,MATCH(A49,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A49,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A49,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A49,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A49,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G49" s="34">
+      <c r="F49" s="25">
+        <f>IF(A49&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A49&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A49,Stage_Storage!$A$11:$A$18,1))+(A49-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A49,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A49,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A49,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A49,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A49,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G49" s="33">
         <f>E49+F49</f>
         <v/>
       </c>
@@ -8838,14 +7555,14 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="32" t="n">
+      <c r="A50" s="31" t="n">
         <v>36.63</v>
       </c>
-      <c r="B50" s="32">
+      <c r="B50" s="31">
         <f>A50-$B$12</f>
         <v/>
       </c>
-      <c r="C50" s="32">
+      <c r="C50" s="31">
         <f>MAX(0,A50-$B$6)</f>
         <v/>
       </c>
@@ -8853,15 +7570,15 @@
         <f>IF(C50&lt;=0,0,($B$7+$B$9*C50)*C50)</f>
         <v/>
       </c>
-      <c r="E50" s="26">
+      <c r="E50" s="25">
         <f>D50*$B$11</f>
         <v/>
       </c>
-      <c r="F50" s="26">
-        <f>IF(A50&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A50&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A50,SS_Amont!$A$11:$A$18,1))+(A50-INDEX(SS_Amont!$A$11:$A$18,MATCH(A50,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A50,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A50,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A50,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A50,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G50" s="34">
+      <c r="F50" s="25">
+        <f>IF(A50&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A50&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A50,Stage_Storage!$A$11:$A$18,1))+(A50-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A50,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A50,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A50,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A50,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A50,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G50" s="33">
         <f>E50+F50</f>
         <v/>
       </c>
@@ -8883,14 +7600,14 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="32" t="n">
+      <c r="A51" s="31" t="n">
         <v>36.68</v>
       </c>
-      <c r="B51" s="32">
+      <c r="B51" s="31">
         <f>A51-$B$12</f>
         <v/>
       </c>
-      <c r="C51" s="32">
+      <c r="C51" s="31">
         <f>MAX(0,A51-$B$6)</f>
         <v/>
       </c>
@@ -8898,15 +7615,15 @@
         <f>IF(C51&lt;=0,0,($B$7+$B$9*C51)*C51)</f>
         <v/>
       </c>
-      <c r="E51" s="26">
+      <c r="E51" s="25">
         <f>D51*$B$11</f>
         <v/>
       </c>
-      <c r="F51" s="26">
-        <f>IF(A51&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A51&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A51,SS_Amont!$A$11:$A$18,1))+(A51-INDEX(SS_Amont!$A$11:$A$18,MATCH(A51,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A51,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A51,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A51,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A51,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G51" s="34">
+      <c r="F51" s="25">
+        <f>IF(A51&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A51&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A51,Stage_Storage!$A$11:$A$18,1))+(A51-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A51,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A51,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A51,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A51,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A51,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G51" s="33">
         <f>E51+F51</f>
         <v/>
       </c>
@@ -8928,14 +7645,14 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="32" t="n">
+      <c r="A52" s="31" t="n">
         <v>36.73</v>
       </c>
-      <c r="B52" s="32">
+      <c r="B52" s="31">
         <f>A52-$B$12</f>
         <v/>
       </c>
-      <c r="C52" s="32">
+      <c r="C52" s="31">
         <f>MAX(0,A52-$B$6)</f>
         <v/>
       </c>
@@ -8943,15 +7660,15 @@
         <f>IF(C52&lt;=0,0,($B$7+$B$9*C52)*C52)</f>
         <v/>
       </c>
-      <c r="E52" s="26">
+      <c r="E52" s="25">
         <f>D52*$B$11</f>
         <v/>
       </c>
-      <c r="F52" s="26">
-        <f>IF(A52&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A52&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A52,SS_Amont!$A$11:$A$18,1))+(A52-INDEX(SS_Amont!$A$11:$A$18,MATCH(A52,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A52,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A52,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A52,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A52,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G52" s="34">
+      <c r="F52" s="25">
+        <f>IF(A52&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A52&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A52,Stage_Storage!$A$11:$A$18,1))+(A52-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A52,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A52,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A52,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A52,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A52,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G52" s="33">
         <f>E52+F52</f>
         <v/>
       </c>
@@ -8973,14 +7690,14 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="32" t="n">
+      <c r="A53" s="31" t="n">
         <v>36.78</v>
       </c>
-      <c r="B53" s="32">
+      <c r="B53" s="31">
         <f>A53-$B$12</f>
         <v/>
       </c>
-      <c r="C53" s="32">
+      <c r="C53" s="31">
         <f>MAX(0,A53-$B$6)</f>
         <v/>
       </c>
@@ -8988,15 +7705,15 @@
         <f>IF(C53&lt;=0,0,($B$7+$B$9*C53)*C53)</f>
         <v/>
       </c>
-      <c r="E53" s="26">
+      <c r="E53" s="25">
         <f>D53*$B$11</f>
         <v/>
       </c>
-      <c r="F53" s="26">
-        <f>IF(A53&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A53&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A53,SS_Amont!$A$11:$A$18,1))+(A53-INDEX(SS_Amont!$A$11:$A$18,MATCH(A53,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A53,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A53,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A53,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A53,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G53" s="34">
+      <c r="F53" s="25">
+        <f>IF(A53&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A53&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A53,Stage_Storage!$A$11:$A$18,1))+(A53-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A53,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A53,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A53,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A53,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A53,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G53" s="33">
         <f>E53+F53</f>
         <v/>
       </c>
@@ -9018,14 +7735,14 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="32" t="n">
+      <c r="A54" s="31" t="n">
         <v>36.83</v>
       </c>
-      <c r="B54" s="32">
+      <c r="B54" s="31">
         <f>A54-$B$12</f>
         <v/>
       </c>
-      <c r="C54" s="32">
+      <c r="C54" s="31">
         <f>MAX(0,A54-$B$6)</f>
         <v/>
       </c>
@@ -9033,15 +7750,15 @@
         <f>IF(C54&lt;=0,0,($B$7+$B$9*C54)*C54)</f>
         <v/>
       </c>
-      <c r="E54" s="26">
+      <c r="E54" s="25">
         <f>D54*$B$11</f>
         <v/>
       </c>
-      <c r="F54" s="26">
-        <f>IF(A54&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A54&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A54,SS_Amont!$A$11:$A$18,1))+(A54-INDEX(SS_Amont!$A$11:$A$18,MATCH(A54,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A54,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A54,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A54,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A54,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G54" s="34">
+      <c r="F54" s="25">
+        <f>IF(A54&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A54&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A54,Stage_Storage!$A$11:$A$18,1))+(A54-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A54,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A54,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A54,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A54,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A54,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G54" s="33">
         <f>E54+F54</f>
         <v/>
       </c>
@@ -9063,14 +7780,14 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="32" t="n">
+      <c r="A55" s="31" t="n">
         <v>36.88</v>
       </c>
-      <c r="B55" s="32">
+      <c r="B55" s="31">
         <f>A55-$B$12</f>
         <v/>
       </c>
-      <c r="C55" s="32">
+      <c r="C55" s="31">
         <f>MAX(0,A55-$B$6)</f>
         <v/>
       </c>
@@ -9078,15 +7795,15 @@
         <f>IF(C55&lt;=0,0,($B$7+$B$9*C55)*C55)</f>
         <v/>
       </c>
-      <c r="E55" s="26">
+      <c r="E55" s="25">
         <f>D55*$B$11</f>
         <v/>
       </c>
-      <c r="F55" s="26">
-        <f>IF(A55&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A55&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A55,SS_Amont!$A$11:$A$18,1))+(A55-INDEX(SS_Amont!$A$11:$A$18,MATCH(A55,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A55,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A55,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A55,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A55,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G55" s="34">
+      <c r="F55" s="25">
+        <f>IF(A55&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A55&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A55,Stage_Storage!$A$11:$A$18,1))+(A55-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A55,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A55,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A55,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A55,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A55,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G55" s="33">
         <f>E55+F55</f>
         <v/>
       </c>
@@ -9108,14 +7825,14 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="32" t="n">
+      <c r="A56" s="31" t="n">
         <v>36.93</v>
       </c>
-      <c r="B56" s="32">
+      <c r="B56" s="31">
         <f>A56-$B$12</f>
         <v/>
       </c>
-      <c r="C56" s="32">
+      <c r="C56" s="31">
         <f>MAX(0,A56-$B$6)</f>
         <v/>
       </c>
@@ -9123,15 +7840,15 @@
         <f>IF(C56&lt;=0,0,($B$7+$B$9*C56)*C56)</f>
         <v/>
       </c>
-      <c r="E56" s="26">
+      <c r="E56" s="25">
         <f>D56*$B$11</f>
         <v/>
       </c>
-      <c r="F56" s="26">
-        <f>IF(A56&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A56&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A56,SS_Amont!$A$11:$A$18,1))+(A56-INDEX(SS_Amont!$A$11:$A$18,MATCH(A56,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A56,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A56,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A56,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A56,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G56" s="34">
+      <c r="F56" s="25">
+        <f>IF(A56&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A56&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A56,Stage_Storage!$A$11:$A$18,1))+(A56-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A56,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A56,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A56,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A56,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A56,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G56" s="33">
         <f>E56+F56</f>
         <v/>
       </c>
@@ -9153,14 +7870,14 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="32" t="n">
+      <c r="A57" s="31" t="n">
         <v>36.98</v>
       </c>
-      <c r="B57" s="32">
+      <c r="B57" s="31">
         <f>A57-$B$12</f>
         <v/>
       </c>
-      <c r="C57" s="32">
+      <c r="C57" s="31">
         <f>MAX(0,A57-$B$6)</f>
         <v/>
       </c>
@@ -9168,15 +7885,15 @@
         <f>IF(C57&lt;=0,0,($B$7+$B$9*C57)*C57)</f>
         <v/>
       </c>
-      <c r="E57" s="26">
+      <c r="E57" s="25">
         <f>D57*$B$11</f>
         <v/>
       </c>
-      <c r="F57" s="26">
-        <f>IF(A57&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A57&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A57,SS_Amont!$A$11:$A$18,1))+(A57-INDEX(SS_Amont!$A$11:$A$18,MATCH(A57,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A57,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A57,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A57,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A57,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G57" s="34">
+      <c r="F57" s="25">
+        <f>IF(A57&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A57&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A57,Stage_Storage!$A$11:$A$18,1))+(A57-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A57,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A57,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A57,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A57,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A57,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G57" s="33">
         <f>E57+F57</f>
         <v/>
       </c>
@@ -9198,14 +7915,14 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="32" t="n">
+      <c r="A58" s="31" t="n">
         <v>37.03</v>
       </c>
-      <c r="B58" s="32">
+      <c r="B58" s="31">
         <f>A58-$B$12</f>
         <v/>
       </c>
-      <c r="C58" s="32">
+      <c r="C58" s="31">
         <f>MAX(0,A58-$B$6)</f>
         <v/>
       </c>
@@ -9213,15 +7930,15 @@
         <f>IF(C58&lt;=0,0,($B$7+$B$9*C58)*C58)</f>
         <v/>
       </c>
-      <c r="E58" s="26">
+      <c r="E58" s="25">
         <f>D58*$B$11</f>
         <v/>
       </c>
-      <c r="F58" s="26">
-        <f>IF(A58&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A58&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A58,SS_Amont!$A$11:$A$18,1))+(A58-INDEX(SS_Amont!$A$11:$A$18,MATCH(A58,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A58,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A58,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A58,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A58,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G58" s="34">
+      <c r="F58" s="25">
+        <f>IF(A58&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A58&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A58,Stage_Storage!$A$11:$A$18,1))+(A58-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A58,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A58,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A58,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A58,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A58,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G58" s="33">
         <f>E58+F58</f>
         <v/>
       </c>
@@ -9243,14 +7960,14 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="32" t="n">
+      <c r="A59" s="31" t="n">
         <v>37.08</v>
       </c>
-      <c r="B59" s="32">
+      <c r="B59" s="31">
         <f>A59-$B$12</f>
         <v/>
       </c>
-      <c r="C59" s="32">
+      <c r="C59" s="31">
         <f>MAX(0,A59-$B$6)</f>
         <v/>
       </c>
@@ -9258,15 +7975,15 @@
         <f>IF(C59&lt;=0,0,($B$7+$B$9*C59)*C59)</f>
         <v/>
       </c>
-      <c r="E59" s="26">
+      <c r="E59" s="25">
         <f>D59*$B$11</f>
         <v/>
       </c>
-      <c r="F59" s="26">
-        <f>IF(A59&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A59&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A59,SS_Amont!$A$11:$A$18,1))+(A59-INDEX(SS_Amont!$A$11:$A$18,MATCH(A59,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A59,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A59,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A59,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A59,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G59" s="34">
+      <c r="F59" s="25">
+        <f>IF(A59&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A59&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A59,Stage_Storage!$A$11:$A$18,1))+(A59-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A59,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A59,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A59,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A59,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A59,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G59" s="33">
         <f>E59+F59</f>
         <v/>
       </c>
@@ -9288,14 +8005,14 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="32" t="n">
+      <c r="A60" s="31" t="n">
         <v>37.13</v>
       </c>
-      <c r="B60" s="32">
+      <c r="B60" s="31">
         <f>A60-$B$12</f>
         <v/>
       </c>
-      <c r="C60" s="32">
+      <c r="C60" s="31">
         <f>MAX(0,A60-$B$6)</f>
         <v/>
       </c>
@@ -9303,15 +8020,15 @@
         <f>IF(C60&lt;=0,0,($B$7+$B$9*C60)*C60)</f>
         <v/>
       </c>
-      <c r="E60" s="26">
+      <c r="E60" s="25">
         <f>D60*$B$11</f>
         <v/>
       </c>
-      <c r="F60" s="26">
-        <f>IF(A60&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A60&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A60,SS_Amont!$A$11:$A$18,1))+(A60-INDEX(SS_Amont!$A$11:$A$18,MATCH(A60,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A60,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A60,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A60,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A60,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G60" s="34">
+      <c r="F60" s="25">
+        <f>IF(A60&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A60&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1))+(A60-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A60,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G60" s="33">
         <f>E60+F60</f>
         <v/>
       </c>
@@ -9333,14 +8050,14 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="32" t="n">
+      <c r="A61" s="31" t="n">
         <v>37.18</v>
       </c>
-      <c r="B61" s="32">
+      <c r="B61" s="31">
         <f>A61-$B$12</f>
         <v/>
       </c>
-      <c r="C61" s="32">
+      <c r="C61" s="31">
         <f>MAX(0,A61-$B$6)</f>
         <v/>
       </c>
@@ -9348,15 +8065,15 @@
         <f>IF(C61&lt;=0,0,($B$7+$B$9*C61)*C61)</f>
         <v/>
       </c>
-      <c r="E61" s="26">
+      <c r="E61" s="25">
         <f>D61*$B$11</f>
         <v/>
       </c>
-      <c r="F61" s="26">
-        <f>IF(A61&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A61&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A61,SS_Amont!$A$11:$A$18,1))+(A61-INDEX(SS_Amont!$A$11:$A$18,MATCH(A61,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A61,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A61,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A61,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A61,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G61" s="34">
+      <c r="F61" s="25">
+        <f>IF(A61&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A61&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1))+(A61-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A61,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G61" s="33">
         <f>E61+F61</f>
         <v/>
       </c>
@@ -9378,14 +8095,14 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="32" t="n">
+      <c r="A62" s="31" t="n">
         <v>37.23</v>
       </c>
-      <c r="B62" s="32">
+      <c r="B62" s="31">
         <f>A62-$B$12</f>
         <v/>
       </c>
-      <c r="C62" s="32">
+      <c r="C62" s="31">
         <f>MAX(0,A62-$B$6)</f>
         <v/>
       </c>
@@ -9393,15 +8110,15 @@
         <f>IF(C62&lt;=0,0,($B$7+$B$9*C62)*C62)</f>
         <v/>
       </c>
-      <c r="E62" s="26">
+      <c r="E62" s="25">
         <f>D62*$B$11</f>
         <v/>
       </c>
-      <c r="F62" s="26">
-        <f>IF(A62&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A62&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A62,SS_Amont!$A$11:$A$18,1))+(A62-INDEX(SS_Amont!$A$11:$A$18,MATCH(A62,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A62,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A62,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A62,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A62,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G62" s="34">
+      <c r="F62" s="25">
+        <f>IF(A62&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A62&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1))+(A62-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A62,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G62" s="33">
         <f>E62+F62</f>
         <v/>
       </c>
@@ -9423,14 +8140,14 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="32" t="n">
+      <c r="A63" s="31" t="n">
         <v>37.28</v>
       </c>
-      <c r="B63" s="32">
+      <c r="B63" s="31">
         <f>A63-$B$12</f>
         <v/>
       </c>
-      <c r="C63" s="32">
+      <c r="C63" s="31">
         <f>MAX(0,A63-$B$6)</f>
         <v/>
       </c>
@@ -9438,15 +8155,15 @@
         <f>IF(C63&lt;=0,0,($B$7+$B$9*C63)*C63)</f>
         <v/>
       </c>
-      <c r="E63" s="26">
+      <c r="E63" s="25">
         <f>D63*$B$11</f>
         <v/>
       </c>
-      <c r="F63" s="26">
-        <f>IF(A63&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A63&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A63,SS_Amont!$A$11:$A$18,1))+(A63-INDEX(SS_Amont!$A$11:$A$18,MATCH(A63,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A63,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A63,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A63,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A63,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G63" s="34">
+      <c r="F63" s="25">
+        <f>IF(A63&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A63&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1))+(A63-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A63,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G63" s="33">
         <f>E63+F63</f>
         <v/>
       </c>
@@ -9468,14 +8185,14 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="32" t="n">
+      <c r="A64" s="31" t="n">
         <v>37.33</v>
       </c>
-      <c r="B64" s="32">
+      <c r="B64" s="31">
         <f>A64-$B$12</f>
         <v/>
       </c>
-      <c r="C64" s="32">
+      <c r="C64" s="31">
         <f>MAX(0,A64-$B$6)</f>
         <v/>
       </c>
@@ -9483,15 +8200,15 @@
         <f>IF(C64&lt;=0,0,($B$7+$B$9*C64)*C64)</f>
         <v/>
       </c>
-      <c r="E64" s="26">
+      <c r="E64" s="25">
         <f>D64*$B$11</f>
         <v/>
       </c>
-      <c r="F64" s="26">
-        <f>IF(A64&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A64&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A64,SS_Amont!$A$11:$A$18,1))+(A64-INDEX(SS_Amont!$A$11:$A$18,MATCH(A64,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A64,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A64,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A64,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A64,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G64" s="34">
+      <c r="F64" s="25">
+        <f>IF(A64&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A64&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1))+(A64-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A64,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G64" s="33">
         <f>E64+F64</f>
         <v/>
       </c>
@@ -9513,14 +8230,14 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="32" t="n">
+      <c r="A65" s="31" t="n">
         <v>37.38</v>
       </c>
-      <c r="B65" s="32">
+      <c r="B65" s="31">
         <f>A65-$B$12</f>
         <v/>
       </c>
-      <c r="C65" s="32">
+      <c r="C65" s="31">
         <f>MAX(0,A65-$B$6)</f>
         <v/>
       </c>
@@ -9528,15 +8245,15 @@
         <f>IF(C65&lt;=0,0,($B$7+$B$9*C65)*C65)</f>
         <v/>
       </c>
-      <c r="E65" s="26">
+      <c r="E65" s="25">
         <f>D65*$B$11</f>
         <v/>
       </c>
-      <c r="F65" s="26">
-        <f>IF(A65&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A65&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A65,SS_Amont!$A$11:$A$18,1))+(A65-INDEX(SS_Amont!$A$11:$A$18,MATCH(A65,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A65,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A65,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A65,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A65,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G65" s="34">
+      <c r="F65" s="25">
+        <f>IF(A65&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A65&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1))+(A65-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G65" s="33">
         <f>E65+F65</f>
         <v/>
       </c>
@@ -9558,14 +8275,14 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="32" t="n">
+      <c r="A66" s="31" t="n">
         <v>37.43</v>
       </c>
-      <c r="B66" s="32">
+      <c r="B66" s="31">
         <f>A66-$B$12</f>
         <v/>
       </c>
-      <c r="C66" s="32">
+      <c r="C66" s="31">
         <f>MAX(0,A66-$B$6)</f>
         <v/>
       </c>
@@ -9573,15 +8290,15 @@
         <f>IF(C66&lt;=0,0,($B$7+$B$9*C66)*C66)</f>
         <v/>
       </c>
-      <c r="E66" s="26">
+      <c r="E66" s="25">
         <f>D66*$B$11</f>
         <v/>
       </c>
-      <c r="F66" s="26">
-        <f>IF(A66&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A66&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A66,SS_Amont!$A$11:$A$18,1))+(A66-INDEX(SS_Amont!$A$11:$A$18,MATCH(A66,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A66,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A66,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A66,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A66,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G66" s="34">
+      <c r="F66" s="25">
+        <f>IF(A66&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A66&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1))+(A66-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G66" s="33">
         <f>E66+F66</f>
         <v/>
       </c>
@@ -9603,14 +8320,14 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="32" t="n">
+      <c r="A67" s="31" t="n">
         <v>37.48</v>
       </c>
-      <c r="B67" s="32">
+      <c r="B67" s="31">
         <f>A67-$B$12</f>
         <v/>
       </c>
-      <c r="C67" s="32">
+      <c r="C67" s="31">
         <f>MAX(0,A67-$B$6)</f>
         <v/>
       </c>
@@ -9618,15 +8335,15 @@
         <f>IF(C67&lt;=0,0,($B$7+$B$9*C67)*C67)</f>
         <v/>
       </c>
-      <c r="E67" s="26">
+      <c r="E67" s="25">
         <f>D67*$B$11</f>
         <v/>
       </c>
-      <c r="F67" s="26">
-        <f>IF(A67&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A67&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A67,SS_Amont!$A$11:$A$18,1))+(A67-INDEX(SS_Amont!$A$11:$A$18,MATCH(A67,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A67,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A67,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A67,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A67,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G67" s="34">
+      <c r="F67" s="25">
+        <f>IF(A67&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A67&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A67,Stage_Storage!$A$11:$A$18,1))+(A67-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A67,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A67,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A67,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A67,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A67,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G67" s="33">
         <f>E67+F67</f>
         <v/>
       </c>
@@ -9648,14 +8365,14 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="32" t="n">
+      <c r="A68" s="31" t="n">
         <v>37.53</v>
       </c>
-      <c r="B68" s="32">
+      <c r="B68" s="31">
         <f>A68-$B$12</f>
         <v/>
       </c>
-      <c r="C68" s="32">
+      <c r="C68" s="31">
         <f>MAX(0,A68-$B$6)</f>
         <v/>
       </c>
@@ -9663,15 +8380,15 @@
         <f>IF(C68&lt;=0,0,($B$7+$B$9*C68)*C68)</f>
         <v/>
       </c>
-      <c r="E68" s="26">
+      <c r="E68" s="25">
         <f>D68*$B$11</f>
         <v/>
       </c>
-      <c r="F68" s="26">
-        <f>IF(A68&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A68&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A68,SS_Amont!$A$11:$A$18,1))+(A68-INDEX(SS_Amont!$A$11:$A$18,MATCH(A68,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A68,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A68,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A68,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A68,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G68" s="34">
+      <c r="F68" s="25">
+        <f>IF(A68&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A68&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A68,Stage_Storage!$A$11:$A$18,1))+(A68-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A68,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A68,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A68,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A68,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A68,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G68" s="33">
         <f>E68+F68</f>
         <v/>
       </c>
@@ -9693,14 +8410,14 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="32" t="n">
+      <c r="A69" s="31" t="n">
         <v>37.58</v>
       </c>
-      <c r="B69" s="32">
+      <c r="B69" s="31">
         <f>A69-$B$12</f>
         <v/>
       </c>
-      <c r="C69" s="32">
+      <c r="C69" s="31">
         <f>MAX(0,A69-$B$6)</f>
         <v/>
       </c>
@@ -9708,15 +8425,15 @@
         <f>IF(C69&lt;=0,0,($B$7+$B$9*C69)*C69)</f>
         <v/>
       </c>
-      <c r="E69" s="26">
+      <c r="E69" s="25">
         <f>D69*$B$11</f>
         <v/>
       </c>
-      <c r="F69" s="26">
-        <f>IF(A69&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A69&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A69,SS_Amont!$A$11:$A$18,1))+(A69-INDEX(SS_Amont!$A$11:$A$18,MATCH(A69,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A69,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A69,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A69,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A69,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G69" s="34">
+      <c r="F69" s="25">
+        <f>IF(A69&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A69&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A69,Stage_Storage!$A$11:$A$18,1))+(A69-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A69,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A69,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A69,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A69,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A69,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G69" s="33">
         <f>E69+F69</f>
         <v/>
       </c>
@@ -9738,14 +8455,14 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="32" t="n">
+      <c r="A70" s="31" t="n">
         <v>37.63</v>
       </c>
-      <c r="B70" s="32">
+      <c r="B70" s="31">
         <f>A70-$B$12</f>
         <v/>
       </c>
-      <c r="C70" s="32">
+      <c r="C70" s="31">
         <f>MAX(0,A70-$B$6)</f>
         <v/>
       </c>
@@ -9753,15 +8470,15 @@
         <f>IF(C70&lt;=0,0,($B$7+$B$9*C70)*C70)</f>
         <v/>
       </c>
-      <c r="E70" s="26">
+      <c r="E70" s="25">
         <f>D70*$B$11</f>
         <v/>
       </c>
-      <c r="F70" s="26">
-        <f>IF(A70&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A70&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A70,SS_Amont!$A$11:$A$18,1))+(A70-INDEX(SS_Amont!$A$11:$A$18,MATCH(A70,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A70,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A70,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A70,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A70,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G70" s="34">
+      <c r="F70" s="25">
+        <f>IF(A70&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A70&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A70,Stage_Storage!$A$11:$A$18,1))+(A70-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A70,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A70,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A70,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A70,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A70,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G70" s="33">
         <f>E70+F70</f>
         <v/>
       </c>
@@ -9783,14 +8500,14 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="32" t="n">
+      <c r="A71" s="31" t="n">
         <v>37.68</v>
       </c>
-      <c r="B71" s="32">
+      <c r="B71" s="31">
         <f>A71-$B$12</f>
         <v/>
       </c>
-      <c r="C71" s="32">
+      <c r="C71" s="31">
         <f>MAX(0,A71-$B$6)</f>
         <v/>
       </c>
@@ -9798,15 +8515,15 @@
         <f>IF(C71&lt;=0,0,($B$7+$B$9*C71)*C71)</f>
         <v/>
       </c>
-      <c r="E71" s="26">
+      <c r="E71" s="25">
         <f>D71*$B$11</f>
         <v/>
       </c>
-      <c r="F71" s="26">
-        <f>IF(A71&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A71&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A71,SS_Amont!$A$11:$A$18,1))+(A71-INDEX(SS_Amont!$A$11:$A$18,MATCH(A71,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A71,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A71,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A71,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A71,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G71" s="34">
+      <c r="F71" s="25">
+        <f>IF(A71&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A71&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A71,Stage_Storage!$A$11:$A$18,1))+(A71-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A71,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A71,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A71,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A71,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A71,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G71" s="33">
         <f>E71+F71</f>
         <v/>
       </c>
@@ -9828,14 +8545,14 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="32" t="n">
+      <c r="A72" s="31" t="n">
         <v>37.73</v>
       </c>
-      <c r="B72" s="32">
+      <c r="B72" s="31">
         <f>A72-$B$12</f>
         <v/>
       </c>
-      <c r="C72" s="32">
+      <c r="C72" s="31">
         <f>MAX(0,A72-$B$6)</f>
         <v/>
       </c>
@@ -9843,15 +8560,15 @@
         <f>IF(C72&lt;=0,0,($B$7+$B$9*C72)*C72)</f>
         <v/>
       </c>
-      <c r="E72" s="26">
+      <c r="E72" s="25">
         <f>D72*$B$11</f>
         <v/>
       </c>
-      <c r="F72" s="26">
-        <f>IF(A72&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A72&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A72,SS_Amont!$A$11:$A$18,1))+(A72-INDEX(SS_Amont!$A$11:$A$18,MATCH(A72,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A72,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A72,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A72,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A72,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G72" s="34">
+      <c r="F72" s="25">
+        <f>IF(A72&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A72&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A72,Stage_Storage!$A$11:$A$18,1))+(A72-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A72,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A72,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A72,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A72,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A72,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G72" s="33">
         <f>E72+F72</f>
         <v/>
       </c>
@@ -9873,14 +8590,14 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="32" t="n">
+      <c r="A73" s="31" t="n">
         <v>37.78</v>
       </c>
-      <c r="B73" s="32">
+      <c r="B73" s="31">
         <f>A73-$B$12</f>
         <v/>
       </c>
-      <c r="C73" s="32">
+      <c r="C73" s="31">
         <f>MAX(0,A73-$B$6)</f>
         <v/>
       </c>
@@ -9888,15 +8605,15 @@
         <f>IF(C73&lt;=0,0,($B$7+$B$9*C73)*C73)</f>
         <v/>
       </c>
-      <c r="E73" s="26">
+      <c r="E73" s="25">
         <f>D73*$B$11</f>
         <v/>
       </c>
-      <c r="F73" s="26">
-        <f>IF(A73&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A73&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A73,SS_Amont!$A$11:$A$18,1))+(A73-INDEX(SS_Amont!$A$11:$A$18,MATCH(A73,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A73,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A73,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A73,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A73,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G73" s="34">
+      <c r="F73" s="25">
+        <f>IF(A73&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A73&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A73,Stage_Storage!$A$11:$A$18,1))+(A73-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A73,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A73,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A73,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A73,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A73,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G73" s="33">
         <f>E73+F73</f>
         <v/>
       </c>
@@ -9918,14 +8635,14 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="32" t="n">
+      <c r="A74" s="31" t="n">
         <v>37.83</v>
       </c>
-      <c r="B74" s="32">
+      <c r="B74" s="31">
         <f>A74-$B$12</f>
         <v/>
       </c>
-      <c r="C74" s="32">
+      <c r="C74" s="31">
         <f>MAX(0,A74-$B$6)</f>
         <v/>
       </c>
@@ -9933,15 +8650,15 @@
         <f>IF(C74&lt;=0,0,($B$7+$B$9*C74)*C74)</f>
         <v/>
       </c>
-      <c r="E74" s="26">
+      <c r="E74" s="25">
         <f>D74*$B$11</f>
         <v/>
       </c>
-      <c r="F74" s="26">
-        <f>IF(A74&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A74&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A74,SS_Amont!$A$11:$A$18,1))+(A74-INDEX(SS_Amont!$A$11:$A$18,MATCH(A74,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A74,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A74,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A74,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A74,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G74" s="34">
+      <c r="F74" s="25">
+        <f>IF(A74&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A74&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A74,Stage_Storage!$A$11:$A$18,1))+(A74-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A74,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A74,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A74,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A74,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A74,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G74" s="33">
         <f>E74+F74</f>
         <v/>
       </c>
@@ -9963,14 +8680,14 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="32" t="n">
+      <c r="A75" s="31" t="n">
         <v>37.88</v>
       </c>
-      <c r="B75" s="32">
+      <c r="B75" s="31">
         <f>A75-$B$12</f>
         <v/>
       </c>
-      <c r="C75" s="32">
+      <c r="C75" s="31">
         <f>MAX(0,A75-$B$6)</f>
         <v/>
       </c>
@@ -9978,15 +8695,15 @@
         <f>IF(C75&lt;=0,0,($B$7+$B$9*C75)*C75)</f>
         <v/>
       </c>
-      <c r="E75" s="26">
+      <c r="E75" s="25">
         <f>D75*$B$11</f>
         <v/>
       </c>
-      <c r="F75" s="26">
-        <f>IF(A75&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A75&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A75,SS_Amont!$A$11:$A$18,1))+(A75-INDEX(SS_Amont!$A$11:$A$18,MATCH(A75,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A75,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A75,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A75,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A75,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G75" s="34">
+      <c r="F75" s="25">
+        <f>IF(A75&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A75&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A75,Stage_Storage!$A$11:$A$18,1))+(A75-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A75,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A75,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A75,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A75,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A75,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G75" s="33">
         <f>E75+F75</f>
         <v/>
       </c>
@@ -10008,14 +8725,14 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="32" t="n">
+      <c r="A76" s="31" t="n">
         <v>37.93</v>
       </c>
-      <c r="B76" s="32">
+      <c r="B76" s="31">
         <f>A76-$B$12</f>
         <v/>
       </c>
-      <c r="C76" s="32">
+      <c r="C76" s="31">
         <f>MAX(0,A76-$B$6)</f>
         <v/>
       </c>
@@ -10023,15 +8740,15 @@
         <f>IF(C76&lt;=0,0,($B$7+$B$9*C76)*C76)</f>
         <v/>
       </c>
-      <c r="E76" s="26">
+      <c r="E76" s="25">
         <f>D76*$B$11</f>
         <v/>
       </c>
-      <c r="F76" s="26">
-        <f>IF(A76&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A76&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A76,SS_Amont!$A$11:$A$18,1))+(A76-INDEX(SS_Amont!$A$11:$A$18,MATCH(A76,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A76,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A76,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A76,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A76,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G76" s="34">
+      <c r="F76" s="25">
+        <f>IF(A76&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A76&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A76,Stage_Storage!$A$11:$A$18,1))+(A76-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A76,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A76,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A76,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A76,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A76,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G76" s="33">
         <f>E76+F76</f>
         <v/>
       </c>
@@ -10053,14 +8770,14 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="32" t="n">
+      <c r="A77" s="31" t="n">
         <v>37.98</v>
       </c>
-      <c r="B77" s="32">
+      <c r="B77" s="31">
         <f>A77-$B$12</f>
         <v/>
       </c>
-      <c r="C77" s="32">
+      <c r="C77" s="31">
         <f>MAX(0,A77-$B$6)</f>
         <v/>
       </c>
@@ -10068,15 +8785,15 @@
         <f>IF(C77&lt;=0,0,($B$7+$B$9*C77)*C77)</f>
         <v/>
       </c>
-      <c r="E77" s="26">
+      <c r="E77" s="25">
         <f>D77*$B$11</f>
         <v/>
       </c>
-      <c r="F77" s="26">
-        <f>IF(A77&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A77&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A77,SS_Amont!$A$11:$A$18,1))+(A77-INDEX(SS_Amont!$A$11:$A$18,MATCH(A77,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A77,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A77,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A77,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A77,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G77" s="34">
+      <c r="F77" s="25">
+        <f>IF(A77&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A77&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A77,Stage_Storage!$A$11:$A$18,1))+(A77-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A77,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A77,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A77,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A77,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A77,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G77" s="33">
         <f>E77+F77</f>
         <v/>
       </c>
@@ -10098,14 +8815,14 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="32" t="n">
+      <c r="A78" s="31" t="n">
         <v>38.03</v>
       </c>
-      <c r="B78" s="32">
+      <c r="B78" s="31">
         <f>A78-$B$12</f>
         <v/>
       </c>
-      <c r="C78" s="32">
+      <c r="C78" s="31">
         <f>MAX(0,A78-$B$6)</f>
         <v/>
       </c>
@@ -10113,15 +8830,15 @@
         <f>IF(C78&lt;=0,0,($B$7+$B$9*C78)*C78)</f>
         <v/>
       </c>
-      <c r="E78" s="26">
+      <c r="E78" s="25">
         <f>D78*$B$11</f>
         <v/>
       </c>
-      <c r="F78" s="26">
-        <f>IF(A78&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A78&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A78,SS_Amont!$A$11:$A$18,1))+(A78-INDEX(SS_Amont!$A$11:$A$18,MATCH(A78,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A78,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A78,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A78,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A78,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G78" s="34">
+      <c r="F78" s="25">
+        <f>IF(A78&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A78&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A78,Stage_Storage!$A$11:$A$18,1))+(A78-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A78,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A78,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A78,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A78,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A78,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G78" s="33">
         <f>E78+F78</f>
         <v/>
       </c>
@@ -10143,14 +8860,14 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="32" t="n">
+      <c r="A79" s="31" t="n">
         <v>38.08</v>
       </c>
-      <c r="B79" s="32">
+      <c r="B79" s="31">
         <f>A79-$B$12</f>
         <v/>
       </c>
-      <c r="C79" s="32">
+      <c r="C79" s="31">
         <f>MAX(0,A79-$B$6)</f>
         <v/>
       </c>
@@ -10158,15 +8875,15 @@
         <f>IF(C79&lt;=0,0,($B$7+$B$9*C79)*C79)</f>
         <v/>
       </c>
-      <c r="E79" s="26">
+      <c r="E79" s="25">
         <f>D79*$B$11</f>
         <v/>
       </c>
-      <c r="F79" s="26">
-        <f>IF(A79&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A79&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A79,SS_Amont!$A$11:$A$18,1))+(A79-INDEX(SS_Amont!$A$11:$A$18,MATCH(A79,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A79,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A79,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A79,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A79,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G79" s="34">
+      <c r="F79" s="25">
+        <f>IF(A79&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A79&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A79,Stage_Storage!$A$11:$A$18,1))+(A79-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A79,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A79,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A79,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A79,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A79,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G79" s="33">
         <f>E79+F79</f>
         <v/>
       </c>
@@ -10188,14 +8905,14 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="32" t="n">
+      <c r="A80" s="31" t="n">
         <v>38.13</v>
       </c>
-      <c r="B80" s="32">
+      <c r="B80" s="31">
         <f>A80-$B$12</f>
         <v/>
       </c>
-      <c r="C80" s="32">
+      <c r="C80" s="31">
         <f>MAX(0,A80-$B$6)</f>
         <v/>
       </c>
@@ -10203,15 +8920,15 @@
         <f>IF(C80&lt;=0,0,($B$7+$B$9*C80)*C80)</f>
         <v/>
       </c>
-      <c r="E80" s="26">
+      <c r="E80" s="25">
         <f>D80*$B$11</f>
         <v/>
       </c>
-      <c r="F80" s="26">
-        <f>IF(A80&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A80&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A80,SS_Amont!$A$11:$A$18,1))+(A80-INDEX(SS_Amont!$A$11:$A$18,MATCH(A80,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A80,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A80,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A80,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A80,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G80" s="34">
+      <c r="F80" s="25">
+        <f>IF(A80&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A80&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A80,Stage_Storage!$A$11:$A$18,1))+(A80-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A80,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A80,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A80,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A80,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A80,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G80" s="33">
         <f>E80+F80</f>
         <v/>
       </c>
@@ -10233,14 +8950,14 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="32" t="n">
+      <c r="A81" s="31" t="n">
         <v>38.18</v>
       </c>
-      <c r="B81" s="32">
+      <c r="B81" s="31">
         <f>A81-$B$12</f>
         <v/>
       </c>
-      <c r="C81" s="32">
+      <c r="C81" s="31">
         <f>MAX(0,A81-$B$6)</f>
         <v/>
       </c>
@@ -10248,15 +8965,15 @@
         <f>IF(C81&lt;=0,0,($B$7+$B$9*C81)*C81)</f>
         <v/>
       </c>
-      <c r="E81" s="26">
+      <c r="E81" s="25">
         <f>D81*$B$11</f>
         <v/>
       </c>
-      <c r="F81" s="26">
-        <f>IF(A81&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A81&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A81,SS_Amont!$A$11:$A$18,1))+(A81-INDEX(SS_Amont!$A$11:$A$18,MATCH(A81,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A81,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A81,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A81,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A81,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G81" s="34">
+      <c r="F81" s="25">
+        <f>IF(A81&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A81&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A81,Stage_Storage!$A$11:$A$18,1))+(A81-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A81,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A81,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A81,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A81,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A81,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G81" s="33">
         <f>E81+F81</f>
         <v/>
       </c>
@@ -10278,14 +8995,14 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="32" t="n">
+      <c r="A82" s="31" t="n">
         <v>38.23</v>
       </c>
-      <c r="B82" s="32">
+      <c r="B82" s="31">
         <f>A82-$B$12</f>
         <v/>
       </c>
-      <c r="C82" s="32">
+      <c r="C82" s="31">
         <f>MAX(0,A82-$B$6)</f>
         <v/>
       </c>
@@ -10293,15 +9010,15 @@
         <f>IF(C82&lt;=0,0,($B$7+$B$9*C82)*C82)</f>
         <v/>
       </c>
-      <c r="E82" s="26">
+      <c r="E82" s="25">
         <f>D82*$B$11</f>
         <v/>
       </c>
-      <c r="F82" s="26">
-        <f>IF(A82&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A82&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A82,SS_Amont!$A$11:$A$18,1))+(A82-INDEX(SS_Amont!$A$11:$A$18,MATCH(A82,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A82,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A82,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A82,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A82,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G82" s="34">
+      <c r="F82" s="25">
+        <f>IF(A82&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A82&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A82,Stage_Storage!$A$11:$A$18,1))+(A82-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A82,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A82,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A82,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A82,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A82,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G82" s="33">
         <f>E82+F82</f>
         <v/>
       </c>
@@ -10323,14 +9040,14 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="32" t="n">
+      <c r="A83" s="31" t="n">
         <v>38.28</v>
       </c>
-      <c r="B83" s="32">
+      <c r="B83" s="31">
         <f>A83-$B$12</f>
         <v/>
       </c>
-      <c r="C83" s="32">
+      <c r="C83" s="31">
         <f>MAX(0,A83-$B$6)</f>
         <v/>
       </c>
@@ -10338,15 +9055,15 @@
         <f>IF(C83&lt;=0,0,($B$7+$B$9*C83)*C83)</f>
         <v/>
       </c>
-      <c r="E83" s="26">
+      <c r="E83" s="25">
         <f>D83*$B$11</f>
         <v/>
       </c>
-      <c r="F83" s="26">
-        <f>IF(A83&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A83&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A83,SS_Amont!$A$11:$A$18,1))+(A83-INDEX(SS_Amont!$A$11:$A$18,MATCH(A83,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A83,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A83,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A83,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A83,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G83" s="34">
+      <c r="F83" s="25">
+        <f>IF(A83&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A83&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A83,Stage_Storage!$A$11:$A$18,1))+(A83-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A83,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A83,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A83,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A83,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A83,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G83" s="33">
         <f>E83+F83</f>
         <v/>
       </c>
@@ -10368,14 +9085,14 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="32" t="n">
+      <c r="A84" s="31" t="n">
         <v>38.33</v>
       </c>
-      <c r="B84" s="32">
+      <c r="B84" s="31">
         <f>A84-$B$12</f>
         <v/>
       </c>
-      <c r="C84" s="32">
+      <c r="C84" s="31">
         <f>MAX(0,A84-$B$6)</f>
         <v/>
       </c>
@@ -10383,15 +9100,15 @@
         <f>IF(C84&lt;=0,0,($B$7+$B$9*C84)*C84)</f>
         <v/>
       </c>
-      <c r="E84" s="26">
+      <c r="E84" s="25">
         <f>D84*$B$11</f>
         <v/>
       </c>
-      <c r="F84" s="26">
-        <f>IF(A84&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A84&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A84,SS_Amont!$A$11:$A$18,1))+(A84-INDEX(SS_Amont!$A$11:$A$18,MATCH(A84,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A84,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A84,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A84,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A84,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G84" s="34">
+      <c r="F84" s="25">
+        <f>IF(A84&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A84&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A84,Stage_Storage!$A$11:$A$18,1))+(A84-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A84,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A84,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A84,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A84,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A84,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G84" s="33">
         <f>E84+F84</f>
         <v/>
       </c>
@@ -10413,14 +9130,14 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="32" t="n">
+      <c r="A85" s="31" t="n">
         <v>38.38</v>
       </c>
-      <c r="B85" s="32">
+      <c r="B85" s="31">
         <f>A85-$B$12</f>
         <v/>
       </c>
-      <c r="C85" s="32">
+      <c r="C85" s="31">
         <f>MAX(0,A85-$B$6)</f>
         <v/>
       </c>
@@ -10428,15 +9145,15 @@
         <f>IF(C85&lt;=0,0,($B$7+$B$9*C85)*C85)</f>
         <v/>
       </c>
-      <c r="E85" s="26">
+      <c r="E85" s="25">
         <f>D85*$B$11</f>
         <v/>
       </c>
-      <c r="F85" s="26">
-        <f>IF(A85&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A85&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A85,SS_Amont!$A$11:$A$18,1))+(A85-INDEX(SS_Amont!$A$11:$A$18,MATCH(A85,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A85,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A85,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A85,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A85,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G85" s="34">
+      <c r="F85" s="25">
+        <f>IF(A85&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A85&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A85,Stage_Storage!$A$11:$A$18,1))+(A85-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A85,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A85,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A85,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A85,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A85,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G85" s="33">
         <f>E85+F85</f>
         <v/>
       </c>
@@ -10458,14 +9175,14 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="32" t="n">
+      <c r="A86" s="31" t="n">
         <v>38.43</v>
       </c>
-      <c r="B86" s="32">
+      <c r="B86" s="31">
         <f>A86-$B$12</f>
         <v/>
       </c>
-      <c r="C86" s="32">
+      <c r="C86" s="31">
         <f>MAX(0,A86-$B$6)</f>
         <v/>
       </c>
@@ -10473,15 +9190,15 @@
         <f>IF(C86&lt;=0,0,($B$7+$B$9*C86)*C86)</f>
         <v/>
       </c>
-      <c r="E86" s="26">
+      <c r="E86" s="25">
         <f>D86*$B$11</f>
         <v/>
       </c>
-      <c r="F86" s="26">
-        <f>IF(A86&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A86&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A86,SS_Amont!$A$11:$A$18,1))+(A86-INDEX(SS_Amont!$A$11:$A$18,MATCH(A86,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A86,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A86,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A86,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A86,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G86" s="34">
+      <c r="F86" s="25">
+        <f>IF(A86&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A86&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A86,Stage_Storage!$A$11:$A$18,1))+(A86-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A86,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A86,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A86,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A86,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A86,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G86" s="33">
         <f>E86+F86</f>
         <v/>
       </c>
@@ -10503,14 +9220,14 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="32" t="n">
+      <c r="A87" s="31" t="n">
         <v>38.48</v>
       </c>
-      <c r="B87" s="32">
+      <c r="B87" s="31">
         <f>A87-$B$12</f>
         <v/>
       </c>
-      <c r="C87" s="32">
+      <c r="C87" s="31">
         <f>MAX(0,A87-$B$6)</f>
         <v/>
       </c>
@@ -10518,15 +9235,15 @@
         <f>IF(C87&lt;=0,0,($B$7+$B$9*C87)*C87)</f>
         <v/>
       </c>
-      <c r="E87" s="26">
+      <c r="E87" s="25">
         <f>D87*$B$11</f>
         <v/>
       </c>
-      <c r="F87" s="26">
-        <f>IF(A87&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A87&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A87,SS_Amont!$A$11:$A$18,1))+(A87-INDEX(SS_Amont!$A$11:$A$18,MATCH(A87,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A87,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A87,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A87,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A87,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G87" s="34">
+      <c r="F87" s="25">
+        <f>IF(A87&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A87&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A87,Stage_Storage!$A$11:$A$18,1))+(A87-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A87,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A87,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A87,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A87,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A87,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G87" s="33">
         <f>E87+F87</f>
         <v/>
       </c>
@@ -10548,14 +9265,14 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="32" t="n">
+      <c r="A88" s="31" t="n">
         <v>38.53</v>
       </c>
-      <c r="B88" s="32">
+      <c r="B88" s="31">
         <f>A88-$B$12</f>
         <v/>
       </c>
-      <c r="C88" s="32">
+      <c r="C88" s="31">
         <f>MAX(0,A88-$B$6)</f>
         <v/>
       </c>
@@ -10563,15 +9280,15 @@
         <f>IF(C88&lt;=0,0,($B$7+$B$9*C88)*C88)</f>
         <v/>
       </c>
-      <c r="E88" s="26">
+      <c r="E88" s="25">
         <f>D88*$B$11</f>
         <v/>
       </c>
-      <c r="F88" s="26">
-        <f>IF(A88&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A88&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A88,SS_Amont!$A$11:$A$18,1))+(A88-INDEX(SS_Amont!$A$11:$A$18,MATCH(A88,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A88,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A88,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A88,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A88,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G88" s="34">
+      <c r="F88" s="25">
+        <f>IF(A88&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A88&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A88,Stage_Storage!$A$11:$A$18,1))+(A88-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A88,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A88,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A88,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A88,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A88,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G88" s="33">
         <f>E88+F88</f>
         <v/>
       </c>
@@ -10593,14 +9310,14 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="32" t="n">
+      <c r="A89" s="31" t="n">
         <v>38.58</v>
       </c>
-      <c r="B89" s="32">
+      <c r="B89" s="31">
         <f>A89-$B$12</f>
         <v/>
       </c>
-      <c r="C89" s="32">
+      <c r="C89" s="31">
         <f>MAX(0,A89-$B$6)</f>
         <v/>
       </c>
@@ -10608,15 +9325,15 @@
         <f>IF(C89&lt;=0,0,($B$7+$B$9*C89)*C89)</f>
         <v/>
       </c>
-      <c r="E89" s="26">
+      <c r="E89" s="25">
         <f>D89*$B$11</f>
         <v/>
       </c>
-      <c r="F89" s="26">
-        <f>IF(A89&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A89&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A89,SS_Amont!$A$11:$A$18,1))+(A89-INDEX(SS_Amont!$A$11:$A$18,MATCH(A89,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A89,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A89,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A89,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A89,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G89" s="34">
+      <c r="F89" s="25">
+        <f>IF(A89&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A89&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A89,Stage_Storage!$A$11:$A$18,1))+(A89-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A89,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A89,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A89,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A89,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A89,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G89" s="33">
         <f>E89+F89</f>
         <v/>
       </c>
@@ -10638,14 +9355,14 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="32" t="n">
+      <c r="A90" s="31" t="n">
         <v>38.63</v>
       </c>
-      <c r="B90" s="32">
+      <c r="B90" s="31">
         <f>A90-$B$12</f>
         <v/>
       </c>
-      <c r="C90" s="32">
+      <c r="C90" s="31">
         <f>MAX(0,A90-$B$6)</f>
         <v/>
       </c>
@@ -10653,15 +9370,15 @@
         <f>IF(C90&lt;=0,0,($B$7+$B$9*C90)*C90)</f>
         <v/>
       </c>
-      <c r="E90" s="26">
+      <c r="E90" s="25">
         <f>D90*$B$11</f>
         <v/>
       </c>
-      <c r="F90" s="26">
-        <f>IF(A90&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A90&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A90,SS_Amont!$A$11:$A$18,1))+(A90-INDEX(SS_Amont!$A$11:$A$18,MATCH(A90,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A90,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A90,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A90,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A90,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G90" s="34">
+      <c r="F90" s="25">
+        <f>IF(A90&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A90&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A90,Stage_Storage!$A$11:$A$18,1))+(A90-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A90,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A90,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A90,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A90,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A90,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G90" s="33">
         <f>E90+F90</f>
         <v/>
       </c>
@@ -10683,14 +9400,14 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="32" t="n">
+      <c r="A91" s="31" t="n">
         <v>38.68</v>
       </c>
-      <c r="B91" s="32">
+      <c r="B91" s="31">
         <f>A91-$B$12</f>
         <v/>
       </c>
-      <c r="C91" s="32">
+      <c r="C91" s="31">
         <f>MAX(0,A91-$B$6)</f>
         <v/>
       </c>
@@ -10698,15 +9415,15 @@
         <f>IF(C91&lt;=0,0,($B$7+$B$9*C91)*C91)</f>
         <v/>
       </c>
-      <c r="E91" s="26">
+      <c r="E91" s="25">
         <f>D91*$B$11</f>
         <v/>
       </c>
-      <c r="F91" s="26">
-        <f>IF(A91&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A91&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A91,SS_Amont!$A$11:$A$18,1))+(A91-INDEX(SS_Amont!$A$11:$A$18,MATCH(A91,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A91,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A91,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A91,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A91,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G91" s="34">
+      <c r="F91" s="25">
+        <f>IF(A91&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A91&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A91,Stage_Storage!$A$11:$A$18,1))+(A91-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A91,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A91,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A91,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A91,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A91,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G91" s="33">
         <f>E91+F91</f>
         <v/>
       </c>
@@ -10728,14 +9445,14 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="32" t="n">
+      <c r="A92" s="31" t="n">
         <v>38.73</v>
       </c>
-      <c r="B92" s="32">
+      <c r="B92" s="31">
         <f>A92-$B$12</f>
         <v/>
       </c>
-      <c r="C92" s="32">
+      <c r="C92" s="31">
         <f>MAX(0,A92-$B$6)</f>
         <v/>
       </c>
@@ -10743,15 +9460,15 @@
         <f>IF(C92&lt;=0,0,($B$7+$B$9*C92)*C92)</f>
         <v/>
       </c>
-      <c r="E92" s="26">
+      <c r="E92" s="25">
         <f>D92*$B$11</f>
         <v/>
       </c>
-      <c r="F92" s="26">
-        <f>IF(A92&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A92&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A92,SS_Amont!$A$11:$A$18,1))+(A92-INDEX(SS_Amont!$A$11:$A$18,MATCH(A92,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A92,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A92,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A92,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A92,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G92" s="34">
+      <c r="F92" s="25">
+        <f>IF(A92&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A92&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A92,Stage_Storage!$A$11:$A$18,1))+(A92-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A92,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A92,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A92,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A92,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A92,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G92" s="33">
         <f>E92+F92</f>
         <v/>
       </c>
@@ -10773,14 +9490,14 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="32" t="n">
+      <c r="A93" s="31" t="n">
         <v>38.78</v>
       </c>
-      <c r="B93" s="32">
+      <c r="B93" s="31">
         <f>A93-$B$12</f>
         <v/>
       </c>
-      <c r="C93" s="32">
+      <c r="C93" s="31">
         <f>MAX(0,A93-$B$6)</f>
         <v/>
       </c>
@@ -10788,15 +9505,15 @@
         <f>IF(C93&lt;=0,0,($B$7+$B$9*C93)*C93)</f>
         <v/>
       </c>
-      <c r="E93" s="26">
+      <c r="E93" s="25">
         <f>D93*$B$11</f>
         <v/>
       </c>
-      <c r="F93" s="26">
-        <f>IF(A93&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A93&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A93,SS_Amont!$A$11:$A$18,1))+(A93-INDEX(SS_Amont!$A$11:$A$18,MATCH(A93,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A93,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A93,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A93,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A93,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G93" s="34">
+      <c r="F93" s="25">
+        <f>IF(A93&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A93&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A93,Stage_Storage!$A$11:$A$18,1))+(A93-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A93,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A93,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A93,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A93,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A93,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G93" s="33">
         <f>E93+F93</f>
         <v/>
       </c>
@@ -10818,14 +9535,14 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="32" t="n">
+      <c r="A94" s="31" t="n">
         <v>38.83</v>
       </c>
-      <c r="B94" s="32">
+      <c r="B94" s="31">
         <f>A94-$B$12</f>
         <v/>
       </c>
-      <c r="C94" s="32">
+      <c r="C94" s="31">
         <f>MAX(0,A94-$B$6)</f>
         <v/>
       </c>
@@ -10833,15 +9550,15 @@
         <f>IF(C94&lt;=0,0,($B$7+$B$9*C94)*C94)</f>
         <v/>
       </c>
-      <c r="E94" s="26">
+      <c r="E94" s="25">
         <f>D94*$B$11</f>
         <v/>
       </c>
-      <c r="F94" s="26">
-        <f>IF(A94&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A94&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A94,SS_Amont!$A$11:$A$18,1))+(A94-INDEX(SS_Amont!$A$11:$A$18,MATCH(A94,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A94,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A94,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A94,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A94,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G94" s="34">
+      <c r="F94" s="25">
+        <f>IF(A94&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A94&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A94,Stage_Storage!$A$11:$A$18,1))+(A94-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A94,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A94,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A94,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A94,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A94,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G94" s="33">
         <f>E94+F94</f>
         <v/>
       </c>
@@ -10863,14 +9580,14 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="32" t="n">
+      <c r="A95" s="31" t="n">
         <v>38.88</v>
       </c>
-      <c r="B95" s="32">
+      <c r="B95" s="31">
         <f>A95-$B$12</f>
         <v/>
       </c>
-      <c r="C95" s="32">
+      <c r="C95" s="31">
         <f>MAX(0,A95-$B$6)</f>
         <v/>
       </c>
@@ -10878,15 +9595,15 @@
         <f>IF(C95&lt;=0,0,($B$7+$B$9*C95)*C95)</f>
         <v/>
       </c>
-      <c r="E95" s="26">
+      <c r="E95" s="25">
         <f>D95*$B$11</f>
         <v/>
       </c>
-      <c r="F95" s="26">
-        <f>IF(A95&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A95&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A95,SS_Amont!$A$11:$A$18,1))+(A95-INDEX(SS_Amont!$A$11:$A$18,MATCH(A95,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A95,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A95,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A95,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A95,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G95" s="34">
+      <c r="F95" s="25">
+        <f>IF(A95&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A95&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A95,Stage_Storage!$A$11:$A$18,1))+(A95-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A95,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A95,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A95,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A95,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A95,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G95" s="33">
         <f>E95+F95</f>
         <v/>
       </c>
@@ -10908,14 +9625,14 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="32" t="n">
+      <c r="A96" s="31" t="n">
         <v>38.93</v>
       </c>
-      <c r="B96" s="32">
+      <c r="B96" s="31">
         <f>A96-$B$12</f>
         <v/>
       </c>
-      <c r="C96" s="32">
+      <c r="C96" s="31">
         <f>MAX(0,A96-$B$6)</f>
         <v/>
       </c>
@@ -10923,15 +9640,15 @@
         <f>IF(C96&lt;=0,0,($B$7+$B$9*C96)*C96)</f>
         <v/>
       </c>
-      <c r="E96" s="26">
+      <c r="E96" s="25">
         <f>D96*$B$11</f>
         <v/>
       </c>
-      <c r="F96" s="26">
-        <f>IF(A96&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A96&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A96,SS_Amont!$A$11:$A$18,1))+(A96-INDEX(SS_Amont!$A$11:$A$18,MATCH(A96,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A96,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A96,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A96,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A96,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G96" s="34">
+      <c r="F96" s="25">
+        <f>IF(A96&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A96&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A96,Stage_Storage!$A$11:$A$18,1))+(A96-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A96,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A96,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A96,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A96,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A96,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G96" s="33">
         <f>E96+F96</f>
         <v/>
       </c>
@@ -10953,14 +9670,14 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="32" t="n">
+      <c r="A97" s="31" t="n">
         <v>38.98</v>
       </c>
-      <c r="B97" s="32">
+      <c r="B97" s="31">
         <f>A97-$B$12</f>
         <v/>
       </c>
-      <c r="C97" s="32">
+      <c r="C97" s="31">
         <f>MAX(0,A97-$B$6)</f>
         <v/>
       </c>
@@ -10968,15 +9685,15 @@
         <f>IF(C97&lt;=0,0,($B$7+$B$9*C97)*C97)</f>
         <v/>
       </c>
-      <c r="E97" s="26">
+      <c r="E97" s="25">
         <f>D97*$B$11</f>
         <v/>
       </c>
-      <c r="F97" s="26">
-        <f>IF(A97&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A97&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A97,SS_Amont!$A$11:$A$18,1))+(A97-INDEX(SS_Amont!$A$11:$A$18,MATCH(A97,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A97,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A97,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A97,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A97,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G97" s="34">
+      <c r="F97" s="25">
+        <f>IF(A97&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A97&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A97,Stage_Storage!$A$11:$A$18,1))+(A97-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A97,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A97,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A97,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A97,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A97,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G97" s="33">
         <f>E97+F97</f>
         <v/>
       </c>
@@ -10998,14 +9715,14 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="32" t="n">
+      <c r="A98" s="31" t="n">
         <v>39.03</v>
       </c>
-      <c r="B98" s="32">
+      <c r="B98" s="31">
         <f>A98-$B$12</f>
         <v/>
       </c>
-      <c r="C98" s="32">
+      <c r="C98" s="31">
         <f>MAX(0,A98-$B$6)</f>
         <v/>
       </c>
@@ -11013,15 +9730,15 @@
         <f>IF(C98&lt;=0,0,($B$7+$B$9*C98)*C98)</f>
         <v/>
       </c>
-      <c r="E98" s="26">
+      <c r="E98" s="25">
         <f>D98*$B$11</f>
         <v/>
       </c>
-      <c r="F98" s="26">
-        <f>IF(A98&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A98&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A98,SS_Amont!$A$11:$A$18,1))+(A98-INDEX(SS_Amont!$A$11:$A$18,MATCH(A98,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A98,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A98,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A98,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A98,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G98" s="34">
+      <c r="F98" s="25">
+        <f>IF(A98&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A98&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A98,Stage_Storage!$A$11:$A$18,1))+(A98-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A98,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A98,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A98,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A98,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A98,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G98" s="33">
         <f>E98+F98</f>
         <v/>
       </c>
@@ -11043,14 +9760,14 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="32" t="n">
+      <c r="A99" s="31" t="n">
         <v>39.08</v>
       </c>
-      <c r="B99" s="32">
+      <c r="B99" s="31">
         <f>A99-$B$12</f>
         <v/>
       </c>
-      <c r="C99" s="32">
+      <c r="C99" s="31">
         <f>MAX(0,A99-$B$6)</f>
         <v/>
       </c>
@@ -11058,15 +9775,15 @@
         <f>IF(C99&lt;=0,0,($B$7+$B$9*C99)*C99)</f>
         <v/>
       </c>
-      <c r="E99" s="26">
+      <c r="E99" s="25">
         <f>D99*$B$11</f>
         <v/>
       </c>
-      <c r="F99" s="26">
-        <f>IF(A99&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A99&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A99,SS_Amont!$A$11:$A$18,1))+(A99-INDEX(SS_Amont!$A$11:$A$18,MATCH(A99,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A99,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A99,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A99,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A99,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G99" s="34">
+      <c r="F99" s="25">
+        <f>IF(A99&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A99&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A99,Stage_Storage!$A$11:$A$18,1))+(A99-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A99,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A99,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A99,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A99,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A99,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G99" s="33">
         <f>E99+F99</f>
         <v/>
       </c>
@@ -11088,14 +9805,14 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="32" t="n">
+      <c r="A100" s="31" t="n">
         <v>39.13</v>
       </c>
-      <c r="B100" s="32">
+      <c r="B100" s="31">
         <f>A100-$B$12</f>
         <v/>
       </c>
-      <c r="C100" s="32">
+      <c r="C100" s="31">
         <f>MAX(0,A100-$B$6)</f>
         <v/>
       </c>
@@ -11103,15 +9820,15 @@
         <f>IF(C100&lt;=0,0,($B$7+$B$9*C100)*C100)</f>
         <v/>
       </c>
-      <c r="E100" s="26">
+      <c r="E100" s="25">
         <f>D100*$B$11</f>
         <v/>
       </c>
-      <c r="F100" s="26">
-        <f>IF(A100&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A100&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A100,SS_Amont!$A$11:$A$18,1))+(A100-INDEX(SS_Amont!$A$11:$A$18,MATCH(A100,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A100,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A100,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A100,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A100,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G100" s="34">
+      <c r="F100" s="25">
+        <f>IF(A100&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A100&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A100,Stage_Storage!$A$11:$A$18,1))+(A100-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A100,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A100,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A100,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A100,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A100,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G100" s="33">
         <f>E100+F100</f>
         <v/>
       </c>
@@ -11133,14 +9850,14 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="32" t="n">
+      <c r="A101" s="31" t="n">
         <v>39.18</v>
       </c>
-      <c r="B101" s="32">
+      <c r="B101" s="31">
         <f>A101-$B$12</f>
         <v/>
       </c>
-      <c r="C101" s="32">
+      <c r="C101" s="31">
         <f>MAX(0,A101-$B$6)</f>
         <v/>
       </c>
@@ -11148,15 +9865,15 @@
         <f>IF(C101&lt;=0,0,($B$7+$B$9*C101)*C101)</f>
         <v/>
       </c>
-      <c r="E101" s="26">
+      <c r="E101" s="25">
         <f>D101*$B$11</f>
         <v/>
       </c>
-      <c r="F101" s="26">
-        <f>IF(A101&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A101&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A101,SS_Amont!$A$11:$A$18,1))+(A101-INDEX(SS_Amont!$A$11:$A$18,MATCH(A101,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A101,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A101,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A101,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A101,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G101" s="34">
+      <c r="F101" s="25">
+        <f>IF(A101&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A101&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A101,Stage_Storage!$A$11:$A$18,1))+(A101-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A101,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A101,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A101,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A101,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A101,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G101" s="33">
         <f>E101+F101</f>
         <v/>
       </c>
@@ -11178,14 +9895,14 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="32" t="n">
+      <c r="A102" s="31" t="n">
         <v>39.23</v>
       </c>
-      <c r="B102" s="32">
+      <c r="B102" s="31">
         <f>A102-$B$12</f>
         <v/>
       </c>
-      <c r="C102" s="32">
+      <c r="C102" s="31">
         <f>MAX(0,A102-$B$6)</f>
         <v/>
       </c>
@@ -11193,15 +9910,15 @@
         <f>IF(C102&lt;=0,0,($B$7+$B$9*C102)*C102)</f>
         <v/>
       </c>
-      <c r="E102" s="26">
+      <c r="E102" s="25">
         <f>D102*$B$11</f>
         <v/>
       </c>
-      <c r="F102" s="26">
-        <f>IF(A102&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A102&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A102,SS_Amont!$A$11:$A$18,1))+(A102-INDEX(SS_Amont!$A$11:$A$18,MATCH(A102,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A102,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A102,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A102,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A102,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G102" s="34">
+      <c r="F102" s="25">
+        <f>IF(A102&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A102&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A102,Stage_Storage!$A$11:$A$18,1))+(A102-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A102,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A102,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A102,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A102,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A102,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G102" s="33">
         <f>E102+F102</f>
         <v/>
       </c>
@@ -11223,14 +9940,14 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="32" t="n">
+      <c r="A103" s="31" t="n">
         <v>39.28</v>
       </c>
-      <c r="B103" s="32">
+      <c r="B103" s="31">
         <f>A103-$B$12</f>
         <v/>
       </c>
-      <c r="C103" s="32">
+      <c r="C103" s="31">
         <f>MAX(0,A103-$B$6)</f>
         <v/>
       </c>
@@ -11238,15 +9955,15 @@
         <f>IF(C103&lt;=0,0,($B$7+$B$9*C103)*C103)</f>
         <v/>
       </c>
-      <c r="E103" s="26">
+      <c r="E103" s="25">
         <f>D103*$B$11</f>
         <v/>
       </c>
-      <c r="F103" s="26">
-        <f>IF(A103&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A103&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A103,SS_Amont!$A$11:$A$18,1))+(A103-INDEX(SS_Amont!$A$11:$A$18,MATCH(A103,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A103,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A103,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A103,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A103,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G103" s="34">
+      <c r="F103" s="25">
+        <f>IF(A103&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A103&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A103,Stage_Storage!$A$11:$A$18,1))+(A103-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A103,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A103,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A103,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A103,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A103,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G103" s="33">
         <f>E103+F103</f>
         <v/>
       </c>
@@ -11268,14 +9985,14 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="32" t="n">
+      <c r="A104" s="31" t="n">
         <v>39.33</v>
       </c>
-      <c r="B104" s="32">
+      <c r="B104" s="31">
         <f>A104-$B$12</f>
         <v/>
       </c>
-      <c r="C104" s="32">
+      <c r="C104" s="31">
         <f>MAX(0,A104-$B$6)</f>
         <v/>
       </c>
@@ -11283,15 +10000,15 @@
         <f>IF(C104&lt;=0,0,($B$7+$B$9*C104)*C104)</f>
         <v/>
       </c>
-      <c r="E104" s="26">
+      <c r="E104" s="25">
         <f>D104*$B$11</f>
         <v/>
       </c>
-      <c r="F104" s="26">
-        <f>IF(A104&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A104&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A104,SS_Amont!$A$11:$A$18,1))+(A104-INDEX(SS_Amont!$A$11:$A$18,MATCH(A104,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A104,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A104,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A104,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A104,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G104" s="34">
+      <c r="F104" s="25">
+        <f>IF(A104&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A104&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A104,Stage_Storage!$A$11:$A$18,1))+(A104-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A104,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A104,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A104,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A104,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A104,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G104" s="33">
         <f>E104+F104</f>
         <v/>
       </c>
@@ -11313,14 +10030,14 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="32" t="n">
+      <c r="A105" s="31" t="n">
         <v>39.38</v>
       </c>
-      <c r="B105" s="32">
+      <c r="B105" s="31">
         <f>A105-$B$12</f>
         <v/>
       </c>
-      <c r="C105" s="32">
+      <c r="C105" s="31">
         <f>MAX(0,A105-$B$6)</f>
         <v/>
       </c>
@@ -11328,15 +10045,15 @@
         <f>IF(C105&lt;=0,0,($B$7+$B$9*C105)*C105)</f>
         <v/>
       </c>
-      <c r="E105" s="26">
+      <c r="E105" s="25">
         <f>D105*$B$11</f>
         <v/>
       </c>
-      <c r="F105" s="26">
-        <f>IF(A105&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A105&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A105,SS_Amont!$A$11:$A$18,1))+(A105-INDEX(SS_Amont!$A$11:$A$18,MATCH(A105,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A105,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A105,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A105,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A105,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G105" s="34">
+      <c r="F105" s="25">
+        <f>IF(A105&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A105&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A105,Stage_Storage!$A$11:$A$18,1))+(A105-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A105,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A105,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A105,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A105,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A105,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G105" s="33">
         <f>E105+F105</f>
         <v/>
       </c>
@@ -11358,14 +10075,14 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="32" t="n">
+      <c r="A106" s="31" t="n">
         <v>39.43</v>
       </c>
-      <c r="B106" s="32">
+      <c r="B106" s="31">
         <f>A106-$B$12</f>
         <v/>
       </c>
-      <c r="C106" s="32">
+      <c r="C106" s="31">
         <f>MAX(0,A106-$B$6)</f>
         <v/>
       </c>
@@ -11373,15 +10090,15 @@
         <f>IF(C106&lt;=0,0,($B$7+$B$9*C106)*C106)</f>
         <v/>
       </c>
-      <c r="E106" s="26">
+      <c r="E106" s="25">
         <f>D106*$B$11</f>
         <v/>
       </c>
-      <c r="F106" s="26">
-        <f>IF(A106&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A106&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A106,SS_Amont!$A$11:$A$18,1))+(A106-INDEX(SS_Amont!$A$11:$A$18,MATCH(A106,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A106,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A106,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A106,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A106,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G106" s="34">
+      <c r="F106" s="25">
+        <f>IF(A106&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A106&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A106,Stage_Storage!$A$11:$A$18,1))+(A106-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A106,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A106,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A106,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A106,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A106,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G106" s="33">
         <f>E106+F106</f>
         <v/>
       </c>
@@ -11403,14 +10120,14 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="32" t="n">
+      <c r="A107" s="31" t="n">
         <v>39.48</v>
       </c>
-      <c r="B107" s="32">
+      <c r="B107" s="31">
         <f>A107-$B$12</f>
         <v/>
       </c>
-      <c r="C107" s="32">
+      <c r="C107" s="31">
         <f>MAX(0,A107-$B$6)</f>
         <v/>
       </c>
@@ -11418,15 +10135,15 @@
         <f>IF(C107&lt;=0,0,($B$7+$B$9*C107)*C107)</f>
         <v/>
       </c>
-      <c r="E107" s="26">
+      <c r="E107" s="25">
         <f>D107*$B$11</f>
         <v/>
       </c>
-      <c r="F107" s="26">
-        <f>IF(A107&lt;=INDEX(SS_Amont!$A$11:$A$18,1),INDEX(SS_Amont!$E$11:$E$18,1),IF(A107&gt;=INDEX(SS_Amont!$A$11:$A$18,ROWS(SS_Amont!$A$11:$A$18)),INDEX(SS_Amont!$E$11:$E$18,ROWS(SS_Amont!$E$11:$E$18)),INDEX(SS_Amont!$E$11:$E$18,MATCH(A107,SS_Amont!$A$11:$A$18,1))+(A107-INDEX(SS_Amont!$A$11:$A$18,MATCH(A107,SS_Amont!$A$11:$A$18,1)))/(INDEX(SS_Amont!$A$11:$A$18,MATCH(A107,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$A$11:$A$18,MATCH(A107,SS_Amont!$A$11:$A$18,1)))*(INDEX(SS_Amont!$E$11:$E$18,MATCH(A107,SS_Amont!$A$11:$A$18,1)+1)-INDEX(SS_Amont!$E$11:$E$18,MATCH(A107,SS_Amont!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G107" s="34">
+      <c r="F107" s="25">
+        <f>IF(A107&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A107&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A107,Stage_Storage!$A$11:$A$18,1))+(A107-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A107,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A107,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A107,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A107,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A107,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G107" s="33">
         <f>E107+F107</f>
         <v/>
       </c>
@@ -11475,14 +10192,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Méthode C — routage avec Qout composé + V = V_pond + V_ditch</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="40" t="inlineStr">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>À chaque pas: WSE lu sur Compose_900!V_total → Qout sur Compose_900. ΔV = (Qin_moy − Qout)×Δt. Si V≈0, Qout = MIN(Qin, Q_plein).</t>
         </is>
@@ -11495,7 +10212,7 @@
           <t>Q_plein réf. (m³/s)</t>
         </is>
       </c>
-      <c r="B5" s="41">
+      <c r="B5" s="40">
         <f>Parametres!B22</f>
         <v/>
       </c>
@@ -11506,7 +10223,7 @@
           <t>Crest (m)</t>
         </is>
       </c>
-      <c r="B6" s="41">
+      <c r="B6" s="40">
         <f>Parametres!B27</f>
         <v/>
       </c>
@@ -11517,7 +10234,7 @@
           <t>Vmax_C (m³)</t>
         </is>
       </c>
-      <c r="B7" s="31">
+      <c r="B7" s="30">
         <f>MAX(F12:F24)</f>
         <v/>
       </c>
@@ -11598,10 +10315,10 @@
         <f>MIN(B12,$B$5)</f>
         <v/>
       </c>
-      <c r="E12" s="26" t="n">
+      <c r="E12" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="34" t="n">
+      <c r="F12" s="33" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -11627,11 +10344,11 @@
         <f>IF(F12&lt;=0.01,MIN(0.5*(B12+B13),$B$5),IF(C13&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C13&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C13,Compose_900!$A$15:$A$107,1))+(C13-INDEX(Compose_900!$A$15:$A$107,MATCH(C13,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C13,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C13,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C13,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C13,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="25">
         <f>(A13-A12)*60</f>
         <v/>
       </c>
-      <c r="F13" s="34">
+      <c r="F13" s="33">
         <f>MAX(0,F12+(0.5*(B12+B13)-D13)*E13)</f>
         <v/>
       </c>
@@ -11657,11 +10374,11 @@
         <f>IF(F13&lt;=0.01,MIN(0.5*(B13+B14),$B$5),IF(C14&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C14&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C14,Compose_900!$A$15:$A$107,1))+(C14-INDEX(Compose_900!$A$15:$A$107,MATCH(C14,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C14,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C14,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C14,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C14,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="25">
         <f>(A14-A13)*60</f>
         <v/>
       </c>
-      <c r="F14" s="34">
+      <c r="F14" s="33">
         <f>MAX(0,F13+(0.5*(B13+B14)-D14)*E14)</f>
         <v/>
       </c>
@@ -11687,11 +10404,11 @@
         <f>IF(F14&lt;=0.01,MIN(0.5*(B14+B15),$B$5),IF(C15&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C15&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C15,Compose_900!$A$15:$A$107,1))+(C15-INDEX(Compose_900!$A$15:$A$107,MATCH(C15,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C15,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C15,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C15,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C15,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="25">
         <f>(A15-A14)*60</f>
         <v/>
       </c>
-      <c r="F15" s="34">
+      <c r="F15" s="33">
         <f>MAX(0,F14+(0.5*(B14+B15)-D15)*E15)</f>
         <v/>
       </c>
@@ -11717,11 +10434,11 @@
         <f>IF(F15&lt;=0.01,MIN(0.5*(B15+B16),$B$5),IF(C16&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C16&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C16,Compose_900!$A$15:$A$107,1))+(C16-INDEX(Compose_900!$A$15:$A$107,MATCH(C16,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C16,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C16,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C16,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C16,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="25">
         <f>(A16-A15)*60</f>
         <v/>
       </c>
-      <c r="F16" s="34">
+      <c r="F16" s="33">
         <f>MAX(0,F15+(0.5*(B15+B16)-D16)*E16)</f>
         <v/>
       </c>
@@ -11747,11 +10464,11 @@
         <f>IF(F16&lt;=0.01,MIN(0.5*(B16+B17),$B$5),IF(C17&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C17&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C17,Compose_900!$A$15:$A$107,1))+(C17-INDEX(Compose_900!$A$15:$A$107,MATCH(C17,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C17,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C17,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C17,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C17,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="25">
         <f>(A17-A16)*60</f>
         <v/>
       </c>
-      <c r="F17" s="34">
+      <c r="F17" s="33">
         <f>MAX(0,F16+(0.5*(B16+B17)-D17)*E17)</f>
         <v/>
       </c>
@@ -11777,11 +10494,11 @@
         <f>IF(F17&lt;=0.01,MIN(0.5*(B17+B18),$B$5),IF(C18&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C18&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C18,Compose_900!$A$15:$A$107,1))+(C18-INDEX(Compose_900!$A$15:$A$107,MATCH(C18,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C18,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C18,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C18,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C18,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="25">
         <f>(A18-A17)*60</f>
         <v/>
       </c>
-      <c r="F18" s="34">
+      <c r="F18" s="33">
         <f>MAX(0,F17+(0.5*(B17+B18)-D18)*E18)</f>
         <v/>
       </c>
@@ -11807,11 +10524,11 @@
         <f>IF(F18&lt;=0.01,MIN(0.5*(B18+B19),$B$5),IF(C19&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C19&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C19,Compose_900!$A$15:$A$107,1))+(C19-INDEX(Compose_900!$A$15:$A$107,MATCH(C19,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C19,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C19,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C19,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C19,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E19" s="26">
+      <c r="E19" s="25">
         <f>(A19-A18)*60</f>
         <v/>
       </c>
-      <c r="F19" s="34">
+      <c r="F19" s="33">
         <f>MAX(0,F18+(0.5*(B18+B19)-D19)*E19)</f>
         <v/>
       </c>
@@ -11837,11 +10554,11 @@
         <f>IF(F19&lt;=0.01,MIN(0.5*(B19+B20),$B$5),IF(C20&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C20&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C20,Compose_900!$A$15:$A$107,1))+(C20-INDEX(Compose_900!$A$15:$A$107,MATCH(C20,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C20,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C20,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C20,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C20,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="25">
         <f>(A20-A19)*60</f>
         <v/>
       </c>
-      <c r="F20" s="34">
+      <c r="F20" s="33">
         <f>MAX(0,F19+(0.5*(B19+B20)-D20)*E20)</f>
         <v/>
       </c>
@@ -11867,11 +10584,11 @@
         <f>IF(F20&lt;=0.01,MIN(0.5*(B20+B21),$B$5),IF(C21&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C21&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C21,Compose_900!$A$15:$A$107,1))+(C21-INDEX(Compose_900!$A$15:$A$107,MATCH(C21,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C21,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C21,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C21,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C21,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="25">
         <f>(A21-A20)*60</f>
         <v/>
       </c>
-      <c r="F21" s="34">
+      <c r="F21" s="33">
         <f>MAX(0,F20+(0.5*(B20+B21)-D21)*E21)</f>
         <v/>
       </c>
@@ -11897,11 +10614,11 @@
         <f>IF(F21&lt;=0.01,MIN(0.5*(B21+B22),$B$5),IF(C22&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C22&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C22,Compose_900!$A$15:$A$107,1))+(C22-INDEX(Compose_900!$A$15:$A$107,MATCH(C22,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C22,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C22,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C22,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C22,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E22" s="26">
+      <c r="E22" s="25">
         <f>(A22-A21)*60</f>
         <v/>
       </c>
-      <c r="F22" s="34">
+      <c r="F22" s="33">
         <f>MAX(0,F21+(0.5*(B21+B22)-D22)*E22)</f>
         <v/>
       </c>
@@ -11927,11 +10644,11 @@
         <f>IF(F22&lt;=0.01,MIN(0.5*(B22+B23),$B$5),IF(C23&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C23&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C23,Compose_900!$A$15:$A$107,1))+(C23-INDEX(Compose_900!$A$15:$A$107,MATCH(C23,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C23,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C23,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C23,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C23,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E23" s="26">
+      <c r="E23" s="25">
         <f>(A23-A22)*60</f>
         <v/>
       </c>
-      <c r="F23" s="34">
+      <c r="F23" s="33">
         <f>MAX(0,F22+(0.5*(B22+B23)-D23)*E23)</f>
         <v/>
       </c>
@@ -11957,11 +10674,11 @@
         <f>IF(F23&lt;=0.01,MIN(0.5*(B23+B24),$B$5),IF(C24&lt;=INDEX(Compose_900!$A$15:$A$107,1),INDEX(Compose_900!$J$15:$J$107,1),IF(C24&gt;=INDEX(Compose_900!$A$15:$A$107,ROWS(Compose_900!$A$15:$A$107)),INDEX(Compose_900!$J$15:$J$107,ROWS(Compose_900!$J$15:$J$107)),INDEX(Compose_900!$J$15:$J$107,MATCH(C24,Compose_900!$A$15:$A$107,1))+(C24-INDEX(Compose_900!$A$15:$A$107,MATCH(C24,Compose_900!$A$15:$A$107,1)))/(INDEX(Compose_900!$A$15:$A$107,MATCH(C24,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$A$15:$A$107,MATCH(C24,Compose_900!$A$15:$A$107,1)))*(INDEX(Compose_900!$J$15:$J$107,MATCH(C24,Compose_900!$A$15:$A$107,1)+1)-INDEX(Compose_900!$J$15:$J$107,MATCH(C24,Compose_900!$A$15:$A$107,1))))))</f>
         <v/>
       </c>
-      <c r="E24" s="26">
+      <c r="E24" s="25">
         <f>(A24-A23)*60</f>
         <v/>
       </c>
-      <c r="F24" s="34">
+      <c r="F24" s="33">
         <f>MAX(0,F23+(0.5*(B23+B24)-D24)*E24)</f>
         <v/>
       </c>
@@ -11984,28 +10701,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>Zone 1 — Stage–storage Ø1500 → Ø900 (amont)</t>
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>Stage–storage du levé — V = f(WSE) → lire le niveau max</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Jaune = WSE et Surface éditables (corriger depuis AutoCAD). ΔWSE, V_pas, V_cumul = formules live (aires moyennes). Cette feuille alimente WSEmax_A/B et V_pond Méthode C. Parametres!B24 (2500 m²) n'est PAS ici — raccourci Méthode B seulement. Ne pas y mettre les surfaces de Zone 2.</t>
+          <t>PROCÉDURE (dans CE fichier): 1) Routage → Vmax_A / Vmax_B / Vmax_C sur Parametres. 2) Cette feuille = V_pond vs WSE (levé topographique — le vrai bassin). 3) Parametres!B39 = WSEmax_A; B45 = WSEmax_B (lus sur CE tableau). 4) Méthode C: V_pond + V_ditch et WSEmax_C sur Compose_900 / Calcul_C (B51). 5) Parametres!B24 (2500 m²) n'est PAS ici: c'est seulement le raccourci H=V/A de Méthode B. Surfaces ci-dessous = votre levé (pas des placeholders).</t>
         </is>
       </c>
     </row>
@@ -12014,12 +10731,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Formule d'un pas (aires moyennes)</t>
+          <t>Formule d'un pas</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="43" t="inlineStr">
+      <c r="A7" s="42" t="inlineStr">
         <is>
           <t>V_pas (m³) = (A_basse + A_haute) / 2 × (WSE_haute − WSE_basse)</t>
         </is>
@@ -12028,14 +10745,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V_cumulatif = somme des V_pas depuis le fond de zone. Jaune = éditer (AutoCAD).</t>
+          <t>V_cumulatif = somme des V_pas depuis le radier</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>WSE / NSE (m) ← ÉDITER</t>
+          <t>WSE / NSE (m)</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -12065,7 +10782,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="n">
+      <c r="A11" s="31" t="n">
         <v>34.88</v>
       </c>
       <c r="B11" s="17" t="n">
@@ -12082,266 +10799,286 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Fond Zone 1 / radier amont Ø900</t>
+          <t>Fond bassin / radier Ø900</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="n">
+      <c r="A12" s="31" t="n">
         <v>35.5</v>
       </c>
       <c r="B12" s="17" t="n">
-        <v>56</v>
-      </c>
-      <c r="C12" s="32">
+        <v>120</v>
+      </c>
+      <c r="C12" s="31">
         <f>A12-A11</f>
         <v/>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="25">
         <f>0.5*(B11+B12)*C12</f>
         <v/>
       </c>
-      <c r="E12" s="34">
+      <c r="E12" s="33">
         <f>E11+D12</f>
         <v/>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Levé Zone 1 — éditer si AutoCAD diffère</t>
+          <t>Levé</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="n">
+      <c r="A13" s="31" t="n">
         <v>36.01</v>
       </c>
       <c r="B13" s="17" t="n">
-        <v>210</v>
-      </c>
-      <c r="C13" s="32">
+        <v>419</v>
+      </c>
+      <c r="C13" s="31">
         <f>A13-A12</f>
         <v/>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="25">
         <f>0.5*(B12+B13)*C13</f>
         <v/>
       </c>
-      <c r="E13" s="34">
+      <c r="E13" s="33">
         <f>E12+D13</f>
         <v/>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Levé Zone 1</t>
+          <t>Levé</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="n">
+      <c r="A14" s="31" t="n">
         <v>36.5</v>
       </c>
       <c r="B14" s="17" t="n">
-        <v>380</v>
-      </c>
-      <c r="C14" s="32">
+        <v>480</v>
+      </c>
+      <c r="C14" s="31">
         <f>A14-A13</f>
         <v/>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="25">
         <f>0.5*(B13+B14)*C14</f>
         <v/>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="33">
         <f>E13+D14</f>
         <v/>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Levé Zone 1</t>
+          <t>Levé</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="n">
+      <c r="A15" s="31" t="n">
         <v>37</v>
       </c>
       <c r="B15" s="17" t="n">
-        <v>400</v>
-      </c>
-      <c r="C15" s="32">
+        <v>720</v>
+      </c>
+      <c r="C15" s="31">
         <f>A15-A14</f>
         <v/>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="25">
         <f>0.5*(B14+B15)*C15</f>
         <v/>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="33">
         <f>E14+D15</f>
         <v/>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Levé Zone 1</t>
+          <t>Levé</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="n">
+      <c r="A16" s="38" t="n">
         <v>37.28</v>
       </c>
       <c r="B16" s="17" t="n">
-        <v>500</v>
-      </c>
-      <c r="C16" s="39">
+        <v>2198</v>
+      </c>
+      <c r="C16" s="38">
         <f>A16-A15</f>
         <v/>
       </c>
-      <c r="D16" s="42">
+      <c r="D16" s="41">
         <f>0.5*(B15+B16)*C16</f>
         <v/>
       </c>
-      <c r="E16" s="42">
+      <c r="E16" s="41">
         <f>E15+D16</f>
         <v/>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>LIMITE PATRON Zone 1 (+1.5 m crown)</t>
+          <t>LIMITE PATRON (+1.5 m crown) — levé</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="n">
+      <c r="A17" s="31" t="n">
         <v>37.4</v>
       </c>
       <c r="B17" s="17" t="n">
-        <v>860</v>
-      </c>
-      <c r="C17" s="32">
+        <v>1516</v>
+      </c>
+      <c r="C17" s="31">
         <f>A17-A16</f>
         <v/>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="25">
         <f>0.5*(B16+B17)*C17</f>
         <v/>
       </c>
-      <c r="E17" s="34">
+      <c r="E17" s="33">
         <f>E16+D17</f>
         <v/>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Levé Zone 1</t>
+          <t>Levé (A↓ vs 37.28 — vérifier si voulu)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="n">
+      <c r="A18" s="31" t="n">
         <v>40</v>
       </c>
       <c r="B18" s="17" t="n">
-        <v>2100</v>
-      </c>
-      <c r="C18" s="32">
+        <v>3746</v>
+      </c>
+      <c r="C18" s="31">
         <f>A18-A17</f>
         <v/>
       </c>
-      <c r="D18" s="26">
+      <c r="D18" s="25">
         <f>0.5*(B17+B18)*C18</f>
         <v/>
       </c>
-      <c r="E18" s="34">
+      <c r="E18" s="33">
         <f>E17+D18</f>
         <v/>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Sommet table Zone 1</t>
+          <t>Levé — sommet table</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V @ 37.28 m (m³)</t>
-        </is>
-      </c>
-      <c r="B21" s="44">
-        <f>E16</f>
-        <v/>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ligne orange — limite patron typique</t>
-        </is>
+          <t>Vmax_A (Calcul_A)</t>
+        </is>
+      </c>
+      <c r="B21" s="20">
+        <f>Parametres!B36</f>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>V @ sommet table (m³)</t>
-        </is>
-      </c>
-      <c r="B22" s="44">
-        <f>E18</f>
+          <t>WSEmax_A (m)</t>
+        </is>
+      </c>
+      <c r="B22" s="42">
+        <f>Parametres!B39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Vmax_B (Calcul_B)</t>
+        </is>
+      </c>
+      <c r="B23" s="20">
+        <f>Parametres!B43</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Vmax_A / WSEmax_A (Parametres)</t>
-        </is>
-      </c>
-      <c r="B24" s="20">
-        <f>Parametres!B36</f>
-        <v/>
-      </c>
-      <c r="C24">
-        <f>Parametres!B39</f>
+          <t>WSEmax_B (m)</t>
+        </is>
+      </c>
+      <c r="B24" s="42">
+        <f>Parametres!B45</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Vmax_B / WSEmax_B (Parametres)</t>
+          <t>Vmax_C / WSEmax_C</t>
         </is>
       </c>
       <c r="B25" s="20">
-        <f>Parametres!B43</f>
+        <f>Parametres!B49</f>
         <v/>
       </c>
       <c r="C25">
-        <f>Parametres!B45</f>
-        <v/>
+        <f>Parametres!B51</f>
+        <v/>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Vmax_C inclut V_ditch — WSEmax_C = Parametres B51</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Vmax_C / WSEmax_C (Parametres)</t>
-        </is>
-      </c>
-      <c r="B26" s="20">
-        <f>Parametres!B49</f>
-        <v/>
-      </c>
-      <c r="C26">
-        <f>Parametres!B51</f>
-        <v/>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Vmax_C inclut V_ditch</t>
-        </is>
-      </c>
-    </row>
+          <t>V disponible à 37.28 m (m³)</t>
+        </is>
+      </c>
+      <c r="B26" s="43">
+        <f>E16</f>
+        <v/>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Si Vmax_A ou Vmax_B &gt; cette valeur → le niveau dépasse la limite patron</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Comment lire le résultat</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="39" t="inlineStr">
+        <is>
+          <t>Exemple: si Vmax_A &gt; V_cumul @ 37.28 (colonne E, ligne orange), alors WSEmax_A &gt; 37.28 m (la table monte vers 37.40 / 40.00 ou 'Hors table'). Jaune = surfaces du levé (éditables). Méthode C: Parametres B49–B52 et Calcul_C (fossé inclus). Note: A(37.40)=1516 &lt; A(37.28)=2198 — inhabituel; confirmer sur plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A2:G4"/>
+    <mergeCell ref="A29:F31"/>
     <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12355,332 +11092,129 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>Zone 2 — Stage–storage Ø900 → Ø1200 (aval)</t>
+      <c r="A1" s="44" t="inlineStr">
+        <is>
+          <t>Où sont les fichiers HY-8 / capacité ?</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>Jaune = WSE et Surface éditables (corriger depuis AutoCAD). ΔWSE, V_pas, V_cumul = formules live. Qin de cette zone = débit sortant du Ø900 (voir Calcul_Aval_A). Sortie contrôlée par Ø1200 (Q_plein ≈ 4.93 m³/s). Ne pas y mettre les surfaces de Zone 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4"/>
+      <c r="A2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ce classeur (rétention Ø900) :</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  engineering/drainage-design/retention_volume/Volume_Retention_Ponceau_900.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+    </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Formule d'un pas (aires moyennes)</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Courbe Q=f(H) FHWA pour CE Ø900 : feuille Courbe_QH_900 (ci-dessus).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="43" t="inlineStr">
-        <is>
-          <t>V_pas (m³) = (A_basse + A_haute) / 2 × (WSE_haute − WSE_basse)</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V_cumulatif = somme des V_pas depuis le fond de zone. Jaune = éditer (AutoCAD).</t>
+          <t>Ancien Excel « type HY-8 / inlet-outlet » (autre projet / Ste-Thérèse) :</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  engineering/drainage-design/Ponceau_Capacite_Inlet_Outlet.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>WSE / NSE (m) ← ÉDITER</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Surface A (m²) ← ÉDITER</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>ΔWSE (m)</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>V_pas (m³)</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>V_cumulatif (m³)</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Rôle</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Branche git: cursor/culvert-excel-capacity-model-d87f</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="n">
-        <v>34.88</v>
-      </c>
-      <c r="B11" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Fond Zone 2 (même grille WSE — éditer)</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="B12" s="17" t="n">
-        <v>60</v>
-      </c>
-      <c r="C12" s="32">
-        <f>A12-A11</f>
-        <v/>
-      </c>
-      <c r="D12" s="26">
-        <f>0.5*(B11+B12)*C12</f>
-        <v/>
-      </c>
-      <c r="E12" s="34">
-        <f>E11+D12</f>
-        <v/>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Levé Zone 2 — éditer si AutoCAD diffère</t>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Modèle composé ponceau Ø1050 + fossé (FHWA + remblai) — PAS le Ø900 de rétention :</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="n">
-        <v>36.01</v>
-      </c>
-      <c r="B13" s="17" t="n">
-        <v>219</v>
-      </c>
-      <c r="C13" s="32">
-        <f>A13-A12</f>
-        <v/>
-      </c>
-      <c r="D13" s="26">
-        <f>0.5*(B12+B13)*C13</f>
-        <v/>
-      </c>
-      <c r="E13" s="34">
-        <f>E12+D13</f>
-        <v/>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Levé Zone 2</t>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  engineering/drainage-design/ponceau_fosse_model/Ponceau_Fosse_Modele_Hydraulique.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="B14" s="17" t="n">
-        <v>150</v>
-      </c>
-      <c r="C14" s="32">
-        <f>A14-A13</f>
-        <v/>
-      </c>
-      <c r="D14" s="26">
-        <f>0.5*(B13+B14)*C14</f>
-        <v/>
-      </c>
-      <c r="E14" s="34">
-        <f>E13+D14</f>
-        <v/>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Levé Zone 2 (A↓ — vérifier plan)</t>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Branche git: cursor/ponceau-fosse-hydraulic-model-d87f</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="B15" s="17" t="n">
-        <v>340</v>
-      </c>
-      <c r="C15" s="32">
-        <f>A15-A14</f>
-        <v/>
-      </c>
-      <c r="D15" s="26">
-        <f>0.5*(B14+B15)*C15</f>
-        <v/>
-      </c>
-      <c r="E15" s="34">
-        <f>E14+D15</f>
-        <v/>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Levé Zone 2</t>
-        </is>
-      </c>
+      <c r="A15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="n">
-        <v>37.28</v>
-      </c>
-      <c r="B16" s="17" t="n">
-        <v>1700</v>
-      </c>
-      <c r="C16" s="39">
-        <f>A16-A15</f>
-        <v/>
-      </c>
-      <c r="D16" s="42">
-        <f>0.5*(B15+B16)*C16</f>
-        <v/>
-      </c>
-      <c r="E16" s="42">
-        <f>E15+D16</f>
-        <v/>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>Levé Zone 2 @ limite patron</t>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>HEC-RAS : pas de projet .ras/.hdf pour ce Ø900. Un DEM Ste-Thérèse est dans</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="B17" s="17" t="n">
-        <v>1460</v>
-      </c>
-      <c r="C17" s="32">
-        <f>A17-A16</f>
-        <v/>
-      </c>
-      <c r="D17" s="26">
-        <f>0.5*(B16+B17)*C17</f>
-        <v/>
-      </c>
-      <c r="E17" s="34">
-        <f>E16+D17</f>
-        <v/>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Levé Zone 2 (A↓ — vérifier plan)</t>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  engineering/hec-ras-data/ (données topo seulement).</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="B18" s="17" t="n">
-        <v>1632</v>
-      </c>
-      <c r="C18" s="32">
-        <f>A18-A17</f>
-        <v/>
-      </c>
-      <c r="D18" s="26">
-        <f>0.5*(B17+B18)*C18</f>
-        <v/>
-      </c>
-      <c r="E18" s="34">
-        <f>E17+D18</f>
-        <v/>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>Sommet table Zone 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>V @ 37.28 m (m³)</t>
-        </is>
-      </c>
-      <c r="B21" s="44">
-        <f>E16</f>
-        <v/>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ligne orange — limite patron typique</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>V @ sommet table (m³)</t>
-        </is>
-      </c>
-      <c r="B22" s="44">
-        <f>E18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Vmax_Aval_A / WSEmax (Parametres)</t>
-        </is>
-      </c>
-      <c r="B24" s="20">
-        <f>Parametres!B56</f>
-        <v/>
-      </c>
-      <c r="C24">
-        <f>Parametres!B57</f>
-        <v/>
+      <c r="A18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Donc: on n'avait pas perdu un HY-8 pour ce bassin Ø900 — on avait des outils</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>similaires pour d'autres sites. La courbe de CE classeur remplace ça pour le Ø900.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A2:G4"/>
-    <mergeCell ref="A7:F7"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/engineering/drainage-design/retention_volume/Volume_Retention_Ponceau_900.xlsx
+++ b/engineering/drainage-design/retention_volume/Volume_Retention_Ponceau_900.xlsx
@@ -1678,7 +1678,7 @@
         <v>0.008489634748272452</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>1.668</v>
+        <v>0.986</v>
       </c>
     </row>
     <row r="7">
@@ -1722,7 +1722,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Capacité Ø900 — Manning pleine section (n = 0,013)</t>
+          <t>Capacité Ø900 — Manning pleine section (TOG n = 0,022)</t>
         </is>
       </c>
     </row>
@@ -1733,11 +1733,11 @@
         </is>
       </c>
       <c r="B13" s="11" t="n">
-        <v>0.013</v>
+        <v>0.022</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fourni (béton typique ~0,012–0,015)</t>
+          <t>TOG (tuyau ondulé galvanisé) n=0,022 — pas béton</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>• Méthode A: Qout fixe = Q_plein Manning Ø900 (n=0,013).</t>
+          <t>• Méthode A: Qout fixe = Q_plein Manning Ø900 (TOG n=0,022).</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2420,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">   A) Q_plein Manning (n=0.013) ≈ 1.668 m³/s → Méthode A (constant).</t>
+          <t xml:space="preserve">   A) Q_plein Manning (TOG n=0.022) ≈ 0.986 m³/s → Méthode A (constant).</t>
         </is>
       </c>
     </row>
@@ -3466,11 +3466,11 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>0.013</v>
+        <v>0.022</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>béton typ. 0.012–0.015</t>
+          <t>TOG n=0,022 (ondulé galvanisé)</t>
         </is>
       </c>
       <c r="E6" s="34" t="inlineStr">
